--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart.sharepoint.com/sites/PVZuid/Shared Documents/Algemeen/WK2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1472" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC804CD-FC7E-426E-981B-232080740777}"/>
+  <xr:revisionPtr revIDLastSave="1489" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98975C70-C5DB-4804-AC8A-EE7ECCB594A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2316" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,8 +1348,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1358,11 +1361,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,76 +1676,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="12.54296875" customWidth="1"/>
-    <col min="22" max="22" width="8.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" customWidth="1"/>
-    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.54296875" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.54296875" customWidth="1"/>
-    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" customWidth="1"/>
-    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.54296875" customWidth="1"/>
-    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.54296875" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.54296875" customWidth="1"/>
-    <col min="45" max="45" width="15.7265625" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.54296875" customWidth="1"/>
-    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="21" width="12.5546875" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" customWidth="1"/>
+    <col min="23" max="23" width="12.5546875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="12.5546875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="12.5546875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.5546875" customWidth="1"/>
+    <col min="29" max="29" width="12.5546875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.5546875" customWidth="1"/>
+    <col min="31" max="31" width="12.5546875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" customWidth="1"/>
+    <col min="33" max="33" width="12.5546875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.5546875" customWidth="1"/>
+    <col min="35" max="35" width="12.5546875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.5546875" customWidth="1"/>
+    <col min="37" max="37" width="12.5546875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.5546875" customWidth="1"/>
+    <col min="39" max="39" width="12.5546875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.5546875" customWidth="1"/>
+    <col min="41" max="41" width="15.5546875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.5546875" customWidth="1"/>
+    <col min="43" max="43" width="15.5546875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.5546875" customWidth="1"/>
+    <col min="45" max="45" width="15.6640625" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.5546875" customWidth="1"/>
+    <col min="47" max="47" width="15.5546875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,11 +1837,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="42"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A2" s="43"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
       </c>
@@ -1981,61 +1981,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,181 +4649,183 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D25" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="11" t="str">
+      <c r="F25" s="11">
         <f>IF(OR($C25="",E25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E25,FIND("-",E25)-1),"")=AW25,IFERROR(--MID(E25,FIND("-",E25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))-(IFERROR(--MID(E25,FIND("-",E25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))-(IFERROR(--MID(E25,FIND("-",E25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(E25,FIND("-",E25)-1),""))=(AW25))+2*((IFERROR(--MID(E25,FIND("-",E25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H25" s="11" t="str">
+      <c r="H25" s="11">
         <f>IF(OR($C25="",G25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G25,FIND("-",G25)-1),"")=AW25,IFERROR(--MID(G25,FIND("-",G25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))-(IFERROR(--MID(G25,FIND("-",G25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))-(IFERROR(--MID(G25,FIND("-",G25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(G25,FIND("-",G25)-1),""))=(AW25))+2*((IFERROR(--MID(G25,FIND("-",G25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="11" t="str">
+      <c r="J25" s="11">
         <f>IF(OR($C25="",I25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I25,FIND("-",I25)-1),"")=AW25,IFERROR(--MID(I25,FIND("-",I25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))-(IFERROR(--MID(I25,FIND("-",I25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))-(IFERROR(--MID(I25,FIND("-",I25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(I25,FIND("-",I25)-1),""))=(AW25))+2*((IFERROR(--MID(I25,FIND("-",I25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L25" s="11" t="str">
+      <c r="L25" s="11">
         <f>IF(OR($C25="",K25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K25,FIND("-",K25)-1),"")=AW25,IFERROR(--MID(K25,FIND("-",K25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))-(IFERROR(--MID(K25,FIND("-",K25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))-(IFERROR(--MID(K25,FIND("-",K25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(K25,FIND("-",K25)-1),""))=(AW25))+2*((IFERROR(--MID(K25,FIND("-",K25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="N25" s="11" t="str">
+      <c r="N25" s="11">
         <f>IF(OR($C25="",M25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M25,FIND("-",M25)-1),"")=AW25,IFERROR(--MID(M25,FIND("-",M25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))-(IFERROR(--MID(M25,FIND("-",M25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))-(IFERROR(--MID(M25,FIND("-",M25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(M25,FIND("-",M25)-1),""))=(AW25))+2*((IFERROR(--MID(M25,FIND("-",M25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="P25" s="11" t="str">
+      <c r="P25" s="11">
         <f>IF(OR($C25="",O25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O25,FIND("-",O25)-1),"")=AW25,IFERROR(--MID(O25,FIND("-",O25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))-(IFERROR(--MID(O25,FIND("-",O25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))-(IFERROR(--MID(O25,FIND("-",O25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(O25,FIND("-",O25)-1),""))=(AW25))+2*((IFERROR(--MID(O25,FIND("-",O25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R25" s="11" t="str">
+      <c r="R25" s="11">
         <f>IF(OR($C25="",Q25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q25,FIND("-",Q25)-1),"")=AW25,IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))-(IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))-(IFERROR(--MID(Q25,FIND("-",Q25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(Q25,FIND("-",Q25)-1),""))=(AW25))+2*((IFERROR(--MID(Q25,FIND("-",Q25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T25" s="11" t="str">
+      <c r="T25" s="11">
         <f>IF(OR($C25="",S25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S25,FIND("-",S25)-1),"")=AW25,IFERROR(--MID(S25,FIND("-",S25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))-(IFERROR(--MID(S25,FIND("-",S25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))-(IFERROR(--MID(S25,FIND("-",S25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(S25,FIND("-",S25)-1),""))=(AW25))+2*((IFERROR(--MID(S25,FIND("-",S25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V25" s="11" t="str">
+      <c r="V25" s="11">
         <f>IF(OR($C25="",U25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U25,FIND("-",U25)-1),"")=AW25,IFERROR(--MID(U25,FIND("-",U25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))-(IFERROR(--MID(U25,FIND("-",U25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))-(IFERROR(--MID(U25,FIND("-",U25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(U25,FIND("-",U25)-1),""))=(AW25))+2*((IFERROR(--MID(U25,FIND("-",U25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X25" s="11" t="str">
+      <c r="X25" s="11">
         <f>IF(OR($C25="",W25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W25,FIND("-",W25)-1),"")=AW25,IFERROR(--MID(W25,FIND("-",W25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))-(IFERROR(--MID(W25,FIND("-",W25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))-(IFERROR(--MID(W25,FIND("-",W25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(W25,FIND("-",W25)-1),""))=(AW25))+2*((IFERROR(--MID(W25,FIND("-",W25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z25" s="11" t="str">
+      <c r="Z25" s="11">
         <f>IF(OR($C25="",Y25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y25,FIND("-",Y25)-1),"")=AW25,IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))-(IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))-(IFERROR(--MID(Y25,FIND("-",Y25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(Y25,FIND("-",Y25)-1),""))=(AW25))+2*((IFERROR(--MID(Y25,FIND("-",Y25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AB25" s="11" t="str">
+      <c r="AB25" s="11">
         <f>IF(OR($C25="",AA25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA25,FIND("-",AA25)-1),"")=AW25,IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))-(IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))-(IFERROR(--MID(AA25,FIND("-",AA25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AA25,FIND("-",AA25)-1),""))=(AW25))+2*((IFERROR(--MID(AA25,FIND("-",AA25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AD25" s="11" t="str">
+      <c r="AD25" s="11">
         <f>IF(OR($C25="",AC25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC25,FIND("-",AC25)-1),"")=AW25,IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))-(IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))-(IFERROR(--MID(AC25,FIND("-",AC25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AC25,FIND("-",AC25)-1),""))=(AW25))+2*((IFERROR(--MID(AC25,FIND("-",AC25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF25" s="11" t="str">
+      <c r="AF25" s="11">
         <f>IF(OR($C25="",AE25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE25,FIND("-",AE25)-1),"")=AW25,IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))-(IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))-(IFERROR(--MID(AE25,FIND("-",AE25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AE25,FIND("-",AE25)-1),""))=(AW25))+2*((IFERROR(--MID(AE25,FIND("-",AE25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH25" s="11" t="str">
+      <c r="AH25" s="11">
         <f>IF(OR($C25="",AG25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG25,FIND("-",AG25)-1),"")=AW25,IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))-(IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))-(IFERROR(--MID(AG25,FIND("-",AG25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AG25,FIND("-",AG25)-1),""))=(AW25))+2*((IFERROR(--MID(AG25,FIND("-",AG25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AJ25" s="11" t="str">
+      <c r="AJ25" s="11">
         <f>IF(OR($C25="",AI25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI25,FIND("-",AI25)-1),"")=AW25,IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))-(IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))-(IFERROR(--MID(AI25,FIND("-",AI25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AI25,FIND("-",AI25)-1),""))=(AW25))+2*((IFERROR(--MID(AI25,FIND("-",AI25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AL25" s="11" t="str">
+      <c r="AL25" s="11">
         <f>IF(OR($C25="",AK25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK25,FIND("-",AK25)-1),"")=AW25,IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))-(IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))-(IFERROR(--MID(AK25,FIND("-",AK25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AK25,FIND("-",AK25)-1),""))=(AW25))+2*((IFERROR(--MID(AK25,FIND("-",AK25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AN25" s="11" t="str">
+      <c r="AN25" s="11">
         <f>IF(OR($C25="",AM25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM25,FIND("-",AM25)-1),"")=AW25,IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))-(IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))-(IFERROR(--MID(AM25,FIND("-",AM25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AM25,FIND("-",AM25)-1),""))=(AW25))+2*((IFERROR(--MID(AM25,FIND("-",AM25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP25" s="11" t="str">
+      <c r="AP25" s="11">
         <f>IF(OR($C25="",AO25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO25,FIND("-",AO25)-1),"")=AW25,IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))-(IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))-(IFERROR(--MID(AO25,FIND("-",AO25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AO25,FIND("-",AO25)-1),""))=(AW25))+2*((IFERROR(--MID(AO25,FIND("-",AO25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AR25" s="11" t="str">
+      <c r="AR25" s="11">
         <f>IF(OR($C25="",AQ25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),"")=AW25,IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))-(IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))-(IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AQ25,FIND("-",AQ25)-1),""))=(AW25))+2*((IFERROR(--MID(AQ25,FIND("-",AQ25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS25" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AT25" s="11" t="str">
+      <c r="AT25" s="11">
         <f>IF(OR($C25="",AS25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS25,FIND("-",AS25)-1),"")=AW25,IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))-(IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))-(IFERROR(--MID(AS25,FIND("-",AS25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AS25,FIND("-",AS25)-1),""))=(AW25))+2*((IFERROR(--MID(AS25,FIND("-",AS25)+1,99),""))=(AX25))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU25" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV25" s="11" t="str">
+      <c r="AV25" s="11">
         <f>IF(OR($C25="",AU25=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU25,FIND("-",AU25)-1),"")=AW25,IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")=AX25),10,5*(SIGN((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))-(IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")))=SIGN((AW25)-(AX25)))+2*(((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))-(IFERROR(--MID(AU25,FIND("-",AU25)+1,99),"")))=((AW25)-(AX25)))+2*((IFERROR(--LEFT(AU25,FIND("-",AU25)-1),""))=(AW25))+2*((IFERROR(--MID(AU25,FIND("-",AU25)+1,99),""))=(AX25))),""))</f>
-        <v/>
-      </c>
-      <c r="AW25" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW25" s="11">
         <f>IF($C25="","",IFERROR(--LEFT($C25,FIND("-",$C25)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX25" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX25" s="11">
         <f>IF($C25="","",IFERROR(--MID($C25,FIND("-",$C25)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -4997,7 +4999,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5055,7 +5057,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5109,7 +5111,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5283,7 +5285,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5457,7 +5459,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5631,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5689,7 +5691,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5743,7 +5745,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5917,7 +5919,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6091,7 +6093,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6265,7 +6267,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6439,7 +6441,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6613,7 +6615,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6671,7 +6673,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6725,7 +6727,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6899,7 +6901,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7073,7 +7075,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7247,7 +7249,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7421,7 +7423,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7479,7 +7481,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7533,7 +7535,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7707,7 +7709,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7881,7 +7883,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8055,7 +8057,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8113,7 +8115,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8167,7 +8169,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8341,7 +8343,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8515,7 +8517,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8689,7 +8691,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8863,7 +8865,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9037,7 +9039,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9095,7 +9097,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9149,7 +9151,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9323,7 +9325,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9497,7 +9499,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9671,7 +9673,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9845,7 +9847,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9903,7 +9905,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9957,7 +9959,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10131,7 +10133,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10305,7 +10307,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10479,7 +10481,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10653,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10711,7 +10713,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10765,7 +10767,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10939,7 +10941,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11113,7 +11115,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11287,7 +11289,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11461,7 +11463,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11519,7 +11521,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11573,7 +11575,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11747,7 +11749,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11921,7 +11923,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12095,7 +12097,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12269,7 +12271,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12327,7 +12329,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12381,7 +12383,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12555,7 +12557,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12729,7 +12731,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12903,7 +12905,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13077,7 +13079,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13251,7 +13253,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13425,7 +13427,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13483,7 +13485,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13537,7 +13539,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13711,7 +13713,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13885,7 +13887,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14059,7 +14061,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14233,7 +14235,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14407,7 +14409,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14581,7 +14583,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14639,7 +14641,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14693,7 +14695,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14867,7 +14869,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15041,7 +15043,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15215,7 +15217,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15389,7 +15391,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15563,7 +15565,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15737,7 +15739,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15795,7 +15797,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15849,7 +15851,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16023,7 +16025,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16197,7 +16199,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16371,7 +16373,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16545,7 +16547,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16603,7 +16605,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16661,7 +16663,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16715,7 +16717,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16769,7 +16771,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16899,7 +16901,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16957,7 +16959,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17011,7 +17013,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17141,7 +17143,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17271,7 +17273,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17329,7 +17331,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17383,7 +17385,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17513,7 +17515,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17643,7 +17645,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17773,7 +17775,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17831,7 +17833,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17885,7 +17887,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18015,7 +18017,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18145,7 +18147,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18275,7 +18277,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18333,7 +18335,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18387,7 +18389,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18517,7 +18519,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18647,7 +18649,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18705,7 +18707,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18759,7 +18761,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18889,7 +18891,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19019,7 +19021,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19149,7 +19151,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19207,7 +19209,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19261,7 +19263,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19391,7 +19393,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19521,7 +19523,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19579,7 +19581,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19637,7 +19639,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19691,7 +19693,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19745,7 +19747,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19875,7 +19877,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20005,7 +20007,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20063,7 +20065,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20117,7 +20119,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20247,7 +20249,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20305,7 +20307,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20359,7 +20361,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20489,7 +20491,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20619,7 +20621,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20677,7 +20679,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20731,7 +20733,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20861,7 +20863,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -20991,7 +20993,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21121,7 +21123,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21179,7 +21181,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21237,7 +21239,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21291,7 +21293,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21345,7 +21347,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21475,7 +21477,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21533,7 +21535,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21587,7 +21589,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21717,7 +21719,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21775,7 +21777,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21829,7 +21831,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21959,7 +21961,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22017,7 +22019,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22071,7 +22073,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22201,7 +22203,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22259,7 +22261,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22317,7 +22319,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22371,7 +22373,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22425,7 +22427,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22555,7 +22557,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22613,7 +22615,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22667,7 +22669,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22797,7 +22799,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22855,7 +22857,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22913,7 +22915,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22967,7 +22969,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23021,7 +23023,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23151,7 +23153,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23209,7 +23211,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23267,7 +23269,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23321,7 +23323,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23375,7 +23377,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23505,7 +23507,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23563,7 +23565,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23623,6 +23625,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23639,60 +23695,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23702,58 +23704,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.26953125" customWidth="1"/>
+    <col min="2" max="2" width="75.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.54296875" customWidth="1"/>
-    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.54296875" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.54296875" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.54296875" customWidth="1"/>
-    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.54296875" customWidth="1"/>
-    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
-    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.54296875" customWidth="1"/>
-    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.54296875" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.54296875" customWidth="1"/>
-    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.54296875" customWidth="1"/>
-    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.54296875" customWidth="1"/>
-    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.54296875" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" customWidth="1"/>
-    <col min="43" max="43" width="10.54296875" customWidth="1"/>
-    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.54296875" customWidth="1"/>
-    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" customWidth="1"/>
+    <col min="22" max="22" width="12.5546875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" customWidth="1"/>
+    <col min="24" max="24" width="12.5546875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" customWidth="1"/>
+    <col min="26" max="26" width="12.5546875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" customWidth="1"/>
+    <col min="28" max="28" width="12.5546875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" customWidth="1"/>
+    <col min="30" max="30" width="12.5546875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.5546875" customWidth="1"/>
+    <col min="32" max="32" width="12.5546875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.5546875" customWidth="1"/>
+    <col min="34" max="34" width="12.5546875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.5546875" customWidth="1"/>
+    <col min="36" max="36" width="12.5546875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.5546875" customWidth="1"/>
+    <col min="38" max="38" width="12.5546875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.5546875" customWidth="1"/>
+    <col min="40" max="40" width="12.5546875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.5546875" customWidth="1"/>
+    <col min="42" max="42" width="12.5546875" customWidth="1"/>
+    <col min="43" max="43" width="10.5546875" customWidth="1"/>
+    <col min="44" max="44" width="12.5546875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.5546875" customWidth="1"/>
+    <col min="46" max="46" width="12.5546875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23859,14 +23861,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24007,7 +24009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24170,7 +24172,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24333,7 +24335,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24496,7 +24498,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24659,7 +24661,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24822,7 +24824,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -24985,7 +24987,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25148,7 +25150,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25311,7 +25313,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25474,7 +25476,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25637,7 +25639,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25800,7 +25802,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25963,7 +25965,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26126,7 +26128,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26289,7 +26291,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26408,6 +26410,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26419,17 +26432,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26441,16 +26443,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7265625" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26459,7 +26461,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26476,7 +26478,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
@@ -26498,7 +26500,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
@@ -26509,7 +26511,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26517,54 +26519,54 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>53</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>53</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
         <v>5</v>
@@ -26575,7 +26577,7 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26583,10 +26585,10 @@
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
@@ -26597,7 +26599,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!Y17</f>
@@ -26605,54 +26607,54 @@
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>49</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>49</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
         <v>9</v>
@@ -26663,7 +26665,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AK17</f>
@@ -26671,10 +26673,10 @@
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
         <v>9</v>
@@ -26685,7 +26687,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!G17</f>
@@ -26693,10 +26695,10 @@
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
@@ -26707,7 +26709,7 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26715,10 +26717,10 @@
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
         <v>11</v>
@@ -26729,7 +26731,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!E17</f>
@@ -26737,46 +26739,46 @@
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>43</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>45</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
         <v>43</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
@@ -26784,73 +26786,73 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>41</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>43</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>40</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>42</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
         <v>16</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>40</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>42</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
@@ -26861,7 +26863,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26869,46 +26871,46 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>38</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>40</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
         <v>38</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
@@ -26916,29 +26918,29 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>36</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>38</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
@@ -26949,7 +26951,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26957,7 +26959,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -26966,6 +26968,10 @@
       <sortCondition descending="1" ref="E2:E22"/>
     </sortState>
   </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E24">
+    <sortCondition descending="1" ref="E3:E24"/>
+    <sortCondition ref="B3:B24"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26973,20 +26979,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" hidden="1"/>
+    <col min="3" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -26994,7 +27000,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27002,7 +27008,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27010,7 +27016,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27018,7 +27024,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27026,7 +27032,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27034,7 +27040,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27042,7 +27048,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27058,16 +27064,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.7265625" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="1" max="1" width="55.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7265625" hidden="1"/>
+    <col min="45" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27115,7 +27121,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27126,7 +27132,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27137,7 +27143,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27148,7 +27154,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27159,7 +27165,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27170,7 +27176,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27181,7 +27187,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27198,14 +27204,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27216,7 +27222,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27227,7 +27233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27235,7 +27241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27243,7 +27249,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27251,7 +27257,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27259,62 +27265,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -27520,15 +27526,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
@@ -27537,6 +27534,15 @@
     <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27559,14 +27565,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -27581,4 +27579,12 @@
     <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1489" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98975C70-C5DB-4804-AC8A-EE7ECCB594A0}"/>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,22 +1730,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,9 +1838,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1985,53 +1985,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -23625,6 +23625,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23641,60 +23695,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23861,12 +23861,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
@@ -26410,6 +26410,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26421,17 +26432,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26480,7 +26480,7 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26496,13 +26496,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26518,13 +26518,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -26540,13 +26540,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -26562,13 +26562,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
+        <f t="shared" si="1"/>
         <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -26584,13 +26584,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
+        <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
@@ -26606,13 +26606,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
+        <f t="shared" si="1"/>
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
@@ -26628,13 +26628,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
@@ -26650,13 +26650,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
+        <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
@@ -26672,13 +26672,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
@@ -26694,13 +26694,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
@@ -26716,13 +26716,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
@@ -26738,13 +26738,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
@@ -26760,13 +26760,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
+        <f t="shared" si="1"/>
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
@@ -26782,13 +26782,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
@@ -26804,13 +26804,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
+        <f t="shared" si="1"/>
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
@@ -26826,13 +26826,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B19" s="1" t="str">
@@ -26848,13 +26848,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
@@ -26870,13 +26870,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
@@ -26892,13 +26892,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
+        <f t="shared" si="1"/>
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
@@ -26914,13 +26914,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
@@ -26936,13 +26936,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
+        <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26958,7 +26958,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
@@ -27331,6 +27331,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27525,41 +27545,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27582,9 +27571,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1489" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98975C70-C5DB-4804-AC8A-EE7ECCB594A0}"/>
+  <xr:revisionPtr revIDLastSave="1495" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5DB20F-E482-49C6-AEDF-0B3746481E0D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <sheet name="Prijzenpot" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Stand!$E$2:$E$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Stand!$E$2:$E$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2317" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -4832,171 +4832,173 @@
       <c r="B26" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D26" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="11" t="str">
+      <c r="F26" s="11">
         <f>IF(OR($C26="",E26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E26,FIND("-",E26)-1),"")=AW26,IFERROR(--MID(E26,FIND("-",E26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))-(IFERROR(--MID(E26,FIND("-",E26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))-(IFERROR(--MID(E26,FIND("-",E26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(E26,FIND("-",E26)-1),""))=(AW26))+2*((IFERROR(--MID(E26,FIND("-",E26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="11" t="str">
+      <c r="H26" s="11">
         <f>IF(OR($C26="",G26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G26,FIND("-",G26)-1),"")=AW26,IFERROR(--MID(G26,FIND("-",G26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))-(IFERROR(--MID(G26,FIND("-",G26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))-(IFERROR(--MID(G26,FIND("-",G26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(G26,FIND("-",G26)-1),""))=(AW26))+2*((IFERROR(--MID(G26,FIND("-",G26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J26" s="11" t="str">
+      <c r="J26" s="11">
         <f>IF(OR($C26="",I26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I26,FIND("-",I26)-1),"")=AW26,IFERROR(--MID(I26,FIND("-",I26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))-(IFERROR(--MID(I26,FIND("-",I26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))-(IFERROR(--MID(I26,FIND("-",I26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(I26,FIND("-",I26)-1),""))=(AW26))+2*((IFERROR(--MID(I26,FIND("-",I26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L26" s="11" t="str">
+      <c r="L26" s="11">
         <f>IF(OR($C26="",K26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K26,FIND("-",K26)-1),"")=AW26,IFERROR(--MID(K26,FIND("-",K26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))-(IFERROR(--MID(K26,FIND("-",K26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))-(IFERROR(--MID(K26,FIND("-",K26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(K26,FIND("-",K26)-1),""))=(AW26))+2*((IFERROR(--MID(K26,FIND("-",K26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N26" s="11" t="str">
+      <c r="N26" s="11">
         <f>IF(OR($C26="",M26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M26,FIND("-",M26)-1),"")=AW26,IFERROR(--MID(M26,FIND("-",M26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))-(IFERROR(--MID(M26,FIND("-",M26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))-(IFERROR(--MID(M26,FIND("-",M26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(M26,FIND("-",M26)-1),""))=(AW26))+2*((IFERROR(--MID(M26,FIND("-",M26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P26" s="11" t="str">
+      <c r="P26" s="11">
         <f>IF(OR($C26="",O26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O26,FIND("-",O26)-1),"")=AW26,IFERROR(--MID(O26,FIND("-",O26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))-(IFERROR(--MID(O26,FIND("-",O26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))-(IFERROR(--MID(O26,FIND("-",O26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(O26,FIND("-",O26)-1),""))=(AW26))+2*((IFERROR(--MID(O26,FIND("-",O26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R26" s="11" t="str">
+      <c r="R26" s="11">
         <f>IF(OR($C26="",Q26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q26,FIND("-",Q26)-1),"")=AW26,IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))-(IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))-(IFERROR(--MID(Q26,FIND("-",Q26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(Q26,FIND("-",Q26)-1),""))=(AW26))+2*((IFERROR(--MID(Q26,FIND("-",Q26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S26" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T26" s="11" t="str">
+      <c r="T26" s="11">
         <f>IF(OR($C26="",S26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S26,FIND("-",S26)-1),"")=AW26,IFERROR(--MID(S26,FIND("-",S26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))-(IFERROR(--MID(S26,FIND("-",S26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))-(IFERROR(--MID(S26,FIND("-",S26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(S26,FIND("-",S26)-1),""))=(AW26))+2*((IFERROR(--MID(S26,FIND("-",S26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V26" s="11" t="str">
+      <c r="V26" s="11">
         <f>IF(OR($C26="",U26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U26,FIND("-",U26)-1),"")=AW26,IFERROR(--MID(U26,FIND("-",U26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))-(IFERROR(--MID(U26,FIND("-",U26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))-(IFERROR(--MID(U26,FIND("-",U26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(U26,FIND("-",U26)-1),""))=(AW26))+2*((IFERROR(--MID(U26,FIND("-",U26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X26" s="11" t="str">
+      <c r="X26" s="11">
         <f>IF(OR($C26="",W26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W26,FIND("-",W26)-1),"")=AW26,IFERROR(--MID(W26,FIND("-",W26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))-(IFERROR(--MID(W26,FIND("-",W26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))-(IFERROR(--MID(W26,FIND("-",W26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(W26,FIND("-",W26)-1),""))=(AW26))+2*((IFERROR(--MID(W26,FIND("-",W26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z26" s="11" t="str">
+      <c r="Z26" s="11">
         <f>IF(OR($C26="",Y26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y26,FIND("-",Y26)-1),"")=AW26,IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))-(IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))-(IFERROR(--MID(Y26,FIND("-",Y26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(Y26,FIND("-",Y26)-1),""))=(AW26))+2*((IFERROR(--MID(Y26,FIND("-",Y26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA26" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB26" s="11" t="str">
+      <c r="AB26" s="11">
         <f>IF(OR($C26="",AA26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA26,FIND("-",AA26)-1),"")=AW26,IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))-(IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))-(IFERROR(--MID(AA26,FIND("-",AA26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AA26,FIND("-",AA26)-1),""))=(AW26))+2*((IFERROR(--MID(AA26,FIND("-",AA26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD26" s="11" t="str">
+      <c r="AD26" s="11">
         <f>IF(OR($C26="",AC26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC26,FIND("-",AC26)-1),"")=AW26,IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))-(IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))-(IFERROR(--MID(AC26,FIND("-",AC26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AC26,FIND("-",AC26)-1),""))=(AW26))+2*((IFERROR(--MID(AC26,FIND("-",AC26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF26" s="11" t="str">
+      <c r="AF26" s="11">
         <f>IF(OR($C26="",AE26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE26,FIND("-",AE26)-1),"")=AW26,IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))-(IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))-(IFERROR(--MID(AE26,FIND("-",AE26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AE26,FIND("-",AE26)-1),""))=(AW26))+2*((IFERROR(--MID(AE26,FIND("-",AE26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH26" s="11" t="str">
+      <c r="AH26" s="11">
         <f>IF(OR($C26="",AG26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG26,FIND("-",AG26)-1),"")=AW26,IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))-(IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))-(IFERROR(--MID(AG26,FIND("-",AG26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AG26,FIND("-",AG26)-1),""))=(AW26))+2*((IFERROR(--MID(AG26,FIND("-",AG26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI26" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ26" s="11" t="str">
+      <c r="AJ26" s="11">
         <f>IF(OR($C26="",AI26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI26,FIND("-",AI26)-1),"")=AW26,IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))-(IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))-(IFERROR(--MID(AI26,FIND("-",AI26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AI26,FIND("-",AI26)-1),""))=(AW26))+2*((IFERROR(--MID(AI26,FIND("-",AI26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK26" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL26" s="11" t="str">
+      <c r="AL26" s="11">
         <f>IF(OR($C26="",AK26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK26,FIND("-",AK26)-1),"")=AW26,IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))-(IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))-(IFERROR(--MID(AK26,FIND("-",AK26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AK26,FIND("-",AK26)-1),""))=(AW26))+2*((IFERROR(--MID(AK26,FIND("-",AK26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM26" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN26" s="11" t="str">
+      <c r="AN26" s="11">
         <f>IF(OR($C26="",AM26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM26,FIND("-",AM26)-1),"")=AW26,IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))-(IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))-(IFERROR(--MID(AM26,FIND("-",AM26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AM26,FIND("-",AM26)-1),""))=(AW26))+2*((IFERROR(--MID(AM26,FIND("-",AM26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP26" s="11" t="str">
+      <c r="AP26" s="11">
         <f>IF(OR($C26="",AO26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO26,FIND("-",AO26)-1),"")=AW26,IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))-(IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))-(IFERROR(--MID(AO26,FIND("-",AO26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AO26,FIND("-",AO26)-1),""))=(AW26))+2*((IFERROR(--MID(AO26,FIND("-",AO26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ26" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR26" s="11" t="str">
+      <c r="AR26" s="11">
         <f>IF(OR($C26="",AQ26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),"")=AW26,IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))-(IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))-(IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AQ26,FIND("-",AQ26)-1),""))=(AW26))+2*((IFERROR(--MID(AQ26,FIND("-",AQ26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS26" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT26" s="11" t="str">
+      <c r="AT26" s="11">
         <f>IF(OR($C26="",AS26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS26,FIND("-",AS26)-1),"")=AW26,IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))-(IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))-(IFERROR(--MID(AS26,FIND("-",AS26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AS26,FIND("-",AS26)-1),""))=(AW26))+2*((IFERROR(--MID(AS26,FIND("-",AS26)+1,99),""))=(AX26))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU26" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV26" s="11" t="str">
+      <c r="AV26" s="11">
         <f>IF(OR($C26="",AU26=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU26,FIND("-",AU26)-1),"")=AW26,IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")=AX26),10,5*(SIGN((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))-(IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")))=SIGN((AW26)-(AX26)))+2*(((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))-(IFERROR(--MID(AU26,FIND("-",AU26)+1,99),"")))=((AW26)-(AX26)))+2*((IFERROR(--LEFT(AU26,FIND("-",AU26)-1),""))=(AW26))+2*((IFERROR(--MID(AU26,FIND("-",AU26)+1,99),""))=(AX26))),""))</f>
-        <v/>
-      </c>
-      <c r="AW26" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW26" s="11">
         <f>IF($C26="","",IFERROR(--LEFT($C26,FIND("-",$C26)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX26" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX26" s="11">
         <f>IF($C26="","",IFERROR(--MID($C26,FIND("-",$C26)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5118,171 +5120,173 @@
       <c r="B29" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D29" s="1" t="s">
         <v>86</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="11" t="str">
+      <c r="F29" s="11">
         <f>IF(OR($C29="",E29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E29,FIND("-",E29)-1),"")=AW29,IFERROR(--MID(E29,FIND("-",E29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))-(IFERROR(--MID(E29,FIND("-",E29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))-(IFERROR(--MID(E29,FIND("-",E29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(E29,FIND("-",E29)-1),""))=(AW29))+2*((IFERROR(--MID(E29,FIND("-",E29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H29" s="11" t="str">
+      <c r="H29" s="11">
         <f>IF(OR($C29="",G29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G29,FIND("-",G29)-1),"")=AW29,IFERROR(--MID(G29,FIND("-",G29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))-(IFERROR(--MID(G29,FIND("-",G29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))-(IFERROR(--MID(G29,FIND("-",G29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(G29,FIND("-",G29)-1),""))=(AW29))+2*((IFERROR(--MID(G29,FIND("-",G29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J29" s="11" t="str">
+      <c r="J29" s="11">
         <f>IF(OR($C29="",I29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I29,FIND("-",I29)-1),"")=AW29,IFERROR(--MID(I29,FIND("-",I29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))-(IFERROR(--MID(I29,FIND("-",I29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))-(IFERROR(--MID(I29,FIND("-",I29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(I29,FIND("-",I29)-1),""))=(AW29))+2*((IFERROR(--MID(I29,FIND("-",I29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L29" s="11" t="str">
+      <c r="L29" s="11">
         <f>IF(OR($C29="",K29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K29,FIND("-",K29)-1),"")=AW29,IFERROR(--MID(K29,FIND("-",K29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))-(IFERROR(--MID(K29,FIND("-",K29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))-(IFERROR(--MID(K29,FIND("-",K29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(K29,FIND("-",K29)-1),""))=(AW29))+2*((IFERROR(--MID(K29,FIND("-",K29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N29" s="11" t="str">
+      <c r="N29" s="11">
         <f>IF(OR($C29="",M29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M29,FIND("-",M29)-1),"")=AW29,IFERROR(--MID(M29,FIND("-",M29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))-(IFERROR(--MID(M29,FIND("-",M29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))-(IFERROR(--MID(M29,FIND("-",M29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(M29,FIND("-",M29)-1),""))=(AW29))+2*((IFERROR(--MID(M29,FIND("-",M29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="P29" s="11" t="str">
+      <c r="P29" s="11">
         <f>IF(OR($C29="",O29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O29,FIND("-",O29)-1),"")=AW29,IFERROR(--MID(O29,FIND("-",O29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))-(IFERROR(--MID(O29,FIND("-",O29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))-(IFERROR(--MID(O29,FIND("-",O29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(O29,FIND("-",O29)-1),""))=(AW29))+2*((IFERROR(--MID(O29,FIND("-",O29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q29" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="R29" s="11" t="str">
+      <c r="R29" s="11">
         <f>IF(OR($C29="",Q29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q29,FIND("-",Q29)-1),"")=AW29,IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))-(IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))-(IFERROR(--MID(Q29,FIND("-",Q29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(Q29,FIND("-",Q29)-1),""))=(AW29))+2*((IFERROR(--MID(Q29,FIND("-",Q29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S29" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T29" s="11" t="str">
+      <c r="T29" s="11">
         <f>IF(OR($C29="",S29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S29,FIND("-",S29)-1),"")=AW29,IFERROR(--MID(S29,FIND("-",S29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))-(IFERROR(--MID(S29,FIND("-",S29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))-(IFERROR(--MID(S29,FIND("-",S29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(S29,FIND("-",S29)-1),""))=(AW29))+2*((IFERROR(--MID(S29,FIND("-",S29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V29" s="11" t="str">
+      <c r="V29" s="11">
         <f>IF(OR($C29="",U29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U29,FIND("-",U29)-1),"")=AW29,IFERROR(--MID(U29,FIND("-",U29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))-(IFERROR(--MID(U29,FIND("-",U29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))-(IFERROR(--MID(U29,FIND("-",U29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(U29,FIND("-",U29)-1),""))=(AW29))+2*((IFERROR(--MID(U29,FIND("-",U29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X29" s="11" t="str">
+      <c r="X29" s="11">
         <f>IF(OR($C29="",W29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W29,FIND("-",W29)-1),"")=AW29,IFERROR(--MID(W29,FIND("-",W29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))-(IFERROR(--MID(W29,FIND("-",W29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))-(IFERROR(--MID(W29,FIND("-",W29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(W29,FIND("-",W29)-1),""))=(AW29))+2*((IFERROR(--MID(W29,FIND("-",W29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z29" s="11" t="str">
+      <c r="Z29" s="11">
         <f>IF(OR($C29="",Y29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y29,FIND("-",Y29)-1),"")=AW29,IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))-(IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))-(IFERROR(--MID(Y29,FIND("-",Y29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(Y29,FIND("-",Y29)-1),""))=(AW29))+2*((IFERROR(--MID(Y29,FIND("-",Y29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB29" s="11" t="str">
+      <c r="AB29" s="11">
         <f>IF(OR($C29="",AA29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA29,FIND("-",AA29)-1),"")=AW29,IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))-(IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))-(IFERROR(--MID(AA29,FIND("-",AA29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AA29,FIND("-",AA29)-1),""))=(AW29))+2*((IFERROR(--MID(AA29,FIND("-",AA29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AD29" s="11" t="str">
+      <c r="AD29" s="11">
         <f>IF(OR($C29="",AC29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC29,FIND("-",AC29)-1),"")=AW29,IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))-(IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))-(IFERROR(--MID(AC29,FIND("-",AC29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AC29,FIND("-",AC29)-1),""))=(AW29))+2*((IFERROR(--MID(AC29,FIND("-",AC29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF29" s="11" t="str">
+      <c r="AF29" s="11">
         <f>IF(OR($C29="",AE29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE29,FIND("-",AE29)-1),"")=AW29,IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))-(IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))-(IFERROR(--MID(AE29,FIND("-",AE29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AE29,FIND("-",AE29)-1),""))=(AW29))+2*((IFERROR(--MID(AE29,FIND("-",AE29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH29" s="11" t="str">
+      <c r="AH29" s="11">
         <f>IF(OR($C29="",AG29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG29,FIND("-",AG29)-1),"")=AW29,IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))-(IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))-(IFERROR(--MID(AG29,FIND("-",AG29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AG29,FIND("-",AG29)-1),""))=(AW29))+2*((IFERROR(--MID(AG29,FIND("-",AG29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ29" s="11" t="str">
+      <c r="AJ29" s="11">
         <f>IF(OR($C29="",AI29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI29,FIND("-",AI29)-1),"")=AW29,IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))-(IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))-(IFERROR(--MID(AI29,FIND("-",AI29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AI29,FIND("-",AI29)-1),""))=(AW29))+2*((IFERROR(--MID(AI29,FIND("-",AI29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL29" s="11" t="str">
+      <c r="AL29" s="11">
         <f>IF(OR($C29="",AK29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK29,FIND("-",AK29)-1),"")=AW29,IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))-(IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))-(IFERROR(--MID(AK29,FIND("-",AK29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AK29,FIND("-",AK29)-1),""))=(AW29))+2*((IFERROR(--MID(AK29,FIND("-",AK29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN29" s="11" t="str">
+      <c r="AN29" s="11">
         <f>IF(OR($C29="",AM29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM29,FIND("-",AM29)-1),"")=AW29,IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))-(IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))-(IFERROR(--MID(AM29,FIND("-",AM29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AM29,FIND("-",AM29)-1),""))=(AW29))+2*((IFERROR(--MID(AM29,FIND("-",AM29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO29" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AP29" s="11" t="str">
+      <c r="AP29" s="11">
         <f>IF(OR($C29="",AO29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO29,FIND("-",AO29)-1),"")=AW29,IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))-(IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))-(IFERROR(--MID(AO29,FIND("-",AO29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AO29,FIND("-",AO29)-1),""))=(AW29))+2*((IFERROR(--MID(AO29,FIND("-",AO29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR29" s="11" t="str">
+      <c r="AR29" s="11">
         <f>IF(OR($C29="",AQ29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),"")=AW29,IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))-(IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))-(IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AQ29,FIND("-",AQ29)-1),""))=(AW29))+2*((IFERROR(--MID(AQ29,FIND("-",AQ29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS29" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AT29" s="11" t="str">
+      <c r="AT29" s="11">
         <f>IF(OR($C29="",AS29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS29,FIND("-",AS29)-1),"")=AW29,IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))-(IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))-(IFERROR(--MID(AS29,FIND("-",AS29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AS29,FIND("-",AS29)-1),""))=(AW29))+2*((IFERROR(--MID(AS29,FIND("-",AS29)+1,99),""))=(AX29))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="AV29" s="11" t="str">
+      <c r="AV29" s="11">
         <f>IF(OR($C29="",AU29=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU29,FIND("-",AU29)-1),"")=AW29,IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")=AX29),10,5*(SIGN((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))-(IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")))=SIGN((AW29)-(AX29)))+2*(((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))-(IFERROR(--MID(AU29,FIND("-",AU29)+1,99),"")))=((AW29)-(AX29)))+2*((IFERROR(--LEFT(AU29,FIND("-",AU29)-1),""))=(AW29))+2*((IFERROR(--MID(AU29,FIND("-",AU29)+1,99),""))=(AX29))),""))</f>
-        <v/>
-      </c>
-      <c r="AW29" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="11">
         <f>IF($C29="","",IFERROR(--LEFT($C29,FIND("-",$C29)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX29" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX29" s="11">
         <f>IF($C29="","",IFERROR(--MID($C29,FIND("-",$C29)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -5292,171 +5296,173 @@
       <c r="B30" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="D30" s="1" t="s">
         <v>88</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F30" s="11" t="str">
+      <c r="F30" s="11">
         <f>IF(OR($C30="",E30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E30,FIND("-",E30)-1),"")=AW30,IFERROR(--MID(E30,FIND("-",E30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))-(IFERROR(--MID(E30,FIND("-",E30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))-(IFERROR(--MID(E30,FIND("-",E30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(E30,FIND("-",E30)-1),""))=(AW30))+2*((IFERROR(--MID(E30,FIND("-",E30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="11" t="str">
+      <c r="H30" s="11">
         <f>IF(OR($C30="",G30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G30,FIND("-",G30)-1),"")=AW30,IFERROR(--MID(G30,FIND("-",G30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))-(IFERROR(--MID(G30,FIND("-",G30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))-(IFERROR(--MID(G30,FIND("-",G30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(G30,FIND("-",G30)-1),""))=(AW30))+2*((IFERROR(--MID(G30,FIND("-",G30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J30" s="11" t="str">
+      <c r="J30" s="11">
         <f>IF(OR($C30="",I30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I30,FIND("-",I30)-1),"")=AW30,IFERROR(--MID(I30,FIND("-",I30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))-(IFERROR(--MID(I30,FIND("-",I30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))-(IFERROR(--MID(I30,FIND("-",I30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(I30,FIND("-",I30)-1),""))=(AW30))+2*((IFERROR(--MID(I30,FIND("-",I30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="L30" s="11" t="str">
+      <c r="L30" s="11">
         <f>IF(OR($C30="",K30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K30,FIND("-",K30)-1),"")=AW30,IFERROR(--MID(K30,FIND("-",K30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))-(IFERROR(--MID(K30,FIND("-",K30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))-(IFERROR(--MID(K30,FIND("-",K30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(K30,FIND("-",K30)-1),""))=(AW30))+2*((IFERROR(--MID(K30,FIND("-",K30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N30" s="11" t="str">
+      <c r="N30" s="11">
         <f>IF(OR($C30="",M30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M30,FIND("-",M30)-1),"")=AW30,IFERROR(--MID(M30,FIND("-",M30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))-(IFERROR(--MID(M30,FIND("-",M30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))-(IFERROR(--MID(M30,FIND("-",M30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(M30,FIND("-",M30)-1),""))=(AW30))+2*((IFERROR(--MID(M30,FIND("-",M30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O30" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="P30" s="11" t="str">
+      <c r="P30" s="11">
         <f>IF(OR($C30="",O30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O30,FIND("-",O30)-1),"")=AW30,IFERROR(--MID(O30,FIND("-",O30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))-(IFERROR(--MID(O30,FIND("-",O30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))-(IFERROR(--MID(O30,FIND("-",O30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(O30,FIND("-",O30)-1),""))=(AW30))+2*((IFERROR(--MID(O30,FIND("-",O30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="R30" s="11" t="str">
+      <c r="R30" s="11">
         <f>IF(OR($C30="",Q30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q30,FIND("-",Q30)-1),"")=AW30,IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))-(IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))-(IFERROR(--MID(Q30,FIND("-",Q30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(Q30,FIND("-",Q30)-1),""))=(AW30))+2*((IFERROR(--MID(Q30,FIND("-",Q30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T30" s="11" t="str">
+      <c r="T30" s="11">
         <f>IF(OR($C30="",S30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S30,FIND("-",S30)-1),"")=AW30,IFERROR(--MID(S30,FIND("-",S30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))-(IFERROR(--MID(S30,FIND("-",S30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))-(IFERROR(--MID(S30,FIND("-",S30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(S30,FIND("-",S30)-1),""))=(AW30))+2*((IFERROR(--MID(S30,FIND("-",S30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V30" s="11" t="str">
+      <c r="V30" s="11">
         <f>IF(OR($C30="",U30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U30,FIND("-",U30)-1),"")=AW30,IFERROR(--MID(U30,FIND("-",U30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))-(IFERROR(--MID(U30,FIND("-",U30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))-(IFERROR(--MID(U30,FIND("-",U30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(U30,FIND("-",U30)-1),""))=(AW30))+2*((IFERROR(--MID(U30,FIND("-",U30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X30" s="11" t="str">
+      <c r="X30" s="11">
         <f>IF(OR($C30="",W30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W30,FIND("-",W30)-1),"")=AW30,IFERROR(--MID(W30,FIND("-",W30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))-(IFERROR(--MID(W30,FIND("-",W30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))-(IFERROR(--MID(W30,FIND("-",W30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(W30,FIND("-",W30)-1),""))=(AW30))+2*((IFERROR(--MID(W30,FIND("-",W30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z30" s="11" t="str">
+      <c r="Z30" s="11">
         <f>IF(OR($C30="",Y30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y30,FIND("-",Y30)-1),"")=AW30,IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))-(IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))-(IFERROR(--MID(Y30,FIND("-",Y30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(Y30,FIND("-",Y30)-1),""))=(AW30))+2*((IFERROR(--MID(Y30,FIND("-",Y30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB30" s="11" t="str">
+      <c r="AB30" s="11">
         <f>IF(OR($C30="",AA30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA30,FIND("-",AA30)-1),"")=AW30,IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))-(IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))-(IFERROR(--MID(AA30,FIND("-",AA30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AA30,FIND("-",AA30)-1),""))=(AW30))+2*((IFERROR(--MID(AA30,FIND("-",AA30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC30" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD30" s="11" t="str">
+      <c r="AD30" s="11">
         <f>IF(OR($C30="",AC30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC30,FIND("-",AC30)-1),"")=AW30,IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))-(IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))-(IFERROR(--MID(AC30,FIND("-",AC30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AC30,FIND("-",AC30)-1),""))=(AW30))+2*((IFERROR(--MID(AC30,FIND("-",AC30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF30" s="11" t="str">
+      <c r="AF30" s="11">
         <f>IF(OR($C30="",AE30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE30,FIND("-",AE30)-1),"")=AW30,IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))-(IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))-(IFERROR(--MID(AE30,FIND("-",AE30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AE30,FIND("-",AE30)-1),""))=(AW30))+2*((IFERROR(--MID(AE30,FIND("-",AE30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH30" s="11" t="str">
+      <c r="AH30" s="11">
         <f>IF(OR($C30="",AG30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG30,FIND("-",AG30)-1),"")=AW30,IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))-(IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))-(IFERROR(--MID(AG30,FIND("-",AG30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AG30,FIND("-",AG30)-1),""))=(AW30))+2*((IFERROR(--MID(AG30,FIND("-",AG30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ30" s="11" t="str">
+      <c r="AJ30" s="11">
         <f>IF(OR($C30="",AI30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI30,FIND("-",AI30)-1),"")=AW30,IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))-(IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))-(IFERROR(--MID(AI30,FIND("-",AI30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AI30,FIND("-",AI30)-1),""))=(AW30))+2*((IFERROR(--MID(AI30,FIND("-",AI30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL30" s="11" t="str">
+      <c r="AL30" s="11">
         <f>IF(OR($C30="",AK30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK30,FIND("-",AK30)-1),"")=AW30,IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))-(IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))-(IFERROR(--MID(AK30,FIND("-",AK30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AK30,FIND("-",AK30)-1),""))=(AW30))+2*((IFERROR(--MID(AK30,FIND("-",AK30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN30" s="11" t="str">
+      <c r="AN30" s="11">
         <f>IF(OR($C30="",AM30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM30,FIND("-",AM30)-1),"")=AW30,IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))-(IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))-(IFERROR(--MID(AM30,FIND("-",AM30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AM30,FIND("-",AM30)-1),""))=(AW30))+2*((IFERROR(--MID(AM30,FIND("-",AM30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO30" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP30" s="11" t="str">
+      <c r="AP30" s="11">
         <f>IF(OR($C30="",AO30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO30,FIND("-",AO30)-1),"")=AW30,IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))-(IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))-(IFERROR(--MID(AO30,FIND("-",AO30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AO30,FIND("-",AO30)-1),""))=(AW30))+2*((IFERROR(--MID(AO30,FIND("-",AO30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ30" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR30" s="11" t="str">
+      <c r="AR30" s="11">
         <f>IF(OR($C30="",AQ30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),"")=AW30,IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))-(IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))-(IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AQ30,FIND("-",AQ30)-1),""))=(AW30))+2*((IFERROR(--MID(AQ30,FIND("-",AQ30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS30" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT30" s="11" t="str">
+      <c r="AT30" s="11">
         <f>IF(OR($C30="",AS30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS30,FIND("-",AS30)-1),"")=AW30,IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))-(IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))-(IFERROR(--MID(AS30,FIND("-",AS30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AS30,FIND("-",AS30)-1),""))=(AW30))+2*((IFERROR(--MID(AS30,FIND("-",AS30)+1,99),""))=(AX30))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU30" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV30" s="11" t="str">
+      <c r="AV30" s="11">
         <f>IF(OR($C30="",AU30=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU30,FIND("-",AU30)-1),"")=AW30,IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")=AX30),10,5*(SIGN((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))-(IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")))=SIGN((AW30)-(AX30)))+2*(((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))-(IFERROR(--MID(AU30,FIND("-",AU30)+1,99),"")))=((AW30)-(AX30)))+2*((IFERROR(--LEFT(AU30,FIND("-",AU30)-1),""))=(AW30))+2*((IFERROR(--MID(AU30,FIND("-",AU30)+1,99),""))=(AX30))),""))</f>
-        <v/>
-      </c>
-      <c r="AW30" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW30" s="11">
         <f>IF($C30="","",IFERROR(--LEFT($C30,FIND("-",$C30)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX30" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX30" s="11">
         <f>IF($C30="","",IFERROR(--MID($C30,FIND("-",$C30)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26480,7 +26486,7 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26489,20 +26495,20 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>62</v>
+        <f>C3+D3</f>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26511,416 +26517,416 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f t="shared" si="1"/>
-        <v>54</v>
+        <f>C4+D4</f>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>53</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>58</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f>C5+D5</f>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>53</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>57</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f>C6+D6</f>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>52</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>57</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f>C7+D7</f>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>51</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>56</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="1"/>
-        <v>51</v>
+        <f>C8+D8</f>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>49</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>55</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f>C9+D9</f>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>49</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>55</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f>C10+D10</f>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>48</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>53</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f>C11+D11</f>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>48</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>52</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f>C12+D12</f>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>46</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>51</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f>C13+D13</f>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>46</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>51</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f>C14+D14</f>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>45</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>50</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" si="1"/>
-        <v>45</v>
+        <f>C15+D15</f>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>43</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>49</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f>C16+D16</f>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>43</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>49</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f t="shared" si="1"/>
-        <v>43</v>
+        <f>C17+D17</f>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>14</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>42</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>49</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>C18+D18</f>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>42</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>47</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>42</v>
+        <f>C19+D19</f>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>41</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>46</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>41</v>
+        <f>C20+D20</f>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>40</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>46</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <f>C21+D21</f>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>38</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>42</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f>C22+D22</f>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
         <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
@@ -26929,43 +26935,43 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f>C23+D23</f>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>37</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>40</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f>C24+D24</f>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E2:E22" xr:uid="{00000000-0009-0000-0000-000002000000}">
+  <autoFilter ref="E2:E24" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E24">
-      <sortCondition descending="1" ref="E2:E22"/>
+      <sortCondition descending="1" ref="E2:E24"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E24">

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1495" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC5DB20F-E482-49C6-AEDF-0B3746481E0D}"/>
+  <xr:revisionPtr revIDLastSave="1501" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6F2941C-A6E0-437F-BAA3-ED82BB58B0CF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2320" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,76 +1676,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.5546875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.5546875" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.5546875" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.5546875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.5546875" customWidth="1"/>
-    <col min="21" max="21" width="12.5546875" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" customWidth="1"/>
-    <col min="23" max="23" width="12.5546875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.5546875" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" customWidth="1"/>
-    <col min="27" max="27" width="12.5546875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.5546875" customWidth="1"/>
-    <col min="29" max="29" width="12.5546875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.5546875" customWidth="1"/>
-    <col min="31" max="31" width="12.5546875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.5546875" customWidth="1"/>
-    <col min="33" max="33" width="12.5546875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" customWidth="1"/>
-    <col min="35" max="35" width="12.5546875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.5546875" customWidth="1"/>
-    <col min="37" max="37" width="12.5546875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.5546875" customWidth="1"/>
-    <col min="39" max="39" width="12.5546875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.5546875" customWidth="1"/>
-    <col min="41" max="41" width="15.5546875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.5546875" customWidth="1"/>
-    <col min="43" max="43" width="15.5546875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.5546875" customWidth="1"/>
-    <col min="45" max="45" width="15.6640625" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.5546875" customWidth="1"/>
-    <col min="47" max="47" width="15.5546875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.54296875" customWidth="1"/>
+    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" customWidth="1"/>
+    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.54296875" customWidth="1"/>
+    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.54296875" customWidth="1"/>
+    <col min="21" max="21" width="12.54296875" customWidth="1"/>
+    <col min="22" max="22" width="8.54296875" customWidth="1"/>
+    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.54296875" customWidth="1"/>
+    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.54296875" customWidth="1"/>
+    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.54296875" customWidth="1"/>
+    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.54296875" customWidth="1"/>
+    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.54296875" customWidth="1"/>
+    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.54296875" customWidth="1"/>
+    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.54296875" customWidth="1"/>
+    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.54296875" customWidth="1"/>
+    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.54296875" customWidth="1"/>
+    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.54296875" customWidth="1"/>
+    <col min="45" max="45" width="15.6328125" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.54296875" customWidth="1"/>
+    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.54296875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,10 +1837,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1981,61 +1981,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5059,7 +5059,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5113,7 +5113,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5465,181 +5465,183 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D31" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="11" t="str">
+      <c r="F31" s="11">
         <f>IF(OR($C31="",E31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E31,FIND("-",E31)-1),"")=AW31,IFERROR(--MID(E31,FIND("-",E31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))-(IFERROR(--MID(E31,FIND("-",E31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))-(IFERROR(--MID(E31,FIND("-",E31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(E31,FIND("-",E31)-1),""))=(AW31))+2*((IFERROR(--MID(E31,FIND("-",E31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="11" t="str">
+      <c r="H31" s="11">
         <f>IF(OR($C31="",G31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G31,FIND("-",G31)-1),"")=AW31,IFERROR(--MID(G31,FIND("-",G31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))-(IFERROR(--MID(G31,FIND("-",G31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))-(IFERROR(--MID(G31,FIND("-",G31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(G31,FIND("-",G31)-1),""))=(AW31))+2*((IFERROR(--MID(G31,FIND("-",G31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J31" s="11" t="str">
+      <c r="J31" s="11">
         <f>IF(OR($C31="",I31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I31,FIND("-",I31)-1),"")=AW31,IFERROR(--MID(I31,FIND("-",I31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))-(IFERROR(--MID(I31,FIND("-",I31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))-(IFERROR(--MID(I31,FIND("-",I31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(I31,FIND("-",I31)-1),""))=(AW31))+2*((IFERROR(--MID(I31,FIND("-",I31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K31" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L31" s="11" t="str">
+      <c r="L31" s="11">
         <f>IF(OR($C31="",K31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K31,FIND("-",K31)-1),"")=AW31,IFERROR(--MID(K31,FIND("-",K31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))-(IFERROR(--MID(K31,FIND("-",K31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))-(IFERROR(--MID(K31,FIND("-",K31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(K31,FIND("-",K31)-1),""))=(AW31))+2*((IFERROR(--MID(K31,FIND("-",K31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N31" s="11" t="str">
+      <c r="N31" s="11">
         <f>IF(OR($C31="",M31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M31,FIND("-",M31)-1),"")=AW31,IFERROR(--MID(M31,FIND("-",M31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))-(IFERROR(--MID(M31,FIND("-",M31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))-(IFERROR(--MID(M31,FIND("-",M31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(M31,FIND("-",M31)-1),""))=(AW31))+2*((IFERROR(--MID(M31,FIND("-",M31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P31" s="11" t="str">
+      <c r="P31" s="11">
         <f>IF(OR($C31="",O31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O31,FIND("-",O31)-1),"")=AW31,IFERROR(--MID(O31,FIND("-",O31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))-(IFERROR(--MID(O31,FIND("-",O31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))-(IFERROR(--MID(O31,FIND("-",O31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(O31,FIND("-",O31)-1),""))=(AW31))+2*((IFERROR(--MID(O31,FIND("-",O31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R31" s="11" t="str">
+      <c r="R31" s="11">
         <f>IF(OR($C31="",Q31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q31,FIND("-",Q31)-1),"")=AW31,IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))-(IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))-(IFERROR(--MID(Q31,FIND("-",Q31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(Q31,FIND("-",Q31)-1),""))=(AW31))+2*((IFERROR(--MID(Q31,FIND("-",Q31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S31" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T31" s="11" t="str">
+      <c r="T31" s="11">
         <f>IF(OR($C31="",S31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S31,FIND("-",S31)-1),"")=AW31,IFERROR(--MID(S31,FIND("-",S31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))-(IFERROR(--MID(S31,FIND("-",S31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))-(IFERROR(--MID(S31,FIND("-",S31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(S31,FIND("-",S31)-1),""))=(AW31))+2*((IFERROR(--MID(S31,FIND("-",S31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V31" s="11" t="str">
+      <c r="V31" s="11">
         <f>IF(OR($C31="",U31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U31,FIND("-",U31)-1),"")=AW31,IFERROR(--MID(U31,FIND("-",U31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))-(IFERROR(--MID(U31,FIND("-",U31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))-(IFERROR(--MID(U31,FIND("-",U31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(U31,FIND("-",U31)-1),""))=(AW31))+2*((IFERROR(--MID(U31,FIND("-",U31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X31" s="11" t="str">
+      <c r="X31" s="11">
         <f>IF(OR($C31="",W31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W31,FIND("-",W31)-1),"")=AW31,IFERROR(--MID(W31,FIND("-",W31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))-(IFERROR(--MID(W31,FIND("-",W31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))-(IFERROR(--MID(W31,FIND("-",W31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(W31,FIND("-",W31)-1),""))=(AW31))+2*((IFERROR(--MID(W31,FIND("-",W31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z31" s="11" t="str">
+      <c r="Z31" s="11">
         <f>IF(OR($C31="",Y31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y31,FIND("-",Y31)-1),"")=AW31,IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))-(IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))-(IFERROR(--MID(Y31,FIND("-",Y31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(Y31,FIND("-",Y31)-1),""))=(AW31))+2*((IFERROR(--MID(Y31,FIND("-",Y31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB31" s="11" t="str">
+      <c r="AB31" s="11">
         <f>IF(OR($C31="",AA31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA31,FIND("-",AA31)-1),"")=AW31,IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))-(IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))-(IFERROR(--MID(AA31,FIND("-",AA31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AA31,FIND("-",AA31)-1),""))=(AW31))+2*((IFERROR(--MID(AA31,FIND("-",AA31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC31" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="AD31" s="11" t="str">
+      <c r="AD31" s="11">
         <f>IF(OR($C31="",AC31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC31,FIND("-",AC31)-1),"")=AW31,IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))-(IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))-(IFERROR(--MID(AC31,FIND("-",AC31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AC31,FIND("-",AC31)-1),""))=(AW31))+2*((IFERROR(--MID(AC31,FIND("-",AC31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF31" s="11" t="str">
+      <c r="AF31" s="11">
         <f>IF(OR($C31="",AE31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE31,FIND("-",AE31)-1),"")=AW31,IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))-(IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))-(IFERROR(--MID(AE31,FIND("-",AE31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AE31,FIND("-",AE31)-1),""))=(AW31))+2*((IFERROR(--MID(AE31,FIND("-",AE31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH31" s="11" t="str">
+      <c r="AH31" s="11">
         <f>IF(OR($C31="",AG31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG31,FIND("-",AG31)-1),"")=AW31,IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))-(IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))-(IFERROR(--MID(AG31,FIND("-",AG31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AG31,FIND("-",AG31)-1),""))=(AW31))+2*((IFERROR(--MID(AG31,FIND("-",AG31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ31" s="11" t="str">
+      <c r="AJ31" s="11">
         <f>IF(OR($C31="",AI31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI31,FIND("-",AI31)-1),"")=AW31,IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))-(IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))-(IFERROR(--MID(AI31,FIND("-",AI31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AI31,FIND("-",AI31)-1),""))=(AW31))+2*((IFERROR(--MID(AI31,FIND("-",AI31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL31" s="11" t="str">
+      <c r="AL31" s="11">
         <f>IF(OR($C31="",AK31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK31,FIND("-",AK31)-1),"")=AW31,IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))-(IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))-(IFERROR(--MID(AK31,FIND("-",AK31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AK31,FIND("-",AK31)-1),""))=(AW31))+2*((IFERROR(--MID(AK31,FIND("-",AK31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM31" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AN31" s="11" t="str">
+      <c r="AN31" s="11">
         <f>IF(OR($C31="",AM31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM31,FIND("-",AM31)-1),"")=AW31,IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))-(IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))-(IFERROR(--MID(AM31,FIND("-",AM31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AM31,FIND("-",AM31)-1),""))=(AW31))+2*((IFERROR(--MID(AM31,FIND("-",AM31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP31" s="11" t="str">
+      <c r="AP31" s="11">
         <f>IF(OR($C31="",AO31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO31,FIND("-",AO31)-1),"")=AW31,IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))-(IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))-(IFERROR(--MID(AO31,FIND("-",AO31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AO31,FIND("-",AO31)-1),""))=(AW31))+2*((IFERROR(--MID(AO31,FIND("-",AO31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ31" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AR31" s="11" t="str">
+      <c r="AR31" s="11">
         <f>IF(OR($C31="",AQ31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),"")=AW31,IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))-(IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))-(IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AQ31,FIND("-",AQ31)-1),""))=(AW31))+2*((IFERROR(--MID(AQ31,FIND("-",AQ31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS31" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT31" s="11" t="str">
+      <c r="AT31" s="11">
         <f>IF(OR($C31="",AS31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS31,FIND("-",AS31)-1),"")=AW31,IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))-(IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))-(IFERROR(--MID(AS31,FIND("-",AS31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AS31,FIND("-",AS31)-1),""))=(AW31))+2*((IFERROR(--MID(AS31,FIND("-",AS31)+1,99),""))=(AX31))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV31" s="11" t="str">
+      <c r="AV31" s="11">
         <f>IF(OR($C31="",AU31=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU31,FIND("-",AU31)-1),"")=AW31,IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")=AX31),10,5*(SIGN((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))-(IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")))=SIGN((AW31)-(AX31)))+2*(((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))-(IFERROR(--MID(AU31,FIND("-",AU31)+1,99),"")))=((AW31)-(AX31)))+2*((IFERROR(--LEFT(AU31,FIND("-",AU31)-1),""))=(AW31))+2*((IFERROR(--MID(AU31,FIND("-",AU31)+1,99),""))=(AX31))),""))</f>
-        <v/>
-      </c>
-      <c r="AW31" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW31" s="11">
         <f>IF($C31="","",IFERROR(--LEFT($C31,FIND("-",$C31)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX31" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX31" s="11">
         <f>IF($C31="","",IFERROR(--MID($C31,FIND("-",$C31)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5697,7 +5699,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5751,355 +5753,359 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>1</v>
       </c>
       <c r="B34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="C34" s="10"/>
+      <c r="C34" s="10" t="s">
+        <v>115</v>
+      </c>
       <c r="D34" s="1" t="s">
         <v>94</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F34" s="11" t="str">
+      <c r="F34" s="11">
         <f>IF(OR($C34="",E34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E34,FIND("-",E34)-1),"")=AW34,IFERROR(--MID(E34,FIND("-",E34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))-(IFERROR(--MID(E34,FIND("-",E34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))-(IFERROR(--MID(E34,FIND("-",E34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(E34,FIND("-",E34)-1),""))=(AW34))+2*((IFERROR(--MID(E34,FIND("-",E34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="11" t="str">
+      <c r="H34" s="11">
         <f>IF(OR($C34="",G34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G34,FIND("-",G34)-1),"")=AW34,IFERROR(--MID(G34,FIND("-",G34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))-(IFERROR(--MID(G34,FIND("-",G34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))-(IFERROR(--MID(G34,FIND("-",G34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(G34,FIND("-",G34)-1),""))=(AW34))+2*((IFERROR(--MID(G34,FIND("-",G34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J34" s="11" t="str">
+      <c r="J34" s="11">
         <f>IF(OR($C34="",I34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I34,FIND("-",I34)-1),"")=AW34,IFERROR(--MID(I34,FIND("-",I34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))-(IFERROR(--MID(I34,FIND("-",I34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))-(IFERROR(--MID(I34,FIND("-",I34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(I34,FIND("-",I34)-1),""))=(AW34))+2*((IFERROR(--MID(I34,FIND("-",I34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L34" s="11" t="str">
+      <c r="L34" s="11">
         <f>IF(OR($C34="",K34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K34,FIND("-",K34)-1),"")=AW34,IFERROR(--MID(K34,FIND("-",K34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))-(IFERROR(--MID(K34,FIND("-",K34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))-(IFERROR(--MID(K34,FIND("-",K34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(K34,FIND("-",K34)-1),""))=(AW34))+2*((IFERROR(--MID(K34,FIND("-",K34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="N34" s="11" t="str">
+      <c r="N34" s="11">
         <f>IF(OR($C34="",M34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M34,FIND("-",M34)-1),"")=AW34,IFERROR(--MID(M34,FIND("-",M34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))-(IFERROR(--MID(M34,FIND("-",M34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))-(IFERROR(--MID(M34,FIND("-",M34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(M34,FIND("-",M34)-1),""))=(AW34))+2*((IFERROR(--MID(M34,FIND("-",M34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O34" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="P34" s="11" t="str">
+      <c r="P34" s="11">
         <f>IF(OR($C34="",O34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O34,FIND("-",O34)-1),"")=AW34,IFERROR(--MID(O34,FIND("-",O34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))-(IFERROR(--MID(O34,FIND("-",O34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))-(IFERROR(--MID(O34,FIND("-",O34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(O34,FIND("-",O34)-1),""))=(AW34))+2*((IFERROR(--MID(O34,FIND("-",O34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="R34" s="11" t="str">
+      <c r="R34" s="11">
         <f>IF(OR($C34="",Q34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q34,FIND("-",Q34)-1),"")=AW34,IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))-(IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))-(IFERROR(--MID(Q34,FIND("-",Q34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(Q34,FIND("-",Q34)-1),""))=(AW34))+2*((IFERROR(--MID(Q34,FIND("-",Q34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T34" s="11" t="str">
+      <c r="T34" s="11">
         <f>IF(OR($C34="",S34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S34,FIND("-",S34)-1),"")=AW34,IFERROR(--MID(S34,FIND("-",S34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))-(IFERROR(--MID(S34,FIND("-",S34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))-(IFERROR(--MID(S34,FIND("-",S34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(S34,FIND("-",S34)-1),""))=(AW34))+2*((IFERROR(--MID(S34,FIND("-",S34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V34" s="11" t="str">
+      <c r="V34" s="11">
         <f>IF(OR($C34="",U34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U34,FIND("-",U34)-1),"")=AW34,IFERROR(--MID(U34,FIND("-",U34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))-(IFERROR(--MID(U34,FIND("-",U34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))-(IFERROR(--MID(U34,FIND("-",U34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(U34,FIND("-",U34)-1),""))=(AW34))+2*((IFERROR(--MID(U34,FIND("-",U34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X34" s="11" t="str">
+      <c r="X34" s="11">
         <f>IF(OR($C34="",W34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W34,FIND("-",W34)-1),"")=AW34,IFERROR(--MID(W34,FIND("-",W34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))-(IFERROR(--MID(W34,FIND("-",W34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))-(IFERROR(--MID(W34,FIND("-",W34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(W34,FIND("-",W34)-1),""))=(AW34))+2*((IFERROR(--MID(W34,FIND("-",W34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z34" s="11" t="str">
+      <c r="Z34" s="11">
         <f>IF(OR($C34="",Y34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y34,FIND("-",Y34)-1),"")=AW34,IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))-(IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))-(IFERROR(--MID(Y34,FIND("-",Y34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(Y34,FIND("-",Y34)-1),""))=(AW34))+2*((IFERROR(--MID(Y34,FIND("-",Y34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB34" s="11" t="str">
+      <c r="AB34" s="11">
         <f>IF(OR($C34="",AA34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA34,FIND("-",AA34)-1),"")=AW34,IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))-(IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))-(IFERROR(--MID(AA34,FIND("-",AA34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AA34,FIND("-",AA34)-1),""))=(AW34))+2*((IFERROR(--MID(AA34,FIND("-",AA34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AD34" s="11" t="str">
+      <c r="AD34" s="11">
         <f>IF(OR($C34="",AC34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC34,FIND("-",AC34)-1),"")=AW34,IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))-(IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))-(IFERROR(--MID(AC34,FIND("-",AC34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AC34,FIND("-",AC34)-1),""))=(AW34))+2*((IFERROR(--MID(AC34,FIND("-",AC34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE34" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AF34" s="11" t="str">
+      <c r="AF34" s="11">
         <f>IF(OR($C34="",AE34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE34,FIND("-",AE34)-1),"")=AW34,IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))-(IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))-(IFERROR(--MID(AE34,FIND("-",AE34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AE34,FIND("-",AE34)-1),""))=(AW34))+2*((IFERROR(--MID(AE34,FIND("-",AE34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG34" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH34" s="11" t="str">
+      <c r="AH34" s="11">
         <f>IF(OR($C34="",AG34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG34,FIND("-",AG34)-1),"")=AW34,IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))-(IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))-(IFERROR(--MID(AG34,FIND("-",AG34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AG34,FIND("-",AG34)-1),""))=(AW34))+2*((IFERROR(--MID(AG34,FIND("-",AG34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ34" s="11" t="str">
+      <c r="AJ34" s="11">
         <f>IF(OR($C34="",AI34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI34,FIND("-",AI34)-1),"")=AW34,IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))-(IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))-(IFERROR(--MID(AI34,FIND("-",AI34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AI34,FIND("-",AI34)-1),""))=(AW34))+2*((IFERROR(--MID(AI34,FIND("-",AI34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AL34" s="11" t="str">
+      <c r="AL34" s="11">
         <f>IF(OR($C34="",AK34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK34,FIND("-",AK34)-1),"")=AW34,IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))-(IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))-(IFERROR(--MID(AK34,FIND("-",AK34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AK34,FIND("-",AK34)-1),""))=(AW34))+2*((IFERROR(--MID(AK34,FIND("-",AK34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN34" s="11" t="str">
+      <c r="AN34" s="11">
         <f>IF(OR($C34="",AM34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM34,FIND("-",AM34)-1),"")=AW34,IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))-(IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))-(IFERROR(--MID(AM34,FIND("-",AM34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AM34,FIND("-",AM34)-1),""))=(AW34))+2*((IFERROR(--MID(AM34,FIND("-",AM34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP34" s="11" t="str">
+      <c r="AP34" s="11">
         <f>IF(OR($C34="",AO34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO34,FIND("-",AO34)-1),"")=AW34,IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))-(IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))-(IFERROR(--MID(AO34,FIND("-",AO34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AO34,FIND("-",AO34)-1),""))=(AW34))+2*((IFERROR(--MID(AO34,FIND("-",AO34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ34" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR34" s="11" t="str">
+      <c r="AR34" s="11">
         <f t="shared" ref="AR34:AR39" si="2">IF(OR($C34="",AQ34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),"")=AW34,IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))-(IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))-(IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AQ34,FIND("-",AQ34)-1),""))=(AW34))+2*((IFERROR(--MID(AQ34,FIND("-",AQ34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS34" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AT34" s="11" t="str">
+      <c r="AT34" s="11">
         <f t="shared" ref="AT34:AT39" si="3">IF(OR($C34="",AS34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS34,FIND("-",AS34)-1),"")=AW34,IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))-(IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))-(IFERROR(--MID(AS34,FIND("-",AS34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AS34,FIND("-",AS34)-1),""))=(AW34))+2*((IFERROR(--MID(AS34,FIND("-",AS34)+1,99),""))=(AX34))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU34" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV34" s="11" t="str">
+      <c r="AV34" s="11">
         <f>IF(OR($C34="",AU34=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU34,FIND("-",AU34)-1),"")=AW34,IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")=AX34),10,5*(SIGN((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))-(IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")))=SIGN((AW34)-(AX34)))+2*(((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))-(IFERROR(--MID(AU34,FIND("-",AU34)+1,99),"")))=((AW34)-(AX34)))+2*((IFERROR(--LEFT(AU34,FIND("-",AU34)-1),""))=(AW34))+2*((IFERROR(--MID(AU34,FIND("-",AU34)+1,99),""))=(AX34))),""))</f>
-        <v/>
-      </c>
-      <c r="AW34" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW34" s="11">
         <f>IF($C34="","",IFERROR(--LEFT($C34,FIND("-",$C34)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX34" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX34" s="11">
         <f>IF($C34="","",IFERROR(--MID($C34,FIND("-",$C34)+1,99),""))</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D35" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="11" t="str">
+      <c r="F35" s="11">
         <f>IF(OR($C35="",E35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E35,FIND("-",E35)-1),"")=AW35,IFERROR(--MID(E35,FIND("-",E35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))-(IFERROR(--MID(E35,FIND("-",E35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))-(IFERROR(--MID(E35,FIND("-",E35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(E35,FIND("-",E35)-1),""))=(AW35))+2*((IFERROR(--MID(E35,FIND("-",E35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H35" s="11" t="str">
+      <c r="H35" s="11">
         <f>IF(OR($C35="",G35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G35,FIND("-",G35)-1),"")=AW35,IFERROR(--MID(G35,FIND("-",G35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))-(IFERROR(--MID(G35,FIND("-",G35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))-(IFERROR(--MID(G35,FIND("-",G35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(G35,FIND("-",G35)-1),""))=(AW35))+2*((IFERROR(--MID(G35,FIND("-",G35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J35" s="11" t="str">
+      <c r="J35" s="11">
         <f>IF(OR($C35="",I35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I35,FIND("-",I35)-1),"")=AW35,IFERROR(--MID(I35,FIND("-",I35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))-(IFERROR(--MID(I35,FIND("-",I35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))-(IFERROR(--MID(I35,FIND("-",I35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(I35,FIND("-",I35)-1),""))=(AW35))+2*((IFERROR(--MID(I35,FIND("-",I35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L35" s="11" t="str">
+      <c r="L35" s="11">
         <f>IF(OR($C35="",K35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K35,FIND("-",K35)-1),"")=AW35,IFERROR(--MID(K35,FIND("-",K35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))-(IFERROR(--MID(K35,FIND("-",K35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))-(IFERROR(--MID(K35,FIND("-",K35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(K35,FIND("-",K35)-1),""))=(AW35))+2*((IFERROR(--MID(K35,FIND("-",K35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N35" s="11" t="str">
+      <c r="N35" s="11">
         <f>IF(OR($C35="",M35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M35,FIND("-",M35)-1),"")=AW35,IFERROR(--MID(M35,FIND("-",M35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))-(IFERROR(--MID(M35,FIND("-",M35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))-(IFERROR(--MID(M35,FIND("-",M35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(M35,FIND("-",M35)-1),""))=(AW35))+2*((IFERROR(--MID(M35,FIND("-",M35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P35" s="11" t="str">
+      <c r="P35" s="11">
         <f>IF(OR($C35="",O35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O35,FIND("-",O35)-1),"")=AW35,IFERROR(--MID(O35,FIND("-",O35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))-(IFERROR(--MID(O35,FIND("-",O35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))-(IFERROR(--MID(O35,FIND("-",O35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(O35,FIND("-",O35)-1),""))=(AW35))+2*((IFERROR(--MID(O35,FIND("-",O35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="11" t="str">
+      <c r="R35" s="11">
         <f>IF(OR($C35="",Q35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q35,FIND("-",Q35)-1),"")=AW35,IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))-(IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))-(IFERROR(--MID(Q35,FIND("-",Q35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(Q35,FIND("-",Q35)-1),""))=(AW35))+2*((IFERROR(--MID(Q35,FIND("-",Q35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S35" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T35" s="11" t="str">
+      <c r="T35" s="11">
         <f>IF(OR($C35="",S35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S35,FIND("-",S35)-1),"")=AW35,IFERROR(--MID(S35,FIND("-",S35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))-(IFERROR(--MID(S35,FIND("-",S35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))-(IFERROR(--MID(S35,FIND("-",S35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(S35,FIND("-",S35)-1),""))=(AW35))+2*((IFERROR(--MID(S35,FIND("-",S35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V35" s="11" t="str">
+      <c r="V35" s="11">
         <f>IF(OR($C35="",U35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U35,FIND("-",U35)-1),"")=AW35,IFERROR(--MID(U35,FIND("-",U35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))-(IFERROR(--MID(U35,FIND("-",U35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))-(IFERROR(--MID(U35,FIND("-",U35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(U35,FIND("-",U35)-1),""))=(AW35))+2*((IFERROR(--MID(U35,FIND("-",U35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X35" s="11" t="str">
+      <c r="X35" s="11">
         <f>IF(OR($C35="",W35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W35,FIND("-",W35)-1),"")=AW35,IFERROR(--MID(W35,FIND("-",W35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))-(IFERROR(--MID(W35,FIND("-",W35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))-(IFERROR(--MID(W35,FIND("-",W35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(W35,FIND("-",W35)-1),""))=(AW35))+2*((IFERROR(--MID(W35,FIND("-",W35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z35" s="11" t="str">
+      <c r="Z35" s="11">
         <f>IF(OR($C35="",Y35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y35,FIND("-",Y35)-1),"")=AW35,IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))-(IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))-(IFERROR(--MID(Y35,FIND("-",Y35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(Y35,FIND("-",Y35)-1),""))=(AW35))+2*((IFERROR(--MID(Y35,FIND("-",Y35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB35" s="11" t="str">
+      <c r="AB35" s="11">
         <f>IF(OR($C35="",AA35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA35,FIND("-",AA35)-1),"")=AW35,IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))-(IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))-(IFERROR(--MID(AA35,FIND("-",AA35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AA35,FIND("-",AA35)-1),""))=(AW35))+2*((IFERROR(--MID(AA35,FIND("-",AA35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD35" s="11" t="str">
+      <c r="AD35" s="11">
         <f>IF(OR($C35="",AC35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC35,FIND("-",AC35)-1),"")=AW35,IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))-(IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))-(IFERROR(--MID(AC35,FIND("-",AC35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AC35,FIND("-",AC35)-1),""))=(AW35))+2*((IFERROR(--MID(AC35,FIND("-",AC35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF35" s="11" t="str">
+      <c r="AF35" s="11">
         <f>IF(OR($C35="",AE35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE35,FIND("-",AE35)-1),"")=AW35,IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))-(IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))-(IFERROR(--MID(AE35,FIND("-",AE35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AE35,FIND("-",AE35)-1),""))=(AW35))+2*((IFERROR(--MID(AE35,FIND("-",AE35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG35" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH35" s="11" t="str">
+      <c r="AH35" s="11">
         <f>IF(OR($C35="",AG35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG35,FIND("-",AG35)-1),"")=AW35,IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))-(IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))-(IFERROR(--MID(AG35,FIND("-",AG35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AG35,FIND("-",AG35)-1),""))=(AW35))+2*((IFERROR(--MID(AG35,FIND("-",AG35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ35" s="11" t="str">
+      <c r="AJ35" s="11">
         <f>IF(OR($C35="",AI35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI35,FIND("-",AI35)-1),"")=AW35,IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))-(IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))-(IFERROR(--MID(AI35,FIND("-",AI35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AI35,FIND("-",AI35)-1),""))=(AW35))+2*((IFERROR(--MID(AI35,FIND("-",AI35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL35" s="11" t="str">
+      <c r="AL35" s="11">
         <f>IF(OR($C35="",AK35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK35,FIND("-",AK35)-1),"")=AW35,IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))-(IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))-(IFERROR(--MID(AK35,FIND("-",AK35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AK35,FIND("-",AK35)-1),""))=(AW35))+2*((IFERROR(--MID(AK35,FIND("-",AK35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN35" s="11" t="str">
+      <c r="AN35" s="11">
         <f>IF(OR($C35="",AM35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM35,FIND("-",AM35)-1),"")=AW35,IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))-(IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))-(IFERROR(--MID(AM35,FIND("-",AM35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AM35,FIND("-",AM35)-1),""))=(AW35))+2*((IFERROR(--MID(AM35,FIND("-",AM35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AP35" s="11" t="str">
+      <c r="AP35" s="11">
         <f>IF(OR($C35="",AO35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO35,FIND("-",AO35)-1),"")=AW35,IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))-(IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))-(IFERROR(--MID(AO35,FIND("-",AO35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AO35,FIND("-",AO35)-1),""))=(AW35))+2*((IFERROR(--MID(AO35,FIND("-",AO35)+1,99),""))=(AX35))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ35" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR35" s="11" t="str">
+      <c r="AR35" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS35" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT35" s="11" t="str">
+      <c r="AT35" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU35" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV35" s="11" t="str">
+      <c r="AV35" s="11">
         <f>IF(OR($C35="",AU35=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU35,FIND("-",AU35)-1),"")=AW35,IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")=AX35),10,5*(SIGN((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))-(IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")))=SIGN((AW35)-(AX35)))+2*(((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))-(IFERROR(--MID(AU35,FIND("-",AU35)+1,99),"")))=((AW35)-(AX35)))+2*((IFERROR(--LEFT(AU35,FIND("-",AU35)-1),""))=(AW35))+2*((IFERROR(--MID(AU35,FIND("-",AU35)+1,99),""))=(AX35))),""))</f>
-        <v/>
-      </c>
-      <c r="AW35" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW35" s="11">
         <f>IF($C35="","",IFERROR(--LEFT($C35,FIND("-",$C35)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX35" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX35" s="11">
         <f>IF($C35="","",IFERROR(--MID($C35,FIND("-",$C35)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6273,7 +6279,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6447,7 +6453,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6621,7 +6627,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6679,7 +6685,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6733,7 +6739,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6907,7 +6913,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7081,7 +7087,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7255,7 +7261,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7429,7 +7435,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7487,7 +7493,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7541,7 +7547,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7715,7 +7721,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7889,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8063,7 +8069,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8121,7 +8127,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8175,7 +8181,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8349,7 +8355,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8523,7 +8529,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8697,7 +8703,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8871,7 +8877,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9045,7 +9051,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9103,7 +9109,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9157,7 +9163,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9331,7 +9337,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9505,7 +9511,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9679,7 +9685,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9853,7 +9859,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9911,7 +9917,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9965,7 +9971,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10139,7 +10145,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10313,7 +10319,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10487,7 +10493,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10661,7 +10667,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10719,7 +10725,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10773,7 +10779,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10947,7 +10953,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11121,7 +11127,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11295,7 +11301,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11469,7 +11475,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11527,7 +11533,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11581,7 +11587,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11755,7 +11761,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11929,7 +11935,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12103,7 +12109,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12277,7 +12283,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12335,7 +12341,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12389,7 +12395,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12563,7 +12569,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12737,7 +12743,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12911,7 +12917,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13085,7 +13091,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13259,7 +13265,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13433,7 +13439,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13491,7 +13497,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13545,7 +13551,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13719,7 +13725,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13893,7 +13899,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14067,7 +14073,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14241,7 +14247,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14415,7 +14421,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14589,7 +14595,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14647,7 +14653,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14701,7 +14707,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14875,7 +14881,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15049,7 +15055,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15223,7 +15229,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15397,7 +15403,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15571,7 +15577,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15745,7 +15751,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15803,7 +15809,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15857,7 +15863,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16031,7 +16037,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16205,7 +16211,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16379,7 +16385,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16553,7 +16559,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16611,7 +16617,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16669,7 +16675,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16723,7 +16729,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16777,7 +16783,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16907,7 +16913,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16965,7 +16971,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17019,7 +17025,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17149,7 +17155,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17279,7 +17285,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17337,7 +17343,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17391,7 +17397,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17521,7 +17527,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17651,7 +17657,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17781,7 +17787,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17839,7 +17845,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17893,7 +17899,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18023,7 +18029,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18153,7 +18159,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18283,7 +18289,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18341,7 +18347,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18395,7 +18401,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18525,7 +18531,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18655,7 +18661,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18713,7 +18719,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18767,7 +18773,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18897,7 +18903,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19027,7 +19033,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19157,7 +19163,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19215,7 +19221,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19269,7 +19275,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19399,7 +19405,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19529,7 +19535,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19587,7 +19593,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19645,7 +19651,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19699,7 +19705,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19753,7 +19759,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19883,7 +19889,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20013,7 +20019,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20071,7 +20077,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20125,7 +20131,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20255,7 +20261,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20313,7 +20319,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20367,7 +20373,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20497,7 +20503,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20627,7 +20633,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20685,7 +20691,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20739,7 +20745,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20869,7 +20875,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -20999,7 +21005,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21129,7 +21135,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21187,7 +21193,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21245,7 +21251,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21299,7 +21305,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21353,7 +21359,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21483,7 +21489,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21541,7 +21547,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21595,7 +21601,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21725,7 +21731,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21783,7 +21789,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21837,7 +21843,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21967,7 +21973,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22025,7 +22031,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22079,7 +22085,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22209,7 +22215,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22267,7 +22273,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22325,7 +22331,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22379,7 +22385,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22433,7 +22439,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22563,7 +22569,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22621,7 +22627,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22675,7 +22681,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22805,7 +22811,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22863,7 +22869,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22921,7 +22927,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22975,7 +22981,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23029,7 +23035,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23159,7 +23165,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23217,7 +23223,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23275,7 +23281,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23329,7 +23335,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23383,7 +23389,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23513,7 +23519,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23571,7 +23577,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23631,6 +23637,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23647,60 +23707,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23710,58 +23716,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.33203125" customWidth="1"/>
+    <col min="2" max="2" width="75.36328125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.5546875" customWidth="1"/>
-    <col min="18" max="18" width="12.5546875" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" customWidth="1"/>
-    <col min="20" max="20" width="12.5546875" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.5546875" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.5546875" customWidth="1"/>
-    <col min="26" max="26" width="12.5546875" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.5546875" customWidth="1"/>
-    <col min="28" max="28" width="12.5546875" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.5546875" customWidth="1"/>
-    <col min="30" max="30" width="12.5546875" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.5546875" customWidth="1"/>
-    <col min="32" max="32" width="12.5546875" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.5546875" customWidth="1"/>
-    <col min="34" max="34" width="12.5546875" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.5546875" customWidth="1"/>
-    <col min="36" max="36" width="12.5546875" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.5546875" customWidth="1"/>
-    <col min="38" max="38" width="12.5546875" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.5546875" customWidth="1"/>
-    <col min="40" max="40" width="12.5546875" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.5546875" customWidth="1"/>
-    <col min="42" max="42" width="12.5546875" customWidth="1"/>
-    <col min="43" max="43" width="10.5546875" customWidth="1"/>
-    <col min="44" max="44" width="12.5546875" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.5546875" customWidth="1"/>
-    <col min="46" max="46" width="12.5546875" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.54296875" customWidth="1"/>
+    <col min="7" max="7" width="10.54296875" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="10.54296875" customWidth="1"/>
+    <col min="10" max="10" width="12.54296875" customWidth="1"/>
+    <col min="11" max="11" width="10.54296875" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" customWidth="1"/>
+    <col min="13" max="13" width="10.54296875" customWidth="1"/>
+    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.54296875" customWidth="1"/>
+    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.54296875" customWidth="1"/>
+    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.54296875" customWidth="1"/>
+    <col min="20" max="20" width="12.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.54296875" customWidth="1"/>
+    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.54296875" customWidth="1"/>
+    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.54296875" customWidth="1"/>
+    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.54296875" customWidth="1"/>
+    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.54296875" customWidth="1"/>
+    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.54296875" customWidth="1"/>
+    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.54296875" customWidth="1"/>
+    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.54296875" customWidth="1"/>
+    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.54296875" customWidth="1"/>
+    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.54296875" customWidth="1"/>
+    <col min="42" max="42" width="12.54296875" customWidth="1"/>
+    <col min="43" max="43" width="10.54296875" customWidth="1"/>
+    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.54296875" customWidth="1"/>
+    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23867,14 +23873,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24015,7 +24021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24178,7 +24184,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24341,7 +24347,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24504,7 +24510,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24667,7 +24673,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24830,7 +24836,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -24993,7 +24999,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25156,7 +25162,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25319,7 +25325,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25482,7 +25488,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25645,7 +25651,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25808,7 +25814,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25971,7 +25977,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26134,7 +26140,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26297,7 +26303,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26416,6 +26422,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26427,17 +26444,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26449,16 +26455,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.6328125" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26467,7 +26473,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26484,73 +26490,73 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>66</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>89</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>65</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>85</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>58</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>81</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
         <v>4</v>
@@ -26561,7 +26567,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!I17</f>
@@ -26569,233 +26575,233 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>57</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>77</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>56</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>76</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
+      </c>
+      <c r="C9" s="11">
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>76</v>
+      </c>
+      <c r="D9" s="11">
+        <f>Bonus_beheer!AK17</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <f>C9+D9</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>55</v>
-      </c>
-      <c r="D9" s="11">
+        <v>74</v>
+      </c>
+      <c r="D10" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
-      <c r="E9" s="11">
-        <f>C9+D9</f>
-        <v>55</v>
+      <c r="E10" s="11">
+        <f>C10+D10</f>
+        <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="str">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>55</v>
-      </c>
-      <c r="D10" s="11">
+        <v>74</v>
+      </c>
+      <c r="D11" s="11">
         <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
-      <c r="E10" s="11">
-        <f>C10+D10</f>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
-      </c>
-      <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>53</v>
-      </c>
-      <c r="D11" s="11">
-        <f>Bonus_beheer!Y17</f>
-        <v>0</v>
-      </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>52</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>72</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
+      </c>
+      <c r="C13" s="11">
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>71</v>
+      </c>
+      <c r="D13" s="11">
+        <f>Bonus_beheer!AG17</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="11">
+        <f>C13+D13</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>51</v>
-      </c>
-      <c r="D13" s="11">
+        <v>70</v>
+      </c>
+      <c r="D14" s="11">
         <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
-      <c r="E13" s="11">
-        <f>C13+D13</f>
-        <v>51</v>
+      <c r="E14" s="11">
+        <f>C14+D14</f>
+        <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
-        <v>11</v>
-      </c>
-      <c r="B14" s="1" t="str">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>51</v>
-      </c>
-      <c r="D14" s="11">
+        <v>70</v>
+      </c>
+      <c r="D15" s="11">
         <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
-      <c r="E14" s="11">
-        <f>C14+D14</f>
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
-      </c>
-      <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>50</v>
-      </c>
-      <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
-        <v>0</v>
-      </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>49</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>69</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26803,7 +26809,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -26811,13 +26817,13 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26825,7 +26831,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -26833,32 +26839,32 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>47</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>66</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
@@ -26869,7 +26875,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26877,13 +26883,13 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26891,7 +26897,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26899,10 +26905,10 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
         <v>20</v>
@@ -26913,7 +26919,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26921,10 +26927,10 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
         <v>20</v>
@@ -26935,7 +26941,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26943,10 +26949,10 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
@@ -26957,7 +26963,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26965,7 +26971,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -26985,20 +26991,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" hidden="1"/>
+    <col min="3" max="16384" width="8.6328125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27006,7 +27012,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27014,7 +27020,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27022,7 +27028,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27030,7 +27036,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27038,7 +27044,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27046,7 +27052,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27054,7 +27060,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27070,16 +27076,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="55.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" customWidth="1"/>
+    <col min="3" max="3" width="30.6328125" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.6640625" hidden="1"/>
+    <col min="45" max="16384" width="8.6328125" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27127,7 +27133,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27138,7 +27144,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27149,7 +27155,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27160,7 +27166,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27171,7 +27177,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27182,7 +27188,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27193,7 +27199,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27210,14 +27216,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27228,7 +27234,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27239,7 +27245,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27247,7 +27253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27255,7 +27261,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27263,7 +27269,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27271,62 +27277,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -27337,26 +27343,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27551,32 +27537,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27593,4 +27574,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1501" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6F2941C-A6E0-437F-BAA3-ED82BB58B0CF}"/>
+  <xr:revisionPtr revIDLastSave="1505" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7562EF02-6743-4AF0-B4A3-1631E7DD1858}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="5196" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2323" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,22 +1730,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,9 +1838,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1985,53 +1985,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -6112,171 +6112,173 @@
       <c r="B36" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D36" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="11" t="str">
+      <c r="F36" s="11">
         <f>IF(OR($C36="",E36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E36,FIND("-",E36)-1),"")=AW36,IFERROR(--MID(E36,FIND("-",E36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))-(IFERROR(--MID(E36,FIND("-",E36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))-(IFERROR(--MID(E36,FIND("-",E36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(E36,FIND("-",E36)-1),""))=(AW36))+2*((IFERROR(--MID(E36,FIND("-",E36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="11" t="str">
+      <c r="H36" s="11">
         <f>IF(OR($C36="",G36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G36,FIND("-",G36)-1),"")=AW36,IFERROR(--MID(G36,FIND("-",G36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))-(IFERROR(--MID(G36,FIND("-",G36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))-(IFERROR(--MID(G36,FIND("-",G36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(G36,FIND("-",G36)-1),""))=(AW36))+2*((IFERROR(--MID(G36,FIND("-",G36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J36" s="11" t="str">
+      <c r="J36" s="11">
         <f>IF(OR($C36="",I36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I36,FIND("-",I36)-1),"")=AW36,IFERROR(--MID(I36,FIND("-",I36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))-(IFERROR(--MID(I36,FIND("-",I36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))-(IFERROR(--MID(I36,FIND("-",I36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(I36,FIND("-",I36)-1),""))=(AW36))+2*((IFERROR(--MID(I36,FIND("-",I36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="11" t="str">
+      <c r="L36" s="11">
         <f>IF(OR($C36="",K36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K36,FIND("-",K36)-1),"")=AW36,IFERROR(--MID(K36,FIND("-",K36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))-(IFERROR(--MID(K36,FIND("-",K36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))-(IFERROR(--MID(K36,FIND("-",K36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(K36,FIND("-",K36)-1),""))=(AW36))+2*((IFERROR(--MID(K36,FIND("-",K36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N36" s="11" t="str">
+      <c r="N36" s="11">
         <f>IF(OR($C36="",M36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M36,FIND("-",M36)-1),"")=AW36,IFERROR(--MID(M36,FIND("-",M36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))-(IFERROR(--MID(M36,FIND("-",M36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))-(IFERROR(--MID(M36,FIND("-",M36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(M36,FIND("-",M36)-1),""))=(AW36))+2*((IFERROR(--MID(M36,FIND("-",M36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P36" s="11" t="str">
+      <c r="P36" s="11">
         <f>IF(OR($C36="",O36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O36,FIND("-",O36)-1),"")=AW36,IFERROR(--MID(O36,FIND("-",O36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))-(IFERROR(--MID(O36,FIND("-",O36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))-(IFERROR(--MID(O36,FIND("-",O36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(O36,FIND("-",O36)-1),""))=(AW36))+2*((IFERROR(--MID(O36,FIND("-",O36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R36" s="11" t="str">
+      <c r="R36" s="11">
         <f>IF(OR($C36="",Q36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q36,FIND("-",Q36)-1),"")=AW36,IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))-(IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))-(IFERROR(--MID(Q36,FIND("-",Q36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(Q36,FIND("-",Q36)-1),""))=(AW36))+2*((IFERROR(--MID(Q36,FIND("-",Q36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S36" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T36" s="11" t="str">
+      <c r="T36" s="11">
         <f>IF(OR($C36="",S36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S36,FIND("-",S36)-1),"")=AW36,IFERROR(--MID(S36,FIND("-",S36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))-(IFERROR(--MID(S36,FIND("-",S36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))-(IFERROR(--MID(S36,FIND("-",S36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(S36,FIND("-",S36)-1),""))=(AW36))+2*((IFERROR(--MID(S36,FIND("-",S36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V36" s="11" t="str">
+      <c r="V36" s="11">
         <f>IF(OR($C36="",U36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U36,FIND("-",U36)-1),"")=AW36,IFERROR(--MID(U36,FIND("-",U36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))-(IFERROR(--MID(U36,FIND("-",U36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))-(IFERROR(--MID(U36,FIND("-",U36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(U36,FIND("-",U36)-1),""))=(AW36))+2*((IFERROR(--MID(U36,FIND("-",U36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X36" s="11" t="str">
+      <c r="X36" s="11">
         <f>IF(OR($C36="",W36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W36,FIND("-",W36)-1),"")=AW36,IFERROR(--MID(W36,FIND("-",W36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))-(IFERROR(--MID(W36,FIND("-",W36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))-(IFERROR(--MID(W36,FIND("-",W36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(W36,FIND("-",W36)-1),""))=(AW36))+2*((IFERROR(--MID(W36,FIND("-",W36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z36" s="11" t="str">
+      <c r="Z36" s="11">
         <f>IF(OR($C36="",Y36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y36,FIND("-",Y36)-1),"")=AW36,IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))-(IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))-(IFERROR(--MID(Y36,FIND("-",Y36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(Y36,FIND("-",Y36)-1),""))=(AW36))+2*((IFERROR(--MID(Y36,FIND("-",Y36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB36" s="11" t="str">
+      <c r="AB36" s="11">
         <f>IF(OR($C36="",AA36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA36,FIND("-",AA36)-1),"")=AW36,IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))-(IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))-(IFERROR(--MID(AA36,FIND("-",AA36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AA36,FIND("-",AA36)-1),""))=(AW36))+2*((IFERROR(--MID(AA36,FIND("-",AA36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC36" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AD36" s="11" t="str">
+      <c r="AD36" s="11">
         <f>IF(OR($C36="",AC36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC36,FIND("-",AC36)-1),"")=AW36,IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))-(IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))-(IFERROR(--MID(AC36,FIND("-",AC36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AC36,FIND("-",AC36)-1),""))=(AW36))+2*((IFERROR(--MID(AC36,FIND("-",AC36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF36" s="11" t="str">
+      <c r="AF36" s="11">
         <f>IF(OR($C36="",AE36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE36,FIND("-",AE36)-1),"")=AW36,IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))-(IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))-(IFERROR(--MID(AE36,FIND("-",AE36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AE36,FIND("-",AE36)-1),""))=(AW36))+2*((IFERROR(--MID(AE36,FIND("-",AE36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH36" s="11" t="str">
+      <c r="AH36" s="11">
         <f>IF(OR($C36="",AG36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG36,FIND("-",AG36)-1),"")=AW36,IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))-(IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))-(IFERROR(--MID(AG36,FIND("-",AG36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AG36,FIND("-",AG36)-1),""))=(AW36))+2*((IFERROR(--MID(AG36,FIND("-",AG36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ36" s="11" t="str">
+      <c r="AJ36" s="11">
         <f>IF(OR($C36="",AI36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI36,FIND("-",AI36)-1),"")=AW36,IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))-(IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))-(IFERROR(--MID(AI36,FIND("-",AI36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AI36,FIND("-",AI36)-1),""))=(AW36))+2*((IFERROR(--MID(AI36,FIND("-",AI36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL36" s="11" t="str">
+      <c r="AL36" s="11">
         <f>IF(OR($C36="",AK36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK36,FIND("-",AK36)-1),"")=AW36,IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))-(IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))-(IFERROR(--MID(AK36,FIND("-",AK36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AK36,FIND("-",AK36)-1),""))=(AW36))+2*((IFERROR(--MID(AK36,FIND("-",AK36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM36" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN36" s="11" t="str">
+      <c r="AN36" s="11">
         <f>IF(OR($C36="",AM36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM36,FIND("-",AM36)-1),"")=AW36,IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))-(IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))-(IFERROR(--MID(AM36,FIND("-",AM36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AM36,FIND("-",AM36)-1),""))=(AW36))+2*((IFERROR(--MID(AM36,FIND("-",AM36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP36" s="11" t="str">
+      <c r="AP36" s="11">
         <f>IF(OR($C36="",AO36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO36,FIND("-",AO36)-1),"")=AW36,IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))-(IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))-(IFERROR(--MID(AO36,FIND("-",AO36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AO36,FIND("-",AO36)-1),""))=(AW36))+2*((IFERROR(--MID(AO36,FIND("-",AO36)+1,99),""))=(AX36))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ36" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR36" s="11" t="str">
+      <c r="AR36" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS36" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT36" s="11" t="str">
+      <c r="AT36" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AV36" s="11" t="str">
+      <c r="AV36" s="11">
         <f>IF(OR($C36="",AU36=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU36,FIND("-",AU36)-1),"")=AW36,IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")=AX36),10,5*(SIGN((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))-(IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")))=SIGN((AW36)-(AX36)))+2*(((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))-(IFERROR(--MID(AU36,FIND("-",AU36)+1,99),"")))=((AW36)-(AX36)))+2*((IFERROR(--LEFT(AU36,FIND("-",AU36)-1),""))=(AW36))+2*((IFERROR(--MID(AU36,FIND("-",AU36)+1,99),""))=(AX36))),""))</f>
-        <v/>
-      </c>
-      <c r="AW36" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW36" s="11">
         <f>IF($C36="","",IFERROR(--LEFT($C36,FIND("-",$C36)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX36" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX36" s="11">
         <f>IF($C36="","",IFERROR(--MID($C36,FIND("-",$C36)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -23637,6 +23639,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23653,60 +23709,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23873,12 +23875,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="21"/>
@@ -26422,6 +26424,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26433,17 +26446,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26501,7 +26503,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26509,7 +26511,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26523,7 +26525,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26531,7 +26533,7 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26545,7 +26547,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26553,7 +26555,7 @@
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26562,42 +26564,42 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>79</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>83</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>77</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>83</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26606,86 +26608,86 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>81</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>79</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>74</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>79</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>74</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>79</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26694,42 +26696,42 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>72</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>77</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>71</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>77</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26738,20 +26740,20 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>70</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>76</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26760,20 +26762,20 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>70</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>76</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26782,64 +26784,64 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>69</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>75</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>68</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>75</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>68</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>74</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26853,7 +26855,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26861,7 +26863,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26875,7 +26877,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26883,7 +26885,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26897,7 +26899,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -26905,7 +26907,7 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -26919,7 +26921,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26927,13 +26929,13 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26941,7 +26943,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26949,7 +26951,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -26963,7 +26965,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26971,7 +26973,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -27343,6 +27345,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27537,17 +27550,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -27558,6 +27560,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27576,23 +27595,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1505" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7562EF02-6743-4AF0-B4A3-1631E7DD1858}"/>
+  <xr:revisionPtr revIDLastSave="1510" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24FD84A-C586-428C-BF4F-C42356C40300}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="5196" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2324" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1676,76 +1676,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" customWidth="1"/>
-    <col min="2" max="2" width="20.54296875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="20.54296875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" style="23" customWidth="1"/>
-    <col min="6" max="6" width="8.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" style="23" customWidth="1"/>
-    <col min="10" max="10" width="8.54296875" customWidth="1"/>
-    <col min="11" max="11" width="12.54296875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.54296875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="12.54296875" style="23" customWidth="1"/>
-    <col min="16" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="12.54296875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="12.54296875" style="23" customWidth="1"/>
-    <col min="20" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="12.54296875" customWidth="1"/>
-    <col min="22" max="22" width="8.54296875" customWidth="1"/>
-    <col min="23" max="23" width="12.54296875" style="23" customWidth="1"/>
-    <col min="24" max="24" width="8.54296875" customWidth="1"/>
-    <col min="25" max="25" width="12.54296875" style="23" customWidth="1"/>
-    <col min="26" max="26" width="8.54296875" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="23" customWidth="1"/>
-    <col min="28" max="28" width="8.54296875" customWidth="1"/>
-    <col min="29" max="29" width="12.54296875" style="23" customWidth="1"/>
-    <col min="30" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="12.54296875" style="23" customWidth="1"/>
-    <col min="32" max="32" width="8.54296875" customWidth="1"/>
-    <col min="33" max="33" width="12.54296875" style="23" customWidth="1"/>
-    <col min="34" max="34" width="8.54296875" customWidth="1"/>
-    <col min="35" max="35" width="12.54296875" style="23" customWidth="1"/>
-    <col min="36" max="36" width="8.54296875" customWidth="1"/>
-    <col min="37" max="37" width="12.54296875" style="23" customWidth="1"/>
-    <col min="38" max="38" width="8.54296875" customWidth="1"/>
-    <col min="39" max="39" width="12.54296875" style="23" customWidth="1"/>
-    <col min="40" max="40" width="8.54296875" customWidth="1"/>
-    <col min="41" max="41" width="15.54296875" style="23" customWidth="1"/>
-    <col min="42" max="42" width="8.54296875" customWidth="1"/>
-    <col min="43" max="43" width="15.54296875" style="23" customWidth="1"/>
-    <col min="44" max="44" width="8.54296875" customWidth="1"/>
-    <col min="45" max="45" width="15.6328125" style="23" customWidth="1"/>
-    <col min="46" max="46" width="8.54296875" customWidth="1"/>
-    <col min="47" max="47" width="15.54296875" style="23" customWidth="1"/>
-    <col min="48" max="48" width="8.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="23" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="23" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="8.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" style="23" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="21" width="12.5546875" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" customWidth="1"/>
+    <col min="23" max="23" width="12.5546875" style="23" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="12.5546875" style="23" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="12.5546875" style="23" customWidth="1"/>
+    <col min="28" max="28" width="8.5546875" customWidth="1"/>
+    <col min="29" max="29" width="12.5546875" style="23" customWidth="1"/>
+    <col min="30" max="30" width="8.5546875" customWidth="1"/>
+    <col min="31" max="31" width="12.5546875" style="23" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" customWidth="1"/>
+    <col min="33" max="33" width="12.5546875" style="23" customWidth="1"/>
+    <col min="34" max="34" width="8.5546875" customWidth="1"/>
+    <col min="35" max="35" width="12.5546875" style="23" customWidth="1"/>
+    <col min="36" max="36" width="8.5546875" customWidth="1"/>
+    <col min="37" max="37" width="12.5546875" style="23" customWidth="1"/>
+    <col min="38" max="38" width="8.5546875" customWidth="1"/>
+    <col min="39" max="39" width="12.5546875" style="23" customWidth="1"/>
+    <col min="40" max="40" width="8.5546875" customWidth="1"/>
+    <col min="41" max="41" width="15.5546875" style="23" customWidth="1"/>
+    <col min="42" max="42" width="8.5546875" customWidth="1"/>
+    <col min="43" max="43" width="15.5546875" style="23" customWidth="1"/>
+    <col min="44" max="44" width="8.5546875" customWidth="1"/>
+    <col min="45" max="45" width="15.6640625" style="23" customWidth="1"/>
+    <col min="46" max="46" width="8.5546875" customWidth="1"/>
+    <col min="47" max="47" width="15.5546875" style="23" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1837,10 +1837,10 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.35">
-      <c r="A2" s="41"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1981,61 +1981,61 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="33" t="s">
         <v>30</v>
       </c>
@@ -2089,7 +2089,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="18"/>
       <c r="C6" s="13"/>
@@ -2323,7 +2323,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2377,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="18"/>
       <c r="C10" s="13"/>
@@ -2787,7 +2787,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>51</v>
       </c>
@@ -2841,7 +2841,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="18"/>
       <c r="C14" s="13"/>
@@ -3251,7 +3251,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>58</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3481,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="18"/>
       <c r="C21" s="13"/>
@@ -4243,7 +4243,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="33" t="s">
         <v>75</v>
       </c>
@@ -4297,7 +4297,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4825,7 +4825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5001,7 +5001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="18"/>
       <c r="C27" s="13"/>
@@ -5059,7 +5059,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="33" t="s">
         <v>84</v>
       </c>
@@ -5113,7 +5113,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="18"/>
       <c r="C32" s="13"/>
@@ -5699,7 +5699,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="33" t="s">
         <v>92</v>
       </c>
@@ -5753,7 +5753,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5929,7 +5929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6105,7 +6105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6281,355 +6281,359 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D37" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="11" t="str">
+      <c r="F37" s="11">
         <f>IF(OR($C37="",E37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E37,FIND("-",E37)-1),"")=AW37,IFERROR(--MID(E37,FIND("-",E37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))-(IFERROR(--MID(E37,FIND("-",E37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))-(IFERROR(--MID(E37,FIND("-",E37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(E37,FIND("-",E37)-1),""))=(AW37))+2*((IFERROR(--MID(E37,FIND("-",E37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H37" s="11" t="str">
+      <c r="H37" s="11">
         <f>IF(OR($C37="",G37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G37,FIND("-",G37)-1),"")=AW37,IFERROR(--MID(G37,FIND("-",G37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))-(IFERROR(--MID(G37,FIND("-",G37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))-(IFERROR(--MID(G37,FIND("-",G37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(G37,FIND("-",G37)-1),""))=(AW37))+2*((IFERROR(--MID(G37,FIND("-",G37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J37" s="11" t="str">
+      <c r="J37" s="11">
         <f>IF(OR($C37="",I37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I37,FIND("-",I37)-1),"")=AW37,IFERROR(--MID(I37,FIND("-",I37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))-(IFERROR(--MID(I37,FIND("-",I37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))-(IFERROR(--MID(I37,FIND("-",I37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(I37,FIND("-",I37)-1),""))=(AW37))+2*((IFERROR(--MID(I37,FIND("-",I37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="11" t="str">
+      <c r="L37" s="11">
         <f>IF(OR($C37="",K37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K37,FIND("-",K37)-1),"")=AW37,IFERROR(--MID(K37,FIND("-",K37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))-(IFERROR(--MID(K37,FIND("-",K37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))-(IFERROR(--MID(K37,FIND("-",K37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(K37,FIND("-",K37)-1),""))=(AW37))+2*((IFERROR(--MID(K37,FIND("-",K37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N37" s="11" t="str">
+      <c r="N37" s="11">
         <f>IF(OR($C37="",M37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M37,FIND("-",M37)-1),"")=AW37,IFERROR(--MID(M37,FIND("-",M37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))-(IFERROR(--MID(M37,FIND("-",M37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))-(IFERROR(--MID(M37,FIND("-",M37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(M37,FIND("-",M37)-1),""))=(AW37))+2*((IFERROR(--MID(M37,FIND("-",M37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O37" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P37" s="11" t="str">
+      <c r="P37" s="11">
         <f>IF(OR($C37="",O37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O37,FIND("-",O37)-1),"")=AW37,IFERROR(--MID(O37,FIND("-",O37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))-(IFERROR(--MID(O37,FIND("-",O37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))-(IFERROR(--MID(O37,FIND("-",O37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(O37,FIND("-",O37)-1),""))=(AW37))+2*((IFERROR(--MID(O37,FIND("-",O37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R37" s="11" t="str">
+      <c r="R37" s="11">
         <f>IF(OR($C37="",Q37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q37,FIND("-",Q37)-1),"")=AW37,IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))-(IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))-(IFERROR(--MID(Q37,FIND("-",Q37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(Q37,FIND("-",Q37)-1),""))=(AW37))+2*((IFERROR(--MID(Q37,FIND("-",Q37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S37" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T37" s="11" t="str">
+      <c r="T37" s="11">
         <f>IF(OR($C37="",S37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S37,FIND("-",S37)-1),"")=AW37,IFERROR(--MID(S37,FIND("-",S37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))-(IFERROR(--MID(S37,FIND("-",S37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))-(IFERROR(--MID(S37,FIND("-",S37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(S37,FIND("-",S37)-1),""))=(AW37))+2*((IFERROR(--MID(S37,FIND("-",S37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V37" s="11" t="str">
+      <c r="V37" s="11">
         <f>IF(OR($C37="",U37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U37,FIND("-",U37)-1),"")=AW37,IFERROR(--MID(U37,FIND("-",U37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))-(IFERROR(--MID(U37,FIND("-",U37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))-(IFERROR(--MID(U37,FIND("-",U37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(U37,FIND("-",U37)-1),""))=(AW37))+2*((IFERROR(--MID(U37,FIND("-",U37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X37" s="11" t="str">
+      <c r="X37" s="11">
         <f>IF(OR($C37="",W37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W37,FIND("-",W37)-1),"")=AW37,IFERROR(--MID(W37,FIND("-",W37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))-(IFERROR(--MID(W37,FIND("-",W37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))-(IFERROR(--MID(W37,FIND("-",W37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(W37,FIND("-",W37)-1),""))=(AW37))+2*((IFERROR(--MID(W37,FIND("-",W37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z37" s="11" t="str">
+      <c r="Z37" s="11">
         <f>IF(OR($C37="",Y37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y37,FIND("-",Y37)-1),"")=AW37,IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))-(IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))-(IFERROR(--MID(Y37,FIND("-",Y37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(Y37,FIND("-",Y37)-1),""))=(AW37))+2*((IFERROR(--MID(Y37,FIND("-",Y37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA37" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AB37" s="11" t="str">
+      <c r="AB37" s="11">
         <f>IF(OR($C37="",AA37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA37,FIND("-",AA37)-1),"")=AW37,IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))-(IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))-(IFERROR(--MID(AA37,FIND("-",AA37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AA37,FIND("-",AA37)-1),""))=(AW37))+2*((IFERROR(--MID(AA37,FIND("-",AA37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD37" s="11" t="str">
+      <c r="AD37" s="11">
         <f>IF(OR($C37="",AC37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC37,FIND("-",AC37)-1),"")=AW37,IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))-(IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))-(IFERROR(--MID(AC37,FIND("-",AC37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AC37,FIND("-",AC37)-1),""))=(AW37))+2*((IFERROR(--MID(AC37,FIND("-",AC37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AF37" s="11" t="str">
+      <c r="AF37" s="11">
         <f>IF(OR($C37="",AE37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE37,FIND("-",AE37)-1),"")=AW37,IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))-(IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))-(IFERROR(--MID(AE37,FIND("-",AE37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AE37,FIND("-",AE37)-1),""))=(AW37))+2*((IFERROR(--MID(AE37,FIND("-",AE37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH37" s="11" t="str">
+      <c r="AH37" s="11">
         <f>IF(OR($C37="",AG37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG37,FIND("-",AG37)-1),"")=AW37,IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))-(IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))-(IFERROR(--MID(AG37,FIND("-",AG37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AG37,FIND("-",AG37)-1),""))=(AW37))+2*((IFERROR(--MID(AG37,FIND("-",AG37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ37" s="11" t="str">
+      <c r="AJ37" s="11">
         <f>IF(OR($C37="",AI37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI37,FIND("-",AI37)-1),"")=AW37,IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))-(IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))-(IFERROR(--MID(AI37,FIND("-",AI37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AI37,FIND("-",AI37)-1),""))=(AW37))+2*((IFERROR(--MID(AI37,FIND("-",AI37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK37" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL37" s="11" t="str">
+      <c r="AL37" s="11">
         <f>IF(OR($C37="",AK37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK37,FIND("-",AK37)-1),"")=AW37,IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))-(IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))-(IFERROR(--MID(AK37,FIND("-",AK37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AK37,FIND("-",AK37)-1),""))=(AW37))+2*((IFERROR(--MID(AK37,FIND("-",AK37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM37" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN37" s="11" t="str">
+      <c r="AN37" s="11">
         <f>IF(OR($C37="",AM37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM37,FIND("-",AM37)-1),"")=AW37,IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))-(IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))-(IFERROR(--MID(AM37,FIND("-",AM37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AM37,FIND("-",AM37)-1),""))=(AW37))+2*((IFERROR(--MID(AM37,FIND("-",AM37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO37" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP37" s="11" t="str">
+      <c r="AP37" s="11">
         <f>IF(OR($C37="",AO37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO37,FIND("-",AO37)-1),"")=AW37,IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))-(IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))-(IFERROR(--MID(AO37,FIND("-",AO37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AO37,FIND("-",AO37)-1),""))=(AW37))+2*((IFERROR(--MID(AO37,FIND("-",AO37)+1,99),""))=(AX37))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AR37" s="11" t="str">
+      <c r="AR37" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT37" s="11" t="str">
+      <c r="AT37" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU37" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AV37" s="11" t="str">
+      <c r="AV37" s="11">
         <f>IF(OR($C37="",AU37=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU37,FIND("-",AU37)-1),"")=AW37,IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")=AX37),10,5*(SIGN((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))-(IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")))=SIGN((AW37)-(AX37)))+2*(((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))-(IFERROR(--MID(AU37,FIND("-",AU37)+1,99),"")))=((AW37)-(AX37)))+2*((IFERROR(--LEFT(AU37,FIND("-",AU37)-1),""))=(AW37))+2*((IFERROR(--MID(AU37,FIND("-",AU37)+1,99),""))=(AX37))),""))</f>
-        <v/>
-      </c>
-      <c r="AW37" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW37" s="11">
         <f>IF($C37="","",IFERROR(--LEFT($C37,FIND("-",$C37)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX37" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX37" s="11">
         <f>IF($C37="","",IFERROR(--MID($C37,FIND("-",$C37)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
       <c r="B38" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C38" s="10"/>
+      <c r="C38" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="D38" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F38" s="11" t="str">
+      <c r="F38" s="11">
         <f>IF(OR($C38="",E38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E38,FIND("-",E38)-1),"")=AW38,IFERROR(--MID(E38,FIND("-",E38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))-(IFERROR(--MID(E38,FIND("-",E38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))-(IFERROR(--MID(E38,FIND("-",E38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(E38,FIND("-",E38)-1),""))=(AW38))+2*((IFERROR(--MID(E38,FIND("-",E38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="H38" s="11" t="str">
+      <c r="H38" s="11">
         <f>IF(OR($C38="",G38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G38,FIND("-",G38)-1),"")=AW38,IFERROR(--MID(G38,FIND("-",G38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))-(IFERROR(--MID(G38,FIND("-",G38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))-(IFERROR(--MID(G38,FIND("-",G38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(G38,FIND("-",G38)-1),""))=(AW38))+2*((IFERROR(--MID(G38,FIND("-",G38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J38" s="11" t="str">
+      <c r="J38" s="11">
         <f>IF(OR($C38="",I38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I38,FIND("-",I38)-1),"")=AW38,IFERROR(--MID(I38,FIND("-",I38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))-(IFERROR(--MID(I38,FIND("-",I38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))-(IFERROR(--MID(I38,FIND("-",I38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(I38,FIND("-",I38)-1),""))=(AW38))+2*((IFERROR(--MID(I38,FIND("-",I38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K38" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="L38" s="11" t="str">
+      <c r="L38" s="11">
         <f>IF(OR($C38="",K38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K38,FIND("-",K38)-1),"")=AW38,IFERROR(--MID(K38,FIND("-",K38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))-(IFERROR(--MID(K38,FIND("-",K38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))-(IFERROR(--MID(K38,FIND("-",K38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(K38,FIND("-",K38)-1),""))=(AW38))+2*((IFERROR(--MID(K38,FIND("-",K38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N38" s="11" t="str">
+      <c r="N38" s="11">
         <f>IF(OR($C38="",M38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M38,FIND("-",M38)-1),"")=AW38,IFERROR(--MID(M38,FIND("-",M38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))-(IFERROR(--MID(M38,FIND("-",M38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))-(IFERROR(--MID(M38,FIND("-",M38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(M38,FIND("-",M38)-1),""))=(AW38))+2*((IFERROR(--MID(M38,FIND("-",M38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P38" s="11" t="str">
+      <c r="P38" s="11">
         <f>IF(OR($C38="",O38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O38,FIND("-",O38)-1),"")=AW38,IFERROR(--MID(O38,FIND("-",O38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))-(IFERROR(--MID(O38,FIND("-",O38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))-(IFERROR(--MID(O38,FIND("-",O38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(O38,FIND("-",O38)-1),""))=(AW38))+2*((IFERROR(--MID(O38,FIND("-",O38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R38" s="11" t="str">
+      <c r="R38" s="11">
         <f>IF(OR($C38="",Q38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q38,FIND("-",Q38)-1),"")=AW38,IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))-(IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))-(IFERROR(--MID(Q38,FIND("-",Q38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(Q38,FIND("-",Q38)-1),""))=(AW38))+2*((IFERROR(--MID(Q38,FIND("-",Q38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S38" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T38" s="11" t="str">
+      <c r="T38" s="11">
         <f>IF(OR($C38="",S38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S38,FIND("-",S38)-1),"")=AW38,IFERROR(--MID(S38,FIND("-",S38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))-(IFERROR(--MID(S38,FIND("-",S38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))-(IFERROR(--MID(S38,FIND("-",S38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(S38,FIND("-",S38)-1),""))=(AW38))+2*((IFERROR(--MID(S38,FIND("-",S38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V38" s="11" t="str">
+      <c r="V38" s="11">
         <f>IF(OR($C38="",U38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U38,FIND("-",U38)-1),"")=AW38,IFERROR(--MID(U38,FIND("-",U38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))-(IFERROR(--MID(U38,FIND("-",U38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))-(IFERROR(--MID(U38,FIND("-",U38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(U38,FIND("-",U38)-1),""))=(AW38))+2*((IFERROR(--MID(U38,FIND("-",U38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X38" s="11" t="str">
+      <c r="X38" s="11">
         <f>IF(OR($C38="",W38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W38,FIND("-",W38)-1),"")=AW38,IFERROR(--MID(W38,FIND("-",W38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))-(IFERROR(--MID(W38,FIND("-",W38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))-(IFERROR(--MID(W38,FIND("-",W38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(W38,FIND("-",W38)-1),""))=(AW38))+2*((IFERROR(--MID(W38,FIND("-",W38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z38" s="11" t="str">
+      <c r="Z38" s="11">
         <f>IF(OR($C38="",Y38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y38,FIND("-",Y38)-1),"")=AW38,IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))-(IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))-(IFERROR(--MID(Y38,FIND("-",Y38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(Y38,FIND("-",Y38)-1),""))=(AW38))+2*((IFERROR(--MID(Y38,FIND("-",Y38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB38" s="11" t="str">
+      <c r="AB38" s="11">
         <f>IF(OR($C38="",AA38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA38,FIND("-",AA38)-1),"")=AW38,IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))-(IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))-(IFERROR(--MID(AA38,FIND("-",AA38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AA38,FIND("-",AA38)-1),""))=(AW38))+2*((IFERROR(--MID(AA38,FIND("-",AA38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC38" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD38" s="11" t="str">
+      <c r="AD38" s="11">
         <f>IF(OR($C38="",AC38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC38,FIND("-",AC38)-1),"")=AW38,IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))-(IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))-(IFERROR(--MID(AC38,FIND("-",AC38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AC38,FIND("-",AC38)-1),""))=(AW38))+2*((IFERROR(--MID(AC38,FIND("-",AC38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF38" s="11" t="str">
+      <c r="AF38" s="11">
         <f>IF(OR($C38="",AE38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE38,FIND("-",AE38)-1),"")=AW38,IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))-(IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))-(IFERROR(--MID(AE38,FIND("-",AE38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AE38,FIND("-",AE38)-1),""))=(AW38))+2*((IFERROR(--MID(AE38,FIND("-",AE38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AG38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH38" s="11" t="str">
+      <c r="AH38" s="11">
         <f>IF(OR($C38="",AG38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG38,FIND("-",AG38)-1),"")=AW38,IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))-(IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))-(IFERROR(--MID(AG38,FIND("-",AG38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AG38,FIND("-",AG38)-1),""))=(AW38))+2*((IFERROR(--MID(AG38,FIND("-",AG38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ38" s="11" t="str">
+      <c r="AJ38" s="11">
         <f>IF(OR($C38="",AI38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI38,FIND("-",AI38)-1),"")=AW38,IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))-(IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))-(IFERROR(--MID(AI38,FIND("-",AI38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AI38,FIND("-",AI38)-1),""))=(AW38))+2*((IFERROR(--MID(AI38,FIND("-",AI38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL38" s="11" t="str">
+      <c r="AL38" s="11">
         <f>IF(OR($C38="",AK38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK38,FIND("-",AK38)-1),"")=AW38,IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))-(IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))-(IFERROR(--MID(AK38,FIND("-",AK38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AK38,FIND("-",AK38)-1),""))=(AW38))+2*((IFERROR(--MID(AK38,FIND("-",AK38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM38" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AN38" s="11" t="str">
+      <c r="AN38" s="11">
         <f>IF(OR($C38="",AM38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM38,FIND("-",AM38)-1),"")=AW38,IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))-(IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))-(IFERROR(--MID(AM38,FIND("-",AM38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AM38,FIND("-",AM38)-1),""))=(AW38))+2*((IFERROR(--MID(AM38,FIND("-",AM38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AP38" s="11" t="str">
+      <c r="AP38" s="11">
         <f>IF(OR($C38="",AO38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO38,FIND("-",AO38)-1),"")=AW38,IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))-(IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))-(IFERROR(--MID(AO38,FIND("-",AO38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AO38,FIND("-",AO38)-1),""))=(AW38))+2*((IFERROR(--MID(AO38,FIND("-",AO38)+1,99),""))=(AX38))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ38" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR38" s="11" t="str">
+      <c r="AR38" s="11">
         <f t="shared" si="2"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS38" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT38" s="11" t="str">
+      <c r="AT38" s="11">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AV38" s="11" t="str">
+      <c r="AV38" s="11">
         <f>IF(OR($C38="",AU38=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU38,FIND("-",AU38)-1),"")=AW38,IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")=AX38),10,5*(SIGN((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))-(IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")))=SIGN((AW38)-(AX38)))+2*(((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))-(IFERROR(--MID(AU38,FIND("-",AU38)+1,99),"")))=((AW38)-(AX38)))+2*((IFERROR(--LEFT(AU38,FIND("-",AU38)-1),""))=(AW38))+2*((IFERROR(--MID(AU38,FIND("-",AU38)+1,99),""))=(AX38))),""))</f>
-        <v/>
-      </c>
-      <c r="AW38" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW38" s="11">
         <f>IF($C38="","",IFERROR(--LEFT($C38,FIND("-",$C38)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX38" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX38" s="11">
         <f>IF($C38="","",IFERROR(--MID($C38,FIND("-",$C38)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
@@ -6687,7 +6691,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="33" t="s">
         <v>103</v>
       </c>
@@ -6741,355 +6745,359 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="10"/>
+      <c r="C41" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D41" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F41" s="11" t="str">
+      <c r="F41" s="11">
         <f>IF(OR($C41="",E41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E41,FIND("-",E41)-1),"")=AW41,IFERROR(--MID(E41,FIND("-",E41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))-(IFERROR(--MID(E41,FIND("-",E41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))-(IFERROR(--MID(E41,FIND("-",E41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(E41,FIND("-",E41)-1),""))=(AW41))+2*((IFERROR(--MID(E41,FIND("-",E41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H41" s="11" t="str">
+      <c r="H41" s="11">
         <f>IF(OR($C41="",G41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G41,FIND("-",G41)-1),"")=AW41,IFERROR(--MID(G41,FIND("-",G41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))-(IFERROR(--MID(G41,FIND("-",G41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))-(IFERROR(--MID(G41,FIND("-",G41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(G41,FIND("-",G41)-1),""))=(AW41))+2*((IFERROR(--MID(G41,FIND("-",G41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J41" s="11" t="str">
+      <c r="J41" s="11">
         <f>IF(OR($C41="",I41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I41,FIND("-",I41)-1),"")=AW41,IFERROR(--MID(I41,FIND("-",I41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))-(IFERROR(--MID(I41,FIND("-",I41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))-(IFERROR(--MID(I41,FIND("-",I41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(I41,FIND("-",I41)-1),""))=(AW41))+2*((IFERROR(--MID(I41,FIND("-",I41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="11" t="str">
+      <c r="L41" s="11">
         <f>IF(OR($C41="",K41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K41,FIND("-",K41)-1),"")=AW41,IFERROR(--MID(K41,FIND("-",K41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))-(IFERROR(--MID(K41,FIND("-",K41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))-(IFERROR(--MID(K41,FIND("-",K41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(K41,FIND("-",K41)-1),""))=(AW41))+2*((IFERROR(--MID(K41,FIND("-",K41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N41" s="11" t="str">
+      <c r="N41" s="11">
         <f>IF(OR($C41="",M41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M41,FIND("-",M41)-1),"")=AW41,IFERROR(--MID(M41,FIND("-",M41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))-(IFERROR(--MID(M41,FIND("-",M41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))-(IFERROR(--MID(M41,FIND("-",M41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(M41,FIND("-",M41)-1),""))=(AW41))+2*((IFERROR(--MID(M41,FIND("-",M41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O41" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P41" s="11" t="str">
+      <c r="P41" s="11">
         <f>IF(OR($C41="",O41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O41,FIND("-",O41)-1),"")=AW41,IFERROR(--MID(O41,FIND("-",O41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))-(IFERROR(--MID(O41,FIND("-",O41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))-(IFERROR(--MID(O41,FIND("-",O41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(O41,FIND("-",O41)-1),""))=(AW41))+2*((IFERROR(--MID(O41,FIND("-",O41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q41" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R41" s="11" t="str">
+      <c r="R41" s="11">
         <f>IF(OR($C41="",Q41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q41,FIND("-",Q41)-1),"")=AW41,IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))-(IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))-(IFERROR(--MID(Q41,FIND("-",Q41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(Q41,FIND("-",Q41)-1),""))=(AW41))+2*((IFERROR(--MID(Q41,FIND("-",Q41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T41" s="11" t="str">
+      <c r="T41" s="11">
         <f>IF(OR($C41="",S41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S41,FIND("-",S41)-1),"")=AW41,IFERROR(--MID(S41,FIND("-",S41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))-(IFERROR(--MID(S41,FIND("-",S41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))-(IFERROR(--MID(S41,FIND("-",S41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(S41,FIND("-",S41)-1),""))=(AW41))+2*((IFERROR(--MID(S41,FIND("-",S41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V41" s="11" t="str">
+      <c r="V41" s="11">
         <f>IF(OR($C41="",U41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U41,FIND("-",U41)-1),"")=AW41,IFERROR(--MID(U41,FIND("-",U41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))-(IFERROR(--MID(U41,FIND("-",U41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))-(IFERROR(--MID(U41,FIND("-",U41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(U41,FIND("-",U41)-1),""))=(AW41))+2*((IFERROR(--MID(U41,FIND("-",U41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X41" s="11" t="str">
+      <c r="X41" s="11">
         <f>IF(OR($C41="",W41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W41,FIND("-",W41)-1),"")=AW41,IFERROR(--MID(W41,FIND("-",W41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))-(IFERROR(--MID(W41,FIND("-",W41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))-(IFERROR(--MID(W41,FIND("-",W41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(W41,FIND("-",W41)-1),""))=(AW41))+2*((IFERROR(--MID(W41,FIND("-",W41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z41" s="11" t="str">
+      <c r="Z41" s="11">
         <f>IF(OR($C41="",Y41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y41,FIND("-",Y41)-1),"")=AW41,IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))-(IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))-(IFERROR(--MID(Y41,FIND("-",Y41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(Y41,FIND("-",Y41)-1),""))=(AW41))+2*((IFERROR(--MID(Y41,FIND("-",Y41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AB41" s="11" t="str">
+      <c r="AB41" s="11">
         <f>IF(OR($C41="",AA41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA41,FIND("-",AA41)-1),"")=AW41,IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))-(IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))-(IFERROR(--MID(AA41,FIND("-",AA41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AA41,FIND("-",AA41)-1),""))=(AW41))+2*((IFERROR(--MID(AA41,FIND("-",AA41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD41" s="11" t="str">
+      <c r="AD41" s="11">
         <f>IF(OR($C41="",AC41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC41,FIND("-",AC41)-1),"")=AW41,IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))-(IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))-(IFERROR(--MID(AC41,FIND("-",AC41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AC41,FIND("-",AC41)-1),""))=(AW41))+2*((IFERROR(--MID(AC41,FIND("-",AC41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE41" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF41" s="11" t="str">
+      <c r="AF41" s="11">
         <f>IF(OR($C41="",AE41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE41,FIND("-",AE41)-1),"")=AW41,IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))-(IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))-(IFERROR(--MID(AE41,FIND("-",AE41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AE41,FIND("-",AE41)-1),""))=(AW41))+2*((IFERROR(--MID(AE41,FIND("-",AE41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG41" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH41" s="11" t="str">
+      <c r="AH41" s="11">
         <f>IF(OR($C41="",AG41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG41,FIND("-",AG41)-1),"")=AW41,IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))-(IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))-(IFERROR(--MID(AG41,FIND("-",AG41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AG41,FIND("-",AG41)-1),""))=(AW41))+2*((IFERROR(--MID(AG41,FIND("-",AG41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ41" s="11" t="str">
+      <c r="AJ41" s="11">
         <f>IF(OR($C41="",AI41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI41,FIND("-",AI41)-1),"")=AW41,IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))-(IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))-(IFERROR(--MID(AI41,FIND("-",AI41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AI41,FIND("-",AI41)-1),""))=(AW41))+2*((IFERROR(--MID(AI41,FIND("-",AI41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL41" s="11" t="str">
+      <c r="AL41" s="11">
         <f>IF(OR($C41="",AK41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK41,FIND("-",AK41)-1),"")=AW41,IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))-(IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))-(IFERROR(--MID(AK41,FIND("-",AK41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AK41,FIND("-",AK41)-1),""))=(AW41))+2*((IFERROR(--MID(AK41,FIND("-",AK41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM41" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN41" s="11" t="str">
+      <c r="AN41" s="11">
         <f>IF(OR($C41="",AM41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM41,FIND("-",AM41)-1),"")=AW41,IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))-(IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))-(IFERROR(--MID(AM41,FIND("-",AM41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AM41,FIND("-",AM41)-1),""))=(AW41))+2*((IFERROR(--MID(AM41,FIND("-",AM41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP41" s="11" t="str">
+      <c r="AP41" s="11">
         <f>IF(OR($C41="",AO41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO41,FIND("-",AO41)-1),"")=AW41,IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))-(IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))-(IFERROR(--MID(AO41,FIND("-",AO41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AO41,FIND("-",AO41)-1),""))=(AW41))+2*((IFERROR(--MID(AO41,FIND("-",AO41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ41" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR41" s="11" t="str">
+      <c r="AR41" s="11">
         <f>IF(OR($C41="",AQ41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),"")=AW41,IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))-(IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))-(IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AQ41,FIND("-",AQ41)-1),""))=(AW41))+2*((IFERROR(--MID(AQ41,FIND("-",AQ41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS41" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AT41" s="11" t="str">
+      <c r="AT41" s="11">
         <f>IF(OR($C41="",AS41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS41,FIND("-",AS41)-1),"")=AW41,IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))-(IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))-(IFERROR(--MID(AS41,FIND("-",AS41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AS41,FIND("-",AS41)-1),""))=(AW41))+2*((IFERROR(--MID(AS41,FIND("-",AS41)+1,99),""))=(AX41))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU41" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV41" s="11" t="str">
+      <c r="AV41" s="11">
         <f>IF(OR($C41="",AU41=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU41,FIND("-",AU41)-1),"")=AW41,IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")=AX41),10,5*(SIGN((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))-(IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")))=SIGN((AW41)-(AX41)))+2*(((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))-(IFERROR(--MID(AU41,FIND("-",AU41)+1,99),"")))=((AW41)-(AX41)))+2*((IFERROR(--LEFT(AU41,FIND("-",AU41)-1),""))=(AW41))+2*((IFERROR(--MID(AU41,FIND("-",AU41)+1,99),""))=(AX41))),""))</f>
-        <v/>
-      </c>
-      <c r="AW41" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW41" s="11">
         <f>IF($C41="","",IFERROR(--LEFT($C41,FIND("-",$C41)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX41" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX41" s="11">
         <f>IF($C41="","",IFERROR(--MID($C41,FIND("-",$C41)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
       <c r="B42" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="C42" s="10"/>
+      <c r="C42" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="D42" s="1" t="s">
         <v>108</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="11" t="str">
+      <c r="F42" s="11">
         <f>IF(OR($C42="",E42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E42,FIND("-",E42)-1),"")=AW42,IFERROR(--MID(E42,FIND("-",E42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))-(IFERROR(--MID(E42,FIND("-",E42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))-(IFERROR(--MID(E42,FIND("-",E42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(E42,FIND("-",E42)-1),""))=(AW42))+2*((IFERROR(--MID(E42,FIND("-",E42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H42" s="11" t="str">
+      <c r="H42" s="11">
         <f>IF(OR($C42="",G42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G42,FIND("-",G42)-1),"")=AW42,IFERROR(--MID(G42,FIND("-",G42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))-(IFERROR(--MID(G42,FIND("-",G42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))-(IFERROR(--MID(G42,FIND("-",G42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(G42,FIND("-",G42)-1),""))=(AW42))+2*((IFERROR(--MID(G42,FIND("-",G42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J42" s="11" t="str">
+      <c r="J42" s="11">
         <f>IF(OR($C42="",I42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I42,FIND("-",I42)-1),"")=AW42,IFERROR(--MID(I42,FIND("-",I42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))-(IFERROR(--MID(I42,FIND("-",I42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))-(IFERROR(--MID(I42,FIND("-",I42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(I42,FIND("-",I42)-1),""))=(AW42))+2*((IFERROR(--MID(I42,FIND("-",I42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L42" s="11" t="str">
+      <c r="L42" s="11">
         <f>IF(OR($C42="",K42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K42,FIND("-",K42)-1),"")=AW42,IFERROR(--MID(K42,FIND("-",K42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))-(IFERROR(--MID(K42,FIND("-",K42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))-(IFERROR(--MID(K42,FIND("-",K42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(K42,FIND("-",K42)-1),""))=(AW42))+2*((IFERROR(--MID(K42,FIND("-",K42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M42" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N42" s="11" t="str">
+      <c r="N42" s="11">
         <f>IF(OR($C42="",M42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M42,FIND("-",M42)-1),"")=AW42,IFERROR(--MID(M42,FIND("-",M42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))-(IFERROR(--MID(M42,FIND("-",M42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))-(IFERROR(--MID(M42,FIND("-",M42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(M42,FIND("-",M42)-1),""))=(AW42))+2*((IFERROR(--MID(M42,FIND("-",M42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O42" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="P42" s="11" t="str">
+      <c r="P42" s="11">
         <f>IF(OR($C42="",O42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O42,FIND("-",O42)-1),"")=AW42,IFERROR(--MID(O42,FIND("-",O42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))-(IFERROR(--MID(O42,FIND("-",O42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))-(IFERROR(--MID(O42,FIND("-",O42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(O42,FIND("-",O42)-1),""))=(AW42))+2*((IFERROR(--MID(O42,FIND("-",O42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q42" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="R42" s="11" t="str">
+      <c r="R42" s="11">
         <f>IF(OR($C42="",Q42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q42,FIND("-",Q42)-1),"")=AW42,IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))-(IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))-(IFERROR(--MID(Q42,FIND("-",Q42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(Q42,FIND("-",Q42)-1),""))=(AW42))+2*((IFERROR(--MID(Q42,FIND("-",Q42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T42" s="11" t="str">
+      <c r="T42" s="11">
         <f>IF(OR($C42="",S42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S42,FIND("-",S42)-1),"")=AW42,IFERROR(--MID(S42,FIND("-",S42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))-(IFERROR(--MID(S42,FIND("-",S42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))-(IFERROR(--MID(S42,FIND("-",S42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(S42,FIND("-",S42)-1),""))=(AW42))+2*((IFERROR(--MID(S42,FIND("-",S42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U42" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="V42" s="11" t="str">
+      <c r="V42" s="11">
         <f>IF(OR($C42="",U42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U42,FIND("-",U42)-1),"")=AW42,IFERROR(--MID(U42,FIND("-",U42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))-(IFERROR(--MID(U42,FIND("-",U42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))-(IFERROR(--MID(U42,FIND("-",U42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(U42,FIND("-",U42)-1),""))=(AW42))+2*((IFERROR(--MID(U42,FIND("-",U42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X42" s="11" t="str">
+      <c r="X42" s="11">
         <f>IF(OR($C42="",W42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W42,FIND("-",W42)-1),"")=AW42,IFERROR(--MID(W42,FIND("-",W42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))-(IFERROR(--MID(W42,FIND("-",W42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))-(IFERROR(--MID(W42,FIND("-",W42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(W42,FIND("-",W42)-1),""))=(AW42))+2*((IFERROR(--MID(W42,FIND("-",W42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Z42" s="11" t="str">
+      <c r="Z42" s="11">
         <f>IF(OR($C42="",Y42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y42,FIND("-",Y42)-1),"")=AW42,IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))-(IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))-(IFERROR(--MID(Y42,FIND("-",Y42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(Y42,FIND("-",Y42)-1),""))=(AW42))+2*((IFERROR(--MID(Y42,FIND("-",Y42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB42" s="11" t="str">
+      <c r="AB42" s="11">
         <f>IF(OR($C42="",AA42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA42,FIND("-",AA42)-1),"")=AW42,IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))-(IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))-(IFERROR(--MID(AA42,FIND("-",AA42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AA42,FIND("-",AA42)-1),""))=(AW42))+2*((IFERROR(--MID(AA42,FIND("-",AA42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD42" s="11" t="str">
+      <c r="AD42" s="11">
         <f>IF(OR($C42="",AC42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC42,FIND("-",AC42)-1),"")=AW42,IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))-(IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))-(IFERROR(--MID(AC42,FIND("-",AC42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AC42,FIND("-",AC42)-1),""))=(AW42))+2*((IFERROR(--MID(AC42,FIND("-",AC42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF42" s="11" t="str">
+      <c r="AF42" s="11">
         <f>IF(OR($C42="",AE42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE42,FIND("-",AE42)-1),"")=AW42,IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))-(IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))-(IFERROR(--MID(AE42,FIND("-",AE42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AE42,FIND("-",AE42)-1),""))=(AW42))+2*((IFERROR(--MID(AE42,FIND("-",AE42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH42" s="11" t="str">
+      <c r="AH42" s="11">
         <f>IF(OR($C42="",AG42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG42,FIND("-",AG42)-1),"")=AW42,IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))-(IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))-(IFERROR(--MID(AG42,FIND("-",AG42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AG42,FIND("-",AG42)-1),""))=(AW42))+2*((IFERROR(--MID(AG42,FIND("-",AG42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AJ42" s="11" t="str">
+      <c r="AJ42" s="11">
         <f>IF(OR($C42="",AI42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI42,FIND("-",AI42)-1),"")=AW42,IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))-(IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))-(IFERROR(--MID(AI42,FIND("-",AI42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AI42,FIND("-",AI42)-1),""))=(AW42))+2*((IFERROR(--MID(AI42,FIND("-",AI42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK42" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL42" s="11" t="str">
+      <c r="AL42" s="11">
         <f>IF(OR($C42="",AK42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK42,FIND("-",AK42)-1),"")=AW42,IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))-(IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))-(IFERROR(--MID(AK42,FIND("-",AK42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AK42,FIND("-",AK42)-1),""))=(AW42))+2*((IFERROR(--MID(AK42,FIND("-",AK42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN42" s="11" t="str">
+      <c r="AN42" s="11">
         <f>IF(OR($C42="",AM42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM42,FIND("-",AM42)-1),"")=AW42,IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))-(IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))-(IFERROR(--MID(AM42,FIND("-",AM42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AM42,FIND("-",AM42)-1),""))=(AW42))+2*((IFERROR(--MID(AM42,FIND("-",AM42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP42" s="11" t="str">
+      <c r="AP42" s="11">
         <f>IF(OR($C42="",AO42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO42,FIND("-",AO42)-1),"")=AW42,IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))-(IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))-(IFERROR(--MID(AO42,FIND("-",AO42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AO42,FIND("-",AO42)-1),""))=(AW42))+2*((IFERROR(--MID(AO42,FIND("-",AO42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR42" s="11" t="str">
+      <c r="AR42" s="11">
         <f>IF(OR($C42="",AQ42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),"")=AW42,IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))-(IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))-(IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AQ42,FIND("-",AQ42)-1),""))=(AW42))+2*((IFERROR(--MID(AQ42,FIND("-",AQ42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT42" s="11" t="str">
+      <c r="AT42" s="11">
         <f>IF(OR($C42="",AS42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS42,FIND("-",AS42)-1),"")=AW42,IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))-(IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))-(IFERROR(--MID(AS42,FIND("-",AS42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AS42,FIND("-",AS42)-1),""))=(AW42))+2*((IFERROR(--MID(AS42,FIND("-",AS42)+1,99),""))=(AX42))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU42" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AV42" s="11" t="str">
+      <c r="AV42" s="11">
         <f>IF(OR($C42="",AU42=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU42,FIND("-",AU42)-1),"")=AW42,IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")=AX42),10,5*(SIGN((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))-(IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")))=SIGN((AW42)-(AX42)))+2*(((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))-(IFERROR(--MID(AU42,FIND("-",AU42)+1,99),"")))=((AW42)-(AX42)))+2*((IFERROR(--LEFT(AU42,FIND("-",AU42)-1),""))=(AW42))+2*((IFERROR(--MID(AU42,FIND("-",AU42)+1,99),""))=(AX42))),""))</f>
-        <v/>
-      </c>
-      <c r="AW42" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW42" s="11">
         <f>IF($C42="","",IFERROR(--LEFT($C42,FIND("-",$C42)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX42" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX42" s="11">
         <f>IF($C42="","",IFERROR(--MID($C42,FIND("-",$C42)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7263,7 +7271,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7437,7 +7445,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="18"/>
       <c r="C45" s="13"/>
@@ -7495,7 +7503,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>110</v>
       </c>
@@ -7549,7 +7557,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7723,7 +7731,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7897,7 +7905,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8071,7 +8079,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="18"/>
       <c r="C50" s="13"/>
@@ -8129,7 +8137,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="33" t="s">
         <v>111</v>
       </c>
@@ -8183,7 +8191,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8357,7 +8365,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8531,7 +8539,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8705,7 +8713,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8879,7 +8887,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9053,7 +9061,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
       <c r="B57" s="18"/>
       <c r="C57" s="13"/>
@@ -9111,7 +9119,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="33" t="s">
         <v>114</v>
       </c>
@@ -9165,7 +9173,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9339,7 +9347,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9513,7 +9521,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9687,7 +9695,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9861,7 +9869,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
       <c r="B63" s="18"/>
       <c r="C63" s="13"/>
@@ -9919,7 +9927,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>116</v>
       </c>
@@ -9973,7 +9981,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10147,7 +10155,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10321,7 +10329,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10495,7 +10503,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10669,7 +10677,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12"/>
       <c r="B69" s="18"/>
       <c r="C69" s="13"/>
@@ -10727,7 +10735,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="33" t="s">
         <v>117</v>
       </c>
@@ -10781,7 +10789,7 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -10955,7 +10963,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11129,7 +11137,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11303,7 +11311,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11477,7 +11485,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
       <c r="B75" s="18"/>
       <c r="C75" s="13"/>
@@ -11535,7 +11543,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="33" t="s">
         <v>118</v>
       </c>
@@ -11589,7 +11597,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11763,7 +11771,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -11937,7 +11945,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12111,7 +12119,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12285,7 +12293,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="18"/>
       <c r="C81" s="13"/>
@@ -12343,7 +12351,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="33" t="s">
         <v>119</v>
       </c>
@@ -12397,7 +12405,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12571,7 +12579,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12745,7 +12753,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -12919,7 +12927,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13093,7 +13101,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13267,7 +13275,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13441,7 +13449,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12"/>
       <c r="B89" s="18"/>
       <c r="C89" s="13"/>
@@ -13499,7 +13507,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="33" t="s">
         <v>122</v>
       </c>
@@ -13553,7 +13561,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13727,7 +13735,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13901,7 +13909,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14075,7 +14083,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14249,7 +14257,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14423,7 +14431,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14597,7 +14605,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="18"/>
       <c r="C97" s="13"/>
@@ -14655,7 +14663,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="33" t="s">
         <v>125</v>
       </c>
@@ -14709,7 +14717,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14883,7 +14891,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15057,7 +15065,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15231,7 +15239,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15405,7 +15413,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15579,7 +15587,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15753,7 +15761,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="18"/>
       <c r="C105" s="13"/>
@@ -15811,7 +15819,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>126</v>
       </c>
@@ -15865,7 +15873,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16039,7 +16047,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16213,7 +16221,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16387,7 +16395,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16561,7 +16569,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="18"/>
       <c r="C111" s="13"/>
@@ -16619,7 +16627,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="18"/>
       <c r="C112" s="13"/>
@@ -16677,7 +16685,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="38" t="s">
         <v>128</v>
       </c>
@@ -16731,7 +16739,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="33" t="s">
         <v>126</v>
       </c>
@@ -16785,7 +16793,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -16915,7 +16923,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="18"/>
       <c r="C116" s="13"/>
@@ -16973,7 +16981,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="33" t="s">
         <v>131</v>
       </c>
@@ -17027,7 +17035,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17157,7 +17165,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17287,7 +17295,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="18"/>
       <c r="C120" s="13"/>
@@ -17345,7 +17353,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="33" t="s">
         <v>136</v>
       </c>
@@ -17399,7 +17407,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17529,7 +17537,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17659,7 +17667,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17789,7 +17797,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="18"/>
       <c r="C125" s="13"/>
@@ -17847,7 +17855,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="33" t="s">
         <v>143</v>
       </c>
@@ -17901,7 +17909,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18031,7 +18039,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18161,7 +18169,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18291,7 +18299,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="18"/>
       <c r="C130" s="13"/>
@@ -18349,7 +18357,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="33" t="s">
         <v>150</v>
       </c>
@@ -18403,7 +18411,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18533,7 +18541,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18663,7 +18671,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="18"/>
       <c r="C134" s="13"/>
@@ -18721,7 +18729,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="33" t="s">
         <v>155</v>
       </c>
@@ -18775,7 +18783,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -18905,7 +18913,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19035,7 +19043,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19165,7 +19173,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="18"/>
       <c r="C139" s="13"/>
@@ -19223,7 +19231,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="33" t="s">
         <v>162</v>
       </c>
@@ -19277,7 +19285,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19407,7 +19415,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19537,7 +19545,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="18"/>
       <c r="C143" s="13"/>
@@ -19595,7 +19603,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="18"/>
       <c r="C144" s="13"/>
@@ -19653,7 +19661,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="38" t="s">
         <v>167</v>
       </c>
@@ -19707,7 +19715,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="33" t="s">
         <v>162</v>
       </c>
@@ -19761,7 +19769,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19891,7 +19899,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20021,7 +20029,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="18"/>
       <c r="C149" s="13"/>
@@ -20079,7 +20087,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="33" t="s">
         <v>172</v>
       </c>
@@ -20133,7 +20141,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20263,7 +20271,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="18"/>
       <c r="C152" s="13"/>
@@ -20321,7 +20329,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="33" t="s">
         <v>175</v>
       </c>
@@ -20375,7 +20383,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20505,7 +20513,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20635,7 +20643,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="18"/>
       <c r="C156" s="13"/>
@@ -20693,7 +20701,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="33" t="s">
         <v>180</v>
       </c>
@@ -20747,7 +20755,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20877,7 +20885,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21007,7 +21015,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21137,7 +21145,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="18"/>
       <c r="C161" s="13"/>
@@ -21195,7 +21203,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="18"/>
       <c r="C162" s="13"/>
@@ -21253,7 +21261,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="38" t="s">
         <v>187</v>
       </c>
@@ -21307,7 +21315,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="33" t="s">
         <v>188</v>
       </c>
@@ -21361,7 +21369,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21491,7 +21499,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="18"/>
       <c r="C166" s="13"/>
@@ -21549,7 +21557,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="33" t="s">
         <v>191</v>
       </c>
@@ -21603,7 +21611,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21733,7 +21741,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="18"/>
       <c r="C169" s="13"/>
@@ -21791,7 +21799,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="33" t="s">
         <v>194</v>
       </c>
@@ -21845,7 +21853,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -21975,7 +21983,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="18"/>
       <c r="C172" s="13"/>
@@ -22033,7 +22041,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="33" t="s">
         <v>197</v>
       </c>
@@ -22087,7 +22095,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22217,7 +22225,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="18"/>
       <c r="C175" s="13"/>
@@ -22275,7 +22283,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="18"/>
       <c r="C176" s="13"/>
@@ -22333,7 +22341,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="38" t="s">
         <v>200</v>
       </c>
@@ -22387,7 +22395,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="33" t="s">
         <v>201</v>
       </c>
@@ -22441,7 +22449,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22571,7 +22579,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="18"/>
       <c r="C180" s="13"/>
@@ -22629,7 +22637,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="33" t="s">
         <v>204</v>
       </c>
@@ -22683,7 +22691,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22813,7 +22821,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="18"/>
       <c r="C183" s="13"/>
@@ -22871,7 +22879,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="18"/>
       <c r="C184" s="13"/>
@@ -22929,7 +22937,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="38" t="s">
         <v>207</v>
       </c>
@@ -22983,7 +22991,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="33" t="s">
         <v>208</v>
       </c>
@@ -23037,7 +23045,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23167,7 +23175,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="18"/>
       <c r="C188" s="13"/>
@@ -23225,7 +23233,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="18"/>
       <c r="C189" s="13"/>
@@ -23283,7 +23291,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="38" t="s">
         <v>211</v>
       </c>
@@ -23337,7 +23345,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="33" t="s">
         <v>212</v>
       </c>
@@ -23391,7 +23399,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23521,7 +23529,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="18"/>
       <c r="C193" s="13"/>
@@ -23579,7 +23587,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="18"/>
       <c r="C194" s="13"/>
@@ -23639,6 +23647,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23655,60 +23717,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23718,58 +23726,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.36328125" customWidth="1"/>
+    <col min="2" max="2" width="75.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" customWidth="1"/>
-    <col min="12" max="12" width="12.54296875" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" customWidth="1"/>
-    <col min="14" max="14" width="12.54296875" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.54296875" customWidth="1"/>
-    <col min="16" max="16" width="12.54296875" style="23" customWidth="1"/>
-    <col min="17" max="17" width="10.54296875" customWidth="1"/>
-    <col min="18" max="18" width="12.54296875" style="23" customWidth="1"/>
-    <col min="19" max="19" width="10.54296875" customWidth="1"/>
-    <col min="20" max="20" width="12.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.54296875" customWidth="1"/>
-    <col min="22" max="22" width="12.54296875" style="23" customWidth="1"/>
-    <col min="23" max="23" width="10.54296875" customWidth="1"/>
-    <col min="24" max="24" width="12.54296875" style="23" customWidth="1"/>
-    <col min="25" max="25" width="10.54296875" customWidth="1"/>
-    <col min="26" max="26" width="12.54296875" style="23" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
-    <col min="28" max="28" width="12.54296875" style="23" customWidth="1"/>
-    <col min="29" max="29" width="10.54296875" customWidth="1"/>
-    <col min="30" max="30" width="12.54296875" style="23" customWidth="1"/>
-    <col min="31" max="31" width="10.54296875" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" style="23" customWidth="1"/>
-    <col min="33" max="33" width="10.54296875" customWidth="1"/>
-    <col min="34" max="34" width="12.54296875" style="23" customWidth="1"/>
-    <col min="35" max="35" width="10.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.54296875" style="23" customWidth="1"/>
-    <col min="37" max="37" width="10.54296875" customWidth="1"/>
-    <col min="38" max="38" width="12.54296875" style="23" customWidth="1"/>
-    <col min="39" max="39" width="10.54296875" customWidth="1"/>
-    <col min="40" max="40" width="12.54296875" style="23" customWidth="1"/>
-    <col min="41" max="41" width="10.54296875" customWidth="1"/>
-    <col min="42" max="42" width="12.54296875" customWidth="1"/>
-    <col min="43" max="43" width="10.54296875" customWidth="1"/>
-    <col min="44" max="44" width="12.54296875" style="23" customWidth="1"/>
-    <col min="45" max="45" width="10.54296875" customWidth="1"/>
-    <col min="46" max="46" width="12.54296875" style="23" customWidth="1"/>
-    <col min="47" max="47" width="10.54296875" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="23" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" style="23" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" customWidth="1"/>
+    <col min="22" max="22" width="12.5546875" style="23" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" customWidth="1"/>
+    <col min="24" max="24" width="12.5546875" style="23" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" customWidth="1"/>
+    <col min="26" max="26" width="12.5546875" style="23" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" customWidth="1"/>
+    <col min="28" max="28" width="12.5546875" style="23" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" customWidth="1"/>
+    <col min="30" max="30" width="12.5546875" style="23" customWidth="1"/>
+    <col min="31" max="31" width="10.5546875" customWidth="1"/>
+    <col min="32" max="32" width="12.5546875" style="23" customWidth="1"/>
+    <col min="33" max="33" width="10.5546875" customWidth="1"/>
+    <col min="34" max="34" width="12.5546875" style="23" customWidth="1"/>
+    <col min="35" max="35" width="10.5546875" customWidth="1"/>
+    <col min="36" max="36" width="12.5546875" style="23" customWidth="1"/>
+    <col min="37" max="37" width="10.5546875" customWidth="1"/>
+    <col min="38" max="38" width="12.5546875" style="23" customWidth="1"/>
+    <col min="39" max="39" width="10.5546875" customWidth="1"/>
+    <col min="40" max="40" width="12.5546875" style="23" customWidth="1"/>
+    <col min="41" max="41" width="10.5546875" customWidth="1"/>
+    <col min="42" max="42" width="12.5546875" customWidth="1"/>
+    <col min="43" max="43" width="10.5546875" customWidth="1"/>
+    <col min="44" max="44" width="12.5546875" style="23" customWidth="1"/>
+    <col min="45" max="45" width="10.5546875" customWidth="1"/>
+    <col min="46" max="46" width="12.5546875" style="23" customWidth="1"/>
+    <col min="47" max="47" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23875,14 +23883,14 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
-    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
       <c r="B2" s="25" t="s">
         <v>215</v>
@@ -24023,7 +24031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24186,7 +24194,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24349,7 +24357,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24512,7 +24520,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24675,7 +24683,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24838,7 +24846,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25001,7 +25009,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25164,7 +25172,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25327,7 +25335,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25490,7 +25498,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25653,7 +25661,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25816,7 +25824,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -25979,7 +25987,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26142,7 +26150,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26305,7 +26313,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26424,6 +26432,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26435,17 +26454,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26457,16 +26465,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.6328125" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>284</v>
       </c>
@@ -26475,7 +26483,7 @@
       <c r="D1" s="17"/>
       <c r="E1" s="17"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>285</v>
       </c>
@@ -26492,7 +26500,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
@@ -26503,7 +26511,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26511,10 +26519,10 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
@@ -26525,7 +26533,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26533,10 +26541,10 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
@@ -26547,7 +26555,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26555,406 +26563,406 @@
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
+      </c>
+      <c r="C6" s="11">
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>104</v>
+      </c>
+      <c r="D6" s="11">
+        <f>Bonus_beheer!AK17</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C6+D6</f>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>83</v>
-      </c>
-      <c r="D6" s="11">
+        <v>99</v>
+      </c>
+      <c r="D7" s="11">
         <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
-      <c r="E6" s="11">
-        <f>C6+D6</f>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>4</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
-      </c>
-      <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>83</v>
-      </c>
-      <c r="D7" s="11">
-        <f>Bonus_beheer!AK17</f>
-        <v>0</v>
-      </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>83</v>
+        <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>81</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>98</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
+      </c>
+      <c r="C9" s="11">
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>98</v>
+      </c>
+      <c r="D9" s="11">
+        <f>Bonus_beheer!AU18</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="11">
+        <f>C9+D9</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
+      </c>
+      <c r="C10" s="11">
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>98</v>
+      </c>
+      <c r="D10" s="11">
+        <f>Bonus_beheer!AU17</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="11">
+        <f>C10+D10</f>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>79</v>
-      </c>
-      <c r="D9" s="11">
+        <v>96</v>
+      </c>
+      <c r="D11" s="11">
         <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
-      <c r="E9" s="11">
-        <f>C9+D9</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
-      </c>
-      <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>79</v>
-      </c>
-      <c r="D10" s="11">
-        <f>Bonus_beheer!M17</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
-        <f>C10+D10</f>
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>7</v>
-      </c>
-      <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
-      </c>
-      <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>79</v>
-      </c>
-      <c r="D11" s="11">
-        <f>Bonus_beheer!Y17</f>
-        <v>0</v>
-      </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>77</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>93</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>10</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>77</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>93</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>92</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>76</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>92</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>75</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>90</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
         <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>75</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>90</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>75</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>74</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>86</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>73</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>85</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>72</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>84</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>70</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>84</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>68</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>77</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
         <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>63</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>73</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
@@ -26965,7 +26973,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26973,7 +26981,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -26993,20 +27001,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.6328125" hidden="1"/>
+    <col min="3" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="17"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27014,7 +27022,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27022,7 +27030,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27030,7 +27038,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27038,7 +27046,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27046,7 +27054,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27054,7 +27062,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27062,7 +27070,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27078,16 +27086,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" zeroHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.6328125" customWidth="1"/>
-    <col min="2" max="2" width="10.6328125" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+    <col min="1" max="1" width="55.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.6328125" hidden="1"/>
+    <col min="45" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>306</v>
       </c>
@@ -27135,7 +27143,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>291</v>
       </c>
@@ -27146,7 +27154,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27157,7 +27165,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27168,7 +27176,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27179,7 +27187,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27190,7 +27198,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27201,7 +27209,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27218,14 +27226,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>319</v>
       </c>
@@ -27236,7 +27244,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27247,7 +27255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27255,7 +27263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27263,7 +27271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27271,7 +27279,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27279,62 +27287,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>4</v>
       </c>
@@ -27345,14 +27353,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27551,27 +27557,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27596,9 +27595,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1510" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F24FD84A-C586-428C-BF4F-C42356C40300}"/>
+  <xr:revisionPtr revIDLastSave="1512" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253EDDE8-7343-4A6F-B3E3-31FAB1F8B949}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,22 +1730,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,9 +1838,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1985,53 +1985,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -7104,171 +7104,173 @@
       <c r="B43" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C43" s="10"/>
+      <c r="C43" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="D43" s="1" t="s">
         <v>32</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="11" t="str">
+      <c r="F43" s="11">
         <f>IF(OR($C43="",E43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E43,FIND("-",E43)-1),"")=AW43,IFERROR(--MID(E43,FIND("-",E43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))-(IFERROR(--MID(E43,FIND("-",E43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))-(IFERROR(--MID(E43,FIND("-",E43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(E43,FIND("-",E43)-1),""))=(AW43))+2*((IFERROR(--MID(E43,FIND("-",E43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="11" t="str">
+      <c r="H43" s="11">
         <f>IF(OR($C43="",G43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G43,FIND("-",G43)-1),"")=AW43,IFERROR(--MID(G43,FIND("-",G43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))-(IFERROR(--MID(G43,FIND("-",G43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))-(IFERROR(--MID(G43,FIND("-",G43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(G43,FIND("-",G43)-1),""))=(AW43))+2*((IFERROR(--MID(G43,FIND("-",G43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="I43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="11" t="str">
+      <c r="J43" s="11">
         <f>IF(OR($C43="",I43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I43,FIND("-",I43)-1),"")=AW43,IFERROR(--MID(I43,FIND("-",I43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))-(IFERROR(--MID(I43,FIND("-",I43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))-(IFERROR(--MID(I43,FIND("-",I43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(I43,FIND("-",I43)-1),""))=(AW43))+2*((IFERROR(--MID(I43,FIND("-",I43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L43" s="11" t="str">
+      <c r="L43" s="11">
         <f>IF(OR($C43="",K43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K43,FIND("-",K43)-1),"")=AW43,IFERROR(--MID(K43,FIND("-",K43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))-(IFERROR(--MID(K43,FIND("-",K43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))-(IFERROR(--MID(K43,FIND("-",K43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(K43,FIND("-",K43)-1),""))=(AW43))+2*((IFERROR(--MID(K43,FIND("-",K43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N43" s="11" t="str">
+      <c r="N43" s="11">
         <f>IF(OR($C43="",M43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M43,FIND("-",M43)-1),"")=AW43,IFERROR(--MID(M43,FIND("-",M43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))-(IFERROR(--MID(M43,FIND("-",M43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))-(IFERROR(--MID(M43,FIND("-",M43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(M43,FIND("-",M43)-1),""))=(AW43))+2*((IFERROR(--MID(M43,FIND("-",M43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P43" s="11" t="str">
+      <c r="P43" s="11">
         <f>IF(OR($C43="",O43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O43,FIND("-",O43)-1),"")=AW43,IFERROR(--MID(O43,FIND("-",O43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))-(IFERROR(--MID(O43,FIND("-",O43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))-(IFERROR(--MID(O43,FIND("-",O43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(O43,FIND("-",O43)-1),""))=(AW43))+2*((IFERROR(--MID(O43,FIND("-",O43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R43" s="11" t="str">
+      <c r="R43" s="11">
         <f>IF(OR($C43="",Q43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q43,FIND("-",Q43)-1),"")=AW43,IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))-(IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))-(IFERROR(--MID(Q43,FIND("-",Q43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(Q43,FIND("-",Q43)-1),""))=(AW43))+2*((IFERROR(--MID(Q43,FIND("-",Q43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S43" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T43" s="11" t="str">
+      <c r="T43" s="11">
         <f>IF(OR($C43="",S43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S43,FIND("-",S43)-1),"")=AW43,IFERROR(--MID(S43,FIND("-",S43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))-(IFERROR(--MID(S43,FIND("-",S43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))-(IFERROR(--MID(S43,FIND("-",S43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(S43,FIND("-",S43)-1),""))=(AW43))+2*((IFERROR(--MID(S43,FIND("-",S43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V43" s="11" t="str">
+      <c r="V43" s="11">
         <f>IF(OR($C43="",U43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U43,FIND("-",U43)-1),"")=AW43,IFERROR(--MID(U43,FIND("-",U43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))-(IFERROR(--MID(U43,FIND("-",U43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))-(IFERROR(--MID(U43,FIND("-",U43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(U43,FIND("-",U43)-1),""))=(AW43))+2*((IFERROR(--MID(U43,FIND("-",U43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W43" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X43" s="11" t="str">
+      <c r="X43" s="11">
         <f>IF(OR($C43="",W43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W43,FIND("-",W43)-1),"")=AW43,IFERROR(--MID(W43,FIND("-",W43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))-(IFERROR(--MID(W43,FIND("-",W43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))-(IFERROR(--MID(W43,FIND("-",W43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(W43,FIND("-",W43)-1),""))=(AW43))+2*((IFERROR(--MID(W43,FIND("-",W43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z43" s="11" t="str">
+      <c r="Z43" s="11">
         <f>IF(OR($C43="",Y43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y43,FIND("-",Y43)-1),"")=AW43,IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))-(IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))-(IFERROR(--MID(Y43,FIND("-",Y43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(Y43,FIND("-",Y43)-1),""))=(AW43))+2*((IFERROR(--MID(Y43,FIND("-",Y43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA43" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB43" s="11" t="str">
+      <c r="AB43" s="11">
         <f>IF(OR($C43="",AA43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA43,FIND("-",AA43)-1),"")=AW43,IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))-(IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))-(IFERROR(--MID(AA43,FIND("-",AA43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AA43,FIND("-",AA43)-1),""))=(AW43))+2*((IFERROR(--MID(AA43,FIND("-",AA43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC43" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AD43" s="11" t="str">
+      <c r="AD43" s="11">
         <f>IF(OR($C43="",AC43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC43,FIND("-",AC43)-1),"")=AW43,IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))-(IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))-(IFERROR(--MID(AC43,FIND("-",AC43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AC43,FIND("-",AC43)-1),""))=(AW43))+2*((IFERROR(--MID(AC43,FIND("-",AC43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF43" s="11" t="str">
+      <c r="AF43" s="11">
         <f>IF(OR($C43="",AE43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE43,FIND("-",AE43)-1),"")=AW43,IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))-(IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))-(IFERROR(--MID(AE43,FIND("-",AE43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AE43,FIND("-",AE43)-1),""))=(AW43))+2*((IFERROR(--MID(AE43,FIND("-",AE43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH43" s="11" t="str">
+      <c r="AH43" s="11">
         <f>IF(OR($C43="",AG43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG43,FIND("-",AG43)-1),"")=AW43,IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))-(IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))-(IFERROR(--MID(AG43,FIND("-",AG43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AG43,FIND("-",AG43)-1),""))=(AW43))+2*((IFERROR(--MID(AG43,FIND("-",AG43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ43" s="11" t="str">
+      <c r="AJ43" s="11">
         <f>IF(OR($C43="",AI43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI43,FIND("-",AI43)-1),"")=AW43,IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))-(IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))-(IFERROR(--MID(AI43,FIND("-",AI43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AI43,FIND("-",AI43)-1),""))=(AW43))+2*((IFERROR(--MID(AI43,FIND("-",AI43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL43" s="11" t="str">
+      <c r="AL43" s="11">
         <f>IF(OR($C43="",AK43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK43,FIND("-",AK43)-1),"")=AW43,IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))-(IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))-(IFERROR(--MID(AK43,FIND("-",AK43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AK43,FIND("-",AK43)-1),""))=(AW43))+2*((IFERROR(--MID(AK43,FIND("-",AK43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN43" s="11" t="str">
+      <c r="AN43" s="11">
         <f>IF(OR($C43="",AM43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM43,FIND("-",AM43)-1),"")=AW43,IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))-(IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))-(IFERROR(--MID(AM43,FIND("-",AM43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AM43,FIND("-",AM43)-1),""))=(AW43))+2*((IFERROR(--MID(AM43,FIND("-",AM43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AO43" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AP43" s="11" t="str">
+      <c r="AP43" s="11">
         <f>IF(OR($C43="",AO43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO43,FIND("-",AO43)-1),"")=AW43,IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))-(IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))-(IFERROR(--MID(AO43,FIND("-",AO43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AO43,FIND("-",AO43)-1),""))=(AW43))+2*((IFERROR(--MID(AO43,FIND("-",AO43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ43" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR43" s="11" t="str">
+      <c r="AR43" s="11">
         <f>IF(OR($C43="",AQ43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),"")=AW43,IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))-(IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))-(IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AQ43,FIND("-",AQ43)-1),""))=(AW43))+2*((IFERROR(--MID(AQ43,FIND("-",AQ43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT43" s="11" t="str">
+      <c r="AT43" s="11">
         <f>IF(OR($C43="",AS43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS43,FIND("-",AS43)-1),"")=AW43,IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))-(IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))-(IFERROR(--MID(AS43,FIND("-",AS43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AS43,FIND("-",AS43)-1),""))=(AW43))+2*((IFERROR(--MID(AS43,FIND("-",AS43)+1,99),""))=(AX43))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU43" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV43" s="11" t="str">
+      <c r="AV43" s="11">
         <f>IF(OR($C43="",AU43=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU43,FIND("-",AU43)-1),"")=AW43,IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")=AX43),10,5*(SIGN((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))-(IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")))=SIGN((AW43)-(AX43)))+2*(((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))-(IFERROR(--MID(AU43,FIND("-",AU43)+1,99),"")))=((AW43)-(AX43)))+2*((IFERROR(--LEFT(AU43,FIND("-",AU43)-1),""))=(AW43))+2*((IFERROR(--MID(AU43,FIND("-",AU43)+1,99),""))=(AX43))),""))</f>
-        <v/>
-      </c>
-      <c r="AW43" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW43" s="11">
         <f>IF($C43="","",IFERROR(--LEFT($C43,FIND("-",$C43)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX43" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX43" s="11">
         <f>IF($C43="","",IFERROR(--MID($C43,FIND("-",$C43)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -23647,6 +23649,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23663,60 +23719,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23883,12 +23885,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
@@ -26432,6 +26434,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26443,17 +26456,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26506,20 +26508,20 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>115</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>118</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26528,20 +26530,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>111</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>117</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26569,23 +26571,23 @@
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>104</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>109</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26594,20 +26596,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>99</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>106</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26621,7 +26623,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26629,46 +26631,46 @@
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>98</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>99</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
         <v>98</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
@@ -26679,67 +26681,67 @@
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>96</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>98</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>93</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>98</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>93</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>95</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26748,20 +26750,20 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>92</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>93</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26770,20 +26772,20 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>92</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>93</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26792,20 +26794,20 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>90</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>92</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26814,20 +26816,20 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>90</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>92</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26836,20 +26838,20 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>86</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>90</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26858,20 +26860,20 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>85</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>88</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26885,7 +26887,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -26893,7 +26895,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26907,7 +26909,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -26915,7 +26917,7 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26924,20 +26926,20 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>77</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>80</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -26946,20 +26948,20 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>73</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>79</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -26973,7 +26975,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26981,7 +26983,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -27353,12 +27355,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27557,20 +27561,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27595,18 +27606,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1512" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{253EDDE8-7343-4A6F-B3E3-31FAB1F8B949}"/>
+  <xr:revisionPtr revIDLastSave="1513" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{259CDF07-A5BB-480B-B910-9F07BA4EFE59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2329" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1348,21 +1348,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,22 +1730,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1825,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,9 +1838,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1985,53 +1985,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -7740,171 +7740,173 @@
       <c r="B48" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="10"/>
+      <c r="C48" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="11" t="str">
+      <c r="F48" s="11">
         <f>IF(OR($C48="",E48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E48,FIND("-",E48)-1),"")=AW48,IFERROR(--MID(E48,FIND("-",E48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))-(IFERROR(--MID(E48,FIND("-",E48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))-(IFERROR(--MID(E48,FIND("-",E48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(E48,FIND("-",E48)-1),""))=(AW48))+2*((IFERROR(--MID(E48,FIND("-",E48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H48" s="11" t="str">
+      <c r="H48" s="11">
         <f>IF(OR($C48="",G48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G48,FIND("-",G48)-1),"")=AW48,IFERROR(--MID(G48,FIND("-",G48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))-(IFERROR(--MID(G48,FIND("-",G48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))-(IFERROR(--MID(G48,FIND("-",G48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(G48,FIND("-",G48)-1),""))=(AW48))+2*((IFERROR(--MID(G48,FIND("-",G48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J48" s="11" t="str">
+      <c r="J48" s="11">
         <f>IF(OR($C48="",I48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I48,FIND("-",I48)-1),"")=AW48,IFERROR(--MID(I48,FIND("-",I48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))-(IFERROR(--MID(I48,FIND("-",I48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))-(IFERROR(--MID(I48,FIND("-",I48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(I48,FIND("-",I48)-1),""))=(AW48))+2*((IFERROR(--MID(I48,FIND("-",I48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K48" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="L48" s="11" t="str">
+      <c r="L48" s="11">
         <f>IF(OR($C48="",K48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K48,FIND("-",K48)-1),"")=AW48,IFERROR(--MID(K48,FIND("-",K48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))-(IFERROR(--MID(K48,FIND("-",K48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))-(IFERROR(--MID(K48,FIND("-",K48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(K48,FIND("-",K48)-1),""))=(AW48))+2*((IFERROR(--MID(K48,FIND("-",K48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N48" s="11" t="str">
+      <c r="N48" s="11">
         <f>IF(OR($C48="",M48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M48,FIND("-",M48)-1),"")=AW48,IFERROR(--MID(M48,FIND("-",M48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))-(IFERROR(--MID(M48,FIND("-",M48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))-(IFERROR(--MID(M48,FIND("-",M48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(M48,FIND("-",M48)-1),""))=(AW48))+2*((IFERROR(--MID(M48,FIND("-",M48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P48" s="11" t="str">
+      <c r="P48" s="11">
         <f>IF(OR($C48="",O48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O48,FIND("-",O48)-1),"")=AW48,IFERROR(--MID(O48,FIND("-",O48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))-(IFERROR(--MID(O48,FIND("-",O48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))-(IFERROR(--MID(O48,FIND("-",O48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(O48,FIND("-",O48)-1),""))=(AW48))+2*((IFERROR(--MID(O48,FIND("-",O48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q48" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="R48" s="11" t="str">
+      <c r="R48" s="11">
         <f>IF(OR($C48="",Q48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q48,FIND("-",Q48)-1),"")=AW48,IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))-(IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))-(IFERROR(--MID(Q48,FIND("-",Q48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(Q48,FIND("-",Q48)-1),""))=(AW48))+2*((IFERROR(--MID(Q48,FIND("-",Q48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S48" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="T48" s="11" t="str">
+      <c r="T48" s="11">
         <f>IF(OR($C48="",S48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S48,FIND("-",S48)-1),"")=AW48,IFERROR(--MID(S48,FIND("-",S48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))-(IFERROR(--MID(S48,FIND("-",S48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))-(IFERROR(--MID(S48,FIND("-",S48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(S48,FIND("-",S48)-1),""))=(AW48))+2*((IFERROR(--MID(S48,FIND("-",S48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V48" s="11" t="str">
+      <c r="V48" s="11">
         <f>IF(OR($C48="",U48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U48,FIND("-",U48)-1),"")=AW48,IFERROR(--MID(U48,FIND("-",U48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))-(IFERROR(--MID(U48,FIND("-",U48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))-(IFERROR(--MID(U48,FIND("-",U48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(U48,FIND("-",U48)-1),""))=(AW48))+2*((IFERROR(--MID(U48,FIND("-",U48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X48" s="11" t="str">
+      <c r="X48" s="11">
         <f>IF(OR($C48="",W48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W48,FIND("-",W48)-1),"")=AW48,IFERROR(--MID(W48,FIND("-",W48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))-(IFERROR(--MID(W48,FIND("-",W48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))-(IFERROR(--MID(W48,FIND("-",W48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(W48,FIND("-",W48)-1),""))=(AW48))+2*((IFERROR(--MID(W48,FIND("-",W48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z48" s="11" t="str">
+      <c r="Z48" s="11">
         <f>IF(OR($C48="",Y48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y48,FIND("-",Y48)-1),"")=AW48,IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))-(IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))-(IFERROR(--MID(Y48,FIND("-",Y48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(Y48,FIND("-",Y48)-1),""))=(AW48))+2*((IFERROR(--MID(Y48,FIND("-",Y48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB48" s="11" t="str">
+      <c r="AB48" s="11">
         <f>IF(OR($C48="",AA48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA48,FIND("-",AA48)-1),"")=AW48,IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))-(IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))-(IFERROR(--MID(AA48,FIND("-",AA48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AA48,FIND("-",AA48)-1),""))=(AW48))+2*((IFERROR(--MID(AA48,FIND("-",AA48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD48" s="11" t="str">
+      <c r="AD48" s="11">
         <f>IF(OR($C48="",AC48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC48,FIND("-",AC48)-1),"")=AW48,IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))-(IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))-(IFERROR(--MID(AC48,FIND("-",AC48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AC48,FIND("-",AC48)-1),""))=(AW48))+2*((IFERROR(--MID(AC48,FIND("-",AC48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF48" s="11" t="str">
+      <c r="AF48" s="11">
         <f>IF(OR($C48="",AE48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE48,FIND("-",AE48)-1),"")=AW48,IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))-(IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))-(IFERROR(--MID(AE48,FIND("-",AE48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AE48,FIND("-",AE48)-1),""))=(AW48))+2*((IFERROR(--MID(AE48,FIND("-",AE48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG48" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH48" s="11" t="str">
+      <c r="AH48" s="11">
         <f>IF(OR($C48="",AG48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG48,FIND("-",AG48)-1),"")=AW48,IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))-(IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))-(IFERROR(--MID(AG48,FIND("-",AG48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AG48,FIND("-",AG48)-1),""))=(AW48))+2*((IFERROR(--MID(AG48,FIND("-",AG48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AJ48" s="11" t="str">
+      <c r="AJ48" s="11">
         <f>IF(OR($C48="",AI48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI48,FIND("-",AI48)-1),"")=AW48,IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))-(IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))-(IFERROR(--MID(AI48,FIND("-",AI48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AI48,FIND("-",AI48)-1),""))=(AW48))+2*((IFERROR(--MID(AI48,FIND("-",AI48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL48" s="11" t="str">
+      <c r="AL48" s="11">
         <f>IF(OR($C48="",AK48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK48,FIND("-",AK48)-1),"")=AW48,IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))-(IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))-(IFERROR(--MID(AK48,FIND("-",AK48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AK48,FIND("-",AK48)-1),""))=(AW48))+2*((IFERROR(--MID(AK48,FIND("-",AK48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM48" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AN48" s="11" t="str">
+      <c r="AN48" s="11">
         <f>IF(OR($C48="",AM48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM48,FIND("-",AM48)-1),"")=AW48,IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))-(IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))-(IFERROR(--MID(AM48,FIND("-",AM48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AM48,FIND("-",AM48)-1),""))=(AW48))+2*((IFERROR(--MID(AM48,FIND("-",AM48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO48" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP48" s="11" t="str">
+      <c r="AP48" s="11">
         <f>IF(OR($C48="",AO48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO48,FIND("-",AO48)-1),"")=AW48,IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))-(IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))-(IFERROR(--MID(AO48,FIND("-",AO48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AO48,FIND("-",AO48)-1),""))=(AW48))+2*((IFERROR(--MID(AO48,FIND("-",AO48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ48" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR48" s="11" t="str">
+      <c r="AR48" s="11">
         <f>IF(OR($C48="",AQ48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),"")=AW48,IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))-(IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))-(IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AQ48,FIND("-",AQ48)-1),""))=(AW48))+2*((IFERROR(--MID(AQ48,FIND("-",AQ48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS48" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AT48" s="11" t="str">
+      <c r="AT48" s="11">
         <f>IF(OR($C48="",AS48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS48,FIND("-",AS48)-1),"")=AW48,IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))-(IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))-(IFERROR(--MID(AS48,FIND("-",AS48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AS48,FIND("-",AS48)-1),""))=(AW48))+2*((IFERROR(--MID(AS48,FIND("-",AS48)+1,99),""))=(AX48))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU48" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV48" s="11" t="str">
+      <c r="AV48" s="11">
         <f>IF(OR($C48="",AU48=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU48,FIND("-",AU48)-1),"")=AW48,IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")=AX48),10,5*(SIGN((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))-(IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")))=SIGN((AW48)-(AX48)))+2*(((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))-(IFERROR(--MID(AU48,FIND("-",AU48)+1,99),"")))=((AW48)-(AX48)))+2*((IFERROR(--LEFT(AU48,FIND("-",AU48)-1),""))=(AW48))+2*((IFERROR(--MID(AU48,FIND("-",AU48)+1,99),""))=(AX48))),""))</f>
-        <v/>
-      </c>
-      <c r="AW48" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW48" s="11">
         <f>IF($C48="","",IFERROR(--LEFT($C48,FIND("-",$C48)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX48" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX48" s="11">
         <f>IF($C48="","",IFERROR(--MID($C48,FIND("-",$C48)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -23649,6 +23651,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23665,60 +23721,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23885,12 +23887,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
@@ -26434,6 +26436,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26445,17 +26458,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26504,8 +26506,8 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
-        <v>1</v>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="str">
         <f>Wedstrijden_beheer!AA1</f>
@@ -26520,14 +26522,14 @@
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="str">
         <f>Wedstrijden_beheer!O1</f>
@@ -26535,20 +26537,20 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
-        <v>117</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -26557,21 +26559,21 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
-        <v>109</v>
+        <f t="shared" si="1"/>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="str">
         <f>Wedstrijden_beheer!G1</f>
@@ -26579,21 +26581,21 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
-        <v>109</v>
+        <f t="shared" si="1"/>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!AK1</f>
@@ -26601,21 +26603,21 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
-        <v>106</v>
+        <f t="shared" si="1"/>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -26630,14 +26632,14 @@
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
         <f>Wedstrijden_beheer!AO1</f>
@@ -26645,21 +26647,21 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
-        <v>99</v>
+        <f t="shared" si="1"/>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
@@ -26667,21 +26669,21 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
-        <v>98</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="str">
         <f>Wedstrijden_beheer!AU1</f>
@@ -26689,21 +26691,21 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
-        <v>98</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
@@ -26711,21 +26713,21 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
-        <v>98</v>
+        <f t="shared" si="1"/>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="str">
         <f>Wedstrijden_beheer!S1</f>
@@ -26733,21 +26735,21 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
-        <v>95</v>
+        <f t="shared" si="1"/>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="str">
         <f>Wedstrijden_beheer!U1</f>
@@ -26755,21 +26757,21 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!Y1</f>
@@ -26777,21 +26779,21 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26806,14 +26808,14 @@
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="str">
         <f>Wedstrijden_beheer!AG1</f>
@@ -26821,21 +26823,21 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
-        <v>92</v>
+        <f t="shared" si="1"/>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!E1</f>
@@ -26843,20 +26845,20 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
-        <v>90</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
@@ -26865,21 +26867,21 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
-        <v>88</v>
+        <f t="shared" si="1"/>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26894,14 +26896,14 @@
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26916,14 +26918,14 @@
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -26931,21 +26933,21 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
-        <v>80</v>
+        <f t="shared" si="1"/>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26953,20 +26955,20 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
-        <v>79</v>
+        <f t="shared" si="1"/>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26975,15 +26977,15 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
-        <v>68</v>
+        <f t="shared" si="1"/>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -27355,14 +27357,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27561,27 +27561,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27606,9 +27599,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1513" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{259CDF07-A5BB-480B-B910-9F07BA4EFE59}"/>
+  <xr:revisionPtr revIDLastSave="1517" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8D159BA-1E0F-4142-8BB4-A1F229E9EF94}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-18285" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1053,24 +1053,28 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF002868"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1125,6 +1129,7 @@
       <sz val="10"/>
       <color rgb="FF1A1A1A"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1348,21 +1353,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1730,22 +1735,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="44"/>
+      <c r="F1" s="39"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1825,11 +1830,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="44"/>
+      <c r="AT1" s="39"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="44"/>
+      <c r="AV1" s="39"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1838,9 +1843,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
+      <c r="A2" s="41"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1985,53 +1990,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="39"/>
-      <c r="AJ3" s="39"/>
-      <c r="AK3" s="39"/>
-      <c r="AL3" s="39"/>
-      <c r="AM3" s="39"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="39"/>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="39"/>
-      <c r="AR3" s="39"/>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="39"/>
-      <c r="AU3" s="39"/>
-      <c r="AV3" s="40"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+      <c r="AA3" s="43"/>
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="43"/>
+      <c r="AD3" s="43"/>
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="43"/>
+      <c r="AG3" s="43"/>
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="43"/>
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="43"/>
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="43"/>
+      <c r="AR3" s="43"/>
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="43"/>
+      <c r="AU3" s="43"/>
+      <c r="AV3" s="44"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -7280,171 +7285,173 @@
       <c r="B44" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="10"/>
+      <c r="C44" s="10" t="s">
+        <v>43</v>
+      </c>
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F44" s="11" t="str">
+      <c r="F44" s="11">
         <f>IF(OR($C44="",E44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E44,FIND("-",E44)-1),"")=AW44,IFERROR(--MID(E44,FIND("-",E44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))-(IFERROR(--MID(E44,FIND("-",E44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))-(IFERROR(--MID(E44,FIND("-",E44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(E44,FIND("-",E44)-1),""))=(AW44))+2*((IFERROR(--MID(E44,FIND("-",E44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="H44" s="11" t="str">
+      <c r="H44" s="11">
         <f>IF(OR($C44="",G44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G44,FIND("-",G44)-1),"")=AW44,IFERROR(--MID(G44,FIND("-",G44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))-(IFERROR(--MID(G44,FIND("-",G44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))-(IFERROR(--MID(G44,FIND("-",G44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(G44,FIND("-",G44)-1),""))=(AW44))+2*((IFERROR(--MID(G44,FIND("-",G44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J44" s="11" t="str">
+      <c r="J44" s="11">
         <f>IF(OR($C44="",I44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I44,FIND("-",I44)-1),"")=AW44,IFERROR(--MID(I44,FIND("-",I44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))-(IFERROR(--MID(I44,FIND("-",I44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))-(IFERROR(--MID(I44,FIND("-",I44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(I44,FIND("-",I44)-1),""))=(AW44))+2*((IFERROR(--MID(I44,FIND("-",I44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L44" s="11" t="str">
+      <c r="L44" s="11">
         <f>IF(OR($C44="",K44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K44,FIND("-",K44)-1),"")=AW44,IFERROR(--MID(K44,FIND("-",K44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))-(IFERROR(--MID(K44,FIND("-",K44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))-(IFERROR(--MID(K44,FIND("-",K44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(K44,FIND("-",K44)-1),""))=(AW44))+2*((IFERROR(--MID(K44,FIND("-",K44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N44" s="11" t="str">
+      <c r="N44" s="11">
         <f>IF(OR($C44="",M44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M44,FIND("-",M44)-1),"")=AW44,IFERROR(--MID(M44,FIND("-",M44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))-(IFERROR(--MID(M44,FIND("-",M44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))-(IFERROR(--MID(M44,FIND("-",M44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(M44,FIND("-",M44)-1),""))=(AW44))+2*((IFERROR(--MID(M44,FIND("-",M44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O44" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P44" s="11" t="str">
+      <c r="P44" s="11">
         <f>IF(OR($C44="",O44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O44,FIND("-",O44)-1),"")=AW44,IFERROR(--MID(O44,FIND("-",O44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))-(IFERROR(--MID(O44,FIND("-",O44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))-(IFERROR(--MID(O44,FIND("-",O44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(O44,FIND("-",O44)-1),""))=(AW44))+2*((IFERROR(--MID(O44,FIND("-",O44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Q44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R44" s="11" t="str">
+      <c r="R44" s="11">
         <f>IF(OR($C44="",Q44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q44,FIND("-",Q44)-1),"")=AW44,IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))-(IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))-(IFERROR(--MID(Q44,FIND("-",Q44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(Q44,FIND("-",Q44)-1),""))=(AW44))+2*((IFERROR(--MID(Q44,FIND("-",Q44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S44" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T44" s="11" t="str">
+      <c r="T44" s="11">
         <f>IF(OR($C44="",S44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S44,FIND("-",S44)-1),"")=AW44,IFERROR(--MID(S44,FIND("-",S44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))-(IFERROR(--MID(S44,FIND("-",S44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))-(IFERROR(--MID(S44,FIND("-",S44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(S44,FIND("-",S44)-1),""))=(AW44))+2*((IFERROR(--MID(S44,FIND("-",S44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V44" s="11" t="str">
+      <c r="V44" s="11">
         <f>IF(OR($C44="",U44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U44,FIND("-",U44)-1),"")=AW44,IFERROR(--MID(U44,FIND("-",U44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))-(IFERROR(--MID(U44,FIND("-",U44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))-(IFERROR(--MID(U44,FIND("-",U44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(U44,FIND("-",U44)-1),""))=(AW44))+2*((IFERROR(--MID(U44,FIND("-",U44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X44" s="11" t="str">
+      <c r="X44" s="11">
         <f>IF(OR($C44="",W44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W44,FIND("-",W44)-1),"")=AW44,IFERROR(--MID(W44,FIND("-",W44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))-(IFERROR(--MID(W44,FIND("-",W44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))-(IFERROR(--MID(W44,FIND("-",W44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(W44,FIND("-",W44)-1),""))=(AW44))+2*((IFERROR(--MID(W44,FIND("-",W44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z44" s="11" t="str">
+      <c r="Z44" s="11">
         <f>IF(OR($C44="",Y44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y44,FIND("-",Y44)-1),"")=AW44,IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))-(IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))-(IFERROR(--MID(Y44,FIND("-",Y44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(Y44,FIND("-",Y44)-1),""))=(AW44))+2*((IFERROR(--MID(Y44,FIND("-",Y44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA44" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB44" s="11" t="str">
+      <c r="AB44" s="11">
         <f>IF(OR($C44="",AA44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA44,FIND("-",AA44)-1),"")=AW44,IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))-(IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))-(IFERROR(--MID(AA44,FIND("-",AA44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AA44,FIND("-",AA44)-1),""))=(AW44))+2*((IFERROR(--MID(AA44,FIND("-",AA44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD44" s="11" t="str">
+      <c r="AD44" s="11">
         <f>IF(OR($C44="",AC44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC44,FIND("-",AC44)-1),"")=AW44,IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))-(IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))-(IFERROR(--MID(AC44,FIND("-",AC44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AC44,FIND("-",AC44)-1),""))=(AW44))+2*((IFERROR(--MID(AC44,FIND("-",AC44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF44" s="11" t="str">
+      <c r="AF44" s="11">
         <f>IF(OR($C44="",AE44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE44,FIND("-",AE44)-1),"")=AW44,IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))-(IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))-(IFERROR(--MID(AE44,FIND("-",AE44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AE44,FIND("-",AE44)-1),""))=(AW44))+2*((IFERROR(--MID(AE44,FIND("-",AE44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH44" s="11" t="str">
+      <c r="AH44" s="11">
         <f>IF(OR($C44="",AG44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG44,FIND("-",AG44)-1),"")=AW44,IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))-(IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))-(IFERROR(--MID(AG44,FIND("-",AG44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AG44,FIND("-",AG44)-1),""))=(AW44))+2*((IFERROR(--MID(AG44,FIND("-",AG44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ44" s="11" t="str">
+      <c r="AJ44" s="11">
         <f>IF(OR($C44="",AI44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI44,FIND("-",AI44)-1),"")=AW44,IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))-(IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))-(IFERROR(--MID(AI44,FIND("-",AI44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AI44,FIND("-",AI44)-1),""))=(AW44))+2*((IFERROR(--MID(AI44,FIND("-",AI44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL44" s="11" t="str">
+      <c r="AL44" s="11">
         <f>IF(OR($C44="",AK44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK44,FIND("-",AK44)-1),"")=AW44,IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))-(IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))-(IFERROR(--MID(AK44,FIND("-",AK44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AK44,FIND("-",AK44)-1),""))=(AW44))+2*((IFERROR(--MID(AK44,FIND("-",AK44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN44" s="11" t="str">
+      <c r="AN44" s="11">
         <f>IF(OR($C44="",AM44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM44,FIND("-",AM44)-1),"")=AW44,IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))-(IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))-(IFERROR(--MID(AM44,FIND("-",AM44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AM44,FIND("-",AM44)-1),""))=(AW44))+2*((IFERROR(--MID(AM44,FIND("-",AM44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP44" s="11" t="str">
+      <c r="AP44" s="11">
         <f>IF(OR($C44="",AO44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO44,FIND("-",AO44)-1),"")=AW44,IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))-(IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))-(IFERROR(--MID(AO44,FIND("-",AO44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AO44,FIND("-",AO44)-1),""))=(AW44))+2*((IFERROR(--MID(AO44,FIND("-",AO44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ44" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR44" s="11" t="str">
+      <c r="AR44" s="11">
         <f>IF(OR($C44="",AQ44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),"")=AW44,IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))-(IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))-(IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AQ44,FIND("-",AQ44)-1),""))=(AW44))+2*((IFERROR(--MID(AQ44,FIND("-",AQ44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS44" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT44" s="11" t="str">
+      <c r="AT44" s="11">
         <f>IF(OR($C44="",AS44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS44,FIND("-",AS44)-1),"")=AW44,IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))-(IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))-(IFERROR(--MID(AS44,FIND("-",AS44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AS44,FIND("-",AS44)-1),""))=(AW44))+2*((IFERROR(--MID(AS44,FIND("-",AS44)+1,99),""))=(AX44))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AV44" s="11" t="str">
+      <c r="AV44" s="11">
         <f>IF(OR($C44="",AU44=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU44,FIND("-",AU44)-1),"")=AW44,IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")=AX44),10,5*(SIGN((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))-(IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")))=SIGN((AW44)-(AX44)))+2*(((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))-(IFERROR(--MID(AU44,FIND("-",AU44)+1,99),"")))=((AW44)-(AX44)))+2*((IFERROR(--LEFT(AU44,FIND("-",AU44)-1),""))=(AW44))+2*((IFERROR(--MID(AU44,FIND("-",AU44)+1,99),""))=(AX44))),""))</f>
-        <v/>
-      </c>
-      <c r="AW44" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW44" s="11">
         <f>IF($C44="","",IFERROR(--LEFT($C44,FIND("-",$C44)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX44" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX44" s="11">
         <f>IF($C44="","",IFERROR(--MID($C44,FIND("-",$C44)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -7566,171 +7573,173 @@
       <c r="B47" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="10"/>
+      <c r="C47" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D47" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F47" s="11" t="str">
+      <c r="F47" s="11">
         <f>IF(OR($C47="",E47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E47,FIND("-",E47)-1),"")=AW47,IFERROR(--MID(E47,FIND("-",E47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))-(IFERROR(--MID(E47,FIND("-",E47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))-(IFERROR(--MID(E47,FIND("-",E47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(E47,FIND("-",E47)-1),""))=(AW47))+2*((IFERROR(--MID(E47,FIND("-",E47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H47" s="11" t="str">
+      <c r="H47" s="11">
         <f>IF(OR($C47="",G47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G47,FIND("-",G47)-1),"")=AW47,IFERROR(--MID(G47,FIND("-",G47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))-(IFERROR(--MID(G47,FIND("-",G47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))-(IFERROR(--MID(G47,FIND("-",G47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(G47,FIND("-",G47)-1),""))=(AW47))+2*((IFERROR(--MID(G47,FIND("-",G47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J47" s="11" t="str">
+      <c r="J47" s="11">
         <f>IF(OR($C47="",I47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I47,FIND("-",I47)-1),"")=AW47,IFERROR(--MID(I47,FIND("-",I47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))-(IFERROR(--MID(I47,FIND("-",I47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))-(IFERROR(--MID(I47,FIND("-",I47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(I47,FIND("-",I47)-1),""))=(AW47))+2*((IFERROR(--MID(I47,FIND("-",I47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L47" s="11" t="str">
+      <c r="L47" s="11">
         <f>IF(OR($C47="",K47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K47,FIND("-",K47)-1),"")=AW47,IFERROR(--MID(K47,FIND("-",K47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))-(IFERROR(--MID(K47,FIND("-",K47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))-(IFERROR(--MID(K47,FIND("-",K47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(K47,FIND("-",K47)-1),""))=(AW47))+2*((IFERROR(--MID(K47,FIND("-",K47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N47" s="11" t="str">
+      <c r="N47" s="11">
         <f>IF(OR($C47="",M47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M47,FIND("-",M47)-1),"")=AW47,IFERROR(--MID(M47,FIND("-",M47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))-(IFERROR(--MID(M47,FIND("-",M47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))-(IFERROR(--MID(M47,FIND("-",M47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(M47,FIND("-",M47)-1),""))=(AW47))+2*((IFERROR(--MID(M47,FIND("-",M47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P47" s="11" t="str">
+      <c r="P47" s="11">
         <f>IF(OR($C47="",O47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O47,FIND("-",O47)-1),"")=AW47,IFERROR(--MID(O47,FIND("-",O47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))-(IFERROR(--MID(O47,FIND("-",O47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))-(IFERROR(--MID(O47,FIND("-",O47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(O47,FIND("-",O47)-1),""))=(AW47))+2*((IFERROR(--MID(O47,FIND("-",O47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q47" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R47" s="11" t="str">
+      <c r="R47" s="11">
         <f>IF(OR($C47="",Q47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q47,FIND("-",Q47)-1),"")=AW47,IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))-(IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))-(IFERROR(--MID(Q47,FIND("-",Q47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(Q47,FIND("-",Q47)-1),""))=(AW47))+2*((IFERROR(--MID(Q47,FIND("-",Q47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S47" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T47" s="11" t="str">
+      <c r="T47" s="11">
         <f>IF(OR($C47="",S47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S47,FIND("-",S47)-1),"")=AW47,IFERROR(--MID(S47,FIND("-",S47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))-(IFERROR(--MID(S47,FIND("-",S47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))-(IFERROR(--MID(S47,FIND("-",S47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(S47,FIND("-",S47)-1),""))=(AW47))+2*((IFERROR(--MID(S47,FIND("-",S47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V47" s="11" t="str">
+      <c r="V47" s="11">
         <f>IF(OR($C47="",U47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U47,FIND("-",U47)-1),"")=AW47,IFERROR(--MID(U47,FIND("-",U47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))-(IFERROR(--MID(U47,FIND("-",U47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))-(IFERROR(--MID(U47,FIND("-",U47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(U47,FIND("-",U47)-1),""))=(AW47))+2*((IFERROR(--MID(U47,FIND("-",U47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X47" s="11" t="str">
+      <c r="X47" s="11">
         <f>IF(OR($C47="",W47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W47,FIND("-",W47)-1),"")=AW47,IFERROR(--MID(W47,FIND("-",W47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))-(IFERROR(--MID(W47,FIND("-",W47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))-(IFERROR(--MID(W47,FIND("-",W47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(W47,FIND("-",W47)-1),""))=(AW47))+2*((IFERROR(--MID(W47,FIND("-",W47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y47" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z47" s="11" t="str">
+      <c r="Z47" s="11">
         <f>IF(OR($C47="",Y47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y47,FIND("-",Y47)-1),"")=AW47,IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))-(IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))-(IFERROR(--MID(Y47,FIND("-",Y47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(Y47,FIND("-",Y47)-1),""))=(AW47))+2*((IFERROR(--MID(Y47,FIND("-",Y47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB47" s="11" t="str">
+      <c r="AB47" s="11">
         <f>IF(OR($C47="",AA47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA47,FIND("-",AA47)-1),"")=AW47,IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))-(IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))-(IFERROR(--MID(AA47,FIND("-",AA47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AA47,FIND("-",AA47)-1),""))=(AW47))+2*((IFERROR(--MID(AA47,FIND("-",AA47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD47" s="11" t="str">
+      <c r="AD47" s="11">
         <f>IF(OR($C47="",AC47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC47,FIND("-",AC47)-1),"")=AW47,IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))-(IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))-(IFERROR(--MID(AC47,FIND("-",AC47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AC47,FIND("-",AC47)-1),""))=(AW47))+2*((IFERROR(--MID(AC47,FIND("-",AC47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF47" s="11" t="str">
+      <c r="AF47" s="11">
         <f>IF(OR($C47="",AE47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE47,FIND("-",AE47)-1),"")=AW47,IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))-(IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))-(IFERROR(--MID(AE47,FIND("-",AE47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AE47,FIND("-",AE47)-1),""))=(AW47))+2*((IFERROR(--MID(AE47,FIND("-",AE47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG47" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AH47" s="11" t="str">
+      <c r="AH47" s="11">
         <f>IF(OR($C47="",AG47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG47,FIND("-",AG47)-1),"")=AW47,IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))-(IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))-(IFERROR(--MID(AG47,FIND("-",AG47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AG47,FIND("-",AG47)-1),""))=(AW47))+2*((IFERROR(--MID(AG47,FIND("-",AG47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ47" s="11" t="str">
+      <c r="AJ47" s="11">
         <f>IF(OR($C47="",AI47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI47,FIND("-",AI47)-1),"")=AW47,IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))-(IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))-(IFERROR(--MID(AI47,FIND("-",AI47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AI47,FIND("-",AI47)-1),""))=(AW47))+2*((IFERROR(--MID(AI47,FIND("-",AI47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL47" s="11" t="str">
+      <c r="AL47" s="11">
         <f>IF(OR($C47="",AK47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK47,FIND("-",AK47)-1),"")=AW47,IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))-(IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))-(IFERROR(--MID(AK47,FIND("-",AK47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AK47,FIND("-",AK47)-1),""))=(AW47))+2*((IFERROR(--MID(AK47,FIND("-",AK47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM47" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AN47" s="11" t="str">
+      <c r="AN47" s="11">
         <f>IF(OR($C47="",AM47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM47,FIND("-",AM47)-1),"")=AW47,IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))-(IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))-(IFERROR(--MID(AM47,FIND("-",AM47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AM47,FIND("-",AM47)-1),""))=(AW47))+2*((IFERROR(--MID(AM47,FIND("-",AM47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO47" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP47" s="11" t="str">
+      <c r="AP47" s="11">
         <f>IF(OR($C47="",AO47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO47,FIND("-",AO47)-1),"")=AW47,IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))-(IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))-(IFERROR(--MID(AO47,FIND("-",AO47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AO47,FIND("-",AO47)-1),""))=(AW47))+2*((IFERROR(--MID(AO47,FIND("-",AO47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AQ47" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR47" s="11" t="str">
+      <c r="AR47" s="11">
         <f>IF(OR($C47="",AQ47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),"")=AW47,IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))-(IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))-(IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AQ47,FIND("-",AQ47)-1),""))=(AW47))+2*((IFERROR(--MID(AQ47,FIND("-",AQ47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT47" s="11" t="str">
+      <c r="AT47" s="11">
         <f>IF(OR($C47="",AS47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS47,FIND("-",AS47)-1),"")=AW47,IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))-(IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))-(IFERROR(--MID(AS47,FIND("-",AS47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AS47,FIND("-",AS47)-1),""))=(AW47))+2*((IFERROR(--MID(AS47,FIND("-",AS47)+1,99),""))=(AX47))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU47" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV47" s="11" t="str">
+      <c r="AV47" s="11">
         <f>IF(OR($C47="",AU47=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU47,FIND("-",AU47)-1),"")=AW47,IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")=AX47),10,5*(SIGN((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))-(IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")))=SIGN((AW47)-(AX47)))+2*(((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))-(IFERROR(--MID(AU47,FIND("-",AU47)+1,99),"")))=((AW47)-(AX47)))+2*((IFERROR(--LEFT(AU47,FIND("-",AU47)-1),""))=(AW47))+2*((IFERROR(--MID(AU47,FIND("-",AU47)+1,99),""))=(AX47))),""))</f>
-        <v/>
-      </c>
-      <c r="AW47" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW47" s="11">
         <f>IF($C47="","",IFERROR(--LEFT($C47,FIND("-",$C47)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX47" s="11" t="str">
+        <v>6</v>
+      </c>
+      <c r="AX47" s="11">
         <f>IF($C47="","",IFERROR(--MID($C47,FIND("-",$C47)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -23651,6 +23660,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23667,60 +23730,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23887,12 +23896,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="44"/>
+      <c r="AS1" s="39"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="44"/>
+      <c r="AU1" s="39"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
@@ -26436,6 +26445,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26447,17 +26467,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26506,448 +26515,448 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
-        <v>2</v>
+        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>118</v>
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>136</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>118</v>
+        <f>C3+D3</f>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>124</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>123</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f t="shared" si="1"/>
-        <v>124</v>
+        <f>C4+D4</f>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>116</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>120</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>116</v>
+        <f>C5+D5</f>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>111</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>119</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>111</v>
+        <f>C6+D6</f>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>113</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>118</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="1"/>
-        <v>113</v>
+        <f>C7+D7</f>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>118</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C8+D8</f>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>106</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>114</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="1"/>
-        <v>106</v>
+        <f>C9+D9</f>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>114</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C10+D10</f>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>114</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C11+D11</f>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>105</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>111</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f t="shared" si="1"/>
-        <v>105</v>
+        <f>C12+D12</f>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>102</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>110</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f t="shared" si="1"/>
-        <v>102</v>
+        <f>C13+D13</f>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>110</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C14+D14</f>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>110</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C15+D15</f>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>92</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>107</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f t="shared" si="1"/>
-        <v>92</v>
+        <f>C16+D16</f>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
         <v>102</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f t="shared" si="1"/>
+        <f>C17+D17</f>
         <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>99</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C18+D18</f>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>90</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>97</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>90</v>
+        <f>C19+D19</f>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>86</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>97</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>86</v>
+        <f>C20+D20</f>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>86</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>93</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>86</v>
+        <f>C21+D21</f>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <v>19</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>87</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>93</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="1"/>
-        <v>87</v>
+        <f>C22+D22</f>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26955,20 +26964,20 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f t="shared" si="1"/>
-        <v>86</v>
+        <f>C23+D23</f>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26977,15 +26986,15 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" si="1"/>
-        <v>75</v>
+        <f>C24+D24</f>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -27366,6 +27375,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27560,17 +27580,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
@@ -27580,6 +27589,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27596,21 +27622,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1517" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8D159BA-1E0F-4142-8BB4-A1F229E9EF94}"/>
+  <xr:revisionPtr revIDLastSave="1518" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F26D27-1769-4F7A-9BC4-D16A2B5AA98E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-18285" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1353,21 +1353,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1735,22 +1735,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="39"/>
+      <c r="F1" s="44"/>
       <c r="G1" s="37" t="s">
         <v>5</v>
       </c>
@@ -1830,11 +1830,11 @@
       <c r="AS1" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="39"/>
+      <c r="AT1" s="44"/>
       <c r="AU1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="39"/>
+      <c r="AV1" s="44"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1843,9 +1843,9 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
+      <c r="A2" s="43"/>
       <c r="B2" s="42"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="43"/>
       <c r="D2" s="42"/>
       <c r="E2" s="27" t="s">
         <v>27</v>
@@ -1990,53 +1990,53 @@
       <c r="A3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
-      <c r="AA3" s="43"/>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="43"/>
-      <c r="AD3" s="43"/>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="43"/>
-      <c r="AG3" s="43"/>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="43"/>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="43"/>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="43"/>
-      <c r="AR3" s="43"/>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="43"/>
-      <c r="AU3" s="43"/>
-      <c r="AV3" s="44"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="39"/>
+      <c r="AK3" s="39"/>
+      <c r="AL3" s="39"/>
+      <c r="AM3" s="39"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="39"/>
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="39"/>
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="39"/>
+      <c r="AV3" s="40"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
@@ -8385,171 +8385,173 @@
       <c r="B53" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="10"/>
+      <c r="C53" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D53" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="11" t="str">
+      <c r="F53" s="11">
         <f>IF(OR($C53="",E53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E53,FIND("-",E53)-1),"")=AW53,IFERROR(--MID(E53,FIND("-",E53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))-(IFERROR(--MID(E53,FIND("-",E53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))-(IFERROR(--MID(E53,FIND("-",E53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(E53,FIND("-",E53)-1),""))=(AW53))+2*((IFERROR(--MID(E53,FIND("-",E53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H53" s="11" t="str">
+      <c r="H53" s="11">
         <f>IF(OR($C53="",G53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G53,FIND("-",G53)-1),"")=AW53,IFERROR(--MID(G53,FIND("-",G53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))-(IFERROR(--MID(G53,FIND("-",G53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))-(IFERROR(--MID(G53,FIND("-",G53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(G53,FIND("-",G53)-1),""))=(AW53))+2*((IFERROR(--MID(G53,FIND("-",G53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I53" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J53" s="11" t="str">
+      <c r="J53" s="11">
         <f>IF(OR($C53="",I53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I53,FIND("-",I53)-1),"")=AW53,IFERROR(--MID(I53,FIND("-",I53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))-(IFERROR(--MID(I53,FIND("-",I53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))-(IFERROR(--MID(I53,FIND("-",I53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(I53,FIND("-",I53)-1),""))=(AW53))+2*((IFERROR(--MID(I53,FIND("-",I53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K53" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L53" s="11" t="str">
+      <c r="L53" s="11">
         <f>IF(OR($C53="",K53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K53,FIND("-",K53)-1),"")=AW53,IFERROR(--MID(K53,FIND("-",K53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))-(IFERROR(--MID(K53,FIND("-",K53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))-(IFERROR(--MID(K53,FIND("-",K53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(K53,FIND("-",K53)-1),""))=(AW53))+2*((IFERROR(--MID(K53,FIND("-",K53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N53" s="11" t="str">
+      <c r="N53" s="11">
         <f>IF(OR($C53="",M53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M53,FIND("-",M53)-1),"")=AW53,IFERROR(--MID(M53,FIND("-",M53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))-(IFERROR(--MID(M53,FIND("-",M53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))-(IFERROR(--MID(M53,FIND("-",M53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(M53,FIND("-",M53)-1),""))=(AW53))+2*((IFERROR(--MID(M53,FIND("-",M53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P53" s="11" t="str">
+      <c r="P53" s="11">
         <f>IF(OR($C53="",O53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O53,FIND("-",O53)-1),"")=AW53,IFERROR(--MID(O53,FIND("-",O53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))-(IFERROR(--MID(O53,FIND("-",O53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))-(IFERROR(--MID(O53,FIND("-",O53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(O53,FIND("-",O53)-1),""))=(AW53))+2*((IFERROR(--MID(O53,FIND("-",O53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="R53" s="11" t="str">
+      <c r="R53" s="11">
         <f>IF(OR($C53="",Q53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q53,FIND("-",Q53)-1),"")=AW53,IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))-(IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))-(IFERROR(--MID(Q53,FIND("-",Q53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(Q53,FIND("-",Q53)-1),""))=(AW53))+2*((IFERROR(--MID(Q53,FIND("-",Q53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T53" s="11" t="str">
+      <c r="T53" s="11">
         <f>IF(OR($C53="",S53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S53,FIND("-",S53)-1),"")=AW53,IFERROR(--MID(S53,FIND("-",S53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))-(IFERROR(--MID(S53,FIND("-",S53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))-(IFERROR(--MID(S53,FIND("-",S53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(S53,FIND("-",S53)-1),""))=(AW53))+2*((IFERROR(--MID(S53,FIND("-",S53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V53" s="11" t="str">
+      <c r="V53" s="11">
         <f>IF(OR($C53="",U53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U53,FIND("-",U53)-1),"")=AW53,IFERROR(--MID(U53,FIND("-",U53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))-(IFERROR(--MID(U53,FIND("-",U53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))-(IFERROR(--MID(U53,FIND("-",U53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(U53,FIND("-",U53)-1),""))=(AW53))+2*((IFERROR(--MID(U53,FIND("-",U53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X53" s="11" t="str">
+      <c r="X53" s="11">
         <f>IF(OR($C53="",W53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W53,FIND("-",W53)-1),"")=AW53,IFERROR(--MID(W53,FIND("-",W53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))-(IFERROR(--MID(W53,FIND("-",W53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))-(IFERROR(--MID(W53,FIND("-",W53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(W53,FIND("-",W53)-1),""))=(AW53))+2*((IFERROR(--MID(W53,FIND("-",W53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z53" s="11" t="str">
+      <c r="Z53" s="11">
         <f>IF(OR($C53="",Y53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y53,FIND("-",Y53)-1),"")=AW53,IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))-(IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))-(IFERROR(--MID(Y53,FIND("-",Y53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(Y53,FIND("-",Y53)-1),""))=(AW53))+2*((IFERROR(--MID(Y53,FIND("-",Y53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AB53" s="11" t="str">
+      <c r="AB53" s="11">
         <f>IF(OR($C53="",AA53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA53,FIND("-",AA53)-1),"")=AW53,IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))-(IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))-(IFERROR(--MID(AA53,FIND("-",AA53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AA53,FIND("-",AA53)-1),""))=(AW53))+2*((IFERROR(--MID(AA53,FIND("-",AA53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD53" s="11" t="str">
+      <c r="AD53" s="11">
         <f>IF(OR($C53="",AC53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC53,FIND("-",AC53)-1),"")=AW53,IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))-(IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))-(IFERROR(--MID(AC53,FIND("-",AC53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AC53,FIND("-",AC53)-1),""))=(AW53))+2*((IFERROR(--MID(AC53,FIND("-",AC53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AF53" s="11" t="str">
+      <c r="AF53" s="11">
         <f>IF(OR($C53="",AE53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE53,FIND("-",AE53)-1),"")=AW53,IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))-(IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))-(IFERROR(--MID(AE53,FIND("-",AE53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AE53,FIND("-",AE53)-1),""))=(AW53))+2*((IFERROR(--MID(AE53,FIND("-",AE53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH53" s="11" t="str">
+      <c r="AH53" s="11">
         <f>IF(OR($C53="",AG53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG53,FIND("-",AG53)-1),"")=AW53,IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))-(IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))-(IFERROR(--MID(AG53,FIND("-",AG53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AG53,FIND("-",AG53)-1),""))=(AW53))+2*((IFERROR(--MID(AG53,FIND("-",AG53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI53" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AJ53" s="11" t="str">
+      <c r="AJ53" s="11">
         <f>IF(OR($C53="",AI53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI53,FIND("-",AI53)-1),"")=AW53,IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))-(IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))-(IFERROR(--MID(AI53,FIND("-",AI53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AI53,FIND("-",AI53)-1),""))=(AW53))+2*((IFERROR(--MID(AI53,FIND("-",AI53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK53" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL53" s="11" t="str">
+      <c r="AL53" s="11">
         <f>IF(OR($C53="",AK53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK53,FIND("-",AK53)-1),"")=AW53,IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))-(IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))-(IFERROR(--MID(AK53,FIND("-",AK53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AK53,FIND("-",AK53)-1),""))=(AW53))+2*((IFERROR(--MID(AK53,FIND("-",AK53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN53" s="11" t="str">
+      <c r="AN53" s="11">
         <f>IF(OR($C53="",AM53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM53,FIND("-",AM53)-1),"")=AW53,IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))-(IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))-(IFERROR(--MID(AM53,FIND("-",AM53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AM53,FIND("-",AM53)-1),""))=(AW53))+2*((IFERROR(--MID(AM53,FIND("-",AM53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO53" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AP53" s="11" t="str">
+      <c r="AP53" s="11">
         <f>IF(OR($C53="",AO53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO53,FIND("-",AO53)-1),"")=AW53,IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))-(IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))-(IFERROR(--MID(AO53,FIND("-",AO53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AO53,FIND("-",AO53)-1),""))=(AW53))+2*((IFERROR(--MID(AO53,FIND("-",AO53)+1,99),""))=(AX53))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ53" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR53" s="11" t="str">
+      <c r="AR53" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS53" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AT53" s="11" t="str">
+      <c r="AT53" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU53" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AV53" s="11" t="str">
+      <c r="AV53" s="11">
         <f>IF(OR($C53="",AU53=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU53,FIND("-",AU53)-1),"")=AW53,IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")=AX53),10,5*(SIGN((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))-(IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")))=SIGN((AW53)-(AX53)))+2*(((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))-(IFERROR(--MID(AU53,FIND("-",AU53)+1,99),"")))=((AW53)-(AX53)))+2*((IFERROR(--LEFT(AU53,FIND("-",AU53)-1),""))=(AW53))+2*((IFERROR(--MID(AU53,FIND("-",AU53)+1,99),""))=(AX53))),""))</f>
-        <v/>
-      </c>
-      <c r="AW53" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW53" s="11">
         <f>IF($C53="","",IFERROR(--LEFT($C53,FIND("-",$C53)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX53" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX53" s="11">
         <f>IF($C53="","",IFERROR(--MID($C53,FIND("-",$C53)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -23660,6 +23662,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23676,60 +23732,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23896,12 +23898,12 @@
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="39"/>
+      <c r="AS1" s="44"/>
       <c r="AT1" s="37" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="39"/>
+      <c r="AU1" s="44"/>
     </row>
     <row r="2" spans="1:47" s="32" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21"/>
@@ -26445,6 +26447,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26456,17 +26469,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26515,7 +26517,7 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26524,20 +26526,20 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
-        <v>136</v>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26546,20 +26548,20 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
-        <v>123</v>
+        <f t="shared" si="1"/>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
@@ -26568,20 +26570,20 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
-        <v>120</v>
+        <f t="shared" si="1"/>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -26590,20 +26592,20 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
-        <v>119</v>
+        <f t="shared" si="1"/>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -26612,20 +26614,20 @@
       </c>
       <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D7" s="11">
         <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
-        <v>118</v>
+        <f t="shared" si="1"/>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B8" s="1" t="str">
@@ -26634,20 +26636,20 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
-        <v>118</v>
+        <f t="shared" si="1"/>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
@@ -26656,20 +26658,20 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
-        <v>114</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
@@ -26678,20 +26680,20 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
-        <v>114</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="1" t="str">
@@ -26700,20 +26702,20 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
-        <v>114</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
@@ -26722,20 +26724,20 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
-        <v>111</v>
+        <f t="shared" si="1"/>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
@@ -26744,20 +26746,20 @@
       </c>
       <c r="C13" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D13" s="11">
         <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B14" s="1" t="str">
@@ -26766,20 +26768,20 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="1" t="str">
@@ -26788,21 +26790,21 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
-        <v>110</v>
+        <f t="shared" si="1"/>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="B16" s="1" t="str">
         <f>Wedstrijden_beheer!M1</f>
@@ -26810,20 +26812,20 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
-        <v>107</v>
+        <f t="shared" si="1"/>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
@@ -26832,21 +26834,21 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
-        <v>102</v>
+        <f t="shared" si="1"/>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="str">
         <f>Wedstrijden_beheer!AC1</f>
@@ -26854,21 +26856,21 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
-        <v>99</v>
+        <f t="shared" si="1"/>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="str">
         <f>Wedstrijden_beheer!AI1</f>
@@ -26876,20 +26878,20 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
-        <v>97</v>
+        <f t="shared" si="1"/>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B20" s="1" t="str">
@@ -26898,21 +26900,21 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
-        <v>97</v>
+        <f t="shared" si="1"/>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="str">
         <f>Wedstrijden_beheer!AS1</f>
@@ -26920,21 +26922,21 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
         <f>Wedstrijden_beheer!Q1</f>
@@ -26942,21 +26944,21 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
-        <v>93</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26964,20 +26966,20 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
-        <v>91</v>
+        <f t="shared" si="1"/>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -26986,15 +26988,15 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
-        <v>89</v>
+        <f t="shared" si="1"/>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -27366,26 +27368,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010048B5CA5D9B2D2E40A04107BA9009336A" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a76a1f1216eebef05d317362f2b46be1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7c2036e6-2c6c-4cc0-93d3-66cc911cb074" xmlns:ns3="7b90d758-d430-4ffd-9227-0f539ac48821" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac005e59cc78a2985128eb85e772a849" ns2:_="" ns3:_="">
     <xsd:import namespace="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
@@ -27580,32 +27562,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC36E1F8-38A3-408A-8859-75EB2F5B45CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27622,4 +27599,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1518" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0F26D27-1769-4F7A-9BC4-D16A2B5AA98E}"/>
+  <xr:revisionPtr revIDLastSave="1522" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73771A5E-726D-4271-B4D3-9F0FB7D23AF0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -7925,171 +7925,173 @@
       <c r="B49" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="10"/>
+      <c r="C49" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D49" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F49" s="11" t="str">
+      <c r="F49" s="11">
         <f>IF(OR($C49="",E49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E49,FIND("-",E49)-1),"")=AW49,IFERROR(--MID(E49,FIND("-",E49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))-(IFERROR(--MID(E49,FIND("-",E49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))-(IFERROR(--MID(E49,FIND("-",E49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(E49,FIND("-",E49)-1),""))=(AW49))+2*((IFERROR(--MID(E49,FIND("-",E49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H49" s="11" t="str">
+      <c r="H49" s="11">
         <f>IF(OR($C49="",G49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G49,FIND("-",G49)-1),"")=AW49,IFERROR(--MID(G49,FIND("-",G49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))-(IFERROR(--MID(G49,FIND("-",G49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))-(IFERROR(--MID(G49,FIND("-",G49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(G49,FIND("-",G49)-1),""))=(AW49))+2*((IFERROR(--MID(G49,FIND("-",G49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J49" s="11" t="str">
+      <c r="J49" s="11">
         <f>IF(OR($C49="",I49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I49,FIND("-",I49)-1),"")=AW49,IFERROR(--MID(I49,FIND("-",I49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))-(IFERROR(--MID(I49,FIND("-",I49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))-(IFERROR(--MID(I49,FIND("-",I49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(I49,FIND("-",I49)-1),""))=(AW49))+2*((IFERROR(--MID(I49,FIND("-",I49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L49" s="11" t="str">
+      <c r="L49" s="11">
         <f>IF(OR($C49="",K49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K49,FIND("-",K49)-1),"")=AW49,IFERROR(--MID(K49,FIND("-",K49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))-(IFERROR(--MID(K49,FIND("-",K49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))-(IFERROR(--MID(K49,FIND("-",K49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(K49,FIND("-",K49)-1),""))=(AW49))+2*((IFERROR(--MID(K49,FIND("-",K49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M49" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N49" s="11" t="str">
+      <c r="N49" s="11">
         <f>IF(OR($C49="",M49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M49,FIND("-",M49)-1),"")=AW49,IFERROR(--MID(M49,FIND("-",M49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))-(IFERROR(--MID(M49,FIND("-",M49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))-(IFERROR(--MID(M49,FIND("-",M49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(M49,FIND("-",M49)-1),""))=(AW49))+2*((IFERROR(--MID(M49,FIND("-",M49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P49" s="11" t="str">
+      <c r="P49" s="11">
         <f>IF(OR($C49="",O49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O49,FIND("-",O49)-1),"")=AW49,IFERROR(--MID(O49,FIND("-",O49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))-(IFERROR(--MID(O49,FIND("-",O49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))-(IFERROR(--MID(O49,FIND("-",O49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(O49,FIND("-",O49)-1),""))=(AW49))+2*((IFERROR(--MID(O49,FIND("-",O49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q49" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R49" s="11" t="str">
+      <c r="R49" s="11">
         <f>IF(OR($C49="",Q49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q49,FIND("-",Q49)-1),"")=AW49,IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))-(IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))-(IFERROR(--MID(Q49,FIND("-",Q49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(Q49,FIND("-",Q49)-1),""))=(AW49))+2*((IFERROR(--MID(Q49,FIND("-",Q49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S49" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="T49" s="11" t="str">
+      <c r="T49" s="11">
         <f>IF(OR($C49="",S49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S49,FIND("-",S49)-1),"")=AW49,IFERROR(--MID(S49,FIND("-",S49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))-(IFERROR(--MID(S49,FIND("-",S49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))-(IFERROR(--MID(S49,FIND("-",S49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(S49,FIND("-",S49)-1),""))=(AW49))+2*((IFERROR(--MID(S49,FIND("-",S49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U49" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V49" s="11" t="str">
+      <c r="V49" s="11">
         <f>IF(OR($C49="",U49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U49,FIND("-",U49)-1),"")=AW49,IFERROR(--MID(U49,FIND("-",U49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))-(IFERROR(--MID(U49,FIND("-",U49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))-(IFERROR(--MID(U49,FIND("-",U49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(U49,FIND("-",U49)-1),""))=(AW49))+2*((IFERROR(--MID(U49,FIND("-",U49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X49" s="11" t="str">
+      <c r="X49" s="11">
         <f>IF(OR($C49="",W49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W49,FIND("-",W49)-1),"")=AW49,IFERROR(--MID(W49,FIND("-",W49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))-(IFERROR(--MID(W49,FIND("-",W49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))-(IFERROR(--MID(W49,FIND("-",W49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(W49,FIND("-",W49)-1),""))=(AW49))+2*((IFERROR(--MID(W49,FIND("-",W49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y49" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z49" s="11" t="str">
+      <c r="Z49" s="11">
         <f>IF(OR($C49="",Y49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y49,FIND("-",Y49)-1),"")=AW49,IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))-(IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))-(IFERROR(--MID(Y49,FIND("-",Y49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(Y49,FIND("-",Y49)-1),""))=(AW49))+2*((IFERROR(--MID(Y49,FIND("-",Y49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA49" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AB49" s="11" t="str">
+      <c r="AB49" s="11">
         <f>IF(OR($C49="",AA49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA49,FIND("-",AA49)-1),"")=AW49,IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))-(IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))-(IFERROR(--MID(AA49,FIND("-",AA49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AA49,FIND("-",AA49)-1),""))=(AW49))+2*((IFERROR(--MID(AA49,FIND("-",AA49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC49" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AD49" s="11" t="str">
+      <c r="AD49" s="11">
         <f>IF(OR($C49="",AC49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC49,FIND("-",AC49)-1),"")=AW49,IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))-(IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))-(IFERROR(--MID(AC49,FIND("-",AC49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AC49,FIND("-",AC49)-1),""))=(AW49))+2*((IFERROR(--MID(AC49,FIND("-",AC49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF49" s="11" t="str">
+      <c r="AF49" s="11">
         <f>IF(OR($C49="",AE49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE49,FIND("-",AE49)-1),"")=AW49,IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))-(IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))-(IFERROR(--MID(AE49,FIND("-",AE49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AE49,FIND("-",AE49)-1),""))=(AW49))+2*((IFERROR(--MID(AE49,FIND("-",AE49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG49" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH49" s="11" t="str">
+      <c r="AH49" s="11">
         <f>IF(OR($C49="",AG49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG49,FIND("-",AG49)-1),"")=AW49,IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))-(IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))-(IFERROR(--MID(AG49,FIND("-",AG49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AG49,FIND("-",AG49)-1),""))=(AW49))+2*((IFERROR(--MID(AG49,FIND("-",AG49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI49" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ49" s="11" t="str">
+      <c r="AJ49" s="11">
         <f>IF(OR($C49="",AI49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI49,FIND("-",AI49)-1),"")=AW49,IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))-(IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))-(IFERROR(--MID(AI49,FIND("-",AI49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AI49,FIND("-",AI49)-1),""))=(AW49))+2*((IFERROR(--MID(AI49,FIND("-",AI49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AL49" s="11" t="str">
+      <c r="AL49" s="11">
         <f>IF(OR($C49="",AK49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK49,FIND("-",AK49)-1),"")=AW49,IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))-(IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))-(IFERROR(--MID(AK49,FIND("-",AK49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AK49,FIND("-",AK49)-1),""))=(AW49))+2*((IFERROR(--MID(AK49,FIND("-",AK49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN49" s="11" t="str">
+      <c r="AN49" s="11">
         <f>IF(OR($C49="",AM49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM49,FIND("-",AM49)-1),"")=AW49,IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))-(IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))-(IFERROR(--MID(AM49,FIND("-",AM49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AM49,FIND("-",AM49)-1),""))=(AW49))+2*((IFERROR(--MID(AM49,FIND("-",AM49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO49" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP49" s="11" t="str">
+      <c r="AP49" s="11">
         <f>IF(OR($C49="",AO49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO49,FIND("-",AO49)-1),"")=AW49,IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))-(IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))-(IFERROR(--MID(AO49,FIND("-",AO49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AO49,FIND("-",AO49)-1),""))=(AW49))+2*((IFERROR(--MID(AO49,FIND("-",AO49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ49" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR49" s="11" t="str">
+      <c r="AR49" s="11">
         <f>IF(OR($C49="",AQ49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),"")=AW49,IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))-(IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))-(IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AQ49,FIND("-",AQ49)-1),""))=(AW49))+2*((IFERROR(--MID(AQ49,FIND("-",AQ49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS49" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT49" s="11" t="str">
+      <c r="AT49" s="11">
         <f>IF(OR($C49="",AS49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS49,FIND("-",AS49)-1),"")=AW49,IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))-(IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))-(IFERROR(--MID(AS49,FIND("-",AS49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AS49,FIND("-",AS49)-1),""))=(AW49))+2*((IFERROR(--MID(AS49,FIND("-",AS49)+1,99),""))=(AX49))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU49" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV49" s="11" t="str">
+      <c r="AV49" s="11">
         <f>IF(OR($C49="",AU49=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU49,FIND("-",AU49)-1),"")=AW49,IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")=AX49),10,5*(SIGN((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))-(IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")))=SIGN((AW49)-(AX49)))+2*(((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))-(IFERROR(--MID(AU49,FIND("-",AU49)+1,99),"")))=((AW49)-(AX49)))+2*((IFERROR(--LEFT(AU49,FIND("-",AU49)-1),""))=(AW49))+2*((IFERROR(--MID(AU49,FIND("-",AU49)+1,99),""))=(AX49))),""))</f>
-        <v/>
-      </c>
-      <c r="AW49" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW49" s="11">
         <f>IF($C49="","",IFERROR(--LEFT($C49,FIND("-",$C49)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX49" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX49" s="11">
         <f>IF($C49="","",IFERROR(--MID($C49,FIND("-",$C49)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8211,171 +8213,173 @@
       <c r="B52" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
+      <c r="C52" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D52" s="1" t="s">
         <v>60</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F52" s="11" t="str">
+      <c r="F52" s="11">
         <f>IF(OR($C52="",E52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E52,FIND("-",E52)-1),"")=AW52,IFERROR(--MID(E52,FIND("-",E52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))-(IFERROR(--MID(E52,FIND("-",E52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))-(IFERROR(--MID(E52,FIND("-",E52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(E52,FIND("-",E52)-1),""))=(AW52))+2*((IFERROR(--MID(E52,FIND("-",E52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H52" s="11" t="str">
+      <c r="H52" s="11">
         <f>IF(OR($C52="",G52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G52,FIND("-",G52)-1),"")=AW52,IFERROR(--MID(G52,FIND("-",G52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))-(IFERROR(--MID(G52,FIND("-",G52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))-(IFERROR(--MID(G52,FIND("-",G52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(G52,FIND("-",G52)-1),""))=(AW52))+2*((IFERROR(--MID(G52,FIND("-",G52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I52" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J52" s="11" t="str">
+      <c r="J52" s="11">
         <f>IF(OR($C52="",I52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I52,FIND("-",I52)-1),"")=AW52,IFERROR(--MID(I52,FIND("-",I52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))-(IFERROR(--MID(I52,FIND("-",I52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))-(IFERROR(--MID(I52,FIND("-",I52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(I52,FIND("-",I52)-1),""))=(AW52))+2*((IFERROR(--MID(I52,FIND("-",I52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K52" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L52" s="11" t="str">
+      <c r="L52" s="11">
         <f>IF(OR($C52="",K52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K52,FIND("-",K52)-1),"")=AW52,IFERROR(--MID(K52,FIND("-",K52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))-(IFERROR(--MID(K52,FIND("-",K52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))-(IFERROR(--MID(K52,FIND("-",K52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(K52,FIND("-",K52)-1),""))=(AW52))+2*((IFERROR(--MID(K52,FIND("-",K52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N52" s="11" t="str">
+      <c r="N52" s="11">
         <f>IF(OR($C52="",M52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M52,FIND("-",M52)-1),"")=AW52,IFERROR(--MID(M52,FIND("-",M52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))-(IFERROR(--MID(M52,FIND("-",M52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))-(IFERROR(--MID(M52,FIND("-",M52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(M52,FIND("-",M52)-1),""))=(AW52))+2*((IFERROR(--MID(M52,FIND("-",M52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P52" s="11" t="str">
+      <c r="P52" s="11">
         <f>IF(OR($C52="",O52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O52,FIND("-",O52)-1),"")=AW52,IFERROR(--MID(O52,FIND("-",O52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))-(IFERROR(--MID(O52,FIND("-",O52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))-(IFERROR(--MID(O52,FIND("-",O52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(O52,FIND("-",O52)-1),""))=(AW52))+2*((IFERROR(--MID(O52,FIND("-",O52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q52" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="R52" s="11" t="str">
+      <c r="R52" s="11">
         <f>IF(OR($C52="",Q52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q52,FIND("-",Q52)-1),"")=AW52,IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))-(IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))-(IFERROR(--MID(Q52,FIND("-",Q52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(Q52,FIND("-",Q52)-1),""))=(AW52))+2*((IFERROR(--MID(Q52,FIND("-",Q52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S52" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T52" s="11" t="str">
+      <c r="T52" s="11">
         <f>IF(OR($C52="",S52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S52,FIND("-",S52)-1),"")=AW52,IFERROR(--MID(S52,FIND("-",S52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))-(IFERROR(--MID(S52,FIND("-",S52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))-(IFERROR(--MID(S52,FIND("-",S52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(S52,FIND("-",S52)-1),""))=(AW52))+2*((IFERROR(--MID(S52,FIND("-",S52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V52" s="11" t="str">
+      <c r="V52" s="11">
         <f>IF(OR($C52="",U52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U52,FIND("-",U52)-1),"")=AW52,IFERROR(--MID(U52,FIND("-",U52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))-(IFERROR(--MID(U52,FIND("-",U52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))-(IFERROR(--MID(U52,FIND("-",U52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(U52,FIND("-",U52)-1),""))=(AW52))+2*((IFERROR(--MID(U52,FIND("-",U52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W52" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X52" s="11" t="str">
+      <c r="X52" s="11">
         <f>IF(OR($C52="",W52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W52,FIND("-",W52)-1),"")=AW52,IFERROR(--MID(W52,FIND("-",W52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))-(IFERROR(--MID(W52,FIND("-",W52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))-(IFERROR(--MID(W52,FIND("-",W52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(W52,FIND("-",W52)-1),""))=(AW52))+2*((IFERROR(--MID(W52,FIND("-",W52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Y52" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="Z52" s="11" t="str">
+      <c r="Z52" s="11">
         <f>IF(OR($C52="",Y52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y52,FIND("-",Y52)-1),"")=AW52,IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))-(IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))-(IFERROR(--MID(Y52,FIND("-",Y52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(Y52,FIND("-",Y52)-1),""))=(AW52))+2*((IFERROR(--MID(Y52,FIND("-",Y52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA52" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB52" s="11" t="str">
+      <c r="AB52" s="11">
         <f>IF(OR($C52="",AA52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA52,FIND("-",AA52)-1),"")=AW52,IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))-(IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))-(IFERROR(--MID(AA52,FIND("-",AA52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AA52,FIND("-",AA52)-1),""))=(AW52))+2*((IFERROR(--MID(AA52,FIND("-",AA52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AD52" s="11" t="str">
+      <c r="AD52" s="11">
         <f>IF(OR($C52="",AC52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC52,FIND("-",AC52)-1),"")=AW52,IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))-(IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))-(IFERROR(--MID(AC52,FIND("-",AC52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AC52,FIND("-",AC52)-1),""))=(AW52))+2*((IFERROR(--MID(AC52,FIND("-",AC52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AE52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF52" s="11" t="str">
+      <c r="AF52" s="11">
         <f>IF(OR($C52="",AE52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE52,FIND("-",AE52)-1),"")=AW52,IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))-(IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))-(IFERROR(--MID(AE52,FIND("-",AE52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AE52,FIND("-",AE52)-1),""))=(AW52))+2*((IFERROR(--MID(AE52,FIND("-",AE52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG52" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH52" s="11" t="str">
+      <c r="AH52" s="11">
         <f>IF(OR($C52="",AG52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG52,FIND("-",AG52)-1),"")=AW52,IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))-(IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))-(IFERROR(--MID(AG52,FIND("-",AG52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AG52,FIND("-",AG52)-1),""))=(AW52))+2*((IFERROR(--MID(AG52,FIND("-",AG52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI52" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ52" s="11" t="str">
+      <c r="AJ52" s="11">
         <f>IF(OR($C52="",AI52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI52,FIND("-",AI52)-1),"")=AW52,IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))-(IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))-(IFERROR(--MID(AI52,FIND("-",AI52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AI52,FIND("-",AI52)-1),""))=(AW52))+2*((IFERROR(--MID(AI52,FIND("-",AI52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK52" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AL52" s="11" t="str">
+      <c r="AL52" s="11">
         <f>IF(OR($C52="",AK52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK52,FIND("-",AK52)-1),"")=AW52,IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))-(IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))-(IFERROR(--MID(AK52,FIND("-",AK52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AK52,FIND("-",AK52)-1),""))=(AW52))+2*((IFERROR(--MID(AK52,FIND("-",AK52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AN52" s="11" t="str">
+      <c r="AN52" s="11">
         <f>IF(OR($C52="",AM52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM52,FIND("-",AM52)-1),"")=AW52,IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))-(IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))-(IFERROR(--MID(AM52,FIND("-",AM52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AM52,FIND("-",AM52)-1),""))=(AW52))+2*((IFERROR(--MID(AM52,FIND("-",AM52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP52" s="11" t="str">
+      <c r="AP52" s="11">
         <f>IF(OR($C52="",AO52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO52,FIND("-",AO52)-1),"")=AW52,IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))-(IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))-(IFERROR(--MID(AO52,FIND("-",AO52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AO52,FIND("-",AO52)-1),""))=(AW52))+2*((IFERROR(--MID(AO52,FIND("-",AO52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ52" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR52" s="11" t="str">
+      <c r="AR52" s="11">
         <f t="shared" ref="AR52:AR57" si="4">IF(OR($C52="",AQ52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),"")=AW52,IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))-(IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))-(IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AQ52,FIND("-",AQ52)-1),""))=(AW52))+2*((IFERROR(--MID(AQ52,FIND("-",AQ52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT52" s="11" t="str">
+      <c r="AT52" s="11">
         <f t="shared" ref="AT52:AT57" si="5">IF(OR($C52="",AS52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS52,FIND("-",AS52)-1),"")=AW52,IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))-(IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))-(IFERROR(--MID(AS52,FIND("-",AS52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AS52,FIND("-",AS52)-1),""))=(AW52))+2*((IFERROR(--MID(AS52,FIND("-",AS52)+1,99),""))=(AX52))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU52" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV52" s="11" t="str">
+      <c r="AV52" s="11">
         <f>IF(OR($C52="",AU52=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU52,FIND("-",AU52)-1),"")=AW52,IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")=AX52),10,5*(SIGN((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))-(IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")))=SIGN((AW52)-(AX52)))+2*(((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))-(IFERROR(--MID(AU52,FIND("-",AU52)+1,99),"")))=((AW52)-(AX52)))+2*((IFERROR(--LEFT(AU52,FIND("-",AU52)-1),""))=(AW52))+2*((IFERROR(--MID(AU52,FIND("-",AU52)+1,99),""))=(AX52))),""))</f>
-        <v/>
-      </c>
-      <c r="AW52" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW52" s="11">
         <f>IF($C52="","",IFERROR(--LEFT($C52,FIND("-",$C52)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX52" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX52" s="11">
         <f>IF($C52="","",IFERROR(--MID($C52,FIND("-",$C52)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -8561,171 +8565,173 @@
       <c r="B54" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="10"/>
+      <c r="C54" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D54" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F54" s="11" t="str">
+      <c r="F54" s="11">
         <f>IF(OR($C54="",E54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E54,FIND("-",E54)-1),"")=AW54,IFERROR(--MID(E54,FIND("-",E54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))-(IFERROR(--MID(E54,FIND("-",E54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))-(IFERROR(--MID(E54,FIND("-",E54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(E54,FIND("-",E54)-1),""))=(AW54))+2*((IFERROR(--MID(E54,FIND("-",E54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H54" s="11" t="str">
+      <c r="H54" s="11">
         <f>IF(OR($C54="",G54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G54,FIND("-",G54)-1),"")=AW54,IFERROR(--MID(G54,FIND("-",G54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))-(IFERROR(--MID(G54,FIND("-",G54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))-(IFERROR(--MID(G54,FIND("-",G54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(G54,FIND("-",G54)-1),""))=(AW54))+2*((IFERROR(--MID(G54,FIND("-",G54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J54" s="11" t="str">
+      <c r="J54" s="11">
         <f>IF(OR($C54="",I54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I54,FIND("-",I54)-1),"")=AW54,IFERROR(--MID(I54,FIND("-",I54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))-(IFERROR(--MID(I54,FIND("-",I54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))-(IFERROR(--MID(I54,FIND("-",I54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(I54,FIND("-",I54)-1),""))=(AW54))+2*((IFERROR(--MID(I54,FIND("-",I54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K54" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L54" s="11" t="str">
+      <c r="L54" s="11">
         <f>IF(OR($C54="",K54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K54,FIND("-",K54)-1),"")=AW54,IFERROR(--MID(K54,FIND("-",K54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))-(IFERROR(--MID(K54,FIND("-",K54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))-(IFERROR(--MID(K54,FIND("-",K54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(K54,FIND("-",K54)-1),""))=(AW54))+2*((IFERROR(--MID(K54,FIND("-",K54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M54" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N54" s="11" t="str">
+      <c r="N54" s="11">
         <f>IF(OR($C54="",M54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M54,FIND("-",M54)-1),"")=AW54,IFERROR(--MID(M54,FIND("-",M54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))-(IFERROR(--MID(M54,FIND("-",M54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))-(IFERROR(--MID(M54,FIND("-",M54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(M54,FIND("-",M54)-1),""))=(AW54))+2*((IFERROR(--MID(M54,FIND("-",M54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P54" s="11" t="str">
+      <c r="P54" s="11">
         <f>IF(OR($C54="",O54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O54,FIND("-",O54)-1),"")=AW54,IFERROR(--MID(O54,FIND("-",O54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))-(IFERROR(--MID(O54,FIND("-",O54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))-(IFERROR(--MID(O54,FIND("-",O54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(O54,FIND("-",O54)-1),""))=(AW54))+2*((IFERROR(--MID(O54,FIND("-",O54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q54" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="R54" s="11" t="str">
+      <c r="R54" s="11">
         <f>IF(OR($C54="",Q54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q54,FIND("-",Q54)-1),"")=AW54,IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))-(IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))-(IFERROR(--MID(Q54,FIND("-",Q54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(Q54,FIND("-",Q54)-1),""))=(AW54))+2*((IFERROR(--MID(Q54,FIND("-",Q54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S54" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T54" s="11" t="str">
+      <c r="T54" s="11">
         <f>IF(OR($C54="",S54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S54,FIND("-",S54)-1),"")=AW54,IFERROR(--MID(S54,FIND("-",S54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))-(IFERROR(--MID(S54,FIND("-",S54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))-(IFERROR(--MID(S54,FIND("-",S54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(S54,FIND("-",S54)-1),""))=(AW54))+2*((IFERROR(--MID(S54,FIND("-",S54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V54" s="11" t="str">
+      <c r="V54" s="11">
         <f>IF(OR($C54="",U54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U54,FIND("-",U54)-1),"")=AW54,IFERROR(--MID(U54,FIND("-",U54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))-(IFERROR(--MID(U54,FIND("-",U54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))-(IFERROR(--MID(U54,FIND("-",U54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(U54,FIND("-",U54)-1),""))=(AW54))+2*((IFERROR(--MID(U54,FIND("-",U54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X54" s="11" t="str">
+      <c r="X54" s="11">
         <f>IF(OR($C54="",W54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W54,FIND("-",W54)-1),"")=AW54,IFERROR(--MID(W54,FIND("-",W54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))-(IFERROR(--MID(W54,FIND("-",W54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))-(IFERROR(--MID(W54,FIND("-",W54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(W54,FIND("-",W54)-1),""))=(AW54))+2*((IFERROR(--MID(W54,FIND("-",W54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z54" s="11" t="str">
+      <c r="Z54" s="11">
         <f>IF(OR($C54="",Y54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y54,FIND("-",Y54)-1),"")=AW54,IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))-(IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))-(IFERROR(--MID(Y54,FIND("-",Y54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(Y54,FIND("-",Y54)-1),""))=(AW54))+2*((IFERROR(--MID(Y54,FIND("-",Y54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB54" s="11" t="str">
+      <c r="AB54" s="11">
         <f>IF(OR($C54="",AA54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA54,FIND("-",AA54)-1),"")=AW54,IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))-(IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))-(IFERROR(--MID(AA54,FIND("-",AA54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AA54,FIND("-",AA54)-1),""))=(AW54))+2*((IFERROR(--MID(AA54,FIND("-",AA54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD54" s="11" t="str">
+      <c r="AD54" s="11">
         <f>IF(OR($C54="",AC54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC54,FIND("-",AC54)-1),"")=AW54,IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))-(IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))-(IFERROR(--MID(AC54,FIND("-",AC54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AC54,FIND("-",AC54)-1),""))=(AW54))+2*((IFERROR(--MID(AC54,FIND("-",AC54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF54" s="11" t="str">
+      <c r="AF54" s="11">
         <f>IF(OR($C54="",AE54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE54,FIND("-",AE54)-1),"")=AW54,IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))-(IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))-(IFERROR(--MID(AE54,FIND("-",AE54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AE54,FIND("-",AE54)-1),""))=(AW54))+2*((IFERROR(--MID(AE54,FIND("-",AE54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH54" s="11" t="str">
+      <c r="AH54" s="11">
         <f>IF(OR($C54="",AG54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG54,FIND("-",AG54)-1),"")=AW54,IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))-(IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))-(IFERROR(--MID(AG54,FIND("-",AG54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AG54,FIND("-",AG54)-1),""))=(AW54))+2*((IFERROR(--MID(AG54,FIND("-",AG54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ54" s="11" t="str">
+      <c r="AJ54" s="11">
         <f>IF(OR($C54="",AI54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI54,FIND("-",AI54)-1),"")=AW54,IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))-(IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))-(IFERROR(--MID(AI54,FIND("-",AI54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AI54,FIND("-",AI54)-1),""))=(AW54))+2*((IFERROR(--MID(AI54,FIND("-",AI54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK54" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL54" s="11" t="str">
+      <c r="AL54" s="11">
         <f>IF(OR($C54="",AK54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK54,FIND("-",AK54)-1),"")=AW54,IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))-(IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))-(IFERROR(--MID(AK54,FIND("-",AK54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AK54,FIND("-",AK54)-1),""))=(AW54))+2*((IFERROR(--MID(AK54,FIND("-",AK54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM54" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN54" s="11" t="str">
+      <c r="AN54" s="11">
         <f>IF(OR($C54="",AM54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM54,FIND("-",AM54)-1),"")=AW54,IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))-(IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))-(IFERROR(--MID(AM54,FIND("-",AM54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AM54,FIND("-",AM54)-1),""))=(AW54))+2*((IFERROR(--MID(AM54,FIND("-",AM54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP54" s="11" t="str">
+      <c r="AP54" s="11">
         <f>IF(OR($C54="",AO54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO54,FIND("-",AO54)-1),"")=AW54,IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))-(IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))-(IFERROR(--MID(AO54,FIND("-",AO54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AO54,FIND("-",AO54)-1),""))=(AW54))+2*((IFERROR(--MID(AO54,FIND("-",AO54)+1,99),""))=(AX54))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ54" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR54" s="11" t="str">
+      <c r="AR54" s="11">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS54" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT54" s="11" t="str">
+      <c r="AT54" s="11">
         <f t="shared" si="5"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU54" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV54" s="11" t="str">
+      <c r="AV54" s="11">
         <f>IF(OR($C54="",AU54=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU54,FIND("-",AU54)-1),"")=AW54,IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")=AX54),10,5*(SIGN((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))-(IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")))=SIGN((AW54)-(AX54)))+2*(((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))-(IFERROR(--MID(AU54,FIND("-",AU54)+1,99),"")))=((AW54)-(AX54)))+2*((IFERROR(--LEFT(AU54,FIND("-",AU54)-1),""))=(AW54))+2*((IFERROR(--MID(AU54,FIND("-",AU54)+1,99),""))=(AX54))),""))</f>
-        <v/>
-      </c>
-      <c r="AW54" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW54" s="11">
         <f>IF($C54="","",IFERROR(--LEFT($C54,FIND("-",$C54)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX54" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX54" s="11">
         <f>IF($C54="","",IFERROR(--MID($C54,FIND("-",$C54)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26517,7 +26523,7 @@
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26526,64 +26532,64 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
-        <v>146</v>
+        <f>C3+D3</f>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>130</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>143</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f t="shared" si="1"/>
-        <v>130</v>
+        <f>C4+D4</f>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>127</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>143</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f t="shared" si="1"/>
-        <v>127</v>
+        <f>C5+D5</f>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -26592,64 +26598,64 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f t="shared" si="1"/>
-        <v>126</v>
+        <f>C6+D6</f>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>125</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>141</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f t="shared" si="1"/>
-        <v>125</v>
+        <f>C7+D7</f>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>125</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>139</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f t="shared" si="1"/>
-        <v>125</v>
+        <f>C8+D8</f>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
@@ -26658,345 +26664,345 @@
       </c>
       <c r="C9" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D9" s="11">
         <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f t="shared" si="1"/>
-        <v>124</v>
+        <f>C9+D9</f>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>124</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>138</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f t="shared" si="1"/>
-        <v>124</v>
+        <f>C10+D10</f>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>124</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>135</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f t="shared" si="1"/>
-        <v>124</v>
+        <f>C11+D11</f>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
         <v>10</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>121</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>134</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f t="shared" si="1"/>
-        <v>121</v>
+        <f>C12+D12</f>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>117</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>133</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f t="shared" si="1"/>
-        <v>117</v>
+        <f>C13+D13</f>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>117</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>131</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f t="shared" si="1"/>
-        <v>117</v>
+        <f>C14+D14</f>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>117</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>131</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f t="shared" si="1"/>
-        <v>117</v>
+        <f>C15+D15</f>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>117</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>126</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f t="shared" si="1"/>
-        <v>117</v>
+        <f>C16+D16</f>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
         <v>15</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>109</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>122</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f t="shared" si="1"/>
-        <v>109</v>
+        <f>C17+D17</f>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>109</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>116</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f t="shared" si="1"/>
-        <v>109</v>
+        <f>C18+D18</f>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>104</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>114</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f t="shared" si="1"/>
-        <v>104</v>
+        <f>C19+D19</f>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>107</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>113</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" si="1"/>
-        <v>107</v>
+        <f>C20+D20</f>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>110</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C21+D21</f>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f t="shared" si="0"/>
+        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>100</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>104</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f>C22+D22</f>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>101</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>102</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f t="shared" si="1"/>
-        <v>101</v>
+        <f>C23+D23</f>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <v>21</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>96</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>102</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f t="shared" si="1"/>
-        <v>96</v>
+        <f>C24+D24</f>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1585" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{825807E3-E369-44C4-9124-C8E65F5763C8}"/>
+  <xr:revisionPtr revIDLastSave="1590" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8BCA05-574A-4194-A70C-8FF320A6B3A5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1361,55 +1361,6 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1424,6 +1375,55 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1789,106 +1789,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="52"/>
-      <c r="G1" s="41" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="42"/>
-      <c r="I1" s="41" t="s">
+      <c r="H1" s="43"/>
+      <c r="I1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="42"/>
-      <c r="K1" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="41" t="s">
+      <c r="J1" s="43"/>
+      <c r="K1" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="43"/>
+      <c r="M1" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="42"/>
-      <c r="O1" s="41" t="s">
+      <c r="N1" s="43"/>
+      <c r="O1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="41" t="s">
+      <c r="P1" s="43"/>
+      <c r="Q1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="42"/>
-      <c r="S1" s="41" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="42"/>
-      <c r="U1" s="41" t="s">
+      <c r="T1" s="43"/>
+      <c r="U1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="42"/>
-      <c r="W1" s="41" t="s">
+      <c r="V1" s="43"/>
+      <c r="W1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="42"/>
-      <c r="Y1" s="41" t="s">
+      <c r="X1" s="43"/>
+      <c r="Y1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="41" t="s">
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="41" t="s">
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="42"/>
-      <c r="AE1" s="41" t="s">
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="42"/>
-      <c r="AG1" s="41" t="s">
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="42"/>
-      <c r="AI1" s="41" t="s">
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="42"/>
-      <c r="AK1" s="41" t="s">
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="42"/>
-      <c r="AM1" s="41" t="s">
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="42"/>
-      <c r="AO1" s="41" t="s">
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="42"/>
-      <c r="AQ1" s="41" t="s">
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="42"/>
-      <c r="AS1" s="41" t="s">
+      <c r="AR1" s="43"/>
+      <c r="AS1" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="41" t="s">
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="53"/>
+      <c r="AV1" s="51"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1897,10 +1897,10 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="50"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="47"/>
+      <c r="A2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="56"/>
       <c r="E2" s="23" t="s">
         <v>27</v>
       </c>
@@ -2041,110 +2041,110 @@
       </c>
     </row>
     <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="44"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="44"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="44"/>
-      <c r="W3" s="44"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="44"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="44"/>
-      <c r="AB3" s="44"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="44"/>
-      <c r="AE3" s="44"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="44"/>
-      <c r="AH3" s="44"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="44"/>
-      <c r="AK3" s="44"/>
-      <c r="AL3" s="44"/>
-      <c r="AM3" s="44"/>
-      <c r="AN3" s="44"/>
-      <c r="AO3" s="44"/>
-      <c r="AP3" s="44"/>
-      <c r="AQ3" s="44"/>
-      <c r="AR3" s="44"/>
-      <c r="AS3" s="44"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="44"/>
-      <c r="AV3" s="45"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="58"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
     <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="39"/>
-      <c r="W4" s="39"/>
-      <c r="X4" s="39"/>
-      <c r="Y4" s="39"/>
-      <c r="Z4" s="39"/>
-      <c r="AA4" s="39"/>
-      <c r="AB4" s="39"/>
-      <c r="AC4" s="39"/>
-      <c r="AD4" s="39"/>
-      <c r="AE4" s="39"/>
-      <c r="AF4" s="39"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="39"/>
-      <c r="AI4" s="39"/>
-      <c r="AJ4" s="39"/>
-      <c r="AK4" s="39"/>
-      <c r="AL4" s="39"/>
-      <c r="AM4" s="39"/>
-      <c r="AN4" s="39"/>
-      <c r="AO4" s="39"/>
-      <c r="AP4" s="39"/>
-      <c r="AQ4" s="39"/>
-      <c r="AR4" s="39"/>
-      <c r="AS4" s="39"/>
-      <c r="AT4" s="39"/>
-      <c r="AU4" s="39"/>
-      <c r="AV4" s="40"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
+      <c r="AT4" s="40"/>
+      <c r="AU4" s="40"/>
+      <c r="AV4" s="41"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
@@ -2383,56 +2383,56 @@
       <c r="AX6" s="12"/>
     </row>
     <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="39"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="39"/>
-      <c r="Z7" s="39"/>
-      <c r="AA7" s="39"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="39"/>
-      <c r="AE7" s="39"/>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="39"/>
-      <c r="AI7" s="39"/>
-      <c r="AJ7" s="39"/>
-      <c r="AK7" s="39"/>
-      <c r="AL7" s="39"/>
-      <c r="AM7" s="39"/>
-      <c r="AN7" s="39"/>
-      <c r="AO7" s="39"/>
-      <c r="AP7" s="39"/>
-      <c r="AQ7" s="39"/>
-      <c r="AR7" s="39"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="39"/>
-      <c r="AU7" s="39"/>
-      <c r="AV7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="41"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
@@ -2847,56 +2847,56 @@
       <c r="AX10" s="12"/>
     </row>
     <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
-      <c r="AK11" s="39"/>
-      <c r="AL11" s="39"/>
-      <c r="AM11" s="39"/>
-      <c r="AN11" s="39"/>
-      <c r="AO11" s="39"/>
-      <c r="AP11" s="39"/>
-      <c r="AQ11" s="39"/>
-      <c r="AR11" s="39"/>
-      <c r="AS11" s="39"/>
-      <c r="AT11" s="39"/>
-      <c r="AU11" s="39"/>
-      <c r="AV11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="40"/>
+      <c r="AR11" s="40"/>
+      <c r="AS11" s="40"/>
+      <c r="AT11" s="40"/>
+      <c r="AU11" s="40"/>
+      <c r="AV11" s="41"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
@@ -3311,56 +3311,56 @@
       <c r="AX14" s="12"/>
     </row>
     <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39"/>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="39"/>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
-      <c r="U15" s="39"/>
-      <c r="V15" s="39"/>
-      <c r="W15" s="39"/>
-      <c r="X15" s="39"/>
-      <c r="Y15" s="39"/>
-      <c r="Z15" s="39"/>
-      <c r="AA15" s="39"/>
-      <c r="AB15" s="39"/>
-      <c r="AC15" s="39"/>
-      <c r="AD15" s="39"/>
-      <c r="AE15" s="39"/>
-      <c r="AF15" s="39"/>
-      <c r="AG15" s="39"/>
-      <c r="AH15" s="39"/>
-      <c r="AI15" s="39"/>
-      <c r="AJ15" s="39"/>
-      <c r="AK15" s="39"/>
-      <c r="AL15" s="39"/>
-      <c r="AM15" s="39"/>
-      <c r="AN15" s="39"/>
-      <c r="AO15" s="39"/>
-      <c r="AP15" s="39"/>
-      <c r="AQ15" s="39"/>
-      <c r="AR15" s="39"/>
-      <c r="AS15" s="39"/>
-      <c r="AT15" s="39"/>
-      <c r="AU15" s="39"/>
-      <c r="AV15" s="40"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="40"/>
+      <c r="AS15" s="40"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="40"/>
+      <c r="AV15" s="41"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
@@ -4303,56 +4303,56 @@
       <c r="AX21" s="12"/>
     </row>
     <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="39"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="39"/>
-      <c r="W22" s="39"/>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
-      <c r="AA22" s="39"/>
-      <c r="AB22" s="39"/>
-      <c r="AC22" s="39"/>
-      <c r="AD22" s="39"/>
-      <c r="AE22" s="39"/>
-      <c r="AF22" s="39"/>
-      <c r="AG22" s="39"/>
-      <c r="AH22" s="39"/>
-      <c r="AI22" s="39"/>
-      <c r="AJ22" s="39"/>
-      <c r="AK22" s="39"/>
-      <c r="AL22" s="39"/>
-      <c r="AM22" s="39"/>
-      <c r="AN22" s="39"/>
-      <c r="AO22" s="39"/>
-      <c r="AP22" s="39"/>
-      <c r="AQ22" s="39"/>
-      <c r="AR22" s="39"/>
-      <c r="AS22" s="39"/>
-      <c r="AT22" s="39"/>
-      <c r="AU22" s="39"/>
-      <c r="AV22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="40"/>
+      <c r="AD22" s="40"/>
+      <c r="AE22" s="40"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="40"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="40"/>
+      <c r="AM22" s="40"/>
+      <c r="AN22" s="40"/>
+      <c r="AO22" s="40"/>
+      <c r="AP22" s="40"/>
+      <c r="AQ22" s="40"/>
+      <c r="AR22" s="40"/>
+      <c r="AS22" s="40"/>
+      <c r="AT22" s="40"/>
+      <c r="AU22" s="40"/>
+      <c r="AV22" s="41"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
@@ -5119,56 +5119,56 @@
       <c r="AX27" s="12"/>
     </row>
     <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="35"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="36"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="36"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="36"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="36"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="35"/>
-      <c r="AA28" s="36"/>
-      <c r="AB28" s="35"/>
-      <c r="AC28" s="36"/>
-      <c r="AD28" s="35"/>
-      <c r="AE28" s="36"/>
-      <c r="AF28" s="35"/>
-      <c r="AG28" s="36"/>
-      <c r="AH28" s="35"/>
-      <c r="AI28" s="36"/>
-      <c r="AJ28" s="35"/>
-      <c r="AK28" s="36"/>
-      <c r="AL28" s="35"/>
-      <c r="AM28" s="36"/>
-      <c r="AN28" s="35"/>
-      <c r="AO28" s="36"/>
-      <c r="AP28" s="35"/>
-      <c r="AQ28" s="35"/>
-      <c r="AR28" s="35"/>
-      <c r="AS28" s="35"/>
-      <c r="AT28" s="35"/>
-      <c r="AU28" s="36"/>
-      <c r="AV28" s="37"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="46"/>
+      <c r="AB28" s="45"/>
+      <c r="AC28" s="46"/>
+      <c r="AD28" s="45"/>
+      <c r="AE28" s="46"/>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="46"/>
+      <c r="AH28" s="45"/>
+      <c r="AI28" s="46"/>
+      <c r="AJ28" s="45"/>
+      <c r="AK28" s="46"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="46"/>
+      <c r="AN28" s="45"/>
+      <c r="AO28" s="46"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+      <c r="AR28" s="45"/>
+      <c r="AS28" s="45"/>
+      <c r="AT28" s="45"/>
+      <c r="AU28" s="46"/>
+      <c r="AV28" s="47"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
@@ -5759,56 +5759,56 @@
       <c r="AX32" s="12"/>
     </row>
     <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="35"/>
-      <c r="U33" s="36"/>
-      <c r="V33" s="35"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="35"/>
-      <c r="Y33" s="36"/>
-      <c r="Z33" s="35"/>
-      <c r="AA33" s="36"/>
-      <c r="AB33" s="35"/>
-      <c r="AC33" s="36"/>
-      <c r="AD33" s="35"/>
-      <c r="AE33" s="36"/>
-      <c r="AF33" s="35"/>
-      <c r="AG33" s="36"/>
-      <c r="AH33" s="35"/>
-      <c r="AI33" s="36"/>
-      <c r="AJ33" s="35"/>
-      <c r="AK33" s="36"/>
-      <c r="AL33" s="35"/>
-      <c r="AM33" s="36"/>
-      <c r="AN33" s="35"/>
-      <c r="AO33" s="36"/>
-      <c r="AP33" s="35"/>
-      <c r="AQ33" s="35"/>
-      <c r="AR33" s="35"/>
-      <c r="AS33" s="35"/>
-      <c r="AT33" s="35"/>
-      <c r="AU33" s="36"/>
-      <c r="AV33" s="37"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="45"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="46"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="46"/>
+      <c r="AD33" s="45"/>
+      <c r="AE33" s="46"/>
+      <c r="AF33" s="45"/>
+      <c r="AG33" s="46"/>
+      <c r="AH33" s="45"/>
+      <c r="AI33" s="46"/>
+      <c r="AJ33" s="45"/>
+      <c r="AK33" s="46"/>
+      <c r="AL33" s="45"/>
+      <c r="AM33" s="46"/>
+      <c r="AN33" s="45"/>
+      <c r="AO33" s="46"/>
+      <c r="AP33" s="45"/>
+      <c r="AQ33" s="45"/>
+      <c r="AR33" s="45"/>
+      <c r="AS33" s="45"/>
+      <c r="AT33" s="45"/>
+      <c r="AU33" s="46"/>
+      <c r="AV33" s="47"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
@@ -6751,56 +6751,56 @@
       <c r="AX39" s="12"/>
     </row>
     <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="36"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="36"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="36"/>
-      <c r="T40" s="35"/>
-      <c r="U40" s="36"/>
-      <c r="V40" s="35"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="35"/>
-      <c r="Y40" s="36"/>
-      <c r="Z40" s="35"/>
-      <c r="AA40" s="36"/>
-      <c r="AB40" s="35"/>
-      <c r="AC40" s="36"/>
-      <c r="AD40" s="35"/>
-      <c r="AE40" s="36"/>
-      <c r="AF40" s="35"/>
-      <c r="AG40" s="36"/>
-      <c r="AH40" s="35"/>
-      <c r="AI40" s="36"/>
-      <c r="AJ40" s="35"/>
-      <c r="AK40" s="36"/>
-      <c r="AL40" s="35"/>
-      <c r="AM40" s="36"/>
-      <c r="AN40" s="35"/>
-      <c r="AO40" s="36"/>
-      <c r="AP40" s="35"/>
-      <c r="AQ40" s="35"/>
-      <c r="AR40" s="35"/>
-      <c r="AS40" s="35"/>
-      <c r="AT40" s="35"/>
-      <c r="AU40" s="36"/>
-      <c r="AV40" s="37"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="45"/>
+      <c r="O40" s="46"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="45"/>
+      <c r="S40" s="46"/>
+      <c r="T40" s="45"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="45"/>
+      <c r="W40" s="46"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="46"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="46"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="46"/>
+      <c r="AD40" s="45"/>
+      <c r="AE40" s="46"/>
+      <c r="AF40" s="45"/>
+      <c r="AG40" s="46"/>
+      <c r="AH40" s="45"/>
+      <c r="AI40" s="46"/>
+      <c r="AJ40" s="45"/>
+      <c r="AK40" s="46"/>
+      <c r="AL40" s="45"/>
+      <c r="AM40" s="46"/>
+      <c r="AN40" s="45"/>
+      <c r="AO40" s="46"/>
+      <c r="AP40" s="45"/>
+      <c r="AQ40" s="45"/>
+      <c r="AR40" s="45"/>
+      <c r="AS40" s="45"/>
+      <c r="AT40" s="45"/>
+      <c r="AU40" s="46"/>
+      <c r="AV40" s="47"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
@@ -7567,56 +7567,56 @@
       <c r="AX45" s="12"/>
     </row>
     <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="34" t="s">
+      <c r="A46" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="35"/>
-      <c r="M46" s="36"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="36"/>
-      <c r="P46" s="35"/>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="36"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="36"/>
-      <c r="V46" s="35"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="35"/>
-      <c r="Y46" s="36"/>
-      <c r="Z46" s="35"/>
-      <c r="AA46" s="36"/>
-      <c r="AB46" s="35"/>
-      <c r="AC46" s="36"/>
-      <c r="AD46" s="35"/>
-      <c r="AE46" s="36"/>
-      <c r="AF46" s="35"/>
-      <c r="AG46" s="36"/>
-      <c r="AH46" s="35"/>
-      <c r="AI46" s="36"/>
-      <c r="AJ46" s="35"/>
-      <c r="AK46" s="36"/>
-      <c r="AL46" s="35"/>
-      <c r="AM46" s="36"/>
-      <c r="AN46" s="35"/>
-      <c r="AO46" s="36"/>
-      <c r="AP46" s="35"/>
-      <c r="AQ46" s="35"/>
-      <c r="AR46" s="35"/>
-      <c r="AS46" s="35"/>
-      <c r="AT46" s="35"/>
-      <c r="AU46" s="36"/>
-      <c r="AV46" s="37"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="45"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="45"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="45"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="45"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="45"/>
+      <c r="Y46" s="46"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="46"/>
+      <c r="AB46" s="45"/>
+      <c r="AC46" s="46"/>
+      <c r="AD46" s="45"/>
+      <c r="AE46" s="46"/>
+      <c r="AF46" s="45"/>
+      <c r="AG46" s="46"/>
+      <c r="AH46" s="45"/>
+      <c r="AI46" s="46"/>
+      <c r="AJ46" s="45"/>
+      <c r="AK46" s="46"/>
+      <c r="AL46" s="45"/>
+      <c r="AM46" s="46"/>
+      <c r="AN46" s="45"/>
+      <c r="AO46" s="46"/>
+      <c r="AP46" s="45"/>
+      <c r="AQ46" s="45"/>
+      <c r="AR46" s="45"/>
+      <c r="AS46" s="45"/>
+      <c r="AT46" s="45"/>
+      <c r="AU46" s="46"/>
+      <c r="AV46" s="47"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
@@ -8207,56 +8207,56 @@
       <c r="AX50" s="12"/>
     </row>
     <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="36"/>
-      <c r="N51" s="35"/>
-      <c r="O51" s="36"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="36"/>
-      <c r="R51" s="35"/>
-      <c r="S51" s="36"/>
-      <c r="T51" s="35"/>
-      <c r="U51" s="36"/>
-      <c r="V51" s="35"/>
-      <c r="W51" s="36"/>
-      <c r="X51" s="35"/>
-      <c r="Y51" s="36"/>
-      <c r="Z51" s="35"/>
-      <c r="AA51" s="36"/>
-      <c r="AB51" s="35"/>
-      <c r="AC51" s="36"/>
-      <c r="AD51" s="35"/>
-      <c r="AE51" s="36"/>
-      <c r="AF51" s="35"/>
-      <c r="AG51" s="36"/>
-      <c r="AH51" s="35"/>
-      <c r="AI51" s="36"/>
-      <c r="AJ51" s="35"/>
-      <c r="AK51" s="36"/>
-      <c r="AL51" s="35"/>
-      <c r="AM51" s="36"/>
-      <c r="AN51" s="35"/>
-      <c r="AO51" s="36"/>
-      <c r="AP51" s="35"/>
-      <c r="AQ51" s="35"/>
-      <c r="AR51" s="35"/>
-      <c r="AS51" s="35"/>
-      <c r="AT51" s="35"/>
-      <c r="AU51" s="36"/>
-      <c r="AV51" s="37"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="45"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="45"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="45"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="45"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="45"/>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="45"/>
+      <c r="AA51" s="46"/>
+      <c r="AB51" s="45"/>
+      <c r="AC51" s="46"/>
+      <c r="AD51" s="45"/>
+      <c r="AE51" s="46"/>
+      <c r="AF51" s="45"/>
+      <c r="AG51" s="46"/>
+      <c r="AH51" s="45"/>
+      <c r="AI51" s="46"/>
+      <c r="AJ51" s="45"/>
+      <c r="AK51" s="46"/>
+      <c r="AL51" s="45"/>
+      <c r="AM51" s="46"/>
+      <c r="AN51" s="45"/>
+      <c r="AO51" s="46"/>
+      <c r="AP51" s="45"/>
+      <c r="AQ51" s="45"/>
+      <c r="AR51" s="45"/>
+      <c r="AS51" s="45"/>
+      <c r="AT51" s="45"/>
+      <c r="AU51" s="46"/>
+      <c r="AV51" s="47"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
@@ -9199,56 +9199,56 @@
       <c r="AX57" s="12"/>
     </row>
     <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="34" t="s">
+      <c r="A58" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="35"/>
-      <c r="C58" s="36"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="36"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="36"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="36"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="36"/>
-      <c r="N58" s="35"/>
-      <c r="O58" s="36"/>
-      <c r="P58" s="35"/>
-      <c r="Q58" s="36"/>
-      <c r="R58" s="35"/>
-      <c r="S58" s="36"/>
-      <c r="T58" s="35"/>
-      <c r="U58" s="36"/>
-      <c r="V58" s="35"/>
-      <c r="W58" s="36"/>
-      <c r="X58" s="35"/>
-      <c r="Y58" s="36"/>
-      <c r="Z58" s="35"/>
-      <c r="AA58" s="36"/>
-      <c r="AB58" s="35"/>
-      <c r="AC58" s="36"/>
-      <c r="AD58" s="35"/>
-      <c r="AE58" s="36"/>
-      <c r="AF58" s="35"/>
-      <c r="AG58" s="36"/>
-      <c r="AH58" s="35"/>
-      <c r="AI58" s="36"/>
-      <c r="AJ58" s="35"/>
-      <c r="AK58" s="36"/>
-      <c r="AL58" s="35"/>
-      <c r="AM58" s="36"/>
-      <c r="AN58" s="35"/>
-      <c r="AO58" s="36"/>
-      <c r="AP58" s="35"/>
-      <c r="AQ58" s="35"/>
-      <c r="AR58" s="35"/>
-      <c r="AS58" s="35"/>
-      <c r="AT58" s="35"/>
-      <c r="AU58" s="36"/>
-      <c r="AV58" s="37"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="45"/>
+      <c r="M58" s="46"/>
+      <c r="N58" s="45"/>
+      <c r="O58" s="46"/>
+      <c r="P58" s="45"/>
+      <c r="Q58" s="46"/>
+      <c r="R58" s="45"/>
+      <c r="S58" s="46"/>
+      <c r="T58" s="45"/>
+      <c r="U58" s="46"/>
+      <c r="V58" s="45"/>
+      <c r="W58" s="46"/>
+      <c r="X58" s="45"/>
+      <c r="Y58" s="46"/>
+      <c r="Z58" s="45"/>
+      <c r="AA58" s="46"/>
+      <c r="AB58" s="45"/>
+      <c r="AC58" s="46"/>
+      <c r="AD58" s="45"/>
+      <c r="AE58" s="46"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="46"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
+      <c r="AJ58" s="45"/>
+      <c r="AK58" s="46"/>
+      <c r="AL58" s="45"/>
+      <c r="AM58" s="46"/>
+      <c r="AN58" s="45"/>
+      <c r="AO58" s="46"/>
+      <c r="AP58" s="45"/>
+      <c r="AQ58" s="45"/>
+      <c r="AR58" s="45"/>
+      <c r="AS58" s="45"/>
+      <c r="AT58" s="45"/>
+      <c r="AU58" s="46"/>
+      <c r="AV58" s="47"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
@@ -9611,171 +9611,173 @@
       <c r="B61" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="10" t="s">
+        <v>63</v>
+      </c>
       <c r="D61" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F61" s="11" t="str">
+      <c r="F61" s="11">
         <f>IF(OR($C61="",E61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E61,FIND("-",E61)-1),"")=AW61,IFERROR(--MID(E61,FIND("-",E61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))-(IFERROR(--MID(E61,FIND("-",E61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))-(IFERROR(--MID(E61,FIND("-",E61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(E61,FIND("-",E61)-1),""))=(AW61))+2*((IFERROR(--MID(E61,FIND("-",E61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H61" s="11" t="str">
+      <c r="H61" s="11">
         <f>IF(OR($C61="",G61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G61,FIND("-",G61)-1),"")=AW61,IFERROR(--MID(G61,FIND("-",G61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))-(IFERROR(--MID(G61,FIND("-",G61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))-(IFERROR(--MID(G61,FIND("-",G61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(G61,FIND("-",G61)-1),""))=(AW61))+2*((IFERROR(--MID(G61,FIND("-",G61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J61" s="11" t="str">
+      <c r="J61" s="11">
         <f>IF(OR($C61="",I61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I61,FIND("-",I61)-1),"")=AW61,IFERROR(--MID(I61,FIND("-",I61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))-(IFERROR(--MID(I61,FIND("-",I61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))-(IFERROR(--MID(I61,FIND("-",I61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(I61,FIND("-",I61)-1),""))=(AW61))+2*((IFERROR(--MID(I61,FIND("-",I61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L61" s="11" t="str">
+      <c r="L61" s="11">
         <f>IF(OR($C61="",K61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K61,FIND("-",K61)-1),"")=AW61,IFERROR(--MID(K61,FIND("-",K61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))-(IFERROR(--MID(K61,FIND("-",K61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))-(IFERROR(--MID(K61,FIND("-",K61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(K61,FIND("-",K61)-1),""))=(AW61))+2*((IFERROR(--MID(K61,FIND("-",K61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="N61" s="11" t="str">
+      <c r="N61" s="11">
         <f>IF(OR($C61="",M61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M61,FIND("-",M61)-1),"")=AW61,IFERROR(--MID(M61,FIND("-",M61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))-(IFERROR(--MID(M61,FIND("-",M61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))-(IFERROR(--MID(M61,FIND("-",M61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(M61,FIND("-",M61)-1),""))=(AW61))+2*((IFERROR(--MID(M61,FIND("-",M61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P61" s="11" t="str">
+      <c r="P61" s="11">
         <f>IF(OR($C61="",O61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O61,FIND("-",O61)-1),"")=AW61,IFERROR(--MID(O61,FIND("-",O61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))-(IFERROR(--MID(O61,FIND("-",O61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))-(IFERROR(--MID(O61,FIND("-",O61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(O61,FIND("-",O61)-1),""))=(AW61))+2*((IFERROR(--MID(O61,FIND("-",O61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="R61" s="11" t="str">
+      <c r="R61" s="11">
         <f>IF(OR($C61="",Q61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q61,FIND("-",Q61)-1),"")=AW61,IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))-(IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))-(IFERROR(--MID(Q61,FIND("-",Q61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(Q61,FIND("-",Q61)-1),""))=(AW61))+2*((IFERROR(--MID(Q61,FIND("-",Q61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="S61" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T61" s="11" t="str">
+      <c r="T61" s="11">
         <f>IF(OR($C61="",S61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S61,FIND("-",S61)-1),"")=AW61,IFERROR(--MID(S61,FIND("-",S61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))-(IFERROR(--MID(S61,FIND("-",S61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))-(IFERROR(--MID(S61,FIND("-",S61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(S61,FIND("-",S61)-1),""))=(AW61))+2*((IFERROR(--MID(S61,FIND("-",S61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V61" s="11" t="str">
+      <c r="V61" s="11">
         <f>IF(OR($C61="",U61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U61,FIND("-",U61)-1),"")=AW61,IFERROR(--MID(U61,FIND("-",U61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))-(IFERROR(--MID(U61,FIND("-",U61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))-(IFERROR(--MID(U61,FIND("-",U61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(U61,FIND("-",U61)-1),""))=(AW61))+2*((IFERROR(--MID(U61,FIND("-",U61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X61" s="11" t="str">
+      <c r="X61" s="11">
         <f>IF(OR($C61="",W61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W61,FIND("-",W61)-1),"")=AW61,IFERROR(--MID(W61,FIND("-",W61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))-(IFERROR(--MID(W61,FIND("-",W61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))-(IFERROR(--MID(W61,FIND("-",W61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(W61,FIND("-",W61)-1),""))=(AW61))+2*((IFERROR(--MID(W61,FIND("-",W61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z61" s="11" t="str">
+      <c r="Z61" s="11">
         <f>IF(OR($C61="",Y61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y61,FIND("-",Y61)-1),"")=AW61,IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))-(IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))-(IFERROR(--MID(Y61,FIND("-",Y61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(Y61,FIND("-",Y61)-1),""))=(AW61))+2*((IFERROR(--MID(Y61,FIND("-",Y61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA61" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="AB61" s="11" t="str">
+      <c r="AB61" s="11">
         <f>IF(OR($C61="",AA61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA61,FIND("-",AA61)-1),"")=AW61,IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))-(IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))-(IFERROR(--MID(AA61,FIND("-",AA61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AA61,FIND("-",AA61)-1),""))=(AW61))+2*((IFERROR(--MID(AA61,FIND("-",AA61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD61" s="11" t="str">
+      <c r="AD61" s="11">
         <f>IF(OR($C61="",AC61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC61,FIND("-",AC61)-1),"")=AW61,IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))-(IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))-(IFERROR(--MID(AC61,FIND("-",AC61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AC61,FIND("-",AC61)-1),""))=(AW61))+2*((IFERROR(--MID(AC61,FIND("-",AC61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF61" s="11" t="str">
+      <c r="AF61" s="11">
         <f>IF(OR($C61="",AE61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE61,FIND("-",AE61)-1),"")=AW61,IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))-(IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))-(IFERROR(--MID(AE61,FIND("-",AE61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AE61,FIND("-",AE61)-1),""))=(AW61))+2*((IFERROR(--MID(AE61,FIND("-",AE61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG61" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH61" s="11" t="str">
+      <c r="AH61" s="11">
         <f>IF(OR($C61="",AG61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG61,FIND("-",AG61)-1),"")=AW61,IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))-(IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))-(IFERROR(--MID(AG61,FIND("-",AG61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AG61,FIND("-",AG61)-1),""))=(AW61))+2*((IFERROR(--MID(AG61,FIND("-",AG61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ61" s="11" t="str">
+      <c r="AJ61" s="11">
         <f>IF(OR($C61="",AI61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI61,FIND("-",AI61)-1),"")=AW61,IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))-(IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))-(IFERROR(--MID(AI61,FIND("-",AI61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AI61,FIND("-",AI61)-1),""))=(AW61))+2*((IFERROR(--MID(AI61,FIND("-",AI61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK61" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL61" s="11" t="str">
+      <c r="AL61" s="11">
         <f>IF(OR($C61="",AK61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK61,FIND("-",AK61)-1),"")=AW61,IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))-(IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))-(IFERROR(--MID(AK61,FIND("-",AK61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AK61,FIND("-",AK61)-1),""))=(AW61))+2*((IFERROR(--MID(AK61,FIND("-",AK61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AN61" s="11" t="str">
+      <c r="AN61" s="11">
         <f>IF(OR($C61="",AM61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM61,FIND("-",AM61)-1),"")=AW61,IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))-(IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))-(IFERROR(--MID(AM61,FIND("-",AM61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AM61,FIND("-",AM61)-1),""))=(AW61))+2*((IFERROR(--MID(AM61,FIND("-",AM61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AP61" s="11" t="str">
+      <c r="AP61" s="11">
         <f>IF(OR($C61="",AO61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO61,FIND("-",AO61)-1),"")=AW61,IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))-(IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))-(IFERROR(--MID(AO61,FIND("-",AO61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AO61,FIND("-",AO61)-1),""))=(AW61))+2*((IFERROR(--MID(AO61,FIND("-",AO61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ61" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR61" s="11" t="str">
+      <c r="AR61" s="11">
         <f>IF(OR($C61="",AQ61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),"")=AW61,IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))-(IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))-(IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AQ61,FIND("-",AQ61)-1),""))=(AW61))+2*((IFERROR(--MID(AQ61,FIND("-",AQ61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS61" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AT61" s="11" t="str">
+      <c r="AT61" s="11">
         <f>IF(OR($C61="",AS61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS61,FIND("-",AS61)-1),"")=AW61,IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))-(IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))-(IFERROR(--MID(AS61,FIND("-",AS61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AS61,FIND("-",AS61)-1),""))=(AW61))+2*((IFERROR(--MID(AS61,FIND("-",AS61)+1,99),""))=(AX61))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU61" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV61" s="11" t="str">
+      <c r="AV61" s="11">
         <f>IF(OR($C61="",AU61=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU61,FIND("-",AU61)-1),"")=AW61,IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")=AX61),10,5*(SIGN((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))-(IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")))=SIGN((AW61)-(AX61)))+2*(((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))-(IFERROR(--MID(AU61,FIND("-",AU61)+1,99),"")))=((AW61)-(AX61)))+2*((IFERROR(--LEFT(AU61,FIND("-",AU61)-1),""))=(AW61))+2*((IFERROR(--MID(AU61,FIND("-",AU61)+1,99),""))=(AX61))),""))</f>
-        <v/>
-      </c>
-      <c r="AW61" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW61" s="11">
         <f>IF($C61="","",IFERROR(--LEFT($C61,FIND("-",$C61)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX61" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX61" s="11">
         <f>IF($C61="","",IFERROR(--MID($C61,FIND("-",$C61)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -9785,171 +9787,173 @@
       <c r="B62" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C62" s="10"/>
+      <c r="C62" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D62" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F62" s="11" t="str">
+      <c r="F62" s="11">
         <f>IF(OR($C62="",E62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E62,FIND("-",E62)-1),"")=AW62,IFERROR(--MID(E62,FIND("-",E62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))-(IFERROR(--MID(E62,FIND("-",E62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))-(IFERROR(--MID(E62,FIND("-",E62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(E62,FIND("-",E62)-1),""))=(AW62))+2*((IFERROR(--MID(E62,FIND("-",E62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H62" s="11" t="str">
+      <c r="H62" s="11">
         <f>IF(OR($C62="",G62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G62,FIND("-",G62)-1),"")=AW62,IFERROR(--MID(G62,FIND("-",G62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))-(IFERROR(--MID(G62,FIND("-",G62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))-(IFERROR(--MID(G62,FIND("-",G62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(G62,FIND("-",G62)-1),""))=(AW62))+2*((IFERROR(--MID(G62,FIND("-",G62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I62" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J62" s="11" t="str">
+      <c r="J62" s="11">
         <f>IF(OR($C62="",I62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I62,FIND("-",I62)-1),"")=AW62,IFERROR(--MID(I62,FIND("-",I62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))-(IFERROR(--MID(I62,FIND("-",I62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))-(IFERROR(--MID(I62,FIND("-",I62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(I62,FIND("-",I62)-1),""))=(AW62))+2*((IFERROR(--MID(I62,FIND("-",I62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K62" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="L62" s="11" t="str">
+      <c r="L62" s="11">
         <f>IF(OR($C62="",K62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K62,FIND("-",K62)-1),"")=AW62,IFERROR(--MID(K62,FIND("-",K62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))-(IFERROR(--MID(K62,FIND("-",K62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))-(IFERROR(--MID(K62,FIND("-",K62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(K62,FIND("-",K62)-1),""))=(AW62))+2*((IFERROR(--MID(K62,FIND("-",K62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N62" s="11" t="str">
+      <c r="N62" s="11">
         <f>IF(OR($C62="",M62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M62,FIND("-",M62)-1),"")=AW62,IFERROR(--MID(M62,FIND("-",M62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))-(IFERROR(--MID(M62,FIND("-",M62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))-(IFERROR(--MID(M62,FIND("-",M62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(M62,FIND("-",M62)-1),""))=(AW62))+2*((IFERROR(--MID(M62,FIND("-",M62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O62" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="P62" s="11" t="str">
+      <c r="P62" s="11">
         <f>IF(OR($C62="",O62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O62,FIND("-",O62)-1),"")=AW62,IFERROR(--MID(O62,FIND("-",O62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))-(IFERROR(--MID(O62,FIND("-",O62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))-(IFERROR(--MID(O62,FIND("-",O62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(O62,FIND("-",O62)-1),""))=(AW62))+2*((IFERROR(--MID(O62,FIND("-",O62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q62" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R62" s="11" t="str">
+      <c r="R62" s="11">
         <f>IF(OR($C62="",Q62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q62,FIND("-",Q62)-1),"")=AW62,IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))-(IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))-(IFERROR(--MID(Q62,FIND("-",Q62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(Q62,FIND("-",Q62)-1),""))=(AW62))+2*((IFERROR(--MID(Q62,FIND("-",Q62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S62" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T62" s="11" t="str">
+      <c r="T62" s="11">
         <f>IF(OR($C62="",S62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S62,FIND("-",S62)-1),"")=AW62,IFERROR(--MID(S62,FIND("-",S62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))-(IFERROR(--MID(S62,FIND("-",S62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))-(IFERROR(--MID(S62,FIND("-",S62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(S62,FIND("-",S62)-1),""))=(AW62))+2*((IFERROR(--MID(S62,FIND("-",S62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V62" s="11" t="str">
+      <c r="V62" s="11">
         <f>IF(OR($C62="",U62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U62,FIND("-",U62)-1),"")=AW62,IFERROR(--MID(U62,FIND("-",U62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))-(IFERROR(--MID(U62,FIND("-",U62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))-(IFERROR(--MID(U62,FIND("-",U62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(U62,FIND("-",U62)-1),""))=(AW62))+2*((IFERROR(--MID(U62,FIND("-",U62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X62" s="11" t="str">
+      <c r="X62" s="11">
         <f>IF(OR($C62="",W62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W62,FIND("-",W62)-1),"")=AW62,IFERROR(--MID(W62,FIND("-",W62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))-(IFERROR(--MID(W62,FIND("-",W62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))-(IFERROR(--MID(W62,FIND("-",W62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(W62,FIND("-",W62)-1),""))=(AW62))+2*((IFERROR(--MID(W62,FIND("-",W62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y62" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z62" s="11" t="str">
+      <c r="Z62" s="11">
         <f>IF(OR($C62="",Y62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y62,FIND("-",Y62)-1),"")=AW62,IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))-(IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))-(IFERROR(--MID(Y62,FIND("-",Y62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(Y62,FIND("-",Y62)-1),""))=(AW62))+2*((IFERROR(--MID(Y62,FIND("-",Y62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB62" s="11" t="str">
+      <c r="AB62" s="11">
         <f>IF(OR($C62="",AA62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA62,FIND("-",AA62)-1),"")=AW62,IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))-(IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))-(IFERROR(--MID(AA62,FIND("-",AA62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AA62,FIND("-",AA62)-1),""))=(AW62))+2*((IFERROR(--MID(AA62,FIND("-",AA62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD62" s="11" t="str">
+      <c r="AD62" s="11">
         <f>IF(OR($C62="",AC62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC62,FIND("-",AC62)-1),"")=AW62,IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))-(IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))-(IFERROR(--MID(AC62,FIND("-",AC62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AC62,FIND("-",AC62)-1),""))=(AW62))+2*((IFERROR(--MID(AC62,FIND("-",AC62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF62" s="11" t="str">
+      <c r="AF62" s="11">
         <f>IF(OR($C62="",AE62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE62,FIND("-",AE62)-1),"")=AW62,IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))-(IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))-(IFERROR(--MID(AE62,FIND("-",AE62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AE62,FIND("-",AE62)-1),""))=(AW62))+2*((IFERROR(--MID(AE62,FIND("-",AE62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH62" s="11" t="str">
+      <c r="AH62" s="11">
         <f>IF(OR($C62="",AG62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG62,FIND("-",AG62)-1),"")=AW62,IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))-(IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))-(IFERROR(--MID(AG62,FIND("-",AG62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AG62,FIND("-",AG62)-1),""))=(AW62))+2*((IFERROR(--MID(AG62,FIND("-",AG62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI62" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ62" s="11" t="str">
+      <c r="AJ62" s="11">
         <f>IF(OR($C62="",AI62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI62,FIND("-",AI62)-1),"")=AW62,IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))-(IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))-(IFERROR(--MID(AI62,FIND("-",AI62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AI62,FIND("-",AI62)-1),""))=(AW62))+2*((IFERROR(--MID(AI62,FIND("-",AI62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL62" s="11" t="str">
+      <c r="AL62" s="11">
         <f>IF(OR($C62="",AK62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK62,FIND("-",AK62)-1),"")=AW62,IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))-(IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))-(IFERROR(--MID(AK62,FIND("-",AK62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AK62,FIND("-",AK62)-1),""))=(AW62))+2*((IFERROR(--MID(AK62,FIND("-",AK62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM62" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN62" s="11" t="str">
+      <c r="AN62" s="11">
         <f>IF(OR($C62="",AM62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM62,FIND("-",AM62)-1),"")=AW62,IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))-(IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))-(IFERROR(--MID(AM62,FIND("-",AM62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AM62,FIND("-",AM62)-1),""))=(AW62))+2*((IFERROR(--MID(AM62,FIND("-",AM62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO62" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP62" s="11" t="str">
+      <c r="AP62" s="11">
         <f>IF(OR($C62="",AO62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO62,FIND("-",AO62)-1),"")=AW62,IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))-(IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))-(IFERROR(--MID(AO62,FIND("-",AO62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AO62,FIND("-",AO62)-1),""))=(AW62))+2*((IFERROR(--MID(AO62,FIND("-",AO62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ62" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR62" s="11" t="str">
+      <c r="AR62" s="11">
         <f>IF(OR($C62="",AQ62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),"")=AW62,IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))-(IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))-(IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AQ62,FIND("-",AQ62)-1),""))=(AW62))+2*((IFERROR(--MID(AQ62,FIND("-",AQ62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS62" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AT62" s="11" t="str">
+      <c r="AT62" s="11">
         <f>IF(OR($C62="",AS62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS62,FIND("-",AS62)-1),"")=AW62,IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))-(IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))-(IFERROR(--MID(AS62,FIND("-",AS62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AS62,FIND("-",AS62)-1),""))=(AW62))+2*((IFERROR(--MID(AS62,FIND("-",AS62)+1,99),""))=(AX62))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU62" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV62" s="11" t="str">
+      <c r="AV62" s="11">
         <f>IF(OR($C62="",AU62=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU62,FIND("-",AU62)-1),"")=AW62,IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")=AX62),10,5*(SIGN((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))-(IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")))=SIGN((AW62)-(AX62)))+2*(((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))-(IFERROR(--MID(AU62,FIND("-",AU62)+1,99),"")))=((AW62)-(AX62)))+2*((IFERROR(--LEFT(AU62,FIND("-",AU62)-1),""))=(AW62))+2*((IFERROR(--MID(AU62,FIND("-",AU62)+1,99),""))=(AX62))),""))</f>
-        <v/>
-      </c>
-      <c r="AW62" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW62" s="11">
         <f>IF($C62="","",IFERROR(--LEFT($C62,FIND("-",$C62)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX62" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX62" s="11">
         <f>IF($C62="","",IFERROR(--MID($C62,FIND("-",$C62)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10011,56 +10015,56 @@
       <c r="AX63" s="12"/>
     </row>
     <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="34" t="s">
+      <c r="A64" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="35"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="36"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="36"/>
-      <c r="L64" s="35"/>
-      <c r="M64" s="36"/>
-      <c r="N64" s="35"/>
-      <c r="O64" s="36"/>
-      <c r="P64" s="35"/>
-      <c r="Q64" s="36"/>
-      <c r="R64" s="35"/>
-      <c r="S64" s="36"/>
-      <c r="T64" s="35"/>
-      <c r="U64" s="36"/>
-      <c r="V64" s="35"/>
-      <c r="W64" s="36"/>
-      <c r="X64" s="35"/>
-      <c r="Y64" s="36"/>
-      <c r="Z64" s="35"/>
-      <c r="AA64" s="36"/>
-      <c r="AB64" s="35"/>
-      <c r="AC64" s="36"/>
-      <c r="AD64" s="35"/>
-      <c r="AE64" s="36"/>
-      <c r="AF64" s="35"/>
-      <c r="AG64" s="36"/>
-      <c r="AH64" s="35"/>
-      <c r="AI64" s="36"/>
-      <c r="AJ64" s="35"/>
-      <c r="AK64" s="36"/>
-      <c r="AL64" s="35"/>
-      <c r="AM64" s="36"/>
-      <c r="AN64" s="35"/>
-      <c r="AO64" s="36"/>
-      <c r="AP64" s="35"/>
-      <c r="AQ64" s="35"/>
-      <c r="AR64" s="35"/>
-      <c r="AS64" s="35"/>
-      <c r="AT64" s="35"/>
-      <c r="AU64" s="36"/>
-      <c r="AV64" s="37"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="45"/>
+      <c r="O64" s="46"/>
+      <c r="P64" s="45"/>
+      <c r="Q64" s="46"/>
+      <c r="R64" s="45"/>
+      <c r="S64" s="46"/>
+      <c r="T64" s="45"/>
+      <c r="U64" s="46"/>
+      <c r="V64" s="45"/>
+      <c r="W64" s="46"/>
+      <c r="X64" s="45"/>
+      <c r="Y64" s="46"/>
+      <c r="Z64" s="45"/>
+      <c r="AA64" s="46"/>
+      <c r="AB64" s="45"/>
+      <c r="AC64" s="46"/>
+      <c r="AD64" s="45"/>
+      <c r="AE64" s="46"/>
+      <c r="AF64" s="45"/>
+      <c r="AG64" s="46"/>
+      <c r="AH64" s="45"/>
+      <c r="AI64" s="46"/>
+      <c r="AJ64" s="45"/>
+      <c r="AK64" s="46"/>
+      <c r="AL64" s="45"/>
+      <c r="AM64" s="46"/>
+      <c r="AN64" s="45"/>
+      <c r="AO64" s="46"/>
+      <c r="AP64" s="45"/>
+      <c r="AQ64" s="45"/>
+      <c r="AR64" s="45"/>
+      <c r="AS64" s="45"/>
+      <c r="AT64" s="45"/>
+      <c r="AU64" s="46"/>
+      <c r="AV64" s="47"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
@@ -10071,171 +10075,173 @@
       <c r="B65" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="D65" s="1" t="s">
         <v>81</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F65" s="11" t="str">
+      <c r="F65" s="11">
         <f>IF(OR($C65="",E65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E65,FIND("-",E65)-1),"")=AW65,IFERROR(--MID(E65,FIND("-",E65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))-(IFERROR(--MID(E65,FIND("-",E65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))-(IFERROR(--MID(E65,FIND("-",E65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(E65,FIND("-",E65)-1),""))=(AW65))+2*((IFERROR(--MID(E65,FIND("-",E65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="11" t="str">
+      <c r="H65" s="11">
         <f>IF(OR($C65="",G65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G65,FIND("-",G65)-1),"")=AW65,IFERROR(--MID(G65,FIND("-",G65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))-(IFERROR(--MID(G65,FIND("-",G65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))-(IFERROR(--MID(G65,FIND("-",G65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(G65,FIND("-",G65)-1),""))=(AW65))+2*((IFERROR(--MID(G65,FIND("-",G65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J65" s="11" t="str">
+      <c r="J65" s="11">
         <f>IF(OR($C65="",I65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I65,FIND("-",I65)-1),"")=AW65,IFERROR(--MID(I65,FIND("-",I65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))-(IFERROR(--MID(I65,FIND("-",I65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))-(IFERROR(--MID(I65,FIND("-",I65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(I65,FIND("-",I65)-1),""))=(AW65))+2*((IFERROR(--MID(I65,FIND("-",I65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K65" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L65" s="11" t="str">
+      <c r="L65" s="11">
         <f>IF(OR($C65="",K65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K65,FIND("-",K65)-1),"")=AW65,IFERROR(--MID(K65,FIND("-",K65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))-(IFERROR(--MID(K65,FIND("-",K65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))-(IFERROR(--MID(K65,FIND("-",K65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(K65,FIND("-",K65)-1),""))=(AW65))+2*((IFERROR(--MID(K65,FIND("-",K65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M65" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N65" s="11" t="str">
+      <c r="N65" s="11">
         <f>IF(OR($C65="",M65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M65,FIND("-",M65)-1),"")=AW65,IFERROR(--MID(M65,FIND("-",M65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))-(IFERROR(--MID(M65,FIND("-",M65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))-(IFERROR(--MID(M65,FIND("-",M65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(M65,FIND("-",M65)-1),""))=(AW65))+2*((IFERROR(--MID(M65,FIND("-",M65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P65" s="11" t="str">
+      <c r="P65" s="11">
         <f>IF(OR($C65="",O65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O65,FIND("-",O65)-1),"")=AW65,IFERROR(--MID(O65,FIND("-",O65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))-(IFERROR(--MID(O65,FIND("-",O65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))-(IFERROR(--MID(O65,FIND("-",O65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(O65,FIND("-",O65)-1),""))=(AW65))+2*((IFERROR(--MID(O65,FIND("-",O65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="R65" s="11" t="str">
+      <c r="R65" s="11">
         <f>IF(OR($C65="",Q65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q65,FIND("-",Q65)-1),"")=AW65,IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))-(IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))-(IFERROR(--MID(Q65,FIND("-",Q65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(Q65,FIND("-",Q65)-1),""))=(AW65))+2*((IFERROR(--MID(Q65,FIND("-",Q65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S65" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T65" s="11" t="str">
+      <c r="T65" s="11">
         <f>IF(OR($C65="",S65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S65,FIND("-",S65)-1),"")=AW65,IFERROR(--MID(S65,FIND("-",S65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))-(IFERROR(--MID(S65,FIND("-",S65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))-(IFERROR(--MID(S65,FIND("-",S65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(S65,FIND("-",S65)-1),""))=(AW65))+2*((IFERROR(--MID(S65,FIND("-",S65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V65" s="11" t="str">
+      <c r="V65" s="11">
         <f>IF(OR($C65="",U65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U65,FIND("-",U65)-1),"")=AW65,IFERROR(--MID(U65,FIND("-",U65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))-(IFERROR(--MID(U65,FIND("-",U65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))-(IFERROR(--MID(U65,FIND("-",U65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(U65,FIND("-",U65)-1),""))=(AW65))+2*((IFERROR(--MID(U65,FIND("-",U65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X65" s="11" t="str">
+      <c r="X65" s="11">
         <f>IF(OR($C65="",W65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W65,FIND("-",W65)-1),"")=AW65,IFERROR(--MID(W65,FIND("-",W65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))-(IFERROR(--MID(W65,FIND("-",W65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))-(IFERROR(--MID(W65,FIND("-",W65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(W65,FIND("-",W65)-1),""))=(AW65))+2*((IFERROR(--MID(W65,FIND("-",W65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z65" s="11" t="str">
+      <c r="Z65" s="11">
         <f>IF(OR($C65="",Y65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y65,FIND("-",Y65)-1),"")=AW65,IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))-(IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))-(IFERROR(--MID(Y65,FIND("-",Y65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(Y65,FIND("-",Y65)-1),""))=(AW65))+2*((IFERROR(--MID(Y65,FIND("-",Y65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA65" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB65" s="11" t="str">
+      <c r="AB65" s="11">
         <f>IF(OR($C65="",AA65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA65,FIND("-",AA65)-1),"")=AW65,IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))-(IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))-(IFERROR(--MID(AA65,FIND("-",AA65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AA65,FIND("-",AA65)-1),""))=(AW65))+2*((IFERROR(--MID(AA65,FIND("-",AA65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD65" s="11" t="str">
+      <c r="AD65" s="11">
         <f>IF(OR($C65="",AC65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC65,FIND("-",AC65)-1),"")=AW65,IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))-(IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))-(IFERROR(--MID(AC65,FIND("-",AC65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AC65,FIND("-",AC65)-1),""))=(AW65))+2*((IFERROR(--MID(AC65,FIND("-",AC65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF65" s="11" t="str">
+      <c r="AF65" s="11">
         <f>IF(OR($C65="",AE65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE65,FIND("-",AE65)-1),"")=AW65,IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))-(IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))-(IFERROR(--MID(AE65,FIND("-",AE65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AE65,FIND("-",AE65)-1),""))=(AW65))+2*((IFERROR(--MID(AE65,FIND("-",AE65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH65" s="11" t="str">
+      <c r="AH65" s="11">
         <f>IF(OR($C65="",AG65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG65,FIND("-",AG65)-1),"")=AW65,IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))-(IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))-(IFERROR(--MID(AG65,FIND("-",AG65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AG65,FIND("-",AG65)-1),""))=(AW65))+2*((IFERROR(--MID(AG65,FIND("-",AG65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI65" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ65" s="11" t="str">
+      <c r="AJ65" s="11">
         <f>IF(OR($C65="",AI65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI65,FIND("-",AI65)-1),"")=AW65,IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))-(IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))-(IFERROR(--MID(AI65,FIND("-",AI65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AI65,FIND("-",AI65)-1),""))=(AW65))+2*((IFERROR(--MID(AI65,FIND("-",AI65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK65" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AL65" s="11" t="str">
+      <c r="AL65" s="11">
         <f>IF(OR($C65="",AK65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK65,FIND("-",AK65)-1),"")=AW65,IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))-(IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))-(IFERROR(--MID(AK65,FIND("-",AK65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AK65,FIND("-",AK65)-1),""))=(AW65))+2*((IFERROR(--MID(AK65,FIND("-",AK65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AM65" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AN65" s="11" t="str">
+      <c r="AN65" s="11">
         <f>IF(OR($C65="",AM65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM65,FIND("-",AM65)-1),"")=AW65,IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))-(IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))-(IFERROR(--MID(AM65,FIND("-",AM65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AM65,FIND("-",AM65)-1),""))=(AW65))+2*((IFERROR(--MID(AM65,FIND("-",AM65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP65" s="11" t="str">
+      <c r="AP65" s="11">
         <f>IF(OR($C65="",AO65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO65,FIND("-",AO65)-1),"")=AW65,IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))-(IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))-(IFERROR(--MID(AO65,FIND("-",AO65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AO65,FIND("-",AO65)-1),""))=(AW65))+2*((IFERROR(--MID(AO65,FIND("-",AO65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ65" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR65" s="11" t="str">
+      <c r="AR65" s="11">
         <f>IF(OR($C65="",AQ65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),"")=AW65,IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))-(IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))-(IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AQ65,FIND("-",AQ65)-1),""))=(AW65))+2*((IFERROR(--MID(AQ65,FIND("-",AQ65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS65" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AT65" s="11" t="str">
+      <c r="AT65" s="11">
         <f>IF(OR($C65="",AS65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS65,FIND("-",AS65)-1),"")=AW65,IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))-(IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))-(IFERROR(--MID(AS65,FIND("-",AS65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AS65,FIND("-",AS65)-1),""))=(AW65))+2*((IFERROR(--MID(AS65,FIND("-",AS65)+1,99),""))=(AX65))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU65" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV65" s="11" t="str">
+      <c r="AV65" s="11">
         <f>IF(OR($C65="",AU65=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU65,FIND("-",AU65)-1),"")=AW65,IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")=AX65),10,5*(SIGN((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))-(IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")))=SIGN((AW65)-(AX65)))+2*(((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))-(IFERROR(--MID(AU65,FIND("-",AU65)+1,99),"")))=((AW65)-(AX65)))+2*((IFERROR(--LEFT(AU65,FIND("-",AU65)-1),""))=(AW65))+2*((IFERROR(--MID(AU65,FIND("-",AU65)+1,99),""))=(AX65))),""))</f>
-        <v/>
-      </c>
-      <c r="AW65" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW65" s="11">
         <f>IF($C65="","",IFERROR(--LEFT($C65,FIND("-",$C65)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX65" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX65" s="11">
         <f>IF($C65="","",IFERROR(--MID($C65,FIND("-",$C65)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10245,171 +10251,173 @@
       <c r="B66" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="10"/>
+      <c r="C66" s="10" t="s">
+        <v>57</v>
+      </c>
       <c r="D66" s="1" t="s">
         <v>83</v>
       </c>
       <c r="E66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F66" s="11" t="str">
+      <c r="F66" s="11">
         <f>IF(OR($C66="",E66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E66,FIND("-",E66)-1),"")=AW66,IFERROR(--MID(E66,FIND("-",E66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))-(IFERROR(--MID(E66,FIND("-",E66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))-(IFERROR(--MID(E66,FIND("-",E66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(E66,FIND("-",E66)-1),""))=(AW66))+2*((IFERROR(--MID(E66,FIND("-",E66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H66" s="11" t="str">
+      <c r="H66" s="11">
         <f>IF(OR($C66="",G66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G66,FIND("-",G66)-1),"")=AW66,IFERROR(--MID(G66,FIND("-",G66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))-(IFERROR(--MID(G66,FIND("-",G66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))-(IFERROR(--MID(G66,FIND("-",G66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(G66,FIND("-",G66)-1),""))=(AW66))+2*((IFERROR(--MID(G66,FIND("-",G66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J66" s="11" t="str">
+      <c r="J66" s="11">
         <f>IF(OR($C66="",I66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I66,FIND("-",I66)-1),"")=AW66,IFERROR(--MID(I66,FIND("-",I66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))-(IFERROR(--MID(I66,FIND("-",I66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))-(IFERROR(--MID(I66,FIND("-",I66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(I66,FIND("-",I66)-1),""))=(AW66))+2*((IFERROR(--MID(I66,FIND("-",I66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L66" s="11" t="str">
+      <c r="L66" s="11">
         <f>IF(OR($C66="",K66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K66,FIND("-",K66)-1),"")=AW66,IFERROR(--MID(K66,FIND("-",K66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))-(IFERROR(--MID(K66,FIND("-",K66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))-(IFERROR(--MID(K66,FIND("-",K66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(K66,FIND("-",K66)-1),""))=(AW66))+2*((IFERROR(--MID(K66,FIND("-",K66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N66" s="11" t="str">
+      <c r="N66" s="11">
         <f>IF(OR($C66="",M66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M66,FIND("-",M66)-1),"")=AW66,IFERROR(--MID(M66,FIND("-",M66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))-(IFERROR(--MID(M66,FIND("-",M66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))-(IFERROR(--MID(M66,FIND("-",M66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(M66,FIND("-",M66)-1),""))=(AW66))+2*((IFERROR(--MID(M66,FIND("-",M66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="P66" s="11" t="str">
+      <c r="P66" s="11">
         <f>IF(OR($C66="",O66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O66,FIND("-",O66)-1),"")=AW66,IFERROR(--MID(O66,FIND("-",O66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))-(IFERROR(--MID(O66,FIND("-",O66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))-(IFERROR(--MID(O66,FIND("-",O66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(O66,FIND("-",O66)-1),""))=(AW66))+2*((IFERROR(--MID(O66,FIND("-",O66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q66" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R66" s="11" t="str">
+      <c r="R66" s="11">
         <f>IF(OR($C66="",Q66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q66,FIND("-",Q66)-1),"")=AW66,IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))-(IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))-(IFERROR(--MID(Q66,FIND("-",Q66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(Q66,FIND("-",Q66)-1),""))=(AW66))+2*((IFERROR(--MID(Q66,FIND("-",Q66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S66" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T66" s="11" t="str">
+      <c r="T66" s="11">
         <f>IF(OR($C66="",S66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S66,FIND("-",S66)-1),"")=AW66,IFERROR(--MID(S66,FIND("-",S66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))-(IFERROR(--MID(S66,FIND("-",S66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))-(IFERROR(--MID(S66,FIND("-",S66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(S66,FIND("-",S66)-1),""))=(AW66))+2*((IFERROR(--MID(S66,FIND("-",S66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V66" s="11" t="str">
+      <c r="V66" s="11">
         <f>IF(OR($C66="",U66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U66,FIND("-",U66)-1),"")=AW66,IFERROR(--MID(U66,FIND("-",U66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))-(IFERROR(--MID(U66,FIND("-",U66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))-(IFERROR(--MID(U66,FIND("-",U66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(U66,FIND("-",U66)-1),""))=(AW66))+2*((IFERROR(--MID(U66,FIND("-",U66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X66" s="11" t="str">
+      <c r="X66" s="11">
         <f>IF(OR($C66="",W66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W66,FIND("-",W66)-1),"")=AW66,IFERROR(--MID(W66,FIND("-",W66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))-(IFERROR(--MID(W66,FIND("-",W66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))-(IFERROR(--MID(W66,FIND("-",W66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(W66,FIND("-",W66)-1),""))=(AW66))+2*((IFERROR(--MID(W66,FIND("-",W66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Z66" s="11" t="str">
+      <c r="Z66" s="11">
         <f>IF(OR($C66="",Y66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y66,FIND("-",Y66)-1),"")=AW66,IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))-(IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))-(IFERROR(--MID(Y66,FIND("-",Y66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(Y66,FIND("-",Y66)-1),""))=(AW66))+2*((IFERROR(--MID(Y66,FIND("-",Y66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB66" s="11" t="str">
+      <c r="AB66" s="11">
         <f>IF(OR($C66="",AA66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA66,FIND("-",AA66)-1),"")=AW66,IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))-(IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))-(IFERROR(--MID(AA66,FIND("-",AA66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AA66,FIND("-",AA66)-1),""))=(AW66))+2*((IFERROR(--MID(AA66,FIND("-",AA66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AD66" s="11" t="str">
+      <c r="AD66" s="11">
         <f>IF(OR($C66="",AC66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC66,FIND("-",AC66)-1),"")=AW66,IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))-(IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))-(IFERROR(--MID(AC66,FIND("-",AC66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AC66,FIND("-",AC66)-1),""))=(AW66))+2*((IFERROR(--MID(AC66,FIND("-",AC66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF66" s="11" t="str">
+      <c r="AF66" s="11">
         <f>IF(OR($C66="",AE66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE66,FIND("-",AE66)-1),"")=AW66,IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))-(IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))-(IFERROR(--MID(AE66,FIND("-",AE66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AE66,FIND("-",AE66)-1),""))=(AW66))+2*((IFERROR(--MID(AE66,FIND("-",AE66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH66" s="11" t="str">
+      <c r="AH66" s="11">
         <f>IF(OR($C66="",AG66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG66,FIND("-",AG66)-1),"")=AW66,IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))-(IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))-(IFERROR(--MID(AG66,FIND("-",AG66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AG66,FIND("-",AG66)-1),""))=(AW66))+2*((IFERROR(--MID(AG66,FIND("-",AG66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AJ66" s="11" t="str">
+      <c r="AJ66" s="11">
         <f>IF(OR($C66="",AI66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI66,FIND("-",AI66)-1),"")=AW66,IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))-(IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))-(IFERROR(--MID(AI66,FIND("-",AI66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AI66,FIND("-",AI66)-1),""))=(AW66))+2*((IFERROR(--MID(AI66,FIND("-",AI66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK66" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AL66" s="11" t="str">
+      <c r="AL66" s="11">
         <f>IF(OR($C66="",AK66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK66,FIND("-",AK66)-1),"")=AW66,IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))-(IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))-(IFERROR(--MID(AK66,FIND("-",AK66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AK66,FIND("-",AK66)-1),""))=(AW66))+2*((IFERROR(--MID(AK66,FIND("-",AK66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM66" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN66" s="11" t="str">
+      <c r="AN66" s="11">
         <f>IF(OR($C66="",AM66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM66,FIND("-",AM66)-1),"")=AW66,IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))-(IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))-(IFERROR(--MID(AM66,FIND("-",AM66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AM66,FIND("-",AM66)-1),""))=(AW66))+2*((IFERROR(--MID(AM66,FIND("-",AM66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO66" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AP66" s="11" t="str">
+      <c r="AP66" s="11">
         <f>IF(OR($C66="",AO66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO66,FIND("-",AO66)-1),"")=AW66,IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))-(IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))-(IFERROR(--MID(AO66,FIND("-",AO66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AO66,FIND("-",AO66)-1),""))=(AW66))+2*((IFERROR(--MID(AO66,FIND("-",AO66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AQ66" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR66" s="11" t="str">
+      <c r="AR66" s="11">
         <f>IF(OR($C66="",AQ66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),"")=AW66,IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))-(IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))-(IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AQ66,FIND("-",AQ66)-1),""))=(AW66))+2*((IFERROR(--MID(AQ66,FIND("-",AQ66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS66" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT66" s="11" t="str">
+      <c r="AT66" s="11">
         <f>IF(OR($C66="",AS66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS66,FIND("-",AS66)-1),"")=AW66,IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))-(IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))-(IFERROR(--MID(AS66,FIND("-",AS66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AS66,FIND("-",AS66)-1),""))=(AW66))+2*((IFERROR(--MID(AS66,FIND("-",AS66)+1,99),""))=(AX66))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU66" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV66" s="11" t="str">
+      <c r="AV66" s="11">
         <f>IF(OR($C66="",AU66=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU66,FIND("-",AU66)-1),"")=AW66,IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")=AX66),10,5*(SIGN((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))-(IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")))=SIGN((AW66)-(AX66)))+2*(((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))-(IFERROR(--MID(AU66,FIND("-",AU66)+1,99),"")))=((AW66)-(AX66)))+2*((IFERROR(--LEFT(AU66,FIND("-",AU66)-1),""))=(AW66))+2*((IFERROR(--MID(AU66,FIND("-",AU66)+1,99),""))=(AX66))),""))</f>
-        <v/>
-      </c>
-      <c r="AW66" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW66" s="11">
         <f>IF($C66="","",IFERROR(--LEFT($C66,FIND("-",$C66)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX66" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX66" s="11">
         <f>IF($C66="","",IFERROR(--MID($C66,FIND("-",$C66)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -10819,56 +10827,56 @@
       <c r="AX69" s="12"/>
     </row>
     <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="34" t="s">
+      <c r="A70" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="35"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="36"/>
-      <c r="L70" s="35"/>
-      <c r="M70" s="36"/>
-      <c r="N70" s="35"/>
-      <c r="O70" s="36"/>
-      <c r="P70" s="35"/>
-      <c r="Q70" s="36"/>
-      <c r="R70" s="35"/>
-      <c r="S70" s="36"/>
-      <c r="T70" s="35"/>
-      <c r="U70" s="36"/>
-      <c r="V70" s="35"/>
-      <c r="W70" s="36"/>
-      <c r="X70" s="35"/>
-      <c r="Y70" s="36"/>
-      <c r="Z70" s="35"/>
-      <c r="AA70" s="36"/>
-      <c r="AB70" s="35"/>
-      <c r="AC70" s="36"/>
-      <c r="AD70" s="35"/>
-      <c r="AE70" s="36"/>
-      <c r="AF70" s="35"/>
-      <c r="AG70" s="36"/>
-      <c r="AH70" s="35"/>
-      <c r="AI70" s="36"/>
-      <c r="AJ70" s="35"/>
-      <c r="AK70" s="36"/>
-      <c r="AL70" s="35"/>
-      <c r="AM70" s="36"/>
-      <c r="AN70" s="35"/>
-      <c r="AO70" s="36"/>
-      <c r="AP70" s="35"/>
-      <c r="AQ70" s="35"/>
-      <c r="AR70" s="35"/>
-      <c r="AS70" s="35"/>
-      <c r="AT70" s="35"/>
-      <c r="AU70" s="36"/>
-      <c r="AV70" s="37"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="46"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="46"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="46"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="46"/>
+      <c r="T70" s="45"/>
+      <c r="U70" s="46"/>
+      <c r="V70" s="45"/>
+      <c r="W70" s="46"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="46"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="46"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="46"/>
+      <c r="AD70" s="45"/>
+      <c r="AE70" s="46"/>
+      <c r="AF70" s="45"/>
+      <c r="AG70" s="46"/>
+      <c r="AH70" s="45"/>
+      <c r="AI70" s="46"/>
+      <c r="AJ70" s="45"/>
+      <c r="AK70" s="46"/>
+      <c r="AL70" s="45"/>
+      <c r="AM70" s="46"/>
+      <c r="AN70" s="45"/>
+      <c r="AO70" s="46"/>
+      <c r="AP70" s="45"/>
+      <c r="AQ70" s="45"/>
+      <c r="AR70" s="45"/>
+      <c r="AS70" s="45"/>
+      <c r="AT70" s="45"/>
+      <c r="AU70" s="46"/>
+      <c r="AV70" s="47"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
@@ -11627,56 +11635,56 @@
       <c r="AX75" s="12"/>
     </row>
     <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="34" t="s">
+      <c r="A76" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="35"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="35"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="36"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="36"/>
-      <c r="L76" s="35"/>
-      <c r="M76" s="36"/>
-      <c r="N76" s="35"/>
-      <c r="O76" s="36"/>
-      <c r="P76" s="35"/>
-      <c r="Q76" s="36"/>
-      <c r="R76" s="35"/>
-      <c r="S76" s="36"/>
-      <c r="T76" s="35"/>
-      <c r="U76" s="36"/>
-      <c r="V76" s="35"/>
-      <c r="W76" s="36"/>
-      <c r="X76" s="35"/>
-      <c r="Y76" s="36"/>
-      <c r="Z76" s="35"/>
-      <c r="AA76" s="36"/>
-      <c r="AB76" s="35"/>
-      <c r="AC76" s="36"/>
-      <c r="AD76" s="35"/>
-      <c r="AE76" s="36"/>
-      <c r="AF76" s="35"/>
-      <c r="AG76" s="36"/>
-      <c r="AH76" s="35"/>
-      <c r="AI76" s="36"/>
-      <c r="AJ76" s="35"/>
-      <c r="AK76" s="36"/>
-      <c r="AL76" s="35"/>
-      <c r="AM76" s="36"/>
-      <c r="AN76" s="35"/>
-      <c r="AO76" s="36"/>
-      <c r="AP76" s="35"/>
-      <c r="AQ76" s="35"/>
-      <c r="AR76" s="35"/>
-      <c r="AS76" s="35"/>
-      <c r="AT76" s="35"/>
-      <c r="AU76" s="36"/>
-      <c r="AV76" s="37"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="46"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="46"/>
+      <c r="P76" s="45"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="45"/>
+      <c r="S76" s="46"/>
+      <c r="T76" s="45"/>
+      <c r="U76" s="46"/>
+      <c r="V76" s="45"/>
+      <c r="W76" s="46"/>
+      <c r="X76" s="45"/>
+      <c r="Y76" s="46"/>
+      <c r="Z76" s="45"/>
+      <c r="AA76" s="46"/>
+      <c r="AB76" s="45"/>
+      <c r="AC76" s="46"/>
+      <c r="AD76" s="45"/>
+      <c r="AE76" s="46"/>
+      <c r="AF76" s="45"/>
+      <c r="AG76" s="46"/>
+      <c r="AH76" s="45"/>
+      <c r="AI76" s="46"/>
+      <c r="AJ76" s="45"/>
+      <c r="AK76" s="46"/>
+      <c r="AL76" s="45"/>
+      <c r="AM76" s="46"/>
+      <c r="AN76" s="45"/>
+      <c r="AO76" s="46"/>
+      <c r="AP76" s="45"/>
+      <c r="AQ76" s="45"/>
+      <c r="AR76" s="45"/>
+      <c r="AS76" s="45"/>
+      <c r="AT76" s="45"/>
+      <c r="AU76" s="46"/>
+      <c r="AV76" s="47"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
@@ -12435,56 +12443,56 @@
       <c r="AX81" s="12"/>
     </row>
     <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="34" t="s">
+      <c r="A82" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="35"/>
-      <c r="C82" s="36"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="36"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="36"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="36"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="36"/>
-      <c r="L82" s="35"/>
-      <c r="M82" s="36"/>
-      <c r="N82" s="35"/>
-      <c r="O82" s="36"/>
-      <c r="P82" s="35"/>
-      <c r="Q82" s="36"/>
-      <c r="R82" s="35"/>
-      <c r="S82" s="36"/>
-      <c r="T82" s="35"/>
-      <c r="U82" s="36"/>
-      <c r="V82" s="35"/>
-      <c r="W82" s="36"/>
-      <c r="X82" s="35"/>
-      <c r="Y82" s="36"/>
-      <c r="Z82" s="35"/>
-      <c r="AA82" s="36"/>
-      <c r="AB82" s="35"/>
-      <c r="AC82" s="36"/>
-      <c r="AD82" s="35"/>
-      <c r="AE82" s="36"/>
-      <c r="AF82" s="35"/>
-      <c r="AG82" s="36"/>
-      <c r="AH82" s="35"/>
-      <c r="AI82" s="36"/>
-      <c r="AJ82" s="35"/>
-      <c r="AK82" s="36"/>
-      <c r="AL82" s="35"/>
-      <c r="AM82" s="36"/>
-      <c r="AN82" s="35"/>
-      <c r="AO82" s="36"/>
-      <c r="AP82" s="35"/>
-      <c r="AQ82" s="35"/>
-      <c r="AR82" s="35"/>
-      <c r="AS82" s="35"/>
-      <c r="AT82" s="35"/>
-      <c r="AU82" s="36"/>
-      <c r="AV82" s="37"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="46"/>
+      <c r="N82" s="45"/>
+      <c r="O82" s="46"/>
+      <c r="P82" s="45"/>
+      <c r="Q82" s="46"/>
+      <c r="R82" s="45"/>
+      <c r="S82" s="46"/>
+      <c r="T82" s="45"/>
+      <c r="U82" s="46"/>
+      <c r="V82" s="45"/>
+      <c r="W82" s="46"/>
+      <c r="X82" s="45"/>
+      <c r="Y82" s="46"/>
+      <c r="Z82" s="45"/>
+      <c r="AA82" s="46"/>
+      <c r="AB82" s="45"/>
+      <c r="AC82" s="46"/>
+      <c r="AD82" s="45"/>
+      <c r="AE82" s="46"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="46"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
+      <c r="AJ82" s="45"/>
+      <c r="AK82" s="46"/>
+      <c r="AL82" s="45"/>
+      <c r="AM82" s="46"/>
+      <c r="AN82" s="45"/>
+      <c r="AO82" s="46"/>
+      <c r="AP82" s="45"/>
+      <c r="AQ82" s="45"/>
+      <c r="AR82" s="45"/>
+      <c r="AS82" s="45"/>
+      <c r="AT82" s="45"/>
+      <c r="AU82" s="46"/>
+      <c r="AV82" s="47"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
@@ -13591,56 +13599,56 @@
       <c r="AX89" s="12"/>
     </row>
     <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="34" t="s">
+      <c r="A90" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="35"/>
-      <c r="C90" s="36"/>
-      <c r="D90" s="35"/>
-      <c r="E90" s="36"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="36"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="36"/>
-      <c r="J90" s="35"/>
-      <c r="K90" s="36"/>
-      <c r="L90" s="35"/>
-      <c r="M90" s="36"/>
-      <c r="N90" s="35"/>
-      <c r="O90" s="36"/>
-      <c r="P90" s="35"/>
-      <c r="Q90" s="36"/>
-      <c r="R90" s="35"/>
-      <c r="S90" s="36"/>
-      <c r="T90" s="35"/>
-      <c r="U90" s="36"/>
-      <c r="V90" s="35"/>
-      <c r="W90" s="36"/>
-      <c r="X90" s="35"/>
-      <c r="Y90" s="36"/>
-      <c r="Z90" s="35"/>
-      <c r="AA90" s="36"/>
-      <c r="AB90" s="35"/>
-      <c r="AC90" s="36"/>
-      <c r="AD90" s="35"/>
-      <c r="AE90" s="36"/>
-      <c r="AF90" s="35"/>
-      <c r="AG90" s="36"/>
-      <c r="AH90" s="35"/>
-      <c r="AI90" s="36"/>
-      <c r="AJ90" s="35"/>
-      <c r="AK90" s="36"/>
-      <c r="AL90" s="35"/>
-      <c r="AM90" s="36"/>
-      <c r="AN90" s="35"/>
-      <c r="AO90" s="36"/>
-      <c r="AP90" s="35"/>
-      <c r="AQ90" s="35"/>
-      <c r="AR90" s="35"/>
-      <c r="AS90" s="35"/>
-      <c r="AT90" s="35"/>
-      <c r="AU90" s="36"/>
-      <c r="AV90" s="37"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="45"/>
+      <c r="M90" s="46"/>
+      <c r="N90" s="45"/>
+      <c r="O90" s="46"/>
+      <c r="P90" s="45"/>
+      <c r="Q90" s="46"/>
+      <c r="R90" s="45"/>
+      <c r="S90" s="46"/>
+      <c r="T90" s="45"/>
+      <c r="U90" s="46"/>
+      <c r="V90" s="45"/>
+      <c r="W90" s="46"/>
+      <c r="X90" s="45"/>
+      <c r="Y90" s="46"/>
+      <c r="Z90" s="45"/>
+      <c r="AA90" s="46"/>
+      <c r="AB90" s="45"/>
+      <c r="AC90" s="46"/>
+      <c r="AD90" s="45"/>
+      <c r="AE90" s="46"/>
+      <c r="AF90" s="45"/>
+      <c r="AG90" s="46"/>
+      <c r="AH90" s="45"/>
+      <c r="AI90" s="46"/>
+      <c r="AJ90" s="45"/>
+      <c r="AK90" s="46"/>
+      <c r="AL90" s="45"/>
+      <c r="AM90" s="46"/>
+      <c r="AN90" s="45"/>
+      <c r="AO90" s="46"/>
+      <c r="AP90" s="45"/>
+      <c r="AQ90" s="45"/>
+      <c r="AR90" s="45"/>
+      <c r="AS90" s="45"/>
+      <c r="AT90" s="45"/>
+      <c r="AU90" s="46"/>
+      <c r="AV90" s="47"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
@@ -14747,56 +14755,56 @@
       <c r="AX97" s="12"/>
     </row>
     <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="34" t="s">
+      <c r="A98" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="35"/>
-      <c r="C98" s="36"/>
-      <c r="D98" s="35"/>
-      <c r="E98" s="36"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="36"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="36"/>
-      <c r="J98" s="35"/>
-      <c r="K98" s="36"/>
-      <c r="L98" s="35"/>
-      <c r="M98" s="36"/>
-      <c r="N98" s="35"/>
-      <c r="O98" s="36"/>
-      <c r="P98" s="35"/>
-      <c r="Q98" s="36"/>
-      <c r="R98" s="35"/>
-      <c r="S98" s="36"/>
-      <c r="T98" s="35"/>
-      <c r="U98" s="36"/>
-      <c r="V98" s="35"/>
-      <c r="W98" s="36"/>
-      <c r="X98" s="35"/>
-      <c r="Y98" s="36"/>
-      <c r="Z98" s="35"/>
-      <c r="AA98" s="36"/>
-      <c r="AB98" s="35"/>
-      <c r="AC98" s="36"/>
-      <c r="AD98" s="35"/>
-      <c r="AE98" s="36"/>
-      <c r="AF98" s="35"/>
-      <c r="AG98" s="36"/>
-      <c r="AH98" s="35"/>
-      <c r="AI98" s="36"/>
-      <c r="AJ98" s="35"/>
-      <c r="AK98" s="36"/>
-      <c r="AL98" s="35"/>
-      <c r="AM98" s="36"/>
-      <c r="AN98" s="35"/>
-      <c r="AO98" s="36"/>
-      <c r="AP98" s="35"/>
-      <c r="AQ98" s="35"/>
-      <c r="AR98" s="35"/>
-      <c r="AS98" s="35"/>
-      <c r="AT98" s="35"/>
-      <c r="AU98" s="36"/>
-      <c r="AV98" s="37"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="46"/>
+      <c r="D98" s="45"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="45"/>
+      <c r="G98" s="46"/>
+      <c r="H98" s="45"/>
+      <c r="I98" s="46"/>
+      <c r="J98" s="45"/>
+      <c r="K98" s="46"/>
+      <c r="L98" s="45"/>
+      <c r="M98" s="46"/>
+      <c r="N98" s="45"/>
+      <c r="O98" s="46"/>
+      <c r="P98" s="45"/>
+      <c r="Q98" s="46"/>
+      <c r="R98" s="45"/>
+      <c r="S98" s="46"/>
+      <c r="T98" s="45"/>
+      <c r="U98" s="46"/>
+      <c r="V98" s="45"/>
+      <c r="W98" s="46"/>
+      <c r="X98" s="45"/>
+      <c r="Y98" s="46"/>
+      <c r="Z98" s="45"/>
+      <c r="AA98" s="46"/>
+      <c r="AB98" s="45"/>
+      <c r="AC98" s="46"/>
+      <c r="AD98" s="45"/>
+      <c r="AE98" s="46"/>
+      <c r="AF98" s="45"/>
+      <c r="AG98" s="46"/>
+      <c r="AH98" s="45"/>
+      <c r="AI98" s="46"/>
+      <c r="AJ98" s="45"/>
+      <c r="AK98" s="46"/>
+      <c r="AL98" s="45"/>
+      <c r="AM98" s="46"/>
+      <c r="AN98" s="45"/>
+      <c r="AO98" s="46"/>
+      <c r="AP98" s="45"/>
+      <c r="AQ98" s="45"/>
+      <c r="AR98" s="45"/>
+      <c r="AS98" s="45"/>
+      <c r="AT98" s="45"/>
+      <c r="AU98" s="46"/>
+      <c r="AV98" s="47"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
@@ -15903,56 +15911,56 @@
       <c r="AX105" s="12"/>
     </row>
     <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="34" t="s">
+      <c r="A106" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="35"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="35"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="35"/>
-      <c r="G106" s="36"/>
-      <c r="H106" s="35"/>
-      <c r="I106" s="36"/>
-      <c r="J106" s="35"/>
-      <c r="K106" s="36"/>
-      <c r="L106" s="35"/>
-      <c r="M106" s="36"/>
-      <c r="N106" s="35"/>
-      <c r="O106" s="36"/>
-      <c r="P106" s="35"/>
-      <c r="Q106" s="36"/>
-      <c r="R106" s="35"/>
-      <c r="S106" s="36"/>
-      <c r="T106" s="35"/>
-      <c r="U106" s="36"/>
-      <c r="V106" s="35"/>
-      <c r="W106" s="36"/>
-      <c r="X106" s="35"/>
-      <c r="Y106" s="36"/>
-      <c r="Z106" s="35"/>
-      <c r="AA106" s="36"/>
-      <c r="AB106" s="35"/>
-      <c r="AC106" s="36"/>
-      <c r="AD106" s="35"/>
-      <c r="AE106" s="36"/>
-      <c r="AF106" s="35"/>
-      <c r="AG106" s="36"/>
-      <c r="AH106" s="35"/>
-      <c r="AI106" s="36"/>
-      <c r="AJ106" s="35"/>
-      <c r="AK106" s="36"/>
-      <c r="AL106" s="35"/>
-      <c r="AM106" s="36"/>
-      <c r="AN106" s="35"/>
-      <c r="AO106" s="36"/>
-      <c r="AP106" s="35"/>
-      <c r="AQ106" s="35"/>
-      <c r="AR106" s="35"/>
-      <c r="AS106" s="35"/>
-      <c r="AT106" s="35"/>
-      <c r="AU106" s="36"/>
-      <c r="AV106" s="37"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="45"/>
+      <c r="E106" s="46"/>
+      <c r="F106" s="45"/>
+      <c r="G106" s="46"/>
+      <c r="H106" s="45"/>
+      <c r="I106" s="46"/>
+      <c r="J106" s="45"/>
+      <c r="K106" s="46"/>
+      <c r="L106" s="45"/>
+      <c r="M106" s="46"/>
+      <c r="N106" s="45"/>
+      <c r="O106" s="46"/>
+      <c r="P106" s="45"/>
+      <c r="Q106" s="46"/>
+      <c r="R106" s="45"/>
+      <c r="S106" s="46"/>
+      <c r="T106" s="45"/>
+      <c r="U106" s="46"/>
+      <c r="V106" s="45"/>
+      <c r="W106" s="46"/>
+      <c r="X106" s="45"/>
+      <c r="Y106" s="46"/>
+      <c r="Z106" s="45"/>
+      <c r="AA106" s="46"/>
+      <c r="AB106" s="45"/>
+      <c r="AC106" s="46"/>
+      <c r="AD106" s="45"/>
+      <c r="AE106" s="46"/>
+      <c r="AF106" s="45"/>
+      <c r="AG106" s="46"/>
+      <c r="AH106" s="45"/>
+      <c r="AI106" s="46"/>
+      <c r="AJ106" s="45"/>
+      <c r="AK106" s="46"/>
+      <c r="AL106" s="45"/>
+      <c r="AM106" s="46"/>
+      <c r="AN106" s="45"/>
+      <c r="AO106" s="46"/>
+      <c r="AP106" s="45"/>
+      <c r="AQ106" s="45"/>
+      <c r="AR106" s="45"/>
+      <c r="AS106" s="45"/>
+      <c r="AT106" s="45"/>
+      <c r="AU106" s="46"/>
+      <c r="AV106" s="47"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
@@ -16769,110 +16777,110 @@
       <c r="AX112" s="12"/>
     </row>
     <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="43" t="s">
+      <c r="A113" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="48"/>
-      <c r="C113" s="49"/>
-      <c r="D113" s="48"/>
-      <c r="E113" s="49"/>
-      <c r="F113" s="48"/>
-      <c r="G113" s="49"/>
-      <c r="H113" s="48"/>
-      <c r="I113" s="49"/>
-      <c r="J113" s="48"/>
-      <c r="K113" s="49"/>
-      <c r="L113" s="48"/>
-      <c r="M113" s="49"/>
-      <c r="N113" s="48"/>
-      <c r="O113" s="49"/>
-      <c r="P113" s="48"/>
-      <c r="Q113" s="49"/>
-      <c r="R113" s="48"/>
-      <c r="S113" s="49"/>
-      <c r="T113" s="48"/>
-      <c r="U113" s="49"/>
-      <c r="V113" s="48"/>
-      <c r="W113" s="49"/>
-      <c r="X113" s="48"/>
-      <c r="Y113" s="49"/>
-      <c r="Z113" s="48"/>
-      <c r="AA113" s="49"/>
-      <c r="AB113" s="48"/>
-      <c r="AC113" s="49"/>
-      <c r="AD113" s="48"/>
-      <c r="AE113" s="49"/>
-      <c r="AF113" s="48"/>
-      <c r="AG113" s="49"/>
-      <c r="AH113" s="48"/>
-      <c r="AI113" s="49"/>
-      <c r="AJ113" s="48"/>
-      <c r="AK113" s="49"/>
-      <c r="AL113" s="48"/>
-      <c r="AM113" s="49"/>
-      <c r="AN113" s="48"/>
-      <c r="AO113" s="49"/>
-      <c r="AP113" s="48"/>
-      <c r="AQ113" s="48"/>
-      <c r="AR113" s="48"/>
-      <c r="AS113" s="48"/>
-      <c r="AT113" s="48"/>
-      <c r="AU113" s="49"/>
-      <c r="AV113" s="42"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="50"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="50"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="50"/>
+      <c r="J113" s="49"/>
+      <c r="K113" s="50"/>
+      <c r="L113" s="49"/>
+      <c r="M113" s="50"/>
+      <c r="N113" s="49"/>
+      <c r="O113" s="50"/>
+      <c r="P113" s="49"/>
+      <c r="Q113" s="50"/>
+      <c r="R113" s="49"/>
+      <c r="S113" s="50"/>
+      <c r="T113" s="49"/>
+      <c r="U113" s="50"/>
+      <c r="V113" s="49"/>
+      <c r="W113" s="50"/>
+      <c r="X113" s="49"/>
+      <c r="Y113" s="50"/>
+      <c r="Z113" s="49"/>
+      <c r="AA113" s="50"/>
+      <c r="AB113" s="49"/>
+      <c r="AC113" s="50"/>
+      <c r="AD113" s="49"/>
+      <c r="AE113" s="50"/>
+      <c r="AF113" s="49"/>
+      <c r="AG113" s="50"/>
+      <c r="AH113" s="49"/>
+      <c r="AI113" s="50"/>
+      <c r="AJ113" s="49"/>
+      <c r="AK113" s="50"/>
+      <c r="AL113" s="49"/>
+      <c r="AM113" s="50"/>
+      <c r="AN113" s="49"/>
+      <c r="AO113" s="50"/>
+      <c r="AP113" s="49"/>
+      <c r="AQ113" s="49"/>
+      <c r="AR113" s="49"/>
+      <c r="AS113" s="49"/>
+      <c r="AT113" s="49"/>
+      <c r="AU113" s="50"/>
+      <c r="AV113" s="43"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
     <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="34" t="s">
+      <c r="A114" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="35"/>
-      <c r="C114" s="36"/>
-      <c r="D114" s="35"/>
-      <c r="E114" s="36"/>
-      <c r="F114" s="35"/>
-      <c r="G114" s="36"/>
-      <c r="H114" s="35"/>
-      <c r="I114" s="36"/>
-      <c r="J114" s="35"/>
-      <c r="K114" s="36"/>
-      <c r="L114" s="35"/>
-      <c r="M114" s="36"/>
-      <c r="N114" s="35"/>
-      <c r="O114" s="36"/>
-      <c r="P114" s="35"/>
-      <c r="Q114" s="36"/>
-      <c r="R114" s="35"/>
-      <c r="S114" s="36"/>
-      <c r="T114" s="35"/>
-      <c r="U114" s="36"/>
-      <c r="V114" s="35"/>
-      <c r="W114" s="36"/>
-      <c r="X114" s="35"/>
-      <c r="Y114" s="36"/>
-      <c r="Z114" s="35"/>
-      <c r="AA114" s="36"/>
-      <c r="AB114" s="35"/>
-      <c r="AC114" s="36"/>
-      <c r="AD114" s="35"/>
-      <c r="AE114" s="36"/>
-      <c r="AF114" s="35"/>
-      <c r="AG114" s="36"/>
-      <c r="AH114" s="35"/>
-      <c r="AI114" s="36"/>
-      <c r="AJ114" s="35"/>
-      <c r="AK114" s="36"/>
-      <c r="AL114" s="35"/>
-      <c r="AM114" s="36"/>
-      <c r="AN114" s="35"/>
-      <c r="AO114" s="36"/>
-      <c r="AP114" s="35"/>
-      <c r="AQ114" s="35"/>
-      <c r="AR114" s="35"/>
-      <c r="AS114" s="35"/>
-      <c r="AT114" s="35"/>
-      <c r="AU114" s="36"/>
-      <c r="AV114" s="37"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="46"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="46"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="46"/>
+      <c r="J114" s="45"/>
+      <c r="K114" s="46"/>
+      <c r="L114" s="45"/>
+      <c r="M114" s="46"/>
+      <c r="N114" s="45"/>
+      <c r="O114" s="46"/>
+      <c r="P114" s="45"/>
+      <c r="Q114" s="46"/>
+      <c r="R114" s="45"/>
+      <c r="S114" s="46"/>
+      <c r="T114" s="45"/>
+      <c r="U114" s="46"/>
+      <c r="V114" s="45"/>
+      <c r="W114" s="46"/>
+      <c r="X114" s="45"/>
+      <c r="Y114" s="46"/>
+      <c r="Z114" s="45"/>
+      <c r="AA114" s="46"/>
+      <c r="AB114" s="45"/>
+      <c r="AC114" s="46"/>
+      <c r="AD114" s="45"/>
+      <c r="AE114" s="46"/>
+      <c r="AF114" s="45"/>
+      <c r="AG114" s="46"/>
+      <c r="AH114" s="45"/>
+      <c r="AI114" s="46"/>
+      <c r="AJ114" s="45"/>
+      <c r="AK114" s="46"/>
+      <c r="AL114" s="45"/>
+      <c r="AM114" s="46"/>
+      <c r="AN114" s="45"/>
+      <c r="AO114" s="46"/>
+      <c r="AP114" s="45"/>
+      <c r="AQ114" s="45"/>
+      <c r="AR114" s="45"/>
+      <c r="AS114" s="45"/>
+      <c r="AT114" s="45"/>
+      <c r="AU114" s="46"/>
+      <c r="AV114" s="47"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
@@ -17065,56 +17073,56 @@
       <c r="AX116" s="12"/>
     </row>
     <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="34" t="s">
+      <c r="A117" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B117" s="35"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="35"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="35"/>
-      <c r="G117" s="36"/>
-      <c r="H117" s="35"/>
-      <c r="I117" s="36"/>
-      <c r="J117" s="35"/>
-      <c r="K117" s="36"/>
-      <c r="L117" s="35"/>
-      <c r="M117" s="36"/>
-      <c r="N117" s="35"/>
-      <c r="O117" s="36"/>
-      <c r="P117" s="35"/>
-      <c r="Q117" s="36"/>
-      <c r="R117" s="35"/>
-      <c r="S117" s="36"/>
-      <c r="T117" s="35"/>
-      <c r="U117" s="36"/>
-      <c r="V117" s="35"/>
-      <c r="W117" s="36"/>
-      <c r="X117" s="35"/>
-      <c r="Y117" s="36"/>
-      <c r="Z117" s="35"/>
-      <c r="AA117" s="36"/>
-      <c r="AB117" s="35"/>
-      <c r="AC117" s="36"/>
-      <c r="AD117" s="35"/>
-      <c r="AE117" s="36"/>
-      <c r="AF117" s="35"/>
-      <c r="AG117" s="36"/>
-      <c r="AH117" s="35"/>
-      <c r="AI117" s="36"/>
-      <c r="AJ117" s="35"/>
-      <c r="AK117" s="36"/>
-      <c r="AL117" s="35"/>
-      <c r="AM117" s="36"/>
-      <c r="AN117" s="35"/>
-      <c r="AO117" s="36"/>
-      <c r="AP117" s="35"/>
-      <c r="AQ117" s="35"/>
-      <c r="AR117" s="35"/>
-      <c r="AS117" s="35"/>
-      <c r="AT117" s="35"/>
-      <c r="AU117" s="36"/>
-      <c r="AV117" s="37"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="46"/>
+      <c r="D117" s="45"/>
+      <c r="E117" s="46"/>
+      <c r="F117" s="45"/>
+      <c r="G117" s="46"/>
+      <c r="H117" s="45"/>
+      <c r="I117" s="46"/>
+      <c r="J117" s="45"/>
+      <c r="K117" s="46"/>
+      <c r="L117" s="45"/>
+      <c r="M117" s="46"/>
+      <c r="N117" s="45"/>
+      <c r="O117" s="46"/>
+      <c r="P117" s="45"/>
+      <c r="Q117" s="46"/>
+      <c r="R117" s="45"/>
+      <c r="S117" s="46"/>
+      <c r="T117" s="45"/>
+      <c r="U117" s="46"/>
+      <c r="V117" s="45"/>
+      <c r="W117" s="46"/>
+      <c r="X117" s="45"/>
+      <c r="Y117" s="46"/>
+      <c r="Z117" s="45"/>
+      <c r="AA117" s="46"/>
+      <c r="AB117" s="45"/>
+      <c r="AC117" s="46"/>
+      <c r="AD117" s="45"/>
+      <c r="AE117" s="46"/>
+      <c r="AF117" s="45"/>
+      <c r="AG117" s="46"/>
+      <c r="AH117" s="45"/>
+      <c r="AI117" s="46"/>
+      <c r="AJ117" s="45"/>
+      <c r="AK117" s="46"/>
+      <c r="AL117" s="45"/>
+      <c r="AM117" s="46"/>
+      <c r="AN117" s="45"/>
+      <c r="AO117" s="46"/>
+      <c r="AP117" s="45"/>
+      <c r="AQ117" s="45"/>
+      <c r="AR117" s="45"/>
+      <c r="AS117" s="45"/>
+      <c r="AT117" s="45"/>
+      <c r="AU117" s="46"/>
+      <c r="AV117" s="47"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
@@ -17437,56 +17445,56 @@
       <c r="AX120" s="12"/>
     </row>
     <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="34" t="s">
+      <c r="A121" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B121" s="35"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="35"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="35"/>
-      <c r="G121" s="36"/>
-      <c r="H121" s="35"/>
-      <c r="I121" s="36"/>
-      <c r="J121" s="35"/>
-      <c r="K121" s="36"/>
-      <c r="L121" s="35"/>
-      <c r="M121" s="36"/>
-      <c r="N121" s="35"/>
-      <c r="O121" s="36"/>
-      <c r="P121" s="35"/>
-      <c r="Q121" s="36"/>
-      <c r="R121" s="35"/>
-      <c r="S121" s="36"/>
-      <c r="T121" s="35"/>
-      <c r="U121" s="36"/>
-      <c r="V121" s="35"/>
-      <c r="W121" s="36"/>
-      <c r="X121" s="35"/>
-      <c r="Y121" s="36"/>
-      <c r="Z121" s="35"/>
-      <c r="AA121" s="36"/>
-      <c r="AB121" s="35"/>
-      <c r="AC121" s="36"/>
-      <c r="AD121" s="35"/>
-      <c r="AE121" s="36"/>
-      <c r="AF121" s="35"/>
-      <c r="AG121" s="36"/>
-      <c r="AH121" s="35"/>
-      <c r="AI121" s="36"/>
-      <c r="AJ121" s="35"/>
-      <c r="AK121" s="36"/>
-      <c r="AL121" s="35"/>
-      <c r="AM121" s="36"/>
-      <c r="AN121" s="35"/>
-      <c r="AO121" s="36"/>
-      <c r="AP121" s="35"/>
-      <c r="AQ121" s="35"/>
-      <c r="AR121" s="35"/>
-      <c r="AS121" s="35"/>
-      <c r="AT121" s="35"/>
-      <c r="AU121" s="36"/>
-      <c r="AV121" s="37"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="46"/>
+      <c r="D121" s="45"/>
+      <c r="E121" s="46"/>
+      <c r="F121" s="45"/>
+      <c r="G121" s="46"/>
+      <c r="H121" s="45"/>
+      <c r="I121" s="46"/>
+      <c r="J121" s="45"/>
+      <c r="K121" s="46"/>
+      <c r="L121" s="45"/>
+      <c r="M121" s="46"/>
+      <c r="N121" s="45"/>
+      <c r="O121" s="46"/>
+      <c r="P121" s="45"/>
+      <c r="Q121" s="46"/>
+      <c r="R121" s="45"/>
+      <c r="S121" s="46"/>
+      <c r="T121" s="45"/>
+      <c r="U121" s="46"/>
+      <c r="V121" s="45"/>
+      <c r="W121" s="46"/>
+      <c r="X121" s="45"/>
+      <c r="Y121" s="46"/>
+      <c r="Z121" s="45"/>
+      <c r="AA121" s="46"/>
+      <c r="AB121" s="45"/>
+      <c r="AC121" s="46"/>
+      <c r="AD121" s="45"/>
+      <c r="AE121" s="46"/>
+      <c r="AF121" s="45"/>
+      <c r="AG121" s="46"/>
+      <c r="AH121" s="45"/>
+      <c r="AI121" s="46"/>
+      <c r="AJ121" s="45"/>
+      <c r="AK121" s="46"/>
+      <c r="AL121" s="45"/>
+      <c r="AM121" s="46"/>
+      <c r="AN121" s="45"/>
+      <c r="AO121" s="46"/>
+      <c r="AP121" s="45"/>
+      <c r="AQ121" s="45"/>
+      <c r="AR121" s="45"/>
+      <c r="AS121" s="45"/>
+      <c r="AT121" s="45"/>
+      <c r="AU121" s="46"/>
+      <c r="AV121" s="47"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
@@ -17939,56 +17947,56 @@
       <c r="AX125" s="12"/>
     </row>
     <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="34" t="s">
+      <c r="A126" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="35"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="35"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="35"/>
-      <c r="G126" s="36"/>
-      <c r="H126" s="35"/>
-      <c r="I126" s="36"/>
-      <c r="J126" s="35"/>
-      <c r="K126" s="36"/>
-      <c r="L126" s="35"/>
-      <c r="M126" s="36"/>
-      <c r="N126" s="35"/>
-      <c r="O126" s="36"/>
-      <c r="P126" s="35"/>
-      <c r="Q126" s="36"/>
-      <c r="R126" s="35"/>
-      <c r="S126" s="36"/>
-      <c r="T126" s="35"/>
-      <c r="U126" s="36"/>
-      <c r="V126" s="35"/>
-      <c r="W126" s="36"/>
-      <c r="X126" s="35"/>
-      <c r="Y126" s="36"/>
-      <c r="Z126" s="35"/>
-      <c r="AA126" s="36"/>
-      <c r="AB126" s="35"/>
-      <c r="AC126" s="36"/>
-      <c r="AD126" s="35"/>
-      <c r="AE126" s="36"/>
-      <c r="AF126" s="35"/>
-      <c r="AG126" s="36"/>
-      <c r="AH126" s="35"/>
-      <c r="AI126" s="36"/>
-      <c r="AJ126" s="35"/>
-      <c r="AK126" s="36"/>
-      <c r="AL126" s="35"/>
-      <c r="AM126" s="36"/>
-      <c r="AN126" s="35"/>
-      <c r="AO126" s="36"/>
-      <c r="AP126" s="35"/>
-      <c r="AQ126" s="35"/>
-      <c r="AR126" s="35"/>
-      <c r="AS126" s="35"/>
-      <c r="AT126" s="35"/>
-      <c r="AU126" s="36"/>
-      <c r="AV126" s="37"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="46"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="46"/>
+      <c r="J126" s="45"/>
+      <c r="K126" s="46"/>
+      <c r="L126" s="45"/>
+      <c r="M126" s="46"/>
+      <c r="N126" s="45"/>
+      <c r="O126" s="46"/>
+      <c r="P126" s="45"/>
+      <c r="Q126" s="46"/>
+      <c r="R126" s="45"/>
+      <c r="S126" s="46"/>
+      <c r="T126" s="45"/>
+      <c r="U126" s="46"/>
+      <c r="V126" s="45"/>
+      <c r="W126" s="46"/>
+      <c r="X126" s="45"/>
+      <c r="Y126" s="46"/>
+      <c r="Z126" s="45"/>
+      <c r="AA126" s="46"/>
+      <c r="AB126" s="45"/>
+      <c r="AC126" s="46"/>
+      <c r="AD126" s="45"/>
+      <c r="AE126" s="46"/>
+      <c r="AF126" s="45"/>
+      <c r="AG126" s="46"/>
+      <c r="AH126" s="45"/>
+      <c r="AI126" s="46"/>
+      <c r="AJ126" s="45"/>
+      <c r="AK126" s="46"/>
+      <c r="AL126" s="45"/>
+      <c r="AM126" s="46"/>
+      <c r="AN126" s="45"/>
+      <c r="AO126" s="46"/>
+      <c r="AP126" s="45"/>
+      <c r="AQ126" s="45"/>
+      <c r="AR126" s="45"/>
+      <c r="AS126" s="45"/>
+      <c r="AT126" s="45"/>
+      <c r="AU126" s="46"/>
+      <c r="AV126" s="47"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
@@ -18441,56 +18449,56 @@
       <c r="AX130" s="12"/>
     </row>
     <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="34" t="s">
+      <c r="A131" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="35"/>
-      <c r="C131" s="36"/>
-      <c r="D131" s="35"/>
-      <c r="E131" s="36"/>
-      <c r="F131" s="35"/>
-      <c r="G131" s="36"/>
-      <c r="H131" s="35"/>
-      <c r="I131" s="36"/>
-      <c r="J131" s="35"/>
-      <c r="K131" s="36"/>
-      <c r="L131" s="35"/>
-      <c r="M131" s="36"/>
-      <c r="N131" s="35"/>
-      <c r="O131" s="36"/>
-      <c r="P131" s="35"/>
-      <c r="Q131" s="36"/>
-      <c r="R131" s="35"/>
-      <c r="S131" s="36"/>
-      <c r="T131" s="35"/>
-      <c r="U131" s="36"/>
-      <c r="V131" s="35"/>
-      <c r="W131" s="36"/>
-      <c r="X131" s="35"/>
-      <c r="Y131" s="36"/>
-      <c r="Z131" s="35"/>
-      <c r="AA131" s="36"/>
-      <c r="AB131" s="35"/>
-      <c r="AC131" s="36"/>
-      <c r="AD131" s="35"/>
-      <c r="AE131" s="36"/>
-      <c r="AF131" s="35"/>
-      <c r="AG131" s="36"/>
-      <c r="AH131" s="35"/>
-      <c r="AI131" s="36"/>
-      <c r="AJ131" s="35"/>
-      <c r="AK131" s="36"/>
-      <c r="AL131" s="35"/>
-      <c r="AM131" s="36"/>
-      <c r="AN131" s="35"/>
-      <c r="AO131" s="36"/>
-      <c r="AP131" s="35"/>
-      <c r="AQ131" s="35"/>
-      <c r="AR131" s="35"/>
-      <c r="AS131" s="35"/>
-      <c r="AT131" s="35"/>
-      <c r="AU131" s="36"/>
-      <c r="AV131" s="37"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="46"/>
+      <c r="D131" s="45"/>
+      <c r="E131" s="46"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="46"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="46"/>
+      <c r="J131" s="45"/>
+      <c r="K131" s="46"/>
+      <c r="L131" s="45"/>
+      <c r="M131" s="46"/>
+      <c r="N131" s="45"/>
+      <c r="O131" s="46"/>
+      <c r="P131" s="45"/>
+      <c r="Q131" s="46"/>
+      <c r="R131" s="45"/>
+      <c r="S131" s="46"/>
+      <c r="T131" s="45"/>
+      <c r="U131" s="46"/>
+      <c r="V131" s="45"/>
+      <c r="W131" s="46"/>
+      <c r="X131" s="45"/>
+      <c r="Y131" s="46"/>
+      <c r="Z131" s="45"/>
+      <c r="AA131" s="46"/>
+      <c r="AB131" s="45"/>
+      <c r="AC131" s="46"/>
+      <c r="AD131" s="45"/>
+      <c r="AE131" s="46"/>
+      <c r="AF131" s="45"/>
+      <c r="AG131" s="46"/>
+      <c r="AH131" s="45"/>
+      <c r="AI131" s="46"/>
+      <c r="AJ131" s="45"/>
+      <c r="AK131" s="46"/>
+      <c r="AL131" s="45"/>
+      <c r="AM131" s="46"/>
+      <c r="AN131" s="45"/>
+      <c r="AO131" s="46"/>
+      <c r="AP131" s="45"/>
+      <c r="AQ131" s="45"/>
+      <c r="AR131" s="45"/>
+      <c r="AS131" s="45"/>
+      <c r="AT131" s="45"/>
+      <c r="AU131" s="46"/>
+      <c r="AV131" s="47"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
@@ -18813,56 +18821,56 @@
       <c r="AX134" s="12"/>
     </row>
     <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="34" t="s">
+      <c r="A135" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="B135" s="35"/>
-      <c r="C135" s="36"/>
-      <c r="D135" s="35"/>
-      <c r="E135" s="36"/>
-      <c r="F135" s="35"/>
-      <c r="G135" s="36"/>
-      <c r="H135" s="35"/>
-      <c r="I135" s="36"/>
-      <c r="J135" s="35"/>
-      <c r="K135" s="36"/>
-      <c r="L135" s="35"/>
-      <c r="M135" s="36"/>
-      <c r="N135" s="35"/>
-      <c r="O135" s="36"/>
-      <c r="P135" s="35"/>
-      <c r="Q135" s="36"/>
-      <c r="R135" s="35"/>
-      <c r="S135" s="36"/>
-      <c r="T135" s="35"/>
-      <c r="U135" s="36"/>
-      <c r="V135" s="35"/>
-      <c r="W135" s="36"/>
-      <c r="X135" s="35"/>
-      <c r="Y135" s="36"/>
-      <c r="Z135" s="35"/>
-      <c r="AA135" s="36"/>
-      <c r="AB135" s="35"/>
-      <c r="AC135" s="36"/>
-      <c r="AD135" s="35"/>
-      <c r="AE135" s="36"/>
-      <c r="AF135" s="35"/>
-      <c r="AG135" s="36"/>
-      <c r="AH135" s="35"/>
-      <c r="AI135" s="36"/>
-      <c r="AJ135" s="35"/>
-      <c r="AK135" s="36"/>
-      <c r="AL135" s="35"/>
-      <c r="AM135" s="36"/>
-      <c r="AN135" s="35"/>
-      <c r="AO135" s="36"/>
-      <c r="AP135" s="35"/>
-      <c r="AQ135" s="35"/>
-      <c r="AR135" s="35"/>
-      <c r="AS135" s="35"/>
-      <c r="AT135" s="35"/>
-      <c r="AU135" s="36"/>
-      <c r="AV135" s="37"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="46"/>
+      <c r="D135" s="45"/>
+      <c r="E135" s="46"/>
+      <c r="F135" s="45"/>
+      <c r="G135" s="46"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="46"/>
+      <c r="J135" s="45"/>
+      <c r="K135" s="46"/>
+      <c r="L135" s="45"/>
+      <c r="M135" s="46"/>
+      <c r="N135" s="45"/>
+      <c r="O135" s="46"/>
+      <c r="P135" s="45"/>
+      <c r="Q135" s="46"/>
+      <c r="R135" s="45"/>
+      <c r="S135" s="46"/>
+      <c r="T135" s="45"/>
+      <c r="U135" s="46"/>
+      <c r="V135" s="45"/>
+      <c r="W135" s="46"/>
+      <c r="X135" s="45"/>
+      <c r="Y135" s="46"/>
+      <c r="Z135" s="45"/>
+      <c r="AA135" s="46"/>
+      <c r="AB135" s="45"/>
+      <c r="AC135" s="46"/>
+      <c r="AD135" s="45"/>
+      <c r="AE135" s="46"/>
+      <c r="AF135" s="45"/>
+      <c r="AG135" s="46"/>
+      <c r="AH135" s="45"/>
+      <c r="AI135" s="46"/>
+      <c r="AJ135" s="45"/>
+      <c r="AK135" s="46"/>
+      <c r="AL135" s="45"/>
+      <c r="AM135" s="46"/>
+      <c r="AN135" s="45"/>
+      <c r="AO135" s="46"/>
+      <c r="AP135" s="45"/>
+      <c r="AQ135" s="45"/>
+      <c r="AR135" s="45"/>
+      <c r="AS135" s="45"/>
+      <c r="AT135" s="45"/>
+      <c r="AU135" s="46"/>
+      <c r="AV135" s="47"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
@@ -19315,56 +19323,56 @@
       <c r="AX139" s="12"/>
     </row>
     <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="34" t="s">
+      <c r="A140" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B140" s="35"/>
-      <c r="C140" s="36"/>
-      <c r="D140" s="35"/>
-      <c r="E140" s="36"/>
-      <c r="F140" s="35"/>
-      <c r="G140" s="36"/>
-      <c r="H140" s="35"/>
-      <c r="I140" s="36"/>
-      <c r="J140" s="35"/>
-      <c r="K140" s="36"/>
-      <c r="L140" s="35"/>
-      <c r="M140" s="36"/>
-      <c r="N140" s="35"/>
-      <c r="O140" s="36"/>
-      <c r="P140" s="35"/>
-      <c r="Q140" s="36"/>
-      <c r="R140" s="35"/>
-      <c r="S140" s="36"/>
-      <c r="T140" s="35"/>
-      <c r="U140" s="36"/>
-      <c r="V140" s="35"/>
-      <c r="W140" s="36"/>
-      <c r="X140" s="35"/>
-      <c r="Y140" s="36"/>
-      <c r="Z140" s="35"/>
-      <c r="AA140" s="36"/>
-      <c r="AB140" s="35"/>
-      <c r="AC140" s="36"/>
-      <c r="AD140" s="35"/>
-      <c r="AE140" s="36"/>
-      <c r="AF140" s="35"/>
-      <c r="AG140" s="36"/>
-      <c r="AH140" s="35"/>
-      <c r="AI140" s="36"/>
-      <c r="AJ140" s="35"/>
-      <c r="AK140" s="36"/>
-      <c r="AL140" s="35"/>
-      <c r="AM140" s="36"/>
-      <c r="AN140" s="35"/>
-      <c r="AO140" s="36"/>
-      <c r="AP140" s="35"/>
-      <c r="AQ140" s="35"/>
-      <c r="AR140" s="35"/>
-      <c r="AS140" s="35"/>
-      <c r="AT140" s="35"/>
-      <c r="AU140" s="36"/>
-      <c r="AV140" s="37"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="46"/>
+      <c r="D140" s="45"/>
+      <c r="E140" s="46"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="46"/>
+      <c r="H140" s="45"/>
+      <c r="I140" s="46"/>
+      <c r="J140" s="45"/>
+      <c r="K140" s="46"/>
+      <c r="L140" s="45"/>
+      <c r="M140" s="46"/>
+      <c r="N140" s="45"/>
+      <c r="O140" s="46"/>
+      <c r="P140" s="45"/>
+      <c r="Q140" s="46"/>
+      <c r="R140" s="45"/>
+      <c r="S140" s="46"/>
+      <c r="T140" s="45"/>
+      <c r="U140" s="46"/>
+      <c r="V140" s="45"/>
+      <c r="W140" s="46"/>
+      <c r="X140" s="45"/>
+      <c r="Y140" s="46"/>
+      <c r="Z140" s="45"/>
+      <c r="AA140" s="46"/>
+      <c r="AB140" s="45"/>
+      <c r="AC140" s="46"/>
+      <c r="AD140" s="45"/>
+      <c r="AE140" s="46"/>
+      <c r="AF140" s="45"/>
+      <c r="AG140" s="46"/>
+      <c r="AH140" s="45"/>
+      <c r="AI140" s="46"/>
+      <c r="AJ140" s="45"/>
+      <c r="AK140" s="46"/>
+      <c r="AL140" s="45"/>
+      <c r="AM140" s="46"/>
+      <c r="AN140" s="45"/>
+      <c r="AO140" s="46"/>
+      <c r="AP140" s="45"/>
+      <c r="AQ140" s="45"/>
+      <c r="AR140" s="45"/>
+      <c r="AS140" s="45"/>
+      <c r="AT140" s="45"/>
+      <c r="AU140" s="46"/>
+      <c r="AV140" s="47"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
@@ -19745,110 +19753,110 @@
       <c r="AX144" s="12"/>
     </row>
     <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="43" t="s">
+      <c r="A145" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="48"/>
-      <c r="C145" s="49"/>
-      <c r="D145" s="48"/>
-      <c r="E145" s="49"/>
-      <c r="F145" s="48"/>
-      <c r="G145" s="49"/>
-      <c r="H145" s="48"/>
-      <c r="I145" s="49"/>
-      <c r="J145" s="48"/>
-      <c r="K145" s="49"/>
-      <c r="L145" s="48"/>
-      <c r="M145" s="49"/>
-      <c r="N145" s="48"/>
-      <c r="O145" s="49"/>
-      <c r="P145" s="48"/>
-      <c r="Q145" s="49"/>
-      <c r="R145" s="48"/>
-      <c r="S145" s="49"/>
-      <c r="T145" s="48"/>
-      <c r="U145" s="49"/>
-      <c r="V145" s="48"/>
-      <c r="W145" s="49"/>
-      <c r="X145" s="48"/>
-      <c r="Y145" s="49"/>
-      <c r="Z145" s="48"/>
-      <c r="AA145" s="49"/>
-      <c r="AB145" s="48"/>
-      <c r="AC145" s="49"/>
-      <c r="AD145" s="48"/>
-      <c r="AE145" s="49"/>
-      <c r="AF145" s="48"/>
-      <c r="AG145" s="49"/>
-      <c r="AH145" s="48"/>
-      <c r="AI145" s="49"/>
-      <c r="AJ145" s="48"/>
-      <c r="AK145" s="49"/>
-      <c r="AL145" s="48"/>
-      <c r="AM145" s="49"/>
-      <c r="AN145" s="48"/>
-      <c r="AO145" s="49"/>
-      <c r="AP145" s="48"/>
-      <c r="AQ145" s="48"/>
-      <c r="AR145" s="48"/>
-      <c r="AS145" s="48"/>
-      <c r="AT145" s="48"/>
-      <c r="AU145" s="49"/>
-      <c r="AV145" s="42"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="50"/>
+      <c r="D145" s="49"/>
+      <c r="E145" s="50"/>
+      <c r="F145" s="49"/>
+      <c r="G145" s="50"/>
+      <c r="H145" s="49"/>
+      <c r="I145" s="50"/>
+      <c r="J145" s="49"/>
+      <c r="K145" s="50"/>
+      <c r="L145" s="49"/>
+      <c r="M145" s="50"/>
+      <c r="N145" s="49"/>
+      <c r="O145" s="50"/>
+      <c r="P145" s="49"/>
+      <c r="Q145" s="50"/>
+      <c r="R145" s="49"/>
+      <c r="S145" s="50"/>
+      <c r="T145" s="49"/>
+      <c r="U145" s="50"/>
+      <c r="V145" s="49"/>
+      <c r="W145" s="50"/>
+      <c r="X145" s="49"/>
+      <c r="Y145" s="50"/>
+      <c r="Z145" s="49"/>
+      <c r="AA145" s="50"/>
+      <c r="AB145" s="49"/>
+      <c r="AC145" s="50"/>
+      <c r="AD145" s="49"/>
+      <c r="AE145" s="50"/>
+      <c r="AF145" s="49"/>
+      <c r="AG145" s="50"/>
+      <c r="AH145" s="49"/>
+      <c r="AI145" s="50"/>
+      <c r="AJ145" s="49"/>
+      <c r="AK145" s="50"/>
+      <c r="AL145" s="49"/>
+      <c r="AM145" s="50"/>
+      <c r="AN145" s="49"/>
+      <c r="AO145" s="50"/>
+      <c r="AP145" s="49"/>
+      <c r="AQ145" s="49"/>
+      <c r="AR145" s="49"/>
+      <c r="AS145" s="49"/>
+      <c r="AT145" s="49"/>
+      <c r="AU145" s="50"/>
+      <c r="AV145" s="43"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
     <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="34" t="s">
+      <c r="A146" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="35"/>
-      <c r="C146" s="36"/>
-      <c r="D146" s="35"/>
-      <c r="E146" s="36"/>
-      <c r="F146" s="35"/>
-      <c r="G146" s="36"/>
-      <c r="H146" s="35"/>
-      <c r="I146" s="36"/>
-      <c r="J146" s="35"/>
-      <c r="K146" s="36"/>
-      <c r="L146" s="35"/>
-      <c r="M146" s="36"/>
-      <c r="N146" s="35"/>
-      <c r="O146" s="36"/>
-      <c r="P146" s="35"/>
-      <c r="Q146" s="36"/>
-      <c r="R146" s="35"/>
-      <c r="S146" s="36"/>
-      <c r="T146" s="35"/>
-      <c r="U146" s="36"/>
-      <c r="V146" s="35"/>
-      <c r="W146" s="36"/>
-      <c r="X146" s="35"/>
-      <c r="Y146" s="36"/>
-      <c r="Z146" s="35"/>
-      <c r="AA146" s="36"/>
-      <c r="AB146" s="35"/>
-      <c r="AC146" s="36"/>
-      <c r="AD146" s="35"/>
-      <c r="AE146" s="36"/>
-      <c r="AF146" s="35"/>
-      <c r="AG146" s="36"/>
-      <c r="AH146" s="35"/>
-      <c r="AI146" s="36"/>
-      <c r="AJ146" s="35"/>
-      <c r="AK146" s="36"/>
-      <c r="AL146" s="35"/>
-      <c r="AM146" s="36"/>
-      <c r="AN146" s="35"/>
-      <c r="AO146" s="36"/>
-      <c r="AP146" s="35"/>
-      <c r="AQ146" s="35"/>
-      <c r="AR146" s="35"/>
-      <c r="AS146" s="35"/>
-      <c r="AT146" s="35"/>
-      <c r="AU146" s="36"/>
-      <c r="AV146" s="37"/>
+      <c r="B146" s="45"/>
+      <c r="C146" s="46"/>
+      <c r="D146" s="45"/>
+      <c r="E146" s="46"/>
+      <c r="F146" s="45"/>
+      <c r="G146" s="46"/>
+      <c r="H146" s="45"/>
+      <c r="I146" s="46"/>
+      <c r="J146" s="45"/>
+      <c r="K146" s="46"/>
+      <c r="L146" s="45"/>
+      <c r="M146" s="46"/>
+      <c r="N146" s="45"/>
+      <c r="O146" s="46"/>
+      <c r="P146" s="45"/>
+      <c r="Q146" s="46"/>
+      <c r="R146" s="45"/>
+      <c r="S146" s="46"/>
+      <c r="T146" s="45"/>
+      <c r="U146" s="46"/>
+      <c r="V146" s="45"/>
+      <c r="W146" s="46"/>
+      <c r="X146" s="45"/>
+      <c r="Y146" s="46"/>
+      <c r="Z146" s="45"/>
+      <c r="AA146" s="46"/>
+      <c r="AB146" s="45"/>
+      <c r="AC146" s="46"/>
+      <c r="AD146" s="45"/>
+      <c r="AE146" s="46"/>
+      <c r="AF146" s="45"/>
+      <c r="AG146" s="46"/>
+      <c r="AH146" s="45"/>
+      <c r="AI146" s="46"/>
+      <c r="AJ146" s="45"/>
+      <c r="AK146" s="46"/>
+      <c r="AL146" s="45"/>
+      <c r="AM146" s="46"/>
+      <c r="AN146" s="45"/>
+      <c r="AO146" s="46"/>
+      <c r="AP146" s="45"/>
+      <c r="AQ146" s="45"/>
+      <c r="AR146" s="45"/>
+      <c r="AS146" s="45"/>
+      <c r="AT146" s="45"/>
+      <c r="AU146" s="46"/>
+      <c r="AV146" s="47"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
@@ -20171,56 +20179,56 @@
       <c r="AX149" s="12"/>
     </row>
     <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="34" t="s">
+      <c r="A150" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B150" s="35"/>
-      <c r="C150" s="36"/>
-      <c r="D150" s="35"/>
-      <c r="E150" s="36"/>
-      <c r="F150" s="35"/>
-      <c r="G150" s="36"/>
-      <c r="H150" s="35"/>
-      <c r="I150" s="36"/>
-      <c r="J150" s="35"/>
-      <c r="K150" s="36"/>
-      <c r="L150" s="35"/>
-      <c r="M150" s="36"/>
-      <c r="N150" s="35"/>
-      <c r="O150" s="36"/>
-      <c r="P150" s="35"/>
-      <c r="Q150" s="36"/>
-      <c r="R150" s="35"/>
-      <c r="S150" s="36"/>
-      <c r="T150" s="35"/>
-      <c r="U150" s="36"/>
-      <c r="V150" s="35"/>
-      <c r="W150" s="36"/>
-      <c r="X150" s="35"/>
-      <c r="Y150" s="36"/>
-      <c r="Z150" s="35"/>
-      <c r="AA150" s="36"/>
-      <c r="AB150" s="35"/>
-      <c r="AC150" s="36"/>
-      <c r="AD150" s="35"/>
-      <c r="AE150" s="36"/>
-      <c r="AF150" s="35"/>
-      <c r="AG150" s="36"/>
-      <c r="AH150" s="35"/>
-      <c r="AI150" s="36"/>
-      <c r="AJ150" s="35"/>
-      <c r="AK150" s="36"/>
-      <c r="AL150" s="35"/>
-      <c r="AM150" s="36"/>
-      <c r="AN150" s="35"/>
-      <c r="AO150" s="36"/>
-      <c r="AP150" s="35"/>
-      <c r="AQ150" s="35"/>
-      <c r="AR150" s="35"/>
-      <c r="AS150" s="35"/>
-      <c r="AT150" s="35"/>
-      <c r="AU150" s="36"/>
-      <c r="AV150" s="37"/>
+      <c r="B150" s="45"/>
+      <c r="C150" s="46"/>
+      <c r="D150" s="45"/>
+      <c r="E150" s="46"/>
+      <c r="F150" s="45"/>
+      <c r="G150" s="46"/>
+      <c r="H150" s="45"/>
+      <c r="I150" s="46"/>
+      <c r="J150" s="45"/>
+      <c r="K150" s="46"/>
+      <c r="L150" s="45"/>
+      <c r="M150" s="46"/>
+      <c r="N150" s="45"/>
+      <c r="O150" s="46"/>
+      <c r="P150" s="45"/>
+      <c r="Q150" s="46"/>
+      <c r="R150" s="45"/>
+      <c r="S150" s="46"/>
+      <c r="T150" s="45"/>
+      <c r="U150" s="46"/>
+      <c r="V150" s="45"/>
+      <c r="W150" s="46"/>
+      <c r="X150" s="45"/>
+      <c r="Y150" s="46"/>
+      <c r="Z150" s="45"/>
+      <c r="AA150" s="46"/>
+      <c r="AB150" s="45"/>
+      <c r="AC150" s="46"/>
+      <c r="AD150" s="45"/>
+      <c r="AE150" s="46"/>
+      <c r="AF150" s="45"/>
+      <c r="AG150" s="46"/>
+      <c r="AH150" s="45"/>
+      <c r="AI150" s="46"/>
+      <c r="AJ150" s="45"/>
+      <c r="AK150" s="46"/>
+      <c r="AL150" s="45"/>
+      <c r="AM150" s="46"/>
+      <c r="AN150" s="45"/>
+      <c r="AO150" s="46"/>
+      <c r="AP150" s="45"/>
+      <c r="AQ150" s="45"/>
+      <c r="AR150" s="45"/>
+      <c r="AS150" s="45"/>
+      <c r="AT150" s="45"/>
+      <c r="AU150" s="46"/>
+      <c r="AV150" s="47"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
@@ -20413,56 +20421,56 @@
       <c r="AX152" s="12"/>
     </row>
     <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="34" t="s">
+      <c r="A153" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="B153" s="35"/>
-      <c r="C153" s="36"/>
-      <c r="D153" s="35"/>
-      <c r="E153" s="36"/>
-      <c r="F153" s="35"/>
-      <c r="G153" s="36"/>
-      <c r="H153" s="35"/>
-      <c r="I153" s="36"/>
-      <c r="J153" s="35"/>
-      <c r="K153" s="36"/>
-      <c r="L153" s="35"/>
-      <c r="M153" s="36"/>
-      <c r="N153" s="35"/>
-      <c r="O153" s="36"/>
-      <c r="P153" s="35"/>
-      <c r="Q153" s="36"/>
-      <c r="R153" s="35"/>
-      <c r="S153" s="36"/>
-      <c r="T153" s="35"/>
-      <c r="U153" s="36"/>
-      <c r="V153" s="35"/>
-      <c r="W153" s="36"/>
-      <c r="X153" s="35"/>
-      <c r="Y153" s="36"/>
-      <c r="Z153" s="35"/>
-      <c r="AA153" s="36"/>
-      <c r="AB153" s="35"/>
-      <c r="AC153" s="36"/>
-      <c r="AD153" s="35"/>
-      <c r="AE153" s="36"/>
-      <c r="AF153" s="35"/>
-      <c r="AG153" s="36"/>
-      <c r="AH153" s="35"/>
-      <c r="AI153" s="36"/>
-      <c r="AJ153" s="35"/>
-      <c r="AK153" s="36"/>
-      <c r="AL153" s="35"/>
-      <c r="AM153" s="36"/>
-      <c r="AN153" s="35"/>
-      <c r="AO153" s="36"/>
-      <c r="AP153" s="35"/>
-      <c r="AQ153" s="35"/>
-      <c r="AR153" s="35"/>
-      <c r="AS153" s="35"/>
-      <c r="AT153" s="35"/>
-      <c r="AU153" s="36"/>
-      <c r="AV153" s="37"/>
+      <c r="B153" s="45"/>
+      <c r="C153" s="46"/>
+      <c r="D153" s="45"/>
+      <c r="E153" s="46"/>
+      <c r="F153" s="45"/>
+      <c r="G153" s="46"/>
+      <c r="H153" s="45"/>
+      <c r="I153" s="46"/>
+      <c r="J153" s="45"/>
+      <c r="K153" s="46"/>
+      <c r="L153" s="45"/>
+      <c r="M153" s="46"/>
+      <c r="N153" s="45"/>
+      <c r="O153" s="46"/>
+      <c r="P153" s="45"/>
+      <c r="Q153" s="46"/>
+      <c r="R153" s="45"/>
+      <c r="S153" s="46"/>
+      <c r="T153" s="45"/>
+      <c r="U153" s="46"/>
+      <c r="V153" s="45"/>
+      <c r="W153" s="46"/>
+      <c r="X153" s="45"/>
+      <c r="Y153" s="46"/>
+      <c r="Z153" s="45"/>
+      <c r="AA153" s="46"/>
+      <c r="AB153" s="45"/>
+      <c r="AC153" s="46"/>
+      <c r="AD153" s="45"/>
+      <c r="AE153" s="46"/>
+      <c r="AF153" s="45"/>
+      <c r="AG153" s="46"/>
+      <c r="AH153" s="45"/>
+      <c r="AI153" s="46"/>
+      <c r="AJ153" s="45"/>
+      <c r="AK153" s="46"/>
+      <c r="AL153" s="45"/>
+      <c r="AM153" s="46"/>
+      <c r="AN153" s="45"/>
+      <c r="AO153" s="46"/>
+      <c r="AP153" s="45"/>
+      <c r="AQ153" s="45"/>
+      <c r="AR153" s="45"/>
+      <c r="AS153" s="45"/>
+      <c r="AT153" s="45"/>
+      <c r="AU153" s="46"/>
+      <c r="AV153" s="47"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
@@ -20785,56 +20793,56 @@
       <c r="AX156" s="12"/>
     </row>
     <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="34" t="s">
+      <c r="A157" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="B157" s="35"/>
-      <c r="C157" s="36"/>
-      <c r="D157" s="35"/>
-      <c r="E157" s="36"/>
-      <c r="F157" s="35"/>
-      <c r="G157" s="36"/>
-      <c r="H157" s="35"/>
-      <c r="I157" s="36"/>
-      <c r="J157" s="35"/>
-      <c r="K157" s="36"/>
-      <c r="L157" s="35"/>
-      <c r="M157" s="36"/>
-      <c r="N157" s="35"/>
-      <c r="O157" s="36"/>
-      <c r="P157" s="35"/>
-      <c r="Q157" s="36"/>
-      <c r="R157" s="35"/>
-      <c r="S157" s="36"/>
-      <c r="T157" s="35"/>
-      <c r="U157" s="36"/>
-      <c r="V157" s="35"/>
-      <c r="W157" s="36"/>
-      <c r="X157" s="35"/>
-      <c r="Y157" s="36"/>
-      <c r="Z157" s="35"/>
-      <c r="AA157" s="36"/>
-      <c r="AB157" s="35"/>
-      <c r="AC157" s="36"/>
-      <c r="AD157" s="35"/>
-      <c r="AE157" s="36"/>
-      <c r="AF157" s="35"/>
-      <c r="AG157" s="36"/>
-      <c r="AH157" s="35"/>
-      <c r="AI157" s="36"/>
-      <c r="AJ157" s="35"/>
-      <c r="AK157" s="36"/>
-      <c r="AL157" s="35"/>
-      <c r="AM157" s="36"/>
-      <c r="AN157" s="35"/>
-      <c r="AO157" s="36"/>
-      <c r="AP157" s="35"/>
-      <c r="AQ157" s="35"/>
-      <c r="AR157" s="35"/>
-      <c r="AS157" s="35"/>
-      <c r="AT157" s="35"/>
-      <c r="AU157" s="36"/>
-      <c r="AV157" s="37"/>
+      <c r="B157" s="45"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="45"/>
+      <c r="E157" s="46"/>
+      <c r="F157" s="45"/>
+      <c r="G157" s="46"/>
+      <c r="H157" s="45"/>
+      <c r="I157" s="46"/>
+      <c r="J157" s="45"/>
+      <c r="K157" s="46"/>
+      <c r="L157" s="45"/>
+      <c r="M157" s="46"/>
+      <c r="N157" s="45"/>
+      <c r="O157" s="46"/>
+      <c r="P157" s="45"/>
+      <c r="Q157" s="46"/>
+      <c r="R157" s="45"/>
+      <c r="S157" s="46"/>
+      <c r="T157" s="45"/>
+      <c r="U157" s="46"/>
+      <c r="V157" s="45"/>
+      <c r="W157" s="46"/>
+      <c r="X157" s="45"/>
+      <c r="Y157" s="46"/>
+      <c r="Z157" s="45"/>
+      <c r="AA157" s="46"/>
+      <c r="AB157" s="45"/>
+      <c r="AC157" s="46"/>
+      <c r="AD157" s="45"/>
+      <c r="AE157" s="46"/>
+      <c r="AF157" s="45"/>
+      <c r="AG157" s="46"/>
+      <c r="AH157" s="45"/>
+      <c r="AI157" s="46"/>
+      <c r="AJ157" s="45"/>
+      <c r="AK157" s="46"/>
+      <c r="AL157" s="45"/>
+      <c r="AM157" s="46"/>
+      <c r="AN157" s="45"/>
+      <c r="AO157" s="46"/>
+      <c r="AP157" s="45"/>
+      <c r="AQ157" s="45"/>
+      <c r="AR157" s="45"/>
+      <c r="AS157" s="45"/>
+      <c r="AT157" s="45"/>
+      <c r="AU157" s="46"/>
+      <c r="AV157" s="47"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
@@ -21345,110 +21353,110 @@
       <c r="AX162" s="12"/>
     </row>
     <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="43" t="s">
+      <c r="A163" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="48"/>
-      <c r="C163" s="49"/>
-      <c r="D163" s="48"/>
-      <c r="E163" s="49"/>
-      <c r="F163" s="48"/>
-      <c r="G163" s="49"/>
-      <c r="H163" s="48"/>
-      <c r="I163" s="49"/>
-      <c r="J163" s="48"/>
-      <c r="K163" s="49"/>
-      <c r="L163" s="48"/>
-      <c r="M163" s="49"/>
-      <c r="N163" s="48"/>
-      <c r="O163" s="49"/>
-      <c r="P163" s="48"/>
-      <c r="Q163" s="49"/>
-      <c r="R163" s="48"/>
-      <c r="S163" s="49"/>
-      <c r="T163" s="48"/>
-      <c r="U163" s="49"/>
-      <c r="V163" s="48"/>
-      <c r="W163" s="49"/>
-      <c r="X163" s="48"/>
-      <c r="Y163" s="49"/>
-      <c r="Z163" s="48"/>
-      <c r="AA163" s="49"/>
-      <c r="AB163" s="48"/>
-      <c r="AC163" s="49"/>
-      <c r="AD163" s="48"/>
-      <c r="AE163" s="49"/>
-      <c r="AF163" s="48"/>
-      <c r="AG163" s="49"/>
-      <c r="AH163" s="48"/>
-      <c r="AI163" s="49"/>
-      <c r="AJ163" s="48"/>
-      <c r="AK163" s="49"/>
-      <c r="AL163" s="48"/>
-      <c r="AM163" s="49"/>
-      <c r="AN163" s="48"/>
-      <c r="AO163" s="49"/>
-      <c r="AP163" s="48"/>
-      <c r="AQ163" s="48"/>
-      <c r="AR163" s="48"/>
-      <c r="AS163" s="48"/>
-      <c r="AT163" s="48"/>
-      <c r="AU163" s="49"/>
-      <c r="AV163" s="42"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="50"/>
+      <c r="D163" s="49"/>
+      <c r="E163" s="50"/>
+      <c r="F163" s="49"/>
+      <c r="G163" s="50"/>
+      <c r="H163" s="49"/>
+      <c r="I163" s="50"/>
+      <c r="J163" s="49"/>
+      <c r="K163" s="50"/>
+      <c r="L163" s="49"/>
+      <c r="M163" s="50"/>
+      <c r="N163" s="49"/>
+      <c r="O163" s="50"/>
+      <c r="P163" s="49"/>
+      <c r="Q163" s="50"/>
+      <c r="R163" s="49"/>
+      <c r="S163" s="50"/>
+      <c r="T163" s="49"/>
+      <c r="U163" s="50"/>
+      <c r="V163" s="49"/>
+      <c r="W163" s="50"/>
+      <c r="X163" s="49"/>
+      <c r="Y163" s="50"/>
+      <c r="Z163" s="49"/>
+      <c r="AA163" s="50"/>
+      <c r="AB163" s="49"/>
+      <c r="AC163" s="50"/>
+      <c r="AD163" s="49"/>
+      <c r="AE163" s="50"/>
+      <c r="AF163" s="49"/>
+      <c r="AG163" s="50"/>
+      <c r="AH163" s="49"/>
+      <c r="AI163" s="50"/>
+      <c r="AJ163" s="49"/>
+      <c r="AK163" s="50"/>
+      <c r="AL163" s="49"/>
+      <c r="AM163" s="50"/>
+      <c r="AN163" s="49"/>
+      <c r="AO163" s="50"/>
+      <c r="AP163" s="49"/>
+      <c r="AQ163" s="49"/>
+      <c r="AR163" s="49"/>
+      <c r="AS163" s="49"/>
+      <c r="AT163" s="49"/>
+      <c r="AU163" s="50"/>
+      <c r="AV163" s="43"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
     <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="34" t="s">
+      <c r="A164" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B164" s="35"/>
-      <c r="C164" s="36"/>
-      <c r="D164" s="35"/>
-      <c r="E164" s="36"/>
-      <c r="F164" s="35"/>
-      <c r="G164" s="36"/>
-      <c r="H164" s="35"/>
-      <c r="I164" s="36"/>
-      <c r="J164" s="35"/>
-      <c r="K164" s="36"/>
-      <c r="L164" s="35"/>
-      <c r="M164" s="36"/>
-      <c r="N164" s="35"/>
-      <c r="O164" s="36"/>
-      <c r="P164" s="35"/>
-      <c r="Q164" s="36"/>
-      <c r="R164" s="35"/>
-      <c r="S164" s="36"/>
-      <c r="T164" s="35"/>
-      <c r="U164" s="36"/>
-      <c r="V164" s="35"/>
-      <c r="W164" s="36"/>
-      <c r="X164" s="35"/>
-      <c r="Y164" s="36"/>
-      <c r="Z164" s="35"/>
-      <c r="AA164" s="36"/>
-      <c r="AB164" s="35"/>
-      <c r="AC164" s="36"/>
-      <c r="AD164" s="35"/>
-      <c r="AE164" s="36"/>
-      <c r="AF164" s="35"/>
-      <c r="AG164" s="36"/>
-      <c r="AH164" s="35"/>
-      <c r="AI164" s="36"/>
-      <c r="AJ164" s="35"/>
-      <c r="AK164" s="36"/>
-      <c r="AL164" s="35"/>
-      <c r="AM164" s="36"/>
-      <c r="AN164" s="35"/>
-      <c r="AO164" s="36"/>
-      <c r="AP164" s="35"/>
-      <c r="AQ164" s="35"/>
-      <c r="AR164" s="35"/>
-      <c r="AS164" s="35"/>
-      <c r="AT164" s="35"/>
-      <c r="AU164" s="36"/>
-      <c r="AV164" s="37"/>
+      <c r="B164" s="45"/>
+      <c r="C164" s="46"/>
+      <c r="D164" s="45"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="45"/>
+      <c r="G164" s="46"/>
+      <c r="H164" s="45"/>
+      <c r="I164" s="46"/>
+      <c r="J164" s="45"/>
+      <c r="K164" s="46"/>
+      <c r="L164" s="45"/>
+      <c r="M164" s="46"/>
+      <c r="N164" s="45"/>
+      <c r="O164" s="46"/>
+      <c r="P164" s="45"/>
+      <c r="Q164" s="46"/>
+      <c r="R164" s="45"/>
+      <c r="S164" s="46"/>
+      <c r="T164" s="45"/>
+      <c r="U164" s="46"/>
+      <c r="V164" s="45"/>
+      <c r="W164" s="46"/>
+      <c r="X164" s="45"/>
+      <c r="Y164" s="46"/>
+      <c r="Z164" s="45"/>
+      <c r="AA164" s="46"/>
+      <c r="AB164" s="45"/>
+      <c r="AC164" s="46"/>
+      <c r="AD164" s="45"/>
+      <c r="AE164" s="46"/>
+      <c r="AF164" s="45"/>
+      <c r="AG164" s="46"/>
+      <c r="AH164" s="45"/>
+      <c r="AI164" s="46"/>
+      <c r="AJ164" s="45"/>
+      <c r="AK164" s="46"/>
+      <c r="AL164" s="45"/>
+      <c r="AM164" s="46"/>
+      <c r="AN164" s="45"/>
+      <c r="AO164" s="46"/>
+      <c r="AP164" s="45"/>
+      <c r="AQ164" s="45"/>
+      <c r="AR164" s="45"/>
+      <c r="AS164" s="45"/>
+      <c r="AT164" s="45"/>
+      <c r="AU164" s="46"/>
+      <c r="AV164" s="47"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
@@ -21641,56 +21649,56 @@
       <c r="AX166" s="12"/>
     </row>
     <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="34" t="s">
+      <c r="A167" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="35"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="35"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="35"/>
-      <c r="G167" s="36"/>
-      <c r="H167" s="35"/>
-      <c r="I167" s="36"/>
-      <c r="J167" s="35"/>
-      <c r="K167" s="36"/>
-      <c r="L167" s="35"/>
-      <c r="M167" s="36"/>
-      <c r="N167" s="35"/>
-      <c r="O167" s="36"/>
-      <c r="P167" s="35"/>
-      <c r="Q167" s="36"/>
-      <c r="R167" s="35"/>
-      <c r="S167" s="36"/>
-      <c r="T167" s="35"/>
-      <c r="U167" s="36"/>
-      <c r="V167" s="35"/>
-      <c r="W167" s="36"/>
-      <c r="X167" s="35"/>
-      <c r="Y167" s="36"/>
-      <c r="Z167" s="35"/>
-      <c r="AA167" s="36"/>
-      <c r="AB167" s="35"/>
-      <c r="AC167" s="36"/>
-      <c r="AD167" s="35"/>
-      <c r="AE167" s="36"/>
-      <c r="AF167" s="35"/>
-      <c r="AG167" s="36"/>
-      <c r="AH167" s="35"/>
-      <c r="AI167" s="36"/>
-      <c r="AJ167" s="35"/>
-      <c r="AK167" s="36"/>
-      <c r="AL167" s="35"/>
-      <c r="AM167" s="36"/>
-      <c r="AN167" s="35"/>
-      <c r="AO167" s="36"/>
-      <c r="AP167" s="35"/>
-      <c r="AQ167" s="35"/>
-      <c r="AR167" s="35"/>
-      <c r="AS167" s="35"/>
-      <c r="AT167" s="35"/>
-      <c r="AU167" s="36"/>
-      <c r="AV167" s="37"/>
+      <c r="B167" s="45"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="45"/>
+      <c r="E167" s="46"/>
+      <c r="F167" s="45"/>
+      <c r="G167" s="46"/>
+      <c r="H167" s="45"/>
+      <c r="I167" s="46"/>
+      <c r="J167" s="45"/>
+      <c r="K167" s="46"/>
+      <c r="L167" s="45"/>
+      <c r="M167" s="46"/>
+      <c r="N167" s="45"/>
+      <c r="O167" s="46"/>
+      <c r="P167" s="45"/>
+      <c r="Q167" s="46"/>
+      <c r="R167" s="45"/>
+      <c r="S167" s="46"/>
+      <c r="T167" s="45"/>
+      <c r="U167" s="46"/>
+      <c r="V167" s="45"/>
+      <c r="W167" s="46"/>
+      <c r="X167" s="45"/>
+      <c r="Y167" s="46"/>
+      <c r="Z167" s="45"/>
+      <c r="AA167" s="46"/>
+      <c r="AB167" s="45"/>
+      <c r="AC167" s="46"/>
+      <c r="AD167" s="45"/>
+      <c r="AE167" s="46"/>
+      <c r="AF167" s="45"/>
+      <c r="AG167" s="46"/>
+      <c r="AH167" s="45"/>
+      <c r="AI167" s="46"/>
+      <c r="AJ167" s="45"/>
+      <c r="AK167" s="46"/>
+      <c r="AL167" s="45"/>
+      <c r="AM167" s="46"/>
+      <c r="AN167" s="45"/>
+      <c r="AO167" s="46"/>
+      <c r="AP167" s="45"/>
+      <c r="AQ167" s="45"/>
+      <c r="AR167" s="45"/>
+      <c r="AS167" s="45"/>
+      <c r="AT167" s="45"/>
+      <c r="AU167" s="46"/>
+      <c r="AV167" s="47"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
@@ -21883,56 +21891,56 @@
       <c r="AX169" s="12"/>
     </row>
     <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="34" t="s">
+      <c r="A170" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="B170" s="35"/>
-      <c r="C170" s="36"/>
-      <c r="D170" s="35"/>
-      <c r="E170" s="36"/>
-      <c r="F170" s="35"/>
-      <c r="G170" s="36"/>
-      <c r="H170" s="35"/>
-      <c r="I170" s="36"/>
-      <c r="J170" s="35"/>
-      <c r="K170" s="36"/>
-      <c r="L170" s="35"/>
-      <c r="M170" s="36"/>
-      <c r="N170" s="35"/>
-      <c r="O170" s="36"/>
-      <c r="P170" s="35"/>
-      <c r="Q170" s="36"/>
-      <c r="R170" s="35"/>
-      <c r="S170" s="36"/>
-      <c r="T170" s="35"/>
-      <c r="U170" s="36"/>
-      <c r="V170" s="35"/>
-      <c r="W170" s="36"/>
-      <c r="X170" s="35"/>
-      <c r="Y170" s="36"/>
-      <c r="Z170" s="35"/>
-      <c r="AA170" s="36"/>
-      <c r="AB170" s="35"/>
-      <c r="AC170" s="36"/>
-      <c r="AD170" s="35"/>
-      <c r="AE170" s="36"/>
-      <c r="AF170" s="35"/>
-      <c r="AG170" s="36"/>
-      <c r="AH170" s="35"/>
-      <c r="AI170" s="36"/>
-      <c r="AJ170" s="35"/>
-      <c r="AK170" s="36"/>
-      <c r="AL170" s="35"/>
-      <c r="AM170" s="36"/>
-      <c r="AN170" s="35"/>
-      <c r="AO170" s="36"/>
-      <c r="AP170" s="35"/>
-      <c r="AQ170" s="35"/>
-      <c r="AR170" s="35"/>
-      <c r="AS170" s="35"/>
-      <c r="AT170" s="35"/>
-      <c r="AU170" s="36"/>
-      <c r="AV170" s="37"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="46"/>
+      <c r="D170" s="45"/>
+      <c r="E170" s="46"/>
+      <c r="F170" s="45"/>
+      <c r="G170" s="46"/>
+      <c r="H170" s="45"/>
+      <c r="I170" s="46"/>
+      <c r="J170" s="45"/>
+      <c r="K170" s="46"/>
+      <c r="L170" s="45"/>
+      <c r="M170" s="46"/>
+      <c r="N170" s="45"/>
+      <c r="O170" s="46"/>
+      <c r="P170" s="45"/>
+      <c r="Q170" s="46"/>
+      <c r="R170" s="45"/>
+      <c r="S170" s="46"/>
+      <c r="T170" s="45"/>
+      <c r="U170" s="46"/>
+      <c r="V170" s="45"/>
+      <c r="W170" s="46"/>
+      <c r="X170" s="45"/>
+      <c r="Y170" s="46"/>
+      <c r="Z170" s="45"/>
+      <c r="AA170" s="46"/>
+      <c r="AB170" s="45"/>
+      <c r="AC170" s="46"/>
+      <c r="AD170" s="45"/>
+      <c r="AE170" s="46"/>
+      <c r="AF170" s="45"/>
+      <c r="AG170" s="46"/>
+      <c r="AH170" s="45"/>
+      <c r="AI170" s="46"/>
+      <c r="AJ170" s="45"/>
+      <c r="AK170" s="46"/>
+      <c r="AL170" s="45"/>
+      <c r="AM170" s="46"/>
+      <c r="AN170" s="45"/>
+      <c r="AO170" s="46"/>
+      <c r="AP170" s="45"/>
+      <c r="AQ170" s="45"/>
+      <c r="AR170" s="45"/>
+      <c r="AS170" s="45"/>
+      <c r="AT170" s="45"/>
+      <c r="AU170" s="46"/>
+      <c r="AV170" s="47"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
@@ -22125,56 +22133,56 @@
       <c r="AX172" s="12"/>
     </row>
     <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="34" t="s">
+      <c r="A173" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="35"/>
-      <c r="C173" s="36"/>
-      <c r="D173" s="35"/>
-      <c r="E173" s="36"/>
-      <c r="F173" s="35"/>
-      <c r="G173" s="36"/>
-      <c r="H173" s="35"/>
-      <c r="I173" s="36"/>
-      <c r="J173" s="35"/>
-      <c r="K173" s="36"/>
-      <c r="L173" s="35"/>
-      <c r="M173" s="36"/>
-      <c r="N173" s="35"/>
-      <c r="O173" s="36"/>
-      <c r="P173" s="35"/>
-      <c r="Q173" s="36"/>
-      <c r="R173" s="35"/>
-      <c r="S173" s="36"/>
-      <c r="T173" s="35"/>
-      <c r="U173" s="36"/>
-      <c r="V173" s="35"/>
-      <c r="W173" s="36"/>
-      <c r="X173" s="35"/>
-      <c r="Y173" s="36"/>
-      <c r="Z173" s="35"/>
-      <c r="AA173" s="36"/>
-      <c r="AB173" s="35"/>
-      <c r="AC173" s="36"/>
-      <c r="AD173" s="35"/>
-      <c r="AE173" s="36"/>
-      <c r="AF173" s="35"/>
-      <c r="AG173" s="36"/>
-      <c r="AH173" s="35"/>
-      <c r="AI173" s="36"/>
-      <c r="AJ173" s="35"/>
-      <c r="AK173" s="36"/>
-      <c r="AL173" s="35"/>
-      <c r="AM173" s="36"/>
-      <c r="AN173" s="35"/>
-      <c r="AO173" s="36"/>
-      <c r="AP173" s="35"/>
-      <c r="AQ173" s="35"/>
-      <c r="AR173" s="35"/>
-      <c r="AS173" s="35"/>
-      <c r="AT173" s="35"/>
-      <c r="AU173" s="36"/>
-      <c r="AV173" s="37"/>
+      <c r="B173" s="45"/>
+      <c r="C173" s="46"/>
+      <c r="D173" s="45"/>
+      <c r="E173" s="46"/>
+      <c r="F173" s="45"/>
+      <c r="G173" s="46"/>
+      <c r="H173" s="45"/>
+      <c r="I173" s="46"/>
+      <c r="J173" s="45"/>
+      <c r="K173" s="46"/>
+      <c r="L173" s="45"/>
+      <c r="M173" s="46"/>
+      <c r="N173" s="45"/>
+      <c r="O173" s="46"/>
+      <c r="P173" s="45"/>
+      <c r="Q173" s="46"/>
+      <c r="R173" s="45"/>
+      <c r="S173" s="46"/>
+      <c r="T173" s="45"/>
+      <c r="U173" s="46"/>
+      <c r="V173" s="45"/>
+      <c r="W173" s="46"/>
+      <c r="X173" s="45"/>
+      <c r="Y173" s="46"/>
+      <c r="Z173" s="45"/>
+      <c r="AA173" s="46"/>
+      <c r="AB173" s="45"/>
+      <c r="AC173" s="46"/>
+      <c r="AD173" s="45"/>
+      <c r="AE173" s="46"/>
+      <c r="AF173" s="45"/>
+      <c r="AG173" s="46"/>
+      <c r="AH173" s="45"/>
+      <c r="AI173" s="46"/>
+      <c r="AJ173" s="45"/>
+      <c r="AK173" s="46"/>
+      <c r="AL173" s="45"/>
+      <c r="AM173" s="46"/>
+      <c r="AN173" s="45"/>
+      <c r="AO173" s="46"/>
+      <c r="AP173" s="45"/>
+      <c r="AQ173" s="45"/>
+      <c r="AR173" s="45"/>
+      <c r="AS173" s="45"/>
+      <c r="AT173" s="45"/>
+      <c r="AU173" s="46"/>
+      <c r="AV173" s="47"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
@@ -22425,110 +22433,110 @@
       <c r="AX176" s="12"/>
     </row>
     <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="43" t="s">
+      <c r="A177" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="B177" s="48"/>
-      <c r="C177" s="49"/>
-      <c r="D177" s="48"/>
-      <c r="E177" s="49"/>
-      <c r="F177" s="48"/>
-      <c r="G177" s="49"/>
-      <c r="H177" s="48"/>
-      <c r="I177" s="49"/>
-      <c r="J177" s="48"/>
-      <c r="K177" s="49"/>
-      <c r="L177" s="48"/>
-      <c r="M177" s="49"/>
-      <c r="N177" s="48"/>
-      <c r="O177" s="49"/>
-      <c r="P177" s="48"/>
-      <c r="Q177" s="49"/>
-      <c r="R177" s="48"/>
-      <c r="S177" s="49"/>
-      <c r="T177" s="48"/>
-      <c r="U177" s="49"/>
-      <c r="V177" s="48"/>
-      <c r="W177" s="49"/>
-      <c r="X177" s="48"/>
-      <c r="Y177" s="49"/>
-      <c r="Z177" s="48"/>
-      <c r="AA177" s="49"/>
-      <c r="AB177" s="48"/>
-      <c r="AC177" s="49"/>
-      <c r="AD177" s="48"/>
-      <c r="AE177" s="49"/>
-      <c r="AF177" s="48"/>
-      <c r="AG177" s="49"/>
-      <c r="AH177" s="48"/>
-      <c r="AI177" s="49"/>
-      <c r="AJ177" s="48"/>
-      <c r="AK177" s="49"/>
-      <c r="AL177" s="48"/>
-      <c r="AM177" s="49"/>
-      <c r="AN177" s="48"/>
-      <c r="AO177" s="49"/>
-      <c r="AP177" s="48"/>
-      <c r="AQ177" s="48"/>
-      <c r="AR177" s="48"/>
-      <c r="AS177" s="48"/>
-      <c r="AT177" s="48"/>
-      <c r="AU177" s="49"/>
-      <c r="AV177" s="42"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="50"/>
+      <c r="D177" s="49"/>
+      <c r="E177" s="50"/>
+      <c r="F177" s="49"/>
+      <c r="G177" s="50"/>
+      <c r="H177" s="49"/>
+      <c r="I177" s="50"/>
+      <c r="J177" s="49"/>
+      <c r="K177" s="50"/>
+      <c r="L177" s="49"/>
+      <c r="M177" s="50"/>
+      <c r="N177" s="49"/>
+      <c r="O177" s="50"/>
+      <c r="P177" s="49"/>
+      <c r="Q177" s="50"/>
+      <c r="R177" s="49"/>
+      <c r="S177" s="50"/>
+      <c r="T177" s="49"/>
+      <c r="U177" s="50"/>
+      <c r="V177" s="49"/>
+      <c r="W177" s="50"/>
+      <c r="X177" s="49"/>
+      <c r="Y177" s="50"/>
+      <c r="Z177" s="49"/>
+      <c r="AA177" s="50"/>
+      <c r="AB177" s="49"/>
+      <c r="AC177" s="50"/>
+      <c r="AD177" s="49"/>
+      <c r="AE177" s="50"/>
+      <c r="AF177" s="49"/>
+      <c r="AG177" s="50"/>
+      <c r="AH177" s="49"/>
+      <c r="AI177" s="50"/>
+      <c r="AJ177" s="49"/>
+      <c r="AK177" s="50"/>
+      <c r="AL177" s="49"/>
+      <c r="AM177" s="50"/>
+      <c r="AN177" s="49"/>
+      <c r="AO177" s="50"/>
+      <c r="AP177" s="49"/>
+      <c r="AQ177" s="49"/>
+      <c r="AR177" s="49"/>
+      <c r="AS177" s="49"/>
+      <c r="AT177" s="49"/>
+      <c r="AU177" s="50"/>
+      <c r="AV177" s="43"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
     <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="34" t="s">
+      <c r="A178" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="35"/>
-      <c r="C178" s="36"/>
-      <c r="D178" s="35"/>
-      <c r="E178" s="36"/>
-      <c r="F178" s="35"/>
-      <c r="G178" s="36"/>
-      <c r="H178" s="35"/>
-      <c r="I178" s="36"/>
-      <c r="J178" s="35"/>
-      <c r="K178" s="36"/>
-      <c r="L178" s="35"/>
-      <c r="M178" s="36"/>
-      <c r="N178" s="35"/>
-      <c r="O178" s="36"/>
-      <c r="P178" s="35"/>
-      <c r="Q178" s="36"/>
-      <c r="R178" s="35"/>
-      <c r="S178" s="36"/>
-      <c r="T178" s="35"/>
-      <c r="U178" s="36"/>
-      <c r="V178" s="35"/>
-      <c r="W178" s="36"/>
-      <c r="X178" s="35"/>
-      <c r="Y178" s="36"/>
-      <c r="Z178" s="35"/>
-      <c r="AA178" s="36"/>
-      <c r="AB178" s="35"/>
-      <c r="AC178" s="36"/>
-      <c r="AD178" s="35"/>
-      <c r="AE178" s="36"/>
-      <c r="AF178" s="35"/>
-      <c r="AG178" s="36"/>
-      <c r="AH178" s="35"/>
-      <c r="AI178" s="36"/>
-      <c r="AJ178" s="35"/>
-      <c r="AK178" s="36"/>
-      <c r="AL178" s="35"/>
-      <c r="AM178" s="36"/>
-      <c r="AN178" s="35"/>
-      <c r="AO178" s="36"/>
-      <c r="AP178" s="35"/>
-      <c r="AQ178" s="35"/>
-      <c r="AR178" s="35"/>
-      <c r="AS178" s="35"/>
-      <c r="AT178" s="35"/>
-      <c r="AU178" s="36"/>
-      <c r="AV178" s="37"/>
+      <c r="B178" s="45"/>
+      <c r="C178" s="46"/>
+      <c r="D178" s="45"/>
+      <c r="E178" s="46"/>
+      <c r="F178" s="45"/>
+      <c r="G178" s="46"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="46"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="46"/>
+      <c r="L178" s="45"/>
+      <c r="M178" s="46"/>
+      <c r="N178" s="45"/>
+      <c r="O178" s="46"/>
+      <c r="P178" s="45"/>
+      <c r="Q178" s="46"/>
+      <c r="R178" s="45"/>
+      <c r="S178" s="46"/>
+      <c r="T178" s="45"/>
+      <c r="U178" s="46"/>
+      <c r="V178" s="45"/>
+      <c r="W178" s="46"/>
+      <c r="X178" s="45"/>
+      <c r="Y178" s="46"/>
+      <c r="Z178" s="45"/>
+      <c r="AA178" s="46"/>
+      <c r="AB178" s="45"/>
+      <c r="AC178" s="46"/>
+      <c r="AD178" s="45"/>
+      <c r="AE178" s="46"/>
+      <c r="AF178" s="45"/>
+      <c r="AG178" s="46"/>
+      <c r="AH178" s="45"/>
+      <c r="AI178" s="46"/>
+      <c r="AJ178" s="45"/>
+      <c r="AK178" s="46"/>
+      <c r="AL178" s="45"/>
+      <c r="AM178" s="46"/>
+      <c r="AN178" s="45"/>
+      <c r="AO178" s="46"/>
+      <c r="AP178" s="45"/>
+      <c r="AQ178" s="45"/>
+      <c r="AR178" s="45"/>
+      <c r="AS178" s="45"/>
+      <c r="AT178" s="45"/>
+      <c r="AU178" s="46"/>
+      <c r="AV178" s="47"/>
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
@@ -22721,56 +22729,56 @@
       <c r="AX180" s="12"/>
     </row>
     <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="34" t="s">
+      <c r="A181" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="B181" s="35"/>
-      <c r="C181" s="36"/>
-      <c r="D181" s="35"/>
-      <c r="E181" s="36"/>
-      <c r="F181" s="35"/>
-      <c r="G181" s="36"/>
-      <c r="H181" s="35"/>
-      <c r="I181" s="36"/>
-      <c r="J181" s="35"/>
-      <c r="K181" s="36"/>
-      <c r="L181" s="35"/>
-      <c r="M181" s="36"/>
-      <c r="N181" s="35"/>
-      <c r="O181" s="36"/>
-      <c r="P181" s="35"/>
-      <c r="Q181" s="36"/>
-      <c r="R181" s="35"/>
-      <c r="S181" s="36"/>
-      <c r="T181" s="35"/>
-      <c r="U181" s="36"/>
-      <c r="V181" s="35"/>
-      <c r="W181" s="36"/>
-      <c r="X181" s="35"/>
-      <c r="Y181" s="36"/>
-      <c r="Z181" s="35"/>
-      <c r="AA181" s="36"/>
-      <c r="AB181" s="35"/>
-      <c r="AC181" s="36"/>
-      <c r="AD181" s="35"/>
-      <c r="AE181" s="36"/>
-      <c r="AF181" s="35"/>
-      <c r="AG181" s="36"/>
-      <c r="AH181" s="35"/>
-      <c r="AI181" s="36"/>
-      <c r="AJ181" s="35"/>
-      <c r="AK181" s="36"/>
-      <c r="AL181" s="35"/>
-      <c r="AM181" s="36"/>
-      <c r="AN181" s="35"/>
-      <c r="AO181" s="36"/>
-      <c r="AP181" s="35"/>
-      <c r="AQ181" s="35"/>
-      <c r="AR181" s="35"/>
-      <c r="AS181" s="35"/>
-      <c r="AT181" s="35"/>
-      <c r="AU181" s="36"/>
-      <c r="AV181" s="37"/>
+      <c r="B181" s="45"/>
+      <c r="C181" s="46"/>
+      <c r="D181" s="45"/>
+      <c r="E181" s="46"/>
+      <c r="F181" s="45"/>
+      <c r="G181" s="46"/>
+      <c r="H181" s="45"/>
+      <c r="I181" s="46"/>
+      <c r="J181" s="45"/>
+      <c r="K181" s="46"/>
+      <c r="L181" s="45"/>
+      <c r="M181" s="46"/>
+      <c r="N181" s="45"/>
+      <c r="O181" s="46"/>
+      <c r="P181" s="45"/>
+      <c r="Q181" s="46"/>
+      <c r="R181" s="45"/>
+      <c r="S181" s="46"/>
+      <c r="T181" s="45"/>
+      <c r="U181" s="46"/>
+      <c r="V181" s="45"/>
+      <c r="W181" s="46"/>
+      <c r="X181" s="45"/>
+      <c r="Y181" s="46"/>
+      <c r="Z181" s="45"/>
+      <c r="AA181" s="46"/>
+      <c r="AB181" s="45"/>
+      <c r="AC181" s="46"/>
+      <c r="AD181" s="45"/>
+      <c r="AE181" s="46"/>
+      <c r="AF181" s="45"/>
+      <c r="AG181" s="46"/>
+      <c r="AH181" s="45"/>
+      <c r="AI181" s="46"/>
+      <c r="AJ181" s="45"/>
+      <c r="AK181" s="46"/>
+      <c r="AL181" s="45"/>
+      <c r="AM181" s="46"/>
+      <c r="AN181" s="45"/>
+      <c r="AO181" s="46"/>
+      <c r="AP181" s="45"/>
+      <c r="AQ181" s="45"/>
+      <c r="AR181" s="45"/>
+      <c r="AS181" s="45"/>
+      <c r="AT181" s="45"/>
+      <c r="AU181" s="46"/>
+      <c r="AV181" s="47"/>
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
@@ -23021,110 +23029,110 @@
       <c r="AX184" s="12"/>
     </row>
     <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="43" t="s">
+      <c r="A185" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="B185" s="48"/>
-      <c r="C185" s="49"/>
-      <c r="D185" s="48"/>
-      <c r="E185" s="49"/>
-      <c r="F185" s="48"/>
-      <c r="G185" s="49"/>
-      <c r="H185" s="48"/>
-      <c r="I185" s="49"/>
-      <c r="J185" s="48"/>
-      <c r="K185" s="49"/>
-      <c r="L185" s="48"/>
-      <c r="M185" s="49"/>
-      <c r="N185" s="48"/>
-      <c r="O185" s="49"/>
-      <c r="P185" s="48"/>
-      <c r="Q185" s="49"/>
-      <c r="R185" s="48"/>
-      <c r="S185" s="49"/>
-      <c r="T185" s="48"/>
-      <c r="U185" s="49"/>
-      <c r="V185" s="48"/>
-      <c r="W185" s="49"/>
-      <c r="X185" s="48"/>
-      <c r="Y185" s="49"/>
-      <c r="Z185" s="48"/>
-      <c r="AA185" s="49"/>
-      <c r="AB185" s="48"/>
-      <c r="AC185" s="49"/>
-      <c r="AD185" s="48"/>
-      <c r="AE185" s="49"/>
-      <c r="AF185" s="48"/>
-      <c r="AG185" s="49"/>
-      <c r="AH185" s="48"/>
-      <c r="AI185" s="49"/>
-      <c r="AJ185" s="48"/>
-      <c r="AK185" s="49"/>
-      <c r="AL185" s="48"/>
-      <c r="AM185" s="49"/>
-      <c r="AN185" s="48"/>
-      <c r="AO185" s="49"/>
-      <c r="AP185" s="48"/>
-      <c r="AQ185" s="48"/>
-      <c r="AR185" s="48"/>
-      <c r="AS185" s="48"/>
-      <c r="AT185" s="48"/>
-      <c r="AU185" s="49"/>
-      <c r="AV185" s="42"/>
+      <c r="B185" s="49"/>
+      <c r="C185" s="50"/>
+      <c r="D185" s="49"/>
+      <c r="E185" s="50"/>
+      <c r="F185" s="49"/>
+      <c r="G185" s="50"/>
+      <c r="H185" s="49"/>
+      <c r="I185" s="50"/>
+      <c r="J185" s="49"/>
+      <c r="K185" s="50"/>
+      <c r="L185" s="49"/>
+      <c r="M185" s="50"/>
+      <c r="N185" s="49"/>
+      <c r="O185" s="50"/>
+      <c r="P185" s="49"/>
+      <c r="Q185" s="50"/>
+      <c r="R185" s="49"/>
+      <c r="S185" s="50"/>
+      <c r="T185" s="49"/>
+      <c r="U185" s="50"/>
+      <c r="V185" s="49"/>
+      <c r="W185" s="50"/>
+      <c r="X185" s="49"/>
+      <c r="Y185" s="50"/>
+      <c r="Z185" s="49"/>
+      <c r="AA185" s="50"/>
+      <c r="AB185" s="49"/>
+      <c r="AC185" s="50"/>
+      <c r="AD185" s="49"/>
+      <c r="AE185" s="50"/>
+      <c r="AF185" s="49"/>
+      <c r="AG185" s="50"/>
+      <c r="AH185" s="49"/>
+      <c r="AI185" s="50"/>
+      <c r="AJ185" s="49"/>
+      <c r="AK185" s="50"/>
+      <c r="AL185" s="49"/>
+      <c r="AM185" s="50"/>
+      <c r="AN185" s="49"/>
+      <c r="AO185" s="50"/>
+      <c r="AP185" s="49"/>
+      <c r="AQ185" s="49"/>
+      <c r="AR185" s="49"/>
+      <c r="AS185" s="49"/>
+      <c r="AT185" s="49"/>
+      <c r="AU185" s="50"/>
+      <c r="AV185" s="43"/>
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
     <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="34" t="s">
+      <c r="A186" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="B186" s="35"/>
-      <c r="C186" s="36"/>
-      <c r="D186" s="35"/>
-      <c r="E186" s="36"/>
-      <c r="F186" s="35"/>
-      <c r="G186" s="36"/>
-      <c r="H186" s="35"/>
-      <c r="I186" s="36"/>
-      <c r="J186" s="35"/>
-      <c r="K186" s="36"/>
-      <c r="L186" s="35"/>
-      <c r="M186" s="36"/>
-      <c r="N186" s="35"/>
-      <c r="O186" s="36"/>
-      <c r="P186" s="35"/>
-      <c r="Q186" s="36"/>
-      <c r="R186" s="35"/>
-      <c r="S186" s="36"/>
-      <c r="T186" s="35"/>
-      <c r="U186" s="36"/>
-      <c r="V186" s="35"/>
-      <c r="W186" s="36"/>
-      <c r="X186" s="35"/>
-      <c r="Y186" s="36"/>
-      <c r="Z186" s="35"/>
-      <c r="AA186" s="36"/>
-      <c r="AB186" s="35"/>
-      <c r="AC186" s="36"/>
-      <c r="AD186" s="35"/>
-      <c r="AE186" s="36"/>
-      <c r="AF186" s="35"/>
-      <c r="AG186" s="36"/>
-      <c r="AH186" s="35"/>
-      <c r="AI186" s="36"/>
-      <c r="AJ186" s="35"/>
-      <c r="AK186" s="36"/>
-      <c r="AL186" s="35"/>
-      <c r="AM186" s="36"/>
-      <c r="AN186" s="35"/>
-      <c r="AO186" s="36"/>
-      <c r="AP186" s="35"/>
-      <c r="AQ186" s="35"/>
-      <c r="AR186" s="35"/>
-      <c r="AS186" s="35"/>
-      <c r="AT186" s="35"/>
-      <c r="AU186" s="36"/>
-      <c r="AV186" s="37"/>
+      <c r="B186" s="45"/>
+      <c r="C186" s="46"/>
+      <c r="D186" s="45"/>
+      <c r="E186" s="46"/>
+      <c r="F186" s="45"/>
+      <c r="G186" s="46"/>
+      <c r="H186" s="45"/>
+      <c r="I186" s="46"/>
+      <c r="J186" s="45"/>
+      <c r="K186" s="46"/>
+      <c r="L186" s="45"/>
+      <c r="M186" s="46"/>
+      <c r="N186" s="45"/>
+      <c r="O186" s="46"/>
+      <c r="P186" s="45"/>
+      <c r="Q186" s="46"/>
+      <c r="R186" s="45"/>
+      <c r="S186" s="46"/>
+      <c r="T186" s="45"/>
+      <c r="U186" s="46"/>
+      <c r="V186" s="45"/>
+      <c r="W186" s="46"/>
+      <c r="X186" s="45"/>
+      <c r="Y186" s="46"/>
+      <c r="Z186" s="45"/>
+      <c r="AA186" s="46"/>
+      <c r="AB186" s="45"/>
+      <c r="AC186" s="46"/>
+      <c r="AD186" s="45"/>
+      <c r="AE186" s="46"/>
+      <c r="AF186" s="45"/>
+      <c r="AG186" s="46"/>
+      <c r="AH186" s="45"/>
+      <c r="AI186" s="46"/>
+      <c r="AJ186" s="45"/>
+      <c r="AK186" s="46"/>
+      <c r="AL186" s="45"/>
+      <c r="AM186" s="46"/>
+      <c r="AN186" s="45"/>
+      <c r="AO186" s="46"/>
+      <c r="AP186" s="45"/>
+      <c r="AQ186" s="45"/>
+      <c r="AR186" s="45"/>
+      <c r="AS186" s="45"/>
+      <c r="AT186" s="45"/>
+      <c r="AU186" s="46"/>
+      <c r="AV186" s="47"/>
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
@@ -23375,110 +23383,110 @@
       <c r="AX189" s="12"/>
     </row>
     <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="43" t="s">
+      <c r="A190" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="B190" s="48"/>
-      <c r="C190" s="49"/>
-      <c r="D190" s="48"/>
-      <c r="E190" s="49"/>
-      <c r="F190" s="48"/>
-      <c r="G190" s="49"/>
-      <c r="H190" s="48"/>
-      <c r="I190" s="49"/>
-      <c r="J190" s="48"/>
-      <c r="K190" s="49"/>
-      <c r="L190" s="48"/>
-      <c r="M190" s="49"/>
-      <c r="N190" s="48"/>
-      <c r="O190" s="49"/>
-      <c r="P190" s="48"/>
-      <c r="Q190" s="49"/>
-      <c r="R190" s="48"/>
-      <c r="S190" s="49"/>
-      <c r="T190" s="48"/>
-      <c r="U190" s="49"/>
-      <c r="V190" s="48"/>
-      <c r="W190" s="49"/>
-      <c r="X190" s="48"/>
-      <c r="Y190" s="49"/>
-      <c r="Z190" s="48"/>
-      <c r="AA190" s="49"/>
-      <c r="AB190" s="48"/>
-      <c r="AC190" s="49"/>
-      <c r="AD190" s="48"/>
-      <c r="AE190" s="49"/>
-      <c r="AF190" s="48"/>
-      <c r="AG190" s="49"/>
-      <c r="AH190" s="48"/>
-      <c r="AI190" s="49"/>
-      <c r="AJ190" s="48"/>
-      <c r="AK190" s="49"/>
-      <c r="AL190" s="48"/>
-      <c r="AM190" s="49"/>
-      <c r="AN190" s="48"/>
-      <c r="AO190" s="49"/>
-      <c r="AP190" s="48"/>
-      <c r="AQ190" s="48"/>
-      <c r="AR190" s="48"/>
-      <c r="AS190" s="48"/>
-      <c r="AT190" s="48"/>
-      <c r="AU190" s="49"/>
-      <c r="AV190" s="42"/>
+      <c r="B190" s="49"/>
+      <c r="C190" s="50"/>
+      <c r="D190" s="49"/>
+      <c r="E190" s="50"/>
+      <c r="F190" s="49"/>
+      <c r="G190" s="50"/>
+      <c r="H190" s="49"/>
+      <c r="I190" s="50"/>
+      <c r="J190" s="49"/>
+      <c r="K190" s="50"/>
+      <c r="L190" s="49"/>
+      <c r="M190" s="50"/>
+      <c r="N190" s="49"/>
+      <c r="O190" s="50"/>
+      <c r="P190" s="49"/>
+      <c r="Q190" s="50"/>
+      <c r="R190" s="49"/>
+      <c r="S190" s="50"/>
+      <c r="T190" s="49"/>
+      <c r="U190" s="50"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="50"/>
+      <c r="X190" s="49"/>
+      <c r="Y190" s="50"/>
+      <c r="Z190" s="49"/>
+      <c r="AA190" s="50"/>
+      <c r="AB190" s="49"/>
+      <c r="AC190" s="50"/>
+      <c r="AD190" s="49"/>
+      <c r="AE190" s="50"/>
+      <c r="AF190" s="49"/>
+      <c r="AG190" s="50"/>
+      <c r="AH190" s="49"/>
+      <c r="AI190" s="50"/>
+      <c r="AJ190" s="49"/>
+      <c r="AK190" s="50"/>
+      <c r="AL190" s="49"/>
+      <c r="AM190" s="50"/>
+      <c r="AN190" s="49"/>
+      <c r="AO190" s="50"/>
+      <c r="AP190" s="49"/>
+      <c r="AQ190" s="49"/>
+      <c r="AR190" s="49"/>
+      <c r="AS190" s="49"/>
+      <c r="AT190" s="49"/>
+      <c r="AU190" s="50"/>
+      <c r="AV190" s="43"/>
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
     <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="34" t="s">
+      <c r="A191" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B191" s="35"/>
-      <c r="C191" s="36"/>
-      <c r="D191" s="35"/>
-      <c r="E191" s="36"/>
-      <c r="F191" s="35"/>
-      <c r="G191" s="36"/>
-      <c r="H191" s="35"/>
-      <c r="I191" s="36"/>
-      <c r="J191" s="35"/>
-      <c r="K191" s="36"/>
-      <c r="L191" s="35"/>
-      <c r="M191" s="36"/>
-      <c r="N191" s="35"/>
-      <c r="O191" s="36"/>
-      <c r="P191" s="35"/>
-      <c r="Q191" s="36"/>
-      <c r="R191" s="35"/>
-      <c r="S191" s="36"/>
-      <c r="T191" s="35"/>
-      <c r="U191" s="36"/>
-      <c r="V191" s="35"/>
-      <c r="W191" s="36"/>
-      <c r="X191" s="35"/>
-      <c r="Y191" s="36"/>
-      <c r="Z191" s="35"/>
-      <c r="AA191" s="36"/>
-      <c r="AB191" s="35"/>
-      <c r="AC191" s="36"/>
-      <c r="AD191" s="35"/>
-      <c r="AE191" s="36"/>
-      <c r="AF191" s="35"/>
-      <c r="AG191" s="36"/>
-      <c r="AH191" s="35"/>
-      <c r="AI191" s="36"/>
-      <c r="AJ191" s="35"/>
-      <c r="AK191" s="36"/>
-      <c r="AL191" s="35"/>
-      <c r="AM191" s="36"/>
-      <c r="AN191" s="35"/>
-      <c r="AO191" s="36"/>
-      <c r="AP191" s="35"/>
-      <c r="AQ191" s="35"/>
-      <c r="AR191" s="35"/>
-      <c r="AS191" s="35"/>
-      <c r="AT191" s="35"/>
-      <c r="AU191" s="36"/>
-      <c r="AV191" s="37"/>
+      <c r="B191" s="45"/>
+      <c r="C191" s="46"/>
+      <c r="D191" s="45"/>
+      <c r="E191" s="46"/>
+      <c r="F191" s="45"/>
+      <c r="G191" s="46"/>
+      <c r="H191" s="45"/>
+      <c r="I191" s="46"/>
+      <c r="J191" s="45"/>
+      <c r="K191" s="46"/>
+      <c r="L191" s="45"/>
+      <c r="M191" s="46"/>
+      <c r="N191" s="45"/>
+      <c r="O191" s="46"/>
+      <c r="P191" s="45"/>
+      <c r="Q191" s="46"/>
+      <c r="R191" s="45"/>
+      <c r="S191" s="46"/>
+      <c r="T191" s="45"/>
+      <c r="U191" s="46"/>
+      <c r="V191" s="45"/>
+      <c r="W191" s="46"/>
+      <c r="X191" s="45"/>
+      <c r="Y191" s="46"/>
+      <c r="Z191" s="45"/>
+      <c r="AA191" s="46"/>
+      <c r="AB191" s="45"/>
+      <c r="AC191" s="46"/>
+      <c r="AD191" s="45"/>
+      <c r="AE191" s="46"/>
+      <c r="AF191" s="45"/>
+      <c r="AG191" s="46"/>
+      <c r="AH191" s="45"/>
+      <c r="AI191" s="46"/>
+      <c r="AJ191" s="45"/>
+      <c r="AK191" s="46"/>
+      <c r="AL191" s="45"/>
+      <c r="AM191" s="46"/>
+      <c r="AN191" s="45"/>
+      <c r="AO191" s="46"/>
+      <c r="AP191" s="45"/>
+      <c r="AQ191" s="45"/>
+      <c r="AR191" s="45"/>
+      <c r="AS191" s="45"/>
+      <c r="AT191" s="45"/>
+      <c r="AU191" s="46"/>
+      <c r="AV191" s="47"/>
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
@@ -23730,6 +23738,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23746,60 +23808,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23864,253 +23872,253 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="55" t="str">
+      <c r="D1" s="59" t="str">
         <f>Wedstrijden_beheer!E1</f>
         <v>Roland</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="54" t="str">
+      <c r="E1" s="60"/>
+      <c r="F1" s="61" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="54" t="str">
+      <c r="G1" s="43"/>
+      <c r="H1" s="61" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="54" t="str">
+      <c r="I1" s="43"/>
+      <c r="J1" s="61" t="str">
         <f>Wedstrijden_beheer!K1</f>
         <v>Karsten</v>
       </c>
-      <c r="K1" s="42"/>
-      <c r="L1" s="54" t="str">
+      <c r="K1" s="43"/>
+      <c r="L1" s="61" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="M1" s="42"/>
-      <c r="N1" s="54" t="str">
+      <c r="M1" s="43"/>
+      <c r="N1" s="61" t="str">
         <f>Wedstrijden_beheer!O1</f>
         <v>Maik</v>
       </c>
-      <c r="O1" s="42"/>
-      <c r="P1" s="54" t="str">
+      <c r="O1" s="43"/>
+      <c r="P1" s="61" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="54" t="str">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="61" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="S1" s="42"/>
-      <c r="T1" s="54" t="str">
+      <c r="S1" s="43"/>
+      <c r="T1" s="61" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="U1" s="42"/>
-      <c r="V1" s="54" t="str">
+      <c r="U1" s="43"/>
+      <c r="V1" s="61" t="str">
         <f>Wedstrijden_beheer!W1</f>
         <v>Jos</v>
       </c>
-      <c r="W1" s="42"/>
-      <c r="X1" s="54" t="str">
+      <c r="W1" s="43"/>
+      <c r="X1" s="61" t="str">
         <f>Wedstrijden_beheer!Y1</f>
         <v>Lesley</v>
       </c>
-      <c r="Y1" s="42"/>
-      <c r="Z1" s="54" t="str">
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="61" t="str">
         <f>Wedstrijden_beheer!AA1</f>
         <v>Ivo</v>
       </c>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="54" t="str">
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="61" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="AC1" s="42"/>
-      <c r="AD1" s="54" t="str">
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="61" t="str">
         <f>Wedstrijden_beheer!AE1</f>
         <v>Jeroen</v>
       </c>
-      <c r="AE1" s="42"/>
-      <c r="AF1" s="54" t="str">
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="61" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="AG1" s="42"/>
-      <c r="AH1" s="54" t="str">
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="61" t="str">
         <f>Wedstrijden_beheer!AI1</f>
         <v>Tim</v>
       </c>
-      <c r="AI1" s="42"/>
-      <c r="AJ1" s="54" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="42"/>
-      <c r="AL1" s="54" t="s">
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="42"/>
-      <c r="AN1" s="54" t="str">
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="61" t="str">
         <f>Wedstrijden_beheer!AO1</f>
         <v>Patrick</v>
       </c>
-      <c r="AO1" s="42"/>
-      <c r="AP1" s="54" t="str">
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="61" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="AQ1" s="42"/>
-      <c r="AR1" s="41" t="str">
+      <c r="AQ1" s="43"/>
+      <c r="AR1" s="42" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="41" t="str">
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="42" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="53"/>
+      <c r="AU1" s="51"/>
     </row>
     <row r="2" spans="1:47" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="57" t="s">
+      <c r="J2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="M2" s="57" t="s">
+      <c r="M2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="59" t="s">
+      <c r="N2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="O2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="59" t="s">
+      <c r="P2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="Q2" s="57" t="s">
+      <c r="Q2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="59" t="s">
+      <c r="R2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="57" t="s">
+      <c r="S2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="T2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="U2" s="57" t="s">
+      <c r="U2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="59" t="s">
+      <c r="V2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="W2" s="57" t="s">
+      <c r="W2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="59" t="s">
+      <c r="X2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="Y2" s="57" t="s">
+      <c r="Y2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="Z2" s="59" t="s">
+      <c r="Z2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AA2" s="57" t="s">
+      <c r="AA2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="59" t="s">
+      <c r="AB2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AC2" s="57" t="s">
+      <c r="AC2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AD2" s="59" t="s">
+      <c r="AD2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AE2" s="57" t="s">
+      <c r="AE2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AF2" s="59" t="s">
+      <c r="AF2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AG2" s="57" t="s">
+      <c r="AG2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AH2" s="59" t="s">
+      <c r="AH2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AI2" s="57" t="s">
+      <c r="AI2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AJ2" s="59" t="s">
+      <c r="AJ2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AK2" s="57" t="s">
+      <c r="AK2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AL2" s="60" t="s">
+      <c r="AL2" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="AM2" s="57" t="s">
+      <c r="AM2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AN2" s="59" t="s">
+      <c r="AN2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AO2" s="57" t="s">
+      <c r="AO2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AP2" s="57" t="s">
+      <c r="AP2" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="AQ2" s="57" t="s">
+      <c r="AQ2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AR2" s="59" t="s">
+      <c r="AR2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AS2" s="57" t="s">
+      <c r="AS2" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="AT2" s="59" t="s">
+      <c r="AT2" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="AU2" s="57" t="s">
+      <c r="AU2" s="34" t="s">
         <v>28</v>
       </c>
     </row>
@@ -26515,6 +26523,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26526,17 +26545,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26567,19 +26575,19 @@
       <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="38" t="s">
         <v>289</v>
       </c>
     </row>
@@ -26594,7 +26602,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26602,7 +26610,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>178</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26611,20 +26619,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>169</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>187</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>169</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26633,20 +26641,20 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>168</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>185</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26655,20 +26663,20 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C6" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>164</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>184</v>
       </c>
       <c r="D6" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26677,20 +26685,20 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>162</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>183</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>162</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26704,7 +26712,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
@@ -26712,7 +26720,7 @@
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26721,20 +26729,20 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>161</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>177</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>161</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26743,20 +26751,20 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>159</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>175</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26770,7 +26778,7 @@
       </c>
       <c r="C11" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="D11" s="11">
         <f>Bonus_beheer!E17</f>
@@ -26778,7 +26786,7 @@
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26792,7 +26800,7 @@
       </c>
       <c r="C12" s="11">
         <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="D12" s="11">
         <f>Bonus_beheer!G17</f>
@@ -26800,7 +26808,7 @@
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>156</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26809,42 +26817,42 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!AQ1</f>
-        <v>Jeno</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>152</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>168</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!AU18</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AU1</f>
-        <v>Raymond</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>152</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>167</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AU17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26853,20 +26861,20 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!AM1</f>
+        <v>Kristel</v>
       </c>
       <c r="C15" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>150</v>
+        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
+        <v>165</v>
       </c>
       <c r="D15" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!AM17</f>
         <v>0</v>
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26875,42 +26883,42 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!AQ1</f>
+        <v>Jeno</v>
       </c>
       <c r="C16" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>148</v>
+        <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
+        <v>161</v>
       </c>
       <c r="D16" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!AU18</f>
         <v>0</v>
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>148</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f>Wedstrijden_beheer!M1</f>
-        <v>Bas</v>
+        <f>Wedstrijden_beheer!AU1</f>
+        <v>Raymond</v>
       </c>
       <c r="C17" s="11">
-        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>143</v>
+        <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
+        <v>161</v>
       </c>
       <c r="D17" s="11">
-        <f>Bonus_beheer!M17</f>
+        <f>Bonus_beheer!AU17</f>
         <v>0</v>
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>143</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26919,20 +26927,20 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f>Wedstrijden_beheer!AC1</f>
-        <v>Ron</v>
+        <f>Wedstrijden_beheer!M1</f>
+        <v>Bas</v>
       </c>
       <c r="C18" s="11">
-        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>135</v>
+        <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
+        <v>159</v>
       </c>
       <c r="D18" s="11">
-        <f>Bonus_beheer!AC17</f>
+        <f>Bonus_beheer!M17</f>
         <v>0</v>
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26941,20 +26949,20 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f>Wedstrijden_beheer!AM1</f>
-        <v>Kristel</v>
+        <f>Wedstrijden_beheer!AC1</f>
+        <v>Ron</v>
       </c>
       <c r="C19" s="11">
-        <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>134</v>
+        <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
+        <v>153</v>
       </c>
       <c r="D19" s="11">
-        <f>Bonus_beheer!AM17</f>
+        <f>Bonus_beheer!AC17</f>
         <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>134</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26963,20 +26971,20 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!K1</f>
+        <v>Karsten</v>
       </c>
       <c r="C20" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>128</v>
+        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
+        <v>142</v>
       </c>
       <c r="D20" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!K17</f>
         <v>0</v>
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -26985,20 +26993,20 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!K1</f>
-        <v>Karsten</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>124</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>137</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!K17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -27012,7 +27020,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -27020,7 +27028,7 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -27034,7 +27042,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -27042,7 +27050,7 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -27056,7 +27064,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -27064,7 +27072,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>116</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -27098,10 +27106,10 @@
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="38" t="s">
         <v>292</v>
       </c>
     </row>
@@ -27227,13 +27235,13 @@
       <c r="AR1" s="3"/>
     </row>
     <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="38" t="s">
         <v>307</v>
       </c>
     </row>
@@ -27436,12 +27444,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27640,20 +27650,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27678,18 +27695,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1590" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8BCA05-574A-4194-A70C-8FF320A6B3A5}"/>
+  <xr:revisionPtr revIDLastSave="1595" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66CB4532-7751-423F-B18E-6573E75C12C5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1735,60 +1735,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.5546875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
-    <col min="4" max="4" width="20.5546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" style="21" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" style="21" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" customWidth="1"/>
-    <col min="11" max="11" width="12.5546875" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" customWidth="1"/>
-    <col min="13" max="13" width="12.5546875" style="21" customWidth="1"/>
-    <col min="14" max="14" width="8.5546875" customWidth="1"/>
-    <col min="15" max="15" width="12.5546875" style="21" customWidth="1"/>
-    <col min="16" max="16" width="8.5546875" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" style="21" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
-    <col min="19" max="19" width="12.5546875" style="21" customWidth="1"/>
-    <col min="20" max="20" width="8.5546875" customWidth="1"/>
-    <col min="21" max="21" width="12.5546875" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" customWidth="1"/>
-    <col min="23" max="23" width="12.5546875" style="21" customWidth="1"/>
-    <col min="24" max="24" width="8.5546875" customWidth="1"/>
-    <col min="25" max="25" width="12.5546875" style="21" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" customWidth="1"/>
-    <col min="27" max="27" width="12.5546875" style="21" customWidth="1"/>
-    <col min="28" max="28" width="8.5546875" customWidth="1"/>
-    <col min="29" max="29" width="12.5546875" style="21" customWidth="1"/>
-    <col min="30" max="30" width="8.5546875" customWidth="1"/>
-    <col min="31" max="31" width="12.5546875" style="21" customWidth="1"/>
-    <col min="32" max="32" width="8.5546875" customWidth="1"/>
-    <col min="33" max="33" width="12.5546875" style="21" customWidth="1"/>
-    <col min="34" max="34" width="8.5546875" customWidth="1"/>
-    <col min="35" max="35" width="12.5546875" style="21" customWidth="1"/>
-    <col min="36" max="36" width="8.5546875" customWidth="1"/>
-    <col min="37" max="37" width="12.5546875" style="21" customWidth="1"/>
-    <col min="38" max="38" width="8.5546875" customWidth="1"/>
-    <col min="39" max="39" width="12.5546875" style="21" customWidth="1"/>
-    <col min="40" max="40" width="8.5546875" customWidth="1"/>
-    <col min="41" max="41" width="15.5546875" style="21" customWidth="1"/>
-    <col min="42" max="42" width="8.5546875" customWidth="1"/>
-    <col min="43" max="43" width="15.5546875" style="21" customWidth="1"/>
-    <col min="44" max="44" width="8.5546875" customWidth="1"/>
-    <col min="45" max="45" width="15.6640625" style="21" customWidth="1"/>
-    <col min="46" max="46" width="8.5546875" customWidth="1"/>
-    <col min="47" max="47" width="15.5546875" style="21" customWidth="1"/>
-    <col min="48" max="48" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="21" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="21" customWidth="1"/>
+    <col min="14" max="14" width="8.5703125" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="21" customWidth="1"/>
+    <col min="16" max="16" width="8.5703125" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="21" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="21" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="21" customWidth="1"/>
+    <col min="24" max="24" width="8.5703125" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="21" customWidth="1"/>
+    <col min="26" max="26" width="8.5703125" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="21" customWidth="1"/>
+    <col min="28" max="28" width="8.5703125" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="21" customWidth="1"/>
+    <col min="30" max="30" width="8.5703125" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="21" customWidth="1"/>
+    <col min="32" max="32" width="8.5703125" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="21" customWidth="1"/>
+    <col min="34" max="34" width="8.5703125" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="21" customWidth="1"/>
+    <col min="36" max="36" width="8.5703125" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="21" customWidth="1"/>
+    <col min="38" max="38" width="8.5703125" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="21" customWidth="1"/>
+    <col min="40" max="40" width="8.5703125" customWidth="1"/>
+    <col min="41" max="41" width="15.5703125" style="21" customWidth="1"/>
+    <col min="42" max="42" width="8.5703125" customWidth="1"/>
+    <col min="43" max="43" width="15.5703125" style="21" customWidth="1"/>
+    <col min="44" max="44" width="8.5703125" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" style="21" customWidth="1"/>
+    <col min="46" max="46" width="8.5703125" customWidth="1"/>
+    <col min="47" max="47" width="15.5703125" style="21" customWidth="1"/>
+    <col min="48" max="48" width="8.5703125" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="53"/>
       <c r="B2" s="56"/>
       <c r="C2" s="53"/>
@@ -2040,7 +2040,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="48" t="s">
         <v>29</v>
       </c>
@@ -2094,7 +2094,7 @@
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39" t="s">
         <v>30</v>
       </c>
@@ -2148,7 +2148,7 @@
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12"/>
       <c r="B6" s="17"/>
       <c r="C6" s="13"/>
@@ -2382,7 +2382,7 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
         <v>40</v>
       </c>
@@ -2436,7 +2436,7 @@
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12"/>
       <c r="B10" s="17"/>
       <c r="C10" s="13"/>
@@ -2846,7 +2846,7 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
         <v>51</v>
       </c>
@@ -2900,7 +2900,7 @@
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12"/>
       <c r="B14" s="17"/>
       <c r="C14" s="13"/>
@@ -3310,7 +3310,7 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
         <v>58</v>
       </c>
@@ -3364,7 +3364,7 @@
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="17"/>
       <c r="C21" s="13"/>
@@ -4302,7 +4302,7 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="39" t="s">
         <v>75</v>
       </c>
@@ -4356,7 +4356,7 @@
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="17"/>
       <c r="C27" s="13"/>
@@ -5118,7 +5118,7 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="44" t="s">
         <v>84</v>
       </c>
@@ -5172,7 +5172,7 @@
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="17"/>
       <c r="C32" s="13"/>
@@ -5758,7 +5758,7 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="44" t="s">
         <v>92</v>
       </c>
@@ -5812,7 +5812,7 @@
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6516,7 +6516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="17"/>
       <c r="C39" s="13"/>
@@ -6750,7 +6750,7 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="44" t="s">
         <v>103</v>
       </c>
@@ -6804,7 +6804,7 @@
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7156,7 +7156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
       <c r="B45" s="17"/>
       <c r="C45" s="13"/>
@@ -7566,7 +7566,7 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="44" t="s">
         <v>110</v>
       </c>
@@ -7620,7 +7620,7 @@
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8148,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12"/>
       <c r="B50" s="17"/>
       <c r="C50" s="13"/>
@@ -8206,7 +8206,7 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="44" t="s">
         <v>111</v>
       </c>
@@ -8260,7 +8260,7 @@
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8964,7 +8964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12"/>
       <c r="B57" s="17"/>
       <c r="C57" s="13"/>
@@ -9198,7 +9198,7 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="44" t="s">
         <v>114</v>
       </c>
@@ -9252,7 +9252,7 @@
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="12"/>
       <c r="B63" s="17"/>
       <c r="C63" s="13"/>
@@ -10014,7 +10014,7 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="44" t="s">
         <v>116</v>
       </c>
@@ -10068,7 +10068,7 @@
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10420,355 +10420,359 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
       <c r="B67" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="10"/>
+      <c r="C67" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="D67" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F67" s="11" t="str">
+      <c r="F67" s="11">
         <f>IF(OR($C67="",E67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E67,FIND("-",E67)-1),"")=AW67,IFERROR(--MID(E67,FIND("-",E67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))-(IFERROR(--MID(E67,FIND("-",E67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))-(IFERROR(--MID(E67,FIND("-",E67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(E67,FIND("-",E67)-1),""))=(AW67))+2*((IFERROR(--MID(E67,FIND("-",E67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H67" s="11" t="str">
+      <c r="H67" s="11">
         <f>IF(OR($C67="",G67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G67,FIND("-",G67)-1),"")=AW67,IFERROR(--MID(G67,FIND("-",G67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))-(IFERROR(--MID(G67,FIND("-",G67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))-(IFERROR(--MID(G67,FIND("-",G67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(G67,FIND("-",G67)-1),""))=(AW67))+2*((IFERROR(--MID(G67,FIND("-",G67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J67" s="11" t="str">
+      <c r="J67" s="11">
         <f>IF(OR($C67="",I67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I67,FIND("-",I67)-1),"")=AW67,IFERROR(--MID(I67,FIND("-",I67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))-(IFERROR(--MID(I67,FIND("-",I67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))-(IFERROR(--MID(I67,FIND("-",I67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(I67,FIND("-",I67)-1),""))=(AW67))+2*((IFERROR(--MID(I67,FIND("-",I67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K67" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L67" s="11" t="str">
+      <c r="L67" s="11">
         <f>IF(OR($C67="",K67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K67,FIND("-",K67)-1),"")=AW67,IFERROR(--MID(K67,FIND("-",K67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))-(IFERROR(--MID(K67,FIND("-",K67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))-(IFERROR(--MID(K67,FIND("-",K67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(K67,FIND("-",K67)-1),""))=(AW67))+2*((IFERROR(--MID(K67,FIND("-",K67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M67" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N67" s="11" t="str">
+      <c r="N67" s="11">
         <f>IF(OR($C67="",M67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M67,FIND("-",M67)-1),"")=AW67,IFERROR(--MID(M67,FIND("-",M67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))-(IFERROR(--MID(M67,FIND("-",M67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))-(IFERROR(--MID(M67,FIND("-",M67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(M67,FIND("-",M67)-1),""))=(AW67))+2*((IFERROR(--MID(M67,FIND("-",M67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P67" s="11" t="str">
+      <c r="P67" s="11">
         <f>IF(OR($C67="",O67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O67,FIND("-",O67)-1),"")=AW67,IFERROR(--MID(O67,FIND("-",O67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))-(IFERROR(--MID(O67,FIND("-",O67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))-(IFERROR(--MID(O67,FIND("-",O67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(O67,FIND("-",O67)-1),""))=(AW67))+2*((IFERROR(--MID(O67,FIND("-",O67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q67" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="R67" s="11" t="str">
+      <c r="R67" s="11">
         <f>IF(OR($C67="",Q67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q67,FIND("-",Q67)-1),"")=AW67,IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))-(IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))-(IFERROR(--MID(Q67,FIND("-",Q67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(Q67,FIND("-",Q67)-1),""))=(AW67))+2*((IFERROR(--MID(Q67,FIND("-",Q67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="S67" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T67" s="11" t="str">
+      <c r="T67" s="11">
         <f>IF(OR($C67="",S67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S67,FIND("-",S67)-1),"")=AW67,IFERROR(--MID(S67,FIND("-",S67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))-(IFERROR(--MID(S67,FIND("-",S67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))-(IFERROR(--MID(S67,FIND("-",S67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(S67,FIND("-",S67)-1),""))=(AW67))+2*((IFERROR(--MID(S67,FIND("-",S67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U67" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="V67" s="11" t="str">
+      <c r="V67" s="11">
         <f>IF(OR($C67="",U67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U67,FIND("-",U67)-1),"")=AW67,IFERROR(--MID(U67,FIND("-",U67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))-(IFERROR(--MID(U67,FIND("-",U67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))-(IFERROR(--MID(U67,FIND("-",U67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(U67,FIND("-",U67)-1),""))=(AW67))+2*((IFERROR(--MID(U67,FIND("-",U67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W67" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X67" s="11" t="str">
+      <c r="X67" s="11">
         <f>IF(OR($C67="",W67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W67,FIND("-",W67)-1),"")=AW67,IFERROR(--MID(W67,FIND("-",W67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))-(IFERROR(--MID(W67,FIND("-",W67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))-(IFERROR(--MID(W67,FIND("-",W67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(W67,FIND("-",W67)-1),""))=(AW67))+2*((IFERROR(--MID(W67,FIND("-",W67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z67" s="11" t="str">
+      <c r="Z67" s="11">
         <f>IF(OR($C67="",Y67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y67,FIND("-",Y67)-1),"")=AW67,IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))-(IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))-(IFERROR(--MID(Y67,FIND("-",Y67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(Y67,FIND("-",Y67)-1),""))=(AW67))+2*((IFERROR(--MID(Y67,FIND("-",Y67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AB67" s="11" t="str">
+      <c r="AB67" s="11">
         <f>IF(OR($C67="",AA67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA67,FIND("-",AA67)-1),"")=AW67,IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))-(IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))-(IFERROR(--MID(AA67,FIND("-",AA67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AA67,FIND("-",AA67)-1),""))=(AW67))+2*((IFERROR(--MID(AA67,FIND("-",AA67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD67" s="11" t="str">
+      <c r="AD67" s="11">
         <f>IF(OR($C67="",AC67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC67,FIND("-",AC67)-1),"")=AW67,IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))-(IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))-(IFERROR(--MID(AC67,FIND("-",AC67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AC67,FIND("-",AC67)-1),""))=(AW67))+2*((IFERROR(--MID(AC67,FIND("-",AC67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF67" s="11" t="str">
+      <c r="AF67" s="11">
         <f>IF(OR($C67="",AE67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE67,FIND("-",AE67)-1),"")=AW67,IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))-(IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))-(IFERROR(--MID(AE67,FIND("-",AE67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AE67,FIND("-",AE67)-1),""))=(AW67))+2*((IFERROR(--MID(AE67,FIND("-",AE67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG67" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH67" s="11" t="str">
+      <c r="AH67" s="11">
         <f>IF(OR($C67="",AG67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG67,FIND("-",AG67)-1),"")=AW67,IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))-(IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))-(IFERROR(--MID(AG67,FIND("-",AG67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AG67,FIND("-",AG67)-1),""))=(AW67))+2*((IFERROR(--MID(AG67,FIND("-",AG67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ67" s="11" t="str">
+      <c r="AJ67" s="11">
         <f>IF(OR($C67="",AI67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI67,FIND("-",AI67)-1),"")=AW67,IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))-(IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))-(IFERROR(--MID(AI67,FIND("-",AI67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AI67,FIND("-",AI67)-1),""))=(AW67))+2*((IFERROR(--MID(AI67,FIND("-",AI67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL67" s="11" t="str">
+      <c r="AL67" s="11">
         <f>IF(OR($C67="",AK67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK67,FIND("-",AK67)-1),"")=AW67,IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))-(IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))-(IFERROR(--MID(AK67,FIND("-",AK67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AK67,FIND("-",AK67)-1),""))=(AW67))+2*((IFERROR(--MID(AK67,FIND("-",AK67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM67" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN67" s="11" t="str">
+      <c r="AN67" s="11">
         <f>IF(OR($C67="",AM67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM67,FIND("-",AM67)-1),"")=AW67,IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))-(IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))-(IFERROR(--MID(AM67,FIND("-",AM67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AM67,FIND("-",AM67)-1),""))=(AW67))+2*((IFERROR(--MID(AM67,FIND("-",AM67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AO67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AP67" s="11" t="str">
+      <c r="AP67" s="11">
         <f>IF(OR($C67="",AO67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO67,FIND("-",AO67)-1),"")=AW67,IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))-(IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))-(IFERROR(--MID(AO67,FIND("-",AO67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AO67,FIND("-",AO67)-1),""))=(AW67))+2*((IFERROR(--MID(AO67,FIND("-",AO67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ67" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR67" s="11" t="str">
+      <c r="AR67" s="11">
         <f>IF(OR($C67="",AQ67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),"")=AW67,IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))-(IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))-(IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AQ67,FIND("-",AQ67)-1),""))=(AW67))+2*((IFERROR(--MID(AQ67,FIND("-",AQ67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS67" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT67" s="11" t="str">
+      <c r="AT67" s="11">
         <f>IF(OR($C67="",AS67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS67,FIND("-",AS67)-1),"")=AW67,IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))-(IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))-(IFERROR(--MID(AS67,FIND("-",AS67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AS67,FIND("-",AS67)-1),""))=(AW67))+2*((IFERROR(--MID(AS67,FIND("-",AS67)+1,99),""))=(AX67))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU67" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV67" s="11" t="str">
+      <c r="AV67" s="11">
         <f>IF(OR($C67="",AU67=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU67,FIND("-",AU67)-1),"")=AW67,IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")=AX67),10,5*(SIGN((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))-(IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")))=SIGN((AW67)-(AX67)))+2*(((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))-(IFERROR(--MID(AU67,FIND("-",AU67)+1,99),"")))=((AW67)-(AX67)))+2*((IFERROR(--LEFT(AU67,FIND("-",AU67)-1),""))=(AW67))+2*((IFERROR(--MID(AU67,FIND("-",AU67)+1,99),""))=(AX67))),""))</f>
-        <v/>
-      </c>
-      <c r="AW67" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW67" s="11">
         <f>IF($C67="","",IFERROR(--LEFT($C67,FIND("-",$C67)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX67" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX67" s="11">
         <f>IF($C67="","",IFERROR(--MID($C67,FIND("-",$C67)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
       <c r="B68" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="10"/>
+      <c r="C68" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="D68" s="1" t="s">
         <v>93</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F68" s="11" t="str">
+      <c r="F68" s="11">
         <f>IF(OR($C68="",E68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E68,FIND("-",E68)-1),"")=AW68,IFERROR(--MID(E68,FIND("-",E68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))-(IFERROR(--MID(E68,FIND("-",E68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))-(IFERROR(--MID(E68,FIND("-",E68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(E68,FIND("-",E68)-1),""))=(AW68))+2*((IFERROR(--MID(E68,FIND("-",E68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="H68" s="11" t="str">
+      <c r="H68" s="11">
         <f>IF(OR($C68="",G68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G68,FIND("-",G68)-1),"")=AW68,IFERROR(--MID(G68,FIND("-",G68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))-(IFERROR(--MID(G68,FIND("-",G68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))-(IFERROR(--MID(G68,FIND("-",G68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(G68,FIND("-",G68)-1),""))=(AW68))+2*((IFERROR(--MID(G68,FIND("-",G68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J68" s="11" t="str">
+      <c r="J68" s="11">
         <f>IF(OR($C68="",I68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I68,FIND("-",I68)-1),"")=AW68,IFERROR(--MID(I68,FIND("-",I68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))-(IFERROR(--MID(I68,FIND("-",I68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))-(IFERROR(--MID(I68,FIND("-",I68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(I68,FIND("-",I68)-1),""))=(AW68))+2*((IFERROR(--MID(I68,FIND("-",I68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="L68" s="11" t="str">
+      <c r="L68" s="11">
         <f>IF(OR($C68="",K68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K68,FIND("-",K68)-1),"")=AW68,IFERROR(--MID(K68,FIND("-",K68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))-(IFERROR(--MID(K68,FIND("-",K68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))-(IFERROR(--MID(K68,FIND("-",K68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(K68,FIND("-",K68)-1),""))=(AW68))+2*((IFERROR(--MID(K68,FIND("-",K68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N68" s="11" t="str">
+      <c r="N68" s="11">
         <f>IF(OR($C68="",M68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M68,FIND("-",M68)-1),"")=AW68,IFERROR(--MID(M68,FIND("-",M68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))-(IFERROR(--MID(M68,FIND("-",M68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))-(IFERROR(--MID(M68,FIND("-",M68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(M68,FIND("-",M68)-1),""))=(AW68))+2*((IFERROR(--MID(M68,FIND("-",M68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="P68" s="11" t="str">
+      <c r="P68" s="11">
         <f>IF(OR($C68="",O68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O68,FIND("-",O68)-1),"")=AW68,IFERROR(--MID(O68,FIND("-",O68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))-(IFERROR(--MID(O68,FIND("-",O68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))-(IFERROR(--MID(O68,FIND("-",O68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(O68,FIND("-",O68)-1),""))=(AW68))+2*((IFERROR(--MID(O68,FIND("-",O68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="R68" s="11" t="str">
+      <c r="R68" s="11">
         <f>IF(OR($C68="",Q68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q68,FIND("-",Q68)-1),"")=AW68,IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))-(IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))-(IFERROR(--MID(Q68,FIND("-",Q68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(Q68,FIND("-",Q68)-1),""))=(AW68))+2*((IFERROR(--MID(Q68,FIND("-",Q68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T68" s="11" t="str">
+      <c r="T68" s="11">
         <f>IF(OR($C68="",S68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S68,FIND("-",S68)-1),"")=AW68,IFERROR(--MID(S68,FIND("-",S68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))-(IFERROR(--MID(S68,FIND("-",S68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))-(IFERROR(--MID(S68,FIND("-",S68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(S68,FIND("-",S68)-1),""))=(AW68))+2*((IFERROR(--MID(S68,FIND("-",S68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="V68" s="11" t="str">
+      <c r="V68" s="11">
         <f>IF(OR($C68="",U68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U68,FIND("-",U68)-1),"")=AW68,IFERROR(--MID(U68,FIND("-",U68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))-(IFERROR(--MID(U68,FIND("-",U68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))-(IFERROR(--MID(U68,FIND("-",U68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(U68,FIND("-",U68)-1),""))=(AW68))+2*((IFERROR(--MID(U68,FIND("-",U68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X68" s="11" t="str">
+      <c r="X68" s="11">
         <f>IF(OR($C68="",W68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W68,FIND("-",W68)-1),"")=AW68,IFERROR(--MID(W68,FIND("-",W68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))-(IFERROR(--MID(W68,FIND("-",W68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))-(IFERROR(--MID(W68,FIND("-",W68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(W68,FIND("-",W68)-1),""))=(AW68))+2*((IFERROR(--MID(W68,FIND("-",W68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="Z68" s="11" t="str">
+      <c r="Z68" s="11">
         <f>IF(OR($C68="",Y68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y68,FIND("-",Y68)-1),"")=AW68,IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))-(IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))-(IFERROR(--MID(Y68,FIND("-",Y68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(Y68,FIND("-",Y68)-1),""))=(AW68))+2*((IFERROR(--MID(Y68,FIND("-",Y68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB68" s="11" t="str">
+      <c r="AB68" s="11">
         <f>IF(OR($C68="",AA68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA68,FIND("-",AA68)-1),"")=AW68,IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))-(IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))-(IFERROR(--MID(AA68,FIND("-",AA68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AA68,FIND("-",AA68)-1),""))=(AW68))+2*((IFERROR(--MID(AA68,FIND("-",AA68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AC68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AD68" s="11" t="str">
+      <c r="AD68" s="11">
         <f>IF(OR($C68="",AC68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC68,FIND("-",AC68)-1),"")=AW68,IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))-(IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))-(IFERROR(--MID(AC68,FIND("-",AC68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AC68,FIND("-",AC68)-1),""))=(AW68))+2*((IFERROR(--MID(AC68,FIND("-",AC68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF68" s="11" t="str">
+      <c r="AF68" s="11">
         <f>IF(OR($C68="",AE68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE68,FIND("-",AE68)-1),"")=AW68,IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))-(IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))-(IFERROR(--MID(AE68,FIND("-",AE68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AE68,FIND("-",AE68)-1),""))=(AW68))+2*((IFERROR(--MID(AE68,FIND("-",AE68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH68" s="11" t="str">
+      <c r="AH68" s="11">
         <f>IF(OR($C68="",AG68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG68,FIND("-",AG68)-1),"")=AW68,IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))-(IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))-(IFERROR(--MID(AG68,FIND("-",AG68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AG68,FIND("-",AG68)-1),""))=(AW68))+2*((IFERROR(--MID(AG68,FIND("-",AG68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AI68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AJ68" s="11" t="str">
+      <c r="AJ68" s="11">
         <f>IF(OR($C68="",AI68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI68,FIND("-",AI68)-1),"")=AW68,IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))-(IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))-(IFERROR(--MID(AI68,FIND("-",AI68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AI68,FIND("-",AI68)-1),""))=(AW68))+2*((IFERROR(--MID(AI68,FIND("-",AI68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL68" s="11" t="str">
+      <c r="AL68" s="11">
         <f>IF(OR($C68="",AK68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK68,FIND("-",AK68)-1),"")=AW68,IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))-(IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))-(IFERROR(--MID(AK68,FIND("-",AK68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AK68,FIND("-",AK68)-1),""))=(AW68))+2*((IFERROR(--MID(AK68,FIND("-",AK68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN68" s="11" t="str">
+      <c r="AN68" s="11">
         <f>IF(OR($C68="",AM68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM68,FIND("-",AM68)-1),"")=AW68,IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))-(IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))-(IFERROR(--MID(AM68,FIND("-",AM68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AM68,FIND("-",AM68)-1),""))=(AW68))+2*((IFERROR(--MID(AM68,FIND("-",AM68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO68" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP68" s="11" t="str">
+      <c r="AP68" s="11">
         <f>IF(OR($C68="",AO68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO68,FIND("-",AO68)-1),"")=AW68,IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))-(IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))-(IFERROR(--MID(AO68,FIND("-",AO68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AO68,FIND("-",AO68)-1),""))=(AW68))+2*((IFERROR(--MID(AO68,FIND("-",AO68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ68" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR68" s="11" t="str">
+      <c r="AR68" s="11">
         <f>IF(OR($C68="",AQ68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),"")=AW68,IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))-(IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))-(IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AQ68,FIND("-",AQ68)-1),""))=(AW68))+2*((IFERROR(--MID(AQ68,FIND("-",AQ68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS68" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AT68" s="11" t="str">
+      <c r="AT68" s="11">
         <f>IF(OR($C68="",AS68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS68,FIND("-",AS68)-1),"")=AW68,IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))-(IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))-(IFERROR(--MID(AS68,FIND("-",AS68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AS68,FIND("-",AS68)-1),""))=(AW68))+2*((IFERROR(--MID(AS68,FIND("-",AS68)+1,99),""))=(AX68))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU68" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AV68" s="11" t="str">
+      <c r="AV68" s="11">
         <f>IF(OR($C68="",AU68=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU68,FIND("-",AU68)-1),"")=AW68,IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")=AX68),10,5*(SIGN((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))-(IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")))=SIGN((AW68)-(AX68)))+2*(((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))-(IFERROR(--MID(AU68,FIND("-",AU68)+1,99),"")))=((AW68)-(AX68)))+2*((IFERROR(--LEFT(AU68,FIND("-",AU68)-1),""))=(AW68))+2*((IFERROR(--MID(AU68,FIND("-",AU68)+1,99),""))=(AX68))),""))</f>
-        <v/>
-      </c>
-      <c r="AW68" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW68" s="11">
         <f>IF($C68="","",IFERROR(--LEFT($C68,FIND("-",$C68)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX68" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX68" s="11">
         <f>IF($C68="","",IFERROR(--MID($C68,FIND("-",$C68)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="12"/>
       <c r="B69" s="17"/>
       <c r="C69" s="13"/>
@@ -10826,7 +10830,7 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="44" t="s">
         <v>117</v>
       </c>
@@ -10880,355 +10884,359 @@
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
       <c r="B71" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="D71" s="1" t="s">
         <v>90</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F71" s="11" t="str">
+      <c r="F71" s="11">
         <f>IF(OR($C71="",E71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E71,FIND("-",E71)-1),"")=AW71,IFERROR(--MID(E71,FIND("-",E71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))-(IFERROR(--MID(E71,FIND("-",E71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))-(IFERROR(--MID(E71,FIND("-",E71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(E71,FIND("-",E71)-1),""))=(AW71))+2*((IFERROR(--MID(E71,FIND("-",E71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H71" s="11" t="str">
+      <c r="H71" s="11">
         <f>IF(OR($C71="",G71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G71,FIND("-",G71)-1),"")=AW71,IFERROR(--MID(G71,FIND("-",G71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))-(IFERROR(--MID(G71,FIND("-",G71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))-(IFERROR(--MID(G71,FIND("-",G71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(G71,FIND("-",G71)-1),""))=(AW71))+2*((IFERROR(--MID(G71,FIND("-",G71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="J71" s="11" t="str">
+      <c r="J71" s="11">
         <f>IF(OR($C71="",I71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I71,FIND("-",I71)-1),"")=AW71,IFERROR(--MID(I71,FIND("-",I71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))-(IFERROR(--MID(I71,FIND("-",I71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))-(IFERROR(--MID(I71,FIND("-",I71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(I71,FIND("-",I71)-1),""))=(AW71))+2*((IFERROR(--MID(I71,FIND("-",I71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="L71" s="11" t="str">
+      <c r="L71" s="11">
         <f>IF(OR($C71="",K71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K71,FIND("-",K71)-1),"")=AW71,IFERROR(--MID(K71,FIND("-",K71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))-(IFERROR(--MID(K71,FIND("-",K71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))-(IFERROR(--MID(K71,FIND("-",K71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(K71,FIND("-",K71)-1),""))=(AW71))+2*((IFERROR(--MID(K71,FIND("-",K71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N71" s="11" t="str">
+      <c r="N71" s="11">
         <f>IF(OR($C71="",M71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M71,FIND("-",M71)-1),"")=AW71,IFERROR(--MID(M71,FIND("-",M71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))-(IFERROR(--MID(M71,FIND("-",M71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))-(IFERROR(--MID(M71,FIND("-",M71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(M71,FIND("-",M71)-1),""))=(AW71))+2*((IFERROR(--MID(M71,FIND("-",M71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P71" s="11" t="str">
+      <c r="P71" s="11">
         <f>IF(OR($C71="",O71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O71,FIND("-",O71)-1),"")=AW71,IFERROR(--MID(O71,FIND("-",O71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))-(IFERROR(--MID(O71,FIND("-",O71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))-(IFERROR(--MID(O71,FIND("-",O71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(O71,FIND("-",O71)-1),""))=(AW71))+2*((IFERROR(--MID(O71,FIND("-",O71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q71" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R71" s="11" t="str">
+      <c r="R71" s="11">
         <f>IF(OR($C71="",Q71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q71,FIND("-",Q71)-1),"")=AW71,IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))-(IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))-(IFERROR(--MID(Q71,FIND("-",Q71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(Q71,FIND("-",Q71)-1),""))=(AW71))+2*((IFERROR(--MID(Q71,FIND("-",Q71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T71" s="11" t="str">
+      <c r="T71" s="11">
         <f>IF(OR($C71="",S71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S71,FIND("-",S71)-1),"")=AW71,IFERROR(--MID(S71,FIND("-",S71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))-(IFERROR(--MID(S71,FIND("-",S71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))-(IFERROR(--MID(S71,FIND("-",S71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(S71,FIND("-",S71)-1),""))=(AW71))+2*((IFERROR(--MID(S71,FIND("-",S71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V71" s="11" t="str">
+      <c r="V71" s="11">
         <f>IF(OR($C71="",U71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U71,FIND("-",U71)-1),"")=AW71,IFERROR(--MID(U71,FIND("-",U71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))-(IFERROR(--MID(U71,FIND("-",U71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))-(IFERROR(--MID(U71,FIND("-",U71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(U71,FIND("-",U71)-1),""))=(AW71))+2*((IFERROR(--MID(U71,FIND("-",U71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X71" s="11" t="str">
+      <c r="X71" s="11">
         <f>IF(OR($C71="",W71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W71,FIND("-",W71)-1),"")=AW71,IFERROR(--MID(W71,FIND("-",W71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))-(IFERROR(--MID(W71,FIND("-",W71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))-(IFERROR(--MID(W71,FIND("-",W71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(W71,FIND("-",W71)-1),""))=(AW71))+2*((IFERROR(--MID(W71,FIND("-",W71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z71" s="11" t="str">
+      <c r="Z71" s="11">
         <f>IF(OR($C71="",Y71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y71,FIND("-",Y71)-1),"")=AW71,IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))-(IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))-(IFERROR(--MID(Y71,FIND("-",Y71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(Y71,FIND("-",Y71)-1),""))=(AW71))+2*((IFERROR(--MID(Y71,FIND("-",Y71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA71" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AB71" s="11" t="str">
+      <c r="AB71" s="11">
         <f>IF(OR($C71="",AA71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA71,FIND("-",AA71)-1),"")=AW71,IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))-(IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))-(IFERROR(--MID(AA71,FIND("-",AA71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AA71,FIND("-",AA71)-1),""))=(AW71))+2*((IFERROR(--MID(AA71,FIND("-",AA71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AD71" s="11" t="str">
+      <c r="AD71" s="11">
         <f>IF(OR($C71="",AC71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC71,FIND("-",AC71)-1),"")=AW71,IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))-(IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))-(IFERROR(--MID(AC71,FIND("-",AC71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AC71,FIND("-",AC71)-1),""))=(AW71))+2*((IFERROR(--MID(AC71,FIND("-",AC71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF71" s="11" t="str">
+      <c r="AF71" s="11">
         <f>IF(OR($C71="",AE71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE71,FIND("-",AE71)-1),"")=AW71,IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))-(IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))-(IFERROR(--MID(AE71,FIND("-",AE71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AE71,FIND("-",AE71)-1),""))=(AW71))+2*((IFERROR(--MID(AE71,FIND("-",AE71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG71" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AH71" s="11" t="str">
+      <c r="AH71" s="11">
         <f>IF(OR($C71="",AG71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG71,FIND("-",AG71)-1),"")=AW71,IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))-(IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))-(IFERROR(--MID(AG71,FIND("-",AG71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AG71,FIND("-",AG71)-1),""))=(AW71))+2*((IFERROR(--MID(AG71,FIND("-",AG71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ71" s="11" t="str">
+      <c r="AJ71" s="11">
         <f>IF(OR($C71="",AI71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI71,FIND("-",AI71)-1),"")=AW71,IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))-(IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))-(IFERROR(--MID(AI71,FIND("-",AI71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AI71,FIND("-",AI71)-1),""))=(AW71))+2*((IFERROR(--MID(AI71,FIND("-",AI71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AK71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL71" s="11" t="str">
+      <c r="AL71" s="11">
         <f>IF(OR($C71="",AK71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK71,FIND("-",AK71)-1),"")=AW71,IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))-(IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))-(IFERROR(--MID(AK71,FIND("-",AK71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AK71,FIND("-",AK71)-1),""))=(AW71))+2*((IFERROR(--MID(AK71,FIND("-",AK71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM71" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AN71" s="11" t="str">
+      <c r="AN71" s="11">
         <f>IF(OR($C71="",AM71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM71,FIND("-",AM71)-1),"")=AW71,IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))-(IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))-(IFERROR(--MID(AM71,FIND("-",AM71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AM71,FIND("-",AM71)-1),""))=(AW71))+2*((IFERROR(--MID(AM71,FIND("-",AM71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO71" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AP71" s="11" t="str">
+      <c r="AP71" s="11">
         <f>IF(OR($C71="",AO71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO71,FIND("-",AO71)-1),"")=AW71,IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))-(IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))-(IFERROR(--MID(AO71,FIND("-",AO71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AO71,FIND("-",AO71)-1),""))=(AW71))+2*((IFERROR(--MID(AO71,FIND("-",AO71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ71" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR71" s="11" t="str">
+      <c r="AR71" s="11">
         <f>IF(OR($C71="",AQ71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),"")=AW71,IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))-(IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))-(IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AQ71,FIND("-",AQ71)-1),""))=(AW71))+2*((IFERROR(--MID(AQ71,FIND("-",AQ71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS71" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT71" s="11" t="str">
+      <c r="AT71" s="11">
         <f>IF(OR($C71="",AS71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS71,FIND("-",AS71)-1),"")=AW71,IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))-(IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))-(IFERROR(--MID(AS71,FIND("-",AS71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AS71,FIND("-",AS71)-1),""))=(AW71))+2*((IFERROR(--MID(AS71,FIND("-",AS71)+1,99),""))=(AX71))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AU71" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV71" s="11" t="str">
+      <c r="AV71" s="11">
         <f>IF(OR($C71="",AU71=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU71,FIND("-",AU71)-1),"")=AW71,IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")=AX71),10,5*(SIGN((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))-(IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")))=SIGN((AW71)-(AX71)))+2*(((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))-(IFERROR(--MID(AU71,FIND("-",AU71)+1,99),"")))=((AW71)-(AX71)))+2*((IFERROR(--LEFT(AU71,FIND("-",AU71)-1),""))=(AW71))+2*((IFERROR(--MID(AU71,FIND("-",AU71)+1,99),""))=(AX71))),""))</f>
-        <v/>
-      </c>
-      <c r="AW71" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW71" s="11">
         <f>IF($C71="","",IFERROR(--LEFT($C71,FIND("-",$C71)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX71" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX71" s="11">
         <f>IF($C71="","",IFERROR(--MID($C71,FIND("-",$C71)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
       <c r="B72" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="D72" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F72" s="11" t="str">
+      <c r="F72" s="11">
         <f>IF(OR($C72="",E72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E72,FIND("-",E72)-1),"")=AW72,IFERROR(--MID(E72,FIND("-",E72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))-(IFERROR(--MID(E72,FIND("-",E72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))-(IFERROR(--MID(E72,FIND("-",E72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(E72,FIND("-",E72)-1),""))=(AW72))+2*((IFERROR(--MID(E72,FIND("-",E72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H72" s="11" t="str">
+      <c r="H72" s="11">
         <f>IF(OR($C72="",G72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G72,FIND("-",G72)-1),"")=AW72,IFERROR(--MID(G72,FIND("-",G72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))-(IFERROR(--MID(G72,FIND("-",G72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))-(IFERROR(--MID(G72,FIND("-",G72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(G72,FIND("-",G72)-1),""))=(AW72))+2*((IFERROR(--MID(G72,FIND("-",G72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J72" s="11" t="str">
+      <c r="J72" s="11">
         <f>IF(OR($C72="",I72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I72,FIND("-",I72)-1),"")=AW72,IFERROR(--MID(I72,FIND("-",I72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))-(IFERROR(--MID(I72,FIND("-",I72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))-(IFERROR(--MID(I72,FIND("-",I72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(I72,FIND("-",I72)-1),""))=(AW72))+2*((IFERROR(--MID(I72,FIND("-",I72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L72" s="11" t="str">
+      <c r="L72" s="11">
         <f>IF(OR($C72="",K72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K72,FIND("-",K72)-1),"")=AW72,IFERROR(--MID(K72,FIND("-",K72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))-(IFERROR(--MID(K72,FIND("-",K72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))-(IFERROR(--MID(K72,FIND("-",K72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(K72,FIND("-",K72)-1),""))=(AW72))+2*((IFERROR(--MID(K72,FIND("-",K72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M72" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N72" s="11" t="str">
+      <c r="N72" s="11">
         <f>IF(OR($C72="",M72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M72,FIND("-",M72)-1),"")=AW72,IFERROR(--MID(M72,FIND("-",M72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))-(IFERROR(--MID(M72,FIND("-",M72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))-(IFERROR(--MID(M72,FIND("-",M72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(M72,FIND("-",M72)-1),""))=(AW72))+2*((IFERROR(--MID(M72,FIND("-",M72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O72" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P72" s="11" t="str">
+      <c r="P72" s="11">
         <f>IF(OR($C72="",O72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O72,FIND("-",O72)-1),"")=AW72,IFERROR(--MID(O72,FIND("-",O72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))-(IFERROR(--MID(O72,FIND("-",O72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))-(IFERROR(--MID(O72,FIND("-",O72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(O72,FIND("-",O72)-1),""))=(AW72))+2*((IFERROR(--MID(O72,FIND("-",O72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Q72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R72" s="11" t="str">
+      <c r="R72" s="11">
         <f>IF(OR($C72="",Q72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q72,FIND("-",Q72)-1),"")=AW72,IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))-(IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))-(IFERROR(--MID(Q72,FIND("-",Q72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(Q72,FIND("-",Q72)-1),""))=(AW72))+2*((IFERROR(--MID(Q72,FIND("-",Q72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S72" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T72" s="11" t="str">
+      <c r="T72" s="11">
         <f>IF(OR($C72="",S72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S72,FIND("-",S72)-1),"")=AW72,IFERROR(--MID(S72,FIND("-",S72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))-(IFERROR(--MID(S72,FIND("-",S72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))-(IFERROR(--MID(S72,FIND("-",S72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(S72,FIND("-",S72)-1),""))=(AW72))+2*((IFERROR(--MID(S72,FIND("-",S72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V72" s="11" t="str">
+      <c r="V72" s="11">
         <f>IF(OR($C72="",U72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U72,FIND("-",U72)-1),"")=AW72,IFERROR(--MID(U72,FIND("-",U72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))-(IFERROR(--MID(U72,FIND("-",U72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))-(IFERROR(--MID(U72,FIND("-",U72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(U72,FIND("-",U72)-1),""))=(AW72))+2*((IFERROR(--MID(U72,FIND("-",U72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="W72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X72" s="11" t="str">
+      <c r="X72" s="11">
         <f>IF(OR($C72="",W72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W72,FIND("-",W72)-1),"")=AW72,IFERROR(--MID(W72,FIND("-",W72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))-(IFERROR(--MID(W72,FIND("-",W72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))-(IFERROR(--MID(W72,FIND("-",W72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(W72,FIND("-",W72)-1),""))=(AW72))+2*((IFERROR(--MID(W72,FIND("-",W72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="Z72" s="11" t="str">
+      <c r="Z72" s="11">
         <f>IF(OR($C72="",Y72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y72,FIND("-",Y72)-1),"")=AW72,IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))-(IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))-(IFERROR(--MID(Y72,FIND("-",Y72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(Y72,FIND("-",Y72)-1),""))=(AW72))+2*((IFERROR(--MID(Y72,FIND("-",Y72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AA72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AB72" s="11" t="str">
+      <c r="AB72" s="11">
         <f>IF(OR($C72="",AA72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA72,FIND("-",AA72)-1),"")=AW72,IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))-(IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))-(IFERROR(--MID(AA72,FIND("-",AA72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AA72,FIND("-",AA72)-1),""))=(AW72))+2*((IFERROR(--MID(AA72,FIND("-",AA72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC72" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AD72" s="11" t="str">
+      <c r="AD72" s="11">
         <f>IF(OR($C72="",AC72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC72,FIND("-",AC72)-1),"")=AW72,IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))-(IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))-(IFERROR(--MID(AC72,FIND("-",AC72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AC72,FIND("-",AC72)-1),""))=(AW72))+2*((IFERROR(--MID(AC72,FIND("-",AC72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF72" s="11" t="str">
+      <c r="AF72" s="11">
         <f>IF(OR($C72="",AE72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE72,FIND("-",AE72)-1),"")=AW72,IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))-(IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))-(IFERROR(--MID(AE72,FIND("-",AE72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AE72,FIND("-",AE72)-1),""))=(AW72))+2*((IFERROR(--MID(AE72,FIND("-",AE72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH72" s="11" t="str">
+      <c r="AH72" s="11">
         <f>IF(OR($C72="",AG72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG72,FIND("-",AG72)-1),"")=AW72,IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))-(IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))-(IFERROR(--MID(AG72,FIND("-",AG72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AG72,FIND("-",AG72)-1),""))=(AW72))+2*((IFERROR(--MID(AG72,FIND("-",AG72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AJ72" s="11" t="str">
+      <c r="AJ72" s="11">
         <f>IF(OR($C72="",AI72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI72,FIND("-",AI72)-1),"")=AW72,IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))-(IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))-(IFERROR(--MID(AI72,FIND("-",AI72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AI72,FIND("-",AI72)-1),""))=(AW72))+2*((IFERROR(--MID(AI72,FIND("-",AI72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK72" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL72" s="11" t="str">
+      <c r="AL72" s="11">
         <f>IF(OR($C72="",AK72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK72,FIND("-",AK72)-1),"")=AW72,IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))-(IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))-(IFERROR(--MID(AK72,FIND("-",AK72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AK72,FIND("-",AK72)-1),""))=(AW72))+2*((IFERROR(--MID(AK72,FIND("-",AK72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM72" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AN72" s="11" t="str">
+      <c r="AN72" s="11">
         <f>IF(OR($C72="",AM72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM72,FIND("-",AM72)-1),"")=AW72,IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))-(IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))-(IFERROR(--MID(AM72,FIND("-",AM72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AM72,FIND("-",AM72)-1),""))=(AW72))+2*((IFERROR(--MID(AM72,FIND("-",AM72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO72" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AP72" s="11" t="str">
+      <c r="AP72" s="11">
         <f>IF(OR($C72="",AO72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO72,FIND("-",AO72)-1),"")=AW72,IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))-(IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))-(IFERROR(--MID(AO72,FIND("-",AO72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AO72,FIND("-",AO72)-1),""))=(AW72))+2*((IFERROR(--MID(AO72,FIND("-",AO72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR72" s="11" t="str">
+      <c r="AR72" s="11">
         <f>IF(OR($C72="",AQ72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),"")=AW72,IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))-(IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))-(IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AQ72,FIND("-",AQ72)-1),""))=(AW72))+2*((IFERROR(--MID(AQ72,FIND("-",AQ72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS72" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT72" s="11" t="str">
+      <c r="AT72" s="11">
         <f>IF(OR($C72="",AS72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS72,FIND("-",AS72)-1),"")=AW72,IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))-(IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))-(IFERROR(--MID(AS72,FIND("-",AS72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AS72,FIND("-",AS72)-1),""))=(AW72))+2*((IFERROR(--MID(AS72,FIND("-",AS72)+1,99),""))=(AX72))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU72" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV72" s="11" t="str">
+      <c r="AV72" s="11">
         <f>IF(OR($C72="",AU72=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU72,FIND("-",AU72)-1),"")=AW72,IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")=AX72),10,5*(SIGN((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))-(IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")))=SIGN((AW72)-(AX72)))+2*(((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))-(IFERROR(--MID(AU72,FIND("-",AU72)+1,99),"")))=((AW72)-(AX72)))+2*((IFERROR(--LEFT(AU72,FIND("-",AU72)-1),""))=(AW72))+2*((IFERROR(--MID(AU72,FIND("-",AU72)+1,99),""))=(AX72))),""))</f>
-        <v/>
-      </c>
-      <c r="AW72" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW72" s="11">
         <f>IF($C72="","",IFERROR(--LEFT($C72,FIND("-",$C72)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX72" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX72" s="11">
         <f>IF($C72="","",IFERROR(--MID($C72,FIND("-",$C72)+1,99),""))</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11402,7 +11410,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11576,7 +11584,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="12"/>
       <c r="B75" s="17"/>
       <c r="C75" s="13"/>
@@ -11634,7 +11642,7 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="44" t="s">
         <v>118</v>
       </c>
@@ -11688,7 +11696,7 @@
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11862,7 +11870,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -12036,7 +12044,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12210,7 +12218,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12384,7 +12392,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12"/>
       <c r="B81" s="17"/>
       <c r="C81" s="13"/>
@@ -12442,7 +12450,7 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="44" t="s">
         <v>119</v>
       </c>
@@ -12496,7 +12504,7 @@
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12670,7 +12678,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12844,7 +12852,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -13018,7 +13026,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13192,7 +13200,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13366,7 +13374,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13540,7 +13548,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="12"/>
       <c r="B89" s="17"/>
       <c r="C89" s="13"/>
@@ -13598,7 +13606,7 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="44" t="s">
         <v>122</v>
       </c>
@@ -13652,7 +13660,7 @@
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13826,7 +13834,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -14000,7 +14008,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14174,7 +14182,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14348,7 +14356,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14522,7 +14530,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14696,7 +14704,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="12"/>
       <c r="B97" s="17"/>
       <c r="C97" s="13"/>
@@ -14754,7 +14762,7 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="44" t="s">
         <v>125</v>
       </c>
@@ -14808,7 +14816,7 @@
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14982,7 +14990,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15156,7 +15164,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15330,7 +15338,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15504,7 +15512,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15678,7 +15686,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15852,7 +15860,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="12"/>
       <c r="B105" s="17"/>
       <c r="C105" s="13"/>
@@ -15910,7 +15918,7 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="44" t="s">
         <v>126</v>
       </c>
@@ -15964,7 +15972,7 @@
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16138,7 +16146,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16312,7 +16320,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16486,7 +16494,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16660,7 +16668,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="12"/>
       <c r="B111" s="17"/>
       <c r="C111" s="13"/>
@@ -16718,7 +16726,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12"/>
       <c r="B112" s="17"/>
       <c r="C112" s="13"/>
@@ -16776,7 +16784,7 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="48" t="s">
         <v>128</v>
       </c>
@@ -16830,7 +16838,7 @@
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="44" t="s">
         <v>126</v>
       </c>
@@ -16884,7 +16892,7 @@
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -17014,7 +17022,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12"/>
       <c r="B116" s="17"/>
       <c r="C116" s="13"/>
@@ -17072,7 +17080,7 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="44" t="s">
         <v>131</v>
       </c>
@@ -17126,7 +17134,7 @@
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17256,7 +17264,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17386,7 +17394,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12"/>
       <c r="B120" s="17"/>
       <c r="C120" s="13"/>
@@ -17444,7 +17452,7 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="44" t="s">
         <v>136</v>
       </c>
@@ -17498,7 +17506,7 @@
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17628,7 +17636,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17758,7 +17766,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17888,7 +17896,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="12"/>
       <c r="B125" s="17"/>
       <c r="C125" s="13"/>
@@ -17946,7 +17954,7 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="44" t="s">
         <v>143</v>
       </c>
@@ -18000,7 +18008,7 @@
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18130,7 +18138,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18260,7 +18268,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18390,7 +18398,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12"/>
       <c r="B130" s="17"/>
       <c r="C130" s="13"/>
@@ -18448,7 +18456,7 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="44" t="s">
         <v>150</v>
       </c>
@@ -18502,7 +18510,7 @@
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18632,7 +18640,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18762,7 +18770,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12"/>
       <c r="B134" s="17"/>
       <c r="C134" s="13"/>
@@ -18820,7 +18828,7 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="44" t="s">
         <v>155</v>
       </c>
@@ -18874,7 +18882,7 @@
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -19004,7 +19012,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19134,7 +19142,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19264,7 +19272,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12"/>
       <c r="B139" s="17"/>
       <c r="C139" s="13"/>
@@ -19322,7 +19330,7 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="44" t="s">
         <v>162</v>
       </c>
@@ -19376,7 +19384,7 @@
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19506,7 +19514,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19636,7 +19644,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12"/>
       <c r="B143" s="17"/>
       <c r="C143" s="13"/>
@@ -19694,7 +19702,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12"/>
       <c r="B144" s="17"/>
       <c r="C144" s="13"/>
@@ -19752,7 +19760,7 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="48" t="s">
         <v>167</v>
       </c>
@@ -19806,7 +19814,7 @@
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="44" t="s">
         <v>162</v>
       </c>
@@ -19860,7 +19868,7 @@
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -19990,7 +19998,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20120,7 +20128,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12"/>
       <c r="B149" s="17"/>
       <c r="C149" s="13"/>
@@ -20178,7 +20186,7 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="44" t="s">
         <v>172</v>
       </c>
@@ -20232,7 +20240,7 @@
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20362,7 +20370,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12"/>
       <c r="B152" s="17"/>
       <c r="C152" s="13"/>
@@ -20420,7 +20428,7 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="44" t="s">
         <v>175</v>
       </c>
@@ -20474,7 +20482,7 @@
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20604,7 +20612,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20734,7 +20742,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12"/>
       <c r="B156" s="17"/>
       <c r="C156" s="13"/>
@@ -20792,7 +20800,7 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="44" t="s">
         <v>180</v>
       </c>
@@ -20846,7 +20854,7 @@
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20976,7 +20984,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21106,7 +21114,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21236,7 +21244,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12"/>
       <c r="B161" s="17"/>
       <c r="C161" s="13"/>
@@ -21294,7 +21302,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12"/>
       <c r="B162" s="17"/>
       <c r="C162" s="13"/>
@@ -21352,7 +21360,7 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="48" t="s">
         <v>187</v>
       </c>
@@ -21406,7 +21414,7 @@
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="44" t="s">
         <v>188</v>
       </c>
@@ -21460,7 +21468,7 @@
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21590,7 +21598,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12"/>
       <c r="B166" s="17"/>
       <c r="C166" s="13"/>
@@ -21648,7 +21656,7 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="44" t="s">
         <v>191</v>
       </c>
@@ -21702,7 +21710,7 @@
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21832,7 +21840,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="12"/>
       <c r="B169" s="17"/>
       <c r="C169" s="13"/>
@@ -21890,7 +21898,7 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="44" t="s">
         <v>194</v>
       </c>
@@ -21944,7 +21952,7 @@
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -22074,7 +22082,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12"/>
       <c r="B172" s="17"/>
       <c r="C172" s="13"/>
@@ -22132,7 +22140,7 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="44" t="s">
         <v>197</v>
       </c>
@@ -22186,7 +22194,7 @@
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22316,7 +22324,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="12"/>
       <c r="B175" s="17"/>
       <c r="C175" s="13"/>
@@ -22374,7 +22382,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12"/>
       <c r="B176" s="17"/>
       <c r="C176" s="13"/>
@@ -22432,7 +22440,7 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="48" t="s">
         <v>200</v>
       </c>
@@ -22486,7 +22494,7 @@
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="44" t="s">
         <v>201</v>
       </c>
@@ -22540,7 +22548,7 @@
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22670,7 +22678,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12"/>
       <c r="B180" s="17"/>
       <c r="C180" s="13"/>
@@ -22728,7 +22736,7 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="44" t="s">
         <v>204</v>
       </c>
@@ -22782,7 +22790,7 @@
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22912,7 +22920,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="12"/>
       <c r="B183" s="17"/>
       <c r="C183" s="13"/>
@@ -22970,7 +22978,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12"/>
       <c r="B184" s="17"/>
       <c r="C184" s="13"/>
@@ -23028,7 +23036,7 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="48" t="s">
         <v>207</v>
       </c>
@@ -23082,7 +23090,7 @@
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="44" t="s">
         <v>208</v>
       </c>
@@ -23136,7 +23144,7 @@
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23266,7 +23274,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12"/>
       <c r="B188" s="17"/>
       <c r="C188" s="13"/>
@@ -23324,7 +23332,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="12"/>
       <c r="B189" s="17"/>
       <c r="C189" s="13"/>
@@ -23382,7 +23390,7 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="48" t="s">
         <v>211</v>
       </c>
@@ -23436,7 +23444,7 @@
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="44" t="s">
         <v>212</v>
       </c>
@@ -23490,7 +23498,7 @@
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23620,7 +23628,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12"/>
       <c r="B193" s="17"/>
       <c r="C193" s="13"/>
@@ -23678,7 +23686,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12"/>
       <c r="B194" s="17"/>
       <c r="C194" s="13"/>
@@ -23817,58 +23825,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.33203125" customWidth="1"/>
+    <col min="2" max="2" width="75.28515625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
-    <col min="8" max="8" width="12.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" customWidth="1"/>
-    <col min="12" max="12" width="12.5546875" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" style="21" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" customWidth="1"/>
-    <col min="16" max="16" width="12.5546875" style="21" customWidth="1"/>
-    <col min="17" max="17" width="10.5546875" customWidth="1"/>
-    <col min="18" max="18" width="12.5546875" style="21" customWidth="1"/>
-    <col min="19" max="19" width="10.5546875" customWidth="1"/>
-    <col min="20" max="20" width="12.5546875" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" style="21" customWidth="1"/>
-    <col min="23" max="23" width="10.5546875" customWidth="1"/>
-    <col min="24" max="24" width="12.5546875" style="21" customWidth="1"/>
-    <col min="25" max="25" width="10.5546875" customWidth="1"/>
-    <col min="26" max="26" width="12.5546875" style="21" customWidth="1"/>
-    <col min="27" max="27" width="10.5546875" customWidth="1"/>
-    <col min="28" max="28" width="12.5546875" style="21" customWidth="1"/>
-    <col min="29" max="29" width="10.5546875" customWidth="1"/>
-    <col min="30" max="30" width="12.5546875" style="21" customWidth="1"/>
-    <col min="31" max="31" width="10.5546875" customWidth="1"/>
-    <col min="32" max="32" width="12.5546875" style="21" customWidth="1"/>
-    <col min="33" max="33" width="10.5546875" customWidth="1"/>
-    <col min="34" max="34" width="12.5546875" style="21" customWidth="1"/>
-    <col min="35" max="35" width="10.5546875" customWidth="1"/>
-    <col min="36" max="36" width="12.5546875" style="21" customWidth="1"/>
-    <col min="37" max="37" width="10.5546875" customWidth="1"/>
-    <col min="38" max="38" width="12.5546875" style="21" customWidth="1"/>
-    <col min="39" max="39" width="10.5546875" customWidth="1"/>
-    <col min="40" max="40" width="12.5546875" style="21" customWidth="1"/>
-    <col min="41" max="41" width="10.5546875" customWidth="1"/>
-    <col min="42" max="42" width="12.5546875" customWidth="1"/>
-    <col min="43" max="43" width="10.5546875" customWidth="1"/>
-    <col min="44" max="44" width="12.5546875" style="21" customWidth="1"/>
-    <col min="45" max="45" width="10.5546875" customWidth="1"/>
-    <col min="46" max="46" width="12.5546875" style="21" customWidth="1"/>
-    <col min="47" max="47" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="21" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="21" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="21" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="21" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" style="21" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="21" customWidth="1"/>
+    <col min="27" max="27" width="10.5703125" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" style="21" customWidth="1"/>
+    <col min="29" max="29" width="10.5703125" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="21" customWidth="1"/>
+    <col min="31" max="31" width="10.5703125" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="21" customWidth="1"/>
+    <col min="33" max="33" width="10.5703125" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="21" customWidth="1"/>
+    <col min="35" max="35" width="10.5703125" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="21" customWidth="1"/>
+    <col min="37" max="37" width="10.5703125" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="21" customWidth="1"/>
+    <col min="39" max="39" width="10.5703125" customWidth="1"/>
+    <col min="40" max="40" width="12.5703125" style="21" customWidth="1"/>
+    <col min="41" max="41" width="10.5703125" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" customWidth="1"/>
+    <col min="43" max="43" width="10.5703125" customWidth="1"/>
+    <col min="44" max="44" width="12.5703125" style="21" customWidth="1"/>
+    <col min="45" max="45" width="10.5703125" customWidth="1"/>
+    <col min="46" max="46" width="12.5703125" style="21" customWidth="1"/>
+    <col min="47" max="47" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -23981,7 +23989,7 @@
       </c>
       <c r="AU1" s="51"/>
     </row>
-    <row r="2" spans="1:47" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" s="28" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34"/>
       <c r="B2" s="35" t="s">
         <v>215</v>
@@ -24122,7 +24130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24285,7 +24293,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24448,7 +24456,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24611,7 +24619,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24774,7 +24782,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24937,7 +24945,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25100,7 +25108,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25263,7 +25271,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25426,7 +25434,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25589,7 +25597,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25752,7 +25760,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25915,7 +25923,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -26078,7 +26086,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26241,7 +26249,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26404,7 +26412,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26556,16 +26564,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>284</v>
       </c>
@@ -26574,7 +26582,7 @@
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>285</v>
       </c>
@@ -26591,29 +26599,29 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f>Wedstrijden_beheer!O1</f>
-        <v>Maik</v>
+        <f>Wedstrijden_beheer!AO1</f>
+        <v>Patrick</v>
       </c>
       <c r="C3" s="11">
-        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>192</v>
+        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
+        <v>213</v>
       </c>
       <c r="D3" s="11">
-        <f>Bonus_beheer!O17</f>
+        <f>Bonus_beheer!AO17</f>
         <v>0</v>
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
         <v>2</v>
@@ -26624,7 +26632,7 @@
       </c>
       <c r="C4" s="11">
         <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="D4" s="11">
         <f>Bonus_beheer!AA17</f>
@@ -26632,76 +26640,76 @@
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>187</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <f>Wedstrijden_beheer!AO1</f>
-        <v>Patrick</v>
+        <v>2</v>
+      </c>
+      <c r="B5" s="29" t="str">
+        <f>Wedstrijden_beheer!E1</f>
+        <v>Roland</v>
       </c>
       <c r="C5" s="11">
-        <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>185</v>
+        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
+        <v>209</v>
       </c>
       <c r="D5" s="11">
-        <f>Bonus_beheer!AO17</f>
+        <f>Bonus_beheer!E17</f>
         <v>0</v>
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
+        <f>Wedstrijden_beheer!O1</f>
+        <v>Maik</v>
+      </c>
+      <c r="C6" s="11">
+        <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
+        <v>208</v>
+      </c>
+      <c r="D6" s="11">
+        <f>Bonus_beheer!O17</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="11">
+        <f>C6+D6</f>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C7" s="11">
         <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>184</v>
-      </c>
-      <c r="D6" s="11">
+        <v>208</v>
+      </c>
+      <c r="D7" s="11">
         <f>Bonus_beheer!I17</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="11">
-        <f>C6+D6</f>
-        <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
-      </c>
-      <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>183</v>
-      </c>
-      <c r="D7" s="11">
-        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>183</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
         <v>6</v>
@@ -26712,7 +26720,7 @@
       </c>
       <c r="C8" s="11">
         <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D8" s="11">
         <f>Bonus_beheer!U17</f>
@@ -26720,32 +26728,32 @@
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>177</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>177</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>203</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>177</v>
+        <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
         <v>8</v>
@@ -26756,7 +26764,7 @@
       </c>
       <c r="C10" s="11">
         <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="D10" s="11">
         <f>Bonus_beheer!AE17</f>
@@ -26764,101 +26772,101 @@
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>175</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
-        <v>8</v>
-      </c>
-      <c r="B11" s="29" t="str">
-        <f>Wedstrijden_beheer!E1</f>
-        <v>Roland</v>
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>175</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>201</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!E17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>175</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>174</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>201</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>174</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!W1</f>
-        <v>Jos</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>168</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>200</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!W17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!W1</f>
+        <v>Jos</v>
       </c>
       <c r="C14" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>167</v>
+        <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
+        <v>189</v>
       </c>
       <c r="D14" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!W17</f>
         <v>0</v>
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>167</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
         <f>Wedstrijden_beheer!AM1</f>
@@ -26866,7 +26874,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26874,10 +26882,10 @@
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
         <v>14</v>
@@ -26888,7 +26896,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AU18</f>
@@ -26896,10 +26904,10 @@
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
         <v>14</v>
@@ -26910,7 +26918,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AU17</f>
@@ -26918,10 +26926,10 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
         <v>16</v>
@@ -26932,7 +26940,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26940,10 +26948,10 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
         <v>17</v>
@@ -26954,7 +26962,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26962,10 +26970,10 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
         <v>18</v>
@@ -26976,7 +26984,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26984,10 +26992,10 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>142</v>
+        <v>163</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
         <v>19</v>
@@ -26998,7 +27006,7 @@
       </c>
       <c r="C21" s="11">
         <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D21" s="11">
         <f>Bonus_beheer!S17</f>
@@ -27006,10 +27014,10 @@
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
         <v>20</v>
@@ -27020,7 +27028,7 @@
       </c>
       <c r="C22" s="11">
         <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="D22" s="11">
         <f>Bonus_beheer!AI17</f>
@@ -27028,10 +27036,10 @@
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>136</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
         <v>21</v>
@@ -27042,7 +27050,7 @@
       </c>
       <c r="C23" s="11">
         <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D23" s="11">
         <f>Bonus_beheer!Q18</f>
@@ -27050,10 +27058,10 @@
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
         <v>21</v>
@@ -27064,7 +27072,7 @@
       </c>
       <c r="C24" s="11">
         <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D24" s="11">
         <f>Bonus_beheer!Q17</f>
@@ -27072,7 +27080,7 @@
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>128</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -27092,20 +27100,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.5546875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.6640625" hidden="1"/>
+    <col min="3" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="16"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
@@ -27113,7 +27121,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27121,7 +27129,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27129,7 +27137,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27137,7 +27145,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27145,7 +27153,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27153,7 +27161,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27161,7 +27169,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27177,16 +27185,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="55.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.6640625" hidden="1"/>
+    <col min="45" max="16384" width="8.7109375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>306</v>
       </c>
@@ -27234,7 +27242,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
@@ -27245,7 +27253,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27256,7 +27264,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27267,7 +27275,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27278,7 +27286,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27289,7 +27297,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27300,7 +27308,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27317,14 +27325,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5546875" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>319</v>
       </c>
@@ -27335,7 +27343,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27346,7 +27354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27354,7 +27362,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27362,7 +27370,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27370,7 +27378,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27378,62 +27386,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="30" t="s">
         <v>4</v>
       </c>
@@ -27661,16 +27669,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1595" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66CB4532-7751-423F-B18E-6573E75C12C5}"/>
+  <xr:revisionPtr revIDLastSave="1601" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5588F279-52C7-423C-818C-CAD1B86D23E5}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="2808" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1376,6 +1376,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1385,23 +1391,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1409,22 +1415,16 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1789,106 +1789,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52" t="s">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="52" t="s">
+      <c r="C1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="42" t="s">
+      <c r="F1" s="57"/>
+      <c r="G1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="47"/>
+      <c r="I1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="42" t="s">
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="47"/>
+      <c r="M1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="43"/>
-      <c r="O1" s="42" t="s">
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="42" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="43"/>
-      <c r="S1" s="42" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="43"/>
-      <c r="U1" s="42" t="s">
+      <c r="T1" s="47"/>
+      <c r="U1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="43"/>
-      <c r="W1" s="42" t="s">
+      <c r="V1" s="47"/>
+      <c r="W1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="42" t="s">
+      <c r="X1" s="47"/>
+      <c r="Y1" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="42" t="s">
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="43"/>
-      <c r="AC1" s="42" t="s">
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="43"/>
-      <c r="AE1" s="42" t="s">
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="42" t="s">
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="42" t="s">
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="42" t="s">
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="42" t="s">
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="42" t="s">
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="42" t="s">
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="43"/>
-      <c r="AS1" s="42" t="s">
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="42" t="s">
+      <c r="AT1" s="58"/>
+      <c r="AU1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="51"/>
+      <c r="AV1" s="58"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1897,10 +1897,10 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="56"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="23" t="s">
         <v>27</v>
       </c>
@@ -2044,107 +2044,107 @@
       <c r="A3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="57"/>
-      <c r="AS3" s="57"/>
-      <c r="AT3" s="57"/>
-      <c r="AU3" s="57"/>
-      <c r="AV3" s="58"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="49"/>
+      <c r="AM3" s="49"/>
+      <c r="AN3" s="49"/>
+      <c r="AO3" s="49"/>
+      <c r="AP3" s="49"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="50"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
     <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="40"/>
-      <c r="AB4" s="40"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="40"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="40"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="40"/>
-      <c r="AJ4" s="40"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="40"/>
-      <c r="AM4" s="40"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="40"/>
-      <c r="AP4" s="40"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="40"/>
-      <c r="AS4" s="40"/>
-      <c r="AT4" s="40"/>
-      <c r="AU4" s="40"/>
-      <c r="AV4" s="41"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AM4" s="44"/>
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="44"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="44"/>
+      <c r="AU4" s="44"/>
+      <c r="AV4" s="45"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
@@ -2383,56 +2383,56 @@
       <c r="AX6" s="12"/>
     </row>
     <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="40"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="40"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="40"/>
-      <c r="AT7" s="40"/>
-      <c r="AU7" s="40"/>
-      <c r="AV7" s="41"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="44"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="44"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="44"/>
+      <c r="AK7" s="44"/>
+      <c r="AL7" s="44"/>
+      <c r="AM7" s="44"/>
+      <c r="AN7" s="44"/>
+      <c r="AO7" s="44"/>
+      <c r="AP7" s="44"/>
+      <c r="AQ7" s="44"/>
+      <c r="AR7" s="44"/>
+      <c r="AS7" s="44"/>
+      <c r="AT7" s="44"/>
+      <c r="AU7" s="44"/>
+      <c r="AV7" s="45"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
@@ -2847,56 +2847,56 @@
       <c r="AX10" s="12"/>
     </row>
     <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="40"/>
-      <c r="AS11" s="40"/>
-      <c r="AT11" s="40"/>
-      <c r="AU11" s="40"/>
-      <c r="AV11" s="41"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
+      <c r="AG11" s="44"/>
+      <c r="AH11" s="44"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="44"/>
+      <c r="AK11" s="44"/>
+      <c r="AL11" s="44"/>
+      <c r="AM11" s="44"/>
+      <c r="AN11" s="44"/>
+      <c r="AO11" s="44"/>
+      <c r="AP11" s="44"/>
+      <c r="AQ11" s="44"/>
+      <c r="AR11" s="44"/>
+      <c r="AS11" s="44"/>
+      <c r="AT11" s="44"/>
+      <c r="AU11" s="44"/>
+      <c r="AV11" s="45"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
@@ -3311,56 +3311,56 @@
       <c r="AX14" s="12"/>
     </row>
     <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="40"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="40"/>
-      <c r="U15" s="40"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="40"/>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="40"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="40"/>
-      <c r="AD15" s="40"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="40"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="40"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="40"/>
-      <c r="AM15" s="40"/>
-      <c r="AN15" s="40"/>
-      <c r="AO15" s="40"/>
-      <c r="AP15" s="40"/>
-      <c r="AQ15" s="40"/>
-      <c r="AR15" s="40"/>
-      <c r="AS15" s="40"/>
-      <c r="AT15" s="40"/>
-      <c r="AU15" s="40"/>
-      <c r="AV15" s="41"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="44"/>
+      <c r="AB15" s="44"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="44"/>
+      <c r="AE15" s="44"/>
+      <c r="AF15" s="44"/>
+      <c r="AG15" s="44"/>
+      <c r="AH15" s="44"/>
+      <c r="AI15" s="44"/>
+      <c r="AJ15" s="44"/>
+      <c r="AK15" s="44"/>
+      <c r="AL15" s="44"/>
+      <c r="AM15" s="44"/>
+      <c r="AN15" s="44"/>
+      <c r="AO15" s="44"/>
+      <c r="AP15" s="44"/>
+      <c r="AQ15" s="44"/>
+      <c r="AR15" s="44"/>
+      <c r="AS15" s="44"/>
+      <c r="AT15" s="44"/>
+      <c r="AU15" s="44"/>
+      <c r="AV15" s="45"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
@@ -4303,56 +4303,56 @@
       <c r="AX21" s="12"/>
     </row>
     <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="40"/>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="40"/>
-      <c r="Z22" s="40"/>
-      <c r="AA22" s="40"/>
-      <c r="AB22" s="40"/>
-      <c r="AC22" s="40"/>
-      <c r="AD22" s="40"/>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="40"/>
-      <c r="AG22" s="40"/>
-      <c r="AH22" s="40"/>
-      <c r="AI22" s="40"/>
-      <c r="AJ22" s="40"/>
-      <c r="AK22" s="40"/>
-      <c r="AL22" s="40"/>
-      <c r="AM22" s="40"/>
-      <c r="AN22" s="40"/>
-      <c r="AO22" s="40"/>
-      <c r="AP22" s="40"/>
-      <c r="AQ22" s="40"/>
-      <c r="AR22" s="40"/>
-      <c r="AS22" s="40"/>
-      <c r="AT22" s="40"/>
-      <c r="AU22" s="40"/>
-      <c r="AV22" s="41"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="44"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="44"/>
+      <c r="AB22" s="44"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="44"/>
+      <c r="AE22" s="44"/>
+      <c r="AF22" s="44"/>
+      <c r="AG22" s="44"/>
+      <c r="AH22" s="44"/>
+      <c r="AI22" s="44"/>
+      <c r="AJ22" s="44"/>
+      <c r="AK22" s="44"/>
+      <c r="AL22" s="44"/>
+      <c r="AM22" s="44"/>
+      <c r="AN22" s="44"/>
+      <c r="AO22" s="44"/>
+      <c r="AP22" s="44"/>
+      <c r="AQ22" s="44"/>
+      <c r="AR22" s="44"/>
+      <c r="AS22" s="44"/>
+      <c r="AT22" s="44"/>
+      <c r="AU22" s="44"/>
+      <c r="AV22" s="45"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
@@ -5119,56 +5119,56 @@
       <c r="AX27" s="12"/>
     </row>
     <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="45"/>
-      <c r="AA28" s="46"/>
-      <c r="AB28" s="45"/>
-      <c r="AC28" s="46"/>
-      <c r="AD28" s="45"/>
-      <c r="AE28" s="46"/>
-      <c r="AF28" s="45"/>
-      <c r="AG28" s="46"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="46"/>
-      <c r="AJ28" s="45"/>
-      <c r="AK28" s="46"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="46"/>
-      <c r="AN28" s="45"/>
-      <c r="AO28" s="46"/>
-      <c r="AP28" s="45"/>
-      <c r="AQ28" s="45"/>
-      <c r="AR28" s="45"/>
-      <c r="AS28" s="45"/>
-      <c r="AT28" s="45"/>
-      <c r="AU28" s="46"/>
-      <c r="AV28" s="47"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="40"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="40"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="40"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="40"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="40"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="40"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="40"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="40"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="40"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="40"/>
+      <c r="AQ28" s="40"/>
+      <c r="AR28" s="40"/>
+      <c r="AS28" s="40"/>
+      <c r="AT28" s="40"/>
+      <c r="AU28" s="41"/>
+      <c r="AV28" s="42"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
@@ -5759,56 +5759,56 @@
       <c r="AX32" s="12"/>
     </row>
     <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="46"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="46"/>
-      <c r="AB33" s="45"/>
-      <c r="AC33" s="46"/>
-      <c r="AD33" s="45"/>
-      <c r="AE33" s="46"/>
-      <c r="AF33" s="45"/>
-      <c r="AG33" s="46"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="46"/>
-      <c r="AJ33" s="45"/>
-      <c r="AK33" s="46"/>
-      <c r="AL33" s="45"/>
-      <c r="AM33" s="46"/>
-      <c r="AN33" s="45"/>
-      <c r="AO33" s="46"/>
-      <c r="AP33" s="45"/>
-      <c r="AQ33" s="45"/>
-      <c r="AR33" s="45"/>
-      <c r="AS33" s="45"/>
-      <c r="AT33" s="45"/>
-      <c r="AU33" s="46"/>
-      <c r="AV33" s="47"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="40"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="40"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="40"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="40"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="40"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="40"/>
+      <c r="AI33" s="41"/>
+      <c r="AJ33" s="40"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="40"/>
+      <c r="AM33" s="41"/>
+      <c r="AN33" s="40"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="40"/>
+      <c r="AQ33" s="40"/>
+      <c r="AR33" s="40"/>
+      <c r="AS33" s="40"/>
+      <c r="AT33" s="40"/>
+      <c r="AU33" s="41"/>
+      <c r="AV33" s="42"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
@@ -6751,56 +6751,56 @@
       <c r="AX39" s="12"/>
     </row>
     <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="45"/>
-      <c r="S40" s="46"/>
-      <c r="T40" s="45"/>
-      <c r="U40" s="46"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="46"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="46"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="46"/>
-      <c r="AB40" s="45"/>
-      <c r="AC40" s="46"/>
-      <c r="AD40" s="45"/>
-      <c r="AE40" s="46"/>
-      <c r="AF40" s="45"/>
-      <c r="AG40" s="46"/>
-      <c r="AH40" s="45"/>
-      <c r="AI40" s="46"/>
-      <c r="AJ40" s="45"/>
-      <c r="AK40" s="46"/>
-      <c r="AL40" s="45"/>
-      <c r="AM40" s="46"/>
-      <c r="AN40" s="45"/>
-      <c r="AO40" s="46"/>
-      <c r="AP40" s="45"/>
-      <c r="AQ40" s="45"/>
-      <c r="AR40" s="45"/>
-      <c r="AS40" s="45"/>
-      <c r="AT40" s="45"/>
-      <c r="AU40" s="46"/>
-      <c r="AV40" s="47"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="40"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="40"/>
+      <c r="Y40" s="41"/>
+      <c r="Z40" s="40"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="40"/>
+      <c r="AC40" s="41"/>
+      <c r="AD40" s="40"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="40"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="40"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="40"/>
+      <c r="AK40" s="41"/>
+      <c r="AL40" s="40"/>
+      <c r="AM40" s="41"/>
+      <c r="AN40" s="40"/>
+      <c r="AO40" s="41"/>
+      <c r="AP40" s="40"/>
+      <c r="AQ40" s="40"/>
+      <c r="AR40" s="40"/>
+      <c r="AS40" s="40"/>
+      <c r="AT40" s="40"/>
+      <c r="AU40" s="41"/>
+      <c r="AV40" s="42"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
@@ -7567,56 +7567,56 @@
       <c r="AX45" s="12"/>
     </row>
     <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="45"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="45"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="45"/>
-      <c r="U46" s="46"/>
-      <c r="V46" s="45"/>
-      <c r="W46" s="46"/>
-      <c r="X46" s="45"/>
-      <c r="Y46" s="46"/>
-      <c r="Z46" s="45"/>
-      <c r="AA46" s="46"/>
-      <c r="AB46" s="45"/>
-      <c r="AC46" s="46"/>
-      <c r="AD46" s="45"/>
-      <c r="AE46" s="46"/>
-      <c r="AF46" s="45"/>
-      <c r="AG46" s="46"/>
-      <c r="AH46" s="45"/>
-      <c r="AI46" s="46"/>
-      <c r="AJ46" s="45"/>
-      <c r="AK46" s="46"/>
-      <c r="AL46" s="45"/>
-      <c r="AM46" s="46"/>
-      <c r="AN46" s="45"/>
-      <c r="AO46" s="46"/>
-      <c r="AP46" s="45"/>
-      <c r="AQ46" s="45"/>
-      <c r="AR46" s="45"/>
-      <c r="AS46" s="45"/>
-      <c r="AT46" s="45"/>
-      <c r="AU46" s="46"/>
-      <c r="AV46" s="47"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="40"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="40"/>
+      <c r="W46" s="41"/>
+      <c r="X46" s="40"/>
+      <c r="Y46" s="41"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="40"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="40"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="40"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="40"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="40"/>
+      <c r="AK46" s="41"/>
+      <c r="AL46" s="40"/>
+      <c r="AM46" s="41"/>
+      <c r="AN46" s="40"/>
+      <c r="AO46" s="41"/>
+      <c r="AP46" s="40"/>
+      <c r="AQ46" s="40"/>
+      <c r="AR46" s="40"/>
+      <c r="AS46" s="40"/>
+      <c r="AT46" s="40"/>
+      <c r="AU46" s="41"/>
+      <c r="AV46" s="42"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
@@ -8207,56 +8207,56 @@
       <c r="AX50" s="12"/>
     </row>
     <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
+      <c r="A51" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="45"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="46"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="45"/>
-      <c r="Y51" s="46"/>
-      <c r="Z51" s="45"/>
-      <c r="AA51" s="46"/>
-      <c r="AB51" s="45"/>
-      <c r="AC51" s="46"/>
-      <c r="AD51" s="45"/>
-      <c r="AE51" s="46"/>
-      <c r="AF51" s="45"/>
-      <c r="AG51" s="46"/>
-      <c r="AH51" s="45"/>
-      <c r="AI51" s="46"/>
-      <c r="AJ51" s="45"/>
-      <c r="AK51" s="46"/>
-      <c r="AL51" s="45"/>
-      <c r="AM51" s="46"/>
-      <c r="AN51" s="45"/>
-      <c r="AO51" s="46"/>
-      <c r="AP51" s="45"/>
-      <c r="AQ51" s="45"/>
-      <c r="AR51" s="45"/>
-      <c r="AS51" s="45"/>
-      <c r="AT51" s="45"/>
-      <c r="AU51" s="46"/>
-      <c r="AV51" s="47"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="40"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="41"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="41"/>
+      <c r="X51" s="40"/>
+      <c r="Y51" s="41"/>
+      <c r="Z51" s="40"/>
+      <c r="AA51" s="41"/>
+      <c r="AB51" s="40"/>
+      <c r="AC51" s="41"/>
+      <c r="AD51" s="40"/>
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="40"/>
+      <c r="AG51" s="41"/>
+      <c r="AH51" s="40"/>
+      <c r="AI51" s="41"/>
+      <c r="AJ51" s="40"/>
+      <c r="AK51" s="41"/>
+      <c r="AL51" s="40"/>
+      <c r="AM51" s="41"/>
+      <c r="AN51" s="40"/>
+      <c r="AO51" s="41"/>
+      <c r="AP51" s="40"/>
+      <c r="AQ51" s="40"/>
+      <c r="AR51" s="40"/>
+      <c r="AS51" s="40"/>
+      <c r="AT51" s="40"/>
+      <c r="AU51" s="41"/>
+      <c r="AV51" s="42"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
@@ -9199,56 +9199,56 @@
       <c r="AX57" s="12"/>
     </row>
     <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="44" t="s">
+      <c r="A58" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="46"/>
-      <c r="N58" s="45"/>
-      <c r="O58" s="46"/>
-      <c r="P58" s="45"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="45"/>
-      <c r="S58" s="46"/>
-      <c r="T58" s="45"/>
-      <c r="U58" s="46"/>
-      <c r="V58" s="45"/>
-      <c r="W58" s="46"/>
-      <c r="X58" s="45"/>
-      <c r="Y58" s="46"/>
-      <c r="Z58" s="45"/>
-      <c r="AA58" s="46"/>
-      <c r="AB58" s="45"/>
-      <c r="AC58" s="46"/>
-      <c r="AD58" s="45"/>
-      <c r="AE58" s="46"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="46"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
-      <c r="AJ58" s="45"/>
-      <c r="AK58" s="46"/>
-      <c r="AL58" s="45"/>
-      <c r="AM58" s="46"/>
-      <c r="AN58" s="45"/>
-      <c r="AO58" s="46"/>
-      <c r="AP58" s="45"/>
-      <c r="AQ58" s="45"/>
-      <c r="AR58" s="45"/>
-      <c r="AS58" s="45"/>
-      <c r="AT58" s="45"/>
-      <c r="AU58" s="46"/>
-      <c r="AV58" s="47"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="41"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="41"/>
+      <c r="R58" s="40"/>
+      <c r="S58" s="41"/>
+      <c r="T58" s="40"/>
+      <c r="U58" s="41"/>
+      <c r="V58" s="40"/>
+      <c r="W58" s="41"/>
+      <c r="X58" s="40"/>
+      <c r="Y58" s="41"/>
+      <c r="Z58" s="40"/>
+      <c r="AA58" s="41"/>
+      <c r="AB58" s="40"/>
+      <c r="AC58" s="41"/>
+      <c r="AD58" s="40"/>
+      <c r="AE58" s="41"/>
+      <c r="AF58" s="40"/>
+      <c r="AG58" s="41"/>
+      <c r="AH58" s="40"/>
+      <c r="AI58" s="41"/>
+      <c r="AJ58" s="40"/>
+      <c r="AK58" s="41"/>
+      <c r="AL58" s="40"/>
+      <c r="AM58" s="41"/>
+      <c r="AN58" s="40"/>
+      <c r="AO58" s="41"/>
+      <c r="AP58" s="40"/>
+      <c r="AQ58" s="40"/>
+      <c r="AR58" s="40"/>
+      <c r="AS58" s="40"/>
+      <c r="AT58" s="40"/>
+      <c r="AU58" s="41"/>
+      <c r="AV58" s="42"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
@@ -10015,56 +10015,56 @@
       <c r="AX63" s="12"/>
     </row>
     <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="44" t="s">
+      <c r="A64" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="45"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="46"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="46"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="46"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="46"/>
-      <c r="T64" s="45"/>
-      <c r="U64" s="46"/>
-      <c r="V64" s="45"/>
-      <c r="W64" s="46"/>
-      <c r="X64" s="45"/>
-      <c r="Y64" s="46"/>
-      <c r="Z64" s="45"/>
-      <c r="AA64" s="46"/>
-      <c r="AB64" s="45"/>
-      <c r="AC64" s="46"/>
-      <c r="AD64" s="45"/>
-      <c r="AE64" s="46"/>
-      <c r="AF64" s="45"/>
-      <c r="AG64" s="46"/>
-      <c r="AH64" s="45"/>
-      <c r="AI64" s="46"/>
-      <c r="AJ64" s="45"/>
-      <c r="AK64" s="46"/>
-      <c r="AL64" s="45"/>
-      <c r="AM64" s="46"/>
-      <c r="AN64" s="45"/>
-      <c r="AO64" s="46"/>
-      <c r="AP64" s="45"/>
-      <c r="AQ64" s="45"/>
-      <c r="AR64" s="45"/>
-      <c r="AS64" s="45"/>
-      <c r="AT64" s="45"/>
-      <c r="AU64" s="46"/>
-      <c r="AV64" s="47"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="41"/>
+      <c r="L64" s="40"/>
+      <c r="M64" s="41"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="41"/>
+      <c r="R64" s="40"/>
+      <c r="S64" s="41"/>
+      <c r="T64" s="40"/>
+      <c r="U64" s="41"/>
+      <c r="V64" s="40"/>
+      <c r="W64" s="41"/>
+      <c r="X64" s="40"/>
+      <c r="Y64" s="41"/>
+      <c r="Z64" s="40"/>
+      <c r="AA64" s="41"/>
+      <c r="AB64" s="40"/>
+      <c r="AC64" s="41"/>
+      <c r="AD64" s="40"/>
+      <c r="AE64" s="41"/>
+      <c r="AF64" s="40"/>
+      <c r="AG64" s="41"/>
+      <c r="AH64" s="40"/>
+      <c r="AI64" s="41"/>
+      <c r="AJ64" s="40"/>
+      <c r="AK64" s="41"/>
+      <c r="AL64" s="40"/>
+      <c r="AM64" s="41"/>
+      <c r="AN64" s="40"/>
+      <c r="AO64" s="41"/>
+      <c r="AP64" s="40"/>
+      <c r="AQ64" s="40"/>
+      <c r="AR64" s="40"/>
+      <c r="AS64" s="40"/>
+      <c r="AT64" s="40"/>
+      <c r="AU64" s="41"/>
+      <c r="AV64" s="42"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
@@ -10831,56 +10831,56 @@
       <c r="AX69" s="12"/>
     </row>
     <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="44" t="s">
+      <c r="A70" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="46"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="46"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="46"/>
-      <c r="T70" s="45"/>
-      <c r="U70" s="46"/>
-      <c r="V70" s="45"/>
-      <c r="W70" s="46"/>
-      <c r="X70" s="45"/>
-      <c r="Y70" s="46"/>
-      <c r="Z70" s="45"/>
-      <c r="AA70" s="46"/>
-      <c r="AB70" s="45"/>
-      <c r="AC70" s="46"/>
-      <c r="AD70" s="45"/>
-      <c r="AE70" s="46"/>
-      <c r="AF70" s="45"/>
-      <c r="AG70" s="46"/>
-      <c r="AH70" s="45"/>
-      <c r="AI70" s="46"/>
-      <c r="AJ70" s="45"/>
-      <c r="AK70" s="46"/>
-      <c r="AL70" s="45"/>
-      <c r="AM70" s="46"/>
-      <c r="AN70" s="45"/>
-      <c r="AO70" s="46"/>
-      <c r="AP70" s="45"/>
-      <c r="AQ70" s="45"/>
-      <c r="AR70" s="45"/>
-      <c r="AS70" s="45"/>
-      <c r="AT70" s="45"/>
-      <c r="AU70" s="46"/>
-      <c r="AV70" s="47"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="41"/>
+      <c r="L70" s="40"/>
+      <c r="M70" s="41"/>
+      <c r="N70" s="40"/>
+      <c r="O70" s="41"/>
+      <c r="P70" s="40"/>
+      <c r="Q70" s="41"/>
+      <c r="R70" s="40"/>
+      <c r="S70" s="41"/>
+      <c r="T70" s="40"/>
+      <c r="U70" s="41"/>
+      <c r="V70" s="40"/>
+      <c r="W70" s="41"/>
+      <c r="X70" s="40"/>
+      <c r="Y70" s="41"/>
+      <c r="Z70" s="40"/>
+      <c r="AA70" s="41"/>
+      <c r="AB70" s="40"/>
+      <c r="AC70" s="41"/>
+      <c r="AD70" s="40"/>
+      <c r="AE70" s="41"/>
+      <c r="AF70" s="40"/>
+      <c r="AG70" s="41"/>
+      <c r="AH70" s="40"/>
+      <c r="AI70" s="41"/>
+      <c r="AJ70" s="40"/>
+      <c r="AK70" s="41"/>
+      <c r="AL70" s="40"/>
+      <c r="AM70" s="41"/>
+      <c r="AN70" s="40"/>
+      <c r="AO70" s="41"/>
+      <c r="AP70" s="40"/>
+      <c r="AQ70" s="40"/>
+      <c r="AR70" s="40"/>
+      <c r="AS70" s="40"/>
+      <c r="AT70" s="40"/>
+      <c r="AU70" s="41"/>
+      <c r="AV70" s="42"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
@@ -11243,171 +11243,173 @@
       <c r="B73" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="D73" s="1" t="s">
         <v>107</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F73" s="11" t="str">
+      <c r="F73" s="11">
         <f>IF(OR($C73="",E73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E73,FIND("-",E73)-1),"")=AW73,IFERROR(--MID(E73,FIND("-",E73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))-(IFERROR(--MID(E73,FIND("-",E73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))-(IFERROR(--MID(E73,FIND("-",E73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(E73,FIND("-",E73)-1),""))=(AW73))+2*((IFERROR(--MID(E73,FIND("-",E73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H73" s="11" t="str">
+      <c r="H73" s="11">
         <f>IF(OR($C73="",G73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G73,FIND("-",G73)-1),"")=AW73,IFERROR(--MID(G73,FIND("-",G73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))-(IFERROR(--MID(G73,FIND("-",G73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))-(IFERROR(--MID(G73,FIND("-",G73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(G73,FIND("-",G73)-1),""))=(AW73))+2*((IFERROR(--MID(G73,FIND("-",G73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J73" s="11" t="str">
+      <c r="J73" s="11">
         <f>IF(OR($C73="",I73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I73,FIND("-",I73)-1),"")=AW73,IFERROR(--MID(I73,FIND("-",I73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))-(IFERROR(--MID(I73,FIND("-",I73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))-(IFERROR(--MID(I73,FIND("-",I73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(I73,FIND("-",I73)-1),""))=(AW73))+2*((IFERROR(--MID(I73,FIND("-",I73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L73" s="11" t="str">
+      <c r="L73" s="11">
         <f>IF(OR($C73="",K73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K73,FIND("-",K73)-1),"")=AW73,IFERROR(--MID(K73,FIND("-",K73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))-(IFERROR(--MID(K73,FIND("-",K73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))-(IFERROR(--MID(K73,FIND("-",K73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(K73,FIND("-",K73)-1),""))=(AW73))+2*((IFERROR(--MID(K73,FIND("-",K73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N73" s="11" t="str">
+      <c r="N73" s="11">
         <f>IF(OR($C73="",M73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M73,FIND("-",M73)-1),"")=AW73,IFERROR(--MID(M73,FIND("-",M73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))-(IFERROR(--MID(M73,FIND("-",M73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))-(IFERROR(--MID(M73,FIND("-",M73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(M73,FIND("-",M73)-1),""))=(AW73))+2*((IFERROR(--MID(M73,FIND("-",M73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P73" s="11" t="str">
+      <c r="P73" s="11">
         <f>IF(OR($C73="",O73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O73,FIND("-",O73)-1),"")=AW73,IFERROR(--MID(O73,FIND("-",O73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))-(IFERROR(--MID(O73,FIND("-",O73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))-(IFERROR(--MID(O73,FIND("-",O73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(O73,FIND("-",O73)-1),""))=(AW73))+2*((IFERROR(--MID(O73,FIND("-",O73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q73" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="R73" s="11" t="str">
+      <c r="R73" s="11">
         <f>IF(OR($C73="",Q73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q73,FIND("-",Q73)-1),"")=AW73,IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))-(IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))-(IFERROR(--MID(Q73,FIND("-",Q73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(Q73,FIND("-",Q73)-1),""))=(AW73))+2*((IFERROR(--MID(Q73,FIND("-",Q73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S73" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T73" s="11" t="str">
+      <c r="T73" s="11">
         <f>IF(OR($C73="",S73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S73,FIND("-",S73)-1),"")=AW73,IFERROR(--MID(S73,FIND("-",S73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))-(IFERROR(--MID(S73,FIND("-",S73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))-(IFERROR(--MID(S73,FIND("-",S73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(S73,FIND("-",S73)-1),""))=(AW73))+2*((IFERROR(--MID(S73,FIND("-",S73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="U73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V73" s="11" t="str">
+      <c r="V73" s="11">
         <f>IF(OR($C73="",U73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U73,FIND("-",U73)-1),"")=AW73,IFERROR(--MID(U73,FIND("-",U73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))-(IFERROR(--MID(U73,FIND("-",U73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))-(IFERROR(--MID(U73,FIND("-",U73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(U73,FIND("-",U73)-1),""))=(AW73))+2*((IFERROR(--MID(U73,FIND("-",U73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="X73" s="11" t="str">
+      <c r="X73" s="11">
         <f>IF(OR($C73="",W73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W73,FIND("-",W73)-1),"")=AW73,IFERROR(--MID(W73,FIND("-",W73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))-(IFERROR(--MID(W73,FIND("-",W73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))-(IFERROR(--MID(W73,FIND("-",W73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(W73,FIND("-",W73)-1),""))=(AW73))+2*((IFERROR(--MID(W73,FIND("-",W73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z73" s="11" t="str">
+      <c r="Z73" s="11">
         <f>IF(OR($C73="",Y73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y73,FIND("-",Y73)-1),"")=AW73,IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))-(IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))-(IFERROR(--MID(Y73,FIND("-",Y73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(Y73,FIND("-",Y73)-1),""))=(AW73))+2*((IFERROR(--MID(Y73,FIND("-",Y73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA73" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AB73" s="11" t="str">
+      <c r="AB73" s="11">
         <f>IF(OR($C73="",AA73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA73,FIND("-",AA73)-1),"")=AW73,IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))-(IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))-(IFERROR(--MID(AA73,FIND("-",AA73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AA73,FIND("-",AA73)-1),""))=(AW73))+2*((IFERROR(--MID(AA73,FIND("-",AA73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC73" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AD73" s="11" t="str">
+      <c r="AD73" s="11">
         <f>IF(OR($C73="",AC73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC73,FIND("-",AC73)-1),"")=AW73,IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))-(IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))-(IFERROR(--MID(AC73,FIND("-",AC73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AC73,FIND("-",AC73)-1),""))=(AW73))+2*((IFERROR(--MID(AC73,FIND("-",AC73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AF73" s="11" t="str">
+      <c r="AF73" s="11">
         <f>IF(OR($C73="",AE73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE73,FIND("-",AE73)-1),"")=AW73,IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))-(IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))-(IFERROR(--MID(AE73,FIND("-",AE73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AE73,FIND("-",AE73)-1),""))=(AW73))+2*((IFERROR(--MID(AE73,FIND("-",AE73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH73" s="11" t="str">
+      <c r="AH73" s="11">
         <f>IF(OR($C73="",AG73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG73,FIND("-",AG73)-1),"")=AW73,IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))-(IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))-(IFERROR(--MID(AG73,FIND("-",AG73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AG73,FIND("-",AG73)-1),""))=(AW73))+2*((IFERROR(--MID(AG73,FIND("-",AG73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI73" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="AJ73" s="11" t="str">
+      <c r="AJ73" s="11">
         <f>IF(OR($C73="",AI73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI73,FIND("-",AI73)-1),"")=AW73,IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))-(IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))-(IFERROR(--MID(AI73,FIND("-",AI73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AI73,FIND("-",AI73)-1),""))=(AW73))+2*((IFERROR(--MID(AI73,FIND("-",AI73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL73" s="11" t="str">
+      <c r="AL73" s="11">
         <f>IF(OR($C73="",AK73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK73,FIND("-",AK73)-1),"")=AW73,IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))-(IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))-(IFERROR(--MID(AK73,FIND("-",AK73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AK73,FIND("-",AK73)-1),""))=(AW73))+2*((IFERROR(--MID(AK73,FIND("-",AK73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM73" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AN73" s="11" t="str">
+      <c r="AN73" s="11">
         <f>IF(OR($C73="",AM73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM73,FIND("-",AM73)-1),"")=AW73,IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))-(IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))-(IFERROR(--MID(AM73,FIND("-",AM73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AM73,FIND("-",AM73)-1),""))=(AW73))+2*((IFERROR(--MID(AM73,FIND("-",AM73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO73" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP73" s="11" t="str">
+      <c r="AP73" s="11">
         <f>IF(OR($C73="",AO73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO73,FIND("-",AO73)-1),"")=AW73,IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))-(IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))-(IFERROR(--MID(AO73,FIND("-",AO73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AO73,FIND("-",AO73)-1),""))=(AW73))+2*((IFERROR(--MID(AO73,FIND("-",AO73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ73" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR73" s="11" t="str">
+      <c r="AR73" s="11">
         <f>IF(OR($C73="",AQ73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),"")=AW73,IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))-(IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))-(IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AQ73,FIND("-",AQ73)-1),""))=(AW73))+2*((IFERROR(--MID(AQ73,FIND("-",AQ73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS73" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT73" s="11" t="str">
+      <c r="AT73" s="11">
         <f>IF(OR($C73="",AS73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS73,FIND("-",AS73)-1),"")=AW73,IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))-(IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))-(IFERROR(--MID(AS73,FIND("-",AS73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AS73,FIND("-",AS73)-1),""))=(AW73))+2*((IFERROR(--MID(AS73,FIND("-",AS73)+1,99),""))=(AX73))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU73" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AV73" s="11" t="str">
+      <c r="AV73" s="11">
         <f>IF(OR($C73="",AU73=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU73,FIND("-",AU73)-1),"")=AW73,IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")=AX73),10,5*(SIGN((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))-(IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")))=SIGN((AW73)-(AX73)))+2*(((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))-(IFERROR(--MID(AU73,FIND("-",AU73)+1,99),"")))=((AW73)-(AX73)))+2*((IFERROR(--LEFT(AU73,FIND("-",AU73)-1),""))=(AW73))+2*((IFERROR(--MID(AU73,FIND("-",AU73)+1,99),""))=(AX73))),""))</f>
-        <v/>
-      </c>
-      <c r="AW73" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AW73" s="11">
         <f>IF($C73="","",IFERROR(--LEFT($C73,FIND("-",$C73)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX73" s="11" t="str">
+        <v>5</v>
+      </c>
+      <c r="AX73" s="11">
         <f>IF($C73="","",IFERROR(--MID($C73,FIND("-",$C73)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -11417,171 +11419,173 @@
       <c r="B74" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C74" s="10"/>
+      <c r="C74" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="D74" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F74" s="11" t="str">
+      <c r="F74" s="11">
         <f>IF(OR($C74="",E74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E74,FIND("-",E74)-1),"")=AW74,IFERROR(--MID(E74,FIND("-",E74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))-(IFERROR(--MID(E74,FIND("-",E74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))-(IFERROR(--MID(E74,FIND("-",E74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(E74,FIND("-",E74)-1),""))=(AW74))+2*((IFERROR(--MID(E74,FIND("-",E74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G74" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="H74" s="11" t="str">
+      <c r="H74" s="11">
         <f>IF(OR($C74="",G74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G74,FIND("-",G74)-1),"")=AW74,IFERROR(--MID(G74,FIND("-",G74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))-(IFERROR(--MID(G74,FIND("-",G74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))-(IFERROR(--MID(G74,FIND("-",G74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(G74,FIND("-",G74)-1),""))=(AW74))+2*((IFERROR(--MID(G74,FIND("-",G74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J74" s="11" t="str">
+      <c r="J74" s="11">
         <f>IF(OR($C74="",I74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I74,FIND("-",I74)-1),"")=AW74,IFERROR(--MID(I74,FIND("-",I74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))-(IFERROR(--MID(I74,FIND("-",I74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))-(IFERROR(--MID(I74,FIND("-",I74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(I74,FIND("-",I74)-1),""))=(AW74))+2*((IFERROR(--MID(I74,FIND("-",I74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K74" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L74" s="11" t="str">
+      <c r="L74" s="11">
         <f>IF(OR($C74="",K74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K74,FIND("-",K74)-1),"")=AW74,IFERROR(--MID(K74,FIND("-",K74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))-(IFERROR(--MID(K74,FIND("-",K74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))-(IFERROR(--MID(K74,FIND("-",K74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(K74,FIND("-",K74)-1),""))=(AW74))+2*((IFERROR(--MID(K74,FIND("-",K74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M74" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="N74" s="11" t="str">
+      <c r="N74" s="11">
         <f>IF(OR($C74="",M74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M74,FIND("-",M74)-1),"")=AW74,IFERROR(--MID(M74,FIND("-",M74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))-(IFERROR(--MID(M74,FIND("-",M74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))-(IFERROR(--MID(M74,FIND("-",M74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(M74,FIND("-",M74)-1),""))=(AW74))+2*((IFERROR(--MID(M74,FIND("-",M74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P74" s="11" t="str">
+      <c r="P74" s="11">
         <f>IF(OR($C74="",O74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O74,FIND("-",O74)-1),"")=AW74,IFERROR(--MID(O74,FIND("-",O74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))-(IFERROR(--MID(O74,FIND("-",O74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))-(IFERROR(--MID(O74,FIND("-",O74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(O74,FIND("-",O74)-1),""))=(AW74))+2*((IFERROR(--MID(O74,FIND("-",O74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q74" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="R74" s="11" t="str">
+      <c r="R74" s="11">
         <f>IF(OR($C74="",Q74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q74,FIND("-",Q74)-1),"")=AW74,IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))-(IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))-(IFERROR(--MID(Q74,FIND("-",Q74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(Q74,FIND("-",Q74)-1),""))=(AW74))+2*((IFERROR(--MID(Q74,FIND("-",Q74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S74" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="T74" s="11" t="str">
+      <c r="T74" s="11">
         <f>IF(OR($C74="",S74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S74,FIND("-",S74)-1),"")=AW74,IFERROR(--MID(S74,FIND("-",S74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))-(IFERROR(--MID(S74,FIND("-",S74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))-(IFERROR(--MID(S74,FIND("-",S74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(S74,FIND("-",S74)-1),""))=(AW74))+2*((IFERROR(--MID(S74,FIND("-",S74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V74" s="11" t="str">
+      <c r="V74" s="11">
         <f>IF(OR($C74="",U74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U74,FIND("-",U74)-1),"")=AW74,IFERROR(--MID(U74,FIND("-",U74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))-(IFERROR(--MID(U74,FIND("-",U74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))-(IFERROR(--MID(U74,FIND("-",U74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(U74,FIND("-",U74)-1),""))=(AW74))+2*((IFERROR(--MID(U74,FIND("-",U74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X74" s="11" t="str">
+      <c r="X74" s="11">
         <f>IF(OR($C74="",W74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W74,FIND("-",W74)-1),"")=AW74,IFERROR(--MID(W74,FIND("-",W74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))-(IFERROR(--MID(W74,FIND("-",W74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))-(IFERROR(--MID(W74,FIND("-",W74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(W74,FIND("-",W74)-1),""))=(AW74))+2*((IFERROR(--MID(W74,FIND("-",W74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z74" s="11" t="str">
+      <c r="Z74" s="11">
         <f>IF(OR($C74="",Y74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y74,FIND("-",Y74)-1),"")=AW74,IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))-(IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))-(IFERROR(--MID(Y74,FIND("-",Y74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(Y74,FIND("-",Y74)-1),""))=(AW74))+2*((IFERROR(--MID(Y74,FIND("-",Y74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA74" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AB74" s="11" t="str">
+      <c r="AB74" s="11">
         <f>IF(OR($C74="",AA74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA74,FIND("-",AA74)-1),"")=AW74,IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))-(IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))-(IFERROR(--MID(AA74,FIND("-",AA74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AA74,FIND("-",AA74)-1),""))=(AW74))+2*((IFERROR(--MID(AA74,FIND("-",AA74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AD74" s="11" t="str">
+      <c r="AD74" s="11">
         <f>IF(OR($C74="",AC74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC74,FIND("-",AC74)-1),"")=AW74,IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))-(IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))-(IFERROR(--MID(AC74,FIND("-",AC74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AC74,FIND("-",AC74)-1),""))=(AW74))+2*((IFERROR(--MID(AC74,FIND("-",AC74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF74" s="11" t="str">
+      <c r="AF74" s="11">
         <f>IF(OR($C74="",AE74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE74,FIND("-",AE74)-1),"")=AW74,IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))-(IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))-(IFERROR(--MID(AE74,FIND("-",AE74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AE74,FIND("-",AE74)-1),""))=(AW74))+2*((IFERROR(--MID(AE74,FIND("-",AE74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH74" s="11" t="str">
+      <c r="AH74" s="11">
         <f>IF(OR($C74="",AG74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG74,FIND("-",AG74)-1),"")=AW74,IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))-(IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))-(IFERROR(--MID(AG74,FIND("-",AG74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AG74,FIND("-",AG74)-1),""))=(AW74))+2*((IFERROR(--MID(AG74,FIND("-",AG74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AI74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AJ74" s="11" t="str">
+      <c r="AJ74" s="11">
         <f>IF(OR($C74="",AI74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI74,FIND("-",AI74)-1),"")=AW74,IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))-(IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))-(IFERROR(--MID(AI74,FIND("-",AI74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AI74,FIND("-",AI74)-1),""))=(AW74))+2*((IFERROR(--MID(AI74,FIND("-",AI74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK74" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AL74" s="11" t="str">
+      <c r="AL74" s="11">
         <f>IF(OR($C74="",AK74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK74,FIND("-",AK74)-1),"")=AW74,IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))-(IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))-(IFERROR(--MID(AK74,FIND("-",AK74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AK74,FIND("-",AK74)-1),""))=(AW74))+2*((IFERROR(--MID(AK74,FIND("-",AK74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM74" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AN74" s="11" t="str">
+      <c r="AN74" s="11">
         <f>IF(OR($C74="",AM74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM74,FIND("-",AM74)-1),"")=AW74,IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))-(IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))-(IFERROR(--MID(AM74,FIND("-",AM74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AM74,FIND("-",AM74)-1),""))=(AW74))+2*((IFERROR(--MID(AM74,FIND("-",AM74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP74" s="11" t="str">
+      <c r="AP74" s="11">
         <f>IF(OR($C74="",AO74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO74,FIND("-",AO74)-1),"")=AW74,IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))-(IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))-(IFERROR(--MID(AO74,FIND("-",AO74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AO74,FIND("-",AO74)-1),""))=(AW74))+2*((IFERROR(--MID(AO74,FIND("-",AO74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ74" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AR74" s="11" t="str">
+      <c r="AR74" s="11">
         <f>IF(OR($C74="",AQ74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),"")=AW74,IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))-(IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))-(IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AQ74,FIND("-",AQ74)-1),""))=(AW74))+2*((IFERROR(--MID(AQ74,FIND("-",AQ74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS74" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT74" s="11" t="str">
+      <c r="AT74" s="11">
         <f>IF(OR($C74="",AS74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS74,FIND("-",AS74)-1),"")=AW74,IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))-(IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))-(IFERROR(--MID(AS74,FIND("-",AS74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AS74,FIND("-",AS74)-1),""))=(AW74))+2*((IFERROR(--MID(AS74,FIND("-",AS74)+1,99),""))=(AX74))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU74" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AV74" s="11" t="str">
+      <c r="AV74" s="11">
         <f>IF(OR($C74="",AU74=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU74,FIND("-",AU74)-1),"")=AW74,IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")=AX74),10,5*(SIGN((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))-(IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")))=SIGN((AW74)-(AX74)))+2*(((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))-(IFERROR(--MID(AU74,FIND("-",AU74)+1,99),"")))=((AW74)-(AX74)))+2*((IFERROR(--LEFT(AU74,FIND("-",AU74)-1),""))=(AW74))+2*((IFERROR(--MID(AU74,FIND("-",AU74)+1,99),""))=(AX74))),""))</f>
-        <v/>
-      </c>
-      <c r="AW74" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW74" s="11">
         <f>IF($C74="","",IFERROR(--LEFT($C74,FIND("-",$C74)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX74" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX74" s="11">
         <f>IF($C74="","",IFERROR(--MID($C74,FIND("-",$C74)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -11643,56 +11647,56 @@
       <c r="AX75" s="12"/>
     </row>
     <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="44" t="s">
+      <c r="A76" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="46"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="46"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="45"/>
-      <c r="S76" s="46"/>
-      <c r="T76" s="45"/>
-      <c r="U76" s="46"/>
-      <c r="V76" s="45"/>
-      <c r="W76" s="46"/>
-      <c r="X76" s="45"/>
-      <c r="Y76" s="46"/>
-      <c r="Z76" s="45"/>
-      <c r="AA76" s="46"/>
-      <c r="AB76" s="45"/>
-      <c r="AC76" s="46"/>
-      <c r="AD76" s="45"/>
-      <c r="AE76" s="46"/>
-      <c r="AF76" s="45"/>
-      <c r="AG76" s="46"/>
-      <c r="AH76" s="45"/>
-      <c r="AI76" s="46"/>
-      <c r="AJ76" s="45"/>
-      <c r="AK76" s="46"/>
-      <c r="AL76" s="45"/>
-      <c r="AM76" s="46"/>
-      <c r="AN76" s="45"/>
-      <c r="AO76" s="46"/>
-      <c r="AP76" s="45"/>
-      <c r="AQ76" s="45"/>
-      <c r="AR76" s="45"/>
-      <c r="AS76" s="45"/>
-      <c r="AT76" s="45"/>
-      <c r="AU76" s="46"/>
-      <c r="AV76" s="47"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="41"/>
+      <c r="L76" s="40"/>
+      <c r="M76" s="41"/>
+      <c r="N76" s="40"/>
+      <c r="O76" s="41"/>
+      <c r="P76" s="40"/>
+      <c r="Q76" s="41"/>
+      <c r="R76" s="40"/>
+      <c r="S76" s="41"/>
+      <c r="T76" s="40"/>
+      <c r="U76" s="41"/>
+      <c r="V76" s="40"/>
+      <c r="W76" s="41"/>
+      <c r="X76" s="40"/>
+      <c r="Y76" s="41"/>
+      <c r="Z76" s="40"/>
+      <c r="AA76" s="41"/>
+      <c r="AB76" s="40"/>
+      <c r="AC76" s="41"/>
+      <c r="AD76" s="40"/>
+      <c r="AE76" s="41"/>
+      <c r="AF76" s="40"/>
+      <c r="AG76" s="41"/>
+      <c r="AH76" s="40"/>
+      <c r="AI76" s="41"/>
+      <c r="AJ76" s="40"/>
+      <c r="AK76" s="41"/>
+      <c r="AL76" s="40"/>
+      <c r="AM76" s="41"/>
+      <c r="AN76" s="40"/>
+      <c r="AO76" s="41"/>
+      <c r="AP76" s="40"/>
+      <c r="AQ76" s="40"/>
+      <c r="AR76" s="40"/>
+      <c r="AS76" s="40"/>
+      <c r="AT76" s="40"/>
+      <c r="AU76" s="41"/>
+      <c r="AV76" s="42"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
@@ -11703,171 +11707,173 @@
       <c r="B77" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="10" t="s">
+        <v>45</v>
+      </c>
       <c r="D77" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F77" s="11" t="str">
+      <c r="F77" s="11">
         <f>IF(OR($C77="",E77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E77,FIND("-",E77)-1),"")=AW77,IFERROR(--MID(E77,FIND("-",E77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))-(IFERROR(--MID(E77,FIND("-",E77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))-(IFERROR(--MID(E77,FIND("-",E77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(E77,FIND("-",E77)-1),""))=(AW77))+2*((IFERROR(--MID(E77,FIND("-",E77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H77" s="11" t="str">
+      <c r="H77" s="11">
         <f>IF(OR($C77="",G77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G77,FIND("-",G77)-1),"")=AW77,IFERROR(--MID(G77,FIND("-",G77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))-(IFERROR(--MID(G77,FIND("-",G77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))-(IFERROR(--MID(G77,FIND("-",G77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(G77,FIND("-",G77)-1),""))=(AW77))+2*((IFERROR(--MID(G77,FIND("-",G77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J77" s="11" t="str">
+      <c r="J77" s="11">
         <f>IF(OR($C77="",I77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I77,FIND("-",I77)-1),"")=AW77,IFERROR(--MID(I77,FIND("-",I77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))-(IFERROR(--MID(I77,FIND("-",I77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))-(IFERROR(--MID(I77,FIND("-",I77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(I77,FIND("-",I77)-1),""))=(AW77))+2*((IFERROR(--MID(I77,FIND("-",I77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="K77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L77" s="11" t="str">
+      <c r="L77" s="11">
         <f>IF(OR($C77="",K77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K77,FIND("-",K77)-1),"")=AW77,IFERROR(--MID(K77,FIND("-",K77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))-(IFERROR(--MID(K77,FIND("-",K77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))-(IFERROR(--MID(K77,FIND("-",K77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(K77,FIND("-",K77)-1),""))=(AW77))+2*((IFERROR(--MID(K77,FIND("-",K77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N77" s="11" t="str">
+      <c r="N77" s="11">
         <f>IF(OR($C77="",M77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M77,FIND("-",M77)-1),"")=AW77,IFERROR(--MID(M77,FIND("-",M77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))-(IFERROR(--MID(M77,FIND("-",M77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))-(IFERROR(--MID(M77,FIND("-",M77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(M77,FIND("-",M77)-1),""))=(AW77))+2*((IFERROR(--MID(M77,FIND("-",M77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="P77" s="11" t="str">
+      <c r="P77" s="11">
         <f>IF(OR($C77="",O77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O77,FIND("-",O77)-1),"")=AW77,IFERROR(--MID(O77,FIND("-",O77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))-(IFERROR(--MID(O77,FIND("-",O77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))-(IFERROR(--MID(O77,FIND("-",O77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(O77,FIND("-",O77)-1),""))=(AW77))+2*((IFERROR(--MID(O77,FIND("-",O77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="R77" s="11" t="str">
+      <c r="R77" s="11">
         <f>IF(OR($C77="",Q77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q77,FIND("-",Q77)-1),"")=AW77,IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))-(IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))-(IFERROR(--MID(Q77,FIND("-",Q77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(Q77,FIND("-",Q77)-1),""))=(AW77))+2*((IFERROR(--MID(Q77,FIND("-",Q77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S77" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T77" s="11" t="str">
+      <c r="T77" s="11">
         <f>IF(OR($C77="",S77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S77,FIND("-",S77)-1),"")=AW77,IFERROR(--MID(S77,FIND("-",S77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))-(IFERROR(--MID(S77,FIND("-",S77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))-(IFERROR(--MID(S77,FIND("-",S77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(S77,FIND("-",S77)-1),""))=(AW77))+2*((IFERROR(--MID(S77,FIND("-",S77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V77" s="11" t="str">
+      <c r="V77" s="11">
         <f>IF(OR($C77="",U77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U77,FIND("-",U77)-1),"")=AW77,IFERROR(--MID(U77,FIND("-",U77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))-(IFERROR(--MID(U77,FIND("-",U77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))-(IFERROR(--MID(U77,FIND("-",U77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(U77,FIND("-",U77)-1),""))=(AW77))+2*((IFERROR(--MID(U77,FIND("-",U77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="X77" s="11" t="str">
+      <c r="X77" s="11">
         <f>IF(OR($C77="",W77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W77,FIND("-",W77)-1),"")=AW77,IFERROR(--MID(W77,FIND("-",W77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))-(IFERROR(--MID(W77,FIND("-",W77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))-(IFERROR(--MID(W77,FIND("-",W77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(W77,FIND("-",W77)-1),""))=(AW77))+2*((IFERROR(--MID(W77,FIND("-",W77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z77" s="11" t="str">
+      <c r="Z77" s="11">
         <f>IF(OR($C77="",Y77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y77,FIND("-",Y77)-1),"")=AW77,IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))-(IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))-(IFERROR(--MID(Y77,FIND("-",Y77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(Y77,FIND("-",Y77)-1),""))=(AW77))+2*((IFERROR(--MID(Y77,FIND("-",Y77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AB77" s="11" t="str">
+      <c r="AB77" s="11">
         <f>IF(OR($C77="",AA77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA77,FIND("-",AA77)-1),"")=AW77,IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))-(IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))-(IFERROR(--MID(AA77,FIND("-",AA77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AA77,FIND("-",AA77)-1),""))=(AW77))+2*((IFERROR(--MID(AA77,FIND("-",AA77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC77" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="AD77" s="11" t="str">
+      <c r="AD77" s="11">
         <f>IF(OR($C77="",AC77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC77,FIND("-",AC77)-1),"")=AW77,IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))-(IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))-(IFERROR(--MID(AC77,FIND("-",AC77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AC77,FIND("-",AC77)-1),""))=(AW77))+2*((IFERROR(--MID(AC77,FIND("-",AC77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF77" s="11" t="str">
+      <c r="AF77" s="11">
         <f>IF(OR($C77="",AE77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE77,FIND("-",AE77)-1),"")=AW77,IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))-(IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))-(IFERROR(--MID(AE77,FIND("-",AE77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AE77,FIND("-",AE77)-1),""))=(AW77))+2*((IFERROR(--MID(AE77,FIND("-",AE77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH77" s="11" t="str">
+      <c r="AH77" s="11">
         <f>IF(OR($C77="",AG77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG77,FIND("-",AG77)-1),"")=AW77,IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))-(IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))-(IFERROR(--MID(AG77,FIND("-",AG77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AG77,FIND("-",AG77)-1),""))=(AW77))+2*((IFERROR(--MID(AG77,FIND("-",AG77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI77" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AJ77" s="11" t="str">
+      <c r="AJ77" s="11">
         <f>IF(OR($C77="",AI77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI77,FIND("-",AI77)-1),"")=AW77,IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))-(IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))-(IFERROR(--MID(AI77,FIND("-",AI77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AI77,FIND("-",AI77)-1),""))=(AW77))+2*((IFERROR(--MID(AI77,FIND("-",AI77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL77" s="11" t="str">
+      <c r="AL77" s="11">
         <f>IF(OR($C77="",AK77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK77,FIND("-",AK77)-1),"")=AW77,IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))-(IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))-(IFERROR(--MID(AK77,FIND("-",AK77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AK77,FIND("-",AK77)-1),""))=(AW77))+2*((IFERROR(--MID(AK77,FIND("-",AK77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM77" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AN77" s="11" t="str">
+      <c r="AN77" s="11">
         <f>IF(OR($C77="",AM77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM77,FIND("-",AM77)-1),"")=AW77,IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))-(IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))-(IFERROR(--MID(AM77,FIND("-",AM77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AM77,FIND("-",AM77)-1),""))=(AW77))+2*((IFERROR(--MID(AM77,FIND("-",AM77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AP77" s="11" t="str">
+      <c r="AP77" s="11">
         <f>IF(OR($C77="",AO77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO77,FIND("-",AO77)-1),"")=AW77,IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))-(IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))-(IFERROR(--MID(AO77,FIND("-",AO77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AO77,FIND("-",AO77)-1),""))=(AW77))+2*((IFERROR(--MID(AO77,FIND("-",AO77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ77" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR77" s="11" t="str">
+      <c r="AR77" s="11">
         <f>IF(OR($C77="",AQ77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),"")=AW77,IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))-(IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))-(IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AQ77,FIND("-",AQ77)-1),""))=(AW77))+2*((IFERROR(--MID(AQ77,FIND("-",AQ77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS77" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT77" s="11" t="str">
+      <c r="AT77" s="11">
         <f>IF(OR($C77="",AS77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS77,FIND("-",AS77)-1),"")=AW77,IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))-(IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))-(IFERROR(--MID(AS77,FIND("-",AS77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AS77,FIND("-",AS77)-1),""))=(AW77))+2*((IFERROR(--MID(AS77,FIND("-",AS77)+1,99),""))=(AX77))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU77" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AV77" s="11" t="str">
+      <c r="AV77" s="11">
         <f>IF(OR($C77="",AU77=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU77,FIND("-",AU77)-1),"")=AW77,IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")=AX77),10,5*(SIGN((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))-(IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")))=SIGN((AW77)-(AX77)))+2*(((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))-(IFERROR(--MID(AU77,FIND("-",AU77)+1,99),"")))=((AW77)-(AX77)))+2*((IFERROR(--LEFT(AU77,FIND("-",AU77)-1),""))=(AW77))+2*((IFERROR(--MID(AU77,FIND("-",AU77)+1,99),""))=(AX77))),""))</f>
-        <v/>
-      </c>
-      <c r="AW77" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW77" s="11">
         <f>IF($C77="","",IFERROR(--LEFT($C77,FIND("-",$C77)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX77" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX77" s="11">
         <f>IF($C77="","",IFERROR(--MID($C77,FIND("-",$C77)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -11877,171 +11883,173 @@
       <c r="B78" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D78" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F78" s="11" t="str">
+      <c r="F78" s="11">
         <f>IF(OR($C78="",E78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E78,FIND("-",E78)-1),"")=AW78,IFERROR(--MID(E78,FIND("-",E78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))-(IFERROR(--MID(E78,FIND("-",E78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))-(IFERROR(--MID(E78,FIND("-",E78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(E78,FIND("-",E78)-1),""))=(AW78))+2*((IFERROR(--MID(E78,FIND("-",E78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H78" s="11" t="str">
+      <c r="H78" s="11">
         <f>IF(OR($C78="",G78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G78,FIND("-",G78)-1),"")=AW78,IFERROR(--MID(G78,FIND("-",G78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))-(IFERROR(--MID(G78,FIND("-",G78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))-(IFERROR(--MID(G78,FIND("-",G78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(G78,FIND("-",G78)-1),""))=(AW78))+2*((IFERROR(--MID(G78,FIND("-",G78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J78" s="11" t="str">
+      <c r="J78" s="11">
         <f>IF(OR($C78="",I78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I78,FIND("-",I78)-1),"")=AW78,IFERROR(--MID(I78,FIND("-",I78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))-(IFERROR(--MID(I78,FIND("-",I78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))-(IFERROR(--MID(I78,FIND("-",I78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(I78,FIND("-",I78)-1),""))=(AW78))+2*((IFERROR(--MID(I78,FIND("-",I78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L78" s="11" t="str">
+      <c r="L78" s="11">
         <f>IF(OR($C78="",K78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K78,FIND("-",K78)-1),"")=AW78,IFERROR(--MID(K78,FIND("-",K78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))-(IFERROR(--MID(K78,FIND("-",K78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))-(IFERROR(--MID(K78,FIND("-",K78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(K78,FIND("-",K78)-1),""))=(AW78))+2*((IFERROR(--MID(K78,FIND("-",K78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="M78" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="N78" s="11" t="str">
+      <c r="N78" s="11">
         <f>IF(OR($C78="",M78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M78,FIND("-",M78)-1),"")=AW78,IFERROR(--MID(M78,FIND("-",M78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))-(IFERROR(--MID(M78,FIND("-",M78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))-(IFERROR(--MID(M78,FIND("-",M78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(M78,FIND("-",M78)-1),""))=(AW78))+2*((IFERROR(--MID(M78,FIND("-",M78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O78" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="P78" s="11" t="str">
+      <c r="P78" s="11">
         <f>IF(OR($C78="",O78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O78,FIND("-",O78)-1),"")=AW78,IFERROR(--MID(O78,FIND("-",O78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))-(IFERROR(--MID(O78,FIND("-",O78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))-(IFERROR(--MID(O78,FIND("-",O78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(O78,FIND("-",O78)-1),""))=(AW78))+2*((IFERROR(--MID(O78,FIND("-",O78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="R78" s="11" t="str">
+      <c r="R78" s="11">
         <f>IF(OR($C78="",Q78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q78,FIND("-",Q78)-1),"")=AW78,IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))-(IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))-(IFERROR(--MID(Q78,FIND("-",Q78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(Q78,FIND("-",Q78)-1),""))=(AW78))+2*((IFERROR(--MID(Q78,FIND("-",Q78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S78" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T78" s="11" t="str">
+      <c r="T78" s="11">
         <f>IF(OR($C78="",S78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S78,FIND("-",S78)-1),"")=AW78,IFERROR(--MID(S78,FIND("-",S78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))-(IFERROR(--MID(S78,FIND("-",S78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))-(IFERROR(--MID(S78,FIND("-",S78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(S78,FIND("-",S78)-1),""))=(AW78))+2*((IFERROR(--MID(S78,FIND("-",S78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="V78" s="11" t="str">
+      <c r="V78" s="11">
         <f>IF(OR($C78="",U78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U78,FIND("-",U78)-1),"")=AW78,IFERROR(--MID(U78,FIND("-",U78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))-(IFERROR(--MID(U78,FIND("-",U78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))-(IFERROR(--MID(U78,FIND("-",U78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(U78,FIND("-",U78)-1),""))=(AW78))+2*((IFERROR(--MID(U78,FIND("-",U78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X78" s="11" t="str">
+      <c r="X78" s="11">
         <f>IF(OR($C78="",W78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W78,FIND("-",W78)-1),"")=AW78,IFERROR(--MID(W78,FIND("-",W78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))-(IFERROR(--MID(W78,FIND("-",W78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))-(IFERROR(--MID(W78,FIND("-",W78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(W78,FIND("-",W78)-1),""))=(AW78))+2*((IFERROR(--MID(W78,FIND("-",W78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y78" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z78" s="11" t="str">
+      <c r="Z78" s="11">
         <f>IF(OR($C78="",Y78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y78,FIND("-",Y78)-1),"")=AW78,IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))-(IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))-(IFERROR(--MID(Y78,FIND("-",Y78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(Y78,FIND("-",Y78)-1),""))=(AW78))+2*((IFERROR(--MID(Y78,FIND("-",Y78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA78" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB78" s="11" t="str">
+      <c r="AB78" s="11">
         <f>IF(OR($C78="",AA78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA78,FIND("-",AA78)-1),"")=AW78,IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))-(IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))-(IFERROR(--MID(AA78,FIND("-",AA78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AA78,FIND("-",AA78)-1),""))=(AW78))+2*((IFERROR(--MID(AA78,FIND("-",AA78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC78" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="AD78" s="11" t="str">
+      <c r="AD78" s="11">
         <f>IF(OR($C78="",AC78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC78,FIND("-",AC78)-1),"")=AW78,IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))-(IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))-(IFERROR(--MID(AC78,FIND("-",AC78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AC78,FIND("-",AC78)-1),""))=(AW78))+2*((IFERROR(--MID(AC78,FIND("-",AC78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF78" s="11" t="str">
+      <c r="AF78" s="11">
         <f>IF(OR($C78="",AE78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE78,FIND("-",AE78)-1),"")=AW78,IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))-(IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))-(IFERROR(--MID(AE78,FIND("-",AE78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AE78,FIND("-",AE78)-1),""))=(AW78))+2*((IFERROR(--MID(AE78,FIND("-",AE78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AH78" s="11" t="str">
+      <c r="AH78" s="11">
         <f>IF(OR($C78="",AG78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG78,FIND("-",AG78)-1),"")=AW78,IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))-(IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))-(IFERROR(--MID(AG78,FIND("-",AG78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AG78,FIND("-",AG78)-1),""))=(AW78))+2*((IFERROR(--MID(AG78,FIND("-",AG78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI78" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AJ78" s="11" t="str">
+      <c r="AJ78" s="11">
         <f>IF(OR($C78="",AI78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI78,FIND("-",AI78)-1),"")=AW78,IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))-(IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))-(IFERROR(--MID(AI78,FIND("-",AI78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AI78,FIND("-",AI78)-1),""))=(AW78))+2*((IFERROR(--MID(AI78,FIND("-",AI78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AK78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL78" s="11" t="str">
+      <c r="AL78" s="11">
         <f>IF(OR($C78="",AK78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK78,FIND("-",AK78)-1),"")=AW78,IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))-(IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))-(IFERROR(--MID(AK78,FIND("-",AK78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AK78,FIND("-",AK78)-1),""))=(AW78))+2*((IFERROR(--MID(AK78,FIND("-",AK78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM78" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN78" s="11" t="str">
+      <c r="AN78" s="11">
         <f>IF(OR($C78="",AM78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM78,FIND("-",AM78)-1),"")=AW78,IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))-(IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))-(IFERROR(--MID(AM78,FIND("-",AM78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AM78,FIND("-",AM78)-1),""))=(AW78))+2*((IFERROR(--MID(AM78,FIND("-",AM78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP78" s="11" t="str">
+      <c r="AP78" s="11">
         <f>IF(OR($C78="",AO78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO78,FIND("-",AO78)-1),"")=AW78,IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))-(IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))-(IFERROR(--MID(AO78,FIND("-",AO78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AO78,FIND("-",AO78)-1),""))=(AW78))+2*((IFERROR(--MID(AO78,FIND("-",AO78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ78" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR78" s="11" t="str">
+      <c r="AR78" s="11">
         <f>IF(OR($C78="",AQ78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),"")=AW78,IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))-(IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))-(IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AQ78,FIND("-",AQ78)-1),""))=(AW78))+2*((IFERROR(--MID(AQ78,FIND("-",AQ78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS78" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT78" s="11" t="str">
+      <c r="AT78" s="11">
         <f>IF(OR($C78="",AS78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS78,FIND("-",AS78)-1),"")=AW78,IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))-(IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))-(IFERROR(--MID(AS78,FIND("-",AS78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AS78,FIND("-",AS78)-1),""))=(AW78))+2*((IFERROR(--MID(AS78,FIND("-",AS78)+1,99),""))=(AX78))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AU78" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV78" s="11" t="str">
+      <c r="AV78" s="11">
         <f>IF(OR($C78="",AU78=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU78,FIND("-",AU78)-1),"")=AW78,IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")=AX78),10,5*(SIGN((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))-(IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")))=SIGN((AW78)-(AX78)))+2*(((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))-(IFERROR(--MID(AU78,FIND("-",AU78)+1,99),"")))=((AW78)-(AX78)))+2*((IFERROR(--LEFT(AU78,FIND("-",AU78)-1),""))=(AW78))+2*((IFERROR(--MID(AU78,FIND("-",AU78)+1,99),""))=(AX78))),""))</f>
-        <v/>
-      </c>
-      <c r="AW78" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW78" s="11">
         <f>IF($C78="","",IFERROR(--LEFT($C78,FIND("-",$C78)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX78" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX78" s="11">
         <f>IF($C78="","",IFERROR(--MID($C78,FIND("-",$C78)+1,99),""))</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -12451,56 +12459,56 @@
       <c r="AX81" s="12"/>
     </row>
     <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="44" t="s">
+      <c r="A82" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="45"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="46"/>
-      <c r="N82" s="45"/>
-      <c r="O82" s="46"/>
-      <c r="P82" s="45"/>
-      <c r="Q82" s="46"/>
-      <c r="R82" s="45"/>
-      <c r="S82" s="46"/>
-      <c r="T82" s="45"/>
-      <c r="U82" s="46"/>
-      <c r="V82" s="45"/>
-      <c r="W82" s="46"/>
-      <c r="X82" s="45"/>
-      <c r="Y82" s="46"/>
-      <c r="Z82" s="45"/>
-      <c r="AA82" s="46"/>
-      <c r="AB82" s="45"/>
-      <c r="AC82" s="46"/>
-      <c r="AD82" s="45"/>
-      <c r="AE82" s="46"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="46"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
-      <c r="AJ82" s="45"/>
-      <c r="AK82" s="46"/>
-      <c r="AL82" s="45"/>
-      <c r="AM82" s="46"/>
-      <c r="AN82" s="45"/>
-      <c r="AO82" s="46"/>
-      <c r="AP82" s="45"/>
-      <c r="AQ82" s="45"/>
-      <c r="AR82" s="45"/>
-      <c r="AS82" s="45"/>
-      <c r="AT82" s="45"/>
-      <c r="AU82" s="46"/>
-      <c r="AV82" s="47"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="41"/>
+      <c r="L82" s="40"/>
+      <c r="M82" s="41"/>
+      <c r="N82" s="40"/>
+      <c r="O82" s="41"/>
+      <c r="P82" s="40"/>
+      <c r="Q82" s="41"/>
+      <c r="R82" s="40"/>
+      <c r="S82" s="41"/>
+      <c r="T82" s="40"/>
+      <c r="U82" s="41"/>
+      <c r="V82" s="40"/>
+      <c r="W82" s="41"/>
+      <c r="X82" s="40"/>
+      <c r="Y82" s="41"/>
+      <c r="Z82" s="40"/>
+      <c r="AA82" s="41"/>
+      <c r="AB82" s="40"/>
+      <c r="AC82" s="41"/>
+      <c r="AD82" s="40"/>
+      <c r="AE82" s="41"/>
+      <c r="AF82" s="40"/>
+      <c r="AG82" s="41"/>
+      <c r="AH82" s="40"/>
+      <c r="AI82" s="41"/>
+      <c r="AJ82" s="40"/>
+      <c r="AK82" s="41"/>
+      <c r="AL82" s="40"/>
+      <c r="AM82" s="41"/>
+      <c r="AN82" s="40"/>
+      <c r="AO82" s="41"/>
+      <c r="AP82" s="40"/>
+      <c r="AQ82" s="40"/>
+      <c r="AR82" s="40"/>
+      <c r="AS82" s="40"/>
+      <c r="AT82" s="40"/>
+      <c r="AU82" s="41"/>
+      <c r="AV82" s="42"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
@@ -13607,56 +13615,56 @@
       <c r="AX89" s="12"/>
     </row>
     <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="44" t="s">
+      <c r="A90" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="45"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="45"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="45"/>
-      <c r="M90" s="46"/>
-      <c r="N90" s="45"/>
-      <c r="O90" s="46"/>
-      <c r="P90" s="45"/>
-      <c r="Q90" s="46"/>
-      <c r="R90" s="45"/>
-      <c r="S90" s="46"/>
-      <c r="T90" s="45"/>
-      <c r="U90" s="46"/>
-      <c r="V90" s="45"/>
-      <c r="W90" s="46"/>
-      <c r="X90" s="45"/>
-      <c r="Y90" s="46"/>
-      <c r="Z90" s="45"/>
-      <c r="AA90" s="46"/>
-      <c r="AB90" s="45"/>
-      <c r="AC90" s="46"/>
-      <c r="AD90" s="45"/>
-      <c r="AE90" s="46"/>
-      <c r="AF90" s="45"/>
-      <c r="AG90" s="46"/>
-      <c r="AH90" s="45"/>
-      <c r="AI90" s="46"/>
-      <c r="AJ90" s="45"/>
-      <c r="AK90" s="46"/>
-      <c r="AL90" s="45"/>
-      <c r="AM90" s="46"/>
-      <c r="AN90" s="45"/>
-      <c r="AO90" s="46"/>
-      <c r="AP90" s="45"/>
-      <c r="AQ90" s="45"/>
-      <c r="AR90" s="45"/>
-      <c r="AS90" s="45"/>
-      <c r="AT90" s="45"/>
-      <c r="AU90" s="46"/>
-      <c r="AV90" s="47"/>
+      <c r="B90" s="40"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="41"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="41"/>
+      <c r="J90" s="40"/>
+      <c r="K90" s="41"/>
+      <c r="L90" s="40"/>
+      <c r="M90" s="41"/>
+      <c r="N90" s="40"/>
+      <c r="O90" s="41"/>
+      <c r="P90" s="40"/>
+      <c r="Q90" s="41"/>
+      <c r="R90" s="40"/>
+      <c r="S90" s="41"/>
+      <c r="T90" s="40"/>
+      <c r="U90" s="41"/>
+      <c r="V90" s="40"/>
+      <c r="W90" s="41"/>
+      <c r="X90" s="40"/>
+      <c r="Y90" s="41"/>
+      <c r="Z90" s="40"/>
+      <c r="AA90" s="41"/>
+      <c r="AB90" s="40"/>
+      <c r="AC90" s="41"/>
+      <c r="AD90" s="40"/>
+      <c r="AE90" s="41"/>
+      <c r="AF90" s="40"/>
+      <c r="AG90" s="41"/>
+      <c r="AH90" s="40"/>
+      <c r="AI90" s="41"/>
+      <c r="AJ90" s="40"/>
+      <c r="AK90" s="41"/>
+      <c r="AL90" s="40"/>
+      <c r="AM90" s="41"/>
+      <c r="AN90" s="40"/>
+      <c r="AO90" s="41"/>
+      <c r="AP90" s="40"/>
+      <c r="AQ90" s="40"/>
+      <c r="AR90" s="40"/>
+      <c r="AS90" s="40"/>
+      <c r="AT90" s="40"/>
+      <c r="AU90" s="41"/>
+      <c r="AV90" s="42"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
@@ -14763,56 +14771,56 @@
       <c r="AX97" s="12"/>
     </row>
     <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="44" t="s">
+      <c r="A98" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="45"/>
-      <c r="C98" s="46"/>
-      <c r="D98" s="45"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="45"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="45"/>
-      <c r="I98" s="46"/>
-      <c r="J98" s="45"/>
-      <c r="K98" s="46"/>
-      <c r="L98" s="45"/>
-      <c r="M98" s="46"/>
-      <c r="N98" s="45"/>
-      <c r="O98" s="46"/>
-      <c r="P98" s="45"/>
-      <c r="Q98" s="46"/>
-      <c r="R98" s="45"/>
-      <c r="S98" s="46"/>
-      <c r="T98" s="45"/>
-      <c r="U98" s="46"/>
-      <c r="V98" s="45"/>
-      <c r="W98" s="46"/>
-      <c r="X98" s="45"/>
-      <c r="Y98" s="46"/>
-      <c r="Z98" s="45"/>
-      <c r="AA98" s="46"/>
-      <c r="AB98" s="45"/>
-      <c r="AC98" s="46"/>
-      <c r="AD98" s="45"/>
-      <c r="AE98" s="46"/>
-      <c r="AF98" s="45"/>
-      <c r="AG98" s="46"/>
-      <c r="AH98" s="45"/>
-      <c r="AI98" s="46"/>
-      <c r="AJ98" s="45"/>
-      <c r="AK98" s="46"/>
-      <c r="AL98" s="45"/>
-      <c r="AM98" s="46"/>
-      <c r="AN98" s="45"/>
-      <c r="AO98" s="46"/>
-      <c r="AP98" s="45"/>
-      <c r="AQ98" s="45"/>
-      <c r="AR98" s="45"/>
-      <c r="AS98" s="45"/>
-      <c r="AT98" s="45"/>
-      <c r="AU98" s="46"/>
-      <c r="AV98" s="47"/>
+      <c r="B98" s="40"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="40"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="40"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="41"/>
+      <c r="L98" s="40"/>
+      <c r="M98" s="41"/>
+      <c r="N98" s="40"/>
+      <c r="O98" s="41"/>
+      <c r="P98" s="40"/>
+      <c r="Q98" s="41"/>
+      <c r="R98" s="40"/>
+      <c r="S98" s="41"/>
+      <c r="T98" s="40"/>
+      <c r="U98" s="41"/>
+      <c r="V98" s="40"/>
+      <c r="W98" s="41"/>
+      <c r="X98" s="40"/>
+      <c r="Y98" s="41"/>
+      <c r="Z98" s="40"/>
+      <c r="AA98" s="41"/>
+      <c r="AB98" s="40"/>
+      <c r="AC98" s="41"/>
+      <c r="AD98" s="40"/>
+      <c r="AE98" s="41"/>
+      <c r="AF98" s="40"/>
+      <c r="AG98" s="41"/>
+      <c r="AH98" s="40"/>
+      <c r="AI98" s="41"/>
+      <c r="AJ98" s="40"/>
+      <c r="AK98" s="41"/>
+      <c r="AL98" s="40"/>
+      <c r="AM98" s="41"/>
+      <c r="AN98" s="40"/>
+      <c r="AO98" s="41"/>
+      <c r="AP98" s="40"/>
+      <c r="AQ98" s="40"/>
+      <c r="AR98" s="40"/>
+      <c r="AS98" s="40"/>
+      <c r="AT98" s="40"/>
+      <c r="AU98" s="41"/>
+      <c r="AV98" s="42"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
@@ -15919,56 +15927,56 @@
       <c r="AX105" s="12"/>
     </row>
     <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="44" t="s">
+      <c r="A106" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="45"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="45"/>
-      <c r="E106" s="46"/>
-      <c r="F106" s="45"/>
-      <c r="G106" s="46"/>
-      <c r="H106" s="45"/>
-      <c r="I106" s="46"/>
-      <c r="J106" s="45"/>
-      <c r="K106" s="46"/>
-      <c r="L106" s="45"/>
-      <c r="M106" s="46"/>
-      <c r="N106" s="45"/>
-      <c r="O106" s="46"/>
-      <c r="P106" s="45"/>
-      <c r="Q106" s="46"/>
-      <c r="R106" s="45"/>
-      <c r="S106" s="46"/>
-      <c r="T106" s="45"/>
-      <c r="U106" s="46"/>
-      <c r="V106" s="45"/>
-      <c r="W106" s="46"/>
-      <c r="X106" s="45"/>
-      <c r="Y106" s="46"/>
-      <c r="Z106" s="45"/>
-      <c r="AA106" s="46"/>
-      <c r="AB106" s="45"/>
-      <c r="AC106" s="46"/>
-      <c r="AD106" s="45"/>
-      <c r="AE106" s="46"/>
-      <c r="AF106" s="45"/>
-      <c r="AG106" s="46"/>
-      <c r="AH106" s="45"/>
-      <c r="AI106" s="46"/>
-      <c r="AJ106" s="45"/>
-      <c r="AK106" s="46"/>
-      <c r="AL106" s="45"/>
-      <c r="AM106" s="46"/>
-      <c r="AN106" s="45"/>
-      <c r="AO106" s="46"/>
-      <c r="AP106" s="45"/>
-      <c r="AQ106" s="45"/>
-      <c r="AR106" s="45"/>
-      <c r="AS106" s="45"/>
-      <c r="AT106" s="45"/>
-      <c r="AU106" s="46"/>
-      <c r="AV106" s="47"/>
+      <c r="B106" s="40"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="40"/>
+      <c r="E106" s="41"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="41"/>
+      <c r="H106" s="40"/>
+      <c r="I106" s="41"/>
+      <c r="J106" s="40"/>
+      <c r="K106" s="41"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="41"/>
+      <c r="N106" s="40"/>
+      <c r="O106" s="41"/>
+      <c r="P106" s="40"/>
+      <c r="Q106" s="41"/>
+      <c r="R106" s="40"/>
+      <c r="S106" s="41"/>
+      <c r="T106" s="40"/>
+      <c r="U106" s="41"/>
+      <c r="V106" s="40"/>
+      <c r="W106" s="41"/>
+      <c r="X106" s="40"/>
+      <c r="Y106" s="41"/>
+      <c r="Z106" s="40"/>
+      <c r="AA106" s="41"/>
+      <c r="AB106" s="40"/>
+      <c r="AC106" s="41"/>
+      <c r="AD106" s="40"/>
+      <c r="AE106" s="41"/>
+      <c r="AF106" s="40"/>
+      <c r="AG106" s="41"/>
+      <c r="AH106" s="40"/>
+      <c r="AI106" s="41"/>
+      <c r="AJ106" s="40"/>
+      <c r="AK106" s="41"/>
+      <c r="AL106" s="40"/>
+      <c r="AM106" s="41"/>
+      <c r="AN106" s="40"/>
+      <c r="AO106" s="41"/>
+      <c r="AP106" s="40"/>
+      <c r="AQ106" s="40"/>
+      <c r="AR106" s="40"/>
+      <c r="AS106" s="40"/>
+      <c r="AT106" s="40"/>
+      <c r="AU106" s="41"/>
+      <c r="AV106" s="42"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
@@ -16788,107 +16796,107 @@
       <c r="A113" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="49"/>
-      <c r="C113" s="50"/>
-      <c r="D113" s="49"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="49"/>
-      <c r="G113" s="50"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="50"/>
-      <c r="J113" s="49"/>
-      <c r="K113" s="50"/>
-      <c r="L113" s="49"/>
-      <c r="M113" s="50"/>
-      <c r="N113" s="49"/>
-      <c r="O113" s="50"/>
-      <c r="P113" s="49"/>
-      <c r="Q113" s="50"/>
-      <c r="R113" s="49"/>
-      <c r="S113" s="50"/>
-      <c r="T113" s="49"/>
-      <c r="U113" s="50"/>
-      <c r="V113" s="49"/>
-      <c r="W113" s="50"/>
-      <c r="X113" s="49"/>
-      <c r="Y113" s="50"/>
-      <c r="Z113" s="49"/>
-      <c r="AA113" s="50"/>
-      <c r="AB113" s="49"/>
-      <c r="AC113" s="50"/>
-      <c r="AD113" s="49"/>
-      <c r="AE113" s="50"/>
-      <c r="AF113" s="49"/>
-      <c r="AG113" s="50"/>
-      <c r="AH113" s="49"/>
-      <c r="AI113" s="50"/>
-      <c r="AJ113" s="49"/>
-      <c r="AK113" s="50"/>
-      <c r="AL113" s="49"/>
-      <c r="AM113" s="50"/>
-      <c r="AN113" s="49"/>
-      <c r="AO113" s="50"/>
-      <c r="AP113" s="49"/>
-      <c r="AQ113" s="49"/>
-      <c r="AR113" s="49"/>
-      <c r="AS113" s="49"/>
-      <c r="AT113" s="49"/>
-      <c r="AU113" s="50"/>
-      <c r="AV113" s="43"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="53"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="53"/>
+      <c r="I113" s="54"/>
+      <c r="J113" s="53"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="53"/>
+      <c r="M113" s="54"/>
+      <c r="N113" s="53"/>
+      <c r="O113" s="54"/>
+      <c r="P113" s="53"/>
+      <c r="Q113" s="54"/>
+      <c r="R113" s="53"/>
+      <c r="S113" s="54"/>
+      <c r="T113" s="53"/>
+      <c r="U113" s="54"/>
+      <c r="V113" s="53"/>
+      <c r="W113" s="54"/>
+      <c r="X113" s="53"/>
+      <c r="Y113" s="54"/>
+      <c r="Z113" s="53"/>
+      <c r="AA113" s="54"/>
+      <c r="AB113" s="53"/>
+      <c r="AC113" s="54"/>
+      <c r="AD113" s="53"/>
+      <c r="AE113" s="54"/>
+      <c r="AF113" s="53"/>
+      <c r="AG113" s="54"/>
+      <c r="AH113" s="53"/>
+      <c r="AI113" s="54"/>
+      <c r="AJ113" s="53"/>
+      <c r="AK113" s="54"/>
+      <c r="AL113" s="53"/>
+      <c r="AM113" s="54"/>
+      <c r="AN113" s="53"/>
+      <c r="AO113" s="54"/>
+      <c r="AP113" s="53"/>
+      <c r="AQ113" s="53"/>
+      <c r="AR113" s="53"/>
+      <c r="AS113" s="53"/>
+      <c r="AT113" s="53"/>
+      <c r="AU113" s="54"/>
+      <c r="AV113" s="47"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
     <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="44" t="s">
+      <c r="A114" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="45"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="45"/>
-      <c r="E114" s="46"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="46"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="46"/>
-      <c r="J114" s="45"/>
-      <c r="K114" s="46"/>
-      <c r="L114" s="45"/>
-      <c r="M114" s="46"/>
-      <c r="N114" s="45"/>
-      <c r="O114" s="46"/>
-      <c r="P114" s="45"/>
-      <c r="Q114" s="46"/>
-      <c r="R114" s="45"/>
-      <c r="S114" s="46"/>
-      <c r="T114" s="45"/>
-      <c r="U114" s="46"/>
-      <c r="V114" s="45"/>
-      <c r="W114" s="46"/>
-      <c r="X114" s="45"/>
-      <c r="Y114" s="46"/>
-      <c r="Z114" s="45"/>
-      <c r="AA114" s="46"/>
-      <c r="AB114" s="45"/>
-      <c r="AC114" s="46"/>
-      <c r="AD114" s="45"/>
-      <c r="AE114" s="46"/>
-      <c r="AF114" s="45"/>
-      <c r="AG114" s="46"/>
-      <c r="AH114" s="45"/>
-      <c r="AI114" s="46"/>
-      <c r="AJ114" s="45"/>
-      <c r="AK114" s="46"/>
-      <c r="AL114" s="45"/>
-      <c r="AM114" s="46"/>
-      <c r="AN114" s="45"/>
-      <c r="AO114" s="46"/>
-      <c r="AP114" s="45"/>
-      <c r="AQ114" s="45"/>
-      <c r="AR114" s="45"/>
-      <c r="AS114" s="45"/>
-      <c r="AT114" s="45"/>
-      <c r="AU114" s="46"/>
-      <c r="AV114" s="47"/>
+      <c r="B114" s="40"/>
+      <c r="C114" s="41"/>
+      <c r="D114" s="40"/>
+      <c r="E114" s="41"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="41"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="41"/>
+      <c r="J114" s="40"/>
+      <c r="K114" s="41"/>
+      <c r="L114" s="40"/>
+      <c r="M114" s="41"/>
+      <c r="N114" s="40"/>
+      <c r="O114" s="41"/>
+      <c r="P114" s="40"/>
+      <c r="Q114" s="41"/>
+      <c r="R114" s="40"/>
+      <c r="S114" s="41"/>
+      <c r="T114" s="40"/>
+      <c r="U114" s="41"/>
+      <c r="V114" s="40"/>
+      <c r="W114" s="41"/>
+      <c r="X114" s="40"/>
+      <c r="Y114" s="41"/>
+      <c r="Z114" s="40"/>
+      <c r="AA114" s="41"/>
+      <c r="AB114" s="40"/>
+      <c r="AC114" s="41"/>
+      <c r="AD114" s="40"/>
+      <c r="AE114" s="41"/>
+      <c r="AF114" s="40"/>
+      <c r="AG114" s="41"/>
+      <c r="AH114" s="40"/>
+      <c r="AI114" s="41"/>
+      <c r="AJ114" s="40"/>
+      <c r="AK114" s="41"/>
+      <c r="AL114" s="40"/>
+      <c r="AM114" s="41"/>
+      <c r="AN114" s="40"/>
+      <c r="AO114" s="41"/>
+      <c r="AP114" s="40"/>
+      <c r="AQ114" s="40"/>
+      <c r="AR114" s="40"/>
+      <c r="AS114" s="40"/>
+      <c r="AT114" s="40"/>
+      <c r="AU114" s="41"/>
+      <c r="AV114" s="42"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
@@ -17081,56 +17089,56 @@
       <c r="AX116" s="12"/>
     </row>
     <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="44" t="s">
+      <c r="A117" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="B117" s="45"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="45"/>
-      <c r="E117" s="46"/>
-      <c r="F117" s="45"/>
-      <c r="G117" s="46"/>
-      <c r="H117" s="45"/>
-      <c r="I117" s="46"/>
-      <c r="J117" s="45"/>
-      <c r="K117" s="46"/>
-      <c r="L117" s="45"/>
-      <c r="M117" s="46"/>
-      <c r="N117" s="45"/>
-      <c r="O117" s="46"/>
-      <c r="P117" s="45"/>
-      <c r="Q117" s="46"/>
-      <c r="R117" s="45"/>
-      <c r="S117" s="46"/>
-      <c r="T117" s="45"/>
-      <c r="U117" s="46"/>
-      <c r="V117" s="45"/>
-      <c r="W117" s="46"/>
-      <c r="X117" s="45"/>
-      <c r="Y117" s="46"/>
-      <c r="Z117" s="45"/>
-      <c r="AA117" s="46"/>
-      <c r="AB117" s="45"/>
-      <c r="AC117" s="46"/>
-      <c r="AD117" s="45"/>
-      <c r="AE117" s="46"/>
-      <c r="AF117" s="45"/>
-      <c r="AG117" s="46"/>
-      <c r="AH117" s="45"/>
-      <c r="AI117" s="46"/>
-      <c r="AJ117" s="45"/>
-      <c r="AK117" s="46"/>
-      <c r="AL117" s="45"/>
-      <c r="AM117" s="46"/>
-      <c r="AN117" s="45"/>
-      <c r="AO117" s="46"/>
-      <c r="AP117" s="45"/>
-      <c r="AQ117" s="45"/>
-      <c r="AR117" s="45"/>
-      <c r="AS117" s="45"/>
-      <c r="AT117" s="45"/>
-      <c r="AU117" s="46"/>
-      <c r="AV117" s="47"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="40"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="41"/>
+      <c r="J117" s="40"/>
+      <c r="K117" s="41"/>
+      <c r="L117" s="40"/>
+      <c r="M117" s="41"/>
+      <c r="N117" s="40"/>
+      <c r="O117" s="41"/>
+      <c r="P117" s="40"/>
+      <c r="Q117" s="41"/>
+      <c r="R117" s="40"/>
+      <c r="S117" s="41"/>
+      <c r="T117" s="40"/>
+      <c r="U117" s="41"/>
+      <c r="V117" s="40"/>
+      <c r="W117" s="41"/>
+      <c r="X117" s="40"/>
+      <c r="Y117" s="41"/>
+      <c r="Z117" s="40"/>
+      <c r="AA117" s="41"/>
+      <c r="AB117" s="40"/>
+      <c r="AC117" s="41"/>
+      <c r="AD117" s="40"/>
+      <c r="AE117" s="41"/>
+      <c r="AF117" s="40"/>
+      <c r="AG117" s="41"/>
+      <c r="AH117" s="40"/>
+      <c r="AI117" s="41"/>
+      <c r="AJ117" s="40"/>
+      <c r="AK117" s="41"/>
+      <c r="AL117" s="40"/>
+      <c r="AM117" s="41"/>
+      <c r="AN117" s="40"/>
+      <c r="AO117" s="41"/>
+      <c r="AP117" s="40"/>
+      <c r="AQ117" s="40"/>
+      <c r="AR117" s="40"/>
+      <c r="AS117" s="40"/>
+      <c r="AT117" s="40"/>
+      <c r="AU117" s="41"/>
+      <c r="AV117" s="42"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
@@ -17453,56 +17461,56 @@
       <c r="AX120" s="12"/>
     </row>
     <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="44" t="s">
+      <c r="A121" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="B121" s="45"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="45"/>
-      <c r="E121" s="46"/>
-      <c r="F121" s="45"/>
-      <c r="G121" s="46"/>
-      <c r="H121" s="45"/>
-      <c r="I121" s="46"/>
-      <c r="J121" s="45"/>
-      <c r="K121" s="46"/>
-      <c r="L121" s="45"/>
-      <c r="M121" s="46"/>
-      <c r="N121" s="45"/>
-      <c r="O121" s="46"/>
-      <c r="P121" s="45"/>
-      <c r="Q121" s="46"/>
-      <c r="R121" s="45"/>
-      <c r="S121" s="46"/>
-      <c r="T121" s="45"/>
-      <c r="U121" s="46"/>
-      <c r="V121" s="45"/>
-      <c r="W121" s="46"/>
-      <c r="X121" s="45"/>
-      <c r="Y121" s="46"/>
-      <c r="Z121" s="45"/>
-      <c r="AA121" s="46"/>
-      <c r="AB121" s="45"/>
-      <c r="AC121" s="46"/>
-      <c r="AD121" s="45"/>
-      <c r="AE121" s="46"/>
-      <c r="AF121" s="45"/>
-      <c r="AG121" s="46"/>
-      <c r="AH121" s="45"/>
-      <c r="AI121" s="46"/>
-      <c r="AJ121" s="45"/>
-      <c r="AK121" s="46"/>
-      <c r="AL121" s="45"/>
-      <c r="AM121" s="46"/>
-      <c r="AN121" s="45"/>
-      <c r="AO121" s="46"/>
-      <c r="AP121" s="45"/>
-      <c r="AQ121" s="45"/>
-      <c r="AR121" s="45"/>
-      <c r="AS121" s="45"/>
-      <c r="AT121" s="45"/>
-      <c r="AU121" s="46"/>
-      <c r="AV121" s="47"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="40"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="40"/>
+      <c r="G121" s="41"/>
+      <c r="H121" s="40"/>
+      <c r="I121" s="41"/>
+      <c r="J121" s="40"/>
+      <c r="K121" s="41"/>
+      <c r="L121" s="40"/>
+      <c r="M121" s="41"/>
+      <c r="N121" s="40"/>
+      <c r="O121" s="41"/>
+      <c r="P121" s="40"/>
+      <c r="Q121" s="41"/>
+      <c r="R121" s="40"/>
+      <c r="S121" s="41"/>
+      <c r="T121" s="40"/>
+      <c r="U121" s="41"/>
+      <c r="V121" s="40"/>
+      <c r="W121" s="41"/>
+      <c r="X121" s="40"/>
+      <c r="Y121" s="41"/>
+      <c r="Z121" s="40"/>
+      <c r="AA121" s="41"/>
+      <c r="AB121" s="40"/>
+      <c r="AC121" s="41"/>
+      <c r="AD121" s="40"/>
+      <c r="AE121" s="41"/>
+      <c r="AF121" s="40"/>
+      <c r="AG121" s="41"/>
+      <c r="AH121" s="40"/>
+      <c r="AI121" s="41"/>
+      <c r="AJ121" s="40"/>
+      <c r="AK121" s="41"/>
+      <c r="AL121" s="40"/>
+      <c r="AM121" s="41"/>
+      <c r="AN121" s="40"/>
+      <c r="AO121" s="41"/>
+      <c r="AP121" s="40"/>
+      <c r="AQ121" s="40"/>
+      <c r="AR121" s="40"/>
+      <c r="AS121" s="40"/>
+      <c r="AT121" s="40"/>
+      <c r="AU121" s="41"/>
+      <c r="AV121" s="42"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
@@ -17955,56 +17963,56 @@
       <c r="AX125" s="12"/>
     </row>
     <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="44" t="s">
+      <c r="A126" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="45"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="46"/>
-      <c r="F126" s="45"/>
-      <c r="G126" s="46"/>
-      <c r="H126" s="45"/>
-      <c r="I126" s="46"/>
-      <c r="J126" s="45"/>
-      <c r="K126" s="46"/>
-      <c r="L126" s="45"/>
-      <c r="M126" s="46"/>
-      <c r="N126" s="45"/>
-      <c r="O126" s="46"/>
-      <c r="P126" s="45"/>
-      <c r="Q126" s="46"/>
-      <c r="R126" s="45"/>
-      <c r="S126" s="46"/>
-      <c r="T126" s="45"/>
-      <c r="U126" s="46"/>
-      <c r="V126" s="45"/>
-      <c r="W126" s="46"/>
-      <c r="X126" s="45"/>
-      <c r="Y126" s="46"/>
-      <c r="Z126" s="45"/>
-      <c r="AA126" s="46"/>
-      <c r="AB126" s="45"/>
-      <c r="AC126" s="46"/>
-      <c r="AD126" s="45"/>
-      <c r="AE126" s="46"/>
-      <c r="AF126" s="45"/>
-      <c r="AG126" s="46"/>
-      <c r="AH126" s="45"/>
-      <c r="AI126" s="46"/>
-      <c r="AJ126" s="45"/>
-      <c r="AK126" s="46"/>
-      <c r="AL126" s="45"/>
-      <c r="AM126" s="46"/>
-      <c r="AN126" s="45"/>
-      <c r="AO126" s="46"/>
-      <c r="AP126" s="45"/>
-      <c r="AQ126" s="45"/>
-      <c r="AR126" s="45"/>
-      <c r="AS126" s="45"/>
-      <c r="AT126" s="45"/>
-      <c r="AU126" s="46"/>
-      <c r="AV126" s="47"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="41"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="41"/>
+      <c r="F126" s="40"/>
+      <c r="G126" s="41"/>
+      <c r="H126" s="40"/>
+      <c r="I126" s="41"/>
+      <c r="J126" s="40"/>
+      <c r="K126" s="41"/>
+      <c r="L126" s="40"/>
+      <c r="M126" s="41"/>
+      <c r="N126" s="40"/>
+      <c r="O126" s="41"/>
+      <c r="P126" s="40"/>
+      <c r="Q126" s="41"/>
+      <c r="R126" s="40"/>
+      <c r="S126" s="41"/>
+      <c r="T126" s="40"/>
+      <c r="U126" s="41"/>
+      <c r="V126" s="40"/>
+      <c r="W126" s="41"/>
+      <c r="X126" s="40"/>
+      <c r="Y126" s="41"/>
+      <c r="Z126" s="40"/>
+      <c r="AA126" s="41"/>
+      <c r="AB126" s="40"/>
+      <c r="AC126" s="41"/>
+      <c r="AD126" s="40"/>
+      <c r="AE126" s="41"/>
+      <c r="AF126" s="40"/>
+      <c r="AG126" s="41"/>
+      <c r="AH126" s="40"/>
+      <c r="AI126" s="41"/>
+      <c r="AJ126" s="40"/>
+      <c r="AK126" s="41"/>
+      <c r="AL126" s="40"/>
+      <c r="AM126" s="41"/>
+      <c r="AN126" s="40"/>
+      <c r="AO126" s="41"/>
+      <c r="AP126" s="40"/>
+      <c r="AQ126" s="40"/>
+      <c r="AR126" s="40"/>
+      <c r="AS126" s="40"/>
+      <c r="AT126" s="40"/>
+      <c r="AU126" s="41"/>
+      <c r="AV126" s="42"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
@@ -18457,56 +18465,56 @@
       <c r="AX130" s="12"/>
     </row>
     <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="44" t="s">
+      <c r="A131" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="45"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="45"/>
-      <c r="E131" s="46"/>
-      <c r="F131" s="45"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="45"/>
-      <c r="I131" s="46"/>
-      <c r="J131" s="45"/>
-      <c r="K131" s="46"/>
-      <c r="L131" s="45"/>
-      <c r="M131" s="46"/>
-      <c r="N131" s="45"/>
-      <c r="O131" s="46"/>
-      <c r="P131" s="45"/>
-      <c r="Q131" s="46"/>
-      <c r="R131" s="45"/>
-      <c r="S131" s="46"/>
-      <c r="T131" s="45"/>
-      <c r="U131" s="46"/>
-      <c r="V131" s="45"/>
-      <c r="W131" s="46"/>
-      <c r="X131" s="45"/>
-      <c r="Y131" s="46"/>
-      <c r="Z131" s="45"/>
-      <c r="AA131" s="46"/>
-      <c r="AB131" s="45"/>
-      <c r="AC131" s="46"/>
-      <c r="AD131" s="45"/>
-      <c r="AE131" s="46"/>
-      <c r="AF131" s="45"/>
-      <c r="AG131" s="46"/>
-      <c r="AH131" s="45"/>
-      <c r="AI131" s="46"/>
-      <c r="AJ131" s="45"/>
-      <c r="AK131" s="46"/>
-      <c r="AL131" s="45"/>
-      <c r="AM131" s="46"/>
-      <c r="AN131" s="45"/>
-      <c r="AO131" s="46"/>
-      <c r="AP131" s="45"/>
-      <c r="AQ131" s="45"/>
-      <c r="AR131" s="45"/>
-      <c r="AS131" s="45"/>
-      <c r="AT131" s="45"/>
-      <c r="AU131" s="46"/>
-      <c r="AV131" s="47"/>
+      <c r="B131" s="40"/>
+      <c r="C131" s="41"/>
+      <c r="D131" s="40"/>
+      <c r="E131" s="41"/>
+      <c r="F131" s="40"/>
+      <c r="G131" s="41"/>
+      <c r="H131" s="40"/>
+      <c r="I131" s="41"/>
+      <c r="J131" s="40"/>
+      <c r="K131" s="41"/>
+      <c r="L131" s="40"/>
+      <c r="M131" s="41"/>
+      <c r="N131" s="40"/>
+      <c r="O131" s="41"/>
+      <c r="P131" s="40"/>
+      <c r="Q131" s="41"/>
+      <c r="R131" s="40"/>
+      <c r="S131" s="41"/>
+      <c r="T131" s="40"/>
+      <c r="U131" s="41"/>
+      <c r="V131" s="40"/>
+      <c r="W131" s="41"/>
+      <c r="X131" s="40"/>
+      <c r="Y131" s="41"/>
+      <c r="Z131" s="40"/>
+      <c r="AA131" s="41"/>
+      <c r="AB131" s="40"/>
+      <c r="AC131" s="41"/>
+      <c r="AD131" s="40"/>
+      <c r="AE131" s="41"/>
+      <c r="AF131" s="40"/>
+      <c r="AG131" s="41"/>
+      <c r="AH131" s="40"/>
+      <c r="AI131" s="41"/>
+      <c r="AJ131" s="40"/>
+      <c r="AK131" s="41"/>
+      <c r="AL131" s="40"/>
+      <c r="AM131" s="41"/>
+      <c r="AN131" s="40"/>
+      <c r="AO131" s="41"/>
+      <c r="AP131" s="40"/>
+      <c r="AQ131" s="40"/>
+      <c r="AR131" s="40"/>
+      <c r="AS131" s="40"/>
+      <c r="AT131" s="40"/>
+      <c r="AU131" s="41"/>
+      <c r="AV131" s="42"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
@@ -18829,56 +18837,56 @@
       <c r="AX134" s="12"/>
     </row>
     <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="44" t="s">
+      <c r="A135" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="B135" s="45"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="45"/>
-      <c r="E135" s="46"/>
-      <c r="F135" s="45"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="45"/>
-      <c r="I135" s="46"/>
-      <c r="J135" s="45"/>
-      <c r="K135" s="46"/>
-      <c r="L135" s="45"/>
-      <c r="M135" s="46"/>
-      <c r="N135" s="45"/>
-      <c r="O135" s="46"/>
-      <c r="P135" s="45"/>
-      <c r="Q135" s="46"/>
-      <c r="R135" s="45"/>
-      <c r="S135" s="46"/>
-      <c r="T135" s="45"/>
-      <c r="U135" s="46"/>
-      <c r="V135" s="45"/>
-      <c r="W135" s="46"/>
-      <c r="X135" s="45"/>
-      <c r="Y135" s="46"/>
-      <c r="Z135" s="45"/>
-      <c r="AA135" s="46"/>
-      <c r="AB135" s="45"/>
-      <c r="AC135" s="46"/>
-      <c r="AD135" s="45"/>
-      <c r="AE135" s="46"/>
-      <c r="AF135" s="45"/>
-      <c r="AG135" s="46"/>
-      <c r="AH135" s="45"/>
-      <c r="AI135" s="46"/>
-      <c r="AJ135" s="45"/>
-      <c r="AK135" s="46"/>
-      <c r="AL135" s="45"/>
-      <c r="AM135" s="46"/>
-      <c r="AN135" s="45"/>
-      <c r="AO135" s="46"/>
-      <c r="AP135" s="45"/>
-      <c r="AQ135" s="45"/>
-      <c r="AR135" s="45"/>
-      <c r="AS135" s="45"/>
-      <c r="AT135" s="45"/>
-      <c r="AU135" s="46"/>
-      <c r="AV135" s="47"/>
+      <c r="B135" s="40"/>
+      <c r="C135" s="41"/>
+      <c r="D135" s="40"/>
+      <c r="E135" s="41"/>
+      <c r="F135" s="40"/>
+      <c r="G135" s="41"/>
+      <c r="H135" s="40"/>
+      <c r="I135" s="41"/>
+      <c r="J135" s="40"/>
+      <c r="K135" s="41"/>
+      <c r="L135" s="40"/>
+      <c r="M135" s="41"/>
+      <c r="N135" s="40"/>
+      <c r="O135" s="41"/>
+      <c r="P135" s="40"/>
+      <c r="Q135" s="41"/>
+      <c r="R135" s="40"/>
+      <c r="S135" s="41"/>
+      <c r="T135" s="40"/>
+      <c r="U135" s="41"/>
+      <c r="V135" s="40"/>
+      <c r="W135" s="41"/>
+      <c r="X135" s="40"/>
+      <c r="Y135" s="41"/>
+      <c r="Z135" s="40"/>
+      <c r="AA135" s="41"/>
+      <c r="AB135" s="40"/>
+      <c r="AC135" s="41"/>
+      <c r="AD135" s="40"/>
+      <c r="AE135" s="41"/>
+      <c r="AF135" s="40"/>
+      <c r="AG135" s="41"/>
+      <c r="AH135" s="40"/>
+      <c r="AI135" s="41"/>
+      <c r="AJ135" s="40"/>
+      <c r="AK135" s="41"/>
+      <c r="AL135" s="40"/>
+      <c r="AM135" s="41"/>
+      <c r="AN135" s="40"/>
+      <c r="AO135" s="41"/>
+      <c r="AP135" s="40"/>
+      <c r="AQ135" s="40"/>
+      <c r="AR135" s="40"/>
+      <c r="AS135" s="40"/>
+      <c r="AT135" s="40"/>
+      <c r="AU135" s="41"/>
+      <c r="AV135" s="42"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
@@ -19331,56 +19339,56 @@
       <c r="AX139" s="12"/>
     </row>
     <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="44" t="s">
+      <c r="A140" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B140" s="45"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="45"/>
-      <c r="E140" s="46"/>
-      <c r="F140" s="45"/>
-      <c r="G140" s="46"/>
-      <c r="H140" s="45"/>
-      <c r="I140" s="46"/>
-      <c r="J140" s="45"/>
-      <c r="K140" s="46"/>
-      <c r="L140" s="45"/>
-      <c r="M140" s="46"/>
-      <c r="N140" s="45"/>
-      <c r="O140" s="46"/>
-      <c r="P140" s="45"/>
-      <c r="Q140" s="46"/>
-      <c r="R140" s="45"/>
-      <c r="S140" s="46"/>
-      <c r="T140" s="45"/>
-      <c r="U140" s="46"/>
-      <c r="V140" s="45"/>
-      <c r="W140" s="46"/>
-      <c r="X140" s="45"/>
-      <c r="Y140" s="46"/>
-      <c r="Z140" s="45"/>
-      <c r="AA140" s="46"/>
-      <c r="AB140" s="45"/>
-      <c r="AC140" s="46"/>
-      <c r="AD140" s="45"/>
-      <c r="AE140" s="46"/>
-      <c r="AF140" s="45"/>
-      <c r="AG140" s="46"/>
-      <c r="AH140" s="45"/>
-      <c r="AI140" s="46"/>
-      <c r="AJ140" s="45"/>
-      <c r="AK140" s="46"/>
-      <c r="AL140" s="45"/>
-      <c r="AM140" s="46"/>
-      <c r="AN140" s="45"/>
-      <c r="AO140" s="46"/>
-      <c r="AP140" s="45"/>
-      <c r="AQ140" s="45"/>
-      <c r="AR140" s="45"/>
-      <c r="AS140" s="45"/>
-      <c r="AT140" s="45"/>
-      <c r="AU140" s="46"/>
-      <c r="AV140" s="47"/>
+      <c r="B140" s="40"/>
+      <c r="C140" s="41"/>
+      <c r="D140" s="40"/>
+      <c r="E140" s="41"/>
+      <c r="F140" s="40"/>
+      <c r="G140" s="41"/>
+      <c r="H140" s="40"/>
+      <c r="I140" s="41"/>
+      <c r="J140" s="40"/>
+      <c r="K140" s="41"/>
+      <c r="L140" s="40"/>
+      <c r="M140" s="41"/>
+      <c r="N140" s="40"/>
+      <c r="O140" s="41"/>
+      <c r="P140" s="40"/>
+      <c r="Q140" s="41"/>
+      <c r="R140" s="40"/>
+      <c r="S140" s="41"/>
+      <c r="T140" s="40"/>
+      <c r="U140" s="41"/>
+      <c r="V140" s="40"/>
+      <c r="W140" s="41"/>
+      <c r="X140" s="40"/>
+      <c r="Y140" s="41"/>
+      <c r="Z140" s="40"/>
+      <c r="AA140" s="41"/>
+      <c r="AB140" s="40"/>
+      <c r="AC140" s="41"/>
+      <c r="AD140" s="40"/>
+      <c r="AE140" s="41"/>
+      <c r="AF140" s="40"/>
+      <c r="AG140" s="41"/>
+      <c r="AH140" s="40"/>
+      <c r="AI140" s="41"/>
+      <c r="AJ140" s="40"/>
+      <c r="AK140" s="41"/>
+      <c r="AL140" s="40"/>
+      <c r="AM140" s="41"/>
+      <c r="AN140" s="40"/>
+      <c r="AO140" s="41"/>
+      <c r="AP140" s="40"/>
+      <c r="AQ140" s="40"/>
+      <c r="AR140" s="40"/>
+      <c r="AS140" s="40"/>
+      <c r="AT140" s="40"/>
+      <c r="AU140" s="41"/>
+      <c r="AV140" s="42"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
@@ -19764,107 +19772,107 @@
       <c r="A145" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="49"/>
-      <c r="C145" s="50"/>
-      <c r="D145" s="49"/>
-      <c r="E145" s="50"/>
-      <c r="F145" s="49"/>
-      <c r="G145" s="50"/>
-      <c r="H145" s="49"/>
-      <c r="I145" s="50"/>
-      <c r="J145" s="49"/>
-      <c r="K145" s="50"/>
-      <c r="L145" s="49"/>
-      <c r="M145" s="50"/>
-      <c r="N145" s="49"/>
-      <c r="O145" s="50"/>
-      <c r="P145" s="49"/>
-      <c r="Q145" s="50"/>
-      <c r="R145" s="49"/>
-      <c r="S145" s="50"/>
-      <c r="T145" s="49"/>
-      <c r="U145" s="50"/>
-      <c r="V145" s="49"/>
-      <c r="W145" s="50"/>
-      <c r="X145" s="49"/>
-      <c r="Y145" s="50"/>
-      <c r="Z145" s="49"/>
-      <c r="AA145" s="50"/>
-      <c r="AB145" s="49"/>
-      <c r="AC145" s="50"/>
-      <c r="AD145" s="49"/>
-      <c r="AE145" s="50"/>
-      <c r="AF145" s="49"/>
-      <c r="AG145" s="50"/>
-      <c r="AH145" s="49"/>
-      <c r="AI145" s="50"/>
-      <c r="AJ145" s="49"/>
-      <c r="AK145" s="50"/>
-      <c r="AL145" s="49"/>
-      <c r="AM145" s="50"/>
-      <c r="AN145" s="49"/>
-      <c r="AO145" s="50"/>
-      <c r="AP145" s="49"/>
-      <c r="AQ145" s="49"/>
-      <c r="AR145" s="49"/>
-      <c r="AS145" s="49"/>
-      <c r="AT145" s="49"/>
-      <c r="AU145" s="50"/>
-      <c r="AV145" s="43"/>
+      <c r="B145" s="53"/>
+      <c r="C145" s="54"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="53"/>
+      <c r="G145" s="54"/>
+      <c r="H145" s="53"/>
+      <c r="I145" s="54"/>
+      <c r="J145" s="53"/>
+      <c r="K145" s="54"/>
+      <c r="L145" s="53"/>
+      <c r="M145" s="54"/>
+      <c r="N145" s="53"/>
+      <c r="O145" s="54"/>
+      <c r="P145" s="53"/>
+      <c r="Q145" s="54"/>
+      <c r="R145" s="53"/>
+      <c r="S145" s="54"/>
+      <c r="T145" s="53"/>
+      <c r="U145" s="54"/>
+      <c r="V145" s="53"/>
+      <c r="W145" s="54"/>
+      <c r="X145" s="53"/>
+      <c r="Y145" s="54"/>
+      <c r="Z145" s="53"/>
+      <c r="AA145" s="54"/>
+      <c r="AB145" s="53"/>
+      <c r="AC145" s="54"/>
+      <c r="AD145" s="53"/>
+      <c r="AE145" s="54"/>
+      <c r="AF145" s="53"/>
+      <c r="AG145" s="54"/>
+      <c r="AH145" s="53"/>
+      <c r="AI145" s="54"/>
+      <c r="AJ145" s="53"/>
+      <c r="AK145" s="54"/>
+      <c r="AL145" s="53"/>
+      <c r="AM145" s="54"/>
+      <c r="AN145" s="53"/>
+      <c r="AO145" s="54"/>
+      <c r="AP145" s="53"/>
+      <c r="AQ145" s="53"/>
+      <c r="AR145" s="53"/>
+      <c r="AS145" s="53"/>
+      <c r="AT145" s="53"/>
+      <c r="AU145" s="54"/>
+      <c r="AV145" s="47"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
     <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="44" t="s">
+      <c r="A146" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="45"/>
-      <c r="C146" s="46"/>
-      <c r="D146" s="45"/>
-      <c r="E146" s="46"/>
-      <c r="F146" s="45"/>
-      <c r="G146" s="46"/>
-      <c r="H146" s="45"/>
-      <c r="I146" s="46"/>
-      <c r="J146" s="45"/>
-      <c r="K146" s="46"/>
-      <c r="L146" s="45"/>
-      <c r="M146" s="46"/>
-      <c r="N146" s="45"/>
-      <c r="O146" s="46"/>
-      <c r="P146" s="45"/>
-      <c r="Q146" s="46"/>
-      <c r="R146" s="45"/>
-      <c r="S146" s="46"/>
-      <c r="T146" s="45"/>
-      <c r="U146" s="46"/>
-      <c r="V146" s="45"/>
-      <c r="W146" s="46"/>
-      <c r="X146" s="45"/>
-      <c r="Y146" s="46"/>
-      <c r="Z146" s="45"/>
-      <c r="AA146" s="46"/>
-      <c r="AB146" s="45"/>
-      <c r="AC146" s="46"/>
-      <c r="AD146" s="45"/>
-      <c r="AE146" s="46"/>
-      <c r="AF146" s="45"/>
-      <c r="AG146" s="46"/>
-      <c r="AH146" s="45"/>
-      <c r="AI146" s="46"/>
-      <c r="AJ146" s="45"/>
-      <c r="AK146" s="46"/>
-      <c r="AL146" s="45"/>
-      <c r="AM146" s="46"/>
-      <c r="AN146" s="45"/>
-      <c r="AO146" s="46"/>
-      <c r="AP146" s="45"/>
-      <c r="AQ146" s="45"/>
-      <c r="AR146" s="45"/>
-      <c r="AS146" s="45"/>
-      <c r="AT146" s="45"/>
-      <c r="AU146" s="46"/>
-      <c r="AV146" s="47"/>
+      <c r="B146" s="40"/>
+      <c r="C146" s="41"/>
+      <c r="D146" s="40"/>
+      <c r="E146" s="41"/>
+      <c r="F146" s="40"/>
+      <c r="G146" s="41"/>
+      <c r="H146" s="40"/>
+      <c r="I146" s="41"/>
+      <c r="J146" s="40"/>
+      <c r="K146" s="41"/>
+      <c r="L146" s="40"/>
+      <c r="M146" s="41"/>
+      <c r="N146" s="40"/>
+      <c r="O146" s="41"/>
+      <c r="P146" s="40"/>
+      <c r="Q146" s="41"/>
+      <c r="R146" s="40"/>
+      <c r="S146" s="41"/>
+      <c r="T146" s="40"/>
+      <c r="U146" s="41"/>
+      <c r="V146" s="40"/>
+      <c r="W146" s="41"/>
+      <c r="X146" s="40"/>
+      <c r="Y146" s="41"/>
+      <c r="Z146" s="40"/>
+      <c r="AA146" s="41"/>
+      <c r="AB146" s="40"/>
+      <c r="AC146" s="41"/>
+      <c r="AD146" s="40"/>
+      <c r="AE146" s="41"/>
+      <c r="AF146" s="40"/>
+      <c r="AG146" s="41"/>
+      <c r="AH146" s="40"/>
+      <c r="AI146" s="41"/>
+      <c r="AJ146" s="40"/>
+      <c r="AK146" s="41"/>
+      <c r="AL146" s="40"/>
+      <c r="AM146" s="41"/>
+      <c r="AN146" s="40"/>
+      <c r="AO146" s="41"/>
+      <c r="AP146" s="40"/>
+      <c r="AQ146" s="40"/>
+      <c r="AR146" s="40"/>
+      <c r="AS146" s="40"/>
+      <c r="AT146" s="40"/>
+      <c r="AU146" s="41"/>
+      <c r="AV146" s="42"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
@@ -20187,56 +20195,56 @@
       <c r="AX149" s="12"/>
     </row>
     <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="44" t="s">
+      <c r="A150" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="B150" s="45"/>
-      <c r="C150" s="46"/>
-      <c r="D150" s="45"/>
-      <c r="E150" s="46"/>
-      <c r="F150" s="45"/>
-      <c r="G150" s="46"/>
-      <c r="H150" s="45"/>
-      <c r="I150" s="46"/>
-      <c r="J150" s="45"/>
-      <c r="K150" s="46"/>
-      <c r="L150" s="45"/>
-      <c r="M150" s="46"/>
-      <c r="N150" s="45"/>
-      <c r="O150" s="46"/>
-      <c r="P150" s="45"/>
-      <c r="Q150" s="46"/>
-      <c r="R150" s="45"/>
-      <c r="S150" s="46"/>
-      <c r="T150" s="45"/>
-      <c r="U150" s="46"/>
-      <c r="V150" s="45"/>
-      <c r="W150" s="46"/>
-      <c r="X150" s="45"/>
-      <c r="Y150" s="46"/>
-      <c r="Z150" s="45"/>
-      <c r="AA150" s="46"/>
-      <c r="AB150" s="45"/>
-      <c r="AC150" s="46"/>
-      <c r="AD150" s="45"/>
-      <c r="AE150" s="46"/>
-      <c r="AF150" s="45"/>
-      <c r="AG150" s="46"/>
-      <c r="AH150" s="45"/>
-      <c r="AI150" s="46"/>
-      <c r="AJ150" s="45"/>
-      <c r="AK150" s="46"/>
-      <c r="AL150" s="45"/>
-      <c r="AM150" s="46"/>
-      <c r="AN150" s="45"/>
-      <c r="AO150" s="46"/>
-      <c r="AP150" s="45"/>
-      <c r="AQ150" s="45"/>
-      <c r="AR150" s="45"/>
-      <c r="AS150" s="45"/>
-      <c r="AT150" s="45"/>
-      <c r="AU150" s="46"/>
-      <c r="AV150" s="47"/>
+      <c r="B150" s="40"/>
+      <c r="C150" s="41"/>
+      <c r="D150" s="40"/>
+      <c r="E150" s="41"/>
+      <c r="F150" s="40"/>
+      <c r="G150" s="41"/>
+      <c r="H150" s="40"/>
+      <c r="I150" s="41"/>
+      <c r="J150" s="40"/>
+      <c r="K150" s="41"/>
+      <c r="L150" s="40"/>
+      <c r="M150" s="41"/>
+      <c r="N150" s="40"/>
+      <c r="O150" s="41"/>
+      <c r="P150" s="40"/>
+      <c r="Q150" s="41"/>
+      <c r="R150" s="40"/>
+      <c r="S150" s="41"/>
+      <c r="T150" s="40"/>
+      <c r="U150" s="41"/>
+      <c r="V150" s="40"/>
+      <c r="W150" s="41"/>
+      <c r="X150" s="40"/>
+      <c r="Y150" s="41"/>
+      <c r="Z150" s="40"/>
+      <c r="AA150" s="41"/>
+      <c r="AB150" s="40"/>
+      <c r="AC150" s="41"/>
+      <c r="AD150" s="40"/>
+      <c r="AE150" s="41"/>
+      <c r="AF150" s="40"/>
+      <c r="AG150" s="41"/>
+      <c r="AH150" s="40"/>
+      <c r="AI150" s="41"/>
+      <c r="AJ150" s="40"/>
+      <c r="AK150" s="41"/>
+      <c r="AL150" s="40"/>
+      <c r="AM150" s="41"/>
+      <c r="AN150" s="40"/>
+      <c r="AO150" s="41"/>
+      <c r="AP150" s="40"/>
+      <c r="AQ150" s="40"/>
+      <c r="AR150" s="40"/>
+      <c r="AS150" s="40"/>
+      <c r="AT150" s="40"/>
+      <c r="AU150" s="41"/>
+      <c r="AV150" s="42"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
@@ -20429,56 +20437,56 @@
       <c r="AX152" s="12"/>
     </row>
     <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="44" t="s">
+      <c r="A153" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="B153" s="45"/>
-      <c r="C153" s="46"/>
-      <c r="D153" s="45"/>
-      <c r="E153" s="46"/>
-      <c r="F153" s="45"/>
-      <c r="G153" s="46"/>
-      <c r="H153" s="45"/>
-      <c r="I153" s="46"/>
-      <c r="J153" s="45"/>
-      <c r="K153" s="46"/>
-      <c r="L153" s="45"/>
-      <c r="M153" s="46"/>
-      <c r="N153" s="45"/>
-      <c r="O153" s="46"/>
-      <c r="P153" s="45"/>
-      <c r="Q153" s="46"/>
-      <c r="R153" s="45"/>
-      <c r="S153" s="46"/>
-      <c r="T153" s="45"/>
-      <c r="U153" s="46"/>
-      <c r="V153" s="45"/>
-      <c r="W153" s="46"/>
-      <c r="X153" s="45"/>
-      <c r="Y153" s="46"/>
-      <c r="Z153" s="45"/>
-      <c r="AA153" s="46"/>
-      <c r="AB153" s="45"/>
-      <c r="AC153" s="46"/>
-      <c r="AD153" s="45"/>
-      <c r="AE153" s="46"/>
-      <c r="AF153" s="45"/>
-      <c r="AG153" s="46"/>
-      <c r="AH153" s="45"/>
-      <c r="AI153" s="46"/>
-      <c r="AJ153" s="45"/>
-      <c r="AK153" s="46"/>
-      <c r="AL153" s="45"/>
-      <c r="AM153" s="46"/>
-      <c r="AN153" s="45"/>
-      <c r="AO153" s="46"/>
-      <c r="AP153" s="45"/>
-      <c r="AQ153" s="45"/>
-      <c r="AR153" s="45"/>
-      <c r="AS153" s="45"/>
-      <c r="AT153" s="45"/>
-      <c r="AU153" s="46"/>
-      <c r="AV153" s="47"/>
+      <c r="B153" s="40"/>
+      <c r="C153" s="41"/>
+      <c r="D153" s="40"/>
+      <c r="E153" s="41"/>
+      <c r="F153" s="40"/>
+      <c r="G153" s="41"/>
+      <c r="H153" s="40"/>
+      <c r="I153" s="41"/>
+      <c r="J153" s="40"/>
+      <c r="K153" s="41"/>
+      <c r="L153" s="40"/>
+      <c r="M153" s="41"/>
+      <c r="N153" s="40"/>
+      <c r="O153" s="41"/>
+      <c r="P153" s="40"/>
+      <c r="Q153" s="41"/>
+      <c r="R153" s="40"/>
+      <c r="S153" s="41"/>
+      <c r="T153" s="40"/>
+      <c r="U153" s="41"/>
+      <c r="V153" s="40"/>
+      <c r="W153" s="41"/>
+      <c r="X153" s="40"/>
+      <c r="Y153" s="41"/>
+      <c r="Z153" s="40"/>
+      <c r="AA153" s="41"/>
+      <c r="AB153" s="40"/>
+      <c r="AC153" s="41"/>
+      <c r="AD153" s="40"/>
+      <c r="AE153" s="41"/>
+      <c r="AF153" s="40"/>
+      <c r="AG153" s="41"/>
+      <c r="AH153" s="40"/>
+      <c r="AI153" s="41"/>
+      <c r="AJ153" s="40"/>
+      <c r="AK153" s="41"/>
+      <c r="AL153" s="40"/>
+      <c r="AM153" s="41"/>
+      <c r="AN153" s="40"/>
+      <c r="AO153" s="41"/>
+      <c r="AP153" s="40"/>
+      <c r="AQ153" s="40"/>
+      <c r="AR153" s="40"/>
+      <c r="AS153" s="40"/>
+      <c r="AT153" s="40"/>
+      <c r="AU153" s="41"/>
+      <c r="AV153" s="42"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
@@ -20801,56 +20809,56 @@
       <c r="AX156" s="12"/>
     </row>
     <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="44" t="s">
+      <c r="A157" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="B157" s="45"/>
-      <c r="C157" s="46"/>
-      <c r="D157" s="45"/>
-      <c r="E157" s="46"/>
-      <c r="F157" s="45"/>
-      <c r="G157" s="46"/>
-      <c r="H157" s="45"/>
-      <c r="I157" s="46"/>
-      <c r="J157" s="45"/>
-      <c r="K157" s="46"/>
-      <c r="L157" s="45"/>
-      <c r="M157" s="46"/>
-      <c r="N157" s="45"/>
-      <c r="O157" s="46"/>
-      <c r="P157" s="45"/>
-      <c r="Q157" s="46"/>
-      <c r="R157" s="45"/>
-      <c r="S157" s="46"/>
-      <c r="T157" s="45"/>
-      <c r="U157" s="46"/>
-      <c r="V157" s="45"/>
-      <c r="W157" s="46"/>
-      <c r="X157" s="45"/>
-      <c r="Y157" s="46"/>
-      <c r="Z157" s="45"/>
-      <c r="AA157" s="46"/>
-      <c r="AB157" s="45"/>
-      <c r="AC157" s="46"/>
-      <c r="AD157" s="45"/>
-      <c r="AE157" s="46"/>
-      <c r="AF157" s="45"/>
-      <c r="AG157" s="46"/>
-      <c r="AH157" s="45"/>
-      <c r="AI157" s="46"/>
-      <c r="AJ157" s="45"/>
-      <c r="AK157" s="46"/>
-      <c r="AL157" s="45"/>
-      <c r="AM157" s="46"/>
-      <c r="AN157" s="45"/>
-      <c r="AO157" s="46"/>
-      <c r="AP157" s="45"/>
-      <c r="AQ157" s="45"/>
-      <c r="AR157" s="45"/>
-      <c r="AS157" s="45"/>
-      <c r="AT157" s="45"/>
-      <c r="AU157" s="46"/>
-      <c r="AV157" s="47"/>
+      <c r="B157" s="40"/>
+      <c r="C157" s="41"/>
+      <c r="D157" s="40"/>
+      <c r="E157" s="41"/>
+      <c r="F157" s="40"/>
+      <c r="G157" s="41"/>
+      <c r="H157" s="40"/>
+      <c r="I157" s="41"/>
+      <c r="J157" s="40"/>
+      <c r="K157" s="41"/>
+      <c r="L157" s="40"/>
+      <c r="M157" s="41"/>
+      <c r="N157" s="40"/>
+      <c r="O157" s="41"/>
+      <c r="P157" s="40"/>
+      <c r="Q157" s="41"/>
+      <c r="R157" s="40"/>
+      <c r="S157" s="41"/>
+      <c r="T157" s="40"/>
+      <c r="U157" s="41"/>
+      <c r="V157" s="40"/>
+      <c r="W157" s="41"/>
+      <c r="X157" s="40"/>
+      <c r="Y157" s="41"/>
+      <c r="Z157" s="40"/>
+      <c r="AA157" s="41"/>
+      <c r="AB157" s="40"/>
+      <c r="AC157" s="41"/>
+      <c r="AD157" s="40"/>
+      <c r="AE157" s="41"/>
+      <c r="AF157" s="40"/>
+      <c r="AG157" s="41"/>
+      <c r="AH157" s="40"/>
+      <c r="AI157" s="41"/>
+      <c r="AJ157" s="40"/>
+      <c r="AK157" s="41"/>
+      <c r="AL157" s="40"/>
+      <c r="AM157" s="41"/>
+      <c r="AN157" s="40"/>
+      <c r="AO157" s="41"/>
+      <c r="AP157" s="40"/>
+      <c r="AQ157" s="40"/>
+      <c r="AR157" s="40"/>
+      <c r="AS157" s="40"/>
+      <c r="AT157" s="40"/>
+      <c r="AU157" s="41"/>
+      <c r="AV157" s="42"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
@@ -21364,107 +21372,107 @@
       <c r="A163" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="49"/>
-      <c r="C163" s="50"/>
-      <c r="D163" s="49"/>
-      <c r="E163" s="50"/>
-      <c r="F163" s="49"/>
-      <c r="G163" s="50"/>
-      <c r="H163" s="49"/>
-      <c r="I163" s="50"/>
-      <c r="J163" s="49"/>
-      <c r="K163" s="50"/>
-      <c r="L163" s="49"/>
-      <c r="M163" s="50"/>
-      <c r="N163" s="49"/>
-      <c r="O163" s="50"/>
-      <c r="P163" s="49"/>
-      <c r="Q163" s="50"/>
-      <c r="R163" s="49"/>
-      <c r="S163" s="50"/>
-      <c r="T163" s="49"/>
-      <c r="U163" s="50"/>
-      <c r="V163" s="49"/>
-      <c r="W163" s="50"/>
-      <c r="X163" s="49"/>
-      <c r="Y163" s="50"/>
-      <c r="Z163" s="49"/>
-      <c r="AA163" s="50"/>
-      <c r="AB163" s="49"/>
-      <c r="AC163" s="50"/>
-      <c r="AD163" s="49"/>
-      <c r="AE163" s="50"/>
-      <c r="AF163" s="49"/>
-      <c r="AG163" s="50"/>
-      <c r="AH163" s="49"/>
-      <c r="AI163" s="50"/>
-      <c r="AJ163" s="49"/>
-      <c r="AK163" s="50"/>
-      <c r="AL163" s="49"/>
-      <c r="AM163" s="50"/>
-      <c r="AN163" s="49"/>
-      <c r="AO163" s="50"/>
-      <c r="AP163" s="49"/>
-      <c r="AQ163" s="49"/>
-      <c r="AR163" s="49"/>
-      <c r="AS163" s="49"/>
-      <c r="AT163" s="49"/>
-      <c r="AU163" s="50"/>
-      <c r="AV163" s="43"/>
+      <c r="B163" s="53"/>
+      <c r="C163" s="54"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="54"/>
+      <c r="F163" s="53"/>
+      <c r="G163" s="54"/>
+      <c r="H163" s="53"/>
+      <c r="I163" s="54"/>
+      <c r="J163" s="53"/>
+      <c r="K163" s="54"/>
+      <c r="L163" s="53"/>
+      <c r="M163" s="54"/>
+      <c r="N163" s="53"/>
+      <c r="O163" s="54"/>
+      <c r="P163" s="53"/>
+      <c r="Q163" s="54"/>
+      <c r="R163" s="53"/>
+      <c r="S163" s="54"/>
+      <c r="T163" s="53"/>
+      <c r="U163" s="54"/>
+      <c r="V163" s="53"/>
+      <c r="W163" s="54"/>
+      <c r="X163" s="53"/>
+      <c r="Y163" s="54"/>
+      <c r="Z163" s="53"/>
+      <c r="AA163" s="54"/>
+      <c r="AB163" s="53"/>
+      <c r="AC163" s="54"/>
+      <c r="AD163" s="53"/>
+      <c r="AE163" s="54"/>
+      <c r="AF163" s="53"/>
+      <c r="AG163" s="54"/>
+      <c r="AH163" s="53"/>
+      <c r="AI163" s="54"/>
+      <c r="AJ163" s="53"/>
+      <c r="AK163" s="54"/>
+      <c r="AL163" s="53"/>
+      <c r="AM163" s="54"/>
+      <c r="AN163" s="53"/>
+      <c r="AO163" s="54"/>
+      <c r="AP163" s="53"/>
+      <c r="AQ163" s="53"/>
+      <c r="AR163" s="53"/>
+      <c r="AS163" s="53"/>
+      <c r="AT163" s="53"/>
+      <c r="AU163" s="54"/>
+      <c r="AV163" s="47"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
     <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="44" t="s">
+      <c r="A164" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="B164" s="45"/>
-      <c r="C164" s="46"/>
-      <c r="D164" s="45"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="45"/>
-      <c r="G164" s="46"/>
-      <c r="H164" s="45"/>
-      <c r="I164" s="46"/>
-      <c r="J164" s="45"/>
-      <c r="K164" s="46"/>
-      <c r="L164" s="45"/>
-      <c r="M164" s="46"/>
-      <c r="N164" s="45"/>
-      <c r="O164" s="46"/>
-      <c r="P164" s="45"/>
-      <c r="Q164" s="46"/>
-      <c r="R164" s="45"/>
-      <c r="S164" s="46"/>
-      <c r="T164" s="45"/>
-      <c r="U164" s="46"/>
-      <c r="V164" s="45"/>
-      <c r="W164" s="46"/>
-      <c r="X164" s="45"/>
-      <c r="Y164" s="46"/>
-      <c r="Z164" s="45"/>
-      <c r="AA164" s="46"/>
-      <c r="AB164" s="45"/>
-      <c r="AC164" s="46"/>
-      <c r="AD164" s="45"/>
-      <c r="AE164" s="46"/>
-      <c r="AF164" s="45"/>
-      <c r="AG164" s="46"/>
-      <c r="AH164" s="45"/>
-      <c r="AI164" s="46"/>
-      <c r="AJ164" s="45"/>
-      <c r="AK164" s="46"/>
-      <c r="AL164" s="45"/>
-      <c r="AM164" s="46"/>
-      <c r="AN164" s="45"/>
-      <c r="AO164" s="46"/>
-      <c r="AP164" s="45"/>
-      <c r="AQ164" s="45"/>
-      <c r="AR164" s="45"/>
-      <c r="AS164" s="45"/>
-      <c r="AT164" s="45"/>
-      <c r="AU164" s="46"/>
-      <c r="AV164" s="47"/>
+      <c r="B164" s="40"/>
+      <c r="C164" s="41"/>
+      <c r="D164" s="40"/>
+      <c r="E164" s="41"/>
+      <c r="F164" s="40"/>
+      <c r="G164" s="41"/>
+      <c r="H164" s="40"/>
+      <c r="I164" s="41"/>
+      <c r="J164" s="40"/>
+      <c r="K164" s="41"/>
+      <c r="L164" s="40"/>
+      <c r="M164" s="41"/>
+      <c r="N164" s="40"/>
+      <c r="O164" s="41"/>
+      <c r="P164" s="40"/>
+      <c r="Q164" s="41"/>
+      <c r="R164" s="40"/>
+      <c r="S164" s="41"/>
+      <c r="T164" s="40"/>
+      <c r="U164" s="41"/>
+      <c r="V164" s="40"/>
+      <c r="W164" s="41"/>
+      <c r="X164" s="40"/>
+      <c r="Y164" s="41"/>
+      <c r="Z164" s="40"/>
+      <c r="AA164" s="41"/>
+      <c r="AB164" s="40"/>
+      <c r="AC164" s="41"/>
+      <c r="AD164" s="40"/>
+      <c r="AE164" s="41"/>
+      <c r="AF164" s="40"/>
+      <c r="AG164" s="41"/>
+      <c r="AH164" s="40"/>
+      <c r="AI164" s="41"/>
+      <c r="AJ164" s="40"/>
+      <c r="AK164" s="41"/>
+      <c r="AL164" s="40"/>
+      <c r="AM164" s="41"/>
+      <c r="AN164" s="40"/>
+      <c r="AO164" s="41"/>
+      <c r="AP164" s="40"/>
+      <c r="AQ164" s="40"/>
+      <c r="AR164" s="40"/>
+      <c r="AS164" s="40"/>
+      <c r="AT164" s="40"/>
+      <c r="AU164" s="41"/>
+      <c r="AV164" s="42"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
@@ -21657,56 +21665,56 @@
       <c r="AX166" s="12"/>
     </row>
     <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="44" t="s">
+      <c r="A167" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="45"/>
-      <c r="C167" s="46"/>
-      <c r="D167" s="45"/>
-      <c r="E167" s="46"/>
-      <c r="F167" s="45"/>
-      <c r="G167" s="46"/>
-      <c r="H167" s="45"/>
-      <c r="I167" s="46"/>
-      <c r="J167" s="45"/>
-      <c r="K167" s="46"/>
-      <c r="L167" s="45"/>
-      <c r="M167" s="46"/>
-      <c r="N167" s="45"/>
-      <c r="O167" s="46"/>
-      <c r="P167" s="45"/>
-      <c r="Q167" s="46"/>
-      <c r="R167" s="45"/>
-      <c r="S167" s="46"/>
-      <c r="T167" s="45"/>
-      <c r="U167" s="46"/>
-      <c r="V167" s="45"/>
-      <c r="W167" s="46"/>
-      <c r="X167" s="45"/>
-      <c r="Y167" s="46"/>
-      <c r="Z167" s="45"/>
-      <c r="AA167" s="46"/>
-      <c r="AB167" s="45"/>
-      <c r="AC167" s="46"/>
-      <c r="AD167" s="45"/>
-      <c r="AE167" s="46"/>
-      <c r="AF167" s="45"/>
-      <c r="AG167" s="46"/>
-      <c r="AH167" s="45"/>
-      <c r="AI167" s="46"/>
-      <c r="AJ167" s="45"/>
-      <c r="AK167" s="46"/>
-      <c r="AL167" s="45"/>
-      <c r="AM167" s="46"/>
-      <c r="AN167" s="45"/>
-      <c r="AO167" s="46"/>
-      <c r="AP167" s="45"/>
-      <c r="AQ167" s="45"/>
-      <c r="AR167" s="45"/>
-      <c r="AS167" s="45"/>
-      <c r="AT167" s="45"/>
-      <c r="AU167" s="46"/>
-      <c r="AV167" s="47"/>
+      <c r="B167" s="40"/>
+      <c r="C167" s="41"/>
+      <c r="D167" s="40"/>
+      <c r="E167" s="41"/>
+      <c r="F167" s="40"/>
+      <c r="G167" s="41"/>
+      <c r="H167" s="40"/>
+      <c r="I167" s="41"/>
+      <c r="J167" s="40"/>
+      <c r="K167" s="41"/>
+      <c r="L167" s="40"/>
+      <c r="M167" s="41"/>
+      <c r="N167" s="40"/>
+      <c r="O167" s="41"/>
+      <c r="P167" s="40"/>
+      <c r="Q167" s="41"/>
+      <c r="R167" s="40"/>
+      <c r="S167" s="41"/>
+      <c r="T167" s="40"/>
+      <c r="U167" s="41"/>
+      <c r="V167" s="40"/>
+      <c r="W167" s="41"/>
+      <c r="X167" s="40"/>
+      <c r="Y167" s="41"/>
+      <c r="Z167" s="40"/>
+      <c r="AA167" s="41"/>
+      <c r="AB167" s="40"/>
+      <c r="AC167" s="41"/>
+      <c r="AD167" s="40"/>
+      <c r="AE167" s="41"/>
+      <c r="AF167" s="40"/>
+      <c r="AG167" s="41"/>
+      <c r="AH167" s="40"/>
+      <c r="AI167" s="41"/>
+      <c r="AJ167" s="40"/>
+      <c r="AK167" s="41"/>
+      <c r="AL167" s="40"/>
+      <c r="AM167" s="41"/>
+      <c r="AN167" s="40"/>
+      <c r="AO167" s="41"/>
+      <c r="AP167" s="40"/>
+      <c r="AQ167" s="40"/>
+      <c r="AR167" s="40"/>
+      <c r="AS167" s="40"/>
+      <c r="AT167" s="40"/>
+      <c r="AU167" s="41"/>
+      <c r="AV167" s="42"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
@@ -21899,56 +21907,56 @@
       <c r="AX169" s="12"/>
     </row>
     <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="44" t="s">
+      <c r="A170" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="B170" s="45"/>
-      <c r="C170" s="46"/>
-      <c r="D170" s="45"/>
-      <c r="E170" s="46"/>
-      <c r="F170" s="45"/>
-      <c r="G170" s="46"/>
-      <c r="H170" s="45"/>
-      <c r="I170" s="46"/>
-      <c r="J170" s="45"/>
-      <c r="K170" s="46"/>
-      <c r="L170" s="45"/>
-      <c r="M170" s="46"/>
-      <c r="N170" s="45"/>
-      <c r="O170" s="46"/>
-      <c r="P170" s="45"/>
-      <c r="Q170" s="46"/>
-      <c r="R170" s="45"/>
-      <c r="S170" s="46"/>
-      <c r="T170" s="45"/>
-      <c r="U170" s="46"/>
-      <c r="V170" s="45"/>
-      <c r="W170" s="46"/>
-      <c r="X170" s="45"/>
-      <c r="Y170" s="46"/>
-      <c r="Z170" s="45"/>
-      <c r="AA170" s="46"/>
-      <c r="AB170" s="45"/>
-      <c r="AC170" s="46"/>
-      <c r="AD170" s="45"/>
-      <c r="AE170" s="46"/>
-      <c r="AF170" s="45"/>
-      <c r="AG170" s="46"/>
-      <c r="AH170" s="45"/>
-      <c r="AI170" s="46"/>
-      <c r="AJ170" s="45"/>
-      <c r="AK170" s="46"/>
-      <c r="AL170" s="45"/>
-      <c r="AM170" s="46"/>
-      <c r="AN170" s="45"/>
-      <c r="AO170" s="46"/>
-      <c r="AP170" s="45"/>
-      <c r="AQ170" s="45"/>
-      <c r="AR170" s="45"/>
-      <c r="AS170" s="45"/>
-      <c r="AT170" s="45"/>
-      <c r="AU170" s="46"/>
-      <c r="AV170" s="47"/>
+      <c r="B170" s="40"/>
+      <c r="C170" s="41"/>
+      <c r="D170" s="40"/>
+      <c r="E170" s="41"/>
+      <c r="F170" s="40"/>
+      <c r="G170" s="41"/>
+      <c r="H170" s="40"/>
+      <c r="I170" s="41"/>
+      <c r="J170" s="40"/>
+      <c r="K170" s="41"/>
+      <c r="L170" s="40"/>
+      <c r="M170" s="41"/>
+      <c r="N170" s="40"/>
+      <c r="O170" s="41"/>
+      <c r="P170" s="40"/>
+      <c r="Q170" s="41"/>
+      <c r="R170" s="40"/>
+      <c r="S170" s="41"/>
+      <c r="T170" s="40"/>
+      <c r="U170" s="41"/>
+      <c r="V170" s="40"/>
+      <c r="W170" s="41"/>
+      <c r="X170" s="40"/>
+      <c r="Y170" s="41"/>
+      <c r="Z170" s="40"/>
+      <c r="AA170" s="41"/>
+      <c r="AB170" s="40"/>
+      <c r="AC170" s="41"/>
+      <c r="AD170" s="40"/>
+      <c r="AE170" s="41"/>
+      <c r="AF170" s="40"/>
+      <c r="AG170" s="41"/>
+      <c r="AH170" s="40"/>
+      <c r="AI170" s="41"/>
+      <c r="AJ170" s="40"/>
+      <c r="AK170" s="41"/>
+      <c r="AL170" s="40"/>
+      <c r="AM170" s="41"/>
+      <c r="AN170" s="40"/>
+      <c r="AO170" s="41"/>
+      <c r="AP170" s="40"/>
+      <c r="AQ170" s="40"/>
+      <c r="AR170" s="40"/>
+      <c r="AS170" s="40"/>
+      <c r="AT170" s="40"/>
+      <c r="AU170" s="41"/>
+      <c r="AV170" s="42"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
@@ -22141,56 +22149,56 @@
       <c r="AX172" s="12"/>
     </row>
     <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="44" t="s">
+      <c r="A173" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="45"/>
-      <c r="C173" s="46"/>
-      <c r="D173" s="45"/>
-      <c r="E173" s="46"/>
-      <c r="F173" s="45"/>
-      <c r="G173" s="46"/>
-      <c r="H173" s="45"/>
-      <c r="I173" s="46"/>
-      <c r="J173" s="45"/>
-      <c r="K173" s="46"/>
-      <c r="L173" s="45"/>
-      <c r="M173" s="46"/>
-      <c r="N173" s="45"/>
-      <c r="O173" s="46"/>
-      <c r="P173" s="45"/>
-      <c r="Q173" s="46"/>
-      <c r="R173" s="45"/>
-      <c r="S173" s="46"/>
-      <c r="T173" s="45"/>
-      <c r="U173" s="46"/>
-      <c r="V173" s="45"/>
-      <c r="W173" s="46"/>
-      <c r="X173" s="45"/>
-      <c r="Y173" s="46"/>
-      <c r="Z173" s="45"/>
-      <c r="AA173" s="46"/>
-      <c r="AB173" s="45"/>
-      <c r="AC173" s="46"/>
-      <c r="AD173" s="45"/>
-      <c r="AE173" s="46"/>
-      <c r="AF173" s="45"/>
-      <c r="AG173" s="46"/>
-      <c r="AH173" s="45"/>
-      <c r="AI173" s="46"/>
-      <c r="AJ173" s="45"/>
-      <c r="AK173" s="46"/>
-      <c r="AL173" s="45"/>
-      <c r="AM173" s="46"/>
-      <c r="AN173" s="45"/>
-      <c r="AO173" s="46"/>
-      <c r="AP173" s="45"/>
-      <c r="AQ173" s="45"/>
-      <c r="AR173" s="45"/>
-      <c r="AS173" s="45"/>
-      <c r="AT173" s="45"/>
-      <c r="AU173" s="46"/>
-      <c r="AV173" s="47"/>
+      <c r="B173" s="40"/>
+      <c r="C173" s="41"/>
+      <c r="D173" s="40"/>
+      <c r="E173" s="41"/>
+      <c r="F173" s="40"/>
+      <c r="G173" s="41"/>
+      <c r="H173" s="40"/>
+      <c r="I173" s="41"/>
+      <c r="J173" s="40"/>
+      <c r="K173" s="41"/>
+      <c r="L173" s="40"/>
+      <c r="M173" s="41"/>
+      <c r="N173" s="40"/>
+      <c r="O173" s="41"/>
+      <c r="P173" s="40"/>
+      <c r="Q173" s="41"/>
+      <c r="R173" s="40"/>
+      <c r="S173" s="41"/>
+      <c r="T173" s="40"/>
+      <c r="U173" s="41"/>
+      <c r="V173" s="40"/>
+      <c r="W173" s="41"/>
+      <c r="X173" s="40"/>
+      <c r="Y173" s="41"/>
+      <c r="Z173" s="40"/>
+      <c r="AA173" s="41"/>
+      <c r="AB173" s="40"/>
+      <c r="AC173" s="41"/>
+      <c r="AD173" s="40"/>
+      <c r="AE173" s="41"/>
+      <c r="AF173" s="40"/>
+      <c r="AG173" s="41"/>
+      <c r="AH173" s="40"/>
+      <c r="AI173" s="41"/>
+      <c r="AJ173" s="40"/>
+      <c r="AK173" s="41"/>
+      <c r="AL173" s="40"/>
+      <c r="AM173" s="41"/>
+      <c r="AN173" s="40"/>
+      <c r="AO173" s="41"/>
+      <c r="AP173" s="40"/>
+      <c r="AQ173" s="40"/>
+      <c r="AR173" s="40"/>
+      <c r="AS173" s="40"/>
+      <c r="AT173" s="40"/>
+      <c r="AU173" s="41"/>
+      <c r="AV173" s="42"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
@@ -22444,107 +22452,107 @@
       <c r="A177" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="B177" s="49"/>
-      <c r="C177" s="50"/>
-      <c r="D177" s="49"/>
-      <c r="E177" s="50"/>
-      <c r="F177" s="49"/>
-      <c r="G177" s="50"/>
-      <c r="H177" s="49"/>
-      <c r="I177" s="50"/>
-      <c r="J177" s="49"/>
-      <c r="K177" s="50"/>
-      <c r="L177" s="49"/>
-      <c r="M177" s="50"/>
-      <c r="N177" s="49"/>
-      <c r="O177" s="50"/>
-      <c r="P177" s="49"/>
-      <c r="Q177" s="50"/>
-      <c r="R177" s="49"/>
-      <c r="S177" s="50"/>
-      <c r="T177" s="49"/>
-      <c r="U177" s="50"/>
-      <c r="V177" s="49"/>
-      <c r="W177" s="50"/>
-      <c r="X177" s="49"/>
-      <c r="Y177" s="50"/>
-      <c r="Z177" s="49"/>
-      <c r="AA177" s="50"/>
-      <c r="AB177" s="49"/>
-      <c r="AC177" s="50"/>
-      <c r="AD177" s="49"/>
-      <c r="AE177" s="50"/>
-      <c r="AF177" s="49"/>
-      <c r="AG177" s="50"/>
-      <c r="AH177" s="49"/>
-      <c r="AI177" s="50"/>
-      <c r="AJ177" s="49"/>
-      <c r="AK177" s="50"/>
-      <c r="AL177" s="49"/>
-      <c r="AM177" s="50"/>
-      <c r="AN177" s="49"/>
-      <c r="AO177" s="50"/>
-      <c r="AP177" s="49"/>
-      <c r="AQ177" s="49"/>
-      <c r="AR177" s="49"/>
-      <c r="AS177" s="49"/>
-      <c r="AT177" s="49"/>
-      <c r="AU177" s="50"/>
-      <c r="AV177" s="43"/>
+      <c r="B177" s="53"/>
+      <c r="C177" s="54"/>
+      <c r="D177" s="53"/>
+      <c r="E177" s="54"/>
+      <c r="F177" s="53"/>
+      <c r="G177" s="54"/>
+      <c r="H177" s="53"/>
+      <c r="I177" s="54"/>
+      <c r="J177" s="53"/>
+      <c r="K177" s="54"/>
+      <c r="L177" s="53"/>
+      <c r="M177" s="54"/>
+      <c r="N177" s="53"/>
+      <c r="O177" s="54"/>
+      <c r="P177" s="53"/>
+      <c r="Q177" s="54"/>
+      <c r="R177" s="53"/>
+      <c r="S177" s="54"/>
+      <c r="T177" s="53"/>
+      <c r="U177" s="54"/>
+      <c r="V177" s="53"/>
+      <c r="W177" s="54"/>
+      <c r="X177" s="53"/>
+      <c r="Y177" s="54"/>
+      <c r="Z177" s="53"/>
+      <c r="AA177" s="54"/>
+      <c r="AB177" s="53"/>
+      <c r="AC177" s="54"/>
+      <c r="AD177" s="53"/>
+      <c r="AE177" s="54"/>
+      <c r="AF177" s="53"/>
+      <c r="AG177" s="54"/>
+      <c r="AH177" s="53"/>
+      <c r="AI177" s="54"/>
+      <c r="AJ177" s="53"/>
+      <c r="AK177" s="54"/>
+      <c r="AL177" s="53"/>
+      <c r="AM177" s="54"/>
+      <c r="AN177" s="53"/>
+      <c r="AO177" s="54"/>
+      <c r="AP177" s="53"/>
+      <c r="AQ177" s="53"/>
+      <c r="AR177" s="53"/>
+      <c r="AS177" s="53"/>
+      <c r="AT177" s="53"/>
+      <c r="AU177" s="54"/>
+      <c r="AV177" s="47"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
     <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="44" t="s">
+      <c r="A178" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="45"/>
-      <c r="C178" s="46"/>
-      <c r="D178" s="45"/>
-      <c r="E178" s="46"/>
-      <c r="F178" s="45"/>
-      <c r="G178" s="46"/>
-      <c r="H178" s="45"/>
-      <c r="I178" s="46"/>
-      <c r="J178" s="45"/>
-      <c r="K178" s="46"/>
-      <c r="L178" s="45"/>
-      <c r="M178" s="46"/>
-      <c r="N178" s="45"/>
-      <c r="O178" s="46"/>
-      <c r="P178" s="45"/>
-      <c r="Q178" s="46"/>
-      <c r="R178" s="45"/>
-      <c r="S178" s="46"/>
-      <c r="T178" s="45"/>
-      <c r="U178" s="46"/>
-      <c r="V178" s="45"/>
-      <c r="W178" s="46"/>
-      <c r="X178" s="45"/>
-      <c r="Y178" s="46"/>
-      <c r="Z178" s="45"/>
-      <c r="AA178" s="46"/>
-      <c r="AB178" s="45"/>
-      <c r="AC178" s="46"/>
-      <c r="AD178" s="45"/>
-      <c r="AE178" s="46"/>
-      <c r="AF178" s="45"/>
-      <c r="AG178" s="46"/>
-      <c r="AH178" s="45"/>
-      <c r="AI178" s="46"/>
-      <c r="AJ178" s="45"/>
-      <c r="AK178" s="46"/>
-      <c r="AL178" s="45"/>
-      <c r="AM178" s="46"/>
-      <c r="AN178" s="45"/>
-      <c r="AO178" s="46"/>
-      <c r="AP178" s="45"/>
-      <c r="AQ178" s="45"/>
-      <c r="AR178" s="45"/>
-      <c r="AS178" s="45"/>
-      <c r="AT178" s="45"/>
-      <c r="AU178" s="46"/>
-      <c r="AV178" s="47"/>
+      <c r="B178" s="40"/>
+      <c r="C178" s="41"/>
+      <c r="D178" s="40"/>
+      <c r="E178" s="41"/>
+      <c r="F178" s="40"/>
+      <c r="G178" s="41"/>
+      <c r="H178" s="40"/>
+      <c r="I178" s="41"/>
+      <c r="J178" s="40"/>
+      <c r="K178" s="41"/>
+      <c r="L178" s="40"/>
+      <c r="M178" s="41"/>
+      <c r="N178" s="40"/>
+      <c r="O178" s="41"/>
+      <c r="P178" s="40"/>
+      <c r="Q178" s="41"/>
+      <c r="R178" s="40"/>
+      <c r="S178" s="41"/>
+      <c r="T178" s="40"/>
+      <c r="U178" s="41"/>
+      <c r="V178" s="40"/>
+      <c r="W178" s="41"/>
+      <c r="X178" s="40"/>
+      <c r="Y178" s="41"/>
+      <c r="Z178" s="40"/>
+      <c r="AA178" s="41"/>
+      <c r="AB178" s="40"/>
+      <c r="AC178" s="41"/>
+      <c r="AD178" s="40"/>
+      <c r="AE178" s="41"/>
+      <c r="AF178" s="40"/>
+      <c r="AG178" s="41"/>
+      <c r="AH178" s="40"/>
+      <c r="AI178" s="41"/>
+      <c r="AJ178" s="40"/>
+      <c r="AK178" s="41"/>
+      <c r="AL178" s="40"/>
+      <c r="AM178" s="41"/>
+      <c r="AN178" s="40"/>
+      <c r="AO178" s="41"/>
+      <c r="AP178" s="40"/>
+      <c r="AQ178" s="40"/>
+      <c r="AR178" s="40"/>
+      <c r="AS178" s="40"/>
+      <c r="AT178" s="40"/>
+      <c r="AU178" s="41"/>
+      <c r="AV178" s="42"/>
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
@@ -22737,56 +22745,56 @@
       <c r="AX180" s="12"/>
     </row>
     <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="44" t="s">
+      <c r="A181" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="B181" s="45"/>
-      <c r="C181" s="46"/>
-      <c r="D181" s="45"/>
-      <c r="E181" s="46"/>
-      <c r="F181" s="45"/>
-      <c r="G181" s="46"/>
-      <c r="H181" s="45"/>
-      <c r="I181" s="46"/>
-      <c r="J181" s="45"/>
-      <c r="K181" s="46"/>
-      <c r="L181" s="45"/>
-      <c r="M181" s="46"/>
-      <c r="N181" s="45"/>
-      <c r="O181" s="46"/>
-      <c r="P181" s="45"/>
-      <c r="Q181" s="46"/>
-      <c r="R181" s="45"/>
-      <c r="S181" s="46"/>
-      <c r="T181" s="45"/>
-      <c r="U181" s="46"/>
-      <c r="V181" s="45"/>
-      <c r="W181" s="46"/>
-      <c r="X181" s="45"/>
-      <c r="Y181" s="46"/>
-      <c r="Z181" s="45"/>
-      <c r="AA181" s="46"/>
-      <c r="AB181" s="45"/>
-      <c r="AC181" s="46"/>
-      <c r="AD181" s="45"/>
-      <c r="AE181" s="46"/>
-      <c r="AF181" s="45"/>
-      <c r="AG181" s="46"/>
-      <c r="AH181" s="45"/>
-      <c r="AI181" s="46"/>
-      <c r="AJ181" s="45"/>
-      <c r="AK181" s="46"/>
-      <c r="AL181" s="45"/>
-      <c r="AM181" s="46"/>
-      <c r="AN181" s="45"/>
-      <c r="AO181" s="46"/>
-      <c r="AP181" s="45"/>
-      <c r="AQ181" s="45"/>
-      <c r="AR181" s="45"/>
-      <c r="AS181" s="45"/>
-      <c r="AT181" s="45"/>
-      <c r="AU181" s="46"/>
-      <c r="AV181" s="47"/>
+      <c r="B181" s="40"/>
+      <c r="C181" s="41"/>
+      <c r="D181" s="40"/>
+      <c r="E181" s="41"/>
+      <c r="F181" s="40"/>
+      <c r="G181" s="41"/>
+      <c r="H181" s="40"/>
+      <c r="I181" s="41"/>
+      <c r="J181" s="40"/>
+      <c r="K181" s="41"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="41"/>
+      <c r="N181" s="40"/>
+      <c r="O181" s="41"/>
+      <c r="P181" s="40"/>
+      <c r="Q181" s="41"/>
+      <c r="R181" s="40"/>
+      <c r="S181" s="41"/>
+      <c r="T181" s="40"/>
+      <c r="U181" s="41"/>
+      <c r="V181" s="40"/>
+      <c r="W181" s="41"/>
+      <c r="X181" s="40"/>
+      <c r="Y181" s="41"/>
+      <c r="Z181" s="40"/>
+      <c r="AA181" s="41"/>
+      <c r="AB181" s="40"/>
+      <c r="AC181" s="41"/>
+      <c r="AD181" s="40"/>
+      <c r="AE181" s="41"/>
+      <c r="AF181" s="40"/>
+      <c r="AG181" s="41"/>
+      <c r="AH181" s="40"/>
+      <c r="AI181" s="41"/>
+      <c r="AJ181" s="40"/>
+      <c r="AK181" s="41"/>
+      <c r="AL181" s="40"/>
+      <c r="AM181" s="41"/>
+      <c r="AN181" s="40"/>
+      <c r="AO181" s="41"/>
+      <c r="AP181" s="40"/>
+      <c r="AQ181" s="40"/>
+      <c r="AR181" s="40"/>
+      <c r="AS181" s="40"/>
+      <c r="AT181" s="40"/>
+      <c r="AU181" s="41"/>
+      <c r="AV181" s="42"/>
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
@@ -23040,107 +23048,107 @@
       <c r="A185" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="B185" s="49"/>
-      <c r="C185" s="50"/>
-      <c r="D185" s="49"/>
-      <c r="E185" s="50"/>
-      <c r="F185" s="49"/>
-      <c r="G185" s="50"/>
-      <c r="H185" s="49"/>
-      <c r="I185" s="50"/>
-      <c r="J185" s="49"/>
-      <c r="K185" s="50"/>
-      <c r="L185" s="49"/>
-      <c r="M185" s="50"/>
-      <c r="N185" s="49"/>
-      <c r="O185" s="50"/>
-      <c r="P185" s="49"/>
-      <c r="Q185" s="50"/>
-      <c r="R185" s="49"/>
-      <c r="S185" s="50"/>
-      <c r="T185" s="49"/>
-      <c r="U185" s="50"/>
-      <c r="V185" s="49"/>
-      <c r="W185" s="50"/>
-      <c r="X185" s="49"/>
-      <c r="Y185" s="50"/>
-      <c r="Z185" s="49"/>
-      <c r="AA185" s="50"/>
-      <c r="AB185" s="49"/>
-      <c r="AC185" s="50"/>
-      <c r="AD185" s="49"/>
-      <c r="AE185" s="50"/>
-      <c r="AF185" s="49"/>
-      <c r="AG185" s="50"/>
-      <c r="AH185" s="49"/>
-      <c r="AI185" s="50"/>
-      <c r="AJ185" s="49"/>
-      <c r="AK185" s="50"/>
-      <c r="AL185" s="49"/>
-      <c r="AM185" s="50"/>
-      <c r="AN185" s="49"/>
-      <c r="AO185" s="50"/>
-      <c r="AP185" s="49"/>
-      <c r="AQ185" s="49"/>
-      <c r="AR185" s="49"/>
-      <c r="AS185" s="49"/>
-      <c r="AT185" s="49"/>
-      <c r="AU185" s="50"/>
-      <c r="AV185" s="43"/>
+      <c r="B185" s="53"/>
+      <c r="C185" s="54"/>
+      <c r="D185" s="53"/>
+      <c r="E185" s="54"/>
+      <c r="F185" s="53"/>
+      <c r="G185" s="54"/>
+      <c r="H185" s="53"/>
+      <c r="I185" s="54"/>
+      <c r="J185" s="53"/>
+      <c r="K185" s="54"/>
+      <c r="L185" s="53"/>
+      <c r="M185" s="54"/>
+      <c r="N185" s="53"/>
+      <c r="O185" s="54"/>
+      <c r="P185" s="53"/>
+      <c r="Q185" s="54"/>
+      <c r="R185" s="53"/>
+      <c r="S185" s="54"/>
+      <c r="T185" s="53"/>
+      <c r="U185" s="54"/>
+      <c r="V185" s="53"/>
+      <c r="W185" s="54"/>
+      <c r="X185" s="53"/>
+      <c r="Y185" s="54"/>
+      <c r="Z185" s="53"/>
+      <c r="AA185" s="54"/>
+      <c r="AB185" s="53"/>
+      <c r="AC185" s="54"/>
+      <c r="AD185" s="53"/>
+      <c r="AE185" s="54"/>
+      <c r="AF185" s="53"/>
+      <c r="AG185" s="54"/>
+      <c r="AH185" s="53"/>
+      <c r="AI185" s="54"/>
+      <c r="AJ185" s="53"/>
+      <c r="AK185" s="54"/>
+      <c r="AL185" s="53"/>
+      <c r="AM185" s="54"/>
+      <c r="AN185" s="53"/>
+      <c r="AO185" s="54"/>
+      <c r="AP185" s="53"/>
+      <c r="AQ185" s="53"/>
+      <c r="AR185" s="53"/>
+      <c r="AS185" s="53"/>
+      <c r="AT185" s="53"/>
+      <c r="AU185" s="54"/>
+      <c r="AV185" s="47"/>
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
     <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="44" t="s">
+      <c r="A186" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="B186" s="45"/>
-      <c r="C186" s="46"/>
-      <c r="D186" s="45"/>
-      <c r="E186" s="46"/>
-      <c r="F186" s="45"/>
-      <c r="G186" s="46"/>
-      <c r="H186" s="45"/>
-      <c r="I186" s="46"/>
-      <c r="J186" s="45"/>
-      <c r="K186" s="46"/>
-      <c r="L186" s="45"/>
-      <c r="M186" s="46"/>
-      <c r="N186" s="45"/>
-      <c r="O186" s="46"/>
-      <c r="P186" s="45"/>
-      <c r="Q186" s="46"/>
-      <c r="R186" s="45"/>
-      <c r="S186" s="46"/>
-      <c r="T186" s="45"/>
-      <c r="U186" s="46"/>
-      <c r="V186" s="45"/>
-      <c r="W186" s="46"/>
-      <c r="X186" s="45"/>
-      <c r="Y186" s="46"/>
-      <c r="Z186" s="45"/>
-      <c r="AA186" s="46"/>
-      <c r="AB186" s="45"/>
-      <c r="AC186" s="46"/>
-      <c r="AD186" s="45"/>
-      <c r="AE186" s="46"/>
-      <c r="AF186" s="45"/>
-      <c r="AG186" s="46"/>
-      <c r="AH186" s="45"/>
-      <c r="AI186" s="46"/>
-      <c r="AJ186" s="45"/>
-      <c r="AK186" s="46"/>
-      <c r="AL186" s="45"/>
-      <c r="AM186" s="46"/>
-      <c r="AN186" s="45"/>
-      <c r="AO186" s="46"/>
-      <c r="AP186" s="45"/>
-      <c r="AQ186" s="45"/>
-      <c r="AR186" s="45"/>
-      <c r="AS186" s="45"/>
-      <c r="AT186" s="45"/>
-      <c r="AU186" s="46"/>
-      <c r="AV186" s="47"/>
+      <c r="B186" s="40"/>
+      <c r="C186" s="41"/>
+      <c r="D186" s="40"/>
+      <c r="E186" s="41"/>
+      <c r="F186" s="40"/>
+      <c r="G186" s="41"/>
+      <c r="H186" s="40"/>
+      <c r="I186" s="41"/>
+      <c r="J186" s="40"/>
+      <c r="K186" s="41"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="41"/>
+      <c r="N186" s="40"/>
+      <c r="O186" s="41"/>
+      <c r="P186" s="40"/>
+      <c r="Q186" s="41"/>
+      <c r="R186" s="40"/>
+      <c r="S186" s="41"/>
+      <c r="T186" s="40"/>
+      <c r="U186" s="41"/>
+      <c r="V186" s="40"/>
+      <c r="W186" s="41"/>
+      <c r="X186" s="40"/>
+      <c r="Y186" s="41"/>
+      <c r="Z186" s="40"/>
+      <c r="AA186" s="41"/>
+      <c r="AB186" s="40"/>
+      <c r="AC186" s="41"/>
+      <c r="AD186" s="40"/>
+      <c r="AE186" s="41"/>
+      <c r="AF186" s="40"/>
+      <c r="AG186" s="41"/>
+      <c r="AH186" s="40"/>
+      <c r="AI186" s="41"/>
+      <c r="AJ186" s="40"/>
+      <c r="AK186" s="41"/>
+      <c r="AL186" s="40"/>
+      <c r="AM186" s="41"/>
+      <c r="AN186" s="40"/>
+      <c r="AO186" s="41"/>
+      <c r="AP186" s="40"/>
+      <c r="AQ186" s="40"/>
+      <c r="AR186" s="40"/>
+      <c r="AS186" s="40"/>
+      <c r="AT186" s="40"/>
+      <c r="AU186" s="41"/>
+      <c r="AV186" s="42"/>
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
@@ -23394,107 +23402,107 @@
       <c r="A190" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="B190" s="49"/>
-      <c r="C190" s="50"/>
-      <c r="D190" s="49"/>
-      <c r="E190" s="50"/>
-      <c r="F190" s="49"/>
-      <c r="G190" s="50"/>
-      <c r="H190" s="49"/>
-      <c r="I190" s="50"/>
-      <c r="J190" s="49"/>
-      <c r="K190" s="50"/>
-      <c r="L190" s="49"/>
-      <c r="M190" s="50"/>
-      <c r="N190" s="49"/>
-      <c r="O190" s="50"/>
-      <c r="P190" s="49"/>
-      <c r="Q190" s="50"/>
-      <c r="R190" s="49"/>
-      <c r="S190" s="50"/>
-      <c r="T190" s="49"/>
-      <c r="U190" s="50"/>
-      <c r="V190" s="49"/>
-      <c r="W190" s="50"/>
-      <c r="X190" s="49"/>
-      <c r="Y190" s="50"/>
-      <c r="Z190" s="49"/>
-      <c r="AA190" s="50"/>
-      <c r="AB190" s="49"/>
-      <c r="AC190" s="50"/>
-      <c r="AD190" s="49"/>
-      <c r="AE190" s="50"/>
-      <c r="AF190" s="49"/>
-      <c r="AG190" s="50"/>
-      <c r="AH190" s="49"/>
-      <c r="AI190" s="50"/>
-      <c r="AJ190" s="49"/>
-      <c r="AK190" s="50"/>
-      <c r="AL190" s="49"/>
-      <c r="AM190" s="50"/>
-      <c r="AN190" s="49"/>
-      <c r="AO190" s="50"/>
-      <c r="AP190" s="49"/>
-      <c r="AQ190" s="49"/>
-      <c r="AR190" s="49"/>
-      <c r="AS190" s="49"/>
-      <c r="AT190" s="49"/>
-      <c r="AU190" s="50"/>
-      <c r="AV190" s="43"/>
+      <c r="B190" s="53"/>
+      <c r="C190" s="54"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="54"/>
+      <c r="F190" s="53"/>
+      <c r="G190" s="54"/>
+      <c r="H190" s="53"/>
+      <c r="I190" s="54"/>
+      <c r="J190" s="53"/>
+      <c r="K190" s="54"/>
+      <c r="L190" s="53"/>
+      <c r="M190" s="54"/>
+      <c r="N190" s="53"/>
+      <c r="O190" s="54"/>
+      <c r="P190" s="53"/>
+      <c r="Q190" s="54"/>
+      <c r="R190" s="53"/>
+      <c r="S190" s="54"/>
+      <c r="T190" s="53"/>
+      <c r="U190" s="54"/>
+      <c r="V190" s="53"/>
+      <c r="W190" s="54"/>
+      <c r="X190" s="53"/>
+      <c r="Y190" s="54"/>
+      <c r="Z190" s="53"/>
+      <c r="AA190" s="54"/>
+      <c r="AB190" s="53"/>
+      <c r="AC190" s="54"/>
+      <c r="AD190" s="53"/>
+      <c r="AE190" s="54"/>
+      <c r="AF190" s="53"/>
+      <c r="AG190" s="54"/>
+      <c r="AH190" s="53"/>
+      <c r="AI190" s="54"/>
+      <c r="AJ190" s="53"/>
+      <c r="AK190" s="54"/>
+      <c r="AL190" s="53"/>
+      <c r="AM190" s="54"/>
+      <c r="AN190" s="53"/>
+      <c r="AO190" s="54"/>
+      <c r="AP190" s="53"/>
+      <c r="AQ190" s="53"/>
+      <c r="AR190" s="53"/>
+      <c r="AS190" s="53"/>
+      <c r="AT190" s="53"/>
+      <c r="AU190" s="54"/>
+      <c r="AV190" s="47"/>
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
     <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="44" t="s">
+      <c r="A191" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="B191" s="45"/>
-      <c r="C191" s="46"/>
-      <c r="D191" s="45"/>
-      <c r="E191" s="46"/>
-      <c r="F191" s="45"/>
-      <c r="G191" s="46"/>
-      <c r="H191" s="45"/>
-      <c r="I191" s="46"/>
-      <c r="J191" s="45"/>
-      <c r="K191" s="46"/>
-      <c r="L191" s="45"/>
-      <c r="M191" s="46"/>
-      <c r="N191" s="45"/>
-      <c r="O191" s="46"/>
-      <c r="P191" s="45"/>
-      <c r="Q191" s="46"/>
-      <c r="R191" s="45"/>
-      <c r="S191" s="46"/>
-      <c r="T191" s="45"/>
-      <c r="U191" s="46"/>
-      <c r="V191" s="45"/>
-      <c r="W191" s="46"/>
-      <c r="X191" s="45"/>
-      <c r="Y191" s="46"/>
-      <c r="Z191" s="45"/>
-      <c r="AA191" s="46"/>
-      <c r="AB191" s="45"/>
-      <c r="AC191" s="46"/>
-      <c r="AD191" s="45"/>
-      <c r="AE191" s="46"/>
-      <c r="AF191" s="45"/>
-      <c r="AG191" s="46"/>
-      <c r="AH191" s="45"/>
-      <c r="AI191" s="46"/>
-      <c r="AJ191" s="45"/>
-      <c r="AK191" s="46"/>
-      <c r="AL191" s="45"/>
-      <c r="AM191" s="46"/>
-      <c r="AN191" s="45"/>
-      <c r="AO191" s="46"/>
-      <c r="AP191" s="45"/>
-      <c r="AQ191" s="45"/>
-      <c r="AR191" s="45"/>
-      <c r="AS191" s="45"/>
-      <c r="AT191" s="45"/>
-      <c r="AU191" s="46"/>
-      <c r="AV191" s="47"/>
+      <c r="B191" s="40"/>
+      <c r="C191" s="41"/>
+      <c r="D191" s="40"/>
+      <c r="E191" s="41"/>
+      <c r="F191" s="40"/>
+      <c r="G191" s="41"/>
+      <c r="H191" s="40"/>
+      <c r="I191" s="41"/>
+      <c r="J191" s="40"/>
+      <c r="K191" s="41"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="41"/>
+      <c r="N191" s="40"/>
+      <c r="O191" s="41"/>
+      <c r="P191" s="40"/>
+      <c r="Q191" s="41"/>
+      <c r="R191" s="40"/>
+      <c r="S191" s="41"/>
+      <c r="T191" s="40"/>
+      <c r="U191" s="41"/>
+      <c r="V191" s="40"/>
+      <c r="W191" s="41"/>
+      <c r="X191" s="40"/>
+      <c r="Y191" s="41"/>
+      <c r="Z191" s="40"/>
+      <c r="AA191" s="41"/>
+      <c r="AB191" s="40"/>
+      <c r="AC191" s="41"/>
+      <c r="AD191" s="40"/>
+      <c r="AE191" s="41"/>
+      <c r="AF191" s="40"/>
+      <c r="AG191" s="41"/>
+      <c r="AH191" s="40"/>
+      <c r="AI191" s="41"/>
+      <c r="AJ191" s="40"/>
+      <c r="AK191" s="41"/>
+      <c r="AL191" s="40"/>
+      <c r="AM191" s="41"/>
+      <c r="AN191" s="40"/>
+      <c r="AO191" s="41"/>
+      <c r="AP191" s="40"/>
+      <c r="AQ191" s="40"/>
+      <c r="AR191" s="40"/>
+      <c r="AS191" s="40"/>
+      <c r="AT191" s="40"/>
+      <c r="AU191" s="41"/>
+      <c r="AV191" s="42"/>
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
@@ -23746,6 +23754,60 @@
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="A22:AV22"/>
+    <mergeCell ref="AQ1:AR1"/>
+    <mergeCell ref="A70:AV70"/>
+    <mergeCell ref="A153:AV153"/>
+    <mergeCell ref="A177:AV177"/>
+    <mergeCell ref="A113:AV113"/>
+    <mergeCell ref="A117:AV117"/>
+    <mergeCell ref="A146:AV146"/>
+    <mergeCell ref="A76:AV76"/>
+    <mergeCell ref="A164:AV164"/>
+    <mergeCell ref="A106:AV106"/>
+    <mergeCell ref="A150:AV150"/>
+    <mergeCell ref="A90:AV90"/>
+    <mergeCell ref="A98:AV98"/>
+    <mergeCell ref="A121:AV121"/>
+    <mergeCell ref="A135:AV135"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
     <mergeCell ref="A64:AV64"/>
     <mergeCell ref="A178:AV178"/>
     <mergeCell ref="A82:AV82"/>
@@ -23762,60 +23824,6 @@
     <mergeCell ref="AO1:AP1"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A51:AV51"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:AV22"/>
-    <mergeCell ref="AQ1:AR1"/>
-    <mergeCell ref="A70:AV70"/>
-    <mergeCell ref="A153:AV153"/>
-    <mergeCell ref="A177:AV177"/>
-    <mergeCell ref="A113:AV113"/>
-    <mergeCell ref="A117:AV117"/>
-    <mergeCell ref="A146:AV146"/>
-    <mergeCell ref="A76:AV76"/>
-    <mergeCell ref="A164:AV164"/>
-    <mergeCell ref="A106:AV106"/>
-    <mergeCell ref="A150:AV150"/>
-    <mergeCell ref="A90:AV90"/>
-    <mergeCell ref="A98:AV98"/>
-    <mergeCell ref="A121:AV121"/>
-    <mergeCell ref="A135:AV135"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23880,114 +23888,114 @@
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="59" t="str">
+      <c r="D1" s="60" t="str">
         <f>Wedstrijden_beheer!E1</f>
         <v>Roland</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61" t="str">
+      <c r="E1" s="61"/>
+      <c r="F1" s="59" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="61" t="str">
+      <c r="G1" s="47"/>
+      <c r="H1" s="59" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="61" t="str">
+      <c r="I1" s="47"/>
+      <c r="J1" s="59" t="str">
         <f>Wedstrijden_beheer!K1</f>
         <v>Karsten</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="61" t="str">
+      <c r="K1" s="47"/>
+      <c r="L1" s="59" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="61" t="str">
+      <c r="M1" s="47"/>
+      <c r="N1" s="59" t="str">
         <f>Wedstrijden_beheer!O1</f>
         <v>Maik</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="61" t="str">
+      <c r="O1" s="47"/>
+      <c r="P1" s="59" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="61" t="str">
+      <c r="Q1" s="47"/>
+      <c r="R1" s="59" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="61" t="str">
+      <c r="S1" s="47"/>
+      <c r="T1" s="59" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="U1" s="43"/>
-      <c r="V1" s="61" t="str">
+      <c r="U1" s="47"/>
+      <c r="V1" s="59" t="str">
         <f>Wedstrijden_beheer!W1</f>
         <v>Jos</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="61" t="str">
+      <c r="W1" s="47"/>
+      <c r="X1" s="59" t="str">
         <f>Wedstrijden_beheer!Y1</f>
         <v>Lesley</v>
       </c>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="61" t="str">
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="59" t="str">
         <f>Wedstrijden_beheer!AA1</f>
         <v>Ivo</v>
       </c>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="61" t="str">
+      <c r="AA1" s="47"/>
+      <c r="AB1" s="59" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="AC1" s="43"/>
-      <c r="AD1" s="61" t="str">
+      <c r="AC1" s="47"/>
+      <c r="AD1" s="59" t="str">
         <f>Wedstrijden_beheer!AE1</f>
         <v>Jeroen</v>
       </c>
-      <c r="AE1" s="43"/>
-      <c r="AF1" s="61" t="str">
+      <c r="AE1" s="47"/>
+      <c r="AF1" s="59" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="61" t="str">
+      <c r="AG1" s="47"/>
+      <c r="AH1" s="59" t="str">
         <f>Wedstrijden_beheer!AI1</f>
         <v>Tim</v>
       </c>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="61" t="s">
+      <c r="AI1" s="47"/>
+      <c r="AJ1" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="61" t="s">
+      <c r="AK1" s="47"/>
+      <c r="AL1" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="61" t="str">
+      <c r="AM1" s="47"/>
+      <c r="AN1" s="59" t="str">
         <f>Wedstrijden_beheer!AO1</f>
         <v>Patrick</v>
       </c>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="61" t="str">
+      <c r="AO1" s="47"/>
+      <c r="AP1" s="59" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="42" t="str">
+      <c r="AQ1" s="47"/>
+      <c r="AR1" s="46" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="42" t="str">
+      <c r="AS1" s="58"/>
+      <c r="AT1" s="46" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="51"/>
+      <c r="AU1" s="58"/>
     </row>
     <row r="2" spans="1:47" s="28" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="34"/>
@@ -26531,6 +26539,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="V1:W1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
     <mergeCell ref="AF1:AG1"/>
@@ -26542,17 +26561,6 @@
     <mergeCell ref="AD1:AE1"/>
     <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="T1:U1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="V1:W1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26610,7 +26618,7 @@
       </c>
       <c r="C3" s="11">
         <f>SUM(Wedstrijden_beheer!AP3:'Wedstrijden_beheer'!AP194)</f>
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="D3" s="11">
         <f>Bonus_beheer!AO17</f>
@@ -26618,7 +26626,7 @@
       </c>
       <c r="E3" s="11">
         <f>C3+D3</f>
-        <v>213</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26627,20 +26635,20 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f>Wedstrijden_beheer!AA1</f>
-        <v>Ivo</v>
+        <f>Wedstrijden_beheer!I1</f>
+        <v>Abdussamed</v>
       </c>
       <c r="C4" s="11">
-        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
-        <v>209</v>
+        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
+        <v>230</v>
       </c>
       <c r="D4" s="11">
-        <f>Bonus_beheer!AA17</f>
+        <f>Bonus_beheer!I17</f>
         <v>0</v>
       </c>
       <c r="E4" s="11">
         <f>C4+D4</f>
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26654,7 +26662,7 @@
       </c>
       <c r="C5" s="11">
         <f>SUM(Wedstrijden_beheer!F3:'Wedstrijden_beheer'!F194)</f>
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="D5" s="11">
         <f>Bonus_beheer!E17</f>
@@ -26662,7 +26670,7 @@
       </c>
       <c r="E5" s="11">
         <f>C5+D5</f>
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26676,7 +26684,7 @@
       </c>
       <c r="C6" s="11">
         <f>SUM(Wedstrijden_beheer!P3:'Wedstrijden_beheer'!P194)</f>
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D6" s="11">
         <f>Bonus_beheer!O17</f>
@@ -26684,29 +26692,29 @@
       </c>
       <c r="E6" s="11">
         <f>C6+D6</f>
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f>Wedstrijden_beheer!I1</f>
-        <v>Abdussamed</v>
+        <f>Wedstrijden_beheer!U1</f>
+        <v>Tom</v>
       </c>
       <c r="C7" s="11">
-        <f>SUM(Wedstrijden_beheer!J3:'Wedstrijden_beheer'!J194)</f>
-        <v>208</v>
+        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
+        <v>227</v>
       </c>
       <c r="D7" s="11">
-        <f>Bonus_beheer!I17</f>
+        <f>Bonus_beheer!U17</f>
         <v>0</v>
       </c>
       <c r="E7" s="11">
         <f>C7+D7</f>
-        <v>208</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26715,20 +26723,20 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f>Wedstrijden_beheer!U1</f>
-        <v>Tom</v>
+        <f>Wedstrijden_beheer!AE1</f>
+        <v>Jeroen</v>
       </c>
       <c r="C8" s="11">
-        <f>SUM(Wedstrijden_beheer!V3:'Wedstrijden_beheer'!V194)</f>
-        <v>204</v>
+        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
+        <v>225</v>
       </c>
       <c r="D8" s="11">
-        <f>Bonus_beheer!U17</f>
+        <f>Bonus_beheer!AE17</f>
         <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>C8+D8</f>
-        <v>204</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26737,42 +26745,42 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f>Wedstrijden_beheer!Y1</f>
-        <v>Lesley</v>
+        <f>Wedstrijden_beheer!AG1</f>
+        <v>Erwin</v>
       </c>
       <c r="C9" s="11">
-        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
-        <v>203</v>
+        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
+        <v>224</v>
       </c>
       <c r="D9" s="11">
-        <f>Bonus_beheer!Y17</f>
+        <f>Bonus_beheer!AG17</f>
         <v>0</v>
       </c>
       <c r="E9" s="11">
         <f>C9+D9</f>
-        <v>203</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f>Wedstrijden_beheer!AE1</f>
-        <v>Jeroen</v>
+        <f>Wedstrijden_beheer!AK1</f>
+        <v>Kim</v>
       </c>
       <c r="C10" s="11">
-        <f>SUM(Wedstrijden_beheer!AF3:'Wedstrijden_beheer'!AF194)</f>
-        <v>202</v>
+        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
+        <v>224</v>
       </c>
       <c r="D10" s="11">
-        <f>Bonus_beheer!AE17</f>
+        <f>Bonus_beheer!AK17</f>
         <v>0</v>
       </c>
       <c r="E10" s="11">
         <f>C10+D10</f>
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26781,20 +26789,20 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f>Wedstrijden_beheer!AG1</f>
-        <v>Erwin</v>
+        <f>Wedstrijden_beheer!AA1</f>
+        <v>Ivo</v>
       </c>
       <c r="C11" s="11">
-        <f>SUM(Wedstrijden_beheer!AH3:'Wedstrijden_beheer'!AH194)</f>
-        <v>201</v>
+        <f>SUM(Wedstrijden_beheer!AB3:'Wedstrijden_beheer'!AB194)</f>
+        <v>223</v>
       </c>
       <c r="D11" s="11">
-        <f>Bonus_beheer!AG17</f>
+        <f>Bonus_beheer!AA17</f>
         <v>0</v>
       </c>
       <c r="E11" s="11">
         <f>C11+D11</f>
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26803,20 +26811,20 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f>Wedstrijden_beheer!AK1</f>
-        <v>Kim</v>
+        <f>Wedstrijden_beheer!G1</f>
+        <v>Nikki</v>
       </c>
       <c r="C12" s="11">
-        <f>SUM(Wedstrijden_beheer!AL3:'Wedstrijden_beheer'!AL194)</f>
-        <v>201</v>
+        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
+        <v>223</v>
       </c>
       <c r="D12" s="11">
-        <f>Bonus_beheer!AK17</f>
+        <f>Bonus_beheer!G17</f>
         <v>0</v>
       </c>
       <c r="E12" s="11">
         <f>C12+D12</f>
-        <v>201</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26825,20 +26833,20 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f>Wedstrijden_beheer!G1</f>
-        <v>Nikki</v>
+        <f>Wedstrijden_beheer!Y1</f>
+        <v>Lesley</v>
       </c>
       <c r="C13" s="11">
-        <f>SUM(Wedstrijden_beheer!H3:'Wedstrijden_beheer'!H194)</f>
-        <v>200</v>
+        <f>SUM(Wedstrijden_beheer!Z3:'Wedstrijden_beheer'!Z194)</f>
+        <v>219</v>
       </c>
       <c r="D13" s="11">
-        <f>Bonus_beheer!G17</f>
+        <f>Bonus_beheer!Y17</f>
         <v>0</v>
       </c>
       <c r="E13" s="11">
         <f>C13+D13</f>
-        <v>200</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26852,7 +26860,7 @@
       </c>
       <c r="C14" s="11">
         <f>SUM(Wedstrijden_beheer!X3:'Wedstrijden_beheer'!X194)</f>
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D14" s="11">
         <f>Bonus_beheer!W17</f>
@@ -26860,7 +26868,7 @@
       </c>
       <c r="E14" s="11">
         <f>C14+D14</f>
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26874,7 +26882,7 @@
       </c>
       <c r="C15" s="11">
         <f>SUM(Wedstrijden_beheer!AN3:'Wedstrijden_beheer'!AN194)</f>
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D15" s="11">
         <f>Bonus_beheer!AM17</f>
@@ -26882,7 +26890,7 @@
       </c>
       <c r="E15" s="11">
         <f>C15+D15</f>
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26896,7 +26904,7 @@
       </c>
       <c r="C16" s="11">
         <f>SUM(Wedstrijden_beheer!AV4:'Wedstrijden_beheer'!AV195)</f>
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D16" s="11">
         <f>Bonus_beheer!AU18</f>
@@ -26904,7 +26912,7 @@
       </c>
       <c r="E16" s="11">
         <f>C16+D16</f>
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26918,7 +26926,7 @@
       </c>
       <c r="C17" s="11">
         <f>SUM(Wedstrijden_beheer!AV3:'Wedstrijden_beheer'!AV194)</f>
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D17" s="11">
         <f>Bonus_beheer!AU17</f>
@@ -26926,7 +26934,7 @@
       </c>
       <c r="E17" s="11">
         <f>C17+D17</f>
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26940,7 +26948,7 @@
       </c>
       <c r="C18" s="11">
         <f>SUM(Wedstrijden_beheer!N3:'Wedstrijden_beheer'!N194)</f>
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="D18" s="11">
         <f>Bonus_beheer!M17</f>
@@ -26948,7 +26956,7 @@
       </c>
       <c r="E18" s="11">
         <f>C18+D18</f>
-        <v>180</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26962,7 +26970,7 @@
       </c>
       <c r="C19" s="11">
         <f>SUM(Wedstrijden_beheer!AD3:'Wedstrijden_beheer'!AD194)</f>
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D19" s="11">
         <f>Bonus_beheer!AC17</f>
@@ -26970,7 +26978,7 @@
       </c>
       <c r="E19" s="11">
         <f>C19+D19</f>
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -26984,7 +26992,7 @@
       </c>
       <c r="C20" s="11">
         <f>SUM(Wedstrijden_beheer!L3:'Wedstrijden_beheer'!L194)</f>
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="D20" s="11">
         <f>Bonus_beheer!K17</f>
@@ -26992,7 +27000,7 @@
       </c>
       <c r="E20" s="11">
         <f>C20+D20</f>
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -27001,20 +27009,20 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f>Wedstrijden_beheer!S1</f>
-        <v>Marc</v>
+        <f>Wedstrijden_beheer!AI1</f>
+        <v>Tim</v>
       </c>
       <c r="C21" s="11">
-        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
-        <v>153</v>
+        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
+        <v>178</v>
       </c>
       <c r="D21" s="11">
-        <f>Bonus_beheer!S17</f>
+        <f>Bonus_beheer!AI17</f>
         <v>0</v>
       </c>
       <c r="E21" s="11">
         <f>C21+D21</f>
-        <v>153</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -27023,64 +27031,64 @@
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f>Wedstrijden_beheer!AI1</f>
-        <v>Tim</v>
+        <f>Wedstrijden_beheer!AS1</f>
+        <v>Andre</v>
       </c>
       <c r="C22" s="11">
-        <f>SUM(Wedstrijden_beheer!AJ3:'Wedstrijden_beheer'!AJ194)</f>
-        <v>151</v>
+        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
+        <v>172</v>
       </c>
       <c r="D22" s="11">
-        <f>Bonus_beheer!AI17</f>
+        <f>Bonus_beheer!Q18</f>
         <v>0</v>
       </c>
       <c r="E22" s="11">
         <f>C22+D22</f>
-        <v>151</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f>Wedstrijden_beheer!AS1</f>
-        <v>Andre</v>
+        <f>Wedstrijden_beheer!Q1</f>
+        <v>Simone</v>
       </c>
       <c r="C23" s="11">
-        <f>SUM(Wedstrijden_beheer!R4:'Wedstrijden_beheer'!R195)</f>
-        <v>149</v>
+        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
+        <v>172</v>
       </c>
       <c r="D23" s="11">
-        <f>Bonus_beheer!Q18</f>
+        <f>Bonus_beheer!Q17</f>
         <v>0</v>
       </c>
       <c r="E23" s="11">
         <f>C23+D23</f>
-        <v>149</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f>Wedstrijden_beheer!Q1</f>
-        <v>Simone</v>
+        <f>Wedstrijden_beheer!S1</f>
+        <v>Marc</v>
       </c>
       <c r="C24" s="11">
-        <f>SUM(Wedstrijden_beheer!R3:'Wedstrijden_beheer'!R194)</f>
-        <v>149</v>
+        <f>SUM(Wedstrijden_beheer!T3:'Wedstrijden_beheer'!T194)</f>
+        <v>160</v>
       </c>
       <c r="D24" s="11">
-        <f>Bonus_beheer!Q17</f>
+        <f>Bonus_beheer!S17</f>
         <v>0</v>
       </c>
       <c r="E24" s="11">
         <f>C24+D24</f>
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -27452,14 +27460,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27658,27 +27664,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27703,9 +27702,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1601" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5588F279-52C7-423C-818C-CAD1B86D23E5}"/>
+  <xr:revisionPtr revIDLastSave="1603" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005805BF-B461-4B16-850C-BDF6888E3F73}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="2808" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Stand!$E$2:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Wedstrijden_beheer!$A$1:$AV$194</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1376,12 +1377,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1391,8 +1386,32 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1400,31 +1419,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1735,160 +1736,160 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AX194"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="18" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="21" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="21" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="21" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="21" customWidth="1"/>
-    <col min="14" max="14" width="8.5703125" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="21" customWidth="1"/>
-    <col min="16" max="16" width="8.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="21" customWidth="1"/>
-    <col min="18" max="18" width="8.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" style="21" customWidth="1"/>
-    <col min="20" max="20" width="8.5703125" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="21" customWidth="1"/>
-    <col min="24" max="24" width="8.5703125" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="21" customWidth="1"/>
-    <col min="26" max="26" width="8.5703125" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" style="21" customWidth="1"/>
-    <col min="28" max="28" width="8.5703125" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="21" customWidth="1"/>
-    <col min="30" max="30" width="8.5703125" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="21" customWidth="1"/>
-    <col min="32" max="32" width="8.5703125" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="21" customWidth="1"/>
-    <col min="34" max="34" width="8.5703125" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="21" customWidth="1"/>
-    <col min="36" max="36" width="8.5703125" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="21" customWidth="1"/>
-    <col min="38" max="38" width="8.5703125" customWidth="1"/>
-    <col min="39" max="39" width="12.5703125" style="21" customWidth="1"/>
-    <col min="40" max="40" width="8.5703125" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="21" customWidth="1"/>
-    <col min="42" max="42" width="8.5703125" customWidth="1"/>
-    <col min="43" max="43" width="15.5703125" style="21" customWidth="1"/>
-    <col min="44" max="44" width="8.5703125" customWidth="1"/>
-    <col min="45" max="45" width="15.7109375" style="21" customWidth="1"/>
-    <col min="46" max="46" width="8.5703125" customWidth="1"/>
-    <col min="47" max="47" width="15.5703125" style="21" customWidth="1"/>
-    <col min="48" max="48" width="8.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" style="21" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" style="21" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="21" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" style="21" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.5546875" style="21" customWidth="1"/>
+    <col min="14" max="14" width="8.5546875" customWidth="1"/>
+    <col min="15" max="15" width="12.5546875" style="21" customWidth="1"/>
+    <col min="16" max="16" width="8.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.5546875" style="21" customWidth="1"/>
+    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="19" max="19" width="12.5546875" style="21" customWidth="1"/>
+    <col min="20" max="20" width="8.5546875" customWidth="1"/>
+    <col min="21" max="21" width="12.5546875" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" customWidth="1"/>
+    <col min="23" max="23" width="12.5546875" style="21" customWidth="1"/>
+    <col min="24" max="24" width="8.5546875" customWidth="1"/>
+    <col min="25" max="25" width="12.5546875" style="21" customWidth="1"/>
+    <col min="26" max="26" width="8.5546875" customWidth="1"/>
+    <col min="27" max="27" width="12.5546875" style="21" customWidth="1"/>
+    <col min="28" max="28" width="8.5546875" customWidth="1"/>
+    <col min="29" max="29" width="12.5546875" style="21" customWidth="1"/>
+    <col min="30" max="30" width="8.5546875" customWidth="1"/>
+    <col min="31" max="31" width="12.5546875" style="21" customWidth="1"/>
+    <col min="32" max="32" width="8.5546875" customWidth="1"/>
+    <col min="33" max="33" width="12.5546875" style="21" customWidth="1"/>
+    <col min="34" max="34" width="8.5546875" customWidth="1"/>
+    <col min="35" max="35" width="12.5546875" style="21" customWidth="1"/>
+    <col min="36" max="36" width="8.5546875" customWidth="1"/>
+    <col min="37" max="37" width="12.5546875" style="21" customWidth="1"/>
+    <col min="38" max="38" width="8.5546875" customWidth="1"/>
+    <col min="39" max="39" width="12.5546875" style="21" customWidth="1"/>
+    <col min="40" max="40" width="8.5546875" customWidth="1"/>
+    <col min="41" max="41" width="15.5546875" style="21" customWidth="1"/>
+    <col min="42" max="42" width="8.5546875" customWidth="1"/>
+    <col min="43" max="43" width="15.5546875" style="21" customWidth="1"/>
+    <col min="44" max="44" width="8.5546875" customWidth="1"/>
+    <col min="45" max="45" width="15.6640625" style="21" customWidth="1"/>
+    <col min="46" max="46" width="8.5546875" customWidth="1"/>
+    <col min="47" max="47" width="15.5546875" style="21" customWidth="1"/>
+    <col min="48" max="48" width="8.5546875" customWidth="1"/>
     <col min="49" max="50" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51" t="s">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A1" s="52" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="51" t="s">
+      <c r="C1" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="46" t="s">
+      <c r="F1" s="55"/>
+      <c r="G1" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="47"/>
-      <c r="I1" s="46" t="s">
+      <c r="H1" s="43"/>
+      <c r="I1" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="47"/>
-      <c r="K1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="46" t="s">
+      <c r="J1" s="43"/>
+      <c r="K1" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="43"/>
+      <c r="M1" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="47"/>
-      <c r="O1" s="46" t="s">
+      <c r="N1" s="43"/>
+      <c r="O1" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="46" t="s">
+      <c r="P1" s="43"/>
+      <c r="Q1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="47"/>
-      <c r="S1" s="46" t="s">
+      <c r="R1" s="43"/>
+      <c r="S1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="47"/>
-      <c r="U1" s="46" t="s">
+      <c r="T1" s="43"/>
+      <c r="U1" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="47"/>
-      <c r="W1" s="46" t="s">
+      <c r="V1" s="43"/>
+      <c r="W1" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="46" t="s">
+      <c r="X1" s="43"/>
+      <c r="Y1" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="47"/>
-      <c r="AA1" s="46" t="s">
+      <c r="Z1" s="43"/>
+      <c r="AA1" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="47"/>
-      <c r="AC1" s="46" t="s">
+      <c r="AB1" s="43"/>
+      <c r="AC1" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="47"/>
-      <c r="AE1" s="46" t="s">
+      <c r="AD1" s="43"/>
+      <c r="AE1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="47"/>
-      <c r="AG1" s="46" t="s">
+      <c r="AF1" s="43"/>
+      <c r="AG1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="47"/>
-      <c r="AI1" s="46" t="s">
+      <c r="AH1" s="43"/>
+      <c r="AI1" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="47"/>
-      <c r="AK1" s="46" t="s">
+      <c r="AJ1" s="43"/>
+      <c r="AK1" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="47"/>
-      <c r="AM1" s="46" t="s">
+      <c r="AL1" s="43"/>
+      <c r="AM1" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="47"/>
-      <c r="AO1" s="46" t="s">
+      <c r="AN1" s="43"/>
+      <c r="AO1" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="47"/>
-      <c r="AQ1" s="46" t="s">
+      <c r="AP1" s="43"/>
+      <c r="AQ1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="47"/>
-      <c r="AS1" s="46" t="s">
+      <c r="AR1" s="43"/>
+      <c r="AS1" s="42" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="58"/>
-      <c r="AU1" s="46" t="s">
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="58"/>
+      <c r="AV1" s="51"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1896,11 +1897,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A2" s="55"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="52"/>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+      <c r="A2" s="53"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="56"/>
       <c r="E2" s="23" t="s">
         <v>27</v>
       </c>
@@ -2040,115 +2041,115 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
-      <c r="AA3" s="49"/>
-      <c r="AB3" s="49"/>
-      <c r="AC3" s="49"/>
-      <c r="AD3" s="49"/>
-      <c r="AE3" s="49"/>
-      <c r="AF3" s="49"/>
-      <c r="AG3" s="49"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="49"/>
-      <c r="AJ3" s="49"/>
-      <c r="AK3" s="49"/>
-      <c r="AL3" s="49"/>
-      <c r="AM3" s="49"/>
-      <c r="AN3" s="49"/>
-      <c r="AO3" s="49"/>
-      <c r="AP3" s="49"/>
-      <c r="AQ3" s="49"/>
-      <c r="AR3" s="49"/>
-      <c r="AS3" s="49"/>
-      <c r="AT3" s="49"/>
-      <c r="AU3" s="49"/>
-      <c r="AV3" s="50"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="58"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
-    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+    <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="44"/>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44"/>
-      <c r="AR4" s="44"/>
-      <c r="AS4" s="44"/>
-      <c r="AT4" s="44"/>
-      <c r="AU4" s="44"/>
-      <c r="AV4" s="45"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="40"/>
+      <c r="O4" s="40"/>
+      <c r="P4" s="40"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="40"/>
+      <c r="S4" s="40"/>
+      <c r="T4" s="40"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="40"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="40"/>
+      <c r="AB4" s="40"/>
+      <c r="AC4" s="40"/>
+      <c r="AD4" s="40"/>
+      <c r="AE4" s="40"/>
+      <c r="AF4" s="40"/>
+      <c r="AG4" s="40"/>
+      <c r="AH4" s="40"/>
+      <c r="AI4" s="40"/>
+      <c r="AJ4" s="40"/>
+      <c r="AK4" s="40"/>
+      <c r="AL4" s="40"/>
+      <c r="AM4" s="40"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="40"/>
+      <c r="AP4" s="40"/>
+      <c r="AQ4" s="40"/>
+      <c r="AR4" s="40"/>
+      <c r="AS4" s="40"/>
+      <c r="AT4" s="40"/>
+      <c r="AU4" s="40"/>
+      <c r="AV4" s="41"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
-    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>1.875</v>
       </c>
@@ -2324,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12"/>
       <c r="B6" s="17"/>
       <c r="C6" s="13"/>
@@ -2382,61 +2383,61 @@
       <c r="AW6" s="12"/>
       <c r="AX6" s="12"/>
     </row>
-    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
+    <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="44"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="44"/>
-      <c r="Q7" s="44"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44"/>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44"/>
-      <c r="AA7" s="44"/>
-      <c r="AB7" s="44"/>
-      <c r="AC7" s="44"/>
-      <c r="AD7" s="44"/>
-      <c r="AE7" s="44"/>
-      <c r="AF7" s="44"/>
-      <c r="AG7" s="44"/>
-      <c r="AH7" s="44"/>
-      <c r="AI7" s="44"/>
-      <c r="AJ7" s="44"/>
-      <c r="AK7" s="44"/>
-      <c r="AL7" s="44"/>
-      <c r="AM7" s="44"/>
-      <c r="AN7" s="44"/>
-      <c r="AO7" s="44"/>
-      <c r="AP7" s="44"/>
-      <c r="AQ7" s="44"/>
-      <c r="AR7" s="44"/>
-      <c r="AS7" s="44"/>
-      <c r="AT7" s="44"/>
-      <c r="AU7" s="44"/>
-      <c r="AV7" s="45"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="40"/>
+      <c r="V7" s="40"/>
+      <c r="W7" s="40"/>
+      <c r="X7" s="40"/>
+      <c r="Y7" s="40"/>
+      <c r="Z7" s="40"/>
+      <c r="AA7" s="40"/>
+      <c r="AB7" s="40"/>
+      <c r="AC7" s="40"/>
+      <c r="AD7" s="40"/>
+      <c r="AE7" s="40"/>
+      <c r="AF7" s="40"/>
+      <c r="AG7" s="40"/>
+      <c r="AH7" s="40"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
+      <c r="AM7" s="40"/>
+      <c r="AN7" s="40"/>
+      <c r="AO7" s="40"/>
+      <c r="AP7" s="40"/>
+      <c r="AQ7" s="40"/>
+      <c r="AR7" s="40"/>
+      <c r="AS7" s="40"/>
+      <c r="AT7" s="40"/>
+      <c r="AU7" s="40"/>
+      <c r="AV7" s="41"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
-    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -2612,7 +2613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>1.875</v>
       </c>
@@ -2788,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12"/>
       <c r="B10" s="17"/>
       <c r="C10" s="13"/>
@@ -2846,61 +2847,61 @@
       <c r="AW10" s="12"/>
       <c r="AX10" s="12"/>
     </row>
-    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+    <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="44"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="44"/>
-      <c r="AE11" s="44"/>
-      <c r="AF11" s="44"/>
-      <c r="AG11" s="44"/>
-      <c r="AH11" s="44"/>
-      <c r="AI11" s="44"/>
-      <c r="AJ11" s="44"/>
-      <c r="AK11" s="44"/>
-      <c r="AL11" s="44"/>
-      <c r="AM11" s="44"/>
-      <c r="AN11" s="44"/>
-      <c r="AO11" s="44"/>
-      <c r="AP11" s="44"/>
-      <c r="AQ11" s="44"/>
-      <c r="AR11" s="44"/>
-      <c r="AS11" s="44"/>
-      <c r="AT11" s="44"/>
-      <c r="AU11" s="44"/>
-      <c r="AV11" s="45"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
+      <c r="I11" s="40"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+      <c r="R11" s="40"/>
+      <c r="S11" s="40"/>
+      <c r="T11" s="40"/>
+      <c r="U11" s="40"/>
+      <c r="V11" s="40"/>
+      <c r="W11" s="40"/>
+      <c r="X11" s="40"/>
+      <c r="Y11" s="40"/>
+      <c r="Z11" s="40"/>
+      <c r="AA11" s="40"/>
+      <c r="AB11" s="40"/>
+      <c r="AC11" s="40"/>
+      <c r="AD11" s="40"/>
+      <c r="AE11" s="40"/>
+      <c r="AF11" s="40"/>
+      <c r="AG11" s="40"/>
+      <c r="AH11" s="40"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
+      <c r="AM11" s="40"/>
+      <c r="AN11" s="40"/>
+      <c r="AO11" s="40"/>
+      <c r="AP11" s="40"/>
+      <c r="AQ11" s="40"/>
+      <c r="AR11" s="40"/>
+      <c r="AS11" s="40"/>
+      <c r="AT11" s="40"/>
+      <c r="AU11" s="40"/>
+      <c r="AV11" s="41"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
-    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>1.125</v>
       </c>
@@ -3076,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>1.875</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12"/>
       <c r="B14" s="17"/>
       <c r="C14" s="13"/>
@@ -3310,61 +3311,61 @@
       <c r="AW14" s="12"/>
       <c r="AX14" s="12"/>
     </row>
-    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+    <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="44"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="44"/>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="44"/>
-      <c r="S15" s="44"/>
-      <c r="T15" s="44"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="44"/>
-      <c r="W15" s="44"/>
-      <c r="X15" s="44"/>
-      <c r="Y15" s="44"/>
-      <c r="Z15" s="44"/>
-      <c r="AA15" s="44"/>
-      <c r="AB15" s="44"/>
-      <c r="AC15" s="44"/>
-      <c r="AD15" s="44"/>
-      <c r="AE15" s="44"/>
-      <c r="AF15" s="44"/>
-      <c r="AG15" s="44"/>
-      <c r="AH15" s="44"/>
-      <c r="AI15" s="44"/>
-      <c r="AJ15" s="44"/>
-      <c r="AK15" s="44"/>
-      <c r="AL15" s="44"/>
-      <c r="AM15" s="44"/>
-      <c r="AN15" s="44"/>
-      <c r="AO15" s="44"/>
-      <c r="AP15" s="44"/>
-      <c r="AQ15" s="44"/>
-      <c r="AR15" s="44"/>
-      <c r="AS15" s="44"/>
-      <c r="AT15" s="44"/>
-      <c r="AU15" s="44"/>
-      <c r="AV15" s="45"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
+      <c r="AA15" s="40"/>
+      <c r="AB15" s="40"/>
+      <c r="AC15" s="40"/>
+      <c r="AD15" s="40"/>
+      <c r="AE15" s="40"/>
+      <c r="AF15" s="40"/>
+      <c r="AG15" s="40"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="40"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="40"/>
+      <c r="AL15" s="40"/>
+      <c r="AM15" s="40"/>
+      <c r="AN15" s="40"/>
+      <c r="AO15" s="40"/>
+      <c r="AP15" s="40"/>
+      <c r="AQ15" s="40"/>
+      <c r="AR15" s="40"/>
+      <c r="AS15" s="40"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="40"/>
+      <c r="AV15" s="41"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
-    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -3540,7 +3541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>1.125</v>
       </c>
@@ -3716,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>1.25</v>
       </c>
@@ -3892,7 +3893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
       <c r="B21" s="17"/>
       <c r="C21" s="13"/>
@@ -4302,61 +4303,61 @@
       <c r="AW21" s="12"/>
       <c r="AX21" s="12"/>
     </row>
-    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+    <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
-      <c r="N22" s="44"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="44"/>
-      <c r="Q22" s="44"/>
-      <c r="R22" s="44"/>
-      <c r="S22" s="44"/>
-      <c r="T22" s="44"/>
-      <c r="U22" s="44"/>
-      <c r="V22" s="44"/>
-      <c r="W22" s="44"/>
-      <c r="X22" s="44"/>
-      <c r="Y22" s="44"/>
-      <c r="Z22" s="44"/>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="44"/>
-      <c r="AE22" s="44"/>
-      <c r="AF22" s="44"/>
-      <c r="AG22" s="44"/>
-      <c r="AH22" s="44"/>
-      <c r="AI22" s="44"/>
-      <c r="AJ22" s="44"/>
-      <c r="AK22" s="44"/>
-      <c r="AL22" s="44"/>
-      <c r="AM22" s="44"/>
-      <c r="AN22" s="44"/>
-      <c r="AO22" s="44"/>
-      <c r="AP22" s="44"/>
-      <c r="AQ22" s="44"/>
-      <c r="AR22" s="44"/>
-      <c r="AS22" s="44"/>
-      <c r="AT22" s="44"/>
-      <c r="AU22" s="44"/>
-      <c r="AV22" s="45"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+      <c r="R22" s="40"/>
+      <c r="S22" s="40"/>
+      <c r="T22" s="40"/>
+      <c r="U22" s="40"/>
+      <c r="V22" s="40"/>
+      <c r="W22" s="40"/>
+      <c r="X22" s="40"/>
+      <c r="Y22" s="40"/>
+      <c r="Z22" s="40"/>
+      <c r="AA22" s="40"/>
+      <c r="AB22" s="40"/>
+      <c r="AC22" s="40"/>
+      <c r="AD22" s="40"/>
+      <c r="AE22" s="40"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="40"/>
+      <c r="AH22" s="40"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="40"/>
+      <c r="AM22" s="40"/>
+      <c r="AN22" s="40"/>
+      <c r="AO22" s="40"/>
+      <c r="AP22" s="40"/>
+      <c r="AQ22" s="40"/>
+      <c r="AR22" s="40"/>
+      <c r="AS22" s="40"/>
+      <c r="AT22" s="40"/>
+      <c r="AU22" s="40"/>
+      <c r="AV22" s="41"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
-    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -4708,7 +4709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>1.75</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>1.875</v>
       </c>
@@ -5060,7 +5061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12"/>
       <c r="B27" s="17"/>
       <c r="C27" s="13"/>
@@ -5118,61 +5119,61 @@
       <c r="AW27" s="12"/>
       <c r="AX27" s="12"/>
     </row>
-    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+    <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="41"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="40"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="40"/>
-      <c r="U28" s="41"/>
-      <c r="V28" s="40"/>
-      <c r="W28" s="41"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="40"/>
-      <c r="AA28" s="41"/>
-      <c r="AB28" s="40"/>
-      <c r="AC28" s="41"/>
-      <c r="AD28" s="40"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="40"/>
-      <c r="AG28" s="41"/>
-      <c r="AH28" s="40"/>
-      <c r="AI28" s="41"/>
-      <c r="AJ28" s="40"/>
-      <c r="AK28" s="41"/>
-      <c r="AL28" s="40"/>
-      <c r="AM28" s="41"/>
-      <c r="AN28" s="40"/>
-      <c r="AO28" s="41"/>
-      <c r="AP28" s="40"/>
-      <c r="AQ28" s="40"/>
-      <c r="AR28" s="40"/>
-      <c r="AS28" s="40"/>
-      <c r="AT28" s="40"/>
-      <c r="AU28" s="41"/>
-      <c r="AV28" s="42"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="45"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="45"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="45"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="45"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="45"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="45"/>
+      <c r="AA28" s="46"/>
+      <c r="AB28" s="45"/>
+      <c r="AC28" s="46"/>
+      <c r="AD28" s="45"/>
+      <c r="AE28" s="46"/>
+      <c r="AF28" s="45"/>
+      <c r="AG28" s="46"/>
+      <c r="AH28" s="45"/>
+      <c r="AI28" s="46"/>
+      <c r="AJ28" s="45"/>
+      <c r="AK28" s="46"/>
+      <c r="AL28" s="45"/>
+      <c r="AM28" s="46"/>
+      <c r="AN28" s="45"/>
+      <c r="AO28" s="46"/>
+      <c r="AP28" s="45"/>
+      <c r="AQ28" s="45"/>
+      <c r="AR28" s="45"/>
+      <c r="AS28" s="45"/>
+      <c r="AT28" s="45"/>
+      <c r="AU28" s="46"/>
+      <c r="AV28" s="47"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
-    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>1</v>
       </c>
@@ -5348,7 +5349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>1.125</v>
       </c>
@@ -5524,7 +5525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>1.875</v>
       </c>
@@ -5700,7 +5701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="17"/>
       <c r="C32" s="13"/>
@@ -5758,61 +5759,61 @@
       <c r="AW32" s="12"/>
       <c r="AX32" s="12"/>
     </row>
-    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39" t="s">
+    <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="40"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="40"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="40"/>
-      <c r="M33" s="41"/>
-      <c r="N33" s="40"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="40"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="40"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="40"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="40"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="40"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="40"/>
-      <c r="AA33" s="41"/>
-      <c r="AB33" s="40"/>
-      <c r="AC33" s="41"/>
-      <c r="AD33" s="40"/>
-      <c r="AE33" s="41"/>
-      <c r="AF33" s="40"/>
-      <c r="AG33" s="41"/>
-      <c r="AH33" s="40"/>
-      <c r="AI33" s="41"/>
-      <c r="AJ33" s="40"/>
-      <c r="AK33" s="41"/>
-      <c r="AL33" s="40"/>
-      <c r="AM33" s="41"/>
-      <c r="AN33" s="40"/>
-      <c r="AO33" s="41"/>
-      <c r="AP33" s="40"/>
-      <c r="AQ33" s="40"/>
-      <c r="AR33" s="40"/>
-      <c r="AS33" s="40"/>
-      <c r="AT33" s="40"/>
-      <c r="AU33" s="41"/>
-      <c r="AV33" s="42"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="45"/>
+      <c r="Q33" s="46"/>
+      <c r="R33" s="45"/>
+      <c r="S33" s="46"/>
+      <c r="T33" s="45"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="45"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="45"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="45"/>
+      <c r="AA33" s="46"/>
+      <c r="AB33" s="45"/>
+      <c r="AC33" s="46"/>
+      <c r="AD33" s="45"/>
+      <c r="AE33" s="46"/>
+      <c r="AF33" s="45"/>
+      <c r="AG33" s="46"/>
+      <c r="AH33" s="45"/>
+      <c r="AI33" s="46"/>
+      <c r="AJ33" s="45"/>
+      <c r="AK33" s="46"/>
+      <c r="AL33" s="45"/>
+      <c r="AM33" s="46"/>
+      <c r="AN33" s="45"/>
+      <c r="AO33" s="46"/>
+      <c r="AP33" s="45"/>
+      <c r="AQ33" s="45"/>
+      <c r="AR33" s="45"/>
+      <c r="AS33" s="45"/>
+      <c r="AT33" s="45"/>
+      <c r="AU33" s="46"/>
+      <c r="AV33" s="47"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
-    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>1</v>
       </c>
@@ -5988,7 +5989,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>1.125</v>
       </c>
@@ -6164,7 +6165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>1.25</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -6516,7 +6517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -6692,7 +6693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12"/>
       <c r="B39" s="17"/>
       <c r="C39" s="13"/>
@@ -6750,61 +6751,61 @@
       <c r="AW39" s="12"/>
       <c r="AX39" s="12"/>
     </row>
-    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="39" t="s">
+    <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="40"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="40"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="40"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="40"/>
-      <c r="M40" s="41"/>
-      <c r="N40" s="40"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="41"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="41"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="41"/>
-      <c r="V40" s="40"/>
-      <c r="W40" s="41"/>
-      <c r="X40" s="40"/>
-      <c r="Y40" s="41"/>
-      <c r="Z40" s="40"/>
-      <c r="AA40" s="41"/>
-      <c r="AB40" s="40"/>
-      <c r="AC40" s="41"/>
-      <c r="AD40" s="40"/>
-      <c r="AE40" s="41"/>
-      <c r="AF40" s="40"/>
-      <c r="AG40" s="41"/>
-      <c r="AH40" s="40"/>
-      <c r="AI40" s="41"/>
-      <c r="AJ40" s="40"/>
-      <c r="AK40" s="41"/>
-      <c r="AL40" s="40"/>
-      <c r="AM40" s="41"/>
-      <c r="AN40" s="40"/>
-      <c r="AO40" s="41"/>
-      <c r="AP40" s="40"/>
-      <c r="AQ40" s="40"/>
-      <c r="AR40" s="40"/>
-      <c r="AS40" s="40"/>
-      <c r="AT40" s="40"/>
-      <c r="AU40" s="41"/>
-      <c r="AV40" s="42"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="46"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="46"/>
+      <c r="N40" s="45"/>
+      <c r="O40" s="46"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="46"/>
+      <c r="R40" s="45"/>
+      <c r="S40" s="46"/>
+      <c r="T40" s="45"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="45"/>
+      <c r="W40" s="46"/>
+      <c r="X40" s="45"/>
+      <c r="Y40" s="46"/>
+      <c r="Z40" s="45"/>
+      <c r="AA40" s="46"/>
+      <c r="AB40" s="45"/>
+      <c r="AC40" s="46"/>
+      <c r="AD40" s="45"/>
+      <c r="AE40" s="46"/>
+      <c r="AF40" s="45"/>
+      <c r="AG40" s="46"/>
+      <c r="AH40" s="45"/>
+      <c r="AI40" s="46"/>
+      <c r="AJ40" s="45"/>
+      <c r="AK40" s="46"/>
+      <c r="AL40" s="45"/>
+      <c r="AM40" s="46"/>
+      <c r="AN40" s="45"/>
+      <c r="AO40" s="46"/>
+      <c r="AP40" s="45"/>
+      <c r="AQ40" s="45"/>
+      <c r="AR40" s="45"/>
+      <c r="AS40" s="45"/>
+      <c r="AT40" s="45"/>
+      <c r="AU40" s="46"/>
+      <c r="AV40" s="47"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
-    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -6980,7 +6981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -7156,7 +7157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>1.75</v>
       </c>
@@ -7332,7 +7333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>1.875</v>
       </c>
@@ -7508,7 +7509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12"/>
       <c r="B45" s="17"/>
       <c r="C45" s="13"/>
@@ -7566,61 +7567,61 @@
       <c r="AW45" s="12"/>
       <c r="AX45" s="12"/>
     </row>
-    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
+    <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="40"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="40"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="40"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="40"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="40"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="40"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="40"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="40"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="40"/>
-      <c r="Y46" s="41"/>
-      <c r="Z46" s="40"/>
-      <c r="AA46" s="41"/>
-      <c r="AB46" s="40"/>
-      <c r="AC46" s="41"/>
-      <c r="AD46" s="40"/>
-      <c r="AE46" s="41"/>
-      <c r="AF46" s="40"/>
-      <c r="AG46" s="41"/>
-      <c r="AH46" s="40"/>
-      <c r="AI46" s="41"/>
-      <c r="AJ46" s="40"/>
-      <c r="AK46" s="41"/>
-      <c r="AL46" s="40"/>
-      <c r="AM46" s="41"/>
-      <c r="AN46" s="40"/>
-      <c r="AO46" s="41"/>
-      <c r="AP46" s="40"/>
-      <c r="AQ46" s="40"/>
-      <c r="AR46" s="40"/>
-      <c r="AS46" s="40"/>
-      <c r="AT46" s="40"/>
-      <c r="AU46" s="41"/>
-      <c r="AV46" s="42"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="46"/>
+      <c r="H46" s="45"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="45"/>
+      <c r="K46" s="46"/>
+      <c r="L46" s="45"/>
+      <c r="M46" s="46"/>
+      <c r="N46" s="45"/>
+      <c r="O46" s="46"/>
+      <c r="P46" s="45"/>
+      <c r="Q46" s="46"/>
+      <c r="R46" s="45"/>
+      <c r="S46" s="46"/>
+      <c r="T46" s="45"/>
+      <c r="U46" s="46"/>
+      <c r="V46" s="45"/>
+      <c r="W46" s="46"/>
+      <c r="X46" s="45"/>
+      <c r="Y46" s="46"/>
+      <c r="Z46" s="45"/>
+      <c r="AA46" s="46"/>
+      <c r="AB46" s="45"/>
+      <c r="AC46" s="46"/>
+      <c r="AD46" s="45"/>
+      <c r="AE46" s="46"/>
+      <c r="AF46" s="45"/>
+      <c r="AG46" s="46"/>
+      <c r="AH46" s="45"/>
+      <c r="AI46" s="46"/>
+      <c r="AJ46" s="45"/>
+      <c r="AK46" s="46"/>
+      <c r="AL46" s="45"/>
+      <c r="AM46" s="46"/>
+      <c r="AN46" s="45"/>
+      <c r="AO46" s="46"/>
+      <c r="AP46" s="45"/>
+      <c r="AQ46" s="45"/>
+      <c r="AR46" s="45"/>
+      <c r="AS46" s="45"/>
+      <c r="AT46" s="45"/>
+      <c r="AU46" s="46"/>
+      <c r="AV46" s="47"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
-    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>1</v>
       </c>
@@ -7796,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>1.125</v>
       </c>
@@ -7972,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>1.875</v>
       </c>
@@ -8148,7 +8149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12"/>
       <c r="B50" s="17"/>
       <c r="C50" s="13"/>
@@ -8206,61 +8207,61 @@
       <c r="AW50" s="12"/>
       <c r="AX50" s="12"/>
     </row>
-    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="39" t="s">
+    <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="40"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="40"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="40"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="40"/>
-      <c r="S51" s="41"/>
-      <c r="T51" s="40"/>
-      <c r="U51" s="41"/>
-      <c r="V51" s="40"/>
-      <c r="W51" s="41"/>
-      <c r="X51" s="40"/>
-      <c r="Y51" s="41"/>
-      <c r="Z51" s="40"/>
-      <c r="AA51" s="41"/>
-      <c r="AB51" s="40"/>
-      <c r="AC51" s="41"/>
-      <c r="AD51" s="40"/>
-      <c r="AE51" s="41"/>
-      <c r="AF51" s="40"/>
-      <c r="AG51" s="41"/>
-      <c r="AH51" s="40"/>
-      <c r="AI51" s="41"/>
-      <c r="AJ51" s="40"/>
-      <c r="AK51" s="41"/>
-      <c r="AL51" s="40"/>
-      <c r="AM51" s="41"/>
-      <c r="AN51" s="40"/>
-      <c r="AO51" s="41"/>
-      <c r="AP51" s="40"/>
-      <c r="AQ51" s="40"/>
-      <c r="AR51" s="40"/>
-      <c r="AS51" s="40"/>
-      <c r="AT51" s="40"/>
-      <c r="AU51" s="41"/>
-      <c r="AV51" s="42"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="46"/>
+      <c r="H51" s="45"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="45"/>
+      <c r="K51" s="46"/>
+      <c r="L51" s="45"/>
+      <c r="M51" s="46"/>
+      <c r="N51" s="45"/>
+      <c r="O51" s="46"/>
+      <c r="P51" s="45"/>
+      <c r="Q51" s="46"/>
+      <c r="R51" s="45"/>
+      <c r="S51" s="46"/>
+      <c r="T51" s="45"/>
+      <c r="U51" s="46"/>
+      <c r="V51" s="45"/>
+      <c r="W51" s="46"/>
+      <c r="X51" s="45"/>
+      <c r="Y51" s="46"/>
+      <c r="Z51" s="45"/>
+      <c r="AA51" s="46"/>
+      <c r="AB51" s="45"/>
+      <c r="AC51" s="46"/>
+      <c r="AD51" s="45"/>
+      <c r="AE51" s="46"/>
+      <c r="AF51" s="45"/>
+      <c r="AG51" s="46"/>
+      <c r="AH51" s="45"/>
+      <c r="AI51" s="46"/>
+      <c r="AJ51" s="45"/>
+      <c r="AK51" s="46"/>
+      <c r="AL51" s="45"/>
+      <c r="AM51" s="46"/>
+      <c r="AN51" s="45"/>
+      <c r="AO51" s="46"/>
+      <c r="AP51" s="45"/>
+      <c r="AQ51" s="45"/>
+      <c r="AR51" s="45"/>
+      <c r="AS51" s="45"/>
+      <c r="AT51" s="45"/>
+      <c r="AU51" s="46"/>
+      <c r="AV51" s="47"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
-    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>1</v>
       </c>
@@ -8436,7 +8437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>1.125</v>
       </c>
@@ -8612,7 +8613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>1.25</v>
       </c>
@@ -8788,7 +8789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -8964,7 +8965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -9140,7 +9141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12"/>
       <c r="B57" s="17"/>
       <c r="C57" s="13"/>
@@ -9198,61 +9199,61 @@
       <c r="AW57" s="12"/>
       <c r="AX57" s="12"/>
     </row>
-    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="39" t="s">
+    <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="40"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="40"/>
-      <c r="M58" s="41"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="41"/>
-      <c r="P58" s="40"/>
-      <c r="Q58" s="41"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="41"/>
-      <c r="T58" s="40"/>
-      <c r="U58" s="41"/>
-      <c r="V58" s="40"/>
-      <c r="W58" s="41"/>
-      <c r="X58" s="40"/>
-      <c r="Y58" s="41"/>
-      <c r="Z58" s="40"/>
-      <c r="AA58" s="41"/>
-      <c r="AB58" s="40"/>
-      <c r="AC58" s="41"/>
-      <c r="AD58" s="40"/>
-      <c r="AE58" s="41"/>
-      <c r="AF58" s="40"/>
-      <c r="AG58" s="41"/>
-      <c r="AH58" s="40"/>
-      <c r="AI58" s="41"/>
-      <c r="AJ58" s="40"/>
-      <c r="AK58" s="41"/>
-      <c r="AL58" s="40"/>
-      <c r="AM58" s="41"/>
-      <c r="AN58" s="40"/>
-      <c r="AO58" s="41"/>
-      <c r="AP58" s="40"/>
-      <c r="AQ58" s="40"/>
-      <c r="AR58" s="40"/>
-      <c r="AS58" s="40"/>
-      <c r="AT58" s="40"/>
-      <c r="AU58" s="41"/>
-      <c r="AV58" s="42"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="45"/>
+      <c r="I58" s="46"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="46"/>
+      <c r="L58" s="45"/>
+      <c r="M58" s="46"/>
+      <c r="N58" s="45"/>
+      <c r="O58" s="46"/>
+      <c r="P58" s="45"/>
+      <c r="Q58" s="46"/>
+      <c r="R58" s="45"/>
+      <c r="S58" s="46"/>
+      <c r="T58" s="45"/>
+      <c r="U58" s="46"/>
+      <c r="V58" s="45"/>
+      <c r="W58" s="46"/>
+      <c r="X58" s="45"/>
+      <c r="Y58" s="46"/>
+      <c r="Z58" s="45"/>
+      <c r="AA58" s="46"/>
+      <c r="AB58" s="45"/>
+      <c r="AC58" s="46"/>
+      <c r="AD58" s="45"/>
+      <c r="AE58" s="46"/>
+      <c r="AF58" s="45"/>
+      <c r="AG58" s="46"/>
+      <c r="AH58" s="45"/>
+      <c r="AI58" s="46"/>
+      <c r="AJ58" s="45"/>
+      <c r="AK58" s="46"/>
+      <c r="AL58" s="45"/>
+      <c r="AM58" s="46"/>
+      <c r="AN58" s="45"/>
+      <c r="AO58" s="46"/>
+      <c r="AP58" s="45"/>
+      <c r="AQ58" s="45"/>
+      <c r="AR58" s="45"/>
+      <c r="AS58" s="45"/>
+      <c r="AT58" s="45"/>
+      <c r="AU58" s="46"/>
+      <c r="AV58" s="47"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
-    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -9428,7 +9429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>1.25</v>
       </c>
@@ -9604,7 +9605,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>1.75</v>
       </c>
@@ -9780,7 +9781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>1.875</v>
       </c>
@@ -9956,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12"/>
       <c r="B63" s="17"/>
       <c r="C63" s="13"/>
@@ -10014,61 +10015,61 @@
       <c r="AW63" s="12"/>
       <c r="AX63" s="12"/>
     </row>
-    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="39" t="s">
+    <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="40"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="40"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="40"/>
-      <c r="I64" s="41"/>
-      <c r="J64" s="40"/>
-      <c r="K64" s="41"/>
-      <c r="L64" s="40"/>
-      <c r="M64" s="41"/>
-      <c r="N64" s="40"/>
-      <c r="O64" s="41"/>
-      <c r="P64" s="40"/>
-      <c r="Q64" s="41"/>
-      <c r="R64" s="40"/>
-      <c r="S64" s="41"/>
-      <c r="T64" s="40"/>
-      <c r="U64" s="41"/>
-      <c r="V64" s="40"/>
-      <c r="W64" s="41"/>
-      <c r="X64" s="40"/>
-      <c r="Y64" s="41"/>
-      <c r="Z64" s="40"/>
-      <c r="AA64" s="41"/>
-      <c r="AB64" s="40"/>
-      <c r="AC64" s="41"/>
-      <c r="AD64" s="40"/>
-      <c r="AE64" s="41"/>
-      <c r="AF64" s="40"/>
-      <c r="AG64" s="41"/>
-      <c r="AH64" s="40"/>
-      <c r="AI64" s="41"/>
-      <c r="AJ64" s="40"/>
-      <c r="AK64" s="41"/>
-      <c r="AL64" s="40"/>
-      <c r="AM64" s="41"/>
-      <c r="AN64" s="40"/>
-      <c r="AO64" s="41"/>
-      <c r="AP64" s="40"/>
-      <c r="AQ64" s="40"/>
-      <c r="AR64" s="40"/>
-      <c r="AS64" s="40"/>
-      <c r="AT64" s="40"/>
-      <c r="AU64" s="41"/>
-      <c r="AV64" s="42"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="46"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="45"/>
+      <c r="I64" s="46"/>
+      <c r="J64" s="45"/>
+      <c r="K64" s="46"/>
+      <c r="L64" s="45"/>
+      <c r="M64" s="46"/>
+      <c r="N64" s="45"/>
+      <c r="O64" s="46"/>
+      <c r="P64" s="45"/>
+      <c r="Q64" s="46"/>
+      <c r="R64" s="45"/>
+      <c r="S64" s="46"/>
+      <c r="T64" s="45"/>
+      <c r="U64" s="46"/>
+      <c r="V64" s="45"/>
+      <c r="W64" s="46"/>
+      <c r="X64" s="45"/>
+      <c r="Y64" s="46"/>
+      <c r="Z64" s="45"/>
+      <c r="AA64" s="46"/>
+      <c r="AB64" s="45"/>
+      <c r="AC64" s="46"/>
+      <c r="AD64" s="45"/>
+      <c r="AE64" s="46"/>
+      <c r="AF64" s="45"/>
+      <c r="AG64" s="46"/>
+      <c r="AH64" s="45"/>
+      <c r="AI64" s="46"/>
+      <c r="AJ64" s="45"/>
+      <c r="AK64" s="46"/>
+      <c r="AL64" s="45"/>
+      <c r="AM64" s="46"/>
+      <c r="AN64" s="45"/>
+      <c r="AO64" s="46"/>
+      <c r="AP64" s="45"/>
+      <c r="AQ64" s="45"/>
+      <c r="AR64" s="45"/>
+      <c r="AS64" s="45"/>
+      <c r="AT64" s="45"/>
+      <c r="AU64" s="46"/>
+      <c r="AV64" s="47"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
-    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>1</v>
       </c>
@@ -10244,7 +10245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>1.125</v>
       </c>
@@ -10420,7 +10421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -10596,7 +10597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -10772,7 +10773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="12"/>
       <c r="B69" s="17"/>
       <c r="C69" s="13"/>
@@ -10830,61 +10831,61 @@
       <c r="AW69" s="12"/>
       <c r="AX69" s="12"/>
     </row>
-    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="39" t="s">
+    <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="40"/>
-      <c r="C70" s="41"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="41"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="41"/>
-      <c r="H70" s="40"/>
-      <c r="I70" s="41"/>
-      <c r="J70" s="40"/>
-      <c r="K70" s="41"/>
-      <c r="L70" s="40"/>
-      <c r="M70" s="41"/>
-      <c r="N70" s="40"/>
-      <c r="O70" s="41"/>
-      <c r="P70" s="40"/>
-      <c r="Q70" s="41"/>
-      <c r="R70" s="40"/>
-      <c r="S70" s="41"/>
-      <c r="T70" s="40"/>
-      <c r="U70" s="41"/>
-      <c r="V70" s="40"/>
-      <c r="W70" s="41"/>
-      <c r="X70" s="40"/>
-      <c r="Y70" s="41"/>
-      <c r="Z70" s="40"/>
-      <c r="AA70" s="41"/>
-      <c r="AB70" s="40"/>
-      <c r="AC70" s="41"/>
-      <c r="AD70" s="40"/>
-      <c r="AE70" s="41"/>
-      <c r="AF70" s="40"/>
-      <c r="AG70" s="41"/>
-      <c r="AH70" s="40"/>
-      <c r="AI70" s="41"/>
-      <c r="AJ70" s="40"/>
-      <c r="AK70" s="41"/>
-      <c r="AL70" s="40"/>
-      <c r="AM70" s="41"/>
-      <c r="AN70" s="40"/>
-      <c r="AO70" s="41"/>
-      <c r="AP70" s="40"/>
-      <c r="AQ70" s="40"/>
-      <c r="AR70" s="40"/>
-      <c r="AS70" s="40"/>
-      <c r="AT70" s="40"/>
-      <c r="AU70" s="41"/>
-      <c r="AV70" s="42"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="46"/>
+      <c r="J70" s="45"/>
+      <c r="K70" s="46"/>
+      <c r="L70" s="45"/>
+      <c r="M70" s="46"/>
+      <c r="N70" s="45"/>
+      <c r="O70" s="46"/>
+      <c r="P70" s="45"/>
+      <c r="Q70" s="46"/>
+      <c r="R70" s="45"/>
+      <c r="S70" s="46"/>
+      <c r="T70" s="45"/>
+      <c r="U70" s="46"/>
+      <c r="V70" s="45"/>
+      <c r="W70" s="46"/>
+      <c r="X70" s="45"/>
+      <c r="Y70" s="46"/>
+      <c r="Z70" s="45"/>
+      <c r="AA70" s="46"/>
+      <c r="AB70" s="45"/>
+      <c r="AC70" s="46"/>
+      <c r="AD70" s="45"/>
+      <c r="AE70" s="46"/>
+      <c r="AF70" s="45"/>
+      <c r="AG70" s="46"/>
+      <c r="AH70" s="45"/>
+      <c r="AI70" s="46"/>
+      <c r="AJ70" s="45"/>
+      <c r="AK70" s="46"/>
+      <c r="AL70" s="45"/>
+      <c r="AM70" s="46"/>
+      <c r="AN70" s="45"/>
+      <c r="AO70" s="46"/>
+      <c r="AP70" s="45"/>
+      <c r="AQ70" s="45"/>
+      <c r="AR70" s="45"/>
+      <c r="AS70" s="45"/>
+      <c r="AT70" s="45"/>
+      <c r="AU70" s="46"/>
+      <c r="AV70" s="47"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
-    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -11060,7 +11061,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -11236,7 +11237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -11412,7 +11413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -11588,7 +11589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12"/>
       <c r="B75" s="17"/>
       <c r="C75" s="13"/>
@@ -11646,61 +11647,61 @@
       <c r="AW75" s="12"/>
       <c r="AX75" s="12"/>
     </row>
-    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="39" t="s">
+    <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="40"/>
-      <c r="C76" s="41"/>
-      <c r="D76" s="40"/>
-      <c r="E76" s="41"/>
-      <c r="F76" s="40"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="40"/>
-      <c r="I76" s="41"/>
-      <c r="J76" s="40"/>
-      <c r="K76" s="41"/>
-      <c r="L76" s="40"/>
-      <c r="M76" s="41"/>
-      <c r="N76" s="40"/>
-      <c r="O76" s="41"/>
-      <c r="P76" s="40"/>
-      <c r="Q76" s="41"/>
-      <c r="R76" s="40"/>
-      <c r="S76" s="41"/>
-      <c r="T76" s="40"/>
-      <c r="U76" s="41"/>
-      <c r="V76" s="40"/>
-      <c r="W76" s="41"/>
-      <c r="X76" s="40"/>
-      <c r="Y76" s="41"/>
-      <c r="Z76" s="40"/>
-      <c r="AA76" s="41"/>
-      <c r="AB76" s="40"/>
-      <c r="AC76" s="41"/>
-      <c r="AD76" s="40"/>
-      <c r="AE76" s="41"/>
-      <c r="AF76" s="40"/>
-      <c r="AG76" s="41"/>
-      <c r="AH76" s="40"/>
-      <c r="AI76" s="41"/>
-      <c r="AJ76" s="40"/>
-      <c r="AK76" s="41"/>
-      <c r="AL76" s="40"/>
-      <c r="AM76" s="41"/>
-      <c r="AN76" s="40"/>
-      <c r="AO76" s="41"/>
-      <c r="AP76" s="40"/>
-      <c r="AQ76" s="40"/>
-      <c r="AR76" s="40"/>
-      <c r="AS76" s="40"/>
-      <c r="AT76" s="40"/>
-      <c r="AU76" s="41"/>
-      <c r="AV76" s="42"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="46"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="46"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="46"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="46"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="46"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="46"/>
+      <c r="P76" s="45"/>
+      <c r="Q76" s="46"/>
+      <c r="R76" s="45"/>
+      <c r="S76" s="46"/>
+      <c r="T76" s="45"/>
+      <c r="U76" s="46"/>
+      <c r="V76" s="45"/>
+      <c r="W76" s="46"/>
+      <c r="X76" s="45"/>
+      <c r="Y76" s="46"/>
+      <c r="Z76" s="45"/>
+      <c r="AA76" s="46"/>
+      <c r="AB76" s="45"/>
+      <c r="AC76" s="46"/>
+      <c r="AD76" s="45"/>
+      <c r="AE76" s="46"/>
+      <c r="AF76" s="45"/>
+      <c r="AG76" s="46"/>
+      <c r="AH76" s="45"/>
+      <c r="AI76" s="46"/>
+      <c r="AJ76" s="45"/>
+      <c r="AK76" s="46"/>
+      <c r="AL76" s="45"/>
+      <c r="AM76" s="46"/>
+      <c r="AN76" s="45"/>
+      <c r="AO76" s="46"/>
+      <c r="AP76" s="45"/>
+      <c r="AQ76" s="45"/>
+      <c r="AR76" s="45"/>
+      <c r="AS76" s="45"/>
+      <c r="AT76" s="45"/>
+      <c r="AU76" s="46"/>
+      <c r="AV76" s="47"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
-    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -12052,7 +12053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>1.875</v>
       </c>
@@ -12226,7 +12227,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>1.875</v>
       </c>
@@ -12400,7 +12401,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12"/>
       <c r="B81" s="17"/>
       <c r="C81" s="13"/>
@@ -12458,61 +12459,61 @@
       <c r="AW81" s="12"/>
       <c r="AX81" s="12"/>
     </row>
-    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="39" t="s">
+    <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="40"/>
-      <c r="C82" s="41"/>
-      <c r="D82" s="40"/>
-      <c r="E82" s="41"/>
-      <c r="F82" s="40"/>
-      <c r="G82" s="41"/>
-      <c r="H82" s="40"/>
-      <c r="I82" s="41"/>
-      <c r="J82" s="40"/>
-      <c r="K82" s="41"/>
-      <c r="L82" s="40"/>
-      <c r="M82" s="41"/>
-      <c r="N82" s="40"/>
-      <c r="O82" s="41"/>
-      <c r="P82" s="40"/>
-      <c r="Q82" s="41"/>
-      <c r="R82" s="40"/>
-      <c r="S82" s="41"/>
-      <c r="T82" s="40"/>
-      <c r="U82" s="41"/>
-      <c r="V82" s="40"/>
-      <c r="W82" s="41"/>
-      <c r="X82" s="40"/>
-      <c r="Y82" s="41"/>
-      <c r="Z82" s="40"/>
-      <c r="AA82" s="41"/>
-      <c r="AB82" s="40"/>
-      <c r="AC82" s="41"/>
-      <c r="AD82" s="40"/>
-      <c r="AE82" s="41"/>
-      <c r="AF82" s="40"/>
-      <c r="AG82" s="41"/>
-      <c r="AH82" s="40"/>
-      <c r="AI82" s="41"/>
-      <c r="AJ82" s="40"/>
-      <c r="AK82" s="41"/>
-      <c r="AL82" s="40"/>
-      <c r="AM82" s="41"/>
-      <c r="AN82" s="40"/>
-      <c r="AO82" s="41"/>
-      <c r="AP82" s="40"/>
-      <c r="AQ82" s="40"/>
-      <c r="AR82" s="40"/>
-      <c r="AS82" s="40"/>
-      <c r="AT82" s="40"/>
-      <c r="AU82" s="41"/>
-      <c r="AV82" s="42"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="46"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="46"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="46"/>
+      <c r="H82" s="45"/>
+      <c r="I82" s="46"/>
+      <c r="J82" s="45"/>
+      <c r="K82" s="46"/>
+      <c r="L82" s="45"/>
+      <c r="M82" s="46"/>
+      <c r="N82" s="45"/>
+      <c r="O82" s="46"/>
+      <c r="P82" s="45"/>
+      <c r="Q82" s="46"/>
+      <c r="R82" s="45"/>
+      <c r="S82" s="46"/>
+      <c r="T82" s="45"/>
+      <c r="U82" s="46"/>
+      <c r="V82" s="45"/>
+      <c r="W82" s="46"/>
+      <c r="X82" s="45"/>
+      <c r="Y82" s="46"/>
+      <c r="Z82" s="45"/>
+      <c r="AA82" s="46"/>
+      <c r="AB82" s="45"/>
+      <c r="AC82" s="46"/>
+      <c r="AD82" s="45"/>
+      <c r="AE82" s="46"/>
+      <c r="AF82" s="45"/>
+      <c r="AG82" s="46"/>
+      <c r="AH82" s="45"/>
+      <c r="AI82" s="46"/>
+      <c r="AJ82" s="45"/>
+      <c r="AK82" s="46"/>
+      <c r="AL82" s="45"/>
+      <c r="AM82" s="46"/>
+      <c r="AN82" s="45"/>
+      <c r="AO82" s="46"/>
+      <c r="AP82" s="45"/>
+      <c r="AQ82" s="45"/>
+      <c r="AR82" s="45"/>
+      <c r="AS82" s="45"/>
+      <c r="AT82" s="45"/>
+      <c r="AU82" s="46"/>
+      <c r="AV82" s="47"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
-    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>1</v>
       </c>
@@ -12686,7 +12687,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>1</v>
       </c>
@@ -12860,7 +12861,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>1.125</v>
       </c>
@@ -13034,7 +13035,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>1.125</v>
       </c>
@@ -13208,7 +13209,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13382,7 +13383,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12"/>
       <c r="B89" s="17"/>
       <c r="C89" s="13"/>
@@ -13614,61 +13615,61 @@
       <c r="AW89" s="12"/>
       <c r="AX89" s="12"/>
     </row>
-    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="39" t="s">
+    <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="40"/>
-      <c r="C90" s="41"/>
-      <c r="D90" s="40"/>
-      <c r="E90" s="41"/>
-      <c r="F90" s="40"/>
-      <c r="G90" s="41"/>
-      <c r="H90" s="40"/>
-      <c r="I90" s="41"/>
-      <c r="J90" s="40"/>
-      <c r="K90" s="41"/>
-      <c r="L90" s="40"/>
-      <c r="M90" s="41"/>
-      <c r="N90" s="40"/>
-      <c r="O90" s="41"/>
-      <c r="P90" s="40"/>
-      <c r="Q90" s="41"/>
-      <c r="R90" s="40"/>
-      <c r="S90" s="41"/>
-      <c r="T90" s="40"/>
-      <c r="U90" s="41"/>
-      <c r="V90" s="40"/>
-      <c r="W90" s="41"/>
-      <c r="X90" s="40"/>
-      <c r="Y90" s="41"/>
-      <c r="Z90" s="40"/>
-      <c r="AA90" s="41"/>
-      <c r="AB90" s="40"/>
-      <c r="AC90" s="41"/>
-      <c r="AD90" s="40"/>
-      <c r="AE90" s="41"/>
-      <c r="AF90" s="40"/>
-      <c r="AG90" s="41"/>
-      <c r="AH90" s="40"/>
-      <c r="AI90" s="41"/>
-      <c r="AJ90" s="40"/>
-      <c r="AK90" s="41"/>
-      <c r="AL90" s="40"/>
-      <c r="AM90" s="41"/>
-      <c r="AN90" s="40"/>
-      <c r="AO90" s="41"/>
-      <c r="AP90" s="40"/>
-      <c r="AQ90" s="40"/>
-      <c r="AR90" s="40"/>
-      <c r="AS90" s="40"/>
-      <c r="AT90" s="40"/>
-      <c r="AU90" s="41"/>
-      <c r="AV90" s="42"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="46"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="46"/>
+      <c r="H90" s="45"/>
+      <c r="I90" s="46"/>
+      <c r="J90" s="45"/>
+      <c r="K90" s="46"/>
+      <c r="L90" s="45"/>
+      <c r="M90" s="46"/>
+      <c r="N90" s="45"/>
+      <c r="O90" s="46"/>
+      <c r="P90" s="45"/>
+      <c r="Q90" s="46"/>
+      <c r="R90" s="45"/>
+      <c r="S90" s="46"/>
+      <c r="T90" s="45"/>
+      <c r="U90" s="46"/>
+      <c r="V90" s="45"/>
+      <c r="W90" s="46"/>
+      <c r="X90" s="45"/>
+      <c r="Y90" s="46"/>
+      <c r="Z90" s="45"/>
+      <c r="AA90" s="46"/>
+      <c r="AB90" s="45"/>
+      <c r="AC90" s="46"/>
+      <c r="AD90" s="45"/>
+      <c r="AE90" s="46"/>
+      <c r="AF90" s="45"/>
+      <c r="AG90" s="46"/>
+      <c r="AH90" s="45"/>
+      <c r="AI90" s="46"/>
+      <c r="AJ90" s="45"/>
+      <c r="AK90" s="46"/>
+      <c r="AL90" s="45"/>
+      <c r="AM90" s="46"/>
+      <c r="AN90" s="45"/>
+      <c r="AO90" s="46"/>
+      <c r="AP90" s="45"/>
+      <c r="AQ90" s="45"/>
+      <c r="AR90" s="45"/>
+      <c r="AS90" s="45"/>
+      <c r="AT90" s="45"/>
+      <c r="AU90" s="46"/>
+      <c r="AV90" s="47"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
-    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -13842,7 +13843,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -14016,7 +14017,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14190,7 +14191,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>1.875</v>
       </c>
@@ -14538,7 +14539,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>1.875</v>
       </c>
@@ -14712,7 +14713,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12"/>
       <c r="B97" s="17"/>
       <c r="C97" s="13"/>
@@ -14770,61 +14771,61 @@
       <c r="AW97" s="12"/>
       <c r="AX97" s="12"/>
     </row>
-    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="39" t="s">
+    <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="40"/>
-      <c r="C98" s="41"/>
-      <c r="D98" s="40"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="40"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="40"/>
-      <c r="I98" s="41"/>
-      <c r="J98" s="40"/>
-      <c r="K98" s="41"/>
-      <c r="L98" s="40"/>
-      <c r="M98" s="41"/>
-      <c r="N98" s="40"/>
-      <c r="O98" s="41"/>
-      <c r="P98" s="40"/>
-      <c r="Q98" s="41"/>
-      <c r="R98" s="40"/>
-      <c r="S98" s="41"/>
-      <c r="T98" s="40"/>
-      <c r="U98" s="41"/>
-      <c r="V98" s="40"/>
-      <c r="W98" s="41"/>
-      <c r="X98" s="40"/>
-      <c r="Y98" s="41"/>
-      <c r="Z98" s="40"/>
-      <c r="AA98" s="41"/>
-      <c r="AB98" s="40"/>
-      <c r="AC98" s="41"/>
-      <c r="AD98" s="40"/>
-      <c r="AE98" s="41"/>
-      <c r="AF98" s="40"/>
-      <c r="AG98" s="41"/>
-      <c r="AH98" s="40"/>
-      <c r="AI98" s="41"/>
-      <c r="AJ98" s="40"/>
-      <c r="AK98" s="41"/>
-      <c r="AL98" s="40"/>
-      <c r="AM98" s="41"/>
-      <c r="AN98" s="40"/>
-      <c r="AO98" s="41"/>
-      <c r="AP98" s="40"/>
-      <c r="AQ98" s="40"/>
-      <c r="AR98" s="40"/>
-      <c r="AS98" s="40"/>
-      <c r="AT98" s="40"/>
-      <c r="AU98" s="41"/>
-      <c r="AV98" s="42"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="46"/>
+      <c r="D98" s="45"/>
+      <c r="E98" s="46"/>
+      <c r="F98" s="45"/>
+      <c r="G98" s="46"/>
+      <c r="H98" s="45"/>
+      <c r="I98" s="46"/>
+      <c r="J98" s="45"/>
+      <c r="K98" s="46"/>
+      <c r="L98" s="45"/>
+      <c r="M98" s="46"/>
+      <c r="N98" s="45"/>
+      <c r="O98" s="46"/>
+      <c r="P98" s="45"/>
+      <c r="Q98" s="46"/>
+      <c r="R98" s="45"/>
+      <c r="S98" s="46"/>
+      <c r="T98" s="45"/>
+      <c r="U98" s="46"/>
+      <c r="V98" s="45"/>
+      <c r="W98" s="46"/>
+      <c r="X98" s="45"/>
+      <c r="Y98" s="46"/>
+      <c r="Z98" s="45"/>
+      <c r="AA98" s="46"/>
+      <c r="AB98" s="45"/>
+      <c r="AC98" s="46"/>
+      <c r="AD98" s="45"/>
+      <c r="AE98" s="46"/>
+      <c r="AF98" s="45"/>
+      <c r="AG98" s="46"/>
+      <c r="AH98" s="45"/>
+      <c r="AI98" s="46"/>
+      <c r="AJ98" s="45"/>
+      <c r="AK98" s="46"/>
+      <c r="AL98" s="45"/>
+      <c r="AM98" s="46"/>
+      <c r="AN98" s="45"/>
+      <c r="AO98" s="46"/>
+      <c r="AP98" s="45"/>
+      <c r="AQ98" s="45"/>
+      <c r="AR98" s="45"/>
+      <c r="AS98" s="45"/>
+      <c r="AT98" s="45"/>
+      <c r="AU98" s="46"/>
+      <c r="AV98" s="47"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
-    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -14998,7 +14999,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -15172,7 +15173,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15346,7 +15347,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -15520,7 +15521,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15694,7 +15695,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -15868,7 +15869,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12"/>
       <c r="B105" s="17"/>
       <c r="C105" s="13"/>
@@ -15926,61 +15927,61 @@
       <c r="AW105" s="12"/>
       <c r="AX105" s="12"/>
     </row>
-    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="39" t="s">
+    <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="40"/>
-      <c r="C106" s="41"/>
-      <c r="D106" s="40"/>
-      <c r="E106" s="41"/>
-      <c r="F106" s="40"/>
-      <c r="G106" s="41"/>
-      <c r="H106" s="40"/>
-      <c r="I106" s="41"/>
-      <c r="J106" s="40"/>
-      <c r="K106" s="41"/>
-      <c r="L106" s="40"/>
-      <c r="M106" s="41"/>
-      <c r="N106" s="40"/>
-      <c r="O106" s="41"/>
-      <c r="P106" s="40"/>
-      <c r="Q106" s="41"/>
-      <c r="R106" s="40"/>
-      <c r="S106" s="41"/>
-      <c r="T106" s="40"/>
-      <c r="U106" s="41"/>
-      <c r="V106" s="40"/>
-      <c r="W106" s="41"/>
-      <c r="X106" s="40"/>
-      <c r="Y106" s="41"/>
-      <c r="Z106" s="40"/>
-      <c r="AA106" s="41"/>
-      <c r="AB106" s="40"/>
-      <c r="AC106" s="41"/>
-      <c r="AD106" s="40"/>
-      <c r="AE106" s="41"/>
-      <c r="AF106" s="40"/>
-      <c r="AG106" s="41"/>
-      <c r="AH106" s="40"/>
-      <c r="AI106" s="41"/>
-      <c r="AJ106" s="40"/>
-      <c r="AK106" s="41"/>
-      <c r="AL106" s="40"/>
-      <c r="AM106" s="41"/>
-      <c r="AN106" s="40"/>
-      <c r="AO106" s="41"/>
-      <c r="AP106" s="40"/>
-      <c r="AQ106" s="40"/>
-      <c r="AR106" s="40"/>
-      <c r="AS106" s="40"/>
-      <c r="AT106" s="40"/>
-      <c r="AU106" s="41"/>
-      <c r="AV106" s="42"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="46"/>
+      <c r="D106" s="45"/>
+      <c r="E106" s="46"/>
+      <c r="F106" s="45"/>
+      <c r="G106" s="46"/>
+      <c r="H106" s="45"/>
+      <c r="I106" s="46"/>
+      <c r="J106" s="45"/>
+      <c r="K106" s="46"/>
+      <c r="L106" s="45"/>
+      <c r="M106" s="46"/>
+      <c r="N106" s="45"/>
+      <c r="O106" s="46"/>
+      <c r="P106" s="45"/>
+      <c r="Q106" s="46"/>
+      <c r="R106" s="45"/>
+      <c r="S106" s="46"/>
+      <c r="T106" s="45"/>
+      <c r="U106" s="46"/>
+      <c r="V106" s="45"/>
+      <c r="W106" s="46"/>
+      <c r="X106" s="45"/>
+      <c r="Y106" s="46"/>
+      <c r="Z106" s="45"/>
+      <c r="AA106" s="46"/>
+      <c r="AB106" s="45"/>
+      <c r="AC106" s="46"/>
+      <c r="AD106" s="45"/>
+      <c r="AE106" s="46"/>
+      <c r="AF106" s="45"/>
+      <c r="AG106" s="46"/>
+      <c r="AH106" s="45"/>
+      <c r="AI106" s="46"/>
+      <c r="AJ106" s="45"/>
+      <c r="AK106" s="46"/>
+      <c r="AL106" s="45"/>
+      <c r="AM106" s="46"/>
+      <c r="AN106" s="45"/>
+      <c r="AO106" s="46"/>
+      <c r="AP106" s="45"/>
+      <c r="AQ106" s="45"/>
+      <c r="AR106" s="45"/>
+      <c r="AS106" s="45"/>
+      <c r="AT106" s="45"/>
+      <c r="AU106" s="46"/>
+      <c r="AV106" s="47"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
-    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>1.0625</v>
       </c>
@@ -16154,7 +16155,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>1.0625</v>
       </c>
@@ -16328,7 +16329,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16502,7 +16503,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>1.166666666666667</v>
       </c>
@@ -16676,7 +16677,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12"/>
       <c r="B111" s="17"/>
       <c r="C111" s="13"/>
@@ -16734,7 +16735,7 @@
       <c r="AW111" s="12"/>
       <c r="AX111" s="12"/>
     </row>
-    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12"/>
       <c r="B112" s="17"/>
       <c r="C112" s="13"/>
@@ -16792,115 +16793,115 @@
       <c r="AW112" s="12"/>
       <c r="AX112" s="12"/>
     </row>
-    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="53"/>
-      <c r="C113" s="54"/>
-      <c r="D113" s="53"/>
-      <c r="E113" s="54"/>
-      <c r="F113" s="53"/>
-      <c r="G113" s="54"/>
-      <c r="H113" s="53"/>
-      <c r="I113" s="54"/>
-      <c r="J113" s="53"/>
-      <c r="K113" s="54"/>
-      <c r="L113" s="53"/>
-      <c r="M113" s="54"/>
-      <c r="N113" s="53"/>
-      <c r="O113" s="54"/>
-      <c r="P113" s="53"/>
-      <c r="Q113" s="54"/>
-      <c r="R113" s="53"/>
-      <c r="S113" s="54"/>
-      <c r="T113" s="53"/>
-      <c r="U113" s="54"/>
-      <c r="V113" s="53"/>
-      <c r="W113" s="54"/>
-      <c r="X113" s="53"/>
-      <c r="Y113" s="54"/>
-      <c r="Z113" s="53"/>
-      <c r="AA113" s="54"/>
-      <c r="AB113" s="53"/>
-      <c r="AC113" s="54"/>
-      <c r="AD113" s="53"/>
-      <c r="AE113" s="54"/>
-      <c r="AF113" s="53"/>
-      <c r="AG113" s="54"/>
-      <c r="AH113" s="53"/>
-      <c r="AI113" s="54"/>
-      <c r="AJ113" s="53"/>
-      <c r="AK113" s="54"/>
-      <c r="AL113" s="53"/>
-      <c r="AM113" s="54"/>
-      <c r="AN113" s="53"/>
-      <c r="AO113" s="54"/>
-      <c r="AP113" s="53"/>
-      <c r="AQ113" s="53"/>
-      <c r="AR113" s="53"/>
-      <c r="AS113" s="53"/>
-      <c r="AT113" s="53"/>
-      <c r="AU113" s="54"/>
-      <c r="AV113" s="47"/>
+      <c r="B113" s="49"/>
+      <c r="C113" s="50"/>
+      <c r="D113" s="49"/>
+      <c r="E113" s="50"/>
+      <c r="F113" s="49"/>
+      <c r="G113" s="50"/>
+      <c r="H113" s="49"/>
+      <c r="I113" s="50"/>
+      <c r="J113" s="49"/>
+      <c r="K113" s="50"/>
+      <c r="L113" s="49"/>
+      <c r="M113" s="50"/>
+      <c r="N113" s="49"/>
+      <c r="O113" s="50"/>
+      <c r="P113" s="49"/>
+      <c r="Q113" s="50"/>
+      <c r="R113" s="49"/>
+      <c r="S113" s="50"/>
+      <c r="T113" s="49"/>
+      <c r="U113" s="50"/>
+      <c r="V113" s="49"/>
+      <c r="W113" s="50"/>
+      <c r="X113" s="49"/>
+      <c r="Y113" s="50"/>
+      <c r="Z113" s="49"/>
+      <c r="AA113" s="50"/>
+      <c r="AB113" s="49"/>
+      <c r="AC113" s="50"/>
+      <c r="AD113" s="49"/>
+      <c r="AE113" s="50"/>
+      <c r="AF113" s="49"/>
+      <c r="AG113" s="50"/>
+      <c r="AH113" s="49"/>
+      <c r="AI113" s="50"/>
+      <c r="AJ113" s="49"/>
+      <c r="AK113" s="50"/>
+      <c r="AL113" s="49"/>
+      <c r="AM113" s="50"/>
+      <c r="AN113" s="49"/>
+      <c r="AO113" s="50"/>
+      <c r="AP113" s="49"/>
+      <c r="AQ113" s="49"/>
+      <c r="AR113" s="49"/>
+      <c r="AS113" s="49"/>
+      <c r="AT113" s="49"/>
+      <c r="AU113" s="50"/>
+      <c r="AV113" s="43"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
-    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="39" t="s">
+    <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="40"/>
-      <c r="C114" s="41"/>
-      <c r="D114" s="40"/>
-      <c r="E114" s="41"/>
-      <c r="F114" s="40"/>
-      <c r="G114" s="41"/>
-      <c r="H114" s="40"/>
-      <c r="I114" s="41"/>
-      <c r="J114" s="40"/>
-      <c r="K114" s="41"/>
-      <c r="L114" s="40"/>
-      <c r="M114" s="41"/>
-      <c r="N114" s="40"/>
-      <c r="O114" s="41"/>
-      <c r="P114" s="40"/>
-      <c r="Q114" s="41"/>
-      <c r="R114" s="40"/>
-      <c r="S114" s="41"/>
-      <c r="T114" s="40"/>
-      <c r="U114" s="41"/>
-      <c r="V114" s="40"/>
-      <c r="W114" s="41"/>
-      <c r="X114" s="40"/>
-      <c r="Y114" s="41"/>
-      <c r="Z114" s="40"/>
-      <c r="AA114" s="41"/>
-      <c r="AB114" s="40"/>
-      <c r="AC114" s="41"/>
-      <c r="AD114" s="40"/>
-      <c r="AE114" s="41"/>
-      <c r="AF114" s="40"/>
-      <c r="AG114" s="41"/>
-      <c r="AH114" s="40"/>
-      <c r="AI114" s="41"/>
-      <c r="AJ114" s="40"/>
-      <c r="AK114" s="41"/>
-      <c r="AL114" s="40"/>
-      <c r="AM114" s="41"/>
-      <c r="AN114" s="40"/>
-      <c r="AO114" s="41"/>
-      <c r="AP114" s="40"/>
-      <c r="AQ114" s="40"/>
-      <c r="AR114" s="40"/>
-      <c r="AS114" s="40"/>
-      <c r="AT114" s="40"/>
-      <c r="AU114" s="41"/>
-      <c r="AV114" s="42"/>
+      <c r="B114" s="45"/>
+      <c r="C114" s="46"/>
+      <c r="D114" s="45"/>
+      <c r="E114" s="46"/>
+      <c r="F114" s="45"/>
+      <c r="G114" s="46"/>
+      <c r="H114" s="45"/>
+      <c r="I114" s="46"/>
+      <c r="J114" s="45"/>
+      <c r="K114" s="46"/>
+      <c r="L114" s="45"/>
+      <c r="M114" s="46"/>
+      <c r="N114" s="45"/>
+      <c r="O114" s="46"/>
+      <c r="P114" s="45"/>
+      <c r="Q114" s="46"/>
+      <c r="R114" s="45"/>
+      <c r="S114" s="46"/>
+      <c r="T114" s="45"/>
+      <c r="U114" s="46"/>
+      <c r="V114" s="45"/>
+      <c r="W114" s="46"/>
+      <c r="X114" s="45"/>
+      <c r="Y114" s="46"/>
+      <c r="Z114" s="45"/>
+      <c r="AA114" s="46"/>
+      <c r="AB114" s="45"/>
+      <c r="AC114" s="46"/>
+      <c r="AD114" s="45"/>
+      <c r="AE114" s="46"/>
+      <c r="AF114" s="45"/>
+      <c r="AG114" s="46"/>
+      <c r="AH114" s="45"/>
+      <c r="AI114" s="46"/>
+      <c r="AJ114" s="45"/>
+      <c r="AK114" s="46"/>
+      <c r="AL114" s="45"/>
+      <c r="AM114" s="46"/>
+      <c r="AN114" s="45"/>
+      <c r="AO114" s="46"/>
+      <c r="AP114" s="45"/>
+      <c r="AQ114" s="45"/>
+      <c r="AR114" s="45"/>
+      <c r="AS114" s="45"/>
+      <c r="AT114" s="45"/>
+      <c r="AU114" s="46"/>
+      <c r="AV114" s="47"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
-    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>1.875</v>
       </c>
@@ -17030,7 +17031,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12"/>
       <c r="B116" s="17"/>
       <c r="C116" s="13"/>
@@ -17088,61 +17089,61 @@
       <c r="AW116" s="12"/>
       <c r="AX116" s="12"/>
     </row>
-    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="39" t="s">
+    <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="B117" s="40"/>
-      <c r="C117" s="41"/>
-      <c r="D117" s="40"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="40"/>
-      <c r="G117" s="41"/>
-      <c r="H117" s="40"/>
-      <c r="I117" s="41"/>
-      <c r="J117" s="40"/>
-      <c r="K117" s="41"/>
-      <c r="L117" s="40"/>
-      <c r="M117" s="41"/>
-      <c r="N117" s="40"/>
-      <c r="O117" s="41"/>
-      <c r="P117" s="40"/>
-      <c r="Q117" s="41"/>
-      <c r="R117" s="40"/>
-      <c r="S117" s="41"/>
-      <c r="T117" s="40"/>
-      <c r="U117" s="41"/>
-      <c r="V117" s="40"/>
-      <c r="W117" s="41"/>
-      <c r="X117" s="40"/>
-      <c r="Y117" s="41"/>
-      <c r="Z117" s="40"/>
-      <c r="AA117" s="41"/>
-      <c r="AB117" s="40"/>
-      <c r="AC117" s="41"/>
-      <c r="AD117" s="40"/>
-      <c r="AE117" s="41"/>
-      <c r="AF117" s="40"/>
-      <c r="AG117" s="41"/>
-      <c r="AH117" s="40"/>
-      <c r="AI117" s="41"/>
-      <c r="AJ117" s="40"/>
-      <c r="AK117" s="41"/>
-      <c r="AL117" s="40"/>
-      <c r="AM117" s="41"/>
-      <c r="AN117" s="40"/>
-      <c r="AO117" s="41"/>
-      <c r="AP117" s="40"/>
-      <c r="AQ117" s="40"/>
-      <c r="AR117" s="40"/>
-      <c r="AS117" s="40"/>
-      <c r="AT117" s="40"/>
-      <c r="AU117" s="41"/>
-      <c r="AV117" s="42"/>
+      <c r="B117" s="45"/>
+      <c r="C117" s="46"/>
+      <c r="D117" s="45"/>
+      <c r="E117" s="46"/>
+      <c r="F117" s="45"/>
+      <c r="G117" s="46"/>
+      <c r="H117" s="45"/>
+      <c r="I117" s="46"/>
+      <c r="J117" s="45"/>
+      <c r="K117" s="46"/>
+      <c r="L117" s="45"/>
+      <c r="M117" s="46"/>
+      <c r="N117" s="45"/>
+      <c r="O117" s="46"/>
+      <c r="P117" s="45"/>
+      <c r="Q117" s="46"/>
+      <c r="R117" s="45"/>
+      <c r="S117" s="46"/>
+      <c r="T117" s="45"/>
+      <c r="U117" s="46"/>
+      <c r="V117" s="45"/>
+      <c r="W117" s="46"/>
+      <c r="X117" s="45"/>
+      <c r="Y117" s="46"/>
+      <c r="Z117" s="45"/>
+      <c r="AA117" s="46"/>
+      <c r="AB117" s="45"/>
+      <c r="AC117" s="46"/>
+      <c r="AD117" s="45"/>
+      <c r="AE117" s="46"/>
+      <c r="AF117" s="45"/>
+      <c r="AG117" s="46"/>
+      <c r="AH117" s="45"/>
+      <c r="AI117" s="46"/>
+      <c r="AJ117" s="45"/>
+      <c r="AK117" s="46"/>
+      <c r="AL117" s="45"/>
+      <c r="AM117" s="46"/>
+      <c r="AN117" s="45"/>
+      <c r="AO117" s="46"/>
+      <c r="AP117" s="45"/>
+      <c r="AQ117" s="45"/>
+      <c r="AR117" s="45"/>
+      <c r="AS117" s="45"/>
+      <c r="AT117" s="45"/>
+      <c r="AU117" s="46"/>
+      <c r="AV117" s="47"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
-    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17272,7 +17273,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>1.9375</v>
       </c>
@@ -17402,7 +17403,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12"/>
       <c r="B120" s="17"/>
       <c r="C120" s="13"/>
@@ -17460,61 +17461,61 @@
       <c r="AW120" s="12"/>
       <c r="AX120" s="12"/>
     </row>
-    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="39" t="s">
+    <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B121" s="40"/>
-      <c r="C121" s="41"/>
-      <c r="D121" s="40"/>
-      <c r="E121" s="41"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="41"/>
-      <c r="H121" s="40"/>
-      <c r="I121" s="41"/>
-      <c r="J121" s="40"/>
-      <c r="K121" s="41"/>
-      <c r="L121" s="40"/>
-      <c r="M121" s="41"/>
-      <c r="N121" s="40"/>
-      <c r="O121" s="41"/>
-      <c r="P121" s="40"/>
-      <c r="Q121" s="41"/>
-      <c r="R121" s="40"/>
-      <c r="S121" s="41"/>
-      <c r="T121" s="40"/>
-      <c r="U121" s="41"/>
-      <c r="V121" s="40"/>
-      <c r="W121" s="41"/>
-      <c r="X121" s="40"/>
-      <c r="Y121" s="41"/>
-      <c r="Z121" s="40"/>
-      <c r="AA121" s="41"/>
-      <c r="AB121" s="40"/>
-      <c r="AC121" s="41"/>
-      <c r="AD121" s="40"/>
-      <c r="AE121" s="41"/>
-      <c r="AF121" s="40"/>
-      <c r="AG121" s="41"/>
-      <c r="AH121" s="40"/>
-      <c r="AI121" s="41"/>
-      <c r="AJ121" s="40"/>
-      <c r="AK121" s="41"/>
-      <c r="AL121" s="40"/>
-      <c r="AM121" s="41"/>
-      <c r="AN121" s="40"/>
-      <c r="AO121" s="41"/>
-      <c r="AP121" s="40"/>
-      <c r="AQ121" s="40"/>
-      <c r="AR121" s="40"/>
-      <c r="AS121" s="40"/>
-      <c r="AT121" s="40"/>
-      <c r="AU121" s="41"/>
-      <c r="AV121" s="42"/>
+      <c r="B121" s="45"/>
+      <c r="C121" s="46"/>
+      <c r="D121" s="45"/>
+      <c r="E121" s="46"/>
+      <c r="F121" s="45"/>
+      <c r="G121" s="46"/>
+      <c r="H121" s="45"/>
+      <c r="I121" s="46"/>
+      <c r="J121" s="45"/>
+      <c r="K121" s="46"/>
+      <c r="L121" s="45"/>
+      <c r="M121" s="46"/>
+      <c r="N121" s="45"/>
+      <c r="O121" s="46"/>
+      <c r="P121" s="45"/>
+      <c r="Q121" s="46"/>
+      <c r="R121" s="45"/>
+      <c r="S121" s="46"/>
+      <c r="T121" s="45"/>
+      <c r="U121" s="46"/>
+      <c r="V121" s="45"/>
+      <c r="W121" s="46"/>
+      <c r="X121" s="45"/>
+      <c r="Y121" s="46"/>
+      <c r="Z121" s="45"/>
+      <c r="AA121" s="46"/>
+      <c r="AB121" s="45"/>
+      <c r="AC121" s="46"/>
+      <c r="AD121" s="45"/>
+      <c r="AE121" s="46"/>
+      <c r="AF121" s="45"/>
+      <c r="AG121" s="46"/>
+      <c r="AH121" s="45"/>
+      <c r="AI121" s="46"/>
+      <c r="AJ121" s="45"/>
+      <c r="AK121" s="46"/>
+      <c r="AL121" s="45"/>
+      <c r="AM121" s="46"/>
+      <c r="AN121" s="45"/>
+      <c r="AO121" s="46"/>
+      <c r="AP121" s="45"/>
+      <c r="AQ121" s="45"/>
+      <c r="AR121" s="45"/>
+      <c r="AS121" s="45"/>
+      <c r="AT121" s="45"/>
+      <c r="AU121" s="46"/>
+      <c r="AV121" s="47"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
-    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>1.125</v>
       </c>
@@ -17644,7 +17645,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -17774,7 +17775,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -17904,7 +17905,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12"/>
       <c r="B125" s="17"/>
       <c r="C125" s="13"/>
@@ -17962,61 +17963,61 @@
       <c r="AW125" s="12"/>
       <c r="AX125" s="12"/>
     </row>
-    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="39" t="s">
+    <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="40"/>
-      <c r="C126" s="41"/>
-      <c r="D126" s="40"/>
-      <c r="E126" s="41"/>
-      <c r="F126" s="40"/>
-      <c r="G126" s="41"/>
-      <c r="H126" s="40"/>
-      <c r="I126" s="41"/>
-      <c r="J126" s="40"/>
-      <c r="K126" s="41"/>
-      <c r="L126" s="40"/>
-      <c r="M126" s="41"/>
-      <c r="N126" s="40"/>
-      <c r="O126" s="41"/>
-      <c r="P126" s="40"/>
-      <c r="Q126" s="41"/>
-      <c r="R126" s="40"/>
-      <c r="S126" s="41"/>
-      <c r="T126" s="40"/>
-      <c r="U126" s="41"/>
-      <c r="V126" s="40"/>
-      <c r="W126" s="41"/>
-      <c r="X126" s="40"/>
-      <c r="Y126" s="41"/>
-      <c r="Z126" s="40"/>
-      <c r="AA126" s="41"/>
-      <c r="AB126" s="40"/>
-      <c r="AC126" s="41"/>
-      <c r="AD126" s="40"/>
-      <c r="AE126" s="41"/>
-      <c r="AF126" s="40"/>
-      <c r="AG126" s="41"/>
-      <c r="AH126" s="40"/>
-      <c r="AI126" s="41"/>
-      <c r="AJ126" s="40"/>
-      <c r="AK126" s="41"/>
-      <c r="AL126" s="40"/>
-      <c r="AM126" s="41"/>
-      <c r="AN126" s="40"/>
-      <c r="AO126" s="41"/>
-      <c r="AP126" s="40"/>
-      <c r="AQ126" s="40"/>
-      <c r="AR126" s="40"/>
-      <c r="AS126" s="40"/>
-      <c r="AT126" s="40"/>
-      <c r="AU126" s="41"/>
-      <c r="AV126" s="42"/>
+      <c r="B126" s="45"/>
+      <c r="C126" s="46"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="46"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="46"/>
+      <c r="H126" s="45"/>
+      <c r="I126" s="46"/>
+      <c r="J126" s="45"/>
+      <c r="K126" s="46"/>
+      <c r="L126" s="45"/>
+      <c r="M126" s="46"/>
+      <c r="N126" s="45"/>
+      <c r="O126" s="46"/>
+      <c r="P126" s="45"/>
+      <c r="Q126" s="46"/>
+      <c r="R126" s="45"/>
+      <c r="S126" s="46"/>
+      <c r="T126" s="45"/>
+      <c r="U126" s="46"/>
+      <c r="V126" s="45"/>
+      <c r="W126" s="46"/>
+      <c r="X126" s="45"/>
+      <c r="Y126" s="46"/>
+      <c r="Z126" s="45"/>
+      <c r="AA126" s="46"/>
+      <c r="AB126" s="45"/>
+      <c r="AC126" s="46"/>
+      <c r="AD126" s="45"/>
+      <c r="AE126" s="46"/>
+      <c r="AF126" s="45"/>
+      <c r="AG126" s="46"/>
+      <c r="AH126" s="45"/>
+      <c r="AI126" s="46"/>
+      <c r="AJ126" s="45"/>
+      <c r="AK126" s="46"/>
+      <c r="AL126" s="45"/>
+      <c r="AM126" s="46"/>
+      <c r="AN126" s="45"/>
+      <c r="AO126" s="46"/>
+      <c r="AP126" s="45"/>
+      <c r="AQ126" s="45"/>
+      <c r="AR126" s="45"/>
+      <c r="AS126" s="45"/>
+      <c r="AT126" s="45"/>
+      <c r="AU126" s="46"/>
+      <c r="AV126" s="47"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
-    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>1.125</v>
       </c>
@@ -18146,7 +18147,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>1.75</v>
       </c>
@@ -18276,7 +18277,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -18406,7 +18407,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12"/>
       <c r="B130" s="17"/>
       <c r="C130" s="13"/>
@@ -18464,61 +18465,61 @@
       <c r="AW130" s="12"/>
       <c r="AX130" s="12"/>
     </row>
-    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="39" t="s">
+    <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="44" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="40"/>
-      <c r="C131" s="41"/>
-      <c r="D131" s="40"/>
-      <c r="E131" s="41"/>
-      <c r="F131" s="40"/>
-      <c r="G131" s="41"/>
-      <c r="H131" s="40"/>
-      <c r="I131" s="41"/>
-      <c r="J131" s="40"/>
-      <c r="K131" s="41"/>
-      <c r="L131" s="40"/>
-      <c r="M131" s="41"/>
-      <c r="N131" s="40"/>
-      <c r="O131" s="41"/>
-      <c r="P131" s="40"/>
-      <c r="Q131" s="41"/>
-      <c r="R131" s="40"/>
-      <c r="S131" s="41"/>
-      <c r="T131" s="40"/>
-      <c r="U131" s="41"/>
-      <c r="V131" s="40"/>
-      <c r="W131" s="41"/>
-      <c r="X131" s="40"/>
-      <c r="Y131" s="41"/>
-      <c r="Z131" s="40"/>
-      <c r="AA131" s="41"/>
-      <c r="AB131" s="40"/>
-      <c r="AC131" s="41"/>
-      <c r="AD131" s="40"/>
-      <c r="AE131" s="41"/>
-      <c r="AF131" s="40"/>
-      <c r="AG131" s="41"/>
-      <c r="AH131" s="40"/>
-      <c r="AI131" s="41"/>
-      <c r="AJ131" s="40"/>
-      <c r="AK131" s="41"/>
-      <c r="AL131" s="40"/>
-      <c r="AM131" s="41"/>
-      <c r="AN131" s="40"/>
-      <c r="AO131" s="41"/>
-      <c r="AP131" s="40"/>
-      <c r="AQ131" s="40"/>
-      <c r="AR131" s="40"/>
-      <c r="AS131" s="40"/>
-      <c r="AT131" s="40"/>
-      <c r="AU131" s="41"/>
-      <c r="AV131" s="42"/>
+      <c r="B131" s="45"/>
+      <c r="C131" s="46"/>
+      <c r="D131" s="45"/>
+      <c r="E131" s="46"/>
+      <c r="F131" s="45"/>
+      <c r="G131" s="46"/>
+      <c r="H131" s="45"/>
+      <c r="I131" s="46"/>
+      <c r="J131" s="45"/>
+      <c r="K131" s="46"/>
+      <c r="L131" s="45"/>
+      <c r="M131" s="46"/>
+      <c r="N131" s="45"/>
+      <c r="O131" s="46"/>
+      <c r="P131" s="45"/>
+      <c r="Q131" s="46"/>
+      <c r="R131" s="45"/>
+      <c r="S131" s="46"/>
+      <c r="T131" s="45"/>
+      <c r="U131" s="46"/>
+      <c r="V131" s="45"/>
+      <c r="W131" s="46"/>
+      <c r="X131" s="45"/>
+      <c r="Y131" s="46"/>
+      <c r="Z131" s="45"/>
+      <c r="AA131" s="46"/>
+      <c r="AB131" s="45"/>
+      <c r="AC131" s="46"/>
+      <c r="AD131" s="45"/>
+      <c r="AE131" s="46"/>
+      <c r="AF131" s="45"/>
+      <c r="AG131" s="46"/>
+      <c r="AH131" s="45"/>
+      <c r="AI131" s="46"/>
+      <c r="AJ131" s="45"/>
+      <c r="AK131" s="46"/>
+      <c r="AL131" s="45"/>
+      <c r="AM131" s="46"/>
+      <c r="AN131" s="45"/>
+      <c r="AO131" s="46"/>
+      <c r="AP131" s="45"/>
+      <c r="AQ131" s="45"/>
+      <c r="AR131" s="45"/>
+      <c r="AS131" s="45"/>
+      <c r="AT131" s="45"/>
+      <c r="AU131" s="46"/>
+      <c r="AV131" s="47"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
-    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -18648,7 +18649,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>1.875</v>
       </c>
@@ -18778,7 +18779,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12"/>
       <c r="B134" s="17"/>
       <c r="C134" s="13"/>
@@ -18836,61 +18837,61 @@
       <c r="AW134" s="12"/>
       <c r="AX134" s="12"/>
     </row>
-    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="39" t="s">
+    <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="B135" s="40"/>
-      <c r="C135" s="41"/>
-      <c r="D135" s="40"/>
-      <c r="E135" s="41"/>
-      <c r="F135" s="40"/>
-      <c r="G135" s="41"/>
-      <c r="H135" s="40"/>
-      <c r="I135" s="41"/>
-      <c r="J135" s="40"/>
-      <c r="K135" s="41"/>
-      <c r="L135" s="40"/>
-      <c r="M135" s="41"/>
-      <c r="N135" s="40"/>
-      <c r="O135" s="41"/>
-      <c r="P135" s="40"/>
-      <c r="Q135" s="41"/>
-      <c r="R135" s="40"/>
-      <c r="S135" s="41"/>
-      <c r="T135" s="40"/>
-      <c r="U135" s="41"/>
-      <c r="V135" s="40"/>
-      <c r="W135" s="41"/>
-      <c r="X135" s="40"/>
-      <c r="Y135" s="41"/>
-      <c r="Z135" s="40"/>
-      <c r="AA135" s="41"/>
-      <c r="AB135" s="40"/>
-      <c r="AC135" s="41"/>
-      <c r="AD135" s="40"/>
-      <c r="AE135" s="41"/>
-      <c r="AF135" s="40"/>
-      <c r="AG135" s="41"/>
-      <c r="AH135" s="40"/>
-      <c r="AI135" s="41"/>
-      <c r="AJ135" s="40"/>
-      <c r="AK135" s="41"/>
-      <c r="AL135" s="40"/>
-      <c r="AM135" s="41"/>
-      <c r="AN135" s="40"/>
-      <c r="AO135" s="41"/>
-      <c r="AP135" s="40"/>
-      <c r="AQ135" s="40"/>
-      <c r="AR135" s="40"/>
-      <c r="AS135" s="40"/>
-      <c r="AT135" s="40"/>
-      <c r="AU135" s="41"/>
-      <c r="AV135" s="42"/>
+      <c r="B135" s="45"/>
+      <c r="C135" s="46"/>
+      <c r="D135" s="45"/>
+      <c r="E135" s="46"/>
+      <c r="F135" s="45"/>
+      <c r="G135" s="46"/>
+      <c r="H135" s="45"/>
+      <c r="I135" s="46"/>
+      <c r="J135" s="45"/>
+      <c r="K135" s="46"/>
+      <c r="L135" s="45"/>
+      <c r="M135" s="46"/>
+      <c r="N135" s="45"/>
+      <c r="O135" s="46"/>
+      <c r="P135" s="45"/>
+      <c r="Q135" s="46"/>
+      <c r="R135" s="45"/>
+      <c r="S135" s="46"/>
+      <c r="T135" s="45"/>
+      <c r="U135" s="46"/>
+      <c r="V135" s="45"/>
+      <c r="W135" s="46"/>
+      <c r="X135" s="45"/>
+      <c r="Y135" s="46"/>
+      <c r="Z135" s="45"/>
+      <c r="AA135" s="46"/>
+      <c r="AB135" s="45"/>
+      <c r="AC135" s="46"/>
+      <c r="AD135" s="45"/>
+      <c r="AE135" s="46"/>
+      <c r="AF135" s="45"/>
+      <c r="AG135" s="46"/>
+      <c r="AH135" s="45"/>
+      <c r="AI135" s="46"/>
+      <c r="AJ135" s="45"/>
+      <c r="AK135" s="46"/>
+      <c r="AL135" s="45"/>
+      <c r="AM135" s="46"/>
+      <c r="AN135" s="45"/>
+      <c r="AO135" s="46"/>
+      <c r="AP135" s="45"/>
+      <c r="AQ135" s="45"/>
+      <c r="AR135" s="45"/>
+      <c r="AS135" s="45"/>
+      <c r="AT135" s="45"/>
+      <c r="AU135" s="46"/>
+      <c r="AV135" s="47"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
-    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>1.041666666666667</v>
       </c>
@@ -19020,7 +19021,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>1.208333333333333</v>
       </c>
@@ -19150,7 +19151,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>1.833333333333333</v>
       </c>
@@ -19280,7 +19281,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12"/>
       <c r="B139" s="17"/>
       <c r="C139" s="13"/>
@@ -19338,61 +19339,61 @@
       <c r="AW139" s="12"/>
       <c r="AX139" s="12"/>
     </row>
-    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="39" t="s">
+    <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B140" s="40"/>
-      <c r="C140" s="41"/>
-      <c r="D140" s="40"/>
-      <c r="E140" s="41"/>
-      <c r="F140" s="40"/>
-      <c r="G140" s="41"/>
-      <c r="H140" s="40"/>
-      <c r="I140" s="41"/>
-      <c r="J140" s="40"/>
-      <c r="K140" s="41"/>
-      <c r="L140" s="40"/>
-      <c r="M140" s="41"/>
-      <c r="N140" s="40"/>
-      <c r="O140" s="41"/>
-      <c r="P140" s="40"/>
-      <c r="Q140" s="41"/>
-      <c r="R140" s="40"/>
-      <c r="S140" s="41"/>
-      <c r="T140" s="40"/>
-      <c r="U140" s="41"/>
-      <c r="V140" s="40"/>
-      <c r="W140" s="41"/>
-      <c r="X140" s="40"/>
-      <c r="Y140" s="41"/>
-      <c r="Z140" s="40"/>
-      <c r="AA140" s="41"/>
-      <c r="AB140" s="40"/>
-      <c r="AC140" s="41"/>
-      <c r="AD140" s="40"/>
-      <c r="AE140" s="41"/>
-      <c r="AF140" s="40"/>
-      <c r="AG140" s="41"/>
-      <c r="AH140" s="40"/>
-      <c r="AI140" s="41"/>
-      <c r="AJ140" s="40"/>
-      <c r="AK140" s="41"/>
-      <c r="AL140" s="40"/>
-      <c r="AM140" s="41"/>
-      <c r="AN140" s="40"/>
-      <c r="AO140" s="41"/>
-      <c r="AP140" s="40"/>
-      <c r="AQ140" s="40"/>
-      <c r="AR140" s="40"/>
-      <c r="AS140" s="40"/>
-      <c r="AT140" s="40"/>
-      <c r="AU140" s="41"/>
-      <c r="AV140" s="42"/>
+      <c r="B140" s="45"/>
+      <c r="C140" s="46"/>
+      <c r="D140" s="45"/>
+      <c r="E140" s="46"/>
+      <c r="F140" s="45"/>
+      <c r="G140" s="46"/>
+      <c r="H140" s="45"/>
+      <c r="I140" s="46"/>
+      <c r="J140" s="45"/>
+      <c r="K140" s="46"/>
+      <c r="L140" s="45"/>
+      <c r="M140" s="46"/>
+      <c r="N140" s="45"/>
+      <c r="O140" s="46"/>
+      <c r="P140" s="45"/>
+      <c r="Q140" s="46"/>
+      <c r="R140" s="45"/>
+      <c r="S140" s="46"/>
+      <c r="T140" s="45"/>
+      <c r="U140" s="46"/>
+      <c r="V140" s="45"/>
+      <c r="W140" s="46"/>
+      <c r="X140" s="45"/>
+      <c r="Y140" s="46"/>
+      <c r="Z140" s="45"/>
+      <c r="AA140" s="46"/>
+      <c r="AB140" s="45"/>
+      <c r="AC140" s="46"/>
+      <c r="AD140" s="45"/>
+      <c r="AE140" s="46"/>
+      <c r="AF140" s="45"/>
+      <c r="AG140" s="46"/>
+      <c r="AH140" s="45"/>
+      <c r="AI140" s="46"/>
+      <c r="AJ140" s="45"/>
+      <c r="AK140" s="46"/>
+      <c r="AL140" s="45"/>
+      <c r="AM140" s="46"/>
+      <c r="AN140" s="45"/>
+      <c r="AO140" s="46"/>
+      <c r="AP140" s="45"/>
+      <c r="AQ140" s="45"/>
+      <c r="AR140" s="45"/>
+      <c r="AS140" s="45"/>
+      <c r="AT140" s="45"/>
+      <c r="AU140" s="46"/>
+      <c r="AV140" s="47"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
-    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>1</v>
       </c>
@@ -19522,7 +19523,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>1.145833333333333</v>
       </c>
@@ -19652,7 +19653,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="12"/>
       <c r="B143" s="17"/>
       <c r="C143" s="13"/>
@@ -19710,7 +19711,7 @@
       <c r="AW143" s="12"/>
       <c r="AX143" s="12"/>
     </row>
-    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="12"/>
       <c r="B144" s="17"/>
       <c r="C144" s="13"/>
@@ -19768,115 +19769,115 @@
       <c r="AW144" s="12"/>
       <c r="AX144" s="12"/>
     </row>
-    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="53"/>
-      <c r="C145" s="54"/>
-      <c r="D145" s="53"/>
-      <c r="E145" s="54"/>
-      <c r="F145" s="53"/>
-      <c r="G145" s="54"/>
-      <c r="H145" s="53"/>
-      <c r="I145" s="54"/>
-      <c r="J145" s="53"/>
-      <c r="K145" s="54"/>
-      <c r="L145" s="53"/>
-      <c r="M145" s="54"/>
-      <c r="N145" s="53"/>
-      <c r="O145" s="54"/>
-      <c r="P145" s="53"/>
-      <c r="Q145" s="54"/>
-      <c r="R145" s="53"/>
-      <c r="S145" s="54"/>
-      <c r="T145" s="53"/>
-      <c r="U145" s="54"/>
-      <c r="V145" s="53"/>
-      <c r="W145" s="54"/>
-      <c r="X145" s="53"/>
-      <c r="Y145" s="54"/>
-      <c r="Z145" s="53"/>
-      <c r="AA145" s="54"/>
-      <c r="AB145" s="53"/>
-      <c r="AC145" s="54"/>
-      <c r="AD145" s="53"/>
-      <c r="AE145" s="54"/>
-      <c r="AF145" s="53"/>
-      <c r="AG145" s="54"/>
-      <c r="AH145" s="53"/>
-      <c r="AI145" s="54"/>
-      <c r="AJ145" s="53"/>
-      <c r="AK145" s="54"/>
-      <c r="AL145" s="53"/>
-      <c r="AM145" s="54"/>
-      <c r="AN145" s="53"/>
-      <c r="AO145" s="54"/>
-      <c r="AP145" s="53"/>
-      <c r="AQ145" s="53"/>
-      <c r="AR145" s="53"/>
-      <c r="AS145" s="53"/>
-      <c r="AT145" s="53"/>
-      <c r="AU145" s="54"/>
-      <c r="AV145" s="47"/>
+      <c r="B145" s="49"/>
+      <c r="C145" s="50"/>
+      <c r="D145" s="49"/>
+      <c r="E145" s="50"/>
+      <c r="F145" s="49"/>
+      <c r="G145" s="50"/>
+      <c r="H145" s="49"/>
+      <c r="I145" s="50"/>
+      <c r="J145" s="49"/>
+      <c r="K145" s="50"/>
+      <c r="L145" s="49"/>
+      <c r="M145" s="50"/>
+      <c r="N145" s="49"/>
+      <c r="O145" s="50"/>
+      <c r="P145" s="49"/>
+      <c r="Q145" s="50"/>
+      <c r="R145" s="49"/>
+      <c r="S145" s="50"/>
+      <c r="T145" s="49"/>
+      <c r="U145" s="50"/>
+      <c r="V145" s="49"/>
+      <c r="W145" s="50"/>
+      <c r="X145" s="49"/>
+      <c r="Y145" s="50"/>
+      <c r="Z145" s="49"/>
+      <c r="AA145" s="50"/>
+      <c r="AB145" s="49"/>
+      <c r="AC145" s="50"/>
+      <c r="AD145" s="49"/>
+      <c r="AE145" s="50"/>
+      <c r="AF145" s="49"/>
+      <c r="AG145" s="50"/>
+      <c r="AH145" s="49"/>
+      <c r="AI145" s="50"/>
+      <c r="AJ145" s="49"/>
+      <c r="AK145" s="50"/>
+      <c r="AL145" s="49"/>
+      <c r="AM145" s="50"/>
+      <c r="AN145" s="49"/>
+      <c r="AO145" s="50"/>
+      <c r="AP145" s="49"/>
+      <c r="AQ145" s="49"/>
+      <c r="AR145" s="49"/>
+      <c r="AS145" s="49"/>
+      <c r="AT145" s="49"/>
+      <c r="AU145" s="50"/>
+      <c r="AV145" s="43"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
-    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="39" t="s">
+    <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="40"/>
-      <c r="C146" s="41"/>
-      <c r="D146" s="40"/>
-      <c r="E146" s="41"/>
-      <c r="F146" s="40"/>
-      <c r="G146" s="41"/>
-      <c r="H146" s="40"/>
-      <c r="I146" s="41"/>
-      <c r="J146" s="40"/>
-      <c r="K146" s="41"/>
-      <c r="L146" s="40"/>
-      <c r="M146" s="41"/>
-      <c r="N146" s="40"/>
-      <c r="O146" s="41"/>
-      <c r="P146" s="40"/>
-      <c r="Q146" s="41"/>
-      <c r="R146" s="40"/>
-      <c r="S146" s="41"/>
-      <c r="T146" s="40"/>
-      <c r="U146" s="41"/>
-      <c r="V146" s="40"/>
-      <c r="W146" s="41"/>
-      <c r="X146" s="40"/>
-      <c r="Y146" s="41"/>
-      <c r="Z146" s="40"/>
-      <c r="AA146" s="41"/>
-      <c r="AB146" s="40"/>
-      <c r="AC146" s="41"/>
-      <c r="AD146" s="40"/>
-      <c r="AE146" s="41"/>
-      <c r="AF146" s="40"/>
-      <c r="AG146" s="41"/>
-      <c r="AH146" s="40"/>
-      <c r="AI146" s="41"/>
-      <c r="AJ146" s="40"/>
-      <c r="AK146" s="41"/>
-      <c r="AL146" s="40"/>
-      <c r="AM146" s="41"/>
-      <c r="AN146" s="40"/>
-      <c r="AO146" s="41"/>
-      <c r="AP146" s="40"/>
-      <c r="AQ146" s="40"/>
-      <c r="AR146" s="40"/>
-      <c r="AS146" s="40"/>
-      <c r="AT146" s="40"/>
-      <c r="AU146" s="41"/>
-      <c r="AV146" s="42"/>
+      <c r="B146" s="45"/>
+      <c r="C146" s="46"/>
+      <c r="D146" s="45"/>
+      <c r="E146" s="46"/>
+      <c r="F146" s="45"/>
+      <c r="G146" s="46"/>
+      <c r="H146" s="45"/>
+      <c r="I146" s="46"/>
+      <c r="J146" s="45"/>
+      <c r="K146" s="46"/>
+      <c r="L146" s="45"/>
+      <c r="M146" s="46"/>
+      <c r="N146" s="45"/>
+      <c r="O146" s="46"/>
+      <c r="P146" s="45"/>
+      <c r="Q146" s="46"/>
+      <c r="R146" s="45"/>
+      <c r="S146" s="46"/>
+      <c r="T146" s="45"/>
+      <c r="U146" s="46"/>
+      <c r="V146" s="45"/>
+      <c r="W146" s="46"/>
+      <c r="X146" s="45"/>
+      <c r="Y146" s="46"/>
+      <c r="Z146" s="45"/>
+      <c r="AA146" s="46"/>
+      <c r="AB146" s="45"/>
+      <c r="AC146" s="46"/>
+      <c r="AD146" s="45"/>
+      <c r="AE146" s="46"/>
+      <c r="AF146" s="45"/>
+      <c r="AG146" s="46"/>
+      <c r="AH146" s="45"/>
+      <c r="AI146" s="46"/>
+      <c r="AJ146" s="45"/>
+      <c r="AK146" s="46"/>
+      <c r="AL146" s="45"/>
+      <c r="AM146" s="46"/>
+      <c r="AN146" s="45"/>
+      <c r="AO146" s="46"/>
+      <c r="AP146" s="45"/>
+      <c r="AQ146" s="45"/>
+      <c r="AR146" s="45"/>
+      <c r="AS146" s="45"/>
+      <c r="AT146" s="45"/>
+      <c r="AU146" s="46"/>
+      <c r="AV146" s="47"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
-    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>1.791666666666667</v>
       </c>
@@ -20006,7 +20007,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -20136,7 +20137,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12"/>
       <c r="B149" s="17"/>
       <c r="C149" s="13"/>
@@ -20194,61 +20195,61 @@
       <c r="AW149" s="12"/>
       <c r="AX149" s="12"/>
     </row>
-    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="39" t="s">
+    <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="B150" s="40"/>
-      <c r="C150" s="41"/>
-      <c r="D150" s="40"/>
-      <c r="E150" s="41"/>
-      <c r="F150" s="40"/>
-      <c r="G150" s="41"/>
-      <c r="H150" s="40"/>
-      <c r="I150" s="41"/>
-      <c r="J150" s="40"/>
-      <c r="K150" s="41"/>
-      <c r="L150" s="40"/>
-      <c r="M150" s="41"/>
-      <c r="N150" s="40"/>
-      <c r="O150" s="41"/>
-      <c r="P150" s="40"/>
-      <c r="Q150" s="41"/>
-      <c r="R150" s="40"/>
-      <c r="S150" s="41"/>
-      <c r="T150" s="40"/>
-      <c r="U150" s="41"/>
-      <c r="V150" s="40"/>
-      <c r="W150" s="41"/>
-      <c r="X150" s="40"/>
-      <c r="Y150" s="41"/>
-      <c r="Z150" s="40"/>
-      <c r="AA150" s="41"/>
-      <c r="AB150" s="40"/>
-      <c r="AC150" s="41"/>
-      <c r="AD150" s="40"/>
-      <c r="AE150" s="41"/>
-      <c r="AF150" s="40"/>
-      <c r="AG150" s="41"/>
-      <c r="AH150" s="40"/>
-      <c r="AI150" s="41"/>
-      <c r="AJ150" s="40"/>
-      <c r="AK150" s="41"/>
-      <c r="AL150" s="40"/>
-      <c r="AM150" s="41"/>
-      <c r="AN150" s="40"/>
-      <c r="AO150" s="41"/>
-      <c r="AP150" s="40"/>
-      <c r="AQ150" s="40"/>
-      <c r="AR150" s="40"/>
-      <c r="AS150" s="40"/>
-      <c r="AT150" s="40"/>
-      <c r="AU150" s="41"/>
-      <c r="AV150" s="42"/>
+      <c r="B150" s="45"/>
+      <c r="C150" s="46"/>
+      <c r="D150" s="45"/>
+      <c r="E150" s="46"/>
+      <c r="F150" s="45"/>
+      <c r="G150" s="46"/>
+      <c r="H150" s="45"/>
+      <c r="I150" s="46"/>
+      <c r="J150" s="45"/>
+      <c r="K150" s="46"/>
+      <c r="L150" s="45"/>
+      <c r="M150" s="46"/>
+      <c r="N150" s="45"/>
+      <c r="O150" s="46"/>
+      <c r="P150" s="45"/>
+      <c r="Q150" s="46"/>
+      <c r="R150" s="45"/>
+      <c r="S150" s="46"/>
+      <c r="T150" s="45"/>
+      <c r="U150" s="46"/>
+      <c r="V150" s="45"/>
+      <c r="W150" s="46"/>
+      <c r="X150" s="45"/>
+      <c r="Y150" s="46"/>
+      <c r="Z150" s="45"/>
+      <c r="AA150" s="46"/>
+      <c r="AB150" s="45"/>
+      <c r="AC150" s="46"/>
+      <c r="AD150" s="45"/>
+      <c r="AE150" s="46"/>
+      <c r="AF150" s="45"/>
+      <c r="AG150" s="46"/>
+      <c r="AH150" s="45"/>
+      <c r="AI150" s="46"/>
+      <c r="AJ150" s="45"/>
+      <c r="AK150" s="46"/>
+      <c r="AL150" s="45"/>
+      <c r="AM150" s="46"/>
+      <c r="AN150" s="45"/>
+      <c r="AO150" s="46"/>
+      <c r="AP150" s="45"/>
+      <c r="AQ150" s="45"/>
+      <c r="AR150" s="45"/>
+      <c r="AS150" s="45"/>
+      <c r="AT150" s="45"/>
+      <c r="AU150" s="46"/>
+      <c r="AV150" s="47"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
-    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -20378,7 +20379,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12"/>
       <c r="B152" s="17"/>
       <c r="C152" s="13"/>
@@ -20436,61 +20437,61 @@
       <c r="AW152" s="12"/>
       <c r="AX152" s="12"/>
     </row>
-    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="39" t="s">
+    <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="B153" s="40"/>
-      <c r="C153" s="41"/>
-      <c r="D153" s="40"/>
-      <c r="E153" s="41"/>
-      <c r="F153" s="40"/>
-      <c r="G153" s="41"/>
-      <c r="H153" s="40"/>
-      <c r="I153" s="41"/>
-      <c r="J153" s="40"/>
-      <c r="K153" s="41"/>
-      <c r="L153" s="40"/>
-      <c r="M153" s="41"/>
-      <c r="N153" s="40"/>
-      <c r="O153" s="41"/>
-      <c r="P153" s="40"/>
-      <c r="Q153" s="41"/>
-      <c r="R153" s="40"/>
-      <c r="S153" s="41"/>
-      <c r="T153" s="40"/>
-      <c r="U153" s="41"/>
-      <c r="V153" s="40"/>
-      <c r="W153" s="41"/>
-      <c r="X153" s="40"/>
-      <c r="Y153" s="41"/>
-      <c r="Z153" s="40"/>
-      <c r="AA153" s="41"/>
-      <c r="AB153" s="40"/>
-      <c r="AC153" s="41"/>
-      <c r="AD153" s="40"/>
-      <c r="AE153" s="41"/>
-      <c r="AF153" s="40"/>
-      <c r="AG153" s="41"/>
-      <c r="AH153" s="40"/>
-      <c r="AI153" s="41"/>
-      <c r="AJ153" s="40"/>
-      <c r="AK153" s="41"/>
-      <c r="AL153" s="40"/>
-      <c r="AM153" s="41"/>
-      <c r="AN153" s="40"/>
-      <c r="AO153" s="41"/>
-      <c r="AP153" s="40"/>
-      <c r="AQ153" s="40"/>
-      <c r="AR153" s="40"/>
-      <c r="AS153" s="40"/>
-      <c r="AT153" s="40"/>
-      <c r="AU153" s="41"/>
-      <c r="AV153" s="42"/>
+      <c r="B153" s="45"/>
+      <c r="C153" s="46"/>
+      <c r="D153" s="45"/>
+      <c r="E153" s="46"/>
+      <c r="F153" s="45"/>
+      <c r="G153" s="46"/>
+      <c r="H153" s="45"/>
+      <c r="I153" s="46"/>
+      <c r="J153" s="45"/>
+      <c r="K153" s="46"/>
+      <c r="L153" s="45"/>
+      <c r="M153" s="46"/>
+      <c r="N153" s="45"/>
+      <c r="O153" s="46"/>
+      <c r="P153" s="45"/>
+      <c r="Q153" s="46"/>
+      <c r="R153" s="45"/>
+      <c r="S153" s="46"/>
+      <c r="T153" s="45"/>
+      <c r="U153" s="46"/>
+      <c r="V153" s="45"/>
+      <c r="W153" s="46"/>
+      <c r="X153" s="45"/>
+      <c r="Y153" s="46"/>
+      <c r="Z153" s="45"/>
+      <c r="AA153" s="46"/>
+      <c r="AB153" s="45"/>
+      <c r="AC153" s="46"/>
+      <c r="AD153" s="45"/>
+      <c r="AE153" s="46"/>
+      <c r="AF153" s="45"/>
+      <c r="AG153" s="46"/>
+      <c r="AH153" s="45"/>
+      <c r="AI153" s="46"/>
+      <c r="AJ153" s="45"/>
+      <c r="AK153" s="46"/>
+      <c r="AL153" s="45"/>
+      <c r="AM153" s="46"/>
+      <c r="AN153" s="45"/>
+      <c r="AO153" s="46"/>
+      <c r="AP153" s="45"/>
+      <c r="AQ153" s="45"/>
+      <c r="AR153" s="45"/>
+      <c r="AS153" s="45"/>
+      <c r="AT153" s="45"/>
+      <c r="AU153" s="46"/>
+      <c r="AV153" s="47"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
-    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20620,7 +20621,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>1.875</v>
       </c>
@@ -20750,7 +20751,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12"/>
       <c r="B156" s="17"/>
       <c r="C156" s="13"/>
@@ -20808,61 +20809,61 @@
       <c r="AW156" s="12"/>
       <c r="AX156" s="12"/>
     </row>
-    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="39" t="s">
+    <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="B157" s="40"/>
-      <c r="C157" s="41"/>
-      <c r="D157" s="40"/>
-      <c r="E157" s="41"/>
-      <c r="F157" s="40"/>
-      <c r="G157" s="41"/>
-      <c r="H157" s="40"/>
-      <c r="I157" s="41"/>
-      <c r="J157" s="40"/>
-      <c r="K157" s="41"/>
-      <c r="L157" s="40"/>
-      <c r="M157" s="41"/>
-      <c r="N157" s="40"/>
-      <c r="O157" s="41"/>
-      <c r="P157" s="40"/>
-      <c r="Q157" s="41"/>
-      <c r="R157" s="40"/>
-      <c r="S157" s="41"/>
-      <c r="T157" s="40"/>
-      <c r="U157" s="41"/>
-      <c r="V157" s="40"/>
-      <c r="W157" s="41"/>
-      <c r="X157" s="40"/>
-      <c r="Y157" s="41"/>
-      <c r="Z157" s="40"/>
-      <c r="AA157" s="41"/>
-      <c r="AB157" s="40"/>
-      <c r="AC157" s="41"/>
-      <c r="AD157" s="40"/>
-      <c r="AE157" s="41"/>
-      <c r="AF157" s="40"/>
-      <c r="AG157" s="41"/>
-      <c r="AH157" s="40"/>
-      <c r="AI157" s="41"/>
-      <c r="AJ157" s="40"/>
-      <c r="AK157" s="41"/>
-      <c r="AL157" s="40"/>
-      <c r="AM157" s="41"/>
-      <c r="AN157" s="40"/>
-      <c r="AO157" s="41"/>
-      <c r="AP157" s="40"/>
-      <c r="AQ157" s="40"/>
-      <c r="AR157" s="40"/>
-      <c r="AS157" s="40"/>
-      <c r="AT157" s="40"/>
-      <c r="AU157" s="41"/>
-      <c r="AV157" s="42"/>
+      <c r="B157" s="45"/>
+      <c r="C157" s="46"/>
+      <c r="D157" s="45"/>
+      <c r="E157" s="46"/>
+      <c r="F157" s="45"/>
+      <c r="G157" s="46"/>
+      <c r="H157" s="45"/>
+      <c r="I157" s="46"/>
+      <c r="J157" s="45"/>
+      <c r="K157" s="46"/>
+      <c r="L157" s="45"/>
+      <c r="M157" s="46"/>
+      <c r="N157" s="45"/>
+      <c r="O157" s="46"/>
+      <c r="P157" s="45"/>
+      <c r="Q157" s="46"/>
+      <c r="R157" s="45"/>
+      <c r="S157" s="46"/>
+      <c r="T157" s="45"/>
+      <c r="U157" s="46"/>
+      <c r="V157" s="45"/>
+      <c r="W157" s="46"/>
+      <c r="X157" s="45"/>
+      <c r="Y157" s="46"/>
+      <c r="Z157" s="45"/>
+      <c r="AA157" s="46"/>
+      <c r="AB157" s="45"/>
+      <c r="AC157" s="46"/>
+      <c r="AD157" s="45"/>
+      <c r="AE157" s="46"/>
+      <c r="AF157" s="45"/>
+      <c r="AG157" s="46"/>
+      <c r="AH157" s="45"/>
+      <c r="AI157" s="46"/>
+      <c r="AJ157" s="45"/>
+      <c r="AK157" s="46"/>
+      <c r="AL157" s="45"/>
+      <c r="AM157" s="46"/>
+      <c r="AN157" s="45"/>
+      <c r="AO157" s="46"/>
+      <c r="AP157" s="45"/>
+      <c r="AQ157" s="45"/>
+      <c r="AR157" s="45"/>
+      <c r="AS157" s="45"/>
+      <c r="AT157" s="45"/>
+      <c r="AU157" s="46"/>
+      <c r="AV157" s="47"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
-    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>1.083333333333333</v>
       </c>
@@ -20992,7 +20993,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>1.75</v>
       </c>
@@ -21122,7 +21123,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21252,7 +21253,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12"/>
       <c r="B161" s="17"/>
       <c r="C161" s="13"/>
@@ -21310,7 +21311,7 @@
       <c r="AW161" s="12"/>
       <c r="AX161" s="12"/>
     </row>
-    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12"/>
       <c r="B162" s="17"/>
       <c r="C162" s="13"/>
@@ -21368,115 +21369,115 @@
       <c r="AW162" s="12"/>
       <c r="AX162" s="12"/>
     </row>
-    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="53"/>
-      <c r="C163" s="54"/>
-      <c r="D163" s="53"/>
-      <c r="E163" s="54"/>
-      <c r="F163" s="53"/>
-      <c r="G163" s="54"/>
-      <c r="H163" s="53"/>
-      <c r="I163" s="54"/>
-      <c r="J163" s="53"/>
-      <c r="K163" s="54"/>
-      <c r="L163" s="53"/>
-      <c r="M163" s="54"/>
-      <c r="N163" s="53"/>
-      <c r="O163" s="54"/>
-      <c r="P163" s="53"/>
-      <c r="Q163" s="54"/>
-      <c r="R163" s="53"/>
-      <c r="S163" s="54"/>
-      <c r="T163" s="53"/>
-      <c r="U163" s="54"/>
-      <c r="V163" s="53"/>
-      <c r="W163" s="54"/>
-      <c r="X163" s="53"/>
-      <c r="Y163" s="54"/>
-      <c r="Z163" s="53"/>
-      <c r="AA163" s="54"/>
-      <c r="AB163" s="53"/>
-      <c r="AC163" s="54"/>
-      <c r="AD163" s="53"/>
-      <c r="AE163" s="54"/>
-      <c r="AF163" s="53"/>
-      <c r="AG163" s="54"/>
-      <c r="AH163" s="53"/>
-      <c r="AI163" s="54"/>
-      <c r="AJ163" s="53"/>
-      <c r="AK163" s="54"/>
-      <c r="AL163" s="53"/>
-      <c r="AM163" s="54"/>
-      <c r="AN163" s="53"/>
-      <c r="AO163" s="54"/>
-      <c r="AP163" s="53"/>
-      <c r="AQ163" s="53"/>
-      <c r="AR163" s="53"/>
-      <c r="AS163" s="53"/>
-      <c r="AT163" s="53"/>
-      <c r="AU163" s="54"/>
-      <c r="AV163" s="47"/>
+      <c r="B163" s="49"/>
+      <c r="C163" s="50"/>
+      <c r="D163" s="49"/>
+      <c r="E163" s="50"/>
+      <c r="F163" s="49"/>
+      <c r="G163" s="50"/>
+      <c r="H163" s="49"/>
+      <c r="I163" s="50"/>
+      <c r="J163" s="49"/>
+      <c r="K163" s="50"/>
+      <c r="L163" s="49"/>
+      <c r="M163" s="50"/>
+      <c r="N163" s="49"/>
+      <c r="O163" s="50"/>
+      <c r="P163" s="49"/>
+      <c r="Q163" s="50"/>
+      <c r="R163" s="49"/>
+      <c r="S163" s="50"/>
+      <c r="T163" s="49"/>
+      <c r="U163" s="50"/>
+      <c r="V163" s="49"/>
+      <c r="W163" s="50"/>
+      <c r="X163" s="49"/>
+      <c r="Y163" s="50"/>
+      <c r="Z163" s="49"/>
+      <c r="AA163" s="50"/>
+      <c r="AB163" s="49"/>
+      <c r="AC163" s="50"/>
+      <c r="AD163" s="49"/>
+      <c r="AE163" s="50"/>
+      <c r="AF163" s="49"/>
+      <c r="AG163" s="50"/>
+      <c r="AH163" s="49"/>
+      <c r="AI163" s="50"/>
+      <c r="AJ163" s="49"/>
+      <c r="AK163" s="50"/>
+      <c r="AL163" s="49"/>
+      <c r="AM163" s="50"/>
+      <c r="AN163" s="49"/>
+      <c r="AO163" s="50"/>
+      <c r="AP163" s="49"/>
+      <c r="AQ163" s="49"/>
+      <c r="AR163" s="49"/>
+      <c r="AS163" s="49"/>
+      <c r="AT163" s="49"/>
+      <c r="AU163" s="50"/>
+      <c r="AV163" s="43"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
-    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="39" t="s">
+    <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="B164" s="40"/>
-      <c r="C164" s="41"/>
-      <c r="D164" s="40"/>
-      <c r="E164" s="41"/>
-      <c r="F164" s="40"/>
-      <c r="G164" s="41"/>
-      <c r="H164" s="40"/>
-      <c r="I164" s="41"/>
-      <c r="J164" s="40"/>
-      <c r="K164" s="41"/>
-      <c r="L164" s="40"/>
-      <c r="M164" s="41"/>
-      <c r="N164" s="40"/>
-      <c r="O164" s="41"/>
-      <c r="P164" s="40"/>
-      <c r="Q164" s="41"/>
-      <c r="R164" s="40"/>
-      <c r="S164" s="41"/>
-      <c r="T164" s="40"/>
-      <c r="U164" s="41"/>
-      <c r="V164" s="40"/>
-      <c r="W164" s="41"/>
-      <c r="X164" s="40"/>
-      <c r="Y164" s="41"/>
-      <c r="Z164" s="40"/>
-      <c r="AA164" s="41"/>
-      <c r="AB164" s="40"/>
-      <c r="AC164" s="41"/>
-      <c r="AD164" s="40"/>
-      <c r="AE164" s="41"/>
-      <c r="AF164" s="40"/>
-      <c r="AG164" s="41"/>
-      <c r="AH164" s="40"/>
-      <c r="AI164" s="41"/>
-      <c r="AJ164" s="40"/>
-      <c r="AK164" s="41"/>
-      <c r="AL164" s="40"/>
-      <c r="AM164" s="41"/>
-      <c r="AN164" s="40"/>
-      <c r="AO164" s="41"/>
-      <c r="AP164" s="40"/>
-      <c r="AQ164" s="40"/>
-      <c r="AR164" s="40"/>
-      <c r="AS164" s="40"/>
-      <c r="AT164" s="40"/>
-      <c r="AU164" s="41"/>
-      <c r="AV164" s="42"/>
+      <c r="B164" s="45"/>
+      <c r="C164" s="46"/>
+      <c r="D164" s="45"/>
+      <c r="E164" s="46"/>
+      <c r="F164" s="45"/>
+      <c r="G164" s="46"/>
+      <c r="H164" s="45"/>
+      <c r="I164" s="46"/>
+      <c r="J164" s="45"/>
+      <c r="K164" s="46"/>
+      <c r="L164" s="45"/>
+      <c r="M164" s="46"/>
+      <c r="N164" s="45"/>
+      <c r="O164" s="46"/>
+      <c r="P164" s="45"/>
+      <c r="Q164" s="46"/>
+      <c r="R164" s="45"/>
+      <c r="S164" s="46"/>
+      <c r="T164" s="45"/>
+      <c r="U164" s="46"/>
+      <c r="V164" s="45"/>
+      <c r="W164" s="46"/>
+      <c r="X164" s="45"/>
+      <c r="Y164" s="46"/>
+      <c r="Z164" s="45"/>
+      <c r="AA164" s="46"/>
+      <c r="AB164" s="45"/>
+      <c r="AC164" s="46"/>
+      <c r="AD164" s="45"/>
+      <c r="AE164" s="46"/>
+      <c r="AF164" s="45"/>
+      <c r="AG164" s="46"/>
+      <c r="AH164" s="45"/>
+      <c r="AI164" s="46"/>
+      <c r="AJ164" s="45"/>
+      <c r="AK164" s="46"/>
+      <c r="AL164" s="45"/>
+      <c r="AM164" s="46"/>
+      <c r="AN164" s="45"/>
+      <c r="AO164" s="46"/>
+      <c r="AP164" s="45"/>
+      <c r="AQ164" s="45"/>
+      <c r="AR164" s="45"/>
+      <c r="AS164" s="45"/>
+      <c r="AT164" s="45"/>
+      <c r="AU164" s="46"/>
+      <c r="AV164" s="47"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
-    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>1.916666666666667</v>
       </c>
@@ -21606,7 +21607,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12"/>
       <c r="B166" s="17"/>
       <c r="C166" s="13"/>
@@ -21664,61 +21665,61 @@
       <c r="AW166" s="12"/>
       <c r="AX166" s="12"/>
     </row>
-    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="39" t="s">
+    <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="40"/>
-      <c r="C167" s="41"/>
-      <c r="D167" s="40"/>
-      <c r="E167" s="41"/>
-      <c r="F167" s="40"/>
-      <c r="G167" s="41"/>
-      <c r="H167" s="40"/>
-      <c r="I167" s="41"/>
-      <c r="J167" s="40"/>
-      <c r="K167" s="41"/>
-      <c r="L167" s="40"/>
-      <c r="M167" s="41"/>
-      <c r="N167" s="40"/>
-      <c r="O167" s="41"/>
-      <c r="P167" s="40"/>
-      <c r="Q167" s="41"/>
-      <c r="R167" s="40"/>
-      <c r="S167" s="41"/>
-      <c r="T167" s="40"/>
-      <c r="U167" s="41"/>
-      <c r="V167" s="40"/>
-      <c r="W167" s="41"/>
-      <c r="X167" s="40"/>
-      <c r="Y167" s="41"/>
-      <c r="Z167" s="40"/>
-      <c r="AA167" s="41"/>
-      <c r="AB167" s="40"/>
-      <c r="AC167" s="41"/>
-      <c r="AD167" s="40"/>
-      <c r="AE167" s="41"/>
-      <c r="AF167" s="40"/>
-      <c r="AG167" s="41"/>
-      <c r="AH167" s="40"/>
-      <c r="AI167" s="41"/>
-      <c r="AJ167" s="40"/>
-      <c r="AK167" s="41"/>
-      <c r="AL167" s="40"/>
-      <c r="AM167" s="41"/>
-      <c r="AN167" s="40"/>
-      <c r="AO167" s="41"/>
-      <c r="AP167" s="40"/>
-      <c r="AQ167" s="40"/>
-      <c r="AR167" s="40"/>
-      <c r="AS167" s="40"/>
-      <c r="AT167" s="40"/>
-      <c r="AU167" s="41"/>
-      <c r="AV167" s="42"/>
+      <c r="B167" s="45"/>
+      <c r="C167" s="46"/>
+      <c r="D167" s="45"/>
+      <c r="E167" s="46"/>
+      <c r="F167" s="45"/>
+      <c r="G167" s="46"/>
+      <c r="H167" s="45"/>
+      <c r="I167" s="46"/>
+      <c r="J167" s="45"/>
+      <c r="K167" s="46"/>
+      <c r="L167" s="45"/>
+      <c r="M167" s="46"/>
+      <c r="N167" s="45"/>
+      <c r="O167" s="46"/>
+      <c r="P167" s="45"/>
+      <c r="Q167" s="46"/>
+      <c r="R167" s="45"/>
+      <c r="S167" s="46"/>
+      <c r="T167" s="45"/>
+      <c r="U167" s="46"/>
+      <c r="V167" s="45"/>
+      <c r="W167" s="46"/>
+      <c r="X167" s="45"/>
+      <c r="Y167" s="46"/>
+      <c r="Z167" s="45"/>
+      <c r="AA167" s="46"/>
+      <c r="AB167" s="45"/>
+      <c r="AC167" s="46"/>
+      <c r="AD167" s="45"/>
+      <c r="AE167" s="46"/>
+      <c r="AF167" s="45"/>
+      <c r="AG167" s="46"/>
+      <c r="AH167" s="45"/>
+      <c r="AI167" s="46"/>
+      <c r="AJ167" s="45"/>
+      <c r="AK167" s="46"/>
+      <c r="AL167" s="45"/>
+      <c r="AM167" s="46"/>
+      <c r="AN167" s="45"/>
+      <c r="AO167" s="46"/>
+      <c r="AP167" s="45"/>
+      <c r="AQ167" s="45"/>
+      <c r="AR167" s="45"/>
+      <c r="AS167" s="45"/>
+      <c r="AT167" s="45"/>
+      <c r="AU167" s="46"/>
+      <c r="AV167" s="47"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
-    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>1.875</v>
       </c>
@@ -21848,7 +21849,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12"/>
       <c r="B169" s="17"/>
       <c r="C169" s="13"/>
@@ -21906,61 +21907,61 @@
       <c r="AW169" s="12"/>
       <c r="AX169" s="12"/>
     </row>
-    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="39" t="s">
+    <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="B170" s="40"/>
-      <c r="C170" s="41"/>
-      <c r="D170" s="40"/>
-      <c r="E170" s="41"/>
-      <c r="F170" s="40"/>
-      <c r="G170" s="41"/>
-      <c r="H170" s="40"/>
-      <c r="I170" s="41"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="41"/>
-      <c r="L170" s="40"/>
-      <c r="M170" s="41"/>
-      <c r="N170" s="40"/>
-      <c r="O170" s="41"/>
-      <c r="P170" s="40"/>
-      <c r="Q170" s="41"/>
-      <c r="R170" s="40"/>
-      <c r="S170" s="41"/>
-      <c r="T170" s="40"/>
-      <c r="U170" s="41"/>
-      <c r="V170" s="40"/>
-      <c r="W170" s="41"/>
-      <c r="X170" s="40"/>
-      <c r="Y170" s="41"/>
-      <c r="Z170" s="40"/>
-      <c r="AA170" s="41"/>
-      <c r="AB170" s="40"/>
-      <c r="AC170" s="41"/>
-      <c r="AD170" s="40"/>
-      <c r="AE170" s="41"/>
-      <c r="AF170" s="40"/>
-      <c r="AG170" s="41"/>
-      <c r="AH170" s="40"/>
-      <c r="AI170" s="41"/>
-      <c r="AJ170" s="40"/>
-      <c r="AK170" s="41"/>
-      <c r="AL170" s="40"/>
-      <c r="AM170" s="41"/>
-      <c r="AN170" s="40"/>
-      <c r="AO170" s="41"/>
-      <c r="AP170" s="40"/>
-      <c r="AQ170" s="40"/>
-      <c r="AR170" s="40"/>
-      <c r="AS170" s="40"/>
-      <c r="AT170" s="40"/>
-      <c r="AU170" s="41"/>
-      <c r="AV170" s="42"/>
+      <c r="B170" s="45"/>
+      <c r="C170" s="46"/>
+      <c r="D170" s="45"/>
+      <c r="E170" s="46"/>
+      <c r="F170" s="45"/>
+      <c r="G170" s="46"/>
+      <c r="H170" s="45"/>
+      <c r="I170" s="46"/>
+      <c r="J170" s="45"/>
+      <c r="K170" s="46"/>
+      <c r="L170" s="45"/>
+      <c r="M170" s="46"/>
+      <c r="N170" s="45"/>
+      <c r="O170" s="46"/>
+      <c r="P170" s="45"/>
+      <c r="Q170" s="46"/>
+      <c r="R170" s="45"/>
+      <c r="S170" s="46"/>
+      <c r="T170" s="45"/>
+      <c r="U170" s="46"/>
+      <c r="V170" s="45"/>
+      <c r="W170" s="46"/>
+      <c r="X170" s="45"/>
+      <c r="Y170" s="46"/>
+      <c r="Z170" s="45"/>
+      <c r="AA170" s="46"/>
+      <c r="AB170" s="45"/>
+      <c r="AC170" s="46"/>
+      <c r="AD170" s="45"/>
+      <c r="AE170" s="46"/>
+      <c r="AF170" s="45"/>
+      <c r="AG170" s="46"/>
+      <c r="AH170" s="45"/>
+      <c r="AI170" s="46"/>
+      <c r="AJ170" s="45"/>
+      <c r="AK170" s="46"/>
+      <c r="AL170" s="45"/>
+      <c r="AM170" s="46"/>
+      <c r="AN170" s="45"/>
+      <c r="AO170" s="46"/>
+      <c r="AP170" s="45"/>
+      <c r="AQ170" s="45"/>
+      <c r="AR170" s="45"/>
+      <c r="AS170" s="45"/>
+      <c r="AT170" s="45"/>
+      <c r="AU170" s="46"/>
+      <c r="AV170" s="47"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
-    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -22090,7 +22091,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12"/>
       <c r="B172" s="17"/>
       <c r="C172" s="13"/>
@@ -22148,61 +22149,61 @@
       <c r="AW172" s="12"/>
       <c r="AX172" s="12"/>
     </row>
-    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="39" t="s">
+    <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="40"/>
-      <c r="C173" s="41"/>
-      <c r="D173" s="40"/>
-      <c r="E173" s="41"/>
-      <c r="F173" s="40"/>
-      <c r="G173" s="41"/>
-      <c r="H173" s="40"/>
-      <c r="I173" s="41"/>
-      <c r="J173" s="40"/>
-      <c r="K173" s="41"/>
-      <c r="L173" s="40"/>
-      <c r="M173" s="41"/>
-      <c r="N173" s="40"/>
-      <c r="O173" s="41"/>
-      <c r="P173" s="40"/>
-      <c r="Q173" s="41"/>
-      <c r="R173" s="40"/>
-      <c r="S173" s="41"/>
-      <c r="T173" s="40"/>
-      <c r="U173" s="41"/>
-      <c r="V173" s="40"/>
-      <c r="W173" s="41"/>
-      <c r="X173" s="40"/>
-      <c r="Y173" s="41"/>
-      <c r="Z173" s="40"/>
-      <c r="AA173" s="41"/>
-      <c r="AB173" s="40"/>
-      <c r="AC173" s="41"/>
-      <c r="AD173" s="40"/>
-      <c r="AE173" s="41"/>
-      <c r="AF173" s="40"/>
-      <c r="AG173" s="41"/>
-      <c r="AH173" s="40"/>
-      <c r="AI173" s="41"/>
-      <c r="AJ173" s="40"/>
-      <c r="AK173" s="41"/>
-      <c r="AL173" s="40"/>
-      <c r="AM173" s="41"/>
-      <c r="AN173" s="40"/>
-      <c r="AO173" s="41"/>
-      <c r="AP173" s="40"/>
-      <c r="AQ173" s="40"/>
-      <c r="AR173" s="40"/>
-      <c r="AS173" s="40"/>
-      <c r="AT173" s="40"/>
-      <c r="AU173" s="41"/>
-      <c r="AV173" s="42"/>
+      <c r="B173" s="45"/>
+      <c r="C173" s="46"/>
+      <c r="D173" s="45"/>
+      <c r="E173" s="46"/>
+      <c r="F173" s="45"/>
+      <c r="G173" s="46"/>
+      <c r="H173" s="45"/>
+      <c r="I173" s="46"/>
+      <c r="J173" s="45"/>
+      <c r="K173" s="46"/>
+      <c r="L173" s="45"/>
+      <c r="M173" s="46"/>
+      <c r="N173" s="45"/>
+      <c r="O173" s="46"/>
+      <c r="P173" s="45"/>
+      <c r="Q173" s="46"/>
+      <c r="R173" s="45"/>
+      <c r="S173" s="46"/>
+      <c r="T173" s="45"/>
+      <c r="U173" s="46"/>
+      <c r="V173" s="45"/>
+      <c r="W173" s="46"/>
+      <c r="X173" s="45"/>
+      <c r="Y173" s="46"/>
+      <c r="Z173" s="45"/>
+      <c r="AA173" s="46"/>
+      <c r="AB173" s="45"/>
+      <c r="AC173" s="46"/>
+      <c r="AD173" s="45"/>
+      <c r="AE173" s="46"/>
+      <c r="AF173" s="45"/>
+      <c r="AG173" s="46"/>
+      <c r="AH173" s="45"/>
+      <c r="AI173" s="46"/>
+      <c r="AJ173" s="45"/>
+      <c r="AK173" s="46"/>
+      <c r="AL173" s="45"/>
+      <c r="AM173" s="46"/>
+      <c r="AN173" s="45"/>
+      <c r="AO173" s="46"/>
+      <c r="AP173" s="45"/>
+      <c r="AQ173" s="45"/>
+      <c r="AR173" s="45"/>
+      <c r="AS173" s="45"/>
+      <c r="AT173" s="45"/>
+      <c r="AU173" s="46"/>
+      <c r="AV173" s="47"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
-    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>1.125</v>
       </c>
@@ -22332,7 +22333,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12"/>
       <c r="B175" s="17"/>
       <c r="C175" s="13"/>
@@ -22390,7 +22391,7 @@
       <c r="AW175" s="12"/>
       <c r="AX175" s="12"/>
     </row>
-    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12"/>
       <c r="B176" s="17"/>
       <c r="C176" s="13"/>
@@ -22448,115 +22449,115 @@
       <c r="AW176" s="12"/>
       <c r="AX176" s="12"/>
     </row>
-    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="B177" s="53"/>
-      <c r="C177" s="54"/>
-      <c r="D177" s="53"/>
-      <c r="E177" s="54"/>
-      <c r="F177" s="53"/>
-      <c r="G177" s="54"/>
-      <c r="H177" s="53"/>
-      <c r="I177" s="54"/>
-      <c r="J177" s="53"/>
-      <c r="K177" s="54"/>
-      <c r="L177" s="53"/>
-      <c r="M177" s="54"/>
-      <c r="N177" s="53"/>
-      <c r="O177" s="54"/>
-      <c r="P177" s="53"/>
-      <c r="Q177" s="54"/>
-      <c r="R177" s="53"/>
-      <c r="S177" s="54"/>
-      <c r="T177" s="53"/>
-      <c r="U177" s="54"/>
-      <c r="V177" s="53"/>
-      <c r="W177" s="54"/>
-      <c r="X177" s="53"/>
-      <c r="Y177" s="54"/>
-      <c r="Z177" s="53"/>
-      <c r="AA177" s="54"/>
-      <c r="AB177" s="53"/>
-      <c r="AC177" s="54"/>
-      <c r="AD177" s="53"/>
-      <c r="AE177" s="54"/>
-      <c r="AF177" s="53"/>
-      <c r="AG177" s="54"/>
-      <c r="AH177" s="53"/>
-      <c r="AI177" s="54"/>
-      <c r="AJ177" s="53"/>
-      <c r="AK177" s="54"/>
-      <c r="AL177" s="53"/>
-      <c r="AM177" s="54"/>
-      <c r="AN177" s="53"/>
-      <c r="AO177" s="54"/>
-      <c r="AP177" s="53"/>
-      <c r="AQ177" s="53"/>
-      <c r="AR177" s="53"/>
-      <c r="AS177" s="53"/>
-      <c r="AT177" s="53"/>
-      <c r="AU177" s="54"/>
-      <c r="AV177" s="47"/>
+      <c r="B177" s="49"/>
+      <c r="C177" s="50"/>
+      <c r="D177" s="49"/>
+      <c r="E177" s="50"/>
+      <c r="F177" s="49"/>
+      <c r="G177" s="50"/>
+      <c r="H177" s="49"/>
+      <c r="I177" s="50"/>
+      <c r="J177" s="49"/>
+      <c r="K177" s="50"/>
+      <c r="L177" s="49"/>
+      <c r="M177" s="50"/>
+      <c r="N177" s="49"/>
+      <c r="O177" s="50"/>
+      <c r="P177" s="49"/>
+      <c r="Q177" s="50"/>
+      <c r="R177" s="49"/>
+      <c r="S177" s="50"/>
+      <c r="T177" s="49"/>
+      <c r="U177" s="50"/>
+      <c r="V177" s="49"/>
+      <c r="W177" s="50"/>
+      <c r="X177" s="49"/>
+      <c r="Y177" s="50"/>
+      <c r="Z177" s="49"/>
+      <c r="AA177" s="50"/>
+      <c r="AB177" s="49"/>
+      <c r="AC177" s="50"/>
+      <c r="AD177" s="49"/>
+      <c r="AE177" s="50"/>
+      <c r="AF177" s="49"/>
+      <c r="AG177" s="50"/>
+      <c r="AH177" s="49"/>
+      <c r="AI177" s="50"/>
+      <c r="AJ177" s="49"/>
+      <c r="AK177" s="50"/>
+      <c r="AL177" s="49"/>
+      <c r="AM177" s="50"/>
+      <c r="AN177" s="49"/>
+      <c r="AO177" s="50"/>
+      <c r="AP177" s="49"/>
+      <c r="AQ177" s="49"/>
+      <c r="AR177" s="49"/>
+      <c r="AS177" s="49"/>
+      <c r="AT177" s="49"/>
+      <c r="AU177" s="50"/>
+      <c r="AV177" s="43"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
-    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="39" t="s">
+    <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="40"/>
-      <c r="C178" s="41"/>
-      <c r="D178" s="40"/>
-      <c r="E178" s="41"/>
-      <c r="F178" s="40"/>
-      <c r="G178" s="41"/>
-      <c r="H178" s="40"/>
-      <c r="I178" s="41"/>
-      <c r="J178" s="40"/>
-      <c r="K178" s="41"/>
-      <c r="L178" s="40"/>
-      <c r="M178" s="41"/>
-      <c r="N178" s="40"/>
-      <c r="O178" s="41"/>
-      <c r="P178" s="40"/>
-      <c r="Q178" s="41"/>
-      <c r="R178" s="40"/>
-      <c r="S178" s="41"/>
-      <c r="T178" s="40"/>
-      <c r="U178" s="41"/>
-      <c r="V178" s="40"/>
-      <c r="W178" s="41"/>
-      <c r="X178" s="40"/>
-      <c r="Y178" s="41"/>
-      <c r="Z178" s="40"/>
-      <c r="AA178" s="41"/>
-      <c r="AB178" s="40"/>
-      <c r="AC178" s="41"/>
-      <c r="AD178" s="40"/>
-      <c r="AE178" s="41"/>
-      <c r="AF178" s="40"/>
-      <c r="AG178" s="41"/>
-      <c r="AH178" s="40"/>
-      <c r="AI178" s="41"/>
-      <c r="AJ178" s="40"/>
-      <c r="AK178" s="41"/>
-      <c r="AL178" s="40"/>
-      <c r="AM178" s="41"/>
-      <c r="AN178" s="40"/>
-      <c r="AO178" s="41"/>
-      <c r="AP178" s="40"/>
-      <c r="AQ178" s="40"/>
-      <c r="AR178" s="40"/>
-      <c r="AS178" s="40"/>
-      <c r="AT178" s="40"/>
-      <c r="AU178" s="41"/>
-      <c r="AV178" s="42"/>
+      <c r="B178" s="45"/>
+      <c r="C178" s="46"/>
+      <c r="D178" s="45"/>
+      <c r="E178" s="46"/>
+      <c r="F178" s="45"/>
+      <c r="G178" s="46"/>
+      <c r="H178" s="45"/>
+      <c r="I178" s="46"/>
+      <c r="J178" s="45"/>
+      <c r="K178" s="46"/>
+      <c r="L178" s="45"/>
+      <c r="M178" s="46"/>
+      <c r="N178" s="45"/>
+      <c r="O178" s="46"/>
+      <c r="P178" s="45"/>
+      <c r="Q178" s="46"/>
+      <c r="R178" s="45"/>
+      <c r="S178" s="46"/>
+      <c r="T178" s="45"/>
+      <c r="U178" s="46"/>
+      <c r="V178" s="45"/>
+      <c r="W178" s="46"/>
+      <c r="X178" s="45"/>
+      <c r="Y178" s="46"/>
+      <c r="Z178" s="45"/>
+      <c r="AA178" s="46"/>
+      <c r="AB178" s="45"/>
+      <c r="AC178" s="46"/>
+      <c r="AD178" s="45"/>
+      <c r="AE178" s="46"/>
+      <c r="AF178" s="45"/>
+      <c r="AG178" s="46"/>
+      <c r="AH178" s="45"/>
+      <c r="AI178" s="46"/>
+      <c r="AJ178" s="45"/>
+      <c r="AK178" s="46"/>
+      <c r="AL178" s="45"/>
+      <c r="AM178" s="46"/>
+      <c r="AN178" s="45"/>
+      <c r="AO178" s="46"/>
+      <c r="AP178" s="45"/>
+      <c r="AQ178" s="45"/>
+      <c r="AR178" s="45"/>
+      <c r="AS178" s="45"/>
+      <c r="AT178" s="45"/>
+      <c r="AU178" s="46"/>
+      <c r="AV178" s="47"/>
       <c r="AW178" s="8"/>
       <c r="AX178" s="8"/>
     </row>
-    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>1.875</v>
       </c>
@@ -22686,7 +22687,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12"/>
       <c r="B180" s="17"/>
       <c r="C180" s="13"/>
@@ -22744,61 +22745,61 @@
       <c r="AW180" s="12"/>
       <c r="AX180" s="12"/>
     </row>
-    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="39" t="s">
+    <row r="181" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="B181" s="40"/>
-      <c r="C181" s="41"/>
-      <c r="D181" s="40"/>
-      <c r="E181" s="41"/>
-      <c r="F181" s="40"/>
-      <c r="G181" s="41"/>
-      <c r="H181" s="40"/>
-      <c r="I181" s="41"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="41"/>
-      <c r="L181" s="40"/>
-      <c r="M181" s="41"/>
-      <c r="N181" s="40"/>
-      <c r="O181" s="41"/>
-      <c r="P181" s="40"/>
-      <c r="Q181" s="41"/>
-      <c r="R181" s="40"/>
-      <c r="S181" s="41"/>
-      <c r="T181" s="40"/>
-      <c r="U181" s="41"/>
-      <c r="V181" s="40"/>
-      <c r="W181" s="41"/>
-      <c r="X181" s="40"/>
-      <c r="Y181" s="41"/>
-      <c r="Z181" s="40"/>
-      <c r="AA181" s="41"/>
-      <c r="AB181" s="40"/>
-      <c r="AC181" s="41"/>
-      <c r="AD181" s="40"/>
-      <c r="AE181" s="41"/>
-      <c r="AF181" s="40"/>
-      <c r="AG181" s="41"/>
-      <c r="AH181" s="40"/>
-      <c r="AI181" s="41"/>
-      <c r="AJ181" s="40"/>
-      <c r="AK181" s="41"/>
-      <c r="AL181" s="40"/>
-      <c r="AM181" s="41"/>
-      <c r="AN181" s="40"/>
-      <c r="AO181" s="41"/>
-      <c r="AP181" s="40"/>
-      <c r="AQ181" s="40"/>
-      <c r="AR181" s="40"/>
-      <c r="AS181" s="40"/>
-      <c r="AT181" s="40"/>
-      <c r="AU181" s="41"/>
-      <c r="AV181" s="42"/>
+      <c r="B181" s="45"/>
+      <c r="C181" s="46"/>
+      <c r="D181" s="45"/>
+      <c r="E181" s="46"/>
+      <c r="F181" s="45"/>
+      <c r="G181" s="46"/>
+      <c r="H181" s="45"/>
+      <c r="I181" s="46"/>
+      <c r="J181" s="45"/>
+      <c r="K181" s="46"/>
+      <c r="L181" s="45"/>
+      <c r="M181" s="46"/>
+      <c r="N181" s="45"/>
+      <c r="O181" s="46"/>
+      <c r="P181" s="45"/>
+      <c r="Q181" s="46"/>
+      <c r="R181" s="45"/>
+      <c r="S181" s="46"/>
+      <c r="T181" s="45"/>
+      <c r="U181" s="46"/>
+      <c r="V181" s="45"/>
+      <c r="W181" s="46"/>
+      <c r="X181" s="45"/>
+      <c r="Y181" s="46"/>
+      <c r="Z181" s="45"/>
+      <c r="AA181" s="46"/>
+      <c r="AB181" s="45"/>
+      <c r="AC181" s="46"/>
+      <c r="AD181" s="45"/>
+      <c r="AE181" s="46"/>
+      <c r="AF181" s="45"/>
+      <c r="AG181" s="46"/>
+      <c r="AH181" s="45"/>
+      <c r="AI181" s="46"/>
+      <c r="AJ181" s="45"/>
+      <c r="AK181" s="46"/>
+      <c r="AL181" s="45"/>
+      <c r="AM181" s="46"/>
+      <c r="AN181" s="45"/>
+      <c r="AO181" s="46"/>
+      <c r="AP181" s="45"/>
+      <c r="AQ181" s="45"/>
+      <c r="AR181" s="45"/>
+      <c r="AS181" s="45"/>
+      <c r="AT181" s="45"/>
+      <c r="AU181" s="46"/>
+      <c r="AV181" s="47"/>
       <c r="AW181" s="8"/>
       <c r="AX181" s="8"/>
     </row>
-    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>1.875</v>
       </c>
@@ -22928,7 +22929,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12"/>
       <c r="B183" s="17"/>
       <c r="C183" s="13"/>
@@ -22986,7 +22987,7 @@
       <c r="AW183" s="12"/>
       <c r="AX183" s="12"/>
     </row>
-    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12"/>
       <c r="B184" s="17"/>
       <c r="C184" s="13"/>
@@ -23044,115 +23045,115 @@
       <c r="AW184" s="12"/>
       <c r="AX184" s="12"/>
     </row>
-    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="B185" s="53"/>
-      <c r="C185" s="54"/>
-      <c r="D185" s="53"/>
-      <c r="E185" s="54"/>
-      <c r="F185" s="53"/>
-      <c r="G185" s="54"/>
-      <c r="H185" s="53"/>
-      <c r="I185" s="54"/>
-      <c r="J185" s="53"/>
-      <c r="K185" s="54"/>
-      <c r="L185" s="53"/>
-      <c r="M185" s="54"/>
-      <c r="N185" s="53"/>
-      <c r="O185" s="54"/>
-      <c r="P185" s="53"/>
-      <c r="Q185" s="54"/>
-      <c r="R185" s="53"/>
-      <c r="S185" s="54"/>
-      <c r="T185" s="53"/>
-      <c r="U185" s="54"/>
-      <c r="V185" s="53"/>
-      <c r="W185" s="54"/>
-      <c r="X185" s="53"/>
-      <c r="Y185" s="54"/>
-      <c r="Z185" s="53"/>
-      <c r="AA185" s="54"/>
-      <c r="AB185" s="53"/>
-      <c r="AC185" s="54"/>
-      <c r="AD185" s="53"/>
-      <c r="AE185" s="54"/>
-      <c r="AF185" s="53"/>
-      <c r="AG185" s="54"/>
-      <c r="AH185" s="53"/>
-      <c r="AI185" s="54"/>
-      <c r="AJ185" s="53"/>
-      <c r="AK185" s="54"/>
-      <c r="AL185" s="53"/>
-      <c r="AM185" s="54"/>
-      <c r="AN185" s="53"/>
-      <c r="AO185" s="54"/>
-      <c r="AP185" s="53"/>
-      <c r="AQ185" s="53"/>
-      <c r="AR185" s="53"/>
-      <c r="AS185" s="53"/>
-      <c r="AT185" s="53"/>
-      <c r="AU185" s="54"/>
-      <c r="AV185" s="47"/>
+      <c r="B185" s="49"/>
+      <c r="C185" s="50"/>
+      <c r="D185" s="49"/>
+      <c r="E185" s="50"/>
+      <c r="F185" s="49"/>
+      <c r="G185" s="50"/>
+      <c r="H185" s="49"/>
+      <c r="I185" s="50"/>
+      <c r="J185" s="49"/>
+      <c r="K185" s="50"/>
+      <c r="L185" s="49"/>
+      <c r="M185" s="50"/>
+      <c r="N185" s="49"/>
+      <c r="O185" s="50"/>
+      <c r="P185" s="49"/>
+      <c r="Q185" s="50"/>
+      <c r="R185" s="49"/>
+      <c r="S185" s="50"/>
+      <c r="T185" s="49"/>
+      <c r="U185" s="50"/>
+      <c r="V185" s="49"/>
+      <c r="W185" s="50"/>
+      <c r="X185" s="49"/>
+      <c r="Y185" s="50"/>
+      <c r="Z185" s="49"/>
+      <c r="AA185" s="50"/>
+      <c r="AB185" s="49"/>
+      <c r="AC185" s="50"/>
+      <c r="AD185" s="49"/>
+      <c r="AE185" s="50"/>
+      <c r="AF185" s="49"/>
+      <c r="AG185" s="50"/>
+      <c r="AH185" s="49"/>
+      <c r="AI185" s="50"/>
+      <c r="AJ185" s="49"/>
+      <c r="AK185" s="50"/>
+      <c r="AL185" s="49"/>
+      <c r="AM185" s="50"/>
+      <c r="AN185" s="49"/>
+      <c r="AO185" s="50"/>
+      <c r="AP185" s="49"/>
+      <c r="AQ185" s="49"/>
+      <c r="AR185" s="49"/>
+      <c r="AS185" s="49"/>
+      <c r="AT185" s="49"/>
+      <c r="AU185" s="50"/>
+      <c r="AV185" s="43"/>
       <c r="AW185" s="7"/>
       <c r="AX185" s="7"/>
     </row>
-    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="39" t="s">
+    <row r="186" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="B186" s="40"/>
-      <c r="C186" s="41"/>
-      <c r="D186" s="40"/>
-      <c r="E186" s="41"/>
-      <c r="F186" s="40"/>
-      <c r="G186" s="41"/>
-      <c r="H186" s="40"/>
-      <c r="I186" s="41"/>
-      <c r="J186" s="40"/>
-      <c r="K186" s="41"/>
-      <c r="L186" s="40"/>
-      <c r="M186" s="41"/>
-      <c r="N186" s="40"/>
-      <c r="O186" s="41"/>
-      <c r="P186" s="40"/>
-      <c r="Q186" s="41"/>
-      <c r="R186" s="40"/>
-      <c r="S186" s="41"/>
-      <c r="T186" s="40"/>
-      <c r="U186" s="41"/>
-      <c r="V186" s="40"/>
-      <c r="W186" s="41"/>
-      <c r="X186" s="40"/>
-      <c r="Y186" s="41"/>
-      <c r="Z186" s="40"/>
-      <c r="AA186" s="41"/>
-      <c r="AB186" s="40"/>
-      <c r="AC186" s="41"/>
-      <c r="AD186" s="40"/>
-      <c r="AE186" s="41"/>
-      <c r="AF186" s="40"/>
-      <c r="AG186" s="41"/>
-      <c r="AH186" s="40"/>
-      <c r="AI186" s="41"/>
-      <c r="AJ186" s="40"/>
-      <c r="AK186" s="41"/>
-      <c r="AL186" s="40"/>
-      <c r="AM186" s="41"/>
-      <c r="AN186" s="40"/>
-      <c r="AO186" s="41"/>
-      <c r="AP186" s="40"/>
-      <c r="AQ186" s="40"/>
-      <c r="AR186" s="40"/>
-      <c r="AS186" s="40"/>
-      <c r="AT186" s="40"/>
-      <c r="AU186" s="41"/>
-      <c r="AV186" s="42"/>
+      <c r="B186" s="45"/>
+      <c r="C186" s="46"/>
+      <c r="D186" s="45"/>
+      <c r="E186" s="46"/>
+      <c r="F186" s="45"/>
+      <c r="G186" s="46"/>
+      <c r="H186" s="45"/>
+      <c r="I186" s="46"/>
+      <c r="J186" s="45"/>
+      <c r="K186" s="46"/>
+      <c r="L186" s="45"/>
+      <c r="M186" s="46"/>
+      <c r="N186" s="45"/>
+      <c r="O186" s="46"/>
+      <c r="P186" s="45"/>
+      <c r="Q186" s="46"/>
+      <c r="R186" s="45"/>
+      <c r="S186" s="46"/>
+      <c r="T186" s="45"/>
+      <c r="U186" s="46"/>
+      <c r="V186" s="45"/>
+      <c r="W186" s="46"/>
+      <c r="X186" s="45"/>
+      <c r="Y186" s="46"/>
+      <c r="Z186" s="45"/>
+      <c r="AA186" s="46"/>
+      <c r="AB186" s="45"/>
+      <c r="AC186" s="46"/>
+      <c r="AD186" s="45"/>
+      <c r="AE186" s="46"/>
+      <c r="AF186" s="45"/>
+      <c r="AG186" s="46"/>
+      <c r="AH186" s="45"/>
+      <c r="AI186" s="46"/>
+      <c r="AJ186" s="45"/>
+      <c r="AK186" s="46"/>
+      <c r="AL186" s="45"/>
+      <c r="AM186" s="46"/>
+      <c r="AN186" s="45"/>
+      <c r="AO186" s="46"/>
+      <c r="AP186" s="45"/>
+      <c r="AQ186" s="45"/>
+      <c r="AR186" s="45"/>
+      <c r="AS186" s="45"/>
+      <c r="AT186" s="45"/>
+      <c r="AU186" s="46"/>
+      <c r="AV186" s="47"/>
       <c r="AW186" s="8"/>
       <c r="AX186" s="8"/>
     </row>
-    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>1.958333333333333</v>
       </c>
@@ -23282,7 +23283,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12"/>
       <c r="B188" s="17"/>
       <c r="C188" s="13"/>
@@ -23340,7 +23341,7 @@
       <c r="AW188" s="12"/>
       <c r="AX188" s="12"/>
     </row>
-    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12"/>
       <c r="B189" s="17"/>
       <c r="C189" s="13"/>
@@ -23398,115 +23399,115 @@
       <c r="AW189" s="12"/>
       <c r="AX189" s="12"/>
     </row>
-    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="B190" s="53"/>
-      <c r="C190" s="54"/>
-      <c r="D190" s="53"/>
-      <c r="E190" s="54"/>
-      <c r="F190" s="53"/>
-      <c r="G190" s="54"/>
-      <c r="H190" s="53"/>
-      <c r="I190" s="54"/>
-      <c r="J190" s="53"/>
-      <c r="K190" s="54"/>
-      <c r="L190" s="53"/>
-      <c r="M190" s="54"/>
-      <c r="N190" s="53"/>
-      <c r="O190" s="54"/>
-      <c r="P190" s="53"/>
-      <c r="Q190" s="54"/>
-      <c r="R190" s="53"/>
-      <c r="S190" s="54"/>
-      <c r="T190" s="53"/>
-      <c r="U190" s="54"/>
-      <c r="V190" s="53"/>
-      <c r="W190" s="54"/>
-      <c r="X190" s="53"/>
-      <c r="Y190" s="54"/>
-      <c r="Z190" s="53"/>
-      <c r="AA190" s="54"/>
-      <c r="AB190" s="53"/>
-      <c r="AC190" s="54"/>
-      <c r="AD190" s="53"/>
-      <c r="AE190" s="54"/>
-      <c r="AF190" s="53"/>
-      <c r="AG190" s="54"/>
-      <c r="AH190" s="53"/>
-      <c r="AI190" s="54"/>
-      <c r="AJ190" s="53"/>
-      <c r="AK190" s="54"/>
-      <c r="AL190" s="53"/>
-      <c r="AM190" s="54"/>
-      <c r="AN190" s="53"/>
-      <c r="AO190" s="54"/>
-      <c r="AP190" s="53"/>
-      <c r="AQ190" s="53"/>
-      <c r="AR190" s="53"/>
-      <c r="AS190" s="53"/>
-      <c r="AT190" s="53"/>
-      <c r="AU190" s="54"/>
-      <c r="AV190" s="47"/>
+      <c r="B190" s="49"/>
+      <c r="C190" s="50"/>
+      <c r="D190" s="49"/>
+      <c r="E190" s="50"/>
+      <c r="F190" s="49"/>
+      <c r="G190" s="50"/>
+      <c r="H190" s="49"/>
+      <c r="I190" s="50"/>
+      <c r="J190" s="49"/>
+      <c r="K190" s="50"/>
+      <c r="L190" s="49"/>
+      <c r="M190" s="50"/>
+      <c r="N190" s="49"/>
+      <c r="O190" s="50"/>
+      <c r="P190" s="49"/>
+      <c r="Q190" s="50"/>
+      <c r="R190" s="49"/>
+      <c r="S190" s="50"/>
+      <c r="T190" s="49"/>
+      <c r="U190" s="50"/>
+      <c r="V190" s="49"/>
+      <c r="W190" s="50"/>
+      <c r="X190" s="49"/>
+      <c r="Y190" s="50"/>
+      <c r="Z190" s="49"/>
+      <c r="AA190" s="50"/>
+      <c r="AB190" s="49"/>
+      <c r="AC190" s="50"/>
+      <c r="AD190" s="49"/>
+      <c r="AE190" s="50"/>
+      <c r="AF190" s="49"/>
+      <c r="AG190" s="50"/>
+      <c r="AH190" s="49"/>
+      <c r="AI190" s="50"/>
+      <c r="AJ190" s="49"/>
+      <c r="AK190" s="50"/>
+      <c r="AL190" s="49"/>
+      <c r="AM190" s="50"/>
+      <c r="AN190" s="49"/>
+      <c r="AO190" s="50"/>
+      <c r="AP190" s="49"/>
+      <c r="AQ190" s="49"/>
+      <c r="AR190" s="49"/>
+      <c r="AS190" s="49"/>
+      <c r="AT190" s="49"/>
+      <c r="AU190" s="50"/>
+      <c r="AV190" s="43"/>
       <c r="AW190" s="7"/>
       <c r="AX190" s="7"/>
     </row>
-    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="39" t="s">
+    <row r="191" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B191" s="40"/>
-      <c r="C191" s="41"/>
-      <c r="D191" s="40"/>
-      <c r="E191" s="41"/>
-      <c r="F191" s="40"/>
-      <c r="G191" s="41"/>
-      <c r="H191" s="40"/>
-      <c r="I191" s="41"/>
-      <c r="J191" s="40"/>
-      <c r="K191" s="41"/>
-      <c r="L191" s="40"/>
-      <c r="M191" s="41"/>
-      <c r="N191" s="40"/>
-      <c r="O191" s="41"/>
-      <c r="P191" s="40"/>
-      <c r="Q191" s="41"/>
-      <c r="R191" s="40"/>
-      <c r="S191" s="41"/>
-      <c r="T191" s="40"/>
-      <c r="U191" s="41"/>
-      <c r="V191" s="40"/>
-      <c r="W191" s="41"/>
-      <c r="X191" s="40"/>
-      <c r="Y191" s="41"/>
-      <c r="Z191" s="40"/>
-      <c r="AA191" s="41"/>
-      <c r="AB191" s="40"/>
-      <c r="AC191" s="41"/>
-      <c r="AD191" s="40"/>
-      <c r="AE191" s="41"/>
-      <c r="AF191" s="40"/>
-      <c r="AG191" s="41"/>
-      <c r="AH191" s="40"/>
-      <c r="AI191" s="41"/>
-      <c r="AJ191" s="40"/>
-      <c r="AK191" s="41"/>
-      <c r="AL191" s="40"/>
-      <c r="AM191" s="41"/>
-      <c r="AN191" s="40"/>
-      <c r="AO191" s="41"/>
-      <c r="AP191" s="40"/>
-      <c r="AQ191" s="40"/>
-      <c r="AR191" s="40"/>
-      <c r="AS191" s="40"/>
-      <c r="AT191" s="40"/>
-      <c r="AU191" s="41"/>
-      <c r="AV191" s="42"/>
+      <c r="B191" s="45"/>
+      <c r="C191" s="46"/>
+      <c r="D191" s="45"/>
+      <c r="E191" s="46"/>
+      <c r="F191" s="45"/>
+      <c r="G191" s="46"/>
+      <c r="H191" s="45"/>
+      <c r="I191" s="46"/>
+      <c r="J191" s="45"/>
+      <c r="K191" s="46"/>
+      <c r="L191" s="45"/>
+      <c r="M191" s="46"/>
+      <c r="N191" s="45"/>
+      <c r="O191" s="46"/>
+      <c r="P191" s="45"/>
+      <c r="Q191" s="46"/>
+      <c r="R191" s="45"/>
+      <c r="S191" s="46"/>
+      <c r="T191" s="45"/>
+      <c r="U191" s="46"/>
+      <c r="V191" s="45"/>
+      <c r="W191" s="46"/>
+      <c r="X191" s="45"/>
+      <c r="Y191" s="46"/>
+      <c r="Z191" s="45"/>
+      <c r="AA191" s="46"/>
+      <c r="AB191" s="45"/>
+      <c r="AC191" s="46"/>
+      <c r="AD191" s="45"/>
+      <c r="AE191" s="46"/>
+      <c r="AF191" s="45"/>
+      <c r="AG191" s="46"/>
+      <c r="AH191" s="45"/>
+      <c r="AI191" s="46"/>
+      <c r="AJ191" s="45"/>
+      <c r="AK191" s="46"/>
+      <c r="AL191" s="45"/>
+      <c r="AM191" s="46"/>
+      <c r="AN191" s="45"/>
+      <c r="AO191" s="46"/>
+      <c r="AP191" s="45"/>
+      <c r="AQ191" s="45"/>
+      <c r="AR191" s="45"/>
+      <c r="AS191" s="45"/>
+      <c r="AT191" s="45"/>
+      <c r="AU191" s="46"/>
+      <c r="AV191" s="47"/>
       <c r="AW191" s="8"/>
       <c r="AX191" s="8"/>
     </row>
-    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>1.875</v>
       </c>
@@ -23636,7 +23637,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12"/>
       <c r="B193" s="17"/>
       <c r="C193" s="13"/>
@@ -23694,7 +23695,7 @@
       <c r="AW193" s="12"/>
       <c r="AX193" s="12"/>
     </row>
-    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12"/>
       <c r="B194" s="17"/>
       <c r="C194" s="13"/>
@@ -23753,7 +23754,85 @@
       <c r="AX194" s="12"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AV194" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4" showButton="0"/>
+    <filterColumn colId="6" showButton="0"/>
+    <filterColumn colId="8" showButton="0"/>
+    <filterColumn colId="10" showButton="0"/>
+    <filterColumn colId="12" showButton="0"/>
+    <filterColumn colId="14" showButton="0"/>
+    <filterColumn colId="16" showButton="0"/>
+    <filterColumn colId="18" showButton="0"/>
+    <filterColumn colId="20" showButton="0"/>
+    <filterColumn colId="22" showButton="0"/>
+    <filterColumn colId="24" showButton="0"/>
+    <filterColumn colId="26" showButton="0"/>
+    <filterColumn colId="28" showButton="0"/>
+    <filterColumn colId="30" showButton="0"/>
+    <filterColumn colId="32" showButton="0"/>
+    <filterColumn colId="34" showButton="0"/>
+    <filterColumn colId="36" showButton="0"/>
+    <filterColumn colId="38" showButton="0"/>
+    <filterColumn colId="40" showButton="0"/>
+    <filterColumn colId="42" showButton="0"/>
+    <filterColumn colId="44" showButton="0"/>
+    <filterColumn colId="46" showButton="0"/>
+  </autoFilter>
   <mergeCells count="70">
+    <mergeCell ref="A64:AV64"/>
+    <mergeCell ref="A178:AV178"/>
+    <mergeCell ref="A82:AV82"/>
+    <mergeCell ref="A4:AV4"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
+    <mergeCell ref="A3:AV3"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A51:AV51"/>
+    <mergeCell ref="A58:AV58"/>
+    <mergeCell ref="A7:AV7"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A191:AV191"/>
+    <mergeCell ref="A145:AV145"/>
+    <mergeCell ref="A163:AV163"/>
+    <mergeCell ref="A173:AV173"/>
+    <mergeCell ref="A114:AV114"/>
+    <mergeCell ref="A186:AV186"/>
+    <mergeCell ref="A167:AV167"/>
+    <mergeCell ref="A157:AV157"/>
+    <mergeCell ref="A181:AV181"/>
+    <mergeCell ref="A126:AV126"/>
+    <mergeCell ref="A140:AV140"/>
+    <mergeCell ref="A131:AV131"/>
+    <mergeCell ref="A190:AV190"/>
+    <mergeCell ref="A185:AV185"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A170:AV170"/>
+    <mergeCell ref="A46:AV46"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A33:AV33"/>
+    <mergeCell ref="A15:AV15"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="A40:AV40"/>
+    <mergeCell ref="A28:AV28"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A11:AV11"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A22:AV22"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A70:AV70"/>
@@ -23770,60 +23849,6 @@
     <mergeCell ref="A98:AV98"/>
     <mergeCell ref="A121:AV121"/>
     <mergeCell ref="A135:AV135"/>
-    <mergeCell ref="A11:AV11"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A185:AV185"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A170:AV170"/>
-    <mergeCell ref="A46:AV46"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A33:AV33"/>
-    <mergeCell ref="A15:AV15"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="A40:AV40"/>
-    <mergeCell ref="A28:AV28"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="A58:AV58"/>
-    <mergeCell ref="A7:AV7"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="A191:AV191"/>
-    <mergeCell ref="A145:AV145"/>
-    <mergeCell ref="A163:AV163"/>
-    <mergeCell ref="A173:AV173"/>
-    <mergeCell ref="A114:AV114"/>
-    <mergeCell ref="A186:AV186"/>
-    <mergeCell ref="A167:AV167"/>
-    <mergeCell ref="A157:AV157"/>
-    <mergeCell ref="A181:AV181"/>
-    <mergeCell ref="A126:AV126"/>
-    <mergeCell ref="A140:AV140"/>
-    <mergeCell ref="A131:AV131"/>
-    <mergeCell ref="A190:AV190"/>
-    <mergeCell ref="A64:AV64"/>
-    <mergeCell ref="A178:AV178"/>
-    <mergeCell ref="A82:AV82"/>
-    <mergeCell ref="A4:AV4"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AM1:AN1"/>
-    <mergeCell ref="A3:AV3"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A51:AV51"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23833,171 +23858,171 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AU17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="75.28515625" customWidth="1"/>
+    <col min="2" max="2" width="75.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="21" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="21" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="21" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="21" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="21" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="21" customWidth="1"/>
-    <col min="25" max="25" width="10.5703125" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="21" customWidth="1"/>
-    <col min="27" max="27" width="10.5703125" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="21" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="21" customWidth="1"/>
-    <col min="31" max="31" width="10.5703125" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="21" customWidth="1"/>
-    <col min="33" max="33" width="10.5703125" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="21" customWidth="1"/>
-    <col min="35" max="35" width="10.5703125" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="21" customWidth="1"/>
-    <col min="37" max="37" width="10.5703125" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="21" customWidth="1"/>
-    <col min="39" max="39" width="10.5703125" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="21" customWidth="1"/>
-    <col min="41" max="41" width="10.5703125" customWidth="1"/>
-    <col min="42" max="42" width="12.5703125" customWidth="1"/>
-    <col min="43" max="43" width="10.5703125" customWidth="1"/>
-    <col min="44" max="44" width="12.5703125" style="21" customWidth="1"/>
-    <col min="45" max="45" width="10.5703125" customWidth="1"/>
-    <col min="46" max="46" width="12.5703125" style="21" customWidth="1"/>
-    <col min="47" max="47" width="10.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" style="21" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="12.5546875" style="21" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" style="21" customWidth="1"/>
+    <col min="19" max="19" width="10.5546875" customWidth="1"/>
+    <col min="20" max="20" width="12.5546875" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" customWidth="1"/>
+    <col min="22" max="22" width="12.5546875" style="21" customWidth="1"/>
+    <col min="23" max="23" width="10.5546875" customWidth="1"/>
+    <col min="24" max="24" width="12.5546875" style="21" customWidth="1"/>
+    <col min="25" max="25" width="10.5546875" customWidth="1"/>
+    <col min="26" max="26" width="12.5546875" style="21" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" customWidth="1"/>
+    <col min="28" max="28" width="12.5546875" style="21" customWidth="1"/>
+    <col min="29" max="29" width="10.5546875" customWidth="1"/>
+    <col min="30" max="30" width="12.5546875" style="21" customWidth="1"/>
+    <col min="31" max="31" width="10.5546875" customWidth="1"/>
+    <col min="32" max="32" width="12.5546875" style="21" customWidth="1"/>
+    <col min="33" max="33" width="10.5546875" customWidth="1"/>
+    <col min="34" max="34" width="12.5546875" style="21" customWidth="1"/>
+    <col min="35" max="35" width="10.5546875" customWidth="1"/>
+    <col min="36" max="36" width="12.5546875" style="21" customWidth="1"/>
+    <col min="37" max="37" width="10.5546875" customWidth="1"/>
+    <col min="38" max="38" width="12.5546875" style="21" customWidth="1"/>
+    <col min="39" max="39" width="10.5546875" customWidth="1"/>
+    <col min="40" max="40" width="12.5546875" style="21" customWidth="1"/>
+    <col min="41" max="41" width="10.5546875" customWidth="1"/>
+    <col min="42" max="42" width="12.5546875" customWidth="1"/>
+    <col min="43" max="43" width="10.5546875" customWidth="1"/>
+    <col min="44" max="44" width="12.5546875" style="21" customWidth="1"/>
+    <col min="45" max="45" width="10.5546875" customWidth="1"/>
+    <col min="46" max="46" width="12.5546875" style="21" customWidth="1"/>
+    <col min="47" max="47" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="60" t="str">
+      <c r="D1" s="59" t="str">
         <f>Wedstrijden_beheer!E1</f>
         <v>Roland</v>
       </c>
-      <c r="E1" s="61"/>
-      <c r="F1" s="59" t="str">
+      <c r="E1" s="60"/>
+      <c r="F1" s="61" t="str">
         <f>Wedstrijden_beheer!G1</f>
         <v>Nikki</v>
       </c>
-      <c r="G1" s="47"/>
-      <c r="H1" s="59" t="str">
+      <c r="G1" s="43"/>
+      <c r="H1" s="61" t="str">
         <f>Wedstrijden_beheer!I1</f>
         <v>Abdussamed</v>
       </c>
-      <c r="I1" s="47"/>
-      <c r="J1" s="59" t="str">
+      <c r="I1" s="43"/>
+      <c r="J1" s="61" t="str">
         <f>Wedstrijden_beheer!K1</f>
         <v>Karsten</v>
       </c>
-      <c r="K1" s="47"/>
-      <c r="L1" s="59" t="str">
+      <c r="K1" s="43"/>
+      <c r="L1" s="61" t="str">
         <f>Wedstrijden_beheer!M1</f>
         <v>Bas</v>
       </c>
-      <c r="M1" s="47"/>
-      <c r="N1" s="59" t="str">
+      <c r="M1" s="43"/>
+      <c r="N1" s="61" t="str">
         <f>Wedstrijden_beheer!O1</f>
         <v>Maik</v>
       </c>
-      <c r="O1" s="47"/>
-      <c r="P1" s="59" t="str">
+      <c r="O1" s="43"/>
+      <c r="P1" s="61" t="str">
         <f>Wedstrijden_beheer!Q1</f>
         <v>Simone</v>
       </c>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="59" t="str">
+      <c r="Q1" s="43"/>
+      <c r="R1" s="61" t="str">
         <f>Wedstrijden_beheer!S1</f>
         <v>Marc</v>
       </c>
-      <c r="S1" s="47"/>
-      <c r="T1" s="59" t="str">
+      <c r="S1" s="43"/>
+      <c r="T1" s="61" t="str">
         <f>Wedstrijden_beheer!U1</f>
         <v>Tom</v>
       </c>
-      <c r="U1" s="47"/>
-      <c r="V1" s="59" t="str">
+      <c r="U1" s="43"/>
+      <c r="V1" s="61" t="str">
         <f>Wedstrijden_beheer!W1</f>
         <v>Jos</v>
       </c>
-      <c r="W1" s="47"/>
-      <c r="X1" s="59" t="str">
+      <c r="W1" s="43"/>
+      <c r="X1" s="61" t="str">
         <f>Wedstrijden_beheer!Y1</f>
         <v>Lesley</v>
       </c>
-      <c r="Y1" s="47"/>
-      <c r="Z1" s="59" t="str">
+      <c r="Y1" s="43"/>
+      <c r="Z1" s="61" t="str">
         <f>Wedstrijden_beheer!AA1</f>
         <v>Ivo</v>
       </c>
-      <c r="AA1" s="47"/>
-      <c r="AB1" s="59" t="str">
+      <c r="AA1" s="43"/>
+      <c r="AB1" s="61" t="str">
         <f>Wedstrijden_beheer!AC1</f>
         <v>Ron</v>
       </c>
-      <c r="AC1" s="47"/>
-      <c r="AD1" s="59" t="str">
+      <c r="AC1" s="43"/>
+      <c r="AD1" s="61" t="str">
         <f>Wedstrijden_beheer!AE1</f>
         <v>Jeroen</v>
       </c>
-      <c r="AE1" s="47"/>
-      <c r="AF1" s="59" t="str">
+      <c r="AE1" s="43"/>
+      <c r="AF1" s="61" t="str">
         <f>Wedstrijden_beheer!AG1</f>
         <v>Erwin</v>
       </c>
-      <c r="AG1" s="47"/>
-      <c r="AH1" s="59" t="str">
+      <c r="AG1" s="43"/>
+      <c r="AH1" s="61" t="str">
         <f>Wedstrijden_beheer!AI1</f>
         <v>Tim</v>
       </c>
-      <c r="AI1" s="47"/>
-      <c r="AJ1" s="59" t="s">
+      <c r="AI1" s="43"/>
+      <c r="AJ1" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="AK1" s="47"/>
-      <c r="AL1" s="59" t="s">
+      <c r="AK1" s="43"/>
+      <c r="AL1" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="AM1" s="47"/>
-      <c r="AN1" s="59" t="str">
+      <c r="AM1" s="43"/>
+      <c r="AN1" s="61" t="str">
         <f>Wedstrijden_beheer!AO1</f>
         <v>Patrick</v>
       </c>
-      <c r="AO1" s="47"/>
-      <c r="AP1" s="59" t="str">
+      <c r="AO1" s="43"/>
+      <c r="AP1" s="61" t="str">
         <f>Wedstrijden_beheer!AQ1</f>
         <v>Jeno</v>
       </c>
-      <c r="AQ1" s="47"/>
-      <c r="AR1" s="46" t="str">
+      <c r="AQ1" s="43"/>
+      <c r="AR1" s="42" t="str">
         <f>Wedstrijden_beheer!AS1</f>
         <v>Andre</v>
       </c>
-      <c r="AS1" s="58"/>
-      <c r="AT1" s="46" t="str">
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="42" t="str">
         <f>Wedstrijden_beheer!AU1</f>
         <v>Raymond</v>
       </c>
-      <c r="AU1" s="58"/>
+      <c r="AU1" s="51"/>
     </row>
-    <row r="2" spans="1:47" s="28" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" s="28" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="34"/>
       <c r="B2" s="35" t="s">
         <v>215</v>
@@ -24138,7 +24163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -24301,7 +24326,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
         <v>2</v>
       </c>
@@ -24464,7 +24489,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>3</v>
       </c>
@@ -24627,7 +24652,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>4</v>
       </c>
@@ -24790,7 +24815,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -24953,7 +24978,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -25116,7 +25141,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -25279,7 +25304,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -25442,7 +25467,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>9</v>
       </c>
@@ -25605,7 +25630,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -25768,7 +25793,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -25931,7 +25956,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -26094,7 +26119,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -26257,7 +26282,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -26420,7 +26445,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11"/>
       <c r="B17" s="14" t="s">
         <v>283</v>
@@ -26539,6 +26564,17 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="AP1:AQ1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AN1:AO1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="J1:K1"/>
@@ -26550,17 +26586,6 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="AR1:AS1"/>
-    <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AP1:AQ1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AN1:AO1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
@@ -26572,16 +26597,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>284</v>
       </c>
@@ -26590,7 +26615,7 @@
       <c r="D1" s="16"/>
       <c r="E1" s="16"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
         <v>285</v>
       </c>
@@ -26607,9 +26632,9 @@
         <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
-        <f>_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
+        <f t="shared" ref="A3:A24" si="0">_xlfn.RANK.EQ(E3,$E$3:$E$90,0)</f>
         <v>1</v>
       </c>
       <c r="B3" s="1" t="str">
@@ -26625,13 +26650,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="11">
-        <f>C3+D3</f>
+        <f t="shared" ref="E3:E24" si="1">C3+D3</f>
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
-        <f>_xlfn.RANK.EQ(E4,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B4" s="1" t="str">
@@ -26647,13 +26672,13 @@
         <v>0</v>
       </c>
       <c r="E4" s="11">
-        <f>C4+D4</f>
+        <f t="shared" si="1"/>
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
-        <f>_xlfn.RANK.EQ(E5,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B5" s="29" t="str">
@@ -26669,13 +26694,13 @@
         <v>0</v>
       </c>
       <c r="E5" s="11">
-        <f>C5+D5</f>
+        <f t="shared" si="1"/>
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
-        <f>_xlfn.RANK.EQ(E6,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="1" t="str">
@@ -26691,13 +26716,13 @@
         <v>0</v>
       </c>
       <c r="E6" s="11">
-        <f>C6+D6</f>
+        <f t="shared" si="1"/>
         <v>229</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
-        <f>_xlfn.RANK.EQ(E7,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B7" s="1" t="str">
@@ -26713,13 +26738,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>C7+D7</f>
+        <f t="shared" si="1"/>
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
-        <f>_xlfn.RANK.EQ(E8,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B8" s="1" t="str">
@@ -26735,13 +26760,13 @@
         <v>0</v>
       </c>
       <c r="E8" s="11">
-        <f>C8+D8</f>
+        <f t="shared" si="1"/>
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
-        <f>_xlfn.RANK.EQ(E9,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B9" s="1" t="str">
@@ -26757,13 +26782,13 @@
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>C9+D9</f>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
-        <f>_xlfn.RANK.EQ(E10,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B10" s="1" t="str">
@@ -26779,13 +26804,13 @@
         <v>0</v>
       </c>
       <c r="E10" s="11">
-        <f>C10+D10</f>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
-        <f>_xlfn.RANK.EQ(E11,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B11" s="1" t="str">
@@ -26801,13 +26826,13 @@
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <f>C11+D11</f>
+        <f t="shared" si="1"/>
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
-        <f>_xlfn.RANK.EQ(E12,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B12" s="1" t="str">
@@ -26823,13 +26848,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="11">
-        <f>C12+D12</f>
+        <f t="shared" si="1"/>
         <v>223</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
-        <f>_xlfn.RANK.EQ(E13,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B13" s="1" t="str">
@@ -26845,13 +26870,13 @@
         <v>0</v>
       </c>
       <c r="E13" s="11">
-        <f>C13+D13</f>
+        <f t="shared" si="1"/>
         <v>219</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
-        <f>_xlfn.RANK.EQ(E14,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B14" s="1" t="str">
@@ -26867,13 +26892,13 @@
         <v>0</v>
       </c>
       <c r="E14" s="11">
-        <f>C14+D14</f>
+        <f t="shared" si="1"/>
         <v>210</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
-        <f>_xlfn.RANK.EQ(E15,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B15" s="1" t="str">
@@ -26889,13 +26914,13 @@
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>C15+D15</f>
+        <f t="shared" si="1"/>
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
-        <f>_xlfn.RANK.EQ(E16,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B16" s="1" t="str">
@@ -26911,13 +26936,13 @@
         <v>0</v>
       </c>
       <c r="E16" s="11">
-        <f>C16+D16</f>
+        <f t="shared" si="1"/>
         <v>204</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
-        <f>_xlfn.RANK.EQ(E17,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B17" s="1" t="str">
@@ -26933,13 +26958,13 @@
         <v>0</v>
       </c>
       <c r="E17" s="11">
-        <f>C17+D17</f>
+        <f t="shared" si="1"/>
         <v>204</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
-        <f>_xlfn.RANK.EQ(E18,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B18" s="1" t="str">
@@ -26955,13 +26980,13 @@
         <v>0</v>
       </c>
       <c r="E18" s="11">
-        <f>C18+D18</f>
+        <f t="shared" si="1"/>
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
-        <f>_xlfn.RANK.EQ(E19,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B19" s="1" t="str">
@@ -26977,13 +27002,13 @@
         <v>0</v>
       </c>
       <c r="E19" s="11">
-        <f>C19+D19</f>
+        <f t="shared" si="1"/>
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
-        <f>_xlfn.RANK.EQ(E20,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B20" s="1" t="str">
@@ -26999,13 +27024,13 @@
         <v>0</v>
       </c>
       <c r="E20" s="11">
-        <f>C20+D20</f>
+        <f t="shared" si="1"/>
         <v>182</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11">
-        <f>_xlfn.RANK.EQ(E21,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B21" s="1" t="str">
@@ -27021,13 +27046,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="11">
-        <f>C21+D21</f>
+        <f t="shared" si="1"/>
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
-        <f>_xlfn.RANK.EQ(E22,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B22" s="1" t="str">
@@ -27043,13 +27068,13 @@
         <v>0</v>
       </c>
       <c r="E22" s="11">
-        <f>C22+D22</f>
+        <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
-        <f>_xlfn.RANK.EQ(E23,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B23" s="1" t="str">
@@ -27065,13 +27090,13 @@
         <v>0</v>
       </c>
       <c r="E23" s="11">
-        <f>C23+D23</f>
+        <f t="shared" si="1"/>
         <v>172</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
-        <f>_xlfn.RANK.EQ(E24,$E$3:$E$90,0)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B24" s="1" t="str">
@@ -27087,7 +27112,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="11">
-        <f>C24+D24</f>
+        <f t="shared" si="1"/>
         <v>160</v>
       </c>
     </row>
@@ -27108,20 +27133,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="1" max="1" width="29.5546875" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="16384" width="8.7109375" hidden="1"/>
+    <col min="3" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>290</v>
       </c>
       <c r="B1" s="16"/>
     </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
@@ -27129,7 +27154,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>293</v>
       </c>
@@ -27137,7 +27162,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>295</v>
       </c>
@@ -27145,7 +27170,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>296</v>
       </c>
@@ -27153,7 +27178,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>298</v>
       </c>
@@ -27161,7 +27186,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>300</v>
       </c>
@@ -27169,7 +27194,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>302</v>
       </c>
@@ -27177,7 +27202,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>304</v>
       </c>
@@ -27193,16 +27218,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AR8"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="55.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
     <col min="4" max="44" width="0" hidden="1" customWidth="1"/>
-    <col min="45" max="16384" width="8.7109375" hidden="1"/>
+    <col min="45" max="16384" width="8.6640625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>306</v>
       </c>
@@ -27250,7 +27275,7 @@
       <c r="AQ1" s="6"/>
       <c r="AR1" s="3"/>
     </row>
-    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
         <v>291</v>
       </c>
@@ -27261,7 +27286,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>308</v>
       </c>
@@ -27272,7 +27297,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>310</v>
       </c>
@@ -27283,7 +27308,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>312</v>
       </c>
@@ -27294,7 +27319,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>314</v>
       </c>
@@ -27305,7 +27330,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>316</v>
       </c>
@@ -27316,7 +27341,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>318</v>
       </c>
@@ -27333,14 +27358,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB261A6-3B9F-400D-BBAF-4858A45169E1}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>319</v>
       </c>
@@ -27351,7 +27376,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>322</v>
       </c>
@@ -27362,7 +27387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>23</v>
       </c>
@@ -27370,7 +27395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>24</v>
       </c>
@@ -27378,7 +27403,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>323</v>
       </c>
@@ -27386,7 +27411,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -27394,62 +27419,62 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="30" t="s">
         <v>4</v>
       </c>
@@ -27460,12 +27485,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27664,20 +27691,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7c2036e6-2c6c-4cc0-93d3-66cc911cb074">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7b90d758-d430-4ffd-9227-0f539ac48821" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -27702,18 +27736,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5367818C-8D56-468A-9A53-C7AB90E97273}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF6CA4E-A4E7-4BEF-969F-6D691108D84C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="7b90d758-d430-4ffd-9227-0f539ac48821"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="7c2036e6-2c6c-4cc0-93d3-66cc911cb074"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/WK2026_poule_beheer.xlsx
+++ b/WK2026_poule_beheer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bismart-my.sharepoint.com/personal/r_meijer_bi-smart_nl/Documents/Documenten/WK 2026/Github/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1603" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{005805BF-B461-4B16-850C-BDF6888E3F73}"/>
+  <xr:revisionPtr revIDLastSave="1610" documentId="8_{E82BF418-5EC5-4A9D-9227-B9F99AE92E74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90BED3F-2ABC-4DDC-AEF7-B713E12B1144}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wedstrijden_beheer" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2358" uniqueCount="330">
   <si>
     <t>Tijd</t>
   </si>
@@ -1377,6 +1377,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1386,23 +1392,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1410,22 +1416,16 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -1790,106 +1790,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52" t="s">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="52" t="s">
+      <c r="C1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="55"/>
-      <c r="G1" s="42" t="s">
+      <c r="F1" s="57"/>
+      <c r="G1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="43"/>
-      <c r="I1" s="42" t="s">
+      <c r="H1" s="47"/>
+      <c r="I1" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="43"/>
-      <c r="K1" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="42" t="s">
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="47"/>
+      <c r="M1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="43"/>
-      <c r="O1" s="42" t="s">
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="42" t="s">
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="43"/>
-      <c r="S1" s="42" t="s">
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="43"/>
-      <c r="U1" s="42" t="s">
+      <c r="T1" s="47"/>
+      <c r="U1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="43"/>
-      <c r="W1" s="42" t="s">
+      <c r="V1" s="47"/>
+      <c r="W1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="42" t="s">
+      <c r="X1" s="47"/>
+      <c r="Y1" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="42" t="s">
+      <c r="Z1" s="47"/>
+      <c r="AA1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="43"/>
-      <c r="AC1" s="42" t="s">
+      <c r="AB1" s="47"/>
+      <c r="AC1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AD1" s="43"/>
-      <c r="AE1" s="42" t="s">
+      <c r="AD1" s="47"/>
+      <c r="AE1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="AF1" s="43"/>
-      <c r="AG1" s="42" t="s">
+      <c r="AF1" s="47"/>
+      <c r="AG1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="AH1" s="43"/>
-      <c r="AI1" s="42" t="s">
+      <c r="AH1" s="47"/>
+      <c r="AI1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="AJ1" s="43"/>
-      <c r="AK1" s="42" t="s">
+      <c r="AJ1" s="47"/>
+      <c r="AK1" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AL1" s="43"/>
-      <c r="AM1" s="42" t="s">
+      <c r="AL1" s="47"/>
+      <c r="AM1" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="43"/>
-      <c r="AO1" s="42" t="s">
+      <c r="AN1" s="47"/>
+      <c r="AO1" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="AP1" s="43"/>
-      <c r="AQ1" s="42" t="s">
+      <c r="AP1" s="47"/>
+      <c r="AQ1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="AR1" s="43"/>
-      <c r="AS1" s="42" t="s">
+      <c r="AR1" s="47"/>
+      <c r="AS1" s="46" t="s">
         <v>324</v>
       </c>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="42" t="s">
+      <c r="AT1" s="58"/>
+      <c r="AU1" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="AV1" s="51"/>
+      <c r="AV1" s="58"/>
       <c r="AW1" s="2" t="s">
         <v>25</v>
       </c>
@@ -1898,10 +1898,10 @@
       </c>
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="56"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="23" t="s">
         <v>27</v>
       </c>
@@ -2045,107 +2045,107 @@
       <c r="A3" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="57"/>
-      <c r="AS3" s="57"/>
-      <c r="AT3" s="57"/>
-      <c r="AU3" s="57"/>
-      <c r="AV3" s="58"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="49"/>
+      <c r="AM3" s="49"/>
+      <c r="AN3" s="49"/>
+      <c r="AO3" s="49"/>
+      <c r="AP3" s="49"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="50"/>
       <c r="AW3" s="7"/>
       <c r="AX3" s="7"/>
     </row>
     <row r="4" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-      <c r="U4" s="40"/>
-      <c r="V4" s="40"/>
-      <c r="W4" s="40"/>
-      <c r="X4" s="40"/>
-      <c r="Y4" s="40"/>
-      <c r="Z4" s="40"/>
-      <c r="AA4" s="40"/>
-      <c r="AB4" s="40"/>
-      <c r="AC4" s="40"/>
-      <c r="AD4" s="40"/>
-      <c r="AE4" s="40"/>
-      <c r="AF4" s="40"/>
-      <c r="AG4" s="40"/>
-      <c r="AH4" s="40"/>
-      <c r="AI4" s="40"/>
-      <c r="AJ4" s="40"/>
-      <c r="AK4" s="40"/>
-      <c r="AL4" s="40"/>
-      <c r="AM4" s="40"/>
-      <c r="AN4" s="40"/>
-      <c r="AO4" s="40"/>
-      <c r="AP4" s="40"/>
-      <c r="AQ4" s="40"/>
-      <c r="AR4" s="40"/>
-      <c r="AS4" s="40"/>
-      <c r="AT4" s="40"/>
-      <c r="AU4" s="40"/>
-      <c r="AV4" s="41"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AM4" s="44"/>
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="44"/>
+      <c r="AS4" s="44"/>
+      <c r="AT4" s="44"/>
+      <c r="AU4" s="44"/>
+      <c r="AV4" s="45"/>
       <c r="AW4" s="8"/>
       <c r="AX4" s="8"/>
     </row>
@@ -2384,56 +2384,56 @@
       <c r="AX6" s="12"/>
     </row>
     <row r="7" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+      <c r="A7" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="40"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="40"/>
-      <c r="W7" s="40"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="40"/>
-      <c r="Z7" s="40"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="40"/>
-      <c r="AC7" s="40"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="40"/>
-      <c r="AF7" s="40"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="40"/>
-      <c r="AI7" s="40"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="40"/>
-      <c r="AL7" s="40"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="40"/>
-      <c r="AO7" s="40"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="40"/>
-      <c r="AR7" s="40"/>
-      <c r="AS7" s="40"/>
-      <c r="AT7" s="40"/>
-      <c r="AU7" s="40"/>
-      <c r="AV7" s="41"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="44"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="44"/>
+      <c r="V7" s="44"/>
+      <c r="W7" s="44"/>
+      <c r="X7" s="44"/>
+      <c r="Y7" s="44"/>
+      <c r="Z7" s="44"/>
+      <c r="AA7" s="44"/>
+      <c r="AB7" s="44"/>
+      <c r="AC7" s="44"/>
+      <c r="AD7" s="44"/>
+      <c r="AE7" s="44"/>
+      <c r="AF7" s="44"/>
+      <c r="AG7" s="44"/>
+      <c r="AH7" s="44"/>
+      <c r="AI7" s="44"/>
+      <c r="AJ7" s="44"/>
+      <c r="AK7" s="44"/>
+      <c r="AL7" s="44"/>
+      <c r="AM7" s="44"/>
+      <c r="AN7" s="44"/>
+      <c r="AO7" s="44"/>
+      <c r="AP7" s="44"/>
+      <c r="AQ7" s="44"/>
+      <c r="AR7" s="44"/>
+      <c r="AS7" s="44"/>
+      <c r="AT7" s="44"/>
+      <c r="AU7" s="44"/>
+      <c r="AV7" s="45"/>
       <c r="AW7" s="8"/>
       <c r="AX7" s="8"/>
     </row>
@@ -2848,56 +2848,56 @@
       <c r="AX10" s="12"/>
     </row>
     <row r="11" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="40"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="40"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="40"/>
-      <c r="W11" s="40"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="40"/>
-      <c r="Z11" s="40"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="40"/>
-      <c r="AC11" s="40"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="40"/>
-      <c r="AF11" s="40"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="40"/>
-      <c r="AI11" s="40"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="40"/>
-      <c r="AL11" s="40"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="40"/>
-      <c r="AO11" s="40"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="40"/>
-      <c r="AR11" s="40"/>
-      <c r="AS11" s="40"/>
-      <c r="AT11" s="40"/>
-      <c r="AU11" s="40"/>
-      <c r="AV11" s="41"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="44"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
+      <c r="AB11" s="44"/>
+      <c r="AC11" s="44"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="44"/>
+      <c r="AF11" s="44"/>
+      <c r="AG11" s="44"/>
+      <c r="AH11" s="44"/>
+      <c r="AI11" s="44"/>
+      <c r="AJ11" s="44"/>
+      <c r="AK11" s="44"/>
+      <c r="AL11" s="44"/>
+      <c r="AM11" s="44"/>
+      <c r="AN11" s="44"/>
+      <c r="AO11" s="44"/>
+      <c r="AP11" s="44"/>
+      <c r="AQ11" s="44"/>
+      <c r="AR11" s="44"/>
+      <c r="AS11" s="44"/>
+      <c r="AT11" s="44"/>
+      <c r="AU11" s="44"/>
+      <c r="AV11" s="45"/>
       <c r="AW11" s="8"/>
       <c r="AX11" s="8"/>
     </row>
@@ -3312,56 +3312,56 @@
       <c r="AX14" s="12"/>
     </row>
     <row r="15" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="40"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="40"/>
-      <c r="U15" s="40"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="40"/>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="40"/>
-      <c r="Z15" s="40"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="40"/>
-      <c r="AC15" s="40"/>
-      <c r="AD15" s="40"/>
-      <c r="AE15" s="40"/>
-      <c r="AF15" s="40"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="40"/>
-      <c r="AK15" s="40"/>
-      <c r="AL15" s="40"/>
-      <c r="AM15" s="40"/>
-      <c r="AN15" s="40"/>
-      <c r="AO15" s="40"/>
-      <c r="AP15" s="40"/>
-      <c r="AQ15" s="40"/>
-      <c r="AR15" s="40"/>
-      <c r="AS15" s="40"/>
-      <c r="AT15" s="40"/>
-      <c r="AU15" s="40"/>
-      <c r="AV15" s="41"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="44"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="44"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
+      <c r="Z15" s="44"/>
+      <c r="AA15" s="44"/>
+      <c r="AB15" s="44"/>
+      <c r="AC15" s="44"/>
+      <c r="AD15" s="44"/>
+      <c r="AE15" s="44"/>
+      <c r="AF15" s="44"/>
+      <c r="AG15" s="44"/>
+      <c r="AH15" s="44"/>
+      <c r="AI15" s="44"/>
+      <c r="AJ15" s="44"/>
+      <c r="AK15" s="44"/>
+      <c r="AL15" s="44"/>
+      <c r="AM15" s="44"/>
+      <c r="AN15" s="44"/>
+      <c r="AO15" s="44"/>
+      <c r="AP15" s="44"/>
+      <c r="AQ15" s="44"/>
+      <c r="AR15" s="44"/>
+      <c r="AS15" s="44"/>
+      <c r="AT15" s="44"/>
+      <c r="AU15" s="44"/>
+      <c r="AV15" s="45"/>
       <c r="AW15" s="8"/>
       <c r="AX15" s="8"/>
     </row>
@@ -4304,56 +4304,56 @@
       <c r="AX21" s="12"/>
     </row>
     <row r="22" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="39" t="s">
+      <c r="A22" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="40"/>
-      <c r="T22" s="40"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="40"/>
-      <c r="W22" s="40"/>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="40"/>
-      <c r="Z22" s="40"/>
-      <c r="AA22" s="40"/>
-      <c r="AB22" s="40"/>
-      <c r="AC22" s="40"/>
-      <c r="AD22" s="40"/>
-      <c r="AE22" s="40"/>
-      <c r="AF22" s="40"/>
-      <c r="AG22" s="40"/>
-      <c r="AH22" s="40"/>
-      <c r="AI22" s="40"/>
-      <c r="AJ22" s="40"/>
-      <c r="AK22" s="40"/>
-      <c r="AL22" s="40"/>
-      <c r="AM22" s="40"/>
-      <c r="AN22" s="40"/>
-      <c r="AO22" s="40"/>
-      <c r="AP22" s="40"/>
-      <c r="AQ22" s="40"/>
-      <c r="AR22" s="40"/>
-      <c r="AS22" s="40"/>
-      <c r="AT22" s="40"/>
-      <c r="AU22" s="40"/>
-      <c r="AV22" s="41"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="44"/>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="44"/>
+      <c r="P22" s="44"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+      <c r="U22" s="44"/>
+      <c r="V22" s="44"/>
+      <c r="W22" s="44"/>
+      <c r="X22" s="44"/>
+      <c r="Y22" s="44"/>
+      <c r="Z22" s="44"/>
+      <c r="AA22" s="44"/>
+      <c r="AB22" s="44"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="44"/>
+      <c r="AE22" s="44"/>
+      <c r="AF22" s="44"/>
+      <c r="AG22" s="44"/>
+      <c r="AH22" s="44"/>
+      <c r="AI22" s="44"/>
+      <c r="AJ22" s="44"/>
+      <c r="AK22" s="44"/>
+      <c r="AL22" s="44"/>
+      <c r="AM22" s="44"/>
+      <c r="AN22" s="44"/>
+      <c r="AO22" s="44"/>
+      <c r="AP22" s="44"/>
+      <c r="AQ22" s="44"/>
+      <c r="AR22" s="44"/>
+      <c r="AS22" s="44"/>
+      <c r="AT22" s="44"/>
+      <c r="AU22" s="44"/>
+      <c r="AV22" s="45"/>
       <c r="AW22" s="8"/>
       <c r="AX22" s="8"/>
     </row>
@@ -5120,56 +5120,56 @@
       <c r="AX27" s="12"/>
     </row>
     <row r="28" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="45"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="45"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="45"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="45"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="45"/>
-      <c r="AA28" s="46"/>
-      <c r="AB28" s="45"/>
-      <c r="AC28" s="46"/>
-      <c r="AD28" s="45"/>
-      <c r="AE28" s="46"/>
-      <c r="AF28" s="45"/>
-      <c r="AG28" s="46"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="46"/>
-      <c r="AJ28" s="45"/>
-      <c r="AK28" s="46"/>
-      <c r="AL28" s="45"/>
-      <c r="AM28" s="46"/>
-      <c r="AN28" s="45"/>
-      <c r="AO28" s="46"/>
-      <c r="AP28" s="45"/>
-      <c r="AQ28" s="45"/>
-      <c r="AR28" s="45"/>
-      <c r="AS28" s="45"/>
-      <c r="AT28" s="45"/>
-      <c r="AU28" s="46"/>
-      <c r="AV28" s="47"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="40"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="40"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="40"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="40"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="40"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="40"/>
+      <c r="W28" s="41"/>
+      <c r="X28" s="40"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="40"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="40"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="40"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="40"/>
+      <c r="AG28" s="41"/>
+      <c r="AH28" s="40"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="40"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="40"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="40"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="40"/>
+      <c r="AQ28" s="40"/>
+      <c r="AR28" s="40"/>
+      <c r="AS28" s="40"/>
+      <c r="AT28" s="40"/>
+      <c r="AU28" s="41"/>
+      <c r="AV28" s="42"/>
       <c r="AW28" s="8"/>
       <c r="AX28" s="8"/>
     </row>
@@ -5760,56 +5760,56 @@
       <c r="AX32" s="12"/>
     </row>
     <row r="33" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="46"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="45"/>
-      <c r="O33" s="46"/>
-      <c r="P33" s="45"/>
-      <c r="Q33" s="46"/>
-      <c r="R33" s="45"/>
-      <c r="S33" s="46"/>
-      <c r="T33" s="45"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="45"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="45"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="45"/>
-      <c r="AA33" s="46"/>
-      <c r="AB33" s="45"/>
-      <c r="AC33" s="46"/>
-      <c r="AD33" s="45"/>
-      <c r="AE33" s="46"/>
-      <c r="AF33" s="45"/>
-      <c r="AG33" s="46"/>
-      <c r="AH33" s="45"/>
-      <c r="AI33" s="46"/>
-      <c r="AJ33" s="45"/>
-      <c r="AK33" s="46"/>
-      <c r="AL33" s="45"/>
-      <c r="AM33" s="46"/>
-      <c r="AN33" s="45"/>
-      <c r="AO33" s="46"/>
-      <c r="AP33" s="45"/>
-      <c r="AQ33" s="45"/>
-      <c r="AR33" s="45"/>
-      <c r="AS33" s="45"/>
-      <c r="AT33" s="45"/>
-      <c r="AU33" s="46"/>
-      <c r="AV33" s="47"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="40"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="40"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="40"/>
+      <c r="M33" s="41"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="41"/>
+      <c r="P33" s="40"/>
+      <c r="Q33" s="41"/>
+      <c r="R33" s="40"/>
+      <c r="S33" s="41"/>
+      <c r="T33" s="40"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="40"/>
+      <c r="W33" s="41"/>
+      <c r="X33" s="40"/>
+      <c r="Y33" s="41"/>
+      <c r="Z33" s="40"/>
+      <c r="AA33" s="41"/>
+      <c r="AB33" s="40"/>
+      <c r="AC33" s="41"/>
+      <c r="AD33" s="40"/>
+      <c r="AE33" s="41"/>
+      <c r="AF33" s="40"/>
+      <c r="AG33" s="41"/>
+      <c r="AH33" s="40"/>
+      <c r="AI33" s="41"/>
+      <c r="AJ33" s="40"/>
+      <c r="AK33" s="41"/>
+      <c r="AL33" s="40"/>
+      <c r="AM33" s="41"/>
+      <c r="AN33" s="40"/>
+      <c r="AO33" s="41"/>
+      <c r="AP33" s="40"/>
+      <c r="AQ33" s="40"/>
+      <c r="AR33" s="40"/>
+      <c r="AS33" s="40"/>
+      <c r="AT33" s="40"/>
+      <c r="AU33" s="41"/>
+      <c r="AV33" s="42"/>
       <c r="AW33" s="8"/>
       <c r="AX33" s="8"/>
     </row>
@@ -6752,56 +6752,56 @@
       <c r="AX39" s="12"/>
     </row>
     <row r="40" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="44" t="s">
+      <c r="A40" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B40" s="45"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="45"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="45"/>
-      <c r="S40" s="46"/>
-      <c r="T40" s="45"/>
-      <c r="U40" s="46"/>
-      <c r="V40" s="45"/>
-      <c r="W40" s="46"/>
-      <c r="X40" s="45"/>
-      <c r="Y40" s="46"/>
-      <c r="Z40" s="45"/>
-      <c r="AA40" s="46"/>
-      <c r="AB40" s="45"/>
-      <c r="AC40" s="46"/>
-      <c r="AD40" s="45"/>
-      <c r="AE40" s="46"/>
-      <c r="AF40" s="45"/>
-      <c r="AG40" s="46"/>
-      <c r="AH40" s="45"/>
-      <c r="AI40" s="46"/>
-      <c r="AJ40" s="45"/>
-      <c r="AK40" s="46"/>
-      <c r="AL40" s="45"/>
-      <c r="AM40" s="46"/>
-      <c r="AN40" s="45"/>
-      <c r="AO40" s="46"/>
-      <c r="AP40" s="45"/>
-      <c r="AQ40" s="45"/>
-      <c r="AR40" s="45"/>
-      <c r="AS40" s="45"/>
-      <c r="AT40" s="45"/>
-      <c r="AU40" s="46"/>
-      <c r="AV40" s="47"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="41"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="41"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="41"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="41"/>
+      <c r="N40" s="40"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="40"/>
+      <c r="Q40" s="41"/>
+      <c r="R40" s="40"/>
+      <c r="S40" s="41"/>
+      <c r="T40" s="40"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="40"/>
+      <c r="W40" s="41"/>
+      <c r="X40" s="40"/>
+      <c r="Y40" s="41"/>
+      <c r="Z40" s="40"/>
+      <c r="AA40" s="41"/>
+      <c r="AB40" s="40"/>
+      <c r="AC40" s="41"/>
+      <c r="AD40" s="40"/>
+      <c r="AE40" s="41"/>
+      <c r="AF40" s="40"/>
+      <c r="AG40" s="41"/>
+      <c r="AH40" s="40"/>
+      <c r="AI40" s="41"/>
+      <c r="AJ40" s="40"/>
+      <c r="AK40" s="41"/>
+      <c r="AL40" s="40"/>
+      <c r="AM40" s="41"/>
+      <c r="AN40" s="40"/>
+      <c r="AO40" s="41"/>
+      <c r="AP40" s="40"/>
+      <c r="AQ40" s="40"/>
+      <c r="AR40" s="40"/>
+      <c r="AS40" s="40"/>
+      <c r="AT40" s="40"/>
+      <c r="AU40" s="41"/>
+      <c r="AV40" s="42"/>
       <c r="AW40" s="8"/>
       <c r="AX40" s="8"/>
     </row>
@@ -7568,56 +7568,56 @@
       <c r="AX45" s="12"/>
     </row>
     <row r="46" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="44" t="s">
+      <c r="A46" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="46"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="46"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="45"/>
-      <c r="M46" s="46"/>
-      <c r="N46" s="45"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="45"/>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="45"/>
-      <c r="S46" s="46"/>
-      <c r="T46" s="45"/>
-      <c r="U46" s="46"/>
-      <c r="V46" s="45"/>
-      <c r="W46" s="46"/>
-      <c r="X46" s="45"/>
-      <c r="Y46" s="46"/>
-      <c r="Z46" s="45"/>
-      <c r="AA46" s="46"/>
-      <c r="AB46" s="45"/>
-      <c r="AC46" s="46"/>
-      <c r="AD46" s="45"/>
-      <c r="AE46" s="46"/>
-      <c r="AF46" s="45"/>
-      <c r="AG46" s="46"/>
-      <c r="AH46" s="45"/>
-      <c r="AI46" s="46"/>
-      <c r="AJ46" s="45"/>
-      <c r="AK46" s="46"/>
-      <c r="AL46" s="45"/>
-      <c r="AM46" s="46"/>
-      <c r="AN46" s="45"/>
-      <c r="AO46" s="46"/>
-      <c r="AP46" s="45"/>
-      <c r="AQ46" s="45"/>
-      <c r="AR46" s="45"/>
-      <c r="AS46" s="45"/>
-      <c r="AT46" s="45"/>
-      <c r="AU46" s="46"/>
-      <c r="AV46" s="47"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="41"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="41"/>
+      <c r="L46" s="40"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="41"/>
+      <c r="P46" s="40"/>
+      <c r="Q46" s="41"/>
+      <c r="R46" s="40"/>
+      <c r="S46" s="41"/>
+      <c r="T46" s="40"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="40"/>
+      <c r="W46" s="41"/>
+      <c r="X46" s="40"/>
+      <c r="Y46" s="41"/>
+      <c r="Z46" s="40"/>
+      <c r="AA46" s="41"/>
+      <c r="AB46" s="40"/>
+      <c r="AC46" s="41"/>
+      <c r="AD46" s="40"/>
+      <c r="AE46" s="41"/>
+      <c r="AF46" s="40"/>
+      <c r="AG46" s="41"/>
+      <c r="AH46" s="40"/>
+      <c r="AI46" s="41"/>
+      <c r="AJ46" s="40"/>
+      <c r="AK46" s="41"/>
+      <c r="AL46" s="40"/>
+      <c r="AM46" s="41"/>
+      <c r="AN46" s="40"/>
+      <c r="AO46" s="41"/>
+      <c r="AP46" s="40"/>
+      <c r="AQ46" s="40"/>
+      <c r="AR46" s="40"/>
+      <c r="AS46" s="40"/>
+      <c r="AT46" s="40"/>
+      <c r="AU46" s="41"/>
+      <c r="AV46" s="42"/>
       <c r="AW46" s="8"/>
       <c r="AX46" s="8"/>
     </row>
@@ -8208,56 +8208,56 @@
       <c r="AX50" s="12"/>
     </row>
     <row r="51" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="44" t="s">
+      <c r="A51" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="45"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="45"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="45"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="45"/>
-      <c r="S51" s="46"/>
-      <c r="T51" s="45"/>
-      <c r="U51" s="46"/>
-      <c r="V51" s="45"/>
-      <c r="W51" s="46"/>
-      <c r="X51" s="45"/>
-      <c r="Y51" s="46"/>
-      <c r="Z51" s="45"/>
-      <c r="AA51" s="46"/>
-      <c r="AB51" s="45"/>
-      <c r="AC51" s="46"/>
-      <c r="AD51" s="45"/>
-      <c r="AE51" s="46"/>
-      <c r="AF51" s="45"/>
-      <c r="AG51" s="46"/>
-      <c r="AH51" s="45"/>
-      <c r="AI51" s="46"/>
-      <c r="AJ51" s="45"/>
-      <c r="AK51" s="46"/>
-      <c r="AL51" s="45"/>
-      <c r="AM51" s="46"/>
-      <c r="AN51" s="45"/>
-      <c r="AO51" s="46"/>
-      <c r="AP51" s="45"/>
-      <c r="AQ51" s="45"/>
-      <c r="AR51" s="45"/>
-      <c r="AS51" s="45"/>
-      <c r="AT51" s="45"/>
-      <c r="AU51" s="46"/>
-      <c r="AV51" s="47"/>
+      <c r="B51" s="40"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="41"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="40"/>
+      <c r="Q51" s="41"/>
+      <c r="R51" s="40"/>
+      <c r="S51" s="41"/>
+      <c r="T51" s="40"/>
+      <c r="U51" s="41"/>
+      <c r="V51" s="40"/>
+      <c r="W51" s="41"/>
+      <c r="X51" s="40"/>
+      <c r="Y51" s="41"/>
+      <c r="Z51" s="40"/>
+      <c r="AA51" s="41"/>
+      <c r="AB51" s="40"/>
+      <c r="AC51" s="41"/>
+      <c r="AD51" s="40"/>
+      <c r="AE51" s="41"/>
+      <c r="AF51" s="40"/>
+      <c r="AG51" s="41"/>
+      <c r="AH51" s="40"/>
+      <c r="AI51" s="41"/>
+      <c r="AJ51" s="40"/>
+      <c r="AK51" s="41"/>
+      <c r="AL51" s="40"/>
+      <c r="AM51" s="41"/>
+      <c r="AN51" s="40"/>
+      <c r="AO51" s="41"/>
+      <c r="AP51" s="40"/>
+      <c r="AQ51" s="40"/>
+      <c r="AR51" s="40"/>
+      <c r="AS51" s="40"/>
+      <c r="AT51" s="40"/>
+      <c r="AU51" s="41"/>
+      <c r="AV51" s="42"/>
       <c r="AW51" s="8"/>
       <c r="AX51" s="8"/>
     </row>
@@ -9200,56 +9200,56 @@
       <c r="AX57" s="12"/>
     </row>
     <row r="58" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="44" t="s">
+      <c r="A58" s="39" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="46"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="46"/>
-      <c r="L58" s="45"/>
-      <c r="M58" s="46"/>
-      <c r="N58" s="45"/>
-      <c r="O58" s="46"/>
-      <c r="P58" s="45"/>
-      <c r="Q58" s="46"/>
-      <c r="R58" s="45"/>
-      <c r="S58" s="46"/>
-      <c r="T58" s="45"/>
-      <c r="U58" s="46"/>
-      <c r="V58" s="45"/>
-      <c r="W58" s="46"/>
-      <c r="X58" s="45"/>
-      <c r="Y58" s="46"/>
-      <c r="Z58" s="45"/>
-      <c r="AA58" s="46"/>
-      <c r="AB58" s="45"/>
-      <c r="AC58" s="46"/>
-      <c r="AD58" s="45"/>
-      <c r="AE58" s="46"/>
-      <c r="AF58" s="45"/>
-      <c r="AG58" s="46"/>
-      <c r="AH58" s="45"/>
-      <c r="AI58" s="46"/>
-      <c r="AJ58" s="45"/>
-      <c r="AK58" s="46"/>
-      <c r="AL58" s="45"/>
-      <c r="AM58" s="46"/>
-      <c r="AN58" s="45"/>
-      <c r="AO58" s="46"/>
-      <c r="AP58" s="45"/>
-      <c r="AQ58" s="45"/>
-      <c r="AR58" s="45"/>
-      <c r="AS58" s="45"/>
-      <c r="AT58" s="45"/>
-      <c r="AU58" s="46"/>
-      <c r="AV58" s="47"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="41"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="40"/>
+      <c r="Q58" s="41"/>
+      <c r="R58" s="40"/>
+      <c r="S58" s="41"/>
+      <c r="T58" s="40"/>
+      <c r="U58" s="41"/>
+      <c r="V58" s="40"/>
+      <c r="W58" s="41"/>
+      <c r="X58" s="40"/>
+      <c r="Y58" s="41"/>
+      <c r="Z58" s="40"/>
+      <c r="AA58" s="41"/>
+      <c r="AB58" s="40"/>
+      <c r="AC58" s="41"/>
+      <c r="AD58" s="40"/>
+      <c r="AE58" s="41"/>
+      <c r="AF58" s="40"/>
+      <c r="AG58" s="41"/>
+      <c r="AH58" s="40"/>
+      <c r="AI58" s="41"/>
+      <c r="AJ58" s="40"/>
+      <c r="AK58" s="41"/>
+      <c r="AL58" s="40"/>
+      <c r="AM58" s="41"/>
+      <c r="AN58" s="40"/>
+      <c r="AO58" s="41"/>
+      <c r="AP58" s="40"/>
+      <c r="AQ58" s="40"/>
+      <c r="AR58" s="40"/>
+      <c r="AS58" s="40"/>
+      <c r="AT58" s="40"/>
+      <c r="AU58" s="41"/>
+      <c r="AV58" s="42"/>
       <c r="AW58" s="8"/>
       <c r="AX58" s="8"/>
     </row>
@@ -10016,56 +10016,56 @@
       <c r="AX63" s="12"/>
     </row>
     <row r="64" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="44" t="s">
+      <c r="A64" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="46"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="46"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="46"/>
-      <c r="J64" s="45"/>
-      <c r="K64" s="46"/>
-      <c r="L64" s="45"/>
-      <c r="M64" s="46"/>
-      <c r="N64" s="45"/>
-      <c r="O64" s="46"/>
-      <c r="P64" s="45"/>
-      <c r="Q64" s="46"/>
-      <c r="R64" s="45"/>
-      <c r="S64" s="46"/>
-      <c r="T64" s="45"/>
-      <c r="U64" s="46"/>
-      <c r="V64" s="45"/>
-      <c r="W64" s="46"/>
-      <c r="X64" s="45"/>
-      <c r="Y64" s="46"/>
-      <c r="Z64" s="45"/>
-      <c r="AA64" s="46"/>
-      <c r="AB64" s="45"/>
-      <c r="AC64" s="46"/>
-      <c r="AD64" s="45"/>
-      <c r="AE64" s="46"/>
-      <c r="AF64" s="45"/>
-      <c r="AG64" s="46"/>
-      <c r="AH64" s="45"/>
-      <c r="AI64" s="46"/>
-      <c r="AJ64" s="45"/>
-      <c r="AK64" s="46"/>
-      <c r="AL64" s="45"/>
-      <c r="AM64" s="46"/>
-      <c r="AN64" s="45"/>
-      <c r="AO64" s="46"/>
-      <c r="AP64" s="45"/>
-      <c r="AQ64" s="45"/>
-      <c r="AR64" s="45"/>
-      <c r="AS64" s="45"/>
-      <c r="AT64" s="45"/>
-      <c r="AU64" s="46"/>
-      <c r="AV64" s="47"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="41"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="41"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="41"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="41"/>
+      <c r="L64" s="40"/>
+      <c r="M64" s="41"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="41"/>
+      <c r="R64" s="40"/>
+      <c r="S64" s="41"/>
+      <c r="T64" s="40"/>
+      <c r="U64" s="41"/>
+      <c r="V64" s="40"/>
+      <c r="W64" s="41"/>
+      <c r="X64" s="40"/>
+      <c r="Y64" s="41"/>
+      <c r="Z64" s="40"/>
+      <c r="AA64" s="41"/>
+      <c r="AB64" s="40"/>
+      <c r="AC64" s="41"/>
+      <c r="AD64" s="40"/>
+      <c r="AE64" s="41"/>
+      <c r="AF64" s="40"/>
+      <c r="AG64" s="41"/>
+      <c r="AH64" s="40"/>
+      <c r="AI64" s="41"/>
+      <c r="AJ64" s="40"/>
+      <c r="AK64" s="41"/>
+      <c r="AL64" s="40"/>
+      <c r="AM64" s="41"/>
+      <c r="AN64" s="40"/>
+      <c r="AO64" s="41"/>
+      <c r="AP64" s="40"/>
+      <c r="AQ64" s="40"/>
+      <c r="AR64" s="40"/>
+      <c r="AS64" s="40"/>
+      <c r="AT64" s="40"/>
+      <c r="AU64" s="41"/>
+      <c r="AV64" s="42"/>
       <c r="AW64" s="8"/>
       <c r="AX64" s="8"/>
     </row>
@@ -10832,56 +10832,56 @@
       <c r="AX69" s="12"/>
     </row>
     <row r="70" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="44" t="s">
+      <c r="A70" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="B70" s="45"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="46"/>
-      <c r="J70" s="45"/>
-      <c r="K70" s="46"/>
-      <c r="L70" s="45"/>
-      <c r="M70" s="46"/>
-      <c r="N70" s="45"/>
-      <c r="O70" s="46"/>
-      <c r="P70" s="45"/>
-      <c r="Q70" s="46"/>
-      <c r="R70" s="45"/>
-      <c r="S70" s="46"/>
-      <c r="T70" s="45"/>
-      <c r="U70" s="46"/>
-      <c r="V70" s="45"/>
-      <c r="W70" s="46"/>
-      <c r="X70" s="45"/>
-      <c r="Y70" s="46"/>
-      <c r="Z70" s="45"/>
-      <c r="AA70" s="46"/>
-      <c r="AB70" s="45"/>
-      <c r="AC70" s="46"/>
-      <c r="AD70" s="45"/>
-      <c r="AE70" s="46"/>
-      <c r="AF70" s="45"/>
-      <c r="AG70" s="46"/>
-      <c r="AH70" s="45"/>
-      <c r="AI70" s="46"/>
-      <c r="AJ70" s="45"/>
-      <c r="AK70" s="46"/>
-      <c r="AL70" s="45"/>
-      <c r="AM70" s="46"/>
-      <c r="AN70" s="45"/>
-      <c r="AO70" s="46"/>
-      <c r="AP70" s="45"/>
-      <c r="AQ70" s="45"/>
-      <c r="AR70" s="45"/>
-      <c r="AS70" s="45"/>
-      <c r="AT70" s="45"/>
-      <c r="AU70" s="46"/>
-      <c r="AV70" s="47"/>
+      <c r="B70" s="40"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="41"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="41"/>
+      <c r="H70" s="40"/>
+      <c r="I70" s="41"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="41"/>
+      <c r="L70" s="40"/>
+      <c r="M70" s="41"/>
+      <c r="N70" s="40"/>
+      <c r="O70" s="41"/>
+      <c r="P70" s="40"/>
+      <c r="Q70" s="41"/>
+      <c r="R70" s="40"/>
+      <c r="S70" s="41"/>
+      <c r="T70" s="40"/>
+      <c r="U70" s="41"/>
+      <c r="V70" s="40"/>
+      <c r="W70" s="41"/>
+      <c r="X70" s="40"/>
+      <c r="Y70" s="41"/>
+      <c r="Z70" s="40"/>
+      <c r="AA70" s="41"/>
+      <c r="AB70" s="40"/>
+      <c r="AC70" s="41"/>
+      <c r="AD70" s="40"/>
+      <c r="AE70" s="41"/>
+      <c r="AF70" s="40"/>
+      <c r="AG70" s="41"/>
+      <c r="AH70" s="40"/>
+      <c r="AI70" s="41"/>
+      <c r="AJ70" s="40"/>
+      <c r="AK70" s="41"/>
+      <c r="AL70" s="40"/>
+      <c r="AM70" s="41"/>
+      <c r="AN70" s="40"/>
+      <c r="AO70" s="41"/>
+      <c r="AP70" s="40"/>
+      <c r="AQ70" s="40"/>
+      <c r="AR70" s="40"/>
+      <c r="AS70" s="40"/>
+      <c r="AT70" s="40"/>
+      <c r="AU70" s="41"/>
+      <c r="AV70" s="42"/>
       <c r="AW70" s="8"/>
       <c r="AX70" s="8"/>
     </row>
@@ -11648,56 +11648,56 @@
       <c r="AX75" s="12"/>
     </row>
     <row r="76" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="44" t="s">
+      <c r="A76" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="46"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="46"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="46"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="46"/>
-      <c r="J76" s="45"/>
-      <c r="K76" s="46"/>
-      <c r="L76" s="45"/>
-      <c r="M76" s="46"/>
-      <c r="N76" s="45"/>
-      <c r="O76" s="46"/>
-      <c r="P76" s="45"/>
-      <c r="Q76" s="46"/>
-      <c r="R76" s="45"/>
-      <c r="S76" s="46"/>
-      <c r="T76" s="45"/>
-      <c r="U76" s="46"/>
-      <c r="V76" s="45"/>
-      <c r="W76" s="46"/>
-      <c r="X76" s="45"/>
-      <c r="Y76" s="46"/>
-      <c r="Z76" s="45"/>
-      <c r="AA76" s="46"/>
-      <c r="AB76" s="45"/>
-      <c r="AC76" s="46"/>
-      <c r="AD76" s="45"/>
-      <c r="AE76" s="46"/>
-      <c r="AF76" s="45"/>
-      <c r="AG76" s="46"/>
-      <c r="AH76" s="45"/>
-      <c r="AI76" s="46"/>
-      <c r="AJ76" s="45"/>
-      <c r="AK76" s="46"/>
-      <c r="AL76" s="45"/>
-      <c r="AM76" s="46"/>
-      <c r="AN76" s="45"/>
-      <c r="AO76" s="46"/>
-      <c r="AP76" s="45"/>
-      <c r="AQ76" s="45"/>
-      <c r="AR76" s="45"/>
-      <c r="AS76" s="45"/>
-      <c r="AT76" s="45"/>
-      <c r="AU76" s="46"/>
-      <c r="AV76" s="47"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="40"/>
+      <c r="E76" s="41"/>
+      <c r="F76" s="40"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="40"/>
+      <c r="I76" s="41"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="41"/>
+      <c r="L76" s="40"/>
+      <c r="M76" s="41"/>
+      <c r="N76" s="40"/>
+      <c r="O76" s="41"/>
+      <c r="P76" s="40"/>
+      <c r="Q76" s="41"/>
+      <c r="R76" s="40"/>
+      <c r="S76" s="41"/>
+      <c r="T76" s="40"/>
+      <c r="U76" s="41"/>
+      <c r="V76" s="40"/>
+      <c r="W76" s="41"/>
+      <c r="X76" s="40"/>
+      <c r="Y76" s="41"/>
+      <c r="Z76" s="40"/>
+      <c r="AA76" s="41"/>
+      <c r="AB76" s="40"/>
+      <c r="AC76" s="41"/>
+      <c r="AD76" s="40"/>
+      <c r="AE76" s="41"/>
+      <c r="AF76" s="40"/>
+      <c r="AG76" s="41"/>
+      <c r="AH76" s="40"/>
+      <c r="AI76" s="41"/>
+      <c r="AJ76" s="40"/>
+      <c r="AK76" s="41"/>
+      <c r="AL76" s="40"/>
+      <c r="AM76" s="41"/>
+      <c r="AN76" s="40"/>
+      <c r="AO76" s="41"/>
+      <c r="AP76" s="40"/>
+      <c r="AQ76" s="40"/>
+      <c r="AR76" s="40"/>
+      <c r="AS76" s="40"/>
+      <c r="AT76" s="40"/>
+      <c r="AU76" s="41"/>
+      <c r="AV76" s="42"/>
       <c r="AW76" s="8"/>
       <c r="AX76" s="8"/>
     </row>
@@ -12060,171 +12060,173 @@
       <c r="B79" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="D79" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F79" s="11" t="str">
+      <c r="F79" s="11">
         <f>IF(OR($C79="",E79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E79,FIND("-",E79)-1),"")=AW79,IFERROR(--MID(E79,FIND("-",E79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))-(IFERROR(--MID(E79,FIND("-",E79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))-(IFERROR(--MID(E79,FIND("-",E79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(E79,FIND("-",E79)-1),""))=(AW79))+2*((IFERROR(--MID(E79,FIND("-",E79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H79" s="11" t="str">
+      <c r="H79" s="11">
         <f>IF(OR($C79="",G79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G79,FIND("-",G79)-1),"")=AW79,IFERROR(--MID(G79,FIND("-",G79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))-(IFERROR(--MID(G79,FIND("-",G79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))-(IFERROR(--MID(G79,FIND("-",G79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(G79,FIND("-",G79)-1),""))=(AW79))+2*((IFERROR(--MID(G79,FIND("-",G79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J79" s="11" t="str">
+      <c r="J79" s="11">
         <f>IF(OR($C79="",I79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I79,FIND("-",I79)-1),"")=AW79,IFERROR(--MID(I79,FIND("-",I79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))-(IFERROR(--MID(I79,FIND("-",I79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))-(IFERROR(--MID(I79,FIND("-",I79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(I79,FIND("-",I79)-1),""))=(AW79))+2*((IFERROR(--MID(I79,FIND("-",I79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K79" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L79" s="11" t="str">
+      <c r="L79" s="11">
         <f>IF(OR($C79="",K79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K79,FIND("-",K79)-1),"")=AW79,IFERROR(--MID(K79,FIND("-",K79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))-(IFERROR(--MID(K79,FIND("-",K79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))-(IFERROR(--MID(K79,FIND("-",K79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(K79,FIND("-",K79)-1),""))=(AW79))+2*((IFERROR(--MID(K79,FIND("-",K79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N79" s="11" t="str">
+      <c r="N79" s="11">
         <f>IF(OR($C79="",M79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M79,FIND("-",M79)-1),"")=AW79,IFERROR(--MID(M79,FIND("-",M79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))-(IFERROR(--MID(M79,FIND("-",M79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))-(IFERROR(--MID(M79,FIND("-",M79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(M79,FIND("-",M79)-1),""))=(AW79))+2*((IFERROR(--MID(M79,FIND("-",M79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P79" s="11" t="str">
+      <c r="P79" s="11">
         <f>IF(OR($C79="",O79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O79,FIND("-",O79)-1),"")=AW79,IFERROR(--MID(O79,FIND("-",O79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))-(IFERROR(--MID(O79,FIND("-",O79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))-(IFERROR(--MID(O79,FIND("-",O79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(O79,FIND("-",O79)-1),""))=(AW79))+2*((IFERROR(--MID(O79,FIND("-",O79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="Q79" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R79" s="11" t="str">
+      <c r="R79" s="11">
         <f>IF(OR($C79="",Q79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q79,FIND("-",Q79)-1),"")=AW79,IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))-(IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))-(IFERROR(--MID(Q79,FIND("-",Q79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(Q79,FIND("-",Q79)-1),""))=(AW79))+2*((IFERROR(--MID(Q79,FIND("-",Q79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="S79" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T79" s="11" t="str">
+      <c r="T79" s="11">
         <f>IF(OR($C79="",S79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S79,FIND("-",S79)-1),"")=AW79,IFERROR(--MID(S79,FIND("-",S79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))-(IFERROR(--MID(S79,FIND("-",S79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))-(IFERROR(--MID(S79,FIND("-",S79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(S79,FIND("-",S79)-1),""))=(AW79))+2*((IFERROR(--MID(S79,FIND("-",S79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="V79" s="11" t="str">
+      <c r="V79" s="11">
         <f>IF(OR($C79="",U79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U79,FIND("-",U79)-1),"")=AW79,IFERROR(--MID(U79,FIND("-",U79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))-(IFERROR(--MID(U79,FIND("-",U79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))-(IFERROR(--MID(U79,FIND("-",U79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(U79,FIND("-",U79)-1),""))=(AW79))+2*((IFERROR(--MID(U79,FIND("-",U79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="W79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="X79" s="11" t="str">
+      <c r="X79" s="11">
         <f>IF(OR($C79="",W79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W79,FIND("-",W79)-1),"")=AW79,IFERROR(--MID(W79,FIND("-",W79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))-(IFERROR(--MID(W79,FIND("-",W79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))-(IFERROR(--MID(W79,FIND("-",W79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(W79,FIND("-",W79)-1),""))=(AW79))+2*((IFERROR(--MID(W79,FIND("-",W79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z79" s="11" t="str">
+      <c r="Z79" s="11">
         <f>IF(OR($C79="",Y79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y79,FIND("-",Y79)-1),"")=AW79,IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))-(IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))-(IFERROR(--MID(Y79,FIND("-",Y79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(Y79,FIND("-",Y79)-1),""))=(AW79))+2*((IFERROR(--MID(Y79,FIND("-",Y79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AB79" s="11" t="str">
+      <c r="AB79" s="11">
         <f>IF(OR($C79="",AA79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA79,FIND("-",AA79)-1),"")=AW79,IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))-(IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))-(IFERROR(--MID(AA79,FIND("-",AA79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AA79,FIND("-",AA79)-1),""))=(AW79))+2*((IFERROR(--MID(AA79,FIND("-",AA79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC79" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="AD79" s="11" t="str">
+      <c r="AD79" s="11">
         <f>IF(OR($C79="",AC79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC79,FIND("-",AC79)-1),"")=AW79,IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))-(IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))-(IFERROR(--MID(AC79,FIND("-",AC79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AC79,FIND("-",AC79)-1),""))=(AW79))+2*((IFERROR(--MID(AC79,FIND("-",AC79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AE79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AF79" s="11" t="str">
+      <c r="AF79" s="11">
         <f>IF(OR($C79="",AE79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE79,FIND("-",AE79)-1),"")=AW79,IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))-(IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))-(IFERROR(--MID(AE79,FIND("-",AE79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AE79,FIND("-",AE79)-1),""))=(AW79))+2*((IFERROR(--MID(AE79,FIND("-",AE79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AG79" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AH79" s="11" t="str">
+      <c r="AH79" s="11">
         <f>IF(OR($C79="",AG79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG79,FIND("-",AG79)-1),"")=AW79,IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))-(IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))-(IFERROR(--MID(AG79,FIND("-",AG79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AG79,FIND("-",AG79)-1),""))=(AW79))+2*((IFERROR(--MID(AG79,FIND("-",AG79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ79" s="11" t="str">
+      <c r="AJ79" s="11">
         <f>IF(OR($C79="",AI79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI79,FIND("-",AI79)-1),"")=AW79,IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))-(IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))-(IFERROR(--MID(AI79,FIND("-",AI79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AI79,FIND("-",AI79)-1),""))=(AW79))+2*((IFERROR(--MID(AI79,FIND("-",AI79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL79" s="11" t="str">
+      <c r="AL79" s="11">
         <f>IF(OR($C79="",AK79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK79,FIND("-",AK79)-1),"")=AW79,IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))-(IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))-(IFERROR(--MID(AK79,FIND("-",AK79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AK79,FIND("-",AK79)-1),""))=(AW79))+2*((IFERROR(--MID(AK79,FIND("-",AK79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AM79" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="AN79" s="11" t="str">
+      <c r="AN79" s="11">
         <f>IF(OR($C79="",AM79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM79,FIND("-",AM79)-1),"")=AW79,IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))-(IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))-(IFERROR(--MID(AM79,FIND("-",AM79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AM79,FIND("-",AM79)-1),""))=(AW79))+2*((IFERROR(--MID(AM79,FIND("-",AM79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO79" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AP79" s="11" t="str">
+      <c r="AP79" s="11">
         <f>IF(OR($C79="",AO79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO79,FIND("-",AO79)-1),"")=AW79,IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))-(IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))-(IFERROR(--MID(AO79,FIND("-",AO79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AO79,FIND("-",AO79)-1),""))=(AW79))+2*((IFERROR(--MID(AO79,FIND("-",AO79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AQ79" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR79" s="11" t="str">
+      <c r="AR79" s="11">
         <f>IF(OR($C79="",AQ79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),"")=AW79,IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))-(IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))-(IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AQ79,FIND("-",AQ79)-1),""))=(AW79))+2*((IFERROR(--MID(AQ79,FIND("-",AQ79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS79" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AT79" s="11" t="str">
+      <c r="AT79" s="11">
         <f>IF(OR($C79="",AS79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS79,FIND("-",AS79)-1),"")=AW79,IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))-(IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))-(IFERROR(--MID(AS79,FIND("-",AS79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AS79,FIND("-",AS79)-1),""))=(AW79))+2*((IFERROR(--MID(AS79,FIND("-",AS79)+1,99),""))=(AX79))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU79" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AV79" s="11" t="str">
+      <c r="AV79" s="11">
         <f>IF(OR($C79="",AU79=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU79,FIND("-",AU79)-1),"")=AW79,IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")=AX79),10,5*(SIGN((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))-(IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")))=SIGN((AW79)-(AX79)))+2*(((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))-(IFERROR(--MID(AU79,FIND("-",AU79)+1,99),"")))=((AW79)-(AX79)))+2*((IFERROR(--LEFT(AU79,FIND("-",AU79)-1),""))=(AW79))+2*((IFERROR(--MID(AU79,FIND("-",AU79)+1,99),""))=(AX79))),""))</f>
-        <v/>
-      </c>
-      <c r="AW79" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AW79" s="11">
         <f>IF($C79="","",IFERROR(--LEFT($C79,FIND("-",$C79)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX79" s="11" t="str">
+        <v>2</v>
+      </c>
+      <c r="AX79" s="11">
         <f>IF($C79="","",IFERROR(--MID($C79,FIND("-",$C79)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12234,171 +12236,173 @@
       <c r="B80" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D80" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F80" s="11" t="str">
+      <c r="F80" s="11">
         <f>IF(OR($C80="",E80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E80,FIND("-",E80)-1),"")=AW80,IFERROR(--MID(E80,FIND("-",E80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))-(IFERROR(--MID(E80,FIND("-",E80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))-(IFERROR(--MID(E80,FIND("-",E80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(E80,FIND("-",E80)-1),""))=(AW80))+2*((IFERROR(--MID(E80,FIND("-",E80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H80" s="11" t="str">
+      <c r="H80" s="11">
         <f>IF(OR($C80="",G80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G80,FIND("-",G80)-1),"")=AW80,IFERROR(--MID(G80,FIND("-",G80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))-(IFERROR(--MID(G80,FIND("-",G80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))-(IFERROR(--MID(G80,FIND("-",G80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(G80,FIND("-",G80)-1),""))=(AW80))+2*((IFERROR(--MID(G80,FIND("-",G80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I80" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="J80" s="11" t="str">
+      <c r="J80" s="11">
         <f>IF(OR($C80="",I80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I80,FIND("-",I80)-1),"")=AW80,IFERROR(--MID(I80,FIND("-",I80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))-(IFERROR(--MID(I80,FIND("-",I80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))-(IFERROR(--MID(I80,FIND("-",I80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(I80,FIND("-",I80)-1),""))=(AW80))+2*((IFERROR(--MID(I80,FIND("-",I80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="L80" s="11" t="str">
+      <c r="L80" s="11">
         <f>IF(OR($C80="",K80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K80,FIND("-",K80)-1),"")=AW80,IFERROR(--MID(K80,FIND("-",K80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))-(IFERROR(--MID(K80,FIND("-",K80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))-(IFERROR(--MID(K80,FIND("-",K80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(K80,FIND("-",K80)-1),""))=(AW80))+2*((IFERROR(--MID(K80,FIND("-",K80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="M80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="N80" s="11" t="str">
+      <c r="N80" s="11">
         <f>IF(OR($C80="",M80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M80,FIND("-",M80)-1),"")=AW80,IFERROR(--MID(M80,FIND("-",M80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))-(IFERROR(--MID(M80,FIND("-",M80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))-(IFERROR(--MID(M80,FIND("-",M80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(M80,FIND("-",M80)-1),""))=(AW80))+2*((IFERROR(--MID(M80,FIND("-",M80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="O80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P80" s="11" t="str">
+      <c r="P80" s="11">
         <f>IF(OR($C80="",O80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O80,FIND("-",O80)-1),"")=AW80,IFERROR(--MID(O80,FIND("-",O80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))-(IFERROR(--MID(O80,FIND("-",O80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))-(IFERROR(--MID(O80,FIND("-",O80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(O80,FIND("-",O80)-1),""))=(AW80))+2*((IFERROR(--MID(O80,FIND("-",O80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q80" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="R80" s="11" t="str">
+      <c r="R80" s="11">
         <f>IF(OR($C80="",Q80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q80,FIND("-",Q80)-1),"")=AW80,IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))-(IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))-(IFERROR(--MID(Q80,FIND("-",Q80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(Q80,FIND("-",Q80)-1),""))=(AW80))+2*((IFERROR(--MID(Q80,FIND("-",Q80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T80" s="11" t="str">
+      <c r="T80" s="11">
         <f>IF(OR($C80="",S80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S80,FIND("-",S80)-1),"")=AW80,IFERROR(--MID(S80,FIND("-",S80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))-(IFERROR(--MID(S80,FIND("-",S80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))-(IFERROR(--MID(S80,FIND("-",S80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(S80,FIND("-",S80)-1),""))=(AW80))+2*((IFERROR(--MID(S80,FIND("-",S80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V80" s="11" t="str">
+      <c r="V80" s="11">
         <f>IF(OR($C80="",U80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U80,FIND("-",U80)-1),"")=AW80,IFERROR(--MID(U80,FIND("-",U80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))-(IFERROR(--MID(U80,FIND("-",U80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))-(IFERROR(--MID(U80,FIND("-",U80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(U80,FIND("-",U80)-1),""))=(AW80))+2*((IFERROR(--MID(U80,FIND("-",U80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W80" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X80" s="11" t="str">
+      <c r="X80" s="11">
         <f>IF(OR($C80="",W80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W80,FIND("-",W80)-1),"")=AW80,IFERROR(--MID(W80,FIND("-",W80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))-(IFERROR(--MID(W80,FIND("-",W80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))-(IFERROR(--MID(W80,FIND("-",W80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(W80,FIND("-",W80)-1),""))=(AW80))+2*((IFERROR(--MID(W80,FIND("-",W80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="Z80" s="11" t="str">
+      <c r="Z80" s="11">
         <f>IF(OR($C80="",Y80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y80,FIND("-",Y80)-1),"")=AW80,IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))-(IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))-(IFERROR(--MID(Y80,FIND("-",Y80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(Y80,FIND("-",Y80)-1),""))=(AW80))+2*((IFERROR(--MID(Y80,FIND("-",Y80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA80" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB80" s="11" t="str">
+      <c r="AB80" s="11">
         <f>IF(OR($C80="",AA80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA80,FIND("-",AA80)-1),"")=AW80,IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))-(IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))-(IFERROR(--MID(AA80,FIND("-",AA80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AA80,FIND("-",AA80)-1),""))=(AW80))+2*((IFERROR(--MID(AA80,FIND("-",AA80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AC80" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="AD80" s="11" t="str">
+      <c r="AD80" s="11">
         <f>IF(OR($C80="",AC80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC80,FIND("-",AC80)-1),"")=AW80,IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))-(IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))-(IFERROR(--MID(AC80,FIND("-",AC80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AC80,FIND("-",AC80)-1),""))=(AW80))+2*((IFERROR(--MID(AC80,FIND("-",AC80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="AE80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF80" s="11" t="str">
+      <c r="AF80" s="11">
         <f>IF(OR($C80="",AE80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE80,FIND("-",AE80)-1),"")=AW80,IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))-(IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))-(IFERROR(--MID(AE80,FIND("-",AE80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AE80,FIND("-",AE80)-1),""))=(AW80))+2*((IFERROR(--MID(AE80,FIND("-",AE80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AH80" s="11" t="str">
+      <c r="AH80" s="11">
         <f>IF(OR($C80="",AG80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG80,FIND("-",AG80)-1),"")=AW80,IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))-(IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))-(IFERROR(--MID(AG80,FIND("-",AG80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AG80,FIND("-",AG80)-1),""))=(AW80))+2*((IFERROR(--MID(AG80,FIND("-",AG80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ80" s="11" t="str">
+      <c r="AJ80" s="11">
         <f>IF(OR($C80="",AI80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI80,FIND("-",AI80)-1),"")=AW80,IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))-(IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))-(IFERROR(--MID(AI80,FIND("-",AI80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AI80,FIND("-",AI80)-1),""))=(AW80))+2*((IFERROR(--MID(AI80,FIND("-",AI80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK80" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AL80" s="11" t="str">
+      <c r="AL80" s="11">
         <f>IF(OR($C80="",AK80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK80,FIND("-",AK80)-1),"")=AW80,IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))-(IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))-(IFERROR(--MID(AK80,FIND("-",AK80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AK80,FIND("-",AK80)-1),""))=(AW80))+2*((IFERROR(--MID(AK80,FIND("-",AK80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM80" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AN80" s="11" t="str">
+      <c r="AN80" s="11">
         <f>IF(OR($C80="",AM80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM80,FIND("-",AM80)-1),"")=AW80,IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))-(IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))-(IFERROR(--MID(AM80,FIND("-",AM80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AM80,FIND("-",AM80)-1),""))=(AW80))+2*((IFERROR(--MID(AM80,FIND("-",AM80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AO80" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP80" s="11" t="str">
+      <c r="AP80" s="11">
         <f>IF(OR($C80="",AO80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO80,FIND("-",AO80)-1),"")=AW80,IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))-(IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))-(IFERROR(--MID(AO80,FIND("-",AO80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AO80,FIND("-",AO80)-1),""))=(AW80))+2*((IFERROR(--MID(AO80,FIND("-",AO80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ80" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="AR80" s="11" t="str">
+      <c r="AR80" s="11">
         <f>IF(OR($C80="",AQ80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),"")=AW80,IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))-(IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))-(IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AQ80,FIND("-",AQ80)-1),""))=(AW80))+2*((IFERROR(--MID(AQ80,FIND("-",AQ80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AS80" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AT80" s="11" t="str">
+      <c r="AT80" s="11">
         <f>IF(OR($C80="",AS80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS80,FIND("-",AS80)-1),"")=AW80,IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))-(IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))-(IFERROR(--MID(AS80,FIND("-",AS80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AS80,FIND("-",AS80)-1),""))=(AW80))+2*((IFERROR(--MID(AS80,FIND("-",AS80)+1,99),""))=(AX80))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU80" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AV80" s="11" t="str">
+      <c r="AV80" s="11">
         <f>IF(OR($C80="",AU80=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU80,FIND("-",AU80)-1),"")=AW80,IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")=AX80),10,5*(SIGN((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))-(IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")))=SIGN((AW80)-(AX80)))+2*(((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))-(IFERROR(--MID(AU80,FIND("-",AU80)+1,99),"")))=((AW80)-(AX80)))+2*((IFERROR(--LEFT(AU80,FIND("-",AU80)-1),""))=(AW80))+2*((IFERROR(--MID(AU80,FIND("-",AU80)+1,99),""))=(AX80))),""))</f>
-        <v/>
-      </c>
-      <c r="AW80" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW80" s="11">
         <f>IF($C80="","",IFERROR(--LEFT($C80,FIND("-",$C80)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX80" s="11" t="str">
+        <v>3</v>
+      </c>
+      <c r="AX80" s="11">
         <f>IF($C80="","",IFERROR(--MID($C80,FIND("-",$C80)+1,99),""))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12460,56 +12464,56 @@
       <c r="AX81" s="12"/>
     </row>
     <row r="82" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="44" t="s">
+      <c r="A82" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B82" s="45"/>
-      <c r="C82" s="46"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="46"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="46"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="46"/>
-      <c r="J82" s="45"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="45"/>
-      <c r="M82" s="46"/>
-      <c r="N82" s="45"/>
-      <c r="O82" s="46"/>
-      <c r="P82" s="45"/>
-      <c r="Q82" s="46"/>
-      <c r="R82" s="45"/>
-      <c r="S82" s="46"/>
-      <c r="T82" s="45"/>
-      <c r="U82" s="46"/>
-      <c r="V82" s="45"/>
-      <c r="W82" s="46"/>
-      <c r="X82" s="45"/>
-      <c r="Y82" s="46"/>
-      <c r="Z82" s="45"/>
-      <c r="AA82" s="46"/>
-      <c r="AB82" s="45"/>
-      <c r="AC82" s="46"/>
-      <c r="AD82" s="45"/>
-      <c r="AE82" s="46"/>
-      <c r="AF82" s="45"/>
-      <c r="AG82" s="46"/>
-      <c r="AH82" s="45"/>
-      <c r="AI82" s="46"/>
-      <c r="AJ82" s="45"/>
-      <c r="AK82" s="46"/>
-      <c r="AL82" s="45"/>
-      <c r="AM82" s="46"/>
-      <c r="AN82" s="45"/>
-      <c r="AO82" s="46"/>
-      <c r="AP82" s="45"/>
-      <c r="AQ82" s="45"/>
-      <c r="AR82" s="45"/>
-      <c r="AS82" s="45"/>
-      <c r="AT82" s="45"/>
-      <c r="AU82" s="46"/>
-      <c r="AV82" s="47"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="40"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="41"/>
+      <c r="L82" s="40"/>
+      <c r="M82" s="41"/>
+      <c r="N82" s="40"/>
+      <c r="O82" s="41"/>
+      <c r="P82" s="40"/>
+      <c r="Q82" s="41"/>
+      <c r="R82" s="40"/>
+      <c r="S82" s="41"/>
+      <c r="T82" s="40"/>
+      <c r="U82" s="41"/>
+      <c r="V82" s="40"/>
+      <c r="W82" s="41"/>
+      <c r="X82" s="40"/>
+      <c r="Y82" s="41"/>
+      <c r="Z82" s="40"/>
+      <c r="AA82" s="41"/>
+      <c r="AB82" s="40"/>
+      <c r="AC82" s="41"/>
+      <c r="AD82" s="40"/>
+      <c r="AE82" s="41"/>
+      <c r="AF82" s="40"/>
+      <c r="AG82" s="41"/>
+      <c r="AH82" s="40"/>
+      <c r="AI82" s="41"/>
+      <c r="AJ82" s="40"/>
+      <c r="AK82" s="41"/>
+      <c r="AL82" s="40"/>
+      <c r="AM82" s="41"/>
+      <c r="AN82" s="40"/>
+      <c r="AO82" s="41"/>
+      <c r="AP82" s="40"/>
+      <c r="AQ82" s="40"/>
+      <c r="AR82" s="40"/>
+      <c r="AS82" s="40"/>
+      <c r="AT82" s="40"/>
+      <c r="AU82" s="41"/>
+      <c r="AV82" s="42"/>
       <c r="AW82" s="8"/>
       <c r="AX82" s="8"/>
     </row>
@@ -12520,171 +12524,173 @@
       <c r="B83" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="D83" s="1" t="s">
         <v>59</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F83" s="11" t="str">
+      <c r="F83" s="11">
         <f t="shared" ref="F83:F88" si="6">IF(OR($C83="",E83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(E83,FIND("-",E83)-1),"")=AW83,IFERROR(--MID(E83,FIND("-",E83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))-(IFERROR(--MID(E83,FIND("-",E83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))-(IFERROR(--MID(E83,FIND("-",E83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(E83,FIND("-",E83)-1),""))=(AW83))+2*((IFERROR(--MID(E83,FIND("-",E83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H83" s="11" t="str">
+      <c r="H83" s="11">
         <f t="shared" ref="H83:H88" si="7">IF(OR($C83="",G83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(G83,FIND("-",G83)-1),"")=AW83,IFERROR(--MID(G83,FIND("-",G83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))-(IFERROR(--MID(G83,FIND("-",G83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))-(IFERROR(--MID(G83,FIND("-",G83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(G83,FIND("-",G83)-1),""))=(AW83))+2*((IFERROR(--MID(G83,FIND("-",G83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J83" s="11" t="str">
+      <c r="J83" s="11">
         <f t="shared" ref="J83:J88" si="8">IF(OR($C83="",I83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(I83,FIND("-",I83)-1),"")=AW83,IFERROR(--MID(I83,FIND("-",I83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))-(IFERROR(--MID(I83,FIND("-",I83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))-(IFERROR(--MID(I83,FIND("-",I83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(I83,FIND("-",I83)-1),""))=(AW83))+2*((IFERROR(--MID(I83,FIND("-",I83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="K83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="L83" s="11" t="str">
+      <c r="L83" s="11">
         <f t="shared" ref="L83:L88" si="9">IF(OR($C83="",K83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(K83,FIND("-",K83)-1),"")=AW83,IFERROR(--MID(K83,FIND("-",K83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))-(IFERROR(--MID(K83,FIND("-",K83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))-(IFERROR(--MID(K83,FIND("-",K83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(K83,FIND("-",K83)-1),""))=(AW83))+2*((IFERROR(--MID(K83,FIND("-",K83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N83" s="11" t="str">
+      <c r="N83" s="11">
         <f t="shared" ref="N83:N88" si="10">IF(OR($C83="",M83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(M83,FIND("-",M83)-1),"")=AW83,IFERROR(--MID(M83,FIND("-",M83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))-(IFERROR(--MID(M83,FIND("-",M83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))-(IFERROR(--MID(M83,FIND("-",M83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(M83,FIND("-",M83)-1),""))=(AW83))+2*((IFERROR(--MID(M83,FIND("-",M83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="O83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="P83" s="11" t="str">
+      <c r="P83" s="11">
         <f t="shared" ref="P83:P88" si="11">IF(OR($C83="",O83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(O83,FIND("-",O83)-1),"")=AW83,IFERROR(--MID(O83,FIND("-",O83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))-(IFERROR(--MID(O83,FIND("-",O83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))-(IFERROR(--MID(O83,FIND("-",O83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(O83,FIND("-",O83)-1),""))=(AW83))+2*((IFERROR(--MID(O83,FIND("-",O83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q83" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R83" s="11" t="str">
+      <c r="R83" s="11">
         <f t="shared" ref="R83:R88" si="12">IF(OR($C83="",Q83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Q83,FIND("-",Q83)-1),"")=AW83,IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))-(IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))-(IFERROR(--MID(Q83,FIND("-",Q83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(Q83,FIND("-",Q83)-1),""))=(AW83))+2*((IFERROR(--MID(Q83,FIND("-",Q83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S83" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="T83" s="11" t="str">
+      <c r="T83" s="11">
         <f t="shared" ref="T83:T88" si="13">IF(OR($C83="",S83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(S83,FIND("-",S83)-1),"")=AW83,IFERROR(--MID(S83,FIND("-",S83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))-(IFERROR(--MID(S83,FIND("-",S83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))-(IFERROR(--MID(S83,FIND("-",S83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(S83,FIND("-",S83)-1),""))=(AW83))+2*((IFERROR(--MID(S83,FIND("-",S83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="U83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="V83" s="11" t="str">
+      <c r="V83" s="11">
         <f t="shared" ref="V83:V88" si="14">IF(OR($C83="",U83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(U83,FIND("-",U83)-1),"")=AW83,IFERROR(--MID(U83,FIND("-",U83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))-(IFERROR(--MID(U83,FIND("-",U83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))-(IFERROR(--MID(U83,FIND("-",U83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(U83,FIND("-",U83)-1),""))=(AW83))+2*((IFERROR(--MID(U83,FIND("-",U83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="X83" s="11" t="str">
+      <c r="X83" s="11">
         <f t="shared" ref="X83:X88" si="15">IF(OR($C83="",W83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(W83,FIND("-",W83)-1),"")=AW83,IFERROR(--MID(W83,FIND("-",W83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))-(IFERROR(--MID(W83,FIND("-",W83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))-(IFERROR(--MID(W83,FIND("-",W83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(W83,FIND("-",W83)-1),""))=(AW83))+2*((IFERROR(--MID(W83,FIND("-",W83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z83" s="11" t="str">
+      <c r="Z83" s="11">
         <f t="shared" ref="Z83:Z88" si="16">IF(OR($C83="",Y83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(Y83,FIND("-",Y83)-1),"")=AW83,IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))-(IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))-(IFERROR(--MID(Y83,FIND("-",Y83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(Y83,FIND("-",Y83)-1),""))=(AW83))+2*((IFERROR(--MID(Y83,FIND("-",Y83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA83" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AB83" s="11" t="str">
+      <c r="AB83" s="11">
         <f t="shared" ref="AB83:AB88" si="17">IF(OR($C83="",AA83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AA83,FIND("-",AA83)-1),"")=AW83,IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))-(IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))-(IFERROR(--MID(AA83,FIND("-",AA83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AA83,FIND("-",AA83)-1),""))=(AW83))+2*((IFERROR(--MID(AA83,FIND("-",AA83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AC83" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="AD83" s="11" t="str">
+      <c r="AD83" s="11">
         <f t="shared" ref="AD83:AD88" si="18">IF(OR($C83="",AC83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AC83,FIND("-",AC83)-1),"")=AW83,IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))-(IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))-(IFERROR(--MID(AC83,FIND("-",AC83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AC83,FIND("-",AC83)-1),""))=(AW83))+2*((IFERROR(--MID(AC83,FIND("-",AC83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AF83" s="11" t="str">
+      <c r="AF83" s="11">
         <f t="shared" ref="AF83:AF88" si="19">IF(OR($C83="",AE83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AE83,FIND("-",AE83)-1),"")=AW83,IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))-(IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))-(IFERROR(--MID(AE83,FIND("-",AE83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AE83,FIND("-",AE83)-1),""))=(AW83))+2*((IFERROR(--MID(AE83,FIND("-",AE83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AH83" s="11" t="str">
+      <c r="AH83" s="11">
         <f t="shared" ref="AH83:AH88" si="20">IF(OR($C83="",AG83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AG83,FIND("-",AG83)-1),"")=AW83,IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))-(IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))-(IFERROR(--MID(AG83,FIND("-",AG83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AG83,FIND("-",AG83)-1),""))=(AW83))+2*((IFERROR(--MID(AG83,FIND("-",AG83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AI83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AJ83" s="11" t="str">
+      <c r="AJ83" s="11">
         <f t="shared" ref="AJ83:AJ88" si="21">IF(OR($C83="",AI83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AI83,FIND("-",AI83)-1),"")=AW83,IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))-(IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))-(IFERROR(--MID(AI83,FIND("-",AI83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AI83,FIND("-",AI83)-1),""))=(AW83))+2*((IFERROR(--MID(AI83,FIND("-",AI83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK83" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AL83" s="11" t="str">
+      <c r="AL83" s="11">
         <f t="shared" ref="AL83:AL88" si="22">IF(OR($C83="",AK83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AK83,FIND("-",AK83)-1),"")=AW83,IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))-(IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))-(IFERROR(--MID(AK83,FIND("-",AK83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AK83,FIND("-",AK83)-1),""))=(AW83))+2*((IFERROR(--MID(AK83,FIND("-",AK83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM83" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AN83" s="11" t="str">
+      <c r="AN83" s="11">
         <f t="shared" ref="AN83:AN88" si="23">IF(OR($C83="",AM83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AM83,FIND("-",AM83)-1),"")=AW83,IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))-(IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))-(IFERROR(--MID(AM83,FIND("-",AM83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AM83,FIND("-",AM83)-1),""))=(AW83))+2*((IFERROR(--MID(AM83,FIND("-",AM83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO83" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP83" s="11" t="str">
+      <c r="AP83" s="11">
         <f t="shared" ref="AP83:AP88" si="24">IF(OR($C83="",AO83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AO83,FIND("-",AO83)-1),"")=AW83,IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))-(IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))-(IFERROR(--MID(AO83,FIND("-",AO83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AO83,FIND("-",AO83)-1),""))=(AW83))+2*((IFERROR(--MID(AO83,FIND("-",AO83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ83" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AR83" s="11" t="str">
+      <c r="AR83" s="11">
         <f t="shared" ref="AR83:AR89" si="25">IF(OR($C83="",AQ83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),"")=AW83,IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))-(IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))-(IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AQ83,FIND("-",AQ83)-1),""))=(AW83))+2*((IFERROR(--MID(AQ83,FIND("-",AQ83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS83" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="AT83" s="11" t="str">
+      <c r="AT83" s="11">
         <f t="shared" ref="AT83:AT89" si="26">IF(OR($C83="",AS83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AS83,FIND("-",AS83)-1),"")=AW83,IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))-(IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))-(IFERROR(--MID(AS83,FIND("-",AS83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AS83,FIND("-",AS83)-1),""))=(AW83))+2*((IFERROR(--MID(AS83,FIND("-",AS83)+1,99),""))=(AX83))),""))</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU83" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AV83" s="11" t="str">
+      <c r="AV83" s="11">
         <f t="shared" ref="AV83:AV88" si="27">IF(OR($C83="",AU83=""),"",IFERROR(IF(AND(IFERROR(--LEFT(AU83,FIND("-",AU83)-1),"")=AW83,IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")=AX83),10,5*(SIGN((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))-(IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")))=SIGN((AW83)-(AX83)))+2*(((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))-(IFERROR(--MID(AU83,FIND("-",AU83)+1,99),"")))=((AW83)-(AX83)))+2*((IFERROR(--LEFT(AU83,FIND("-",AU83)-1),""))=(AW83))+2*((IFERROR(--MID(AU83,FIND("-",AU83)+1,99),""))=(AX83))),""))</f>
-        <v/>
-      </c>
-      <c r="AW83" s="11" t="str">
+        <v>10</v>
+      </c>
+      <c r="AW83" s="11">
         <f t="shared" ref="AW83:AW88" si="28">IF($C83="","",IFERROR(--LEFT($C83,FIND("-",$C83)-1),""))</f>
-        <v/>
-      </c>
-      <c r="AX83" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX83" s="11">
         <f t="shared" ref="AX83:AX88" si="29">IF($C83="","",IFERROR(--MID($C83,FIND("-",$C83)+1,99),""))</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12694,171 +12700,173 @@
       <c r="B84" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="10" t="s">
+        <v>62</v>
+      </c>
       <c r="D84" s="1" t="s">
         <v>64</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F84" s="11" t="str">
+      <c r="F84" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H84" s="11" t="str">
+      <c r="H84" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="J84" s="11" t="str">
+      <c r="J84" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K84" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="L84" s="11" t="str">
+      <c r="L84" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N84" s="11" t="str">
+      <c r="N84" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="P84" s="11" t="str">
+      <c r="P84" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Q84" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="R84" s="11" t="str">
+      <c r="R84" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="S84" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T84" s="11" t="str">
+      <c r="T84" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="V84" s="11" t="str">
+      <c r="V84" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="W84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="X84" s="11" t="str">
+      <c r="X84" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="Y84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="Z84" s="11" t="str">
+      <c r="Z84" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AA84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AB84" s="11" t="str">
+      <c r="AB84" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC84" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD84" s="11" t="str">
+      <c r="AD84" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AF84" s="11" t="str">
+      <c r="AF84" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AG84" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AH84" s="11" t="str">
+      <c r="AH84" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AJ84" s="11" t="str">
+      <c r="AJ84" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AK84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AL84" s="11" t="str">
+      <c r="AL84" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AM84" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AN84" s="11" t="str">
+      <c r="AN84" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AP84" s="11" t="str">
+      <c r="AP84" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ84" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AR84" s="11" t="str">
+      <c r="AR84" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AS84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AT84" s="11" t="str">
+      <c r="AT84" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AU84" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="AV84" s="11" t="str">
+      <c r="AV84" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW84" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW84" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX84" s="11" t="str">
+        <v>4</v>
+      </c>
+      <c r="AX84" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -12868,171 +12876,173 @@
       <c r="B85" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="10" t="s">
+        <v>56</v>
+      </c>
       <c r="D85" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F85" s="11" t="str">
+      <c r="F85" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H85" s="11" t="str">
+      <c r="H85" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J85" s="11" t="str">
+      <c r="J85" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="K85" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="L85" s="11" t="str">
+      <c r="L85" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="M85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N85" s="11" t="str">
+      <c r="N85" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="O85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="P85" s="11" t="str">
+      <c r="P85" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q85" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R85" s="11" t="str">
+      <c r="R85" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S85" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T85" s="11" t="str">
+      <c r="T85" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="U85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="V85" s="11" t="str">
+      <c r="V85" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="W85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="X85" s="11" t="str">
+      <c r="X85" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="Y85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="Z85" s="11" t="str">
+      <c r="Z85" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB85" s="11" t="str">
+      <c r="AB85" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AC85" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD85" s="11" t="str">
+      <c r="AD85" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AE85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF85" s="11" t="str">
+      <c r="AF85" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AG85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AH85" s="11" t="str">
+      <c r="AH85" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AI85" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="AJ85" s="11" t="str">
+      <c r="AJ85" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AK85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AL85" s="11" t="str">
+      <c r="AL85" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AM85" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AN85" s="11" t="str">
+      <c r="AN85" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AO85" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AP85" s="11" t="str">
+      <c r="AP85" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AQ85" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AR85" s="11" t="str">
+      <c r="AR85" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AS85" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AT85" s="11" t="str">
+      <c r="AT85" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AU85" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AV85" s="11" t="str">
+      <c r="AV85" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW85" s="11" t="str">
+        <v>7</v>
+      </c>
+      <c r="AW85" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX85" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AX85" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13042,171 +13052,173 @@
       <c r="B86" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C86" s="10"/>
+      <c r="C86" s="10" t="s">
+        <v>39</v>
+      </c>
       <c r="D86" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F86" s="11" t="str">
+      <c r="F86" s="11">
         <f t="shared" si="6"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="G86" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H86" s="11" t="str">
+      <c r="H86" s="11">
         <f t="shared" si="7"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I86" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="J86" s="11" t="str">
+      <c r="J86" s="11">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="K86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="L86" s="11" t="str">
+      <c r="L86" s="11">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N86" s="11" t="str">
+      <c r="N86" s="11">
         <f t="shared" si="10"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="O86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="P86" s="11" t="str">
+      <c r="P86" s="11">
         <f t="shared" si="11"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q86" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="R86" s="11" t="str">
+      <c r="R86" s="11">
         <f t="shared" si="12"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="S86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="T86" s="11" t="str">
+      <c r="T86" s="11">
         <f t="shared" si="13"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="U86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="V86" s="11" t="str">
+      <c r="V86" s="11">
         <f t="shared" si="14"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="X86" s="11" t="str">
+      <c r="X86" s="11">
         <f t="shared" si="15"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="Y86" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="Z86" s="11" t="str">
+      <c r="Z86" s="11">
         <f t="shared" si="16"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AB86" s="11" t="str">
+      <c r="AB86" s="11">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AC86" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="AD86" s="11" t="str">
+      <c r="AD86" s="11">
         <f t="shared" si="18"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="AE86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AF86" s="11" t="str">
+      <c r="AF86" s="11">
         <f t="shared" si="19"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AG86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AH86" s="11" t="str">
+      <c r="AH86" s="11">
         <f t="shared" si="20"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AI86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AJ86" s="11" t="str">
+      <c r="AJ86" s="11">
         <f t="shared" si="21"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AK86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AL86" s="11" t="str">
+      <c r="AL86" s="11">
         <f t="shared" si="22"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AM86" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="AN86" s="11" t="str">
+      <c r="AN86" s="11">
         <f t="shared" si="23"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AO86" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="AP86" s="11" t="str">
+      <c r="AP86" s="11">
         <f t="shared" si="24"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AQ86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AR86" s="11" t="str">
+      <c r="AR86" s="11">
         <f t="shared" si="25"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AS86" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AT86" s="11" t="str">
+      <c r="AT86" s="11">
         <f t="shared" si="26"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AU86" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AV86" s="11" t="str">
+      <c r="AV86" s="11">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="AW86" s="11" t="str">
+        <v>0</v>
+      </c>
+      <c r="AW86" s="11">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AX86" s="11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AX86" s="11">
         <f t="shared" si="29"/>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -13616,56 +13628,56 @@
       <c r="AX89" s="12"/>
     </row>
     <row r="90" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="44" t="s">
+      <c r="A90" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="45"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="46"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="46"/>
-      <c r="J90" s="45"/>
-      <c r="K90" s="46"/>
-      <c r="L90" s="45"/>
-      <c r="M90" s="46"/>
-      <c r="N90" s="45"/>
-      <c r="O90" s="46"/>
-      <c r="P90" s="45"/>
-      <c r="Q90" s="46"/>
-      <c r="R90" s="45"/>
-      <c r="S90" s="46"/>
-      <c r="T90" s="45"/>
-      <c r="U90" s="46"/>
-      <c r="V90" s="45"/>
-      <c r="W90" s="46"/>
-      <c r="X90" s="45"/>
-      <c r="Y90" s="46"/>
-      <c r="Z90" s="45"/>
-      <c r="AA90" s="46"/>
-      <c r="AB90" s="45"/>
-      <c r="AC90" s="46"/>
-      <c r="AD90" s="45"/>
-      <c r="AE90" s="46"/>
-      <c r="AF90" s="45"/>
-      <c r="AG90" s="46"/>
-      <c r="AH90" s="45"/>
-      <c r="AI90" s="46"/>
-      <c r="AJ90" s="45"/>
-      <c r="AK90" s="46"/>
-      <c r="AL90" s="45"/>
-      <c r="AM90" s="46"/>
-      <c r="AN90" s="45"/>
-      <c r="AO90" s="46"/>
-      <c r="AP90" s="45"/>
-      <c r="AQ90" s="45"/>
-      <c r="AR90" s="45"/>
-      <c r="AS90" s="45"/>
-      <c r="AT90" s="45"/>
-      <c r="AU90" s="46"/>
-      <c r="AV90" s="47"/>
+      <c r="B90" s="40"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="40"/>
+      <c r="E90" s="41"/>
+      <c r="F90" s="40"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="40"/>
+      <c r="I90" s="41"/>
+      <c r="J90" s="40"/>
+      <c r="K90" s="41"/>
+      <c r="L90" s="40"/>
+      <c r="M90" s="41"/>
+      <c r="N90" s="40"/>
+      <c r="O90" s="41"/>
+      <c r="P90" s="40"/>
+      <c r="Q90" s="41"/>
+      <c r="R90" s="40"/>
+      <c r="S90" s="41"/>
+      <c r="T90" s="40"/>
+      <c r="U90" s="41"/>
+      <c r="V90" s="40"/>
+      <c r="W90" s="41"/>
+      <c r="X90" s="40"/>
+      <c r="Y90" s="41"/>
+      <c r="Z90" s="40"/>
+      <c r="AA90" s="41"/>
+      <c r="AB90" s="40"/>
+      <c r="AC90" s="41"/>
+      <c r="AD90" s="40"/>
+      <c r="AE90" s="41"/>
+      <c r="AF90" s="40"/>
+      <c r="AG90" s="41"/>
+      <c r="AH90" s="40"/>
+      <c r="AI90" s="41"/>
+      <c r="AJ90" s="40"/>
+      <c r="AK90" s="41"/>
+      <c r="AL90" s="40"/>
+      <c r="AM90" s="41"/>
+      <c r="AN90" s="40"/>
+      <c r="AO90" s="41"/>
+      <c r="AP90" s="40"/>
+      <c r="AQ90" s="40"/>
+      <c r="AR90" s="40"/>
+      <c r="AS90" s="40"/>
+      <c r="AT90" s="40"/>
+      <c r="AU90" s="41"/>
+      <c r="AV90" s="42"/>
       <c r="AW90" s="8"/>
       <c r="AX90" s="8"/>
     </row>
@@ -14772,56 +14784,56 @@
       <c r="AX97" s="12"/>
     </row>
     <row r="98" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="44" t="s">
+      <c r="A98" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="B98" s="45"/>
-      <c r="C98" s="46"/>
-      <c r="D98" s="45"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="45"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="45"/>
-      <c r="I98" s="46"/>
-      <c r="J98" s="45"/>
-      <c r="K98" s="46"/>
-      <c r="L98" s="45"/>
-      <c r="M98" s="46"/>
-      <c r="N98" s="45"/>
-      <c r="O98" s="46"/>
-      <c r="P98" s="45"/>
-      <c r="Q98" s="46"/>
-      <c r="R98" s="45"/>
-      <c r="S98" s="46"/>
-      <c r="T98" s="45"/>
-      <c r="U98" s="46"/>
-      <c r="V98" s="45"/>
-      <c r="W98" s="46"/>
-      <c r="X98" s="45"/>
-      <c r="Y98" s="46"/>
-      <c r="Z98" s="45"/>
-      <c r="AA98" s="46"/>
-      <c r="AB98" s="45"/>
-      <c r="AC98" s="46"/>
-      <c r="AD98" s="45"/>
-      <c r="AE98" s="46"/>
-      <c r="AF98" s="45"/>
-      <c r="AG98" s="46"/>
-      <c r="AH98" s="45"/>
-      <c r="AI98" s="46"/>
-      <c r="AJ98" s="45"/>
-      <c r="AK98" s="46"/>
-      <c r="AL98" s="45"/>
-      <c r="AM98" s="46"/>
-      <c r="AN98" s="45"/>
-      <c r="AO98" s="46"/>
-      <c r="AP98" s="45"/>
-      <c r="AQ98" s="45"/>
-      <c r="AR98" s="45"/>
-      <c r="AS98" s="45"/>
-      <c r="AT98" s="45"/>
-      <c r="AU98" s="46"/>
-      <c r="AV98" s="47"/>
+      <c r="B98" s="40"/>
+      <c r="C98" s="41"/>
+      <c r="D98" s="40"/>
+      <c r="E98" s="41"/>
+      <c r="F98" s="40"/>
+      <c r="G98" s="41"/>
+      <c r="H98" s="40"/>
+      <c r="I98" s="41"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="41"/>
+      <c r="L98" s="40"/>
+      <c r="M98" s="41"/>
+      <c r="N98" s="40"/>
+      <c r="O98" s="41"/>
+      <c r="P98" s="40"/>
+      <c r="Q98" s="41"/>
+      <c r="R98" s="40"/>
+      <c r="S98" s="41"/>
+      <c r="T98" s="40"/>
+      <c r="U98" s="41"/>
+      <c r="V98" s="40"/>
+      <c r="W98" s="41"/>
+      <c r="X98" s="40"/>
+      <c r="Y98" s="41"/>
+      <c r="Z98" s="40"/>
+      <c r="AA98" s="41"/>
+      <c r="AB98" s="40"/>
+      <c r="AC98" s="41"/>
+      <c r="AD98" s="40"/>
+      <c r="AE98" s="41"/>
+      <c r="AF98" s="40"/>
+      <c r="AG98" s="41"/>
+      <c r="AH98" s="40"/>
+      <c r="AI98" s="41"/>
+      <c r="AJ98" s="40"/>
+      <c r="AK98" s="41"/>
+      <c r="AL98" s="40"/>
+      <c r="AM98" s="41"/>
+      <c r="AN98" s="40"/>
+      <c r="AO98" s="41"/>
+      <c r="AP98" s="40"/>
+      <c r="AQ98" s="40"/>
+      <c r="AR98" s="40"/>
+      <c r="AS98" s="40"/>
+      <c r="AT98" s="40"/>
+      <c r="AU98" s="41"/>
+      <c r="AV98" s="42"/>
       <c r="AW98" s="8"/>
       <c r="AX98" s="8"/>
     </row>
@@ -15928,56 +15940,56 @@
       <c r="AX105" s="12"/>
     </row>
     <row r="106" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="44" t="s">
+      <c r="A106" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B106" s="45"/>
-      <c r="C106" s="46"/>
-      <c r="D106" s="45"/>
-      <c r="E106" s="46"/>
-      <c r="F106" s="45"/>
-      <c r="G106" s="46"/>
-      <c r="H106" s="45"/>
-      <c r="I106" s="46"/>
-      <c r="J106" s="45"/>
-      <c r="K106" s="46"/>
-      <c r="L106" s="45"/>
-      <c r="M106" s="46"/>
-      <c r="N106" s="45"/>
-      <c r="O106" s="46"/>
-      <c r="P106" s="45"/>
-      <c r="Q106" s="46"/>
-      <c r="R106" s="45"/>
-      <c r="S106" s="46"/>
-      <c r="T106" s="45"/>
-      <c r="U106" s="46"/>
-      <c r="V106" s="45"/>
-      <c r="W106" s="46"/>
-      <c r="X106" s="45"/>
-      <c r="Y106" s="46"/>
-      <c r="Z106" s="45"/>
-      <c r="AA106" s="46"/>
-      <c r="AB106" s="45"/>
-      <c r="AC106" s="46"/>
-      <c r="AD106" s="45"/>
-      <c r="AE106" s="46"/>
-      <c r="AF106" s="45"/>
-      <c r="AG106" s="46"/>
-      <c r="AH106" s="45"/>
-      <c r="AI106" s="46"/>
-      <c r="AJ106" s="45"/>
-      <c r="AK106" s="46"/>
-      <c r="AL106" s="45"/>
-      <c r="AM106" s="46"/>
-      <c r="AN106" s="45"/>
-      <c r="AO106" s="46"/>
-      <c r="AP106" s="45"/>
-      <c r="AQ106" s="45"/>
-      <c r="AR106" s="45"/>
-      <c r="AS106" s="45"/>
-      <c r="AT106" s="45"/>
-      <c r="AU106" s="46"/>
-      <c r="AV106" s="47"/>
+      <c r="B106" s="40"/>
+      <c r="C106" s="41"/>
+      <c r="D106" s="40"/>
+      <c r="E106" s="41"/>
+      <c r="F106" s="40"/>
+      <c r="G106" s="41"/>
+      <c r="H106" s="40"/>
+      <c r="I106" s="41"/>
+      <c r="J106" s="40"/>
+      <c r="K106" s="41"/>
+      <c r="L106" s="40"/>
+      <c r="M106" s="41"/>
+      <c r="N106" s="40"/>
+      <c r="O106" s="41"/>
+      <c r="P106" s="40"/>
+      <c r="Q106" s="41"/>
+      <c r="R106" s="40"/>
+      <c r="S106" s="41"/>
+      <c r="T106" s="40"/>
+      <c r="U106" s="41"/>
+      <c r="V106" s="40"/>
+      <c r="W106" s="41"/>
+      <c r="X106" s="40"/>
+      <c r="Y106" s="41"/>
+      <c r="Z106" s="40"/>
+      <c r="AA106" s="41"/>
+      <c r="AB106" s="40"/>
+      <c r="AC106" s="41"/>
+      <c r="AD106" s="40"/>
+      <c r="AE106" s="41"/>
+      <c r="AF106" s="40"/>
+      <c r="AG106" s="41"/>
+      <c r="AH106" s="40"/>
+      <c r="AI106" s="41"/>
+      <c r="AJ106" s="40"/>
+      <c r="AK106" s="41"/>
+      <c r="AL106" s="40"/>
+      <c r="AM106" s="41"/>
+      <c r="AN106" s="40"/>
+      <c r="AO106" s="41"/>
+      <c r="AP106" s="40"/>
+      <c r="AQ106" s="40"/>
+      <c r="AR106" s="40"/>
+      <c r="AS106" s="40"/>
+      <c r="AT106" s="40"/>
+      <c r="AU106" s="41"/>
+      <c r="AV106" s="42"/>
       <c r="AW106" s="8"/>
       <c r="AX106" s="8"/>
     </row>
@@ -16797,107 +16809,107 @@
       <c r="A113" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="49"/>
-      <c r="C113" s="50"/>
-      <c r="D113" s="49"/>
-      <c r="E113" s="50"/>
-      <c r="F113" s="49"/>
-      <c r="G113" s="50"/>
-      <c r="H113" s="49"/>
-      <c r="I113" s="50"/>
-      <c r="J113" s="49"/>
-      <c r="K113" s="50"/>
-      <c r="L113" s="49"/>
-      <c r="M113" s="50"/>
-      <c r="N113" s="49"/>
-      <c r="O113" s="50"/>
-      <c r="P113" s="49"/>
-      <c r="Q113" s="50"/>
-      <c r="R113" s="49"/>
-      <c r="S113" s="50"/>
-      <c r="T113" s="49"/>
-      <c r="U113" s="50"/>
-      <c r="V113" s="49"/>
-      <c r="W113" s="50"/>
-      <c r="X113" s="49"/>
-      <c r="Y113" s="50"/>
-      <c r="Z113" s="49"/>
-      <c r="AA113" s="50"/>
-      <c r="AB113" s="49"/>
-      <c r="AC113" s="50"/>
-      <c r="AD113" s="49"/>
-      <c r="AE113" s="50"/>
-      <c r="AF113" s="49"/>
-      <c r="AG113" s="50"/>
-      <c r="AH113" s="49"/>
-      <c r="AI113" s="50"/>
-      <c r="AJ113" s="49"/>
-      <c r="AK113" s="50"/>
-      <c r="AL113" s="49"/>
-      <c r="AM113" s="50"/>
-      <c r="AN113" s="49"/>
-      <c r="AO113" s="50"/>
-      <c r="AP113" s="49"/>
-      <c r="AQ113" s="49"/>
-      <c r="AR113" s="49"/>
-      <c r="AS113" s="49"/>
-      <c r="AT113" s="49"/>
-      <c r="AU113" s="50"/>
-      <c r="AV113" s="43"/>
+      <c r="B113" s="53"/>
+      <c r="C113" s="54"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="54"/>
+      <c r="F113" s="53"/>
+      <c r="G113" s="54"/>
+      <c r="H113" s="53"/>
+      <c r="I113" s="54"/>
+      <c r="J113" s="53"/>
+      <c r="K113" s="54"/>
+      <c r="L113" s="53"/>
+      <c r="M113" s="54"/>
+      <c r="N113" s="53"/>
+      <c r="O113" s="54"/>
+      <c r="P113" s="53"/>
+      <c r="Q113" s="54"/>
+      <c r="R113" s="53"/>
+      <c r="S113" s="54"/>
+      <c r="T113" s="53"/>
+      <c r="U113" s="54"/>
+      <c r="V113" s="53"/>
+      <c r="W113" s="54"/>
+      <c r="X113" s="53"/>
+      <c r="Y113" s="54"/>
+      <c r="Z113" s="53"/>
+      <c r="AA113" s="54"/>
+      <c r="AB113" s="53"/>
+      <c r="AC113" s="54"/>
+      <c r="AD113" s="53"/>
+      <c r="AE113" s="54"/>
+      <c r="AF113" s="53"/>
+      <c r="AG113" s="54"/>
+      <c r="AH113" s="53"/>
+      <c r="AI113" s="54"/>
+      <c r="AJ113" s="53"/>
+      <c r="AK113" s="54"/>
+      <c r="AL113" s="53"/>
+      <c r="AM113" s="54"/>
+      <c r="AN113" s="53"/>
+      <c r="AO113" s="54"/>
+      <c r="AP113" s="53"/>
+      <c r="AQ113" s="53"/>
+      <c r="AR113" s="53"/>
+      <c r="AS113" s="53"/>
+      <c r="AT113" s="53"/>
+      <c r="AU113" s="54"/>
+      <c r="AV113" s="47"/>
       <c r="AW113" s="7"/>
       <c r="AX113" s="7"/>
     </row>
     <row r="114" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="44" t="s">
+      <c r="A114" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="B114" s="45"/>
-      <c r="C114" s="46"/>
-      <c r="D114" s="45"/>
-      <c r="E114" s="46"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="46"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="46"/>
-      <c r="J114" s="45"/>
-      <c r="K114" s="46"/>
-      <c r="L114" s="45"/>
-      <c r="M114" s="46"/>
-      <c r="N114" s="45"/>
-      <c r="O114" s="46"/>
-      <c r="P114" s="45"/>
-      <c r="Q114" s="46"/>
-      <c r="R114" s="45"/>
-      <c r="S114" s="46"/>
-      <c r="T114" s="45"/>
-      <c r="U114" s="46"/>
-      <c r="V114" s="45"/>
-      <c r="W114" s="46"/>
-      <c r="X114" s="45"/>
-      <c r="Y114" s="46"/>
-      <c r="Z114" s="45"/>
-      <c r="AA114" s="46"/>
-      <c r="AB114" s="45"/>
-      <c r="AC114" s="46"/>
-      <c r="AD114" s="45"/>
-      <c r="AE114" s="46"/>
-      <c r="AF114" s="45"/>
-      <c r="AG114" s="46"/>
-      <c r="AH114" s="45"/>
-      <c r="AI114" s="46"/>
-      <c r="AJ114" s="45"/>
-      <c r="AK114" s="46"/>
-      <c r="AL114" s="45"/>
-      <c r="AM114" s="46"/>
-      <c r="AN114" s="45"/>
-      <c r="AO114" s="46"/>
-      <c r="AP114" s="45"/>
-      <c r="AQ114" s="45"/>
-      <c r="AR114" s="45"/>
-      <c r="AS114" s="45"/>
-      <c r="AT114" s="45"/>
-      <c r="AU114" s="46"/>
-      <c r="AV114" s="47"/>
+      <c r="B114" s="40"/>
+      <c r="C114" s="41"/>
+      <c r="D114" s="40"/>
+      <c r="E114" s="41"/>
+      <c r="F114" s="40"/>
+      <c r="G114" s="41"/>
+      <c r="H114" s="40"/>
+      <c r="I114" s="41"/>
+      <c r="J114" s="40"/>
+      <c r="K114" s="41"/>
+      <c r="L114" s="40"/>
+      <c r="M114" s="41"/>
+      <c r="N114" s="40"/>
+      <c r="O114" s="41"/>
+      <c r="P114" s="40"/>
+      <c r="Q114" s="41"/>
+      <c r="R114" s="40"/>
+      <c r="S114" s="41"/>
+      <c r="T114" s="40"/>
+      <c r="U114" s="41"/>
+      <c r="V114" s="40"/>
+      <c r="W114" s="41"/>
+      <c r="X114" s="40"/>
+      <c r="Y114" s="41"/>
+      <c r="Z114" s="40"/>
+      <c r="AA114" s="41"/>
+      <c r="AB114" s="40"/>
+      <c r="AC114" s="41"/>
+      <c r="AD114" s="40"/>
+      <c r="AE114" s="41"/>
+      <c r="AF114" s="40"/>
+      <c r="AG114" s="41"/>
+      <c r="AH114" s="40"/>
+      <c r="AI114" s="41"/>
+      <c r="AJ114" s="40"/>
+      <c r="AK114" s="41"/>
+      <c r="AL114" s="40"/>
+      <c r="AM114" s="41"/>
+      <c r="AN114" s="40"/>
+      <c r="AO114" s="41"/>
+      <c r="AP114" s="40"/>
+      <c r="AQ114" s="40"/>
+      <c r="AR114" s="40"/>
+      <c r="AS114" s="40"/>
+      <c r="AT114" s="40"/>
+      <c r="AU114" s="41"/>
+      <c r="AV114" s="42"/>
       <c r="AW114" s="8"/>
       <c r="AX114" s="8"/>
     </row>
@@ -17090,56 +17102,56 @@
       <c r="AX116" s="12"/>
     </row>
     <row r="117" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="44" t="s">
+      <c r="A117" s="39" t="s">
         <v>131</v>
       </c>
-      <c r="B117" s="45"/>
-      <c r="C117" s="46"/>
-      <c r="D117" s="45"/>
-      <c r="E117" s="46"/>
-      <c r="F117" s="45"/>
-      <c r="G117" s="46"/>
-      <c r="H117" s="45"/>
-      <c r="I117" s="46"/>
-      <c r="J117" s="45"/>
-      <c r="K117" s="46"/>
-      <c r="L117" s="45"/>
-      <c r="M117" s="46"/>
-      <c r="N117" s="45"/>
-      <c r="O117" s="46"/>
-      <c r="P117" s="45"/>
-      <c r="Q117" s="46"/>
-      <c r="R117" s="45"/>
-      <c r="S117" s="46"/>
-      <c r="T117" s="45"/>
-      <c r="U117" s="46"/>
-      <c r="V117" s="45"/>
-      <c r="W117" s="46"/>
-      <c r="X117" s="45"/>
-      <c r="Y117" s="46"/>
-      <c r="Z117" s="45"/>
-      <c r="AA117" s="46"/>
-      <c r="AB117" s="45"/>
-      <c r="AC117" s="46"/>
-      <c r="AD117" s="45"/>
-      <c r="AE117" s="46"/>
-      <c r="AF117" s="45"/>
-      <c r="AG117" s="46"/>
-      <c r="AH117" s="45"/>
-      <c r="AI117" s="46"/>
-      <c r="AJ117" s="45"/>
-      <c r="AK117" s="46"/>
-      <c r="AL117" s="45"/>
-      <c r="AM117" s="46"/>
-      <c r="AN117" s="45"/>
-      <c r="AO117" s="46"/>
-      <c r="AP117" s="45"/>
-      <c r="AQ117" s="45"/>
-      <c r="AR117" s="45"/>
-      <c r="AS117" s="45"/>
-      <c r="AT117" s="45"/>
-      <c r="AU117" s="46"/>
-      <c r="AV117" s="47"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="40"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="40"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="41"/>
+      <c r="J117" s="40"/>
+      <c r="K117" s="41"/>
+      <c r="L117" s="40"/>
+      <c r="M117" s="41"/>
+      <c r="N117" s="40"/>
+      <c r="O117" s="41"/>
+      <c r="P117" s="40"/>
+      <c r="Q117" s="41"/>
+      <c r="R117" s="40"/>
+      <c r="S117" s="41"/>
+      <c r="T117" s="40"/>
+      <c r="U117" s="41"/>
+      <c r="V117" s="40"/>
+      <c r="W117" s="41"/>
+      <c r="X117" s="40"/>
+      <c r="Y117" s="41"/>
+      <c r="Z117" s="40"/>
+      <c r="AA117" s="41"/>
+      <c r="AB117" s="40"/>
+      <c r="AC117" s="41"/>
+      <c r="AD117" s="40"/>
+      <c r="AE117" s="41"/>
+      <c r="AF117" s="40"/>
+      <c r="AG117" s="41"/>
+      <c r="AH117" s="40"/>
+      <c r="AI117" s="41"/>
+      <c r="AJ117" s="40"/>
+      <c r="AK117" s="41"/>
+      <c r="AL117" s="40"/>
+      <c r="AM117" s="41"/>
+      <c r="AN117" s="40"/>
+      <c r="AO117" s="41"/>
+      <c r="AP117" s="40"/>
+      <c r="AQ117" s="40"/>
+      <c r="AR117" s="40"/>
+      <c r="AS117" s="40"/>
+      <c r="AT117" s="40"/>
+      <c r="AU117" s="41"/>
+      <c r="AV117" s="42"/>
       <c r="AW117" s="8"/>
       <c r="AX117" s="8"/>
     </row>
@@ -17462,56 +17474,56 @@
       <c r="AX120" s="12"/>
     </row>
     <row r="121" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="44" t="s">
+      <c r="A121" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="B121" s="45"/>
-      <c r="C121" s="46"/>
-      <c r="D121" s="45"/>
-      <c r="E121" s="46"/>
-      <c r="F121" s="45"/>
-      <c r="G121" s="46"/>
-      <c r="H121" s="45"/>
-      <c r="I121" s="46"/>
-      <c r="J121" s="45"/>
-      <c r="K121" s="46"/>
-      <c r="L121" s="45"/>
-      <c r="M121" s="46"/>
-      <c r="N121" s="45"/>
-      <c r="O121" s="46"/>
-      <c r="P121" s="45"/>
-      <c r="Q121" s="46"/>
-      <c r="R121" s="45"/>
-      <c r="S121" s="46"/>
-      <c r="T121" s="45"/>
-      <c r="U121" s="46"/>
-      <c r="V121" s="45"/>
-      <c r="W121" s="46"/>
-      <c r="X121" s="45"/>
-      <c r="Y121" s="46"/>
-      <c r="Z121" s="45"/>
-      <c r="AA121" s="46"/>
-      <c r="AB121" s="45"/>
-      <c r="AC121" s="46"/>
-      <c r="AD121" s="45"/>
-      <c r="AE121" s="46"/>
-      <c r="AF121" s="45"/>
-      <c r="AG121" s="46"/>
-      <c r="AH121" s="45"/>
-      <c r="AI121" s="46"/>
-      <c r="AJ121" s="45"/>
-      <c r="AK121" s="46"/>
-      <c r="AL121" s="45"/>
-      <c r="AM121" s="46"/>
-      <c r="AN121" s="45"/>
-      <c r="AO121" s="46"/>
-      <c r="AP121" s="45"/>
-      <c r="AQ121" s="45"/>
-      <c r="AR121" s="45"/>
-      <c r="AS121" s="45"/>
-      <c r="AT121" s="45"/>
-      <c r="AU121" s="46"/>
-      <c r="AV121" s="47"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="41"/>
+      <c r="D121" s="40"/>
+      <c r="E121" s="41"/>
+      <c r="F121" s="40"/>
+      <c r="G121" s="41"/>
+      <c r="H121" s="40"/>
+      <c r="I121" s="41"/>
+      <c r="J121" s="40"/>
+      <c r="K121" s="41"/>
+      <c r="L121" s="40"/>
+      <c r="M121" s="41"/>
+      <c r="N121" s="40"/>
+      <c r="O121" s="41"/>
+      <c r="P121" s="40"/>
+      <c r="Q121" s="41"/>
+      <c r="R121" s="40"/>
+      <c r="S121" s="41"/>
+      <c r="T121" s="40"/>
+      <c r="U121" s="41"/>
+      <c r="V121" s="40"/>
+      <c r="W121" s="41"/>
+      <c r="X121" s="40"/>
+      <c r="Y121" s="41"/>
+      <c r="Z121" s="40"/>
+      <c r="AA121" s="41"/>
+      <c r="AB121" s="40"/>
+      <c r="AC121" s="41"/>
+      <c r="AD121" s="40"/>
+      <c r="AE121" s="41"/>
+      <c r="AF121" s="40"/>
+      <c r="AG121" s="41"/>
+      <c r="AH121" s="40"/>
+      <c r="AI121" s="41"/>
+      <c r="AJ121" s="40"/>
+      <c r="AK121" s="41"/>
+      <c r="AL121" s="40"/>
+      <c r="AM121" s="41"/>
+      <c r="AN121" s="40"/>
+      <c r="AO121" s="41"/>
+      <c r="AP121" s="40"/>
+      <c r="AQ121" s="40"/>
+      <c r="AR121" s="40"/>
+      <c r="AS121" s="40"/>
+      <c r="AT121" s="40"/>
+      <c r="AU121" s="41"/>
+      <c r="AV121" s="42"/>
       <c r="AW121" s="8"/>
       <c r="AX121" s="8"/>
     </row>
@@ -17964,56 +17976,56 @@
       <c r="AX125" s="12"/>
     </row>
     <row r="126" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="44" t="s">
+      <c r="A126" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="B126" s="45"/>
-      <c r="C126" s="46"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="46"/>
-      <c r="F126" s="45"/>
-      <c r="G126" s="46"/>
-      <c r="H126" s="45"/>
-      <c r="I126" s="46"/>
-      <c r="J126" s="45"/>
-      <c r="K126" s="46"/>
-      <c r="L126" s="45"/>
-      <c r="M126" s="46"/>
-      <c r="N126" s="45"/>
-      <c r="O126" s="46"/>
-      <c r="P126" s="45"/>
-      <c r="Q126" s="46"/>
-      <c r="R126" s="45"/>
-      <c r="S126" s="46"/>
-      <c r="T126" s="45"/>
-      <c r="U126" s="46"/>
-      <c r="V126" s="45"/>
-      <c r="W126" s="46"/>
-      <c r="X126" s="45"/>
-      <c r="Y126" s="46"/>
-      <c r="Z126" s="45"/>
-      <c r="AA126" s="46"/>
-      <c r="AB126" s="45"/>
-      <c r="AC126" s="46"/>
-      <c r="AD126" s="45"/>
-      <c r="AE126" s="46"/>
-      <c r="AF126" s="45"/>
-      <c r="AG126" s="46"/>
-      <c r="AH126" s="45"/>
-      <c r="AI126" s="46"/>
-      <c r="AJ126" s="45"/>
-      <c r="AK126" s="46"/>
-      <c r="AL126" s="45"/>
-      <c r="AM126" s="46"/>
-      <c r="AN126" s="45"/>
-      <c r="AO126" s="46"/>
-      <c r="AP126" s="45"/>
-      <c r="AQ126" s="45"/>
-      <c r="AR126" s="45"/>
-      <c r="AS126" s="45"/>
-      <c r="AT126" s="45"/>
-      <c r="AU126" s="46"/>
-      <c r="AV126" s="47"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="41"/>
+      <c r="D126" s="40"/>
+      <c r="E126" s="41"/>
+      <c r="F126" s="40"/>
+      <c r="G126" s="41"/>
+      <c r="H126" s="40"/>
+      <c r="I126" s="41"/>
+      <c r="J126" s="40"/>
+      <c r="K126" s="41"/>
+      <c r="L126" s="40"/>
+      <c r="M126" s="41"/>
+      <c r="N126" s="40"/>
+      <c r="O126" s="41"/>
+      <c r="P126" s="40"/>
+      <c r="Q126" s="41"/>
+      <c r="R126" s="40"/>
+      <c r="S126" s="41"/>
+      <c r="T126" s="40"/>
+      <c r="U126" s="41"/>
+      <c r="V126" s="40"/>
+      <c r="W126" s="41"/>
+      <c r="X126" s="40"/>
+      <c r="Y126" s="41"/>
+      <c r="Z126" s="40"/>
+      <c r="AA126" s="41"/>
+      <c r="AB126" s="40"/>
+      <c r="AC126" s="41"/>
+      <c r="AD126" s="40"/>
+      <c r="AE126" s="41"/>
+      <c r="AF126" s="40"/>
+      <c r="AG126" s="41"/>
+      <c r="AH126" s="40"/>
+      <c r="AI126" s="41"/>
+      <c r="AJ126" s="40"/>
+      <c r="AK126" s="41"/>
+      <c r="AL126" s="40"/>
+      <c r="AM126" s="41"/>
+      <c r="AN126" s="40"/>
+      <c r="AO126" s="41"/>
+      <c r="AP126" s="40"/>
+      <c r="AQ126" s="40"/>
+      <c r="AR126" s="40"/>
+      <c r="AS126" s="40"/>
+      <c r="AT126" s="40"/>
+      <c r="AU126" s="41"/>
+      <c r="AV126" s="42"/>
       <c r="AW126" s="8"/>
       <c r="AX126" s="8"/>
     </row>
@@ -18466,56 +18478,56 @@
       <c r="AX130" s="12"/>
     </row>
     <row r="131" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="44" t="s">
+      <c r="A131" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="B131" s="45"/>
-      <c r="C131" s="46"/>
-      <c r="D131" s="45"/>
-      <c r="E131" s="46"/>
-      <c r="F131" s="45"/>
-      <c r="G131" s="46"/>
-      <c r="H131" s="45"/>
-      <c r="I131" s="46"/>
-      <c r="J131" s="45"/>
-      <c r="K131" s="46"/>
-      <c r="L131" s="45"/>
-      <c r="M131" s="46"/>
-      <c r="N131" s="45"/>
-      <c r="O131" s="46"/>
-      <c r="P131" s="45"/>
-      <c r="Q131" s="46"/>
-      <c r="R131" s="45"/>
-      <c r="S131" s="46"/>
-      <c r="T131" s="45"/>
-      <c r="U131" s="46"/>
-      <c r="V131" s="45"/>
-      <c r="W131" s="46"/>
-      <c r="X131" s="45"/>
-      <c r="Y131" s="46"/>
-      <c r="Z131" s="45"/>
-      <c r="AA131" s="46"/>
-      <c r="AB131" s="45"/>
-      <c r="AC131" s="46"/>
-      <c r="AD131" s="45"/>
-      <c r="AE131" s="46"/>
-      <c r="AF131" s="45"/>
-      <c r="AG131" s="46"/>
-      <c r="AH131" s="45"/>
-      <c r="AI131" s="46"/>
-      <c r="AJ131" s="45"/>
-      <c r="AK131" s="46"/>
-      <c r="AL131" s="45"/>
-      <c r="AM131" s="46"/>
-      <c r="AN131" s="45"/>
-      <c r="AO131" s="46"/>
-      <c r="AP131" s="45"/>
-      <c r="AQ131" s="45"/>
-      <c r="AR131" s="45"/>
-      <c r="AS131" s="45"/>
-      <c r="AT131" s="45"/>
-      <c r="AU131" s="46"/>
-      <c r="AV131" s="47"/>
+      <c r="B131" s="40"/>
+      <c r="C131" s="41"/>
+      <c r="D131" s="40"/>
+      <c r="E131" s="41"/>
+      <c r="F131" s="40"/>
+      <c r="G131" s="41"/>
+      <c r="H131" s="40"/>
+      <c r="I131" s="41"/>
+      <c r="J131" s="40"/>
+      <c r="K131" s="41"/>
+      <c r="L131" s="40"/>
+      <c r="M131" s="41"/>
+      <c r="N131" s="40"/>
+      <c r="O131" s="41"/>
+      <c r="P131" s="40"/>
+      <c r="Q131" s="41"/>
+      <c r="R131" s="40"/>
+      <c r="S131" s="41"/>
+      <c r="T131" s="40"/>
+      <c r="U131" s="41"/>
+      <c r="V131" s="40"/>
+      <c r="W131" s="41"/>
+      <c r="X131" s="40"/>
+      <c r="Y131" s="41"/>
+      <c r="Z131" s="40"/>
+      <c r="AA131" s="41"/>
+      <c r="AB131" s="40"/>
+      <c r="AC131" s="41"/>
+      <c r="AD131" s="40"/>
+      <c r="AE131" s="41"/>
+      <c r="AF131" s="40"/>
+      <c r="AG131" s="41"/>
+      <c r="AH131" s="40"/>
+      <c r="AI131" s="41"/>
+      <c r="AJ131" s="40"/>
+      <c r="AK131" s="41"/>
+      <c r="AL131" s="40"/>
+      <c r="AM131" s="41"/>
+      <c r="AN131" s="40"/>
+      <c r="AO131" s="41"/>
+      <c r="AP131" s="40"/>
+      <c r="AQ131" s="40"/>
+      <c r="AR131" s="40"/>
+      <c r="AS131" s="40"/>
+      <c r="AT131" s="40"/>
+      <c r="AU131" s="41"/>
+      <c r="AV131" s="42"/>
       <c r="AW131" s="8"/>
       <c r="AX131" s="8"/>
     </row>
@@ -18838,56 +18850,56 @@
       <c r="AX134" s="12"/>
     </row>
     <row r="135" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="44" t="s">
+      <c r="A135" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="B135" s="45"/>
-      <c r="C135" s="46"/>
-      <c r="D135" s="45"/>
-      <c r="E135" s="46"/>
-      <c r="F135" s="45"/>
-      <c r="G135" s="46"/>
-      <c r="H135" s="45"/>
-      <c r="I135" s="46"/>
-      <c r="J135" s="45"/>
-      <c r="K135" s="46"/>
-      <c r="L135" s="45"/>
-      <c r="M135" s="46"/>
-      <c r="N135" s="45"/>
-      <c r="O135" s="46"/>
-      <c r="P135" s="45"/>
-      <c r="Q135" s="46"/>
-      <c r="R135" s="45"/>
-      <c r="S135" s="46"/>
-      <c r="T135" s="45"/>
-      <c r="U135" s="46"/>
-      <c r="V135" s="45"/>
-      <c r="W135" s="46"/>
-      <c r="X135" s="45"/>
-      <c r="Y135" s="46"/>
-      <c r="Z135" s="45"/>
-      <c r="AA135" s="46"/>
-      <c r="AB135" s="45"/>
-      <c r="AC135" s="46"/>
-      <c r="AD135" s="45"/>
-      <c r="AE135" s="46"/>
-      <c r="AF135" s="45"/>
-      <c r="AG135" s="46"/>
-      <c r="AH135" s="45"/>
-      <c r="AI135" s="46"/>
-      <c r="AJ135" s="45"/>
-      <c r="AK135" s="46"/>
-      <c r="AL135" s="45"/>
-      <c r="AM135" s="46"/>
-      <c r="AN135" s="45"/>
-      <c r="AO135" s="46"/>
-      <c r="AP135" s="45"/>
-      <c r="AQ135" s="45"/>
-      <c r="AR135" s="45"/>
-      <c r="AS135" s="45"/>
-      <c r="AT135" s="45"/>
-      <c r="AU135" s="46"/>
-      <c r="AV135" s="47"/>
+      <c r="B135" s="40"/>
+      <c r="C135" s="41"/>
+      <c r="D135" s="40"/>
+      <c r="E135" s="41"/>
+      <c r="F135" s="40"/>
+      <c r="G135" s="41"/>
+      <c r="H135" s="40"/>
+      <c r="I135" s="41"/>
+      <c r="J135" s="40"/>
+      <c r="K135" s="41"/>
+      <c r="L135" s="40"/>
+      <c r="M135" s="41"/>
+      <c r="N135" s="40"/>
+      <c r="O135" s="41"/>
+      <c r="P135" s="40"/>
+      <c r="Q135" s="41"/>
+      <c r="R135" s="40"/>
+      <c r="S135" s="41"/>
+      <c r="T135" s="40"/>
+      <c r="U135" s="41"/>
+      <c r="V135" s="40"/>
+      <c r="W135" s="41"/>
+      <c r="X135" s="40"/>
+      <c r="Y135" s="41"/>
+      <c r="Z135" s="40"/>
+      <c r="AA135" s="41"/>
+      <c r="AB135" s="40"/>
+      <c r="AC135" s="41"/>
+      <c r="AD135" s="40"/>
+      <c r="AE135" s="41"/>
+      <c r="AF135" s="40"/>
+      <c r="AG135" s="41"/>
+      <c r="AH135" s="40"/>
+      <c r="AI135" s="41"/>
+      <c r="AJ135" s="40"/>
+      <c r="AK135" s="41"/>
+      <c r="AL135" s="40"/>
+      <c r="AM135" s="41"/>
+      <c r="AN135" s="40"/>
+      <c r="AO135" s="41"/>
+      <c r="AP135" s="40"/>
+      <c r="AQ135" s="40"/>
+      <c r="AR135" s="40"/>
+      <c r="AS135" s="40"/>
+      <c r="AT135" s="40"/>
+      <c r="AU135" s="41"/>
+      <c r="AV135" s="42"/>
       <c r="AW135" s="8"/>
       <c r="AX135" s="8"/>
     </row>
@@ -19340,56 +19352,56 @@
       <c r="AX139" s="12"/>
     </row>
     <row r="140" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="44" t="s">
+      <c r="A140" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B140" s="45"/>
-      <c r="C140" s="46"/>
-      <c r="D140" s="45"/>
-      <c r="E140" s="46"/>
-      <c r="F140" s="45"/>
-      <c r="G140" s="46"/>
-      <c r="H140" s="45"/>
-      <c r="I140" s="46"/>
-      <c r="J140" s="45"/>
-      <c r="K140" s="46"/>
-      <c r="L140" s="45"/>
-      <c r="M140" s="46"/>
-      <c r="N140" s="45"/>
-      <c r="O140" s="46"/>
-      <c r="P140" s="45"/>
-      <c r="Q140" s="46"/>
-      <c r="R140" s="45"/>
-      <c r="S140" s="46"/>
-      <c r="T140" s="45"/>
-      <c r="U140" s="46"/>
-      <c r="V140" s="45"/>
-      <c r="W140" s="46"/>
-      <c r="X140" s="45"/>
-      <c r="Y140" s="46"/>
-      <c r="Z140" s="45"/>
-      <c r="AA140" s="46"/>
-      <c r="AB140" s="45"/>
-      <c r="AC140" s="46"/>
-      <c r="AD140" s="45"/>
-      <c r="AE140" s="46"/>
-      <c r="AF140" s="45"/>
-      <c r="AG140" s="46"/>
-      <c r="AH140" s="45"/>
-      <c r="AI140" s="46"/>
-      <c r="AJ140" s="45"/>
-      <c r="AK140" s="46"/>
-      <c r="AL140" s="45"/>
-      <c r="AM140" s="46"/>
-      <c r="AN140" s="45"/>
-      <c r="AO140" s="46"/>
-      <c r="AP140" s="45"/>
-      <c r="AQ140" s="45"/>
-      <c r="AR140" s="45"/>
-      <c r="AS140" s="45"/>
-      <c r="AT140" s="45"/>
-      <c r="AU140" s="46"/>
-      <c r="AV140" s="47"/>
+      <c r="B140" s="40"/>
+      <c r="C140" s="41"/>
+      <c r="D140" s="40"/>
+      <c r="E140" s="41"/>
+      <c r="F140" s="40"/>
+      <c r="G140" s="41"/>
+      <c r="H140" s="40"/>
+      <c r="I140" s="41"/>
+      <c r="J140" s="40"/>
+      <c r="K140" s="41"/>
+      <c r="L140" s="40"/>
+      <c r="M140" s="41"/>
+      <c r="N140" s="40"/>
+      <c r="O140" s="41"/>
+      <c r="P140" s="40"/>
+      <c r="Q140" s="41"/>
+      <c r="R140" s="40"/>
+      <c r="S140" s="41"/>
+      <c r="T140" s="40"/>
+      <c r="U140" s="41"/>
+      <c r="V140" s="40"/>
+      <c r="W140" s="41"/>
+      <c r="X140" s="40"/>
+      <c r="Y140" s="41"/>
+      <c r="Z140" s="40"/>
+      <c r="AA140" s="41"/>
+      <c r="AB140" s="40"/>
+      <c r="AC140" s="41"/>
+      <c r="AD140" s="40"/>
+      <c r="AE140" s="41"/>
+      <c r="AF140" s="40"/>
+      <c r="AG140" s="41"/>
+      <c r="AH140" s="40"/>
+      <c r="AI140" s="41"/>
+      <c r="AJ140" s="40"/>
+      <c r="AK140" s="41"/>
+      <c r="AL140" s="40"/>
+      <c r="AM140" s="41"/>
+      <c r="AN140" s="40"/>
+      <c r="AO140" s="41"/>
+      <c r="AP140" s="40"/>
+      <c r="AQ140" s="40"/>
+      <c r="AR140" s="40"/>
+      <c r="AS140" s="40"/>
+      <c r="AT140" s="40"/>
+      <c r="AU140" s="41"/>
+      <c r="AV140" s="42"/>
       <c r="AW140" s="8"/>
       <c r="AX140" s="8"/>
     </row>
@@ -19773,107 +19785,107 @@
       <c r="A145" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B145" s="49"/>
-      <c r="C145" s="50"/>
-      <c r="D145" s="49"/>
-      <c r="E145" s="50"/>
-      <c r="F145" s="49"/>
-      <c r="G145" s="50"/>
-      <c r="H145" s="49"/>
-      <c r="I145" s="50"/>
-      <c r="J145" s="49"/>
-      <c r="K145" s="50"/>
-      <c r="L145" s="49"/>
-      <c r="M145" s="50"/>
-      <c r="N145" s="49"/>
-      <c r="O145" s="50"/>
-      <c r="P145" s="49"/>
-      <c r="Q145" s="50"/>
-      <c r="R145" s="49"/>
-      <c r="S145" s="50"/>
-      <c r="T145" s="49"/>
-      <c r="U145" s="50"/>
-      <c r="V145" s="49"/>
-      <c r="W145" s="50"/>
-      <c r="X145" s="49"/>
-      <c r="Y145" s="50"/>
-      <c r="Z145" s="49"/>
-      <c r="AA145" s="50"/>
-      <c r="AB145" s="49"/>
-      <c r="AC145" s="50"/>
-      <c r="AD145" s="49"/>
-      <c r="AE145" s="50"/>
-      <c r="AF145" s="49"/>
-      <c r="AG145" s="50"/>
-      <c r="AH145" s="49"/>
-      <c r="AI145" s="50"/>
-      <c r="AJ145" s="49"/>
-      <c r="AK145" s="50"/>
-      <c r="AL145" s="49"/>
-      <c r="AM145" s="50"/>
-      <c r="AN145" s="49"/>
-      <c r="AO145" s="50"/>
-      <c r="AP145" s="49"/>
-      <c r="AQ145" s="49"/>
-      <c r="AR145" s="49"/>
-      <c r="AS145" s="49"/>
-      <c r="AT145" s="49"/>
-      <c r="AU145" s="50"/>
-      <c r="AV145" s="43"/>
+      <c r="B145" s="53"/>
+      <c r="C145" s="54"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="53"/>
+      <c r="G145" s="54"/>
+      <c r="H145" s="53"/>
+      <c r="I145" s="54"/>
+      <c r="J145" s="53"/>
+      <c r="K145" s="54"/>
+      <c r="L145" s="53"/>
+      <c r="M145" s="54"/>
+      <c r="N145" s="53"/>
+      <c r="O145" s="54"/>
+      <c r="P145" s="53"/>
+      <c r="Q145" s="54"/>
+      <c r="R145" s="53"/>
+      <c r="S145" s="54"/>
+      <c r="T145" s="53"/>
+      <c r="U145" s="54"/>
+      <c r="V145" s="53"/>
+      <c r="W145" s="54"/>
+      <c r="X145" s="53"/>
+      <c r="Y145" s="54"/>
+      <c r="Z145" s="53"/>
+      <c r="AA145" s="54"/>
+      <c r="AB145" s="53"/>
+      <c r="AC145" s="54"/>
+      <c r="AD145" s="53"/>
+      <c r="AE145" s="54"/>
+      <c r="AF145" s="53"/>
+      <c r="AG145" s="54"/>
+      <c r="AH145" s="53"/>
+      <c r="AI145" s="54"/>
+      <c r="AJ145" s="53"/>
+      <c r="AK145" s="54"/>
+      <c r="AL145" s="53"/>
+      <c r="AM145" s="54"/>
+      <c r="AN145" s="53"/>
+      <c r="AO145" s="54"/>
+      <c r="AP145" s="53"/>
+      <c r="AQ145" s="53"/>
+      <c r="AR145" s="53"/>
+      <c r="AS145" s="53"/>
+      <c r="AT145" s="53"/>
+      <c r="AU145" s="54"/>
+      <c r="AV145" s="47"/>
       <c r="AW145" s="7"/>
       <c r="AX145" s="7"/>
     </row>
     <row r="146" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="44" t="s">
+      <c r="A146" s="39" t="s">
         <v>162</v>
       </c>
-      <c r="B146" s="45"/>
-      <c r="C146" s="46"/>
-      <c r="D146" s="45"/>
-      <c r="E146" s="46"/>
-      <c r="F146" s="45"/>
-      <c r="G146" s="46"/>
-      <c r="H146" s="45"/>
-      <c r="I146" s="46"/>
-      <c r="J146" s="45"/>
-      <c r="K146" s="46"/>
-      <c r="L146" s="45"/>
-      <c r="M146" s="46"/>
-      <c r="N146" s="45"/>
-      <c r="O146" s="46"/>
-      <c r="P146" s="45"/>
-      <c r="Q146" s="46"/>
-      <c r="R146" s="45"/>
-      <c r="S146" s="46"/>
-      <c r="T146" s="45"/>
-      <c r="U146" s="46"/>
-      <c r="V146" s="45"/>
-      <c r="W146" s="46"/>
-      <c r="X146" s="45"/>
-      <c r="Y146" s="46"/>
-      <c r="Z146" s="45"/>
-      <c r="AA146" s="46"/>
-      <c r="AB146" s="45"/>
-      <c r="AC146" s="46"/>
-      <c r="AD146" s="45"/>
-      <c r="AE146" s="46"/>
-      <c r="AF146" s="45"/>
-      <c r="AG146" s="46"/>
-      <c r="AH146" s="45"/>
-      <c r="AI146" s="46"/>
-      <c r="AJ146" s="45"/>
-      <c r="AK146" s="46"/>
-      <c r="AL146" s="45"/>
-      <c r="AM146" s="46"/>
-      <c r="AN146" s="45"/>
-      <c r="AO146" s="46"/>
-      <c r="AP146" s="45"/>
-      <c r="AQ146" s="45"/>
-      <c r="AR146" s="45"/>
-      <c r="AS146" s="45"/>
-      <c r="AT146" s="45"/>
-      <c r="AU146" s="46"/>
-      <c r="AV146" s="47"/>
+      <c r="B146" s="40"/>
+      <c r="C146" s="41"/>
+      <c r="D146" s="40"/>
+      <c r="E146" s="41"/>
+      <c r="F146" s="40"/>
+      <c r="G146" s="41"/>
+      <c r="H146" s="40"/>
+      <c r="I146" s="41"/>
+      <c r="J146" s="40"/>
+      <c r="K146" s="41"/>
+      <c r="L146" s="40"/>
+      <c r="M146" s="41"/>
+      <c r="N146" s="40"/>
+      <c r="O146" s="41"/>
+      <c r="P146" s="40"/>
+      <c r="Q146" s="41"/>
+      <c r="R146" s="40"/>
+      <c r="S146" s="41"/>
+      <c r="T146" s="40"/>
+      <c r="U146" s="41"/>
+      <c r="V146" s="40"/>
+      <c r="W146" s="41"/>
+      <c r="X146" s="40"/>
+      <c r="Y146" s="41"/>
+      <c r="Z146" s="40"/>
+      <c r="AA146" s="41"/>
+      <c r="AB146" s="40"/>
+      <c r="AC146" s="41"/>
+      <c r="AD146" s="40"/>
+      <c r="AE146" s="41"/>
+      <c r="AF146" s="40"/>
+      <c r="AG146" s="41"/>
+      <c r="AH146" s="40"/>
+      <c r="AI146" s="41"/>
+      <c r="AJ146" s="40"/>
+      <c r="AK146" s="41"/>
+      <c r="AL146" s="40"/>
+      <c r="AM146" s="41"/>
+      <c r="AN146" s="40"/>
+      <c r="AO146" s="41"/>
+      <c r="AP146" s="40"/>
+      <c r="AQ146" s="40"/>
+      <c r="AR146" s="40"/>
+      <c r="AS146" s="40"/>
+      <c r="AT146" s="40"/>
+      <c r="AU146" s="41"/>
+      <c r="AV146" s="42"/>
       <c r="AW146" s="8"/>
       <c r="AX146" s="8"/>
     </row>
@@ -20196,56 +20208,56 @@
       <c r="AX149" s="12"/>
     </row>
     <row r="150" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="44" t="s">
+      <c r="A150" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="B150" s="45"/>
-      <c r="C150" s="46"/>
-      <c r="D150" s="45"/>
-      <c r="E150" s="46"/>
-      <c r="F150" s="45"/>
-      <c r="G150" s="46"/>
-      <c r="H150" s="45"/>
-      <c r="I150" s="46"/>
-      <c r="J150" s="45"/>
-      <c r="K150" s="46"/>
-      <c r="L150" s="45"/>
-      <c r="M150" s="46"/>
-      <c r="N150" s="45"/>
-      <c r="O150" s="46"/>
-      <c r="P150" s="45"/>
-      <c r="Q150" s="46"/>
-      <c r="R150" s="45"/>
-      <c r="S150" s="46"/>
-      <c r="T150" s="45"/>
-      <c r="U150" s="46"/>
-      <c r="V150" s="45"/>
-      <c r="W150" s="46"/>
-      <c r="X150" s="45"/>
-      <c r="Y150" s="46"/>
-      <c r="Z150" s="45"/>
-      <c r="AA150" s="46"/>
-      <c r="AB150" s="45"/>
-      <c r="AC150" s="46"/>
-      <c r="AD150" s="45"/>
-      <c r="AE150" s="46"/>
-      <c r="AF150" s="45"/>
-      <c r="AG150" s="46"/>
-      <c r="AH150" s="45"/>
-      <c r="AI150" s="46"/>
-      <c r="AJ150" s="45"/>
-      <c r="AK150" s="46"/>
-      <c r="AL150" s="45"/>
-      <c r="AM150" s="46"/>
-      <c r="AN150" s="45"/>
-      <c r="AO150" s="46"/>
-      <c r="AP150" s="45"/>
-      <c r="AQ150" s="45"/>
-      <c r="AR150" s="45"/>
-      <c r="AS150" s="45"/>
-      <c r="AT150" s="45"/>
-      <c r="AU150" s="46"/>
-      <c r="AV150" s="47"/>
+      <c r="B150" s="40"/>
+      <c r="C150" s="41"/>
+      <c r="D150" s="40"/>
+      <c r="E150" s="41"/>
+      <c r="F150" s="40"/>
+      <c r="G150" s="41"/>
+      <c r="H150" s="40"/>
+      <c r="I150" s="41"/>
+      <c r="J150" s="40"/>
+      <c r="K150" s="41"/>
+      <c r="L150" s="40"/>
+      <c r="M150" s="41"/>
+      <c r="N150" s="40"/>
+      <c r="O150" s="41"/>
+      <c r="P150" s="40"/>
+      <c r="Q150" s="41"/>
+      <c r="R150" s="40"/>
+      <c r="S150" s="41"/>
+      <c r="T150" s="40"/>
+      <c r="U150" s="41"/>
+      <c r="V150" s="40"/>
+      <c r="W150" s="41"/>
+      <c r="X150" s="40"/>
+      <c r="Y150" s="41"/>
+      <c r="Z150" s="40"/>
+      <c r="AA150" s="41"/>
+      <c r="AB150" s="40"/>
+      <c r="AC150" s="41"/>
+      <c r="AD150" s="40"/>
+      <c r="AE150" s="41"/>
+      <c r="AF150" s="40"/>
+      <c r="AG150" s="41"/>
+      <c r="AH150" s="40"/>
+      <c r="AI150" s="41"/>
+      <c r="AJ150" s="40"/>
+      <c r="AK150" s="41"/>
+      <c r="AL150" s="40"/>
+      <c r="AM150" s="41"/>
+      <c r="AN150" s="40"/>
+      <c r="AO150" s="41"/>
+      <c r="AP150" s="40"/>
+      <c r="AQ150" s="40"/>
+      <c r="AR150" s="40"/>
+      <c r="AS150" s="40"/>
+      <c r="AT150" s="40"/>
+      <c r="AU150" s="41"/>
+      <c r="AV150" s="42"/>
       <c r="AW150" s="8"/>
       <c r="AX150" s="8"/>
     </row>
@@ -20438,56 +20450,56 @@
       <c r="AX152" s="12"/>
     </row>
     <row r="153" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="44" t="s">
+      <c r="A153" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="B153" s="45"/>
-      <c r="C153" s="46"/>
-      <c r="D153" s="45"/>
-      <c r="E153" s="46"/>
-      <c r="F153" s="45"/>
-      <c r="G153" s="46"/>
-      <c r="H153" s="45"/>
-      <c r="I153" s="46"/>
-      <c r="J153" s="45"/>
-      <c r="K153" s="46"/>
-      <c r="L153" s="45"/>
-      <c r="M153" s="46"/>
-      <c r="N153" s="45"/>
-      <c r="O153" s="46"/>
-      <c r="P153" s="45"/>
-      <c r="Q153" s="46"/>
-      <c r="R153" s="45"/>
-      <c r="S153" s="46"/>
-      <c r="T153" s="45"/>
-      <c r="U153" s="46"/>
-      <c r="V153" s="45"/>
-      <c r="W153" s="46"/>
-      <c r="X153" s="45"/>
-      <c r="Y153" s="46"/>
-      <c r="Z153" s="45"/>
-      <c r="AA153" s="46"/>
-      <c r="AB153" s="45"/>
-      <c r="AC153" s="46"/>
-      <c r="AD153" s="45"/>
-      <c r="AE153" s="46"/>
-      <c r="AF153" s="45"/>
-      <c r="AG153" s="46"/>
-      <c r="AH153" s="45"/>
-      <c r="AI153" s="46"/>
-      <c r="AJ153" s="45"/>
-      <c r="AK153" s="46"/>
-      <c r="AL153" s="45"/>
-      <c r="AM153" s="46"/>
-      <c r="AN153" s="45"/>
-      <c r="AO153" s="46"/>
-      <c r="AP153" s="45"/>
-      <c r="AQ153" s="45"/>
-      <c r="AR153" s="45"/>
-      <c r="AS153" s="45"/>
-      <c r="AT153" s="45"/>
-      <c r="AU153" s="46"/>
-      <c r="AV153" s="47"/>
+      <c r="B153" s="40"/>
+      <c r="C153" s="41"/>
+      <c r="D153" s="40"/>
+      <c r="E153" s="41"/>
+      <c r="F153" s="40"/>
+      <c r="G153" s="41"/>
+      <c r="H153" s="40"/>
+      <c r="I153" s="41"/>
+      <c r="J153" s="40"/>
+      <c r="K153" s="41"/>
+      <c r="L153" s="40"/>
+      <c r="M153" s="41"/>
+      <c r="N153" s="40"/>
+      <c r="O153" s="41"/>
+      <c r="P153" s="40"/>
+      <c r="Q153" s="41"/>
+      <c r="R153" s="40"/>
+      <c r="S153" s="41"/>
+      <c r="T153" s="40"/>
+      <c r="U153" s="41"/>
+      <c r="V153" s="40"/>
+      <c r="W153" s="41"/>
+      <c r="X153" s="40"/>
+      <c r="Y153" s="41"/>
+      <c r="Z153" s="40"/>
+      <c r="AA153" s="41"/>
+      <c r="AB153" s="40"/>
+      <c r="AC153" s="41"/>
+      <c r="AD153" s="40"/>
+      <c r="AE153" s="41"/>
+      <c r="AF153" s="40"/>
+      <c r="AG153" s="41"/>
+      <c r="AH153" s="40"/>
+      <c r="AI153" s="41"/>
+      <c r="AJ153" s="40"/>
+      <c r="AK153" s="41"/>
+      <c r="AL153" s="40"/>
+      <c r="AM153" s="41"/>
+      <c r="AN153" s="40"/>
+      <c r="AO153" s="41"/>
+      <c r="AP153" s="40"/>
+      <c r="AQ153" s="40"/>
+      <c r="AR153" s="40"/>
+      <c r="AS153" s="40"/>
+      <c r="AT153" s="40"/>
+      <c r="AU153" s="41"/>
+      <c r="AV153" s="42"/>
       <c r="AW153" s="8"/>
       <c r="AX153" s="8"/>
     </row>
@@ -20810,56 +20822,56 @@
       <c r="AX156" s="12"/>
     </row>
     <row r="157" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="44" t="s">
+      <c r="A157" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="B157" s="45"/>
-      <c r="C157" s="46"/>
-      <c r="D157" s="45"/>
-      <c r="E157" s="46"/>
-      <c r="F157" s="45"/>
-      <c r="G157" s="46"/>
-      <c r="H157" s="45"/>
-      <c r="I157" s="46"/>
-      <c r="J157" s="45"/>
-      <c r="K157" s="46"/>
-      <c r="L157" s="45"/>
-      <c r="M157" s="46"/>
-      <c r="N157" s="45"/>
-      <c r="O157" s="46"/>
-      <c r="P157" s="45"/>
-      <c r="Q157" s="46"/>
-      <c r="R157" s="45"/>
-      <c r="S157" s="46"/>
-      <c r="T157" s="45"/>
-      <c r="U157" s="46"/>
-      <c r="V157" s="45"/>
-      <c r="W157" s="46"/>
-      <c r="X157" s="45"/>
-      <c r="Y157" s="46"/>
-      <c r="Z157" s="45"/>
-      <c r="AA157" s="46"/>
-      <c r="AB157" s="45"/>
-      <c r="AC157" s="46"/>
-      <c r="AD157" s="45"/>
-      <c r="AE157" s="46"/>
-      <c r="AF157" s="45"/>
-      <c r="AG157" s="46"/>
-      <c r="AH157" s="45"/>
-      <c r="AI157" s="46"/>
-      <c r="AJ157" s="45"/>
-      <c r="AK157" s="46"/>
-      <c r="AL157" s="45"/>
-      <c r="AM157" s="46"/>
-      <c r="AN157" s="45"/>
-      <c r="AO157" s="46"/>
-      <c r="AP157" s="45"/>
-      <c r="AQ157" s="45"/>
-      <c r="AR157" s="45"/>
-      <c r="AS157" s="45"/>
-      <c r="AT157" s="45"/>
-      <c r="AU157" s="46"/>
-      <c r="AV157" s="47"/>
+      <c r="B157" s="40"/>
+      <c r="C157" s="41"/>
+      <c r="D157" s="40"/>
+      <c r="E157" s="41"/>
+      <c r="F157" s="40"/>
+      <c r="G157" s="41"/>
+      <c r="H157" s="40"/>
+      <c r="I157" s="41"/>
+      <c r="J157" s="40"/>
+      <c r="K157" s="41"/>
+      <c r="L157" s="40"/>
+      <c r="M157" s="41"/>
+      <c r="N157" s="40"/>
+      <c r="O157" s="41"/>
+      <c r="P157" s="40"/>
+      <c r="Q157" s="41"/>
+      <c r="R157" s="40"/>
+      <c r="S157" s="41"/>
+      <c r="T157" s="40"/>
+      <c r="U157" s="41"/>
+      <c r="V157" s="40"/>
+      <c r="W157" s="41"/>
+      <c r="X157" s="40"/>
+      <c r="Y157" s="41"/>
+      <c r="Z157" s="40"/>
+      <c r="AA157" s="41"/>
+      <c r="AB157" s="40"/>
+      <c r="AC157" s="41"/>
+      <c r="AD157" s="40"/>
+      <c r="AE157" s="41"/>
+      <c r="AF157" s="40"/>
+      <c r="AG157" s="41"/>
+      <c r="AH157" s="40"/>
+      <c r="AI157" s="41"/>
+      <c r="AJ157" s="40"/>
+      <c r="AK157" s="41"/>
+      <c r="AL157" s="40"/>
+      <c r="AM157" s="41"/>
+      <c r="AN157" s="40"/>
+      <c r="AO157" s="41"/>
+      <c r="AP157" s="40"/>
+      <c r="AQ157" s="40"/>
+      <c r="AR157" s="40"/>
+      <c r="AS157" s="40"/>
+      <c r="AT157" s="40"/>
+      <c r="AU157" s="41"/>
+      <c r="AV157" s="42"/>
       <c r="AW157" s="8"/>
       <c r="AX157" s="8"/>
     </row>
@@ -21373,107 +21385,107 @@
       <c r="A163" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="B163" s="49"/>
-      <c r="C163" s="50"/>
-      <c r="D163" s="49"/>
-      <c r="E163" s="50"/>
-      <c r="F163" s="49"/>
-      <c r="G163" s="50"/>
-      <c r="H163" s="49"/>
-      <c r="I163" s="50"/>
-      <c r="J163" s="49"/>
-      <c r="K163" s="50"/>
-      <c r="L163" s="49"/>
-      <c r="M163" s="50"/>
-      <c r="N163" s="49"/>
-      <c r="O163" s="50"/>
-      <c r="P163" s="49"/>
-      <c r="Q163" s="50"/>
-      <c r="R163" s="49"/>
-      <c r="S163" s="50"/>
-      <c r="T163" s="49"/>
-      <c r="U163" s="50"/>
-      <c r="V163" s="49"/>
-      <c r="W163" s="50"/>
-      <c r="X163" s="49"/>
-      <c r="Y163" s="50"/>
-      <c r="Z163" s="49"/>
-      <c r="AA163" s="50"/>
-      <c r="AB163" s="49"/>
-      <c r="AC163" s="50"/>
-      <c r="AD163" s="49"/>
-      <c r="AE163" s="50"/>
-      <c r="AF163" s="49"/>
-      <c r="AG163" s="50"/>
-      <c r="AH163" s="49"/>
-      <c r="AI163" s="50"/>
-      <c r="AJ163" s="49"/>
-      <c r="AK163" s="50"/>
-      <c r="AL163" s="49"/>
-      <c r="AM163" s="50"/>
-      <c r="AN163" s="49"/>
-      <c r="AO163" s="50"/>
-      <c r="AP163" s="49"/>
-      <c r="AQ163" s="49"/>
-      <c r="AR163" s="49"/>
-      <c r="AS163" s="49"/>
-      <c r="AT163" s="49"/>
-      <c r="AU163" s="50"/>
-      <c r="AV163" s="43"/>
+      <c r="B163" s="53"/>
+      <c r="C163" s="54"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="54"/>
+      <c r="F163" s="53"/>
+      <c r="G163" s="54"/>
+      <c r="H163" s="53"/>
+      <c r="I163" s="54"/>
+      <c r="J163" s="53"/>
+      <c r="K163" s="54"/>
+      <c r="L163" s="53"/>
+      <c r="M163" s="54"/>
+      <c r="N163" s="53"/>
+      <c r="O163" s="54"/>
+      <c r="P163" s="53"/>
+      <c r="Q163" s="54"/>
+      <c r="R163" s="53"/>
+      <c r="S163" s="54"/>
+      <c r="T163" s="53"/>
+      <c r="U163" s="54"/>
+      <c r="V163" s="53"/>
+      <c r="W163" s="54"/>
+      <c r="X163" s="53"/>
+      <c r="Y163" s="54"/>
+      <c r="Z163" s="53"/>
+      <c r="AA163" s="54"/>
+      <c r="AB163" s="53"/>
+      <c r="AC163" s="54"/>
+      <c r="AD163" s="53"/>
+      <c r="AE163" s="54"/>
+      <c r="AF163" s="53"/>
+      <c r="AG163" s="54"/>
+      <c r="AH163" s="53"/>
+      <c r="AI163" s="54"/>
+      <c r="AJ163" s="53"/>
+      <c r="AK163" s="54"/>
+      <c r="AL163" s="53"/>
+      <c r="AM163" s="54"/>
+      <c r="AN163" s="53"/>
+      <c r="AO163" s="54"/>
+      <c r="AP163" s="53"/>
+      <c r="AQ163" s="53"/>
+      <c r="AR163" s="53"/>
+      <c r="AS163" s="53"/>
+      <c r="AT163" s="53"/>
+      <c r="AU163" s="54"/>
+      <c r="AV163" s="47"/>
       <c r="AW163" s="7"/>
       <c r="AX163" s="7"/>
     </row>
     <row r="164" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="44" t="s">
+      <c r="A164" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="B164" s="45"/>
-      <c r="C164" s="46"/>
-      <c r="D164" s="45"/>
-      <c r="E164" s="46"/>
-      <c r="F164" s="45"/>
-      <c r="G164" s="46"/>
-      <c r="H164" s="45"/>
-      <c r="I164" s="46"/>
-      <c r="J164" s="45"/>
-      <c r="K164" s="46"/>
-      <c r="L164" s="45"/>
-      <c r="M164" s="46"/>
-      <c r="N164" s="45"/>
-      <c r="O164" s="46"/>
-      <c r="P164" s="45"/>
-      <c r="Q164" s="46"/>
-      <c r="R164" s="45"/>
-      <c r="S164" s="46"/>
-      <c r="T164" s="45"/>
-      <c r="U164" s="46"/>
-      <c r="V164" s="45"/>
-      <c r="W164" s="46"/>
-      <c r="X164" s="45"/>
-      <c r="Y164" s="46"/>
-      <c r="Z164" s="45"/>
-      <c r="AA164" s="46"/>
-      <c r="AB164" s="45"/>
-      <c r="AC164" s="46"/>
-      <c r="AD164" s="45"/>
-      <c r="AE164" s="46"/>
-      <c r="AF164" s="45"/>
-      <c r="AG164" s="46"/>
-      <c r="AH164" s="45"/>
-      <c r="AI164" s="46"/>
-      <c r="AJ164" s="45"/>
-      <c r="AK164" s="46"/>
-      <c r="AL164" s="45"/>
-      <c r="AM164" s="46"/>
-      <c r="AN164" s="45"/>
-      <c r="AO164" s="46"/>
-      <c r="AP164" s="45"/>
-      <c r="AQ164" s="45"/>
-      <c r="AR164" s="45"/>
-      <c r="AS164" s="45"/>
-      <c r="AT164" s="45"/>
-      <c r="AU164" s="46"/>
-      <c r="AV164" s="47"/>
+      <c r="B164" s="40"/>
+      <c r="C164" s="41"/>
+      <c r="D164" s="40"/>
+      <c r="E164" s="41"/>
+      <c r="F164" s="40"/>
+      <c r="G164" s="41"/>
+      <c r="H164" s="40"/>
+      <c r="I164" s="41"/>
+      <c r="J164" s="40"/>
+      <c r="K164" s="41"/>
+      <c r="L164" s="40"/>
+      <c r="M164" s="41"/>
+      <c r="N164" s="40"/>
+      <c r="O164" s="41"/>
+      <c r="P164" s="40"/>
+      <c r="Q164" s="41"/>
+      <c r="R164" s="40"/>
+      <c r="S164" s="41"/>
+      <c r="T164" s="40"/>
+      <c r="U164" s="41"/>
+      <c r="V164" s="40"/>
+      <c r="W164" s="41"/>
+      <c r="X164" s="40"/>
+      <c r="Y164" s="41"/>
+      <c r="Z164" s="40"/>
+      <c r="AA164" s="41"/>
+      <c r="AB164" s="40"/>
+      <c r="AC164" s="41"/>
+      <c r="AD164" s="40"/>
+      <c r="AE164" s="41"/>
+      <c r="AF164" s="40"/>
+      <c r="AG164" s="41"/>
+      <c r="AH164" s="40"/>
+      <c r="AI164" s="41"/>
+      <c r="AJ164" s="40"/>
+      <c r="AK164" s="41"/>
+      <c r="AL164" s="40"/>
+      <c r="AM164" s="41"/>
+      <c r="AN164" s="40"/>
+      <c r="AO164" s="41"/>
+      <c r="AP164" s="40"/>
+      <c r="AQ164" s="40"/>
+      <c r="AR164" s="40"/>
+      <c r="AS164" s="40"/>
+      <c r="AT164" s="40"/>
+      <c r="AU164" s="41"/>
+      <c r="AV164" s="42"/>
       <c r="AW164" s="8"/>
       <c r="AX164" s="8"/>
     </row>
@@ -21666,56 +21678,56 @@
       <c r="AX166" s="12"/>
     </row>
     <row r="167" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="44" t="s">
+      <c r="A167" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="B167" s="45"/>
-      <c r="C167" s="46"/>
-      <c r="D167" s="45"/>
-      <c r="E167" s="46"/>
-      <c r="F167" s="45"/>
-      <c r="G167" s="46"/>
-      <c r="H167" s="45"/>
-      <c r="I167" s="46"/>
-      <c r="J167" s="45"/>
-      <c r="K167" s="46"/>
-      <c r="L167" s="45"/>
-      <c r="M167" s="46"/>
-      <c r="N167" s="45"/>
-      <c r="O167" s="46"/>
-      <c r="P167" s="45"/>
-      <c r="Q167" s="46"/>
-      <c r="R167" s="45"/>
-      <c r="S167" s="46"/>
-      <c r="T167" s="45"/>
-      <c r="U167" s="46"/>
-      <c r="V167" s="45"/>
-      <c r="W167" s="46"/>
-      <c r="X167" s="45"/>
-      <c r="Y167" s="46"/>
-      <c r="Z167" s="45"/>
-      <c r="AA167" s="46"/>
-      <c r="AB167" s="45"/>
-      <c r="AC167" s="46"/>
-      <c r="AD167" s="45"/>
-      <c r="AE167" s="46"/>
-      <c r="AF167" s="45"/>
-      <c r="AG167" s="46"/>
-      <c r="AH167" s="45"/>
-      <c r="AI167" s="46"/>
-      <c r="AJ167" s="45"/>
-      <c r="AK167" s="46"/>
-      <c r="AL167" s="45"/>
-      <c r="AM167" s="46"/>
-      <c r="AN167" s="45"/>
-      <c r="AO167" s="46"/>
-      <c r="AP167" s="45"/>
-      <c r="AQ167" s="45"/>
-      <c r="AR167" s="45"/>
-      <c r="AS167" s="45"/>
-      <c r="AT167" s="45"/>
-      <c r="AU167" s="46"/>
-      <c r="AV167" s="47"/>
+      <c r="B167" s="40"/>
+      <c r="C167" s="41"/>
+      <c r="D167" s="40"/>
+      <c r="E167" s="41"/>
+      <c r="F167" s="40"/>
+      <c r="G167" s="41"/>
+      <c r="H167" s="40"/>
+      <c r="I167" s="41"/>
+      <c r="J167" s="40"/>
+      <c r="K167" s="41"/>
+      <c r="L167" s="40"/>
+      <c r="M167" s="41"/>
+      <c r="N167" s="40"/>
+      <c r="O167" s="41"/>
+      <c r="P167" s="40"/>
+      <c r="Q167" s="41"/>
+      <c r="R167" s="40"/>
+      <c r="S167" s="41"/>
+      <c r="T167" s="40"/>
+      <c r="U167" s="41"/>
+      <c r="V167" s="40"/>
+      <c r="W167" s="41"/>
+      <c r="X167" s="40"/>
+      <c r="Y167" s="41"/>
+      <c r="Z167" s="40"/>
+      <c r="AA167" s="41"/>
+      <c r="AB167" s="40"/>
+      <c r="AC167" s="41"/>
+      <c r="AD167" s="40"/>
+      <c r="AE167" s="41"/>
+      <c r="AF167" s="40"/>
+      <c r="AG167" s="41"/>
+      <c r="AH167" s="40"/>
+      <c r="AI167" s="41"/>
+      <c r="AJ167" s="40"/>
+      <c r="AK167" s="41"/>
+      <c r="AL167" s="40"/>
+      <c r="AM167" s="41"/>
+      <c r="AN167" s="40"/>
+      <c r="AO167" s="41"/>
+      <c r="AP167" s="40"/>
+      <c r="AQ167" s="40"/>
+      <c r="AR167" s="40"/>
+      <c r="AS167" s="40"/>
+      <c r="AT167" s="40"/>
+      <c r="AU167" s="41"/>
+      <c r="AV167" s="42"/>
       <c r="AW167" s="8"/>
       <c r="AX167" s="8"/>
     </row>
@@ -21908,56 +21920,56 @@
       <c r="AX169" s="12"/>
     </row>
     <row r="170" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="44" t="s">
+      <c r="A170" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="B170" s="45"/>
-      <c r="C170" s="46"/>
-      <c r="D170" s="45"/>
-      <c r="E170" s="46"/>
-      <c r="F170" s="45"/>
-      <c r="G170" s="46"/>
-      <c r="H170" s="45"/>
-      <c r="I170" s="46"/>
-      <c r="J170" s="45"/>
-      <c r="K170" s="46"/>
-      <c r="L170" s="45"/>
-      <c r="M170" s="46"/>
-      <c r="N170" s="45"/>
-      <c r="O170" s="46"/>
-      <c r="P170" s="45"/>
-      <c r="Q170" s="46"/>
-      <c r="R170" s="45"/>
-      <c r="S170" s="46"/>
-      <c r="T170" s="45"/>
-      <c r="U170" s="46"/>
-      <c r="V170" s="45"/>
-      <c r="W170" s="46"/>
-      <c r="X170" s="45"/>
-      <c r="Y170" s="46"/>
-      <c r="Z170" s="45"/>
-      <c r="AA170" s="46"/>
-      <c r="AB170" s="45"/>
-      <c r="AC170" s="46"/>
-      <c r="AD170" s="45"/>
-      <c r="AE170" s="46"/>
-      <c r="AF170" s="45"/>
-      <c r="AG170" s="46"/>
-      <c r="AH170" s="45"/>
-      <c r="AI170" s="46"/>
-      <c r="AJ170" s="45"/>
-      <c r="AK170" s="46"/>
-      <c r="AL170" s="45"/>
-      <c r="AM170" s="46"/>
-      <c r="AN170" s="45"/>
-      <c r="AO170" s="46"/>
-      <c r="AP170" s="45"/>
-      <c r="AQ170" s="45"/>
-      <c r="AR170" s="45"/>
-      <c r="AS170" s="45"/>
-      <c r="AT170" s="45"/>
-      <c r="AU170" s="46"/>
-      <c r="AV170" s="47"/>
+      <c r="B170" s="40"/>
+      <c r="C170" s="41"/>
+      <c r="D170" s="40"/>
+      <c r="E170" s="41"/>
+      <c r="F170" s="40"/>
+      <c r="G170" s="41"/>
+      <c r="H170" s="40"/>
+      <c r="I170" s="41"/>
+      <c r="J170" s="40"/>
+      <c r="K170" s="41"/>
+      <c r="L170" s="40"/>
+      <c r="M170" s="41"/>
+      <c r="N170" s="40"/>
+      <c r="O170" s="41"/>
+      <c r="P170" s="40"/>
+      <c r="Q170" s="41"/>
+      <c r="R170" s="40"/>
+      <c r="S170" s="41"/>
+      <c r="T170" s="40"/>
+      <c r="U170" s="41"/>
+      <c r="V170" s="40"/>
+      <c r="W170" s="41"/>
+      <c r="X170" s="40"/>
+      <c r="Y170" s="41"/>
+      <c r="Z170" s="40"/>
+      <c r="AA170" s="41"/>
+      <c r="AB170" s="40"/>
+      <c r="AC170" s="41"/>
+      <c r="AD170" s="40"/>
+      <c r="AE170" s="41"/>
+      <c r="AF170" s="40"/>
+      <c r="AG170" s="41"/>
+      <c r="AH170" s="40"/>
+      <c r="AI170" s="41"/>
+      <c r="AJ170" s="40"/>
+      <c r="AK170" s="41"/>
+      <c r="AL170" s="40"/>
+      <c r="AM170" s="41"/>
+      <c r="AN170" s="40"/>
+      <c r="AO170" s="41"/>
+      <c r="AP170" s="40"/>
+      <c r="AQ170" s="40"/>
+      <c r="AR170" s="40"/>
+      <c r="AS170" s="40"/>
+      <c r="AT170" s="40"/>
+      <c r="AU170" s="41"/>
+      <c r="AV170" s="42"/>
       <c r="AW170" s="8"/>
       <c r="AX170" s="8"/>
     </row>
@@ -22150,56 +22162,56 @@
       <c r="AX172" s="12"/>
     </row>
     <row r="173" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="44" t="s">
+      <c r="A173" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="B173" s="45"/>
-      <c r="C173" s="46"/>
-      <c r="D173" s="45"/>
-      <c r="E173" s="46"/>
-      <c r="F173" s="45"/>
-      <c r="G173" s="46"/>
-      <c r="H173" s="45"/>
-      <c r="I173" s="46"/>
-      <c r="J173" s="45"/>
-      <c r="K173" s="46"/>
-      <c r="L173" s="45"/>
-      <c r="M173" s="46"/>
-      <c r="N173" s="45"/>
-      <c r="O173" s="46"/>
-      <c r="P173" s="45"/>
-      <c r="Q173" s="46"/>
-      <c r="R173" s="45"/>
-      <c r="S173" s="46"/>
-      <c r="T173" s="45"/>
-      <c r="U173" s="46"/>
-      <c r="V173" s="45"/>
-      <c r="W173" s="46"/>
-      <c r="X173" s="45"/>
-      <c r="Y173" s="46"/>
-      <c r="Z173" s="45"/>
-      <c r="AA173" s="46"/>
-      <c r="AB173" s="45"/>
-      <c r="AC173" s="46"/>
-      <c r="AD173" s="45"/>
-      <c r="AE173" s="46"/>
-      <c r="AF173" s="45"/>
-      <c r="AG173" s="46"/>
-      <c r="AH173" s="45"/>
-      <c r="AI173" s="46"/>
-      <c r="AJ173" s="45"/>
-      <c r="AK173" s="46"/>
-      <c r="AL173" s="45"/>
-      <c r="AM173" s="46"/>
-      <c r="AN173" s="45"/>
-      <c r="AO173" s="46"/>
-      <c r="AP173" s="45"/>
-      <c r="AQ173" s="45"/>
-      <c r="AR173" s="45"/>
-      <c r="AS173" s="45"/>
-      <c r="AT173" s="45"/>
-      <c r="AU173" s="46"/>
-      <c r="AV173" s="47"/>
+      <c r="B173" s="40"/>
+      <c r="C173" s="41"/>
+      <c r="D173" s="40"/>
+      <c r="E173" s="41"/>
+      <c r="F173" s="40"/>
+      <c r="G173" s="41"/>
+      <c r="H173" s="40"/>
+      <c r="I173" s="41"/>
+      <c r="J173" s="40"/>
+      <c r="K173" s="41"/>
+      <c r="L173" s="40"/>
+      <c r="M173" s="41"/>
+      <c r="N173" s="40"/>
+      <c r="O173" s="41"/>
+      <c r="P173" s="40"/>
+      <c r="Q173" s="41"/>
+      <c r="R173" s="40"/>
+      <c r="S173" s="41"/>
+      <c r="T173" s="40"/>
+      <c r="U173" s="41"/>
+      <c r="V173" s="40"/>
+      <c r="W173" s="41"/>
+      <c r="X173" s="40"/>
+      <c r="Y173" s="41"/>
+      <c r="Z173" s="40"/>
+      <c r="AA173" s="41"/>
+      <c r="AB173" s="40"/>
+      <c r="AC173" s="41"/>
+      <c r="AD173" s="40"/>
+      <c r="AE173" s="41"/>
+      <c r="AF173" s="40"/>
+      <c r="AG173" s="41"/>
+      <c r="AH173" s="40"/>
+      <c r="AI173" s="41"/>
+      <c r="AJ173" s="40"/>
+      <c r="AK173" s="41"/>
+      <c r="AL173" s="40"/>
+      <c r="AM173" s="41"/>
+      <c r="AN173" s="40"/>
+      <c r="AO173" s="41"/>
+      <c r="AP173" s="40"/>
+      <c r="AQ173" s="40"/>
+      <c r="AR173" s="40"/>
+      <c r="AS173" s="40"/>
+      <c r="AT173" s="40"/>
+      <c r="AU173" s="41"/>
+      <c r="AV173" s="42"/>
       <c r="AW173" s="8"/>
       <c r="AX173" s="8"/>
     </row>
@@ -22453,107 +22465,107 @@
       <c r="A177" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="B177" s="49"/>
-      <c r="C177" s="50"/>
-      <c r="D177" s="49"/>
-      <c r="E177" s="50"/>
-      <c r="F177" s="49"/>
-      <c r="G177" s="50"/>
-      <c r="H177" s="49"/>
-      <c r="I177" s="50"/>
-      <c r="J177" s="49"/>
-      <c r="K177" s="50"/>
-      <c r="L177" s="49"/>
-      <c r="M177" s="50"/>
-      <c r="N177" s="49"/>
-      <c r="O177" s="50"/>
-      <c r="P177" s="49"/>
-      <c r="Q177" s="50"/>
-      <c r="R177" s="49"/>
-      <c r="S177" s="50"/>
-      <c r="T177" s="49"/>
-      <c r="U177" s="50"/>
-      <c r="V177" s="49"/>
-      <c r="W177" s="50"/>
-      <c r="X177" s="49"/>
-      <c r="Y177" s="50"/>
-      <c r="Z177" s="49"/>
-      <c r="AA177" s="50"/>
-      <c r="AB177" s="49"/>
-      <c r="AC177" s="50"/>
-      <c r="AD177" s="49"/>
-      <c r="AE177" s="50"/>
-      <c r="AF177" s="49"/>
-      <c r="AG177" s="50"/>
-      <c r="AH177" s="49"/>
-      <c r="AI177" s="50"/>
-      <c r="AJ177" s="49"/>
-      <c r="AK177" s="50"/>
-      <c r="AL177" s="49"/>
-      <c r="AM177" s="50"/>
-      <c r="AN177" s="49"/>
-      <c r="AO177" s="50"/>
-      <c r="AP177" s="49"/>
-      <c r="AQ177" s="49"/>
-      <c r="AR177" s="49"/>
-      <c r="AS177" s="49"/>
-      <c r="AT177" s="49"/>
-      <c r="AU177" s="50"/>
-      <c r="AV177" s="43"/>
+      <c r="B177" s="53"/>
+      <c r="C177" s="54"/>
+      <c r="D177" s="53"/>
+      <c r="E177" s="54"/>
+      <c r="F177" s="53"/>
+      <c r="G177" s="54"/>
+      <c r="H177" s="53"/>
+      <c r="I177" s="54"/>
+      <c r="J177" s="53"/>
+      <c r="K177" s="54"/>
+      <c r="L177" s="53"/>
+      <c r="M177" s="54"/>
+      <c r="N177" s="53"/>
+      <c r="O177" s="54"/>
+      <c r="P177" s="53"/>
+      <c r="Q177" s="54"/>
+      <c r="R177" s="53"/>
+      <c r="S177" s="54"/>
+      <c r="T177" s="53"/>
+      <c r="U177" s="54"/>
+      <c r="V177" s="53"/>
+      <c r="W177" s="54"/>
+      <c r="X177" s="53"/>
+      <c r="Y177" s="54"/>
+      <c r="Z177" s="53"/>
+      <c r="AA177" s="54"/>
+      <c r="AB177" s="53"/>
+      <c r="AC177" s="54"/>
+      <c r="AD177" s="53"/>
+      <c r="AE177" s="54"/>
+      <c r="AF177" s="53"/>
+      <c r="AG177" s="54"/>
+      <c r="AH177" s="53"/>
+      <c r="AI177" s="54"/>
+      <c r="AJ177" s="53"/>
+      <c r="AK177" s="54"/>
+      <c r="AL177" s="53"/>
+      <c r="AM177" s="54"/>
+      <c r="AN177" s="53"/>
+      <c r="AO177" s="54"/>
+      <c r="AP177" s="53"/>
+      <c r="AQ177" s="53"/>
+      <c r="AR177" s="53"/>
+      <c r="AS177" s="53"/>
+      <c r="AT177" s="53"/>
+      <c r="AU177" s="54"/>
+      <c r="AV177" s="47"/>
       <c r="AW177" s="7"/>
       <c r="AX177" s="7"/>
     </row>
     <row r="178" spans="1:50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="44" t="s">
+      <c r="A178" s="39" t="s">
         <v>201</v>
       </c>
-      <c r="B178" s="45"/>
-      <c r="C178" s="46"/>
-      <c r="D178" s="45"/>
-     